--- a/xlsdir/配置-总表.xlsx
+++ b/xlsdir/配置-总表.xlsx
@@ -4,24 +4,25 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27930" windowHeight="12525" tabRatio="673"/>
+    <workbookView windowWidth="27930" windowHeight="12975" tabRatio="673" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="hero|玩家角色" sheetId="27" r:id="rId1"/>
     <sheet name="card|卡牌" sheetId="29" r:id="rId2"/>
     <sheet name="monster|魔物" sheetId="28" r:id="rId3"/>
-    <sheet name="Sheet3" sheetId="30" r:id="rId4"/>
-    <sheet name="Sheet1" sheetId="11" state="hidden" r:id="rId5"/>
+    <sheet name="combat|战斗" sheetId="31" r:id="rId4"/>
+    <sheet name="Sheet3" sheetId="30" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="11" state="hidden" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'monster|魔物'!$A$1:$R$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'monster|魔物'!$A$1:$O$16</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="274">
   <si>
     <t>ID</t>
   </si>
@@ -139,13 +140,7 @@
     <t>attack_points</t>
   </si>
   <si>
-    <t>defense_points</t>
-  </si>
-  <si>
-    <t>speed</t>
-  </si>
-  <si>
-    <t>tags</t>
+    <t>entityID</t>
   </si>
   <si>
     <t>怪物名</t>
@@ -163,49 +158,43 @@
     <t>攻击力</t>
   </si>
   <si>
-    <t>防御力</t>
-  </si>
-  <si>
-    <t>速度</t>
-  </si>
-  <si>
-    <t>标签</t>
-  </si>
-  <si>
-    <t>Goblin</t>
+    <t>实体名</t>
+  </si>
+  <si>
+    <t>slime</t>
+  </si>
+  <si>
+    <t>史莱姆</t>
   </si>
   <si>
     <t>一个矮小而丑陋的怪物，生活在森林深处。</t>
   </si>
   <si>
-    <t>森林*小怪*低级</t>
-  </si>
-  <si>
-    <t>Orc</t>
-  </si>
-  <si>
-    <t>一个高大而强壮的怪物，经常在草原上活动。</t>
-  </si>
-  <si>
-    <t>草原*小怪*中级</t>
-  </si>
-  <si>
-    <t>Troll</t>
-  </si>
-  <si>
-    <t>一个极其强壮的怪物，生活在山区和洞穴中。</t>
-  </si>
-  <si>
-    <t>山区*洞穴*高级</t>
-  </si>
-  <si>
-    <t>Dragon</t>
-  </si>
-  <si>
-    <t>一只传说中的龙，无人能够抵挡其猛烈的攻击。</t>
-  </si>
-  <si>
-    <t>龙*中级</t>
+    <t>character_slime</t>
+  </si>
+  <si>
+    <t>mark_01</t>
+  </si>
+  <si>
+    <t>mark_02</t>
+  </si>
+  <si>
+    <t>mark_03</t>
+  </si>
+  <si>
+    <t>战斗名</t>
+  </si>
+  <si>
+    <t>位置1</t>
+  </si>
+  <si>
+    <t>位置2</t>
+  </si>
+  <si>
+    <t>位置3</t>
+  </si>
+  <si>
+    <t>测试用</t>
   </si>
   <si>
     <t>MAX_HP</t>
@@ -656,6 +645,9 @@
   </si>
   <si>
     <t>鳍</t>
+  </si>
+  <si>
+    <t>速度</t>
   </si>
   <si>
     <t>企业家</t>
@@ -1133,18 +1125,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799951170384838"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1339,7 +1325,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="56">
+  <borders count="55">
     <border>
       <left/>
       <right/>
@@ -1738,17 +1724,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color auto="1"/>
       </left>
@@ -1818,6 +1793,19 @@
     <border>
       <left/>
       <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
       <top style="medium">
         <color auto="1"/>
       </top>
@@ -1876,7 +1864,7 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right style="thin">
+      <right style="medium">
         <color auto="1"/>
       </right>
       <top style="thin">
@@ -1890,21 +1878,6 @@
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
       <top style="thin">
         <color auto="1"/>
       </top>
@@ -1912,7 +1885,9 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
       <right style="thin">
         <color auto="1"/>
       </right>
@@ -2068,7 +2043,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="48" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="47" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2080,119 +2055,119 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="49" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="49" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="50" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="48" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="48" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="49" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="51" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="52" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="51" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="53" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="54" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="55" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="50" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="51" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="50" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="52" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="53" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="54" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="129">
+  <cellXfs count="120">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2298,7 +2273,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
@@ -2307,13 +2285,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="26" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="26" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1">
@@ -2325,19 +2297,82 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="34" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="35" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="37" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1">
@@ -2346,238 +2381,151 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="31" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="38" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="39" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="40" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="41" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="42" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="43" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="34" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="35" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="36" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="37" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="28" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="30" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="38" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="39" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="40" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="41" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="42" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="35" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="36" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="37" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="32" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="33" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="34" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="31" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="32" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="33" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="22" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="25" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="44" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="45" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="43" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="44" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="45" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="46" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="43" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="21" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="22" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="47" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="46" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1" quotePrefix="1">
@@ -2934,51 +2882,52 @@
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultColWidth="8.85833333333333" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="8.33333333333333" style="41" customWidth="1"/>
+    <col min="1" max="1" width="8.33333333333333" style="40" customWidth="1"/>
     <col min="2" max="2" width="11.8916666666667" customWidth="1"/>
     <col min="3" max="3" width="8.33333333333333" customWidth="1"/>
     <col min="4" max="4" width="20.6666666666667" customWidth="1" outlineLevel="1"/>
+    <col min="5" max="5" width="31.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="120" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="120" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="120" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="126" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="127"/>
-      <c r="G1" s="127"/>
-    </row>
-    <row r="2" s="125" customFormat="1" ht="27" spans="1:7">
-      <c r="A2" s="121" t="s">
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+    </row>
+    <row r="2" s="119" customFormat="1" ht="27" spans="1:7">
+      <c r="A2" s="118" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="122" t="s">
+      <c r="B2" s="118" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="122" t="s">
+      <c r="C2" s="118" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="122" t="s">
+      <c r="D2" s="118" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="122" t="s">
+      <c r="E2" s="118" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="128" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" s="128" t="s">
+      <c r="F2" s="118" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="118" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2989,42 +2938,42 @@
       <c r="B3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="120" t="s">
+      <c r="C3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="120" t="s">
+      <c r="D3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="120" t="s">
+      <c r="E3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="21" t="s">
+      <c r="F3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="127" t="s">
+      <c r="G3" s="4" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="35">
+      <c r="A4" s="10">
         <v>1</v>
       </c>
-      <c r="B4" s="35" t="s">
+      <c r="B4" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="35">
+      <c r="C4" s="10">
         <v>80</v>
       </c>
-      <c r="D4" s="35" t="s">
+      <c r="D4" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="35" t="s">
+      <c r="E4" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="10">
         <v>99</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="10" t="s">
         <v>18</v>
       </c>
     </row>
@@ -3048,27 +2997,27 @@
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="120" t="s">
+      <c r="B1" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="120" t="s">
+      <c r="C1" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D1" s="120" t="s">
+      <c r="D1" s="4" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="2" ht="40.5" spans="1:4">
-      <c r="A2" s="121" t="s">
+      <c r="A2" s="118" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="122" t="s">
+      <c r="B2" s="118" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="123" t="s">
+      <c r="C2" s="118" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="120" t="s">
+      <c r="D2" s="4" t="s">
         <v>24</v>
       </c>
     </row>
@@ -3079,52 +3028,52 @@
       <c r="B3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="120" t="s">
+      <c r="C3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="120" t="s">
+      <c r="D3" s="4" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="35" t="s">
+      <c r="A4" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="B4" s="124" t="s">
+      <c r="B4" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="C4" s="35">
+      <c r="C4" s="10">
         <v>1</v>
       </c>
-      <c r="D4" s="35" t="s">
+      <c r="D4" s="10" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="35" t="s">
+      <c r="A5" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="124" t="s">
+      <c r="B5" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="C5" s="35">
+      <c r="C5" s="10">
         <v>2</v>
       </c>
-      <c r="D5" s="35" t="s">
+      <c r="D5" s="10" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="35" t="s">
+      <c r="A6" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="124" t="s">
+      <c r="B6" s="35" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="35">
+      <c r="C6" s="10">
         <v>1</v>
       </c>
-      <c r="D6" s="35" t="s">
+      <c r="D6" s="10" t="s">
         <v>33</v>
       </c>
     </row>
@@ -3137,510 +3086,343 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R19"/>
+  <dimension ref="A1:O16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="7.66666666666667" customWidth="1"/>
     <col min="2" max="2" width="11.4666666666667" style="21" customWidth="1"/>
     <col min="3" max="3" width="30.1333333333333" customWidth="1"/>
-    <col min="4" max="4" width="11.4666666666667" style="21" customWidth="1"/>
+    <col min="4" max="4" width="7" style="21" customWidth="1"/>
     <col min="5" max="5" width="15.225" customWidth="1"/>
-    <col min="6" max="6" width="15.225" style="41" customWidth="1" outlineLevel="1"/>
-    <col min="7" max="8" width="8" customWidth="1" outlineLevel="1"/>
-    <col min="9" max="9" width="16.4416666666667" customWidth="1" outlineLevel="1"/>
-    <col min="10" max="10" width="8" style="42" customWidth="1" outlineLevel="1"/>
-    <col min="13" max="13" width="9" style="42"/>
-    <col min="14" max="14" width="7.26666666666667" style="43" customWidth="1"/>
-    <col min="18" max="18" width="6.4" customWidth="1"/>
+    <col min="6" max="6" width="15.225" style="40" customWidth="1" outlineLevel="1"/>
+    <col min="7" max="7" width="17.125" style="41" customWidth="1" outlineLevel="1"/>
+    <col min="10" max="10" width="9" style="41"/>
+    <col min="11" max="11" width="7.26666666666667" style="42" customWidth="1"/>
+    <col min="15" max="15" width="6.4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
-      <c r="A1" s="44" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="45" t="s">
+    <row r="1" spans="1:15">
+      <c r="A1" s="43" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="44" t="s">
         <v>34</v>
       </c>
-      <c r="C1" s="46" t="s">
+      <c r="C1" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="D1" s="47" t="s">
+      <c r="D1" s="45" t="s">
         <v>35</v>
       </c>
-      <c r="E1" s="47" t="s">
+      <c r="E1" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F1" s="48" t="s">
+      <c r="F1" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="H1" s="46"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="26"/>
+      <c r="K1" s="97"/>
+      <c r="L1" s="52"/>
+      <c r="M1" s="4"/>
+      <c r="N1" s="26"/>
+      <c r="O1" s="41"/>
+    </row>
+    <row r="2" spans="1:15">
+      <c r="A2" s="43" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="44" t="s">
         <v>39</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="C2" s="44" t="s">
         <v>40</v>
       </c>
-      <c r="J1" s="26"/>
-      <c r="K1" s="90"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="26"/>
-      <c r="N1" s="91"/>
-      <c r="O1" s="48"/>
-      <c r="P1" s="4"/>
-      <c r="Q1" s="26"/>
-      <c r="R1" s="42"/>
-    </row>
-    <row r="2" spans="1:18">
-      <c r="A2" s="44" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="45" t="s">
+      <c r="D2" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="C2" s="46" t="s">
+      <c r="E2" s="45" t="s">
         <v>42</v>
       </c>
-      <c r="D2" s="47" t="s">
+      <c r="F2" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="E2" s="47" t="s">
+      <c r="G2" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="F2" s="48" t="s">
+      <c r="H2" s="46"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="26"/>
+      <c r="K2" s="97"/>
+      <c r="L2" s="52"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="26"/>
+      <c r="O2" s="41"/>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="44" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="44" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="45" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="45" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" s="46"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="26"/>
+      <c r="K3" s="97"/>
+      <c r="L3" s="52"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="26"/>
+      <c r="O3" s="41"/>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="47" t="s">
         <v>45</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="B4" s="48" t="s">
         <v>46</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="C4" s="48" t="s">
         <v>47</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="D4" s="49">
+        <v>3</v>
+      </c>
+      <c r="E4" s="49">
+        <v>50</v>
+      </c>
+      <c r="F4" s="50">
+        <v>10</v>
+      </c>
+      <c r="G4" s="51" t="s">
         <v>48</v>
       </c>
-      <c r="J2" s="26"/>
-      <c r="K2" s="90"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="26"/>
-      <c r="N2" s="91"/>
-      <c r="O2" s="48"/>
-      <c r="P2" s="4"/>
-      <c r="Q2" s="26"/>
-      <c r="R2" s="42"/>
-    </row>
-    <row r="3" spans="1:18">
-      <c r="A3" s="44" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="45" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="47" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="47" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="48" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="H3" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="I3" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="J3" s="26"/>
-      <c r="K3" s="90"/>
-      <c r="L3" s="10"/>
-      <c r="M3" s="26"/>
-      <c r="N3" s="91"/>
-      <c r="O3" s="48"/>
-      <c r="P3" s="4"/>
-      <c r="Q3" s="26"/>
-      <c r="R3" s="42"/>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" s="44">
-        <v>1001</v>
-      </c>
-      <c r="B4" s="45" t="s">
-        <v>49</v>
-      </c>
-      <c r="C4" s="46" t="s">
-        <v>50</v>
-      </c>
-      <c r="D4" s="47">
-        <v>3</v>
-      </c>
-      <c r="E4" s="47">
-        <v>50</v>
-      </c>
-      <c r="F4" s="48">
-        <v>10</v>
-      </c>
-      <c r="G4" s="10">
-        <v>5</v>
-      </c>
-      <c r="H4" s="10">
-        <v>20</v>
-      </c>
-      <c r="I4" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="J4" s="91"/>
-      <c r="K4" s="48"/>
-      <c r="L4" s="4"/>
-      <c r="M4" s="26"/>
-      <c r="N4" s="42"/>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" s="44">
-        <v>1002</v>
-      </c>
-      <c r="B5" s="45" t="s">
-        <v>52</v>
-      </c>
-      <c r="C5" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="D5" s="47">
-        <v>5</v>
-      </c>
-      <c r="E5" s="47">
-        <v>100</v>
-      </c>
-      <c r="F5" s="48">
-        <v>20</v>
-      </c>
-      <c r="G5" s="10">
-        <v>10</v>
-      </c>
-      <c r="H5" s="10">
-        <v>30</v>
-      </c>
-      <c r="I5" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="J5" s="91"/>
-      <c r="K5" s="48"/>
-      <c r="L5" s="4"/>
-      <c r="M5" s="26"/>
-      <c r="N5" s="42"/>
+      <c r="H4" s="52"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="26"/>
+      <c r="K4" s="41"/>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="A5" s="53"/>
+      <c r="B5" s="44"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="55"/>
+      <c r="E5" s="55"/>
+      <c r="F5" s="52"/>
+      <c r="G5" s="26"/>
+      <c r="H5" s="46"/>
+      <c r="I5" s="10"/>
+      <c r="J5" s="26"/>
+      <c r="K5" s="97"/>
+      <c r="L5" s="52"/>
+      <c r="M5" s="4"/>
+      <c r="N5" s="26"/>
+      <c r="O5" s="41"/>
     </row>
     <row r="6" spans="1:14">
-      <c r="A6" s="44">
-        <v>1003</v>
-      </c>
-      <c r="B6" s="45" t="s">
-        <v>55</v>
-      </c>
-      <c r="C6" s="46" t="s">
-        <v>56</v>
-      </c>
-      <c r="D6" s="47">
-        <v>8</v>
-      </c>
-      <c r="E6" s="47">
-        <v>200</v>
-      </c>
-      <c r="F6" s="48">
-        <v>40</v>
-      </c>
-      <c r="G6" s="10">
-        <v>20</v>
-      </c>
-      <c r="H6" s="10">
-        <v>40</v>
-      </c>
-      <c r="I6" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="J6" s="48"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="26"/>
-      <c r="N6"/>
-    </row>
-    <row r="7" s="36" customFormat="1" spans="1:14">
-      <c r="A7" s="49">
-        <v>1004</v>
-      </c>
-      <c r="B7" s="50" t="s">
-        <v>58</v>
-      </c>
-      <c r="C7" s="51" t="s">
-        <v>59</v>
-      </c>
-      <c r="D7" s="52">
-        <v>20</v>
-      </c>
-      <c r="E7" s="52">
-        <v>1000</v>
-      </c>
-      <c r="F7" s="53">
-        <v>100</v>
-      </c>
-      <c r="G7" s="54">
-        <v>50</v>
-      </c>
-      <c r="H7" s="54">
-        <v>80</v>
-      </c>
-      <c r="I7" s="54" t="s">
-        <v>60</v>
-      </c>
-      <c r="J7" s="92"/>
-      <c r="K7" s="48"/>
-      <c r="L7" s="4"/>
-      <c r="M7" s="17"/>
-      <c r="N7" s="93"/>
-    </row>
-    <row r="8" spans="1:18">
-      <c r="A8" s="44"/>
-      <c r="B8" s="45"/>
-      <c r="C8" s="46"/>
-      <c r="D8" s="47"/>
-      <c r="E8" s="47"/>
-      <c r="F8" s="48"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
+      <c r="A6" s="53"/>
+      <c r="B6" s="44"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="55"/>
+      <c r="E6" s="55"/>
+      <c r="F6" s="52"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="46"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="26"/>
+      <c r="K6" s="97"/>
+      <c r="L6" s="52"/>
+      <c r="M6" s="4"/>
+      <c r="N6" s="26"/>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7" s="53"/>
+      <c r="B7" s="44"/>
+      <c r="C7" s="54"/>
+      <c r="D7" s="55"/>
+      <c r="E7" s="55"/>
+      <c r="F7" s="52"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="46"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="26"/>
+      <c r="K7" s="97"/>
+      <c r="L7" s="52"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="26"/>
+      <c r="O7" s="41"/>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8" s="53"/>
+      <c r="B8" s="44"/>
+      <c r="C8" s="54"/>
+      <c r="D8" s="55"/>
+      <c r="E8" s="55"/>
+      <c r="F8" s="52"/>
+      <c r="G8" s="26"/>
+      <c r="H8" s="46"/>
       <c r="I8" s="10"/>
       <c r="J8" s="26"/>
-      <c r="K8" s="90"/>
-      <c r="L8" s="10"/>
-      <c r="M8" s="26"/>
-      <c r="N8" s="91"/>
-      <c r="O8" s="48"/>
-      <c r="P8" s="4"/>
-      <c r="Q8" s="26"/>
-      <c r="R8" s="42"/>
-    </row>
-    <row r="9" spans="1:17">
-      <c r="A9" s="44"/>
-      <c r="B9" s="45"/>
-      <c r="C9" s="46"/>
-      <c r="D9" s="47"/>
-      <c r="E9" s="47"/>
-      <c r="F9" s="48"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
+      <c r="K8" s="97"/>
+      <c r="L8" s="52"/>
+      <c r="M8" s="4"/>
+      <c r="N8" s="26"/>
+      <c r="O8" s="41"/>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9" s="53"/>
+      <c r="B9" s="44"/>
+      <c r="C9" s="54"/>
+      <c r="D9" s="55"/>
+      <c r="E9" s="55"/>
+      <c r="F9" s="52"/>
+      <c r="G9" s="26"/>
+      <c r="H9" s="46"/>
       <c r="I9" s="10"/>
       <c r="J9" s="26"/>
-      <c r="K9" s="90"/>
-      <c r="L9" s="10"/>
-      <c r="M9" s="26"/>
-      <c r="N9" s="91"/>
-      <c r="O9" s="48"/>
-      <c r="P9" s="4"/>
-      <c r="Q9" s="26"/>
-    </row>
-    <row r="10" spans="1:18">
-      <c r="A10" s="44"/>
-      <c r="B10" s="45"/>
-      <c r="C10" s="46"/>
-      <c r="D10" s="47"/>
-      <c r="E10" s="47"/>
-      <c r="F10" s="48"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
+      <c r="K9" s="97"/>
+      <c r="L9" s="52"/>
+      <c r="M9" s="4"/>
+      <c r="N9" s="26"/>
+      <c r="O9" s="41"/>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="A10" s="53"/>
+      <c r="B10" s="44"/>
+      <c r="C10" s="54"/>
+      <c r="D10" s="55"/>
+      <c r="E10" s="55"/>
+      <c r="F10" s="52"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="46"/>
       <c r="I10" s="10"/>
       <c r="J10" s="26"/>
-      <c r="K10" s="90"/>
-      <c r="L10" s="10"/>
-      <c r="M10" s="26"/>
-      <c r="N10" s="91"/>
-      <c r="O10" s="48"/>
-      <c r="P10" s="4"/>
-      <c r="Q10" s="26"/>
-      <c r="R10" s="42"/>
-    </row>
-    <row r="11" spans="1:18">
-      <c r="A11" s="44"/>
-      <c r="B11" s="45"/>
-      <c r="C11" s="46"/>
-      <c r="D11" s="47"/>
-      <c r="E11" s="47"/>
-      <c r="F11" s="48"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="26"/>
-      <c r="K11" s="90"/>
-      <c r="L11" s="10"/>
-      <c r="M11" s="26"/>
-      <c r="N11" s="91"/>
-      <c r="O11" s="48"/>
-      <c r="P11" s="4"/>
-      <c r="Q11" s="26"/>
-      <c r="R11" s="42"/>
-    </row>
-    <row r="12" spans="1:18">
-      <c r="A12" s="44"/>
-      <c r="B12" s="45"/>
-      <c r="C12" s="46"/>
-      <c r="D12" s="47"/>
-      <c r="E12" s="47"/>
-      <c r="F12" s="48"/>
-      <c r="G12" s="10"/>
-      <c r="H12" s="10"/>
-      <c r="I12" s="10"/>
-      <c r="J12" s="26"/>
-      <c r="K12" s="90"/>
-      <c r="L12" s="10"/>
-      <c r="M12" s="26"/>
-      <c r="N12" s="91"/>
-      <c r="O12" s="48"/>
-      <c r="P12" s="4"/>
-      <c r="Q12" s="26"/>
-      <c r="R12" s="42"/>
-    </row>
-    <row r="13" spans="1:18">
-      <c r="A13" s="44"/>
-      <c r="B13" s="45"/>
-      <c r="C13" s="46"/>
-      <c r="D13" s="47"/>
-      <c r="E13" s="47"/>
-      <c r="F13" s="48"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10"/>
-      <c r="I13" s="10"/>
-      <c r="J13" s="26"/>
-      <c r="K13" s="90"/>
-      <c r="L13" s="10"/>
-      <c r="M13" s="26"/>
-      <c r="N13" s="91"/>
-      <c r="O13" s="48"/>
-      <c r="P13" s="4"/>
-      <c r="Q13" s="26"/>
-      <c r="R13" s="42"/>
-    </row>
-    <row r="14" ht="14.25" spans="1:18">
-      <c r="A14" s="55"/>
-      <c r="B14" s="56"/>
-      <c r="C14" s="57"/>
-      <c r="D14" s="58"/>
-      <c r="E14" s="58"/>
-      <c r="F14" s="59"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="12"/>
-      <c r="J14" s="29"/>
-      <c r="K14" s="94"/>
-      <c r="L14" s="12"/>
-      <c r="M14" s="29"/>
-      <c r="N14" s="95"/>
-      <c r="O14" s="48"/>
-      <c r="P14" s="4"/>
-      <c r="Q14" s="26"/>
-      <c r="R14" s="42"/>
-    </row>
-    <row r="15" s="37" customFormat="1" spans="1:18">
-      <c r="A15" s="60"/>
-      <c r="B15" s="61"/>
-      <c r="C15" s="62"/>
-      <c r="D15" s="63"/>
-      <c r="E15" s="63"/>
-      <c r="F15" s="64"/>
-      <c r="G15" s="65"/>
-      <c r="H15" s="65"/>
-      <c r="I15" s="65"/>
-      <c r="J15" s="96"/>
-      <c r="K15" s="97"/>
-      <c r="L15" s="65"/>
-      <c r="M15" s="96"/>
-      <c r="N15" s="98"/>
-      <c r="O15" s="70"/>
-      <c r="P15" s="99"/>
-      <c r="Q15" s="100"/>
-      <c r="R15" s="115"/>
-    </row>
-    <row r="16" s="38" customFormat="1" spans="1:18">
-      <c r="A16" s="66"/>
-      <c r="B16" s="67"/>
-      <c r="C16" s="68"/>
-      <c r="D16" s="69"/>
-      <c r="E16" s="69"/>
-      <c r="F16" s="70"/>
-      <c r="G16" s="71"/>
-      <c r="H16" s="71"/>
-      <c r="I16" s="71"/>
-      <c r="J16" s="100"/>
-      <c r="K16" s="101"/>
-      <c r="L16" s="71"/>
-      <c r="M16" s="100"/>
-      <c r="N16" s="102"/>
-      <c r="O16" s="70"/>
-      <c r="P16" s="99"/>
-      <c r="Q16" s="100"/>
-      <c r="R16" s="116"/>
-    </row>
-    <row r="17" s="38" customFormat="1" ht="14.25" spans="1:18">
-      <c r="A17" s="72"/>
-      <c r="B17" s="73"/>
-      <c r="C17" s="74"/>
-      <c r="D17" s="75"/>
-      <c r="E17" s="75"/>
-      <c r="F17" s="76"/>
-      <c r="G17" s="77"/>
-      <c r="H17" s="77"/>
-      <c r="I17" s="77"/>
-      <c r="J17" s="103"/>
-      <c r="K17" s="104"/>
-      <c r="L17" s="77"/>
-      <c r="M17" s="103"/>
-      <c r="N17" s="105"/>
-      <c r="O17" s="70"/>
-      <c r="P17" s="99"/>
-      <c r="Q17" s="100"/>
-      <c r="R17" s="116"/>
-    </row>
-    <row r="18" s="39" customFormat="1" spans="1:18">
-      <c r="A18" s="78"/>
-      <c r="B18" s="79"/>
-      <c r="C18" s="80"/>
-      <c r="D18" s="81"/>
-      <c r="E18" s="81"/>
-      <c r="F18" s="82"/>
-      <c r="G18" s="83"/>
-      <c r="H18" s="83"/>
-      <c r="I18" s="83"/>
-      <c r="J18" s="106"/>
-      <c r="K18" s="107"/>
-      <c r="L18" s="83"/>
-      <c r="M18" s="106"/>
-      <c r="N18" s="108"/>
-      <c r="O18" s="109"/>
-      <c r="P18" s="110"/>
-      <c r="Q18" s="117"/>
-      <c r="R18" s="118"/>
-    </row>
-    <row r="19" s="40" customFormat="1" ht="14.25" spans="1:18">
-      <c r="A19" s="84"/>
-      <c r="B19" s="85"/>
-      <c r="C19" s="86"/>
-      <c r="D19" s="87"/>
-      <c r="E19" s="87"/>
-      <c r="F19" s="88"/>
-      <c r="G19" s="89"/>
-      <c r="H19" s="89"/>
-      <c r="I19" s="89"/>
-      <c r="J19" s="111"/>
-      <c r="K19" s="112"/>
-      <c r="L19" s="89"/>
-      <c r="M19" s="111"/>
-      <c r="N19" s="113"/>
-      <c r="O19" s="88"/>
-      <c r="P19" s="114"/>
-      <c r="Q19" s="111"/>
-      <c r="R19" s="119"/>
+      <c r="K10" s="97"/>
+      <c r="L10" s="52"/>
+      <c r="M10" s="4"/>
+      <c r="N10" s="26"/>
+      <c r="O10" s="41"/>
+    </row>
+    <row r="11" ht="14.25" spans="1:15">
+      <c r="A11" s="56"/>
+      <c r="B11" s="57"/>
+      <c r="C11" s="58"/>
+      <c r="D11" s="59"/>
+      <c r="E11" s="59"/>
+      <c r="F11" s="60"/>
+      <c r="G11" s="29"/>
+      <c r="H11" s="61"/>
+      <c r="I11" s="12"/>
+      <c r="J11" s="29"/>
+      <c r="K11" s="98"/>
+      <c r="L11" s="52"/>
+      <c r="M11" s="4"/>
+      <c r="N11" s="26"/>
+      <c r="O11" s="41"/>
+    </row>
+    <row r="12" s="36" customFormat="1" spans="1:15">
+      <c r="A12" s="62"/>
+      <c r="B12" s="63"/>
+      <c r="C12" s="64"/>
+      <c r="D12" s="65"/>
+      <c r="E12" s="65"/>
+      <c r="F12" s="66"/>
+      <c r="G12" s="67"/>
+      <c r="H12" s="68"/>
+      <c r="I12" s="99"/>
+      <c r="J12" s="67"/>
+      <c r="K12" s="100"/>
+      <c r="L12" s="73"/>
+      <c r="M12" s="101"/>
+      <c r="N12" s="74"/>
+      <c r="O12" s="102"/>
+    </row>
+    <row r="13" s="37" customFormat="1" spans="1:15">
+      <c r="A13" s="69"/>
+      <c r="B13" s="70"/>
+      <c r="C13" s="71"/>
+      <c r="D13" s="72"/>
+      <c r="E13" s="72"/>
+      <c r="F13" s="73"/>
+      <c r="G13" s="74"/>
+      <c r="H13" s="75"/>
+      <c r="I13" s="103"/>
+      <c r="J13" s="74"/>
+      <c r="K13" s="104"/>
+      <c r="L13" s="73"/>
+      <c r="M13" s="101"/>
+      <c r="N13" s="74"/>
+      <c r="O13" s="105"/>
+    </row>
+    <row r="14" s="37" customFormat="1" ht="14.25" spans="1:15">
+      <c r="A14" s="76"/>
+      <c r="B14" s="77"/>
+      <c r="C14" s="78"/>
+      <c r="D14" s="79"/>
+      <c r="E14" s="79"/>
+      <c r="F14" s="80"/>
+      <c r="G14" s="81"/>
+      <c r="H14" s="82"/>
+      <c r="I14" s="106"/>
+      <c r="J14" s="81"/>
+      <c r="K14" s="107"/>
+      <c r="L14" s="73"/>
+      <c r="M14" s="101"/>
+      <c r="N14" s="74"/>
+      <c r="O14" s="105"/>
+    </row>
+    <row r="15" s="38" customFormat="1" spans="1:15">
+      <c r="A15" s="83"/>
+      <c r="B15" s="84"/>
+      <c r="C15" s="85"/>
+      <c r="D15" s="86"/>
+      <c r="E15" s="86"/>
+      <c r="F15" s="87"/>
+      <c r="G15" s="88"/>
+      <c r="H15" s="89"/>
+      <c r="I15" s="108"/>
+      <c r="J15" s="88"/>
+      <c r="K15" s="109"/>
+      <c r="L15" s="110"/>
+      <c r="M15" s="111"/>
+      <c r="N15" s="112"/>
+      <c r="O15" s="113"/>
+    </row>
+    <row r="16" s="39" customFormat="1" ht="14.25" spans="1:15">
+      <c r="A16" s="90"/>
+      <c r="B16" s="91"/>
+      <c r="C16" s="92"/>
+      <c r="D16" s="93"/>
+      <c r="E16" s="93"/>
+      <c r="F16" s="94"/>
+      <c r="G16" s="95"/>
+      <c r="H16" s="96"/>
+      <c r="I16" s="114"/>
+      <c r="J16" s="95"/>
+      <c r="K16" s="115"/>
+      <c r="L16" s="94"/>
+      <c r="M16" s="116"/>
+      <c r="N16" s="95"/>
+      <c r="O16" s="117"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3652,51 +3434,73 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C7:F9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="4"/>
   <sheetData>
-    <row r="7" spans="3:5">
-      <c r="C7" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7">
-        <v>5</v>
-      </c>
-      <c r="E7" t="str">
-        <f t="shared" ref="E7:E9" si="0">C7&amp;"*"&amp;D7</f>
-        <v>strike*5</v>
-      </c>
-    </row>
-    <row r="8" spans="3:6">
-      <c r="C8" s="35" t="s">
-        <v>28</v>
-      </c>
-      <c r="D8">
-        <v>4</v>
-      </c>
-      <c r="E8" t="str">
-        <f t="shared" si="0"/>
-        <v>defense*4</v>
-      </c>
-      <c r="F8" t="str">
-        <f>E7&amp;"*"&amp;E8</f>
-        <v>strike*5*defense*4</v>
-      </c>
-    </row>
-    <row r="9" spans="3:6">
-      <c r="C9" s="35" t="s">
-        <v>31</v>
-      </c>
-      <c r="D9">
+    <row r="1" spans="1:5">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="10">
         <v>1</v>
       </c>
-      <c r="E9" t="str">
-        <f t="shared" si="0"/>
-        <v>trounce*1</v>
-      </c>
-      <c r="F9" t="str">
-        <f>F8&amp;"*"&amp;E9</f>
-        <v>strike*5*defense*4*trounce*1</v>
+      <c r="B4" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="D4" s="10"/>
+      <c r="E4" s="35" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -3708,6 +3512,62 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
+  <dimension ref="C7:F9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <sheetData>
+    <row r="7" spans="3:5">
+      <c r="C7" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7">
+        <v>5</v>
+      </c>
+      <c r="E7" t="str">
+        <f t="shared" ref="E7:E9" si="0">C7&amp;"*"&amp;D7</f>
+        <v>strike*5</v>
+      </c>
+    </row>
+    <row r="8" spans="3:6">
+      <c r="C8" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8">
+        <v>4</v>
+      </c>
+      <c r="E8" t="str">
+        <f t="shared" si="0"/>
+        <v>defense*4</v>
+      </c>
+      <c r="F8" t="str">
+        <f>E7&amp;"*"&amp;E8</f>
+        <v>strike*5*defense*4</v>
+      </c>
+    </row>
+    <row r="9" spans="3:6">
+      <c r="C9" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9" t="str">
+        <f t="shared" si="0"/>
+        <v>trounce*1</v>
+      </c>
+      <c r="F9" t="str">
+        <f>F8&amp;"*"&amp;E9</f>
+        <v>strike*5*defense*4*trounce*1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:AA41"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
@@ -3719,67 +3579,67 @@
         <v>34</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="R1" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="S1" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="T1" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="U1" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="R1" s="13" t="s">
+      <c r="V1" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="W1" s="14" t="s">
         <v>77</v>
-      </c>
-      <c r="T1" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="U1" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="V1" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="W1" s="14" t="s">
-        <v>81</v>
       </c>
       <c r="X1" s="15"/>
       <c r="Y1" s="15"/>
@@ -3791,82 +3651,82 @@
         <v>5</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="H2" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="I2" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="J2" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="K2" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="L2" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="M2" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="N2" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="O2" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="P2" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="Q2" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="R2" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="O2" s="4" t="s">
+      <c r="S2" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="T2" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="Q2" s="4" t="s">
+      <c r="U2" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="R2" s="16" t="s">
+      <c r="V2" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="S2" s="4" t="s">
+      <c r="W2" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="X2" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="T2" s="4" t="s">
+      <c r="Y2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="U2" s="4" t="s">
+      <c r="Z2" s="32" t="s">
         <v>101</v>
       </c>
-      <c r="V2" s="4" t="s">
+      <c r="AA2" s="33" t="s">
         <v>102</v>
-      </c>
-      <c r="W2" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="X2" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="Y2" s="32" t="s">
-        <v>104</v>
-      </c>
-      <c r="Z2" s="32" t="s">
-        <v>105</v>
-      </c>
-      <c r="AA2" s="33" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="3" ht="14.25" spans="1:27">
@@ -3957,7 +3817,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C4" s="8">
         <v>10</v>
@@ -4012,17 +3872,17 @@
       <c r="U4" s="8"/>
       <c r="V4" s="8"/>
       <c r="W4" s="23"/>
-      <c r="X4" s="129" t="s">
-        <v>108</v>
+      <c r="X4" s="120" t="s">
+        <v>104</v>
       </c>
       <c r="Y4" s="8" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="Z4" s="8" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="AA4" s="23" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="5" spans="1:27">
@@ -4030,7 +3890,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C5" s="10">
         <v>10</v>
@@ -4086,16 +3946,16 @@
       <c r="V5" s="10"/>
       <c r="W5" s="26"/>
       <c r="X5" s="27" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="Y5" s="10" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="Z5" s="10" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="AA5" s="26" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:27">
@@ -4103,7 +3963,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C6" s="10">
         <v>10</v>
@@ -4159,16 +4019,16 @@
       <c r="V6" s="10"/>
       <c r="W6" s="26"/>
       <c r="X6" s="27" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="Y6" s="10" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="Z6" s="10" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="AA6" s="26" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7" spans="1:27">
@@ -4176,7 +4036,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C7" s="10">
         <v>10</v>
@@ -4232,16 +4092,16 @@
       <c r="V7" s="10"/>
       <c r="W7" s="26"/>
       <c r="X7" s="27" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="Y7" s="10" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="Z7" s="10" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="AA7" s="26" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="8" spans="1:27">
@@ -4249,7 +4109,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C8" s="10">
         <v>10</v>
@@ -4305,16 +4165,16 @@
       <c r="V8" s="10"/>
       <c r="W8" s="26"/>
       <c r="X8" s="27" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="Y8" s="10" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="Z8" s="10" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="AA8" s="26" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="9" spans="1:27">
@@ -4322,7 +4182,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C9" s="10">
         <v>10</v>
@@ -4378,16 +4238,16 @@
       <c r="V9" s="10"/>
       <c r="W9" s="26"/>
       <c r="X9" s="27" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="Y9" s="10" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="Z9" s="10" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="AA9" s="26" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
     <row r="10" spans="1:27">
@@ -4395,7 +4255,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C10" s="10">
         <v>10</v>
@@ -4451,16 +4311,16 @@
       <c r="V10" s="10"/>
       <c r="W10" s="26"/>
       <c r="X10" s="27" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="Y10" s="10" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="Z10" s="10" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AA10" s="26" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="11" spans="1:27">
@@ -4468,7 +4328,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C11" s="10">
         <v>10</v>
@@ -4524,16 +4384,16 @@
       <c r="V11" s="10"/>
       <c r="W11" s="26"/>
       <c r="X11" s="27" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="Y11" s="10" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="Z11" s="10" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="AA11" s="26" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12" spans="1:27">
@@ -4541,7 +4401,7 @@
         <v>9</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C12" s="10">
         <v>10</v>
@@ -4597,16 +4457,16 @@
       <c r="V12" s="10"/>
       <c r="W12" s="26"/>
       <c r="X12" s="27" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="Y12" s="10" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="Z12" s="10" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="AA12" s="26" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="13" spans="1:27">
@@ -4614,7 +4474,7 @@
         <v>10</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C13" s="10">
         <v>10</v>
@@ -4670,16 +4530,16 @@
       <c r="V13" s="10"/>
       <c r="W13" s="26"/>
       <c r="X13" s="27" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="Y13" s="10" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="Z13" s="10" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="AA13" s="26" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="14" spans="1:27">
@@ -4687,7 +4547,7 @@
         <v>11</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C14" s="10">
         <v>10</v>
@@ -4743,16 +4603,16 @@
       <c r="V14" s="10"/>
       <c r="W14" s="26"/>
       <c r="X14" s="27" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="Y14" s="10" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="Z14" s="10" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="AA14" s="26" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="15" spans="1:27">
@@ -4760,7 +4620,7 @@
         <v>12</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C15" s="10">
         <v>10</v>
@@ -4816,16 +4676,16 @@
       <c r="V15" s="10"/>
       <c r="W15" s="26"/>
       <c r="X15" s="27" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="Y15" s="10" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="Z15" s="10" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="AA15" s="26" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="16" spans="1:27">
@@ -4833,7 +4693,7 @@
         <v>13</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C16" s="10">
         <v>10</v>
@@ -4889,16 +4749,16 @@
       <c r="V16" s="10"/>
       <c r="W16" s="26"/>
       <c r="X16" s="27" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="Y16" s="10" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="Z16" s="10" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="AA16" s="26" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="17" spans="1:27">
@@ -4906,7 +4766,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C17" s="10">
         <v>10</v>
@@ -4962,16 +4822,16 @@
       <c r="V17" s="10"/>
       <c r="W17" s="26"/>
       <c r="X17" s="27" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="Y17" s="10" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="Z17" s="10" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="AA17" s="26" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
     </row>
     <row r="18" spans="1:27">
@@ -4979,7 +4839,7 @@
         <v>15</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C18" s="10">
         <v>10</v>
@@ -5035,16 +4895,16 @@
       <c r="V18" s="10"/>
       <c r="W18" s="26"/>
       <c r="X18" s="27" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="Y18" s="10" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="Z18" s="10" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="AA18" s="26" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
     </row>
     <row r="19" spans="1:27">
@@ -5052,7 +4912,7 @@
         <v>16</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="C19" s="10">
         <v>10</v>
@@ -5108,16 +4968,16 @@
       <c r="V19" s="10"/>
       <c r="W19" s="26"/>
       <c r="X19" s="27" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="Y19" s="10" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="Z19" s="10" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="AA19" s="26" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="20" spans="1:27">
@@ -5125,7 +4985,7 @@
         <v>17</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C20" s="10">
         <v>10</v>
@@ -5181,16 +5041,16 @@
       <c r="V20" s="10"/>
       <c r="W20" s="26"/>
       <c r="X20" s="27" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="Y20" s="10" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="Z20" s="10" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="AA20" s="26" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="21" spans="1:27">
@@ -5198,7 +5058,7 @@
         <v>18</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C21" s="10">
         <v>10</v>
@@ -5254,16 +5114,16 @@
       <c r="V21" s="10"/>
       <c r="W21" s="26"/>
       <c r="X21" s="27" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="Y21" s="10" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="Z21" s="10" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="AA21" s="26" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="22" spans="1:27">
@@ -5271,7 +5131,7 @@
         <v>19</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C22" s="10">
         <v>10</v>
@@ -5327,16 +5187,16 @@
       <c r="V22" s="10"/>
       <c r="W22" s="26"/>
       <c r="X22" s="27" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="Y22" s="10" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="Z22" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="AA22" s="26" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
     </row>
     <row r="23" spans="1:27">
@@ -5344,7 +5204,7 @@
         <v>20</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C23" s="10">
         <v>10</v>
@@ -5400,16 +5260,16 @@
       <c r="V23" s="10"/>
       <c r="W23" s="26"/>
       <c r="X23" s="27" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="Y23" s="10" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="Z23" s="10" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="AA23" s="26" t="s">
-        <v>47</v>
+        <v>189</v>
       </c>
     </row>
     <row r="24" spans="1:27">
@@ -5417,7 +5277,7 @@
         <v>21</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C24" s="10">
         <v>10</v>
@@ -5473,16 +5333,16 @@
       <c r="V24" s="10"/>
       <c r="W24" s="26"/>
       <c r="X24" s="27" t="s">
+        <v>191</v>
+      </c>
+      <c r="Y24" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="Z24" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="AA24" s="26" t="s">
         <v>194</v>
-      </c>
-      <c r="Y24" s="10" t="s">
-        <v>195</v>
-      </c>
-      <c r="Z24" s="10" t="s">
-        <v>196</v>
-      </c>
-      <c r="AA24" s="26" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="25" spans="1:27">
@@ -5490,7 +5350,7 @@
         <v>22</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C25" s="10">
         <v>10</v>
@@ -5546,16 +5406,16 @@
       <c r="V25" s="10"/>
       <c r="W25" s="26"/>
       <c r="X25" s="27" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="Y25" s="10" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="Z25" s="10" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="AA25" s="26" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="26" spans="1:27">
@@ -5563,7 +5423,7 @@
         <v>23</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C26" s="10">
         <v>10</v>
@@ -5619,16 +5479,16 @@
       <c r="V26" s="10"/>
       <c r="W26" s="26"/>
       <c r="X26" s="27" t="s">
+        <v>200</v>
+      </c>
+      <c r="Y26" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="Z26" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="AA26" s="26" t="s">
         <v>203</v>
-      </c>
-      <c r="Y26" s="10" t="s">
-        <v>204</v>
-      </c>
-      <c r="Z26" s="10" t="s">
-        <v>205</v>
-      </c>
-      <c r="AA26" s="26" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="27" spans="1:27">
@@ -5636,7 +5496,7 @@
         <v>24</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C27" s="10">
         <v>10</v>
@@ -5692,16 +5552,16 @@
       <c r="V27" s="10"/>
       <c r="W27" s="26"/>
       <c r="X27" s="27" t="s">
+        <v>205</v>
+      </c>
+      <c r="Y27" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="Z27" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="AA27" s="26" t="s">
         <v>208</v>
-      </c>
-      <c r="Y27" s="10" t="s">
-        <v>209</v>
-      </c>
-      <c r="Z27" s="10" t="s">
-        <v>210</v>
-      </c>
-      <c r="AA27" s="26" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="28" spans="1:27">
@@ -5709,7 +5569,7 @@
         <v>25</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C28" s="10">
         <v>10</v>
@@ -5765,16 +5625,16 @@
       <c r="V28" s="10"/>
       <c r="W28" s="26"/>
       <c r="X28" s="27" t="s">
+        <v>210</v>
+      </c>
+      <c r="Y28" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="Z28" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="AA28" s="26" t="s">
         <v>213</v>
-      </c>
-      <c r="Y28" s="10" t="s">
-        <v>214</v>
-      </c>
-      <c r="Z28" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="AA28" s="26" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="29" spans="1:27">
@@ -5782,7 +5642,7 @@
         <v>26</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C29" s="10">
         <v>10</v>
@@ -5838,16 +5698,16 @@
       <c r="V29" s="10"/>
       <c r="W29" s="26"/>
       <c r="X29" s="27" t="s">
+        <v>215</v>
+      </c>
+      <c r="Y29" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="Z29" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="AA29" s="26" t="s">
         <v>218</v>
-      </c>
-      <c r="Y29" s="10" t="s">
-        <v>219</v>
-      </c>
-      <c r="Z29" s="10" t="s">
-        <v>220</v>
-      </c>
-      <c r="AA29" s="26" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="30" spans="1:27">
@@ -5855,7 +5715,7 @@
         <v>27</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C30" s="10">
         <v>10</v>
@@ -5911,16 +5771,16 @@
       <c r="V30" s="10"/>
       <c r="W30" s="26"/>
       <c r="X30" s="27" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="Y30" s="10" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="Z30" s="10" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="AA30" s="26" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="31" spans="1:27">
@@ -5928,7 +5788,7 @@
         <v>28</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C31" s="10">
         <v>10</v>
@@ -5984,16 +5844,16 @@
       <c r="V31" s="10"/>
       <c r="W31" s="26"/>
       <c r="X31" s="27" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="Y31" s="10" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="Z31" s="10" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="AA31" s="26" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="32" spans="1:27">
@@ -6001,7 +5861,7 @@
         <v>29</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C32" s="10">
         <v>10</v>
@@ -6057,16 +5917,16 @@
       <c r="V32" s="10"/>
       <c r="W32" s="26"/>
       <c r="X32" s="27" t="s">
+        <v>228</v>
+      </c>
+      <c r="Y32" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="Z32" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="AA32" s="26" t="s">
         <v>231</v>
-      </c>
-      <c r="Y32" s="10" t="s">
-        <v>232</v>
-      </c>
-      <c r="Z32" s="10" t="s">
-        <v>233</v>
-      </c>
-      <c r="AA32" s="26" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="33" spans="1:27">
@@ -6074,7 +5934,7 @@
         <v>30</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="C33" s="10">
         <v>10</v>
@@ -6130,16 +5990,16 @@
       <c r="V33" s="10"/>
       <c r="W33" s="26"/>
       <c r="X33" s="27" t="s">
+        <v>233</v>
+      </c>
+      <c r="Y33" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="Z33" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="AA33" s="26" t="s">
         <v>236</v>
-      </c>
-      <c r="Y33" s="10" t="s">
-        <v>237</v>
-      </c>
-      <c r="Z33" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="AA33" s="26" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="34" spans="1:27">
@@ -6147,7 +6007,7 @@
         <v>31</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="C34" s="10">
         <v>10</v>
@@ -6203,16 +6063,16 @@
       <c r="V34" s="10"/>
       <c r="W34" s="26"/>
       <c r="X34" s="27" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="Y34" s="10" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="Z34" s="10" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="AA34" s="26" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="35" spans="1:27">
@@ -6220,7 +6080,7 @@
         <v>32</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C35" s="10">
         <v>10</v>
@@ -6276,16 +6136,16 @@
       <c r="V35" s="10"/>
       <c r="W35" s="26"/>
       <c r="X35" s="27" t="s">
+        <v>242</v>
+      </c>
+      <c r="Y35" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z35" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="AA35" s="26" t="s">
         <v>245</v>
-      </c>
-      <c r="Y35" s="10" t="s">
-        <v>246</v>
-      </c>
-      <c r="Z35" s="10" t="s">
-        <v>247</v>
-      </c>
-      <c r="AA35" s="26" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="36" spans="1:27">
@@ -6293,7 +6153,7 @@
         <v>33</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="C36" s="10">
         <v>10</v>
@@ -6349,16 +6209,16 @@
       <c r="V36" s="10"/>
       <c r="W36" s="26"/>
       <c r="X36" s="27" t="s">
+        <v>247</v>
+      </c>
+      <c r="Y36" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="Z36" s="10" t="s">
+        <v>249</v>
+      </c>
+      <c r="AA36" s="26" t="s">
         <v>250</v>
-      </c>
-      <c r="Y36" s="10" t="s">
-        <v>251</v>
-      </c>
-      <c r="Z36" s="10" t="s">
-        <v>252</v>
-      </c>
-      <c r="AA36" s="26" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="37" spans="1:27">
@@ -6366,7 +6226,7 @@
         <v>34</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C37" s="10">
         <v>10</v>
@@ -6422,16 +6282,16 @@
       <c r="V37" s="10"/>
       <c r="W37" s="26"/>
       <c r="X37" s="27" t="s">
+        <v>252</v>
+      </c>
+      <c r="Y37" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="Z37" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="AA37" s="26" t="s">
         <v>255</v>
-      </c>
-      <c r="Y37" s="10" t="s">
-        <v>256</v>
-      </c>
-      <c r="Z37" s="10" t="s">
-        <v>257</v>
-      </c>
-      <c r="AA37" s="26" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="38" spans="1:27">
@@ -6439,7 +6299,7 @@
         <v>35</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C38" s="10">
         <v>10</v>
@@ -6495,16 +6355,16 @@
       <c r="V38" s="10"/>
       <c r="W38" s="26"/>
       <c r="X38" s="27" t="s">
+        <v>257</v>
+      </c>
+      <c r="Y38" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="Z38" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="AA38" s="26" t="s">
         <v>260</v>
-      </c>
-      <c r="Y38" s="10" t="s">
-        <v>261</v>
-      </c>
-      <c r="Z38" s="10" t="s">
-        <v>262</v>
-      </c>
-      <c r="AA38" s="26" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="39" spans="1:27">
@@ -6512,7 +6372,7 @@
         <v>36</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C39" s="10">
         <v>10</v>
@@ -6568,16 +6428,16 @@
       <c r="V39" s="10"/>
       <c r="W39" s="26"/>
       <c r="X39" s="27" t="s">
+        <v>262</v>
+      </c>
+      <c r="Y39" s="10" t="s">
+        <v>263</v>
+      </c>
+      <c r="Z39" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="AA39" s="26" t="s">
         <v>265</v>
-      </c>
-      <c r="Y39" s="10" t="s">
-        <v>266</v>
-      </c>
-      <c r="Z39" s="10" t="s">
-        <v>267</v>
-      </c>
-      <c r="AA39" s="26" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="40" spans="1:27">
@@ -6585,7 +6445,7 @@
         <v>37</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="C40" s="10">
         <v>10</v>
@@ -6641,16 +6501,16 @@
       <c r="V40" s="10"/>
       <c r="W40" s="26"/>
       <c r="X40" s="27" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="Y40" s="10" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="Z40" s="10" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="AA40" s="26" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="41" ht="14.25" spans="1:27">
@@ -6658,7 +6518,7 @@
         <v>38</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="C41" s="12">
         <v>10</v>
@@ -6714,16 +6574,16 @@
       <c r="V41" s="12"/>
       <c r="W41" s="29"/>
       <c r="X41" s="30" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="Y41" s="12" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="Z41" s="12" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="AA41" s="29" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>

--- a/xlsdir/配置-总表.xlsx
+++ b/xlsdir/配置-总表.xlsx
@@ -4,53 +4,87 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27930" windowHeight="12975" tabRatio="673" activeTab="1"/>
+    <workbookView windowHeight="18375" tabRatio="673" activeTab="4"/>
   </bookViews>
   <sheets>
-    <sheet name="hero|玩家角色" sheetId="27" r:id="rId1"/>
-    <sheet name="card|卡牌" sheetId="29" r:id="rId2"/>
+    <sheet name="character|角色" sheetId="32" r:id="rId1"/>
+    <sheet name="hero|玩家角色" sheetId="27" r:id="rId2"/>
     <sheet name="monster|魔物" sheetId="28" r:id="rId3"/>
-    <sheet name="combat|战斗" sheetId="31" r:id="rId4"/>
-    <sheet name="Sheet3" sheetId="30" r:id="rId5"/>
-    <sheet name="Sheet1" sheetId="11" state="hidden" r:id="rId6"/>
+    <sheet name="card|卡牌" sheetId="29" r:id="rId4"/>
+    <sheet name="combat|战斗" sheetId="31" r:id="rId5"/>
+    <sheet name="Sheet3" sheetId="30" r:id="rId6"/>
+    <sheet name="Sheet1" sheetId="11" state="hidden" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'monster|魔物'!$A$1:$O$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'monster|魔物'!$A$1:$B$4</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="266">
   <si>
     <t>ID</t>
   </si>
   <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>health</t>
+  </si>
+  <si>
+    <t>attack</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>编号</t>
+  </si>
+  <si>
+    <t>角色名</t>
+  </si>
+  <si>
+    <t>生命值</t>
+  </si>
+  <si>
+    <t>攻击力</t>
+  </si>
+  <si>
+    <t>描述</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>铁甲战士</t>
+  </si>
+  <si>
+    <t>铁甲军团残留下的士兵，他出卖自己的灵魂，获得了恶魔的力量。</t>
+  </si>
+  <si>
+    <t>slime</t>
+  </si>
+  <si>
+    <t>史莱姆</t>
+  </si>
+  <si>
+    <t>一个矮小而丑陋的怪物，生活在森林深处。</t>
+  </si>
+  <si>
     <t>hero_name</t>
   </si>
   <si>
-    <t>health</t>
-  </si>
-  <si>
-    <t>background_story</t>
-  </si>
-  <si>
     <t>initial_deck</t>
   </si>
   <si>
-    <t>编号</t>
-  </si>
-  <si>
     <t>英雄的名字</t>
   </si>
   <si>
-    <t>英雄的生命值</t>
-  </si>
-  <si>
-    <t>英雄的背景故事描述</t>
-  </si>
-  <si>
     <t>初始卡牌</t>
   </si>
   <si>
@@ -60,34 +94,22 @@
     <t>被动技能</t>
   </si>
   <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
     <t>string[]</t>
   </si>
   <si>
-    <t>铁甲战士</t>
-  </si>
-  <si>
-    <t>铁甲军团残留下的士兵，他出卖自己的灵魂，获得了恶魔的力量。</t>
-  </si>
-  <si>
     <t>strike*5*defense*4*trounce*1</t>
   </si>
   <si>
     <t>燃烧之血，战斗结束时恢复6点生命。</t>
   </si>
   <si>
+    <t>怪物名</t>
+  </si>
+  <si>
     <t>card_name</t>
   </si>
   <si>
     <t>card_type</t>
-  </si>
-  <si>
-    <t>description</t>
   </si>
   <si>
     <t>卡牌名</t>
@@ -128,58 +150,13 @@
     <t>造成8点伤害，给与2层易伤</t>
   </si>
   <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>level</t>
-  </si>
-  <si>
-    <t>health_points</t>
-  </si>
-  <si>
-    <t>attack_points</t>
-  </si>
-  <si>
-    <t>entityID</t>
-  </si>
-  <si>
-    <t>怪物名</t>
-  </si>
-  <si>
-    <t>怪物描述</t>
-  </si>
-  <si>
-    <t>等级</t>
-  </si>
-  <si>
-    <t>生命值</t>
-  </si>
-  <si>
-    <t>攻击力</t>
-  </si>
-  <si>
-    <t>实体名</t>
-  </si>
-  <si>
-    <t>slime</t>
-  </si>
-  <si>
-    <t>史莱姆</t>
-  </si>
-  <si>
-    <t>一个矮小而丑陋的怪物，生活在森林深处。</t>
-  </si>
-  <si>
-    <t>character_slime</t>
-  </si>
-  <si>
-    <t>mark_01</t>
-  </si>
-  <si>
-    <t>mark_02</t>
-  </si>
-  <si>
-    <t>mark_03</t>
+    <t>mark_04</t>
+  </si>
+  <si>
+    <t>mark_05</t>
+  </si>
+  <si>
+    <t>mark_06</t>
   </si>
   <si>
     <t>战斗名</t>
@@ -1125,24 +1102,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799951170384838"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1219,6 +1184,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1325,7 +1296,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="55">
+  <borders count="37">
     <border>
       <left/>
       <right/>
@@ -1667,24 +1638,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color auto="1"/>
       </left>
@@ -1713,210 +1666,12 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color auto="1"/>
       </left>
       <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
+      <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -2043,7 +1798,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="47" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2055,119 +1810,119 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="48" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="48" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="49" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="31" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="50" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="51" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="50" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="52" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="53" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="54" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="32" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="33" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="32" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="34" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="35" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="36" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="120">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2276,257 +2031,32 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="26" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="34" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="35" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="37" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="38" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="39" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="40" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="41" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="42" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="43" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="34" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="35" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="36" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="37" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="31" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="32" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="33" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="22" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="25" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="44" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="45" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="46" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1" quotePrefix="1">
       <alignment vertical="center"/>
@@ -2879,17 +2409,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultColWidth="8.85833333333333" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="6"/>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="8.33333333333333" style="40" customWidth="1"/>
-    <col min="2" max="2" width="11.8916666666667" customWidth="1"/>
-    <col min="3" max="3" width="8.33333333333333" customWidth="1"/>
-    <col min="4" max="4" width="20.6666666666667" customWidth="1" outlineLevel="1"/>
-    <col min="5" max="5" width="31.5" customWidth="1"/>
+    <col min="5" max="5" width="37" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:5">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -2899,82 +2425,79 @@
       <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-    </row>
-    <row r="2" s="119" customFormat="1" ht="27" spans="1:7">
-      <c r="A2" s="118" t="s">
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="118" t="s">
+      <c r="B2" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="118" t="s">
+      <c r="C2" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="118" t="s">
+      <c r="D2" s="43" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="118" t="s">
+      <c r="E2" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="118" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" s="118" t="s">
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+      <c r="D3" s="43" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="43" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" s="10">
         <v>1</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C4" s="10">
         <v>80</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="44">
+        <v>0</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="35" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="35">
+        <v>50</v>
+      </c>
+      <c r="D5" s="35">
+        <v>10</v>
+      </c>
+      <c r="E5" s="35" t="s">
         <v>16</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" s="10">
-        <v>99</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -2984,6 +2507,136 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultColWidth="8.85833333333333" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="1" width="8.33333333333333" style="42" customWidth="1"/>
+    <col min="2" max="2" width="11.8916666666667" customWidth="1"/>
+    <col min="3" max="3" width="31.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+    </row>
+    <row r="2" s="41" customFormat="1" spans="1:5">
+      <c r="A2" s="36" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="36" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="36" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" s="36" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="10">
+        <v>1</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="10">
+        <v>99</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="1"/>
+  <cols>
+    <col min="1" max="1" width="7.66666666666667" customWidth="1"/>
+    <col min="2" max="2" width="11.4666666666667" style="21" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="37" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="38" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="37" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="38" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="38" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="39" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="40" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D6"/>
@@ -2998,509 +2651,83 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" ht="40.5" spans="1:4">
-      <c r="A2" s="118" t="s">
+      <c r="A2" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="118" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" s="118" t="s">
-        <v>23</v>
+      <c r="B2" s="36" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="36" t="s">
+        <v>30</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="10" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="B4" s="35" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="C4" s="10">
         <v>1</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="10" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="B5" s="35" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="C5" s="10">
         <v>2</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="10" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B6" s="35" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="C6" s="10">
         <v>1</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>33</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:O16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <cols>
-    <col min="1" max="1" width="7.66666666666667" customWidth="1"/>
-    <col min="2" max="2" width="11.4666666666667" style="21" customWidth="1"/>
-    <col min="3" max="3" width="30.1333333333333" customWidth="1"/>
-    <col min="4" max="4" width="7" style="21" customWidth="1"/>
-    <col min="5" max="5" width="15.225" customWidth="1"/>
-    <col min="6" max="6" width="15.225" style="40" customWidth="1" outlineLevel="1"/>
-    <col min="7" max="7" width="17.125" style="41" customWidth="1" outlineLevel="1"/>
-    <col min="10" max="10" width="9" style="41"/>
-    <col min="11" max="11" width="7.26666666666667" style="42" customWidth="1"/>
-    <col min="15" max="15" width="6.4" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:15">
-      <c r="A1" s="43" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="44" t="s">
-        <v>34</v>
-      </c>
-      <c r="C1" s="44" t="s">
-        <v>21</v>
-      </c>
-      <c r="D1" s="45" t="s">
-        <v>35</v>
-      </c>
-      <c r="E1" s="45" t="s">
-        <v>36</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G1" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="H1" s="46"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="26"/>
-      <c r="K1" s="97"/>
-      <c r="L1" s="52"/>
-      <c r="M1" s="4"/>
-      <c r="N1" s="26"/>
-      <c r="O1" s="41"/>
-    </row>
-    <row r="2" spans="1:15">
-      <c r="A2" s="43" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="44" t="s">
-        <v>39</v>
-      </c>
-      <c r="C2" s="44" t="s">
         <v>40</v>
-      </c>
-      <c r="D2" s="45" t="s">
-        <v>41</v>
-      </c>
-      <c r="E2" s="45" t="s">
-        <v>42</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="G2" s="17" t="s">
-        <v>44</v>
-      </c>
-      <c r="H2" s="46"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="26"/>
-      <c r="K2" s="97"/>
-      <c r="L2" s="52"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="26"/>
-      <c r="O2" s="41"/>
-    </row>
-    <row r="3" spans="1:15">
-      <c r="A3" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="44" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="44" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="45" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="45" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="H3" s="46"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="26"/>
-      <c r="K3" s="97"/>
-      <c r="L3" s="52"/>
-      <c r="M3" s="4"/>
-      <c r="N3" s="26"/>
-      <c r="O3" s="41"/>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" s="47" t="s">
-        <v>45</v>
-      </c>
-      <c r="B4" s="48" t="s">
-        <v>46</v>
-      </c>
-      <c r="C4" s="48" t="s">
-        <v>47</v>
-      </c>
-      <c r="D4" s="49">
-        <v>3</v>
-      </c>
-      <c r="E4" s="49">
-        <v>50</v>
-      </c>
-      <c r="F4" s="50">
-        <v>10</v>
-      </c>
-      <c r="G4" s="51" t="s">
-        <v>48</v>
-      </c>
-      <c r="H4" s="52"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="26"/>
-      <c r="K4" s="41"/>
-    </row>
-    <row r="5" spans="1:15">
-      <c r="A5" s="53"/>
-      <c r="B5" s="44"/>
-      <c r="C5" s="54"/>
-      <c r="D5" s="55"/>
-      <c r="E5" s="55"/>
-      <c r="F5" s="52"/>
-      <c r="G5" s="26"/>
-      <c r="H5" s="46"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="26"/>
-      <c r="K5" s="97"/>
-      <c r="L5" s="52"/>
-      <c r="M5" s="4"/>
-      <c r="N5" s="26"/>
-      <c r="O5" s="41"/>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" s="53"/>
-      <c r="B6" s="44"/>
-      <c r="C6" s="54"/>
-      <c r="D6" s="55"/>
-      <c r="E6" s="55"/>
-      <c r="F6" s="52"/>
-      <c r="G6" s="26"/>
-      <c r="H6" s="46"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="26"/>
-      <c r="K6" s="97"/>
-      <c r="L6" s="52"/>
-      <c r="M6" s="4"/>
-      <c r="N6" s="26"/>
-    </row>
-    <row r="7" spans="1:15">
-      <c r="A7" s="53"/>
-      <c r="B7" s="44"/>
-      <c r="C7" s="54"/>
-      <c r="D7" s="55"/>
-      <c r="E7" s="55"/>
-      <c r="F7" s="52"/>
-      <c r="G7" s="26"/>
-      <c r="H7" s="46"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="26"/>
-      <c r="K7" s="97"/>
-      <c r="L7" s="52"/>
-      <c r="M7" s="4"/>
-      <c r="N7" s="26"/>
-      <c r="O7" s="41"/>
-    </row>
-    <row r="8" spans="1:15">
-      <c r="A8" s="53"/>
-      <c r="B8" s="44"/>
-      <c r="C8" s="54"/>
-      <c r="D8" s="55"/>
-      <c r="E8" s="55"/>
-      <c r="F8" s="52"/>
-      <c r="G8" s="26"/>
-      <c r="H8" s="46"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="26"/>
-      <c r="K8" s="97"/>
-      <c r="L8" s="52"/>
-      <c r="M8" s="4"/>
-      <c r="N8" s="26"/>
-      <c r="O8" s="41"/>
-    </row>
-    <row r="9" spans="1:15">
-      <c r="A9" s="53"/>
-      <c r="B9" s="44"/>
-      <c r="C9" s="54"/>
-      <c r="D9" s="55"/>
-      <c r="E9" s="55"/>
-      <c r="F9" s="52"/>
-      <c r="G9" s="26"/>
-      <c r="H9" s="46"/>
-      <c r="I9" s="10"/>
-      <c r="J9" s="26"/>
-      <c r="K9" s="97"/>
-      <c r="L9" s="52"/>
-      <c r="M9" s="4"/>
-      <c r="N9" s="26"/>
-      <c r="O9" s="41"/>
-    </row>
-    <row r="10" spans="1:15">
-      <c r="A10" s="53"/>
-      <c r="B10" s="44"/>
-      <c r="C10" s="54"/>
-      <c r="D10" s="55"/>
-      <c r="E10" s="55"/>
-      <c r="F10" s="52"/>
-      <c r="G10" s="26"/>
-      <c r="H10" s="46"/>
-      <c r="I10" s="10"/>
-      <c r="J10" s="26"/>
-      <c r="K10" s="97"/>
-      <c r="L10" s="52"/>
-      <c r="M10" s="4"/>
-      <c r="N10" s="26"/>
-      <c r="O10" s="41"/>
-    </row>
-    <row r="11" ht="14.25" spans="1:15">
-      <c r="A11" s="56"/>
-      <c r="B11" s="57"/>
-      <c r="C11" s="58"/>
-      <c r="D11" s="59"/>
-      <c r="E11" s="59"/>
-      <c r="F11" s="60"/>
-      <c r="G11" s="29"/>
-      <c r="H11" s="61"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="29"/>
-      <c r="K11" s="98"/>
-      <c r="L11" s="52"/>
-      <c r="M11" s="4"/>
-      <c r="N11" s="26"/>
-      <c r="O11" s="41"/>
-    </row>
-    <row r="12" s="36" customFormat="1" spans="1:15">
-      <c r="A12" s="62"/>
-      <c r="B12" s="63"/>
-      <c r="C12" s="64"/>
-      <c r="D12" s="65"/>
-      <c r="E12" s="65"/>
-      <c r="F12" s="66"/>
-      <c r="G12" s="67"/>
-      <c r="H12" s="68"/>
-      <c r="I12" s="99"/>
-      <c r="J12" s="67"/>
-      <c r="K12" s="100"/>
-      <c r="L12" s="73"/>
-      <c r="M12" s="101"/>
-      <c r="N12" s="74"/>
-      <c r="O12" s="102"/>
-    </row>
-    <row r="13" s="37" customFormat="1" spans="1:15">
-      <c r="A13" s="69"/>
-      <c r="B13" s="70"/>
-      <c r="C13" s="71"/>
-      <c r="D13" s="72"/>
-      <c r="E13" s="72"/>
-      <c r="F13" s="73"/>
-      <c r="G13" s="74"/>
-      <c r="H13" s="75"/>
-      <c r="I13" s="103"/>
-      <c r="J13" s="74"/>
-      <c r="K13" s="104"/>
-      <c r="L13" s="73"/>
-      <c r="M13" s="101"/>
-      <c r="N13" s="74"/>
-      <c r="O13" s="105"/>
-    </row>
-    <row r="14" s="37" customFormat="1" ht="14.25" spans="1:15">
-      <c r="A14" s="76"/>
-      <c r="B14" s="77"/>
-      <c r="C14" s="78"/>
-      <c r="D14" s="79"/>
-      <c r="E14" s="79"/>
-      <c r="F14" s="80"/>
-      <c r="G14" s="81"/>
-      <c r="H14" s="82"/>
-      <c r="I14" s="106"/>
-      <c r="J14" s="81"/>
-      <c r="K14" s="107"/>
-      <c r="L14" s="73"/>
-      <c r="M14" s="101"/>
-      <c r="N14" s="74"/>
-      <c r="O14" s="105"/>
-    </row>
-    <row r="15" s="38" customFormat="1" spans="1:15">
-      <c r="A15" s="83"/>
-      <c r="B15" s="84"/>
-      <c r="C15" s="85"/>
-      <c r="D15" s="86"/>
-      <c r="E15" s="86"/>
-      <c r="F15" s="87"/>
-      <c r="G15" s="88"/>
-      <c r="H15" s="89"/>
-      <c r="I15" s="108"/>
-      <c r="J15" s="88"/>
-      <c r="K15" s="109"/>
-      <c r="L15" s="110"/>
-      <c r="M15" s="111"/>
-      <c r="N15" s="112"/>
-      <c r="O15" s="113"/>
-    </row>
-    <row r="16" s="39" customFormat="1" ht="14.25" spans="1:15">
-      <c r="A16" s="90"/>
-      <c r="B16" s="91"/>
-      <c r="C16" s="92"/>
-      <c r="D16" s="93"/>
-      <c r="E16" s="93"/>
-      <c r="F16" s="94"/>
-      <c r="G16" s="95"/>
-      <c r="H16" s="96"/>
-      <c r="I16" s="114"/>
-      <c r="J16" s="95"/>
-      <c r="K16" s="115"/>
-      <c r="L16" s="94"/>
-      <c r="M16" s="116"/>
-      <c r="N16" s="95"/>
-      <c r="O16" s="117"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="4"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="10">
-        <v>1</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="C4" s="35" t="s">
-        <v>45</v>
-      </c>
-      <c r="D4" s="10"/>
-      <c r="E4" s="35" t="s">
-        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -3512,51 +2739,73 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C7:F9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="4"/>
   <sheetData>
-    <row r="7" spans="3:5">
-      <c r="C7" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7">
-        <v>5</v>
-      </c>
-      <c r="E7" t="str">
-        <f t="shared" ref="E7:E9" si="0">C7&amp;"*"&amp;D7</f>
-        <v>strike*5</v>
-      </c>
-    </row>
-    <row r="8" spans="3:6">
-      <c r="C8" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="D8">
-        <v>4</v>
-      </c>
-      <c r="E8" t="str">
-        <f t="shared" si="0"/>
-        <v>defense*4</v>
-      </c>
-      <c r="F8" t="str">
-        <f>E7&amp;"*"&amp;E8</f>
-        <v>strike*5*defense*4</v>
-      </c>
-    </row>
-    <row r="9" spans="3:6">
-      <c r="C9" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="D9">
+    <row r="1" spans="1:5">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="E9" t="str">
-        <f t="shared" si="0"/>
-        <v>trounce*1</v>
-      </c>
-      <c r="F9" t="str">
-        <f>F8&amp;"*"&amp;E9</f>
-        <v>strike*5*defense*4*trounce*1</v>
+      <c r="C1" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="10">
+        <v>1</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" s="35" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="10"/>
+      <c r="E4" s="35" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -3568,6 +2817,62 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
+  <dimension ref="C7:F9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <sheetData>
+    <row r="7" spans="3:5">
+      <c r="C7" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7">
+        <v>5</v>
+      </c>
+      <c r="E7" t="str">
+        <f t="shared" ref="E7:E9" si="0">C7&amp;"*"&amp;D7</f>
+        <v>strike*5</v>
+      </c>
+    </row>
+    <row r="8" spans="3:6">
+      <c r="C8" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8">
+        <v>4</v>
+      </c>
+      <c r="E8" t="str">
+        <f t="shared" si="0"/>
+        <v>defense*4</v>
+      </c>
+      <c r="F8" t="str">
+        <f>E7&amp;"*"&amp;E8</f>
+        <v>strike*5*defense*4</v>
+      </c>
+    </row>
+    <row r="9" spans="3:6">
+      <c r="C9" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9" t="str">
+        <f t="shared" si="0"/>
+        <v>trounce*1</v>
+      </c>
+      <c r="F9" t="str">
+        <f>F8&amp;"*"&amp;E9</f>
+        <v>strike*5*defense*4*trounce*1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:AA41"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
@@ -3576,70 +2881,70 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="K1" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="R1" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="S1" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="T1" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="U1" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="V1" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="W1" s="14" t="s">
         <v>69</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="R1" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="S1" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="T1" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="U1" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="V1" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="W1" s="14" t="s">
-        <v>77</v>
       </c>
       <c r="X1" s="15"/>
       <c r="Y1" s="15"/>
@@ -3651,165 +2956,165 @@
         <v>5</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="J2" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="K2" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="L2" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="M2" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="N2" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="O2" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="P2" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="Q2" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="R2" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="S2" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="T2" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="U2" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="V2" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="O2" s="4" t="s">
+      <c r="W2" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="X2" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="Y2" s="32" t="s">
         <v>92</v>
       </c>
-      <c r="Q2" s="4" t="s">
+      <c r="Z2" s="32" t="s">
         <v>93</v>
       </c>
-      <c r="R2" s="16" t="s">
+      <c r="AA2" s="33" t="s">
         <v>94</v>
-      </c>
-      <c r="S2" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="T2" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="U2" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="V2" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="W2" s="17" t="s">
-        <v>93</v>
-      </c>
-      <c r="X2" s="18" t="s">
-        <v>99</v>
-      </c>
-      <c r="Y2" s="32" t="s">
-        <v>100</v>
-      </c>
-      <c r="Z2" s="32" t="s">
-        <v>101</v>
-      </c>
-      <c r="AA2" s="33" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="3" ht="14.25" spans="1:27">
       <c r="A3" s="5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="M3" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="O3" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="P3" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Q3" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="R3" s="19" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="S3" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T3" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="U3" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="V3" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="W3" s="20" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="X3" s="21" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Y3" s="21" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z3" s="21" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AA3" s="34" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:27">
@@ -3817,7 +3122,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="C4" s="8">
         <v>10</v>
@@ -3872,17 +3177,17 @@
       <c r="U4" s="8"/>
       <c r="V4" s="8"/>
       <c r="W4" s="23"/>
-      <c r="X4" s="120" t="s">
-        <v>104</v>
+      <c r="X4" s="45" t="s">
+        <v>96</v>
       </c>
       <c r="Y4" s="8" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="Z4" s="8" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="AA4" s="23" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:27">
@@ -3890,7 +3195,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="C5" s="10">
         <v>10</v>
@@ -3946,16 +3251,16 @@
       <c r="V5" s="10"/>
       <c r="W5" s="26"/>
       <c r="X5" s="27" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="Y5" s="10" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="Z5" s="10" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="AA5" s="26" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:27">
@@ -3963,7 +3268,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C6" s="10">
         <v>10</v>
@@ -4019,16 +3324,16 @@
       <c r="V6" s="10"/>
       <c r="W6" s="26"/>
       <c r="X6" s="27" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="Y6" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="Z6" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="Z6" s="10" t="s">
-        <v>113</v>
-      </c>
       <c r="AA6" s="26" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7" spans="1:27">
@@ -4036,7 +3341,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="C7" s="10">
         <v>10</v>
@@ -4092,16 +3397,16 @@
       <c r="V7" s="10"/>
       <c r="W7" s="26"/>
       <c r="X7" s="27" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="Y7" s="10" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="Z7" s="10" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="AA7" s="26" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" spans="1:27">
@@ -4109,7 +3414,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="C8" s="10">
         <v>10</v>
@@ -4165,16 +3470,16 @@
       <c r="V8" s="10"/>
       <c r="W8" s="26"/>
       <c r="X8" s="27" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="Y8" s="10" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="Z8" s="10" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="AA8" s="26" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
     </row>
     <row r="9" spans="1:27">
@@ -4182,7 +3487,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="C9" s="10">
         <v>10</v>
@@ -4238,16 +3543,16 @@
       <c r="V9" s="10"/>
       <c r="W9" s="26"/>
       <c r="X9" s="27" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="Y9" s="10" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="Z9" s="10" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="AA9" s="26" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10" spans="1:27">
@@ -4255,7 +3560,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="C10" s="10">
         <v>10</v>
@@ -4311,16 +3616,16 @@
       <c r="V10" s="10"/>
       <c r="W10" s="26"/>
       <c r="X10" s="27" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="Y10" s="10" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="Z10" s="10" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="AA10" s="26" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
     </row>
     <row r="11" spans="1:27">
@@ -4328,7 +3633,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="C11" s="10">
         <v>10</v>
@@ -4384,16 +3689,16 @@
       <c r="V11" s="10"/>
       <c r="W11" s="26"/>
       <c r="X11" s="27" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="Y11" s="10" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="Z11" s="10" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="AA11" s="26" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
     </row>
     <row r="12" spans="1:27">
@@ -4401,7 +3706,7 @@
         <v>9</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="C12" s="10">
         <v>10</v>
@@ -4457,16 +3762,16 @@
       <c r="V12" s="10"/>
       <c r="W12" s="26"/>
       <c r="X12" s="27" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="Y12" s="10" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="Z12" s="10" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="AA12" s="26" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13" spans="1:27">
@@ -4474,7 +3779,7 @@
         <v>10</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="C13" s="10">
         <v>10</v>
@@ -4530,16 +3835,16 @@
       <c r="V13" s="10"/>
       <c r="W13" s="26"/>
       <c r="X13" s="27" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="Y13" s="10" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="Z13" s="10" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="AA13" s="26" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
     </row>
     <row r="14" spans="1:27">
@@ -4547,7 +3852,7 @@
         <v>11</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="C14" s="10">
         <v>10</v>
@@ -4603,16 +3908,16 @@
       <c r="V14" s="10"/>
       <c r="W14" s="26"/>
       <c r="X14" s="27" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="Y14" s="10" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="Z14" s="10" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="AA14" s="26" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
     </row>
     <row r="15" spans="1:27">
@@ -4620,7 +3925,7 @@
         <v>12</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="C15" s="10">
         <v>10</v>
@@ -4676,16 +3981,16 @@
       <c r="V15" s="10"/>
       <c r="W15" s="26"/>
       <c r="X15" s="27" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="Y15" s="10" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="Z15" s="10" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="AA15" s="26" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
     </row>
     <row r="16" spans="1:27">
@@ -4693,7 +3998,7 @@
         <v>13</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="C16" s="10">
         <v>10</v>
@@ -4749,16 +4054,16 @@
       <c r="V16" s="10"/>
       <c r="W16" s="26"/>
       <c r="X16" s="27" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="Y16" s="10" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="Z16" s="10" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="AA16" s="26" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17" spans="1:27">
@@ -4766,7 +4071,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="C17" s="10">
         <v>10</v>
@@ -4822,16 +4127,16 @@
       <c r="V17" s="10"/>
       <c r="W17" s="26"/>
       <c r="X17" s="27" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="Y17" s="10" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="Z17" s="10" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="AA17" s="26" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
     </row>
     <row r="18" spans="1:27">
@@ -4839,7 +4144,7 @@
         <v>15</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="C18" s="10">
         <v>10</v>
@@ -4895,16 +4200,16 @@
       <c r="V18" s="10"/>
       <c r="W18" s="26"/>
       <c r="X18" s="27" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="Y18" s="10" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="Z18" s="10" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="AA18" s="26" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
     </row>
     <row r="19" spans="1:27">
@@ -4912,7 +4217,7 @@
         <v>16</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="C19" s="10">
         <v>10</v>
@@ -4968,16 +4273,16 @@
       <c r="V19" s="10"/>
       <c r="W19" s="26"/>
       <c r="X19" s="27" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="Y19" s="10" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="Z19" s="10" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="AA19" s="26" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
     </row>
     <row r="20" spans="1:27">
@@ -4985,7 +4290,7 @@
         <v>17</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="C20" s="10">
         <v>10</v>
@@ -5041,16 +4346,16 @@
       <c r="V20" s="10"/>
       <c r="W20" s="26"/>
       <c r="X20" s="27" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="Y20" s="10" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="Z20" s="10" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="AA20" s="26" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="21" spans="1:27">
@@ -5058,7 +4363,7 @@
         <v>18</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="C21" s="10">
         <v>10</v>
@@ -5114,16 +4419,16 @@
       <c r="V21" s="10"/>
       <c r="W21" s="26"/>
       <c r="X21" s="27" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="Y21" s="10" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="Z21" s="10" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="AA21" s="26" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
     </row>
     <row r="22" spans="1:27">
@@ -5131,7 +4436,7 @@
         <v>19</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="C22" s="10">
         <v>10</v>
@@ -5187,16 +4492,16 @@
       <c r="V22" s="10"/>
       <c r="W22" s="26"/>
       <c r="X22" s="27" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="Y22" s="10" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="Z22" s="10" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="AA22" s="26" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
     </row>
     <row r="23" spans="1:27">
@@ -5204,7 +4509,7 @@
         <v>20</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="C23" s="10">
         <v>10</v>
@@ -5260,16 +4565,16 @@
       <c r="V23" s="10"/>
       <c r="W23" s="26"/>
       <c r="X23" s="27" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="Y23" s="10" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="Z23" s="10" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="AA23" s="26" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
     </row>
     <row r="24" spans="1:27">
@@ -5277,7 +4582,7 @@
         <v>21</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="C24" s="10">
         <v>10</v>
@@ -5333,16 +4638,16 @@
       <c r="V24" s="10"/>
       <c r="W24" s="26"/>
       <c r="X24" s="27" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="Y24" s="10" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="Z24" s="10" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="AA24" s="26" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
     </row>
     <row r="25" spans="1:27">
@@ -5350,7 +4655,7 @@
         <v>22</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="C25" s="10">
         <v>10</v>
@@ -5406,16 +4711,16 @@
       <c r="V25" s="10"/>
       <c r="W25" s="26"/>
       <c r="X25" s="27" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="Y25" s="10" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="Z25" s="10" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="AA25" s="26" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
     </row>
     <row r="26" spans="1:27">
@@ -5423,7 +4728,7 @@
         <v>23</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="C26" s="10">
         <v>10</v>
@@ -5479,16 +4784,16 @@
       <c r="V26" s="10"/>
       <c r="W26" s="26"/>
       <c r="X26" s="27" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="Y26" s="10" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="Z26" s="10" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="AA26" s="26" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
     </row>
     <row r="27" spans="1:27">
@@ -5496,7 +4801,7 @@
         <v>24</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="C27" s="10">
         <v>10</v>
@@ -5552,16 +4857,16 @@
       <c r="V27" s="10"/>
       <c r="W27" s="26"/>
       <c r="X27" s="27" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="Y27" s="10" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="Z27" s="10" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="AA27" s="26" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
     </row>
     <row r="28" spans="1:27">
@@ -5569,7 +4874,7 @@
         <v>25</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="C28" s="10">
         <v>10</v>
@@ -5625,16 +4930,16 @@
       <c r="V28" s="10"/>
       <c r="W28" s="26"/>
       <c r="X28" s="27" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="Y28" s="10" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="Z28" s="10" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="AA28" s="26" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
     </row>
     <row r="29" spans="1:27">
@@ -5642,7 +4947,7 @@
         <v>26</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="C29" s="10">
         <v>10</v>
@@ -5698,16 +5003,16 @@
       <c r="V29" s="10"/>
       <c r="W29" s="26"/>
       <c r="X29" s="27" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="Y29" s="10" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="Z29" s="10" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="AA29" s="26" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
     </row>
     <row r="30" spans="1:27">
@@ -5715,7 +5020,7 @@
         <v>27</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="C30" s="10">
         <v>10</v>
@@ -5771,16 +5076,16 @@
       <c r="V30" s="10"/>
       <c r="W30" s="26"/>
       <c r="X30" s="27" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="Y30" s="10" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="Z30" s="10" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="AA30" s="26" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
     </row>
     <row r="31" spans="1:27">
@@ -5788,7 +5093,7 @@
         <v>28</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="C31" s="10">
         <v>10</v>
@@ -5844,16 +5149,16 @@
       <c r="V31" s="10"/>
       <c r="W31" s="26"/>
       <c r="X31" s="27" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="Y31" s="10" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="Z31" s="10" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="AA31" s="26" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
     </row>
     <row r="32" spans="1:27">
@@ -5861,7 +5166,7 @@
         <v>29</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="C32" s="10">
         <v>10</v>
@@ -5917,16 +5222,16 @@
       <c r="V32" s="10"/>
       <c r="W32" s="26"/>
       <c r="X32" s="27" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="Y32" s="10" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="Z32" s="10" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="AA32" s="26" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
     </row>
     <row r="33" spans="1:27">
@@ -5934,7 +5239,7 @@
         <v>30</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="C33" s="10">
         <v>10</v>
@@ -5990,16 +5295,16 @@
       <c r="V33" s="10"/>
       <c r="W33" s="26"/>
       <c r="X33" s="27" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="Y33" s="10" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="Z33" s="10" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="AA33" s="26" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
     </row>
     <row r="34" spans="1:27">
@@ -6007,7 +5312,7 @@
         <v>31</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="C34" s="10">
         <v>10</v>
@@ -6063,16 +5368,16 @@
       <c r="V34" s="10"/>
       <c r="W34" s="26"/>
       <c r="X34" s="27" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="Y34" s="10" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="Z34" s="10" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="AA34" s="26" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
     </row>
     <row r="35" spans="1:27">
@@ -6080,7 +5385,7 @@
         <v>32</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="C35" s="10">
         <v>10</v>
@@ -6136,16 +5441,16 @@
       <c r="V35" s="10"/>
       <c r="W35" s="26"/>
       <c r="X35" s="27" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="Y35" s="10" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="Z35" s="10" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="AA35" s="26" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
     </row>
     <row r="36" spans="1:27">
@@ -6153,7 +5458,7 @@
         <v>33</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="C36" s="10">
         <v>10</v>
@@ -6209,16 +5514,16 @@
       <c r="V36" s="10"/>
       <c r="W36" s="26"/>
       <c r="X36" s="27" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="Y36" s="10" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="Z36" s="10" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="AA36" s="26" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
     </row>
     <row r="37" spans="1:27">
@@ -6226,7 +5531,7 @@
         <v>34</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="C37" s="10">
         <v>10</v>
@@ -6282,16 +5587,16 @@
       <c r="V37" s="10"/>
       <c r="W37" s="26"/>
       <c r="X37" s="27" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="Y37" s="10" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="Z37" s="10" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="AA37" s="26" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
     </row>
     <row r="38" spans="1:27">
@@ -6299,7 +5604,7 @@
         <v>35</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="C38" s="10">
         <v>10</v>
@@ -6355,16 +5660,16 @@
       <c r="V38" s="10"/>
       <c r="W38" s="26"/>
       <c r="X38" s="27" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="Y38" s="10" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="Z38" s="10" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="AA38" s="26" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
     </row>
     <row r="39" spans="1:27">
@@ -6372,7 +5677,7 @@
         <v>36</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="C39" s="10">
         <v>10</v>
@@ -6428,16 +5733,16 @@
       <c r="V39" s="10"/>
       <c r="W39" s="26"/>
       <c r="X39" s="27" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="Y39" s="10" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="Z39" s="10" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="AA39" s="26" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
     </row>
     <row r="40" spans="1:27">
@@ -6445,7 +5750,7 @@
         <v>37</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="C40" s="10">
         <v>10</v>
@@ -6501,16 +5806,16 @@
       <c r="V40" s="10"/>
       <c r="W40" s="26"/>
       <c r="X40" s="27" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="Y40" s="10" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="Z40" s="10" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="AA40" s="26" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
     </row>
     <row r="41" ht="14.25" spans="1:27">
@@ -6518,7 +5823,7 @@
         <v>38</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="C41" s="12">
         <v>10</v>
@@ -6574,16 +5879,16 @@
       <c r="V41" s="12"/>
       <c r="W41" s="29"/>
       <c r="X41" s="30" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="Y41" s="12" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="Z41" s="12" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="AA41" s="29" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>

--- a/xlsdir/配置-总表.xlsx
+++ b/xlsdir/配置-总表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="18375" tabRatio="673" activeTab="4"/>
+    <workbookView windowWidth="27930" windowHeight="12975" tabRatio="673" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="character|角色" sheetId="32" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="268">
   <si>
     <t>ID</t>
   </si>
@@ -110,6 +110,9 @@
   </si>
   <si>
     <t>card_type</t>
+  </si>
+  <si>
+    <t>cost</t>
   </si>
   <si>
     <t>卡牌名</t>
@@ -118,6 +121,9 @@
     <t>卡牌类型
 1攻击
 2技能</t>
+  </si>
+  <si>
+    <t>成本</t>
   </si>
   <si>
     <t>卡牌描述</t>
@@ -1922,7 +1928,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2050,12 +2056,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1" quotePrefix="1">
@@ -2425,10 +2425,10 @@
       <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="43" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="43" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2442,10 +2442,10 @@
       <c r="C2" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="43" t="s">
+      <c r="D2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="43" t="s">
+      <c r="E2" s="4" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2459,10 +2459,10 @@
       <c r="C3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="43" t="s">
+      <c r="D3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="43" t="s">
+      <c r="E3" s="4" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2476,7 +2476,7 @@
       <c r="C4" s="10">
         <v>80</v>
       </c>
-      <c r="D4" s="44">
+      <c r="D4" s="10">
         <v>0</v>
       </c>
       <c r="E4" s="10" t="s">
@@ -2639,14 +2639,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="3"/>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="4"/>
   <cols>
     <col min="2" max="3" width="11.625" customWidth="1"/>
-    <col min="4" max="4" width="67.25" customWidth="1"/>
+    <col min="4" max="4" width="5.875" customWidth="1"/>
+    <col min="5" max="5" width="67.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -2657,24 +2658,30 @@
         <v>28</v>
       </c>
       <c r="D1" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" ht="40.5" spans="1:4">
+    <row r="2" ht="40.5" spans="1:5">
       <c r="A2" s="36" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="36" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C2" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="D2" s="4" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="D2" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" s="4" t="s">
         <v>10</v>
       </c>
@@ -2685,49 +2692,61 @@
         <v>11</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>11</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" s="10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B4" s="35" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C4" s="10">
         <v>1</v>
       </c>
-      <c r="D4" s="10" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+      <c r="D4" s="10">
+        <v>1</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" s="10" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B5" s="35" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C5" s="10">
         <v>2</v>
       </c>
-      <c r="D5" s="10" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+      <c r="D5" s="10">
+        <v>1</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" s="10" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B6" s="35" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C6" s="10">
         <v>1</v>
       </c>
-      <c r="D6" s="10" t="s">
-        <v>40</v>
+      <c r="D6" s="10">
+        <v>2</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -2750,13 +2769,13 @@
         <v>1</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -2764,16 +2783,16 @@
         <v>0</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -2798,7 +2817,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C4" s="35" t="s">
         <v>14</v>
@@ -2822,7 +2841,7 @@
   <sheetData>
     <row r="7" spans="3:5">
       <c r="C7" s="10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D7">
         <v>5</v>
@@ -2834,7 +2853,7 @@
     </row>
     <row r="8" spans="3:6">
       <c r="C8" s="10" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D8">
         <v>4</v>
@@ -2850,7 +2869,7 @@
     </row>
     <row r="9" spans="3:6">
       <c r="C9" s="10" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -2884,67 +2903,67 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="Q1" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="R1" s="13" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="S1" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="T1" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="U1" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="V1" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="W1" s="14" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="X1" s="15"/>
       <c r="Y1" s="15"/>
@@ -2956,82 +2975,82 @@
         <v>5</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="R2" s="16" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="S2" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="T2" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="U2" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="V2" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="W2" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="T2" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="U2" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="V2" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="W2" s="17" t="s">
-        <v>85</v>
-      </c>
       <c r="X2" s="18" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="Y2" s="32" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="Z2" s="32" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AA2" s="33" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" ht="14.25" spans="1:27">
@@ -3122,7 +3141,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C4" s="8">
         <v>10</v>
@@ -3177,17 +3196,17 @@
       <c r="U4" s="8"/>
       <c r="V4" s="8"/>
       <c r="W4" s="23"/>
-      <c r="X4" s="45" t="s">
-        <v>96</v>
+      <c r="X4" s="43" t="s">
+        <v>98</v>
       </c>
       <c r="Y4" s="8" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="Z4" s="8" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AA4" s="23" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:27">
@@ -3195,7 +3214,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C5" s="10">
         <v>10</v>
@@ -3251,16 +3270,16 @@
       <c r="V5" s="10"/>
       <c r="W5" s="26"/>
       <c r="X5" s="27" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="Y5" s="10" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="Z5" s="10" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AA5" s="26" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6" spans="1:27">
@@ -3268,7 +3287,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C6" s="10">
         <v>10</v>
@@ -3324,16 +3343,16 @@
       <c r="V6" s="10"/>
       <c r="W6" s="26"/>
       <c r="X6" s="27" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="Y6" s="10" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="Z6" s="10" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="AA6" s="26" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="7" spans="1:27">
@@ -3341,7 +3360,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C7" s="10">
         <v>10</v>
@@ -3397,16 +3416,16 @@
       <c r="V7" s="10"/>
       <c r="W7" s="26"/>
       <c r="X7" s="27" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="Y7" s="10" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="Z7" s="10" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="AA7" s="26" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="8" spans="1:27">
@@ -3414,7 +3433,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C8" s="10">
         <v>10</v>
@@ -3470,16 +3489,16 @@
       <c r="V8" s="10"/>
       <c r="W8" s="26"/>
       <c r="X8" s="27" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="Y8" s="10" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="Z8" s="10" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AA8" s="26" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="9" spans="1:27">
@@ -3487,7 +3506,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C9" s="10">
         <v>10</v>
@@ -3543,16 +3562,16 @@
       <c r="V9" s="10"/>
       <c r="W9" s="26"/>
       <c r="X9" s="27" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="Y9" s="10" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="Z9" s="10" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="AA9" s="26" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10" spans="1:27">
@@ -3560,7 +3579,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C10" s="10">
         <v>10</v>
@@ -3616,16 +3635,16 @@
       <c r="V10" s="10"/>
       <c r="W10" s="26"/>
       <c r="X10" s="27" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="Y10" s="10" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="Z10" s="10" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="AA10" s="26" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="11" spans="1:27">
@@ -3633,7 +3652,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C11" s="10">
         <v>10</v>
@@ -3689,16 +3708,16 @@
       <c r="V11" s="10"/>
       <c r="W11" s="26"/>
       <c r="X11" s="27" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="Y11" s="10" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="Z11" s="10" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="AA11" s="26" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12" spans="1:27">
@@ -3706,7 +3725,7 @@
         <v>9</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C12" s="10">
         <v>10</v>
@@ -3762,16 +3781,16 @@
       <c r="V12" s="10"/>
       <c r="W12" s="26"/>
       <c r="X12" s="27" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="Y12" s="10" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="Z12" s="10" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="AA12" s="26" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="13" spans="1:27">
@@ -3779,7 +3798,7 @@
         <v>10</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C13" s="10">
         <v>10</v>
@@ -3835,16 +3854,16 @@
       <c r="V13" s="10"/>
       <c r="W13" s="26"/>
       <c r="X13" s="27" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="Y13" s="10" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="Z13" s="10" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AA13" s="26" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14" spans="1:27">
@@ -3852,7 +3871,7 @@
         <v>11</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C14" s="10">
         <v>10</v>
@@ -3908,16 +3927,16 @@
       <c r="V14" s="10"/>
       <c r="W14" s="26"/>
       <c r="X14" s="27" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="Y14" s="10" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="Z14" s="10" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="AA14" s="26" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="15" spans="1:27">
@@ -3925,7 +3944,7 @@
         <v>12</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C15" s="10">
         <v>10</v>
@@ -3981,16 +4000,16 @@
       <c r="V15" s="10"/>
       <c r="W15" s="26"/>
       <c r="X15" s="27" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="Y15" s="10" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="Z15" s="10" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="AA15" s="26" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="16" spans="1:27">
@@ -3998,7 +4017,7 @@
         <v>13</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C16" s="10">
         <v>10</v>
@@ -4054,16 +4073,16 @@
       <c r="V16" s="10"/>
       <c r="W16" s="26"/>
       <c r="X16" s="27" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="Y16" s="10" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="Z16" s="10" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="AA16" s="26" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17" spans="1:27">
@@ -4071,7 +4090,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C17" s="10">
         <v>10</v>
@@ -4127,16 +4146,16 @@
       <c r="V17" s="10"/>
       <c r="W17" s="26"/>
       <c r="X17" s="27" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="Y17" s="10" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="Z17" s="10" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AA17" s="26" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="18" spans="1:27">
@@ -4144,7 +4163,7 @@
         <v>15</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C18" s="10">
         <v>10</v>
@@ -4200,16 +4219,16 @@
       <c r="V18" s="10"/>
       <c r="W18" s="26"/>
       <c r="X18" s="27" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="Y18" s="10" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="Z18" s="10" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="AA18" s="26" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="19" spans="1:27">
@@ -4217,7 +4236,7 @@
         <v>16</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C19" s="10">
         <v>10</v>
@@ -4273,16 +4292,16 @@
       <c r="V19" s="10"/>
       <c r="W19" s="26"/>
       <c r="X19" s="27" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="Y19" s="10" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="Z19" s="10" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="AA19" s="26" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="20" spans="1:27">
@@ -4290,7 +4309,7 @@
         <v>17</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C20" s="10">
         <v>10</v>
@@ -4346,16 +4365,16 @@
       <c r="V20" s="10"/>
       <c r="W20" s="26"/>
       <c r="X20" s="27" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Y20" s="10" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Z20" s="10" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="AA20" s="26" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21" spans="1:27">
@@ -4363,7 +4382,7 @@
         <v>18</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C21" s="10">
         <v>10</v>
@@ -4419,16 +4438,16 @@
       <c r="V21" s="10"/>
       <c r="W21" s="26"/>
       <c r="X21" s="27" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Y21" s="10" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Z21" s="10" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AA21" s="26" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="22" spans="1:27">
@@ -4436,7 +4455,7 @@
         <v>19</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C22" s="10">
         <v>10</v>
@@ -4492,16 +4511,16 @@
       <c r="V22" s="10"/>
       <c r="W22" s="26"/>
       <c r="X22" s="27" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Y22" s="10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Z22" s="10" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="AA22" s="26" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="23" spans="1:27">
@@ -4509,7 +4528,7 @@
         <v>20</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C23" s="10">
         <v>10</v>
@@ -4565,16 +4584,16 @@
       <c r="V23" s="10"/>
       <c r="W23" s="26"/>
       <c r="X23" s="27" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Y23" s="10" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Z23" s="10" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="AA23" s="26" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="24" spans="1:27">
@@ -4582,7 +4601,7 @@
         <v>21</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C24" s="10">
         <v>10</v>
@@ -4638,16 +4657,16 @@
       <c r="V24" s="10"/>
       <c r="W24" s="26"/>
       <c r="X24" s="27" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Y24" s="10" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Z24" s="10" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="AA24" s="26" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="25" spans="1:27">
@@ -4655,7 +4674,7 @@
         <v>22</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C25" s="10">
         <v>10</v>
@@ -4711,16 +4730,16 @@
       <c r="V25" s="10"/>
       <c r="W25" s="26"/>
       <c r="X25" s="27" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Y25" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Z25" s="10" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="AA25" s="26" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="26" spans="1:27">
@@ -4728,7 +4747,7 @@
         <v>23</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C26" s="10">
         <v>10</v>
@@ -4784,16 +4803,16 @@
       <c r="V26" s="10"/>
       <c r="W26" s="26"/>
       <c r="X26" s="27" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Y26" s="10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Z26" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="AA26" s="26" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="27" spans="1:27">
@@ -4801,7 +4820,7 @@
         <v>24</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C27" s="10">
         <v>10</v>
@@ -4857,16 +4876,16 @@
       <c r="V27" s="10"/>
       <c r="W27" s="26"/>
       <c r="X27" s="27" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Y27" s="10" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Z27" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AA27" s="26" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="28" spans="1:27">
@@ -4874,7 +4893,7 @@
         <v>25</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C28" s="10">
         <v>10</v>
@@ -4930,16 +4949,16 @@
       <c r="V28" s="10"/>
       <c r="W28" s="26"/>
       <c r="X28" s="27" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Y28" s="10" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Z28" s="10" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="AA28" s="26" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="29" spans="1:27">
@@ -4947,7 +4966,7 @@
         <v>26</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C29" s="10">
         <v>10</v>
@@ -5003,16 +5022,16 @@
       <c r="V29" s="10"/>
       <c r="W29" s="26"/>
       <c r="X29" s="27" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Y29" s="10" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Z29" s="10" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AA29" s="26" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="30" spans="1:27">
@@ -5020,7 +5039,7 @@
         <v>27</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C30" s="10">
         <v>10</v>
@@ -5076,16 +5095,16 @@
       <c r="V30" s="10"/>
       <c r="W30" s="26"/>
       <c r="X30" s="27" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Y30" s="10" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Z30" s="10" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AA30" s="26" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="31" spans="1:27">
@@ -5093,7 +5112,7 @@
         <v>28</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C31" s="10">
         <v>10</v>
@@ -5149,16 +5168,16 @@
       <c r="V31" s="10"/>
       <c r="W31" s="26"/>
       <c r="X31" s="27" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Y31" s="10" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Z31" s="10" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AA31" s="26" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="32" spans="1:27">
@@ -5166,7 +5185,7 @@
         <v>29</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C32" s="10">
         <v>10</v>
@@ -5222,16 +5241,16 @@
       <c r="V32" s="10"/>
       <c r="W32" s="26"/>
       <c r="X32" s="27" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Y32" s="10" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Z32" s="10" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AA32" s="26" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="33" spans="1:27">
@@ -5239,7 +5258,7 @@
         <v>30</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C33" s="10">
         <v>10</v>
@@ -5295,16 +5314,16 @@
       <c r="V33" s="10"/>
       <c r="W33" s="26"/>
       <c r="X33" s="27" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Y33" s="10" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Z33" s="10" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="AA33" s="26" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="34" spans="1:27">
@@ -5312,7 +5331,7 @@
         <v>31</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C34" s="10">
         <v>10</v>
@@ -5368,16 +5387,16 @@
       <c r="V34" s="10"/>
       <c r="W34" s="26"/>
       <c r="X34" s="27" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Y34" s="10" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Z34" s="10" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="AA34" s="26" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="35" spans="1:27">
@@ -5385,7 +5404,7 @@
         <v>32</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C35" s="10">
         <v>10</v>
@@ -5441,16 +5460,16 @@
       <c r="V35" s="10"/>
       <c r="W35" s="26"/>
       <c r="X35" s="27" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Y35" s="10" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Z35" s="10" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AA35" s="26" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="36" spans="1:27">
@@ -5458,7 +5477,7 @@
         <v>33</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C36" s="10">
         <v>10</v>
@@ -5514,16 +5533,16 @@
       <c r="V36" s="10"/>
       <c r="W36" s="26"/>
       <c r="X36" s="27" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Y36" s="10" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Z36" s="10" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AA36" s="26" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="37" spans="1:27">
@@ -5531,7 +5550,7 @@
         <v>34</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C37" s="10">
         <v>10</v>
@@ -5587,16 +5606,16 @@
       <c r="V37" s="10"/>
       <c r="W37" s="26"/>
       <c r="X37" s="27" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Y37" s="10" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Z37" s="10" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AA37" s="26" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="38" spans="1:27">
@@ -5604,7 +5623,7 @@
         <v>35</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C38" s="10">
         <v>10</v>
@@ -5660,16 +5679,16 @@
       <c r="V38" s="10"/>
       <c r="W38" s="26"/>
       <c r="X38" s="27" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Y38" s="10" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Z38" s="10" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AA38" s="26" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="39" spans="1:27">
@@ -5677,7 +5696,7 @@
         <v>36</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C39" s="10">
         <v>10</v>
@@ -5733,16 +5752,16 @@
       <c r="V39" s="10"/>
       <c r="W39" s="26"/>
       <c r="X39" s="27" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Y39" s="10" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Z39" s="10" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AA39" s="26" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="40" spans="1:27">
@@ -5750,7 +5769,7 @@
         <v>37</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C40" s="10">
         <v>10</v>
@@ -5806,16 +5825,16 @@
       <c r="V40" s="10"/>
       <c r="W40" s="26"/>
       <c r="X40" s="27" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Y40" s="10" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Z40" s="10" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AA40" s="26" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="41" ht="14.25" spans="1:27">
@@ -5823,7 +5842,7 @@
         <v>38</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C41" s="12">
         <v>10</v>
@@ -5879,16 +5898,16 @@
       <c r="V41" s="12"/>
       <c r="W41" s="29"/>
       <c r="X41" s="30" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Y41" s="12" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Z41" s="12" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AA41" s="29" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/xlsdir/配置-总表.xlsx
+++ b/xlsdir/配置-总表.xlsx
@@ -1,29 +1,49 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26924"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\24102\Documents\project-sx\xlsdir\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1540E82-9635-4A70-A1F5-A54521DC30CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="27930" windowHeight="12975" tabRatio="673" activeTab="3"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="673" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="character|角色" sheetId="32" r:id="rId1"/>
-    <sheet name="hero|玩家角色" sheetId="27" r:id="rId2"/>
-    <sheet name="monster|魔物" sheetId="28" r:id="rId3"/>
-    <sheet name="card|卡牌" sheetId="29" r:id="rId4"/>
-    <sheet name="combat|战斗" sheetId="31" r:id="rId5"/>
-    <sheet name="Sheet3" sheetId="30" r:id="rId6"/>
-    <sheet name="Sheet1" sheetId="11" state="hidden" r:id="rId7"/>
+    <sheet name="combat|战斗" sheetId="31" r:id="rId1"/>
+    <sheet name="character|角色" sheetId="32" r:id="rId2"/>
+    <sheet name="hero|玩家角色" sheetId="27" r:id="rId3"/>
+    <sheet name="monster|魔物" sheetId="28" r:id="rId4"/>
+    <sheet name="card|卡牌" sheetId="29" r:id="rId5"/>
+    <sheet name="ability|技能" sheetId="33" r:id="rId6"/>
+    <sheet name="ability_effect|技能效果" sheetId="34" r:id="rId7"/>
+    <sheet name="attribute|属性" sheetId="35" r:id="rId8"/>
+    <sheet name="Sheet1" sheetId="11" r:id="rId9"/>
+    <sheet name="sheet2" sheetId="30" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'monster|魔物'!$A$1:$B$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'monster|魔物'!$A$1:$B$4</definedName>
   </definedNames>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="340">
   <si>
     <t>ID</t>
   </si>
@@ -936,18 +956,267 @@
   <si>
     <t>抹杀者</t>
   </si>
+  <si>
+    <t>texture</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>卡牌图标</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>res://asserts/cards/card_icons/card_defense.png</t>
+  </si>
+  <si>
+    <t>res://asserts/cards/card_icons/card_strike.png</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>res://asserts/cards/card_icons/card_trounce.png</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>注释</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能名</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>ability_name</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能描述</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>effect_name</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>给与2层易伤</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>造成8点伤害</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能效果名</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能效果描述</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>给予易伤</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>trounce_01</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>trounce_02</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>BaseValue</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>MaxHealth</t>
+  </si>
+  <si>
+    <t>角色的最大生命值</t>
+  </si>
+  <si>
+    <t>CurrentHealth</t>
+  </si>
+  <si>
+    <t>角色当前的生命值</t>
+  </si>
+  <si>
+    <t>MaxEnergy</t>
+  </si>
+  <si>
+    <t>角色可以累积的最大能量值</t>
+  </si>
+  <si>
+    <t>CurrentEnergy</t>
+  </si>
+  <si>
+    <t>角色当前的能量值</t>
+  </si>
+  <si>
+    <t>BaseAttack</t>
+  </si>
+  <si>
+    <t>角色基础的攻击力</t>
+  </si>
+  <si>
+    <t>BaseDefense</t>
+  </si>
+  <si>
+    <t>角色基础的防御值</t>
+  </si>
+  <si>
+    <t>Gold</t>
+  </si>
+  <si>
+    <t>角色持有的金币数量</t>
+  </si>
+  <si>
+    <t>Strength</t>
+  </si>
+  <si>
+    <t>增加角色攻击力的强化值</t>
+  </si>
+  <si>
+    <t>Dexterity</t>
+  </si>
+  <si>
+    <t>影响角色行动速度或攻击速度的属性</t>
+  </si>
+  <si>
+    <t>MagicPower</t>
+  </si>
+  <si>
+    <t>影响角色魔法或特殊技能效果的属性</t>
+  </si>
+  <si>
+    <t>Shield</t>
+  </si>
+  <si>
+    <t>充当额外生命值的保护层</t>
+  </si>
+  <si>
+    <t>属性描述</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>float</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>属性名</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>最大生命值</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>当前生命值</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>最大能量值</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>当前能量值</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击力</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>防御力</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>金币</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>力量</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>敏捷</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>魔法</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>护盾</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>最小值</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>最大值</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>可见性</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>visibility</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>max</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>min</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>bool</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 能量消耗</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 效果ID列表</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 目标类型</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 触发时机</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 持续回合</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 稀有度</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 类别</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="21">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -964,104 +1233,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1069,46 +1251,38 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <sz val="9"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <sz val="9.6"/>
+      <color rgb="FF374151"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <sz val="9.6"/>
+      <color rgb="FF374151"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <sz val="9.6"/>
+      <color rgb="FF374151"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1117,192 +1291,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor rgb="FFF7F7F8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="37">
+  <borders count="29">
     <border>
       <left/>
       <right/>
@@ -1680,255 +1674,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="31" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="32" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="33" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="32" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="34" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="35" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="36" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2001,9 +1753,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -2034,9 +1783,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -2046,10 +1792,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2058,65 +1804,51 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1" quotePrefix="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="19" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2130,7 +1862,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="CCE8CF"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -2403,19 +2135,151 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="10">
+        <v>1</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="C7:F9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="7" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C7" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7">
+        <v>5</v>
+      </c>
+      <c r="E7" t="str">
+        <f t="shared" ref="E7:E9" si="0">C7&amp;"*"&amp;D7</f>
+        <v>strike*5</v>
+      </c>
+    </row>
+    <row r="8" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C8" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8">
+        <v>4</v>
+      </c>
+      <c r="E8" t="str">
+        <f t="shared" si="0"/>
+        <v>defense*4</v>
+      </c>
+      <c r="F8" t="str">
+        <f>E7&amp;"*"&amp;E8</f>
+        <v>strike*5*defense*4</v>
+      </c>
+    </row>
+    <row r="9" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C9" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9" t="str">
+        <f t="shared" si="0"/>
+        <v>trounce*1</v>
+      </c>
+      <c r="F9" t="str">
+        <f>F8&amp;"*"&amp;E9</f>
+        <v>strike*5*defense*4*trounce*1</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="5" max="5" width="37" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -2432,14 +2296,14 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="36" t="s">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="36" t="s">
+      <c r="B2" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="36" t="s">
+      <c r="C2" s="34" t="s">
         <v>7</v>
       </c>
       <c r="D2" s="4" t="s">
@@ -2449,7 +2313,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>10</v>
       </c>
@@ -2466,7 +2330,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="10">
         <v>1</v>
       </c>
@@ -2483,419 +2347,811 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="35" t="s">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="35" t="s">
+      <c r="B5" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="35">
+      <c r="C5" s="10">
         <v>50</v>
       </c>
-      <c r="D5" s="35">
-        <v>10</v>
-      </c>
-      <c r="E5" s="35" t="s">
+      <c r="D5" s="10">
+        <v>10</v>
+      </c>
+      <c r="E5" s="10" t="s">
         <v>16</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultColWidth="8.85833333333333" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="4"/>
-  <cols>
-    <col min="1" max="1" width="8.33333333333333" style="42" customWidth="1"/>
-    <col min="2" max="2" width="11.8916666666667" customWidth="1"/>
-    <col min="3" max="3" width="31.5" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-    </row>
-    <row r="2" s="41" customFormat="1" spans="1:5">
-      <c r="A2" s="36" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="36" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" s="36" t="s">
-        <v>21</v>
-      </c>
-      <c r="E2" s="36" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="10">
-        <v>1</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" s="10">
-        <v>99</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>25</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.66666666666667" customWidth="1"/>
-    <col min="2" max="2" width="11.4666666666667" style="21" customWidth="1"/>
+    <col min="1" max="1" width="8.33203125" style="40" customWidth="1"/>
+    <col min="2" max="2" width="11.86328125" customWidth="1"/>
+    <col min="3" max="3" width="31.46484375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="37" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="38" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+    </row>
+    <row r="2" spans="1:5" s="39" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="34" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="34" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="34" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" s="34" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="10">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="37" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="38" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="38" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="39" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="40" t="s">
-        <v>15</v>
+      <c r="B4" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="10">
+        <v>99</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="3" width="11.625" customWidth="1"/>
-    <col min="4" max="4" width="5.875" customWidth="1"/>
-    <col min="5" max="5" width="67.25" customWidth="1"/>
+    <col min="1" max="1" width="7.6640625" customWidth="1"/>
+    <col min="2" max="2" width="11.46484375" style="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" ht="40.5" spans="1:5">
-      <c r="A2" s="36" t="s">
-        <v>5</v>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="36" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="35" t="s">
+        <v>0</v>
       </c>
       <c r="B2" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="C2" s="36" t="s">
-        <v>31</v>
-      </c>
-      <c r="D2" s="36" t="s">
-        <v>32</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="B4" s="35" t="s">
-        <v>35</v>
-      </c>
-      <c r="C4" s="10">
-        <v>1</v>
-      </c>
-      <c r="D4" s="10">
-        <v>1</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="B5" s="35" t="s">
-        <v>38</v>
-      </c>
-      <c r="C5" s="10">
-        <v>2</v>
-      </c>
-      <c r="D5" s="10">
-        <v>1</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="B6" s="35" t="s">
-        <v>41</v>
-      </c>
-      <c r="C6" s="10">
-        <v>1</v>
-      </c>
-      <c r="D6" s="10">
-        <v>2</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>42</v>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="35" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="36" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="37" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="38" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="3" width="11.59765625" customWidth="1"/>
+    <col min="4" max="4" width="5.86328125" customWidth="1"/>
+    <col min="5" max="5" width="24.6640625" customWidth="1"/>
+    <col min="6" max="6" width="56.19921875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="42" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="A2" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="34" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2" s="43" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="42" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" s="10">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="10">
+      <c r="D4" s="10">
         <v>1</v>
       </c>
-      <c r="B4" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="C4" s="35" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="10"/>
-      <c r="E4" s="35" t="s">
-        <v>14</v>
+      <c r="E4" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4" s="44" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" s="10">
+        <v>2</v>
+      </c>
+      <c r="D5" s="10">
+        <v>1</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="10">
+        <v>1</v>
+      </c>
+      <c r="D6" s="10">
+        <v>2</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="F6" s="44" t="s">
+        <v>273</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="C7:F9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B33D2148-8412-4B4D-9F87-3CA753CB34C0}">
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="16.73046875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.265625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="7" spans="3:5">
-      <c r="C7" s="10" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="42" t="s">
+        <v>274</v>
+      </c>
+      <c r="C1" s="42" t="s">
+        <v>277</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="42" t="s">
+        <v>274</v>
+      </c>
+      <c r="C2" s="42" t="s">
+        <v>276</v>
+      </c>
+      <c r="D2" s="42" t="s">
+        <v>278</v>
+      </c>
+      <c r="E2" s="47" t="s">
+        <v>333</v>
+      </c>
+      <c r="F2" s="47" t="s">
+        <v>334</v>
+      </c>
+      <c r="G2" s="47" t="s">
+        <v>335</v>
+      </c>
+      <c r="H2" s="47" t="s">
+        <v>336</v>
+      </c>
+      <c r="I2" s="47" t="s">
+        <v>337</v>
+      </c>
+      <c r="J2" s="47" t="s">
+        <v>338</v>
+      </c>
+      <c r="K2" s="47" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="42" t="s">
+        <v>274</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="D7">
-        <v>5</v>
-      </c>
-      <c r="E7" t="str">
-        <f t="shared" ref="E7:E9" si="0">C7&amp;"*"&amp;D7</f>
-        <v>strike*5</v>
-      </c>
-    </row>
-    <row r="8" spans="3:6">
-      <c r="C8" s="10" t="s">
+      <c r="C4" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="D8">
-        <v>4</v>
-      </c>
-      <c r="E8" t="str">
-        <f t="shared" si="0"/>
-        <v>defense*4</v>
-      </c>
-      <c r="F8" t="str">
-        <f>E7&amp;"*"&amp;E8</f>
-        <v>strike*5*defense*4</v>
-      </c>
-    </row>
-    <row r="9" spans="3:6">
-      <c r="C9" s="10" t="s">
+      <c r="C5" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="E9" t="str">
-        <f t="shared" si="0"/>
-        <v>trounce*1</v>
-      </c>
-      <c r="F9" t="str">
-        <f>F8&amp;"*"&amp;E9</f>
-        <v>strike*5*defense*4*trounce*1</v>
+      <c r="C6" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A5D68F6-6A69-4994-8A54-CD8F7D229E72}">
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.3984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.265625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="42" t="s">
+        <v>274</v>
+      </c>
+      <c r="C1" s="42" t="s">
+        <v>279</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="42" t="s">
+        <v>274</v>
+      </c>
+      <c r="C2" s="42" t="s">
+        <v>282</v>
+      </c>
+      <c r="D2" s="42" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="42" t="s">
+        <v>274</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="10"/>
+      <c r="C5" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="44" t="s">
+        <v>285</v>
+      </c>
+      <c r="B6" s="10"/>
+      <c r="C6" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" s="44" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="44" t="s">
+        <v>286</v>
+      </c>
+      <c r="B7" s="10"/>
+      <c r="C7" s="45" t="s">
+        <v>284</v>
+      </c>
+      <c r="D7" s="46" t="s">
+        <v>280</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5EA7D5D-311E-4C1E-90F0-7DA998873B51}">
+  <dimension ref="A1:G14"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="20.46484375" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="48" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="48" t="s">
+        <v>287</v>
+      </c>
+      <c r="C1" s="48" t="s">
+        <v>288</v>
+      </c>
+      <c r="D1" s="48" t="s">
+        <v>289</v>
+      </c>
+      <c r="E1" s="48" t="s">
+        <v>331</v>
+      </c>
+      <c r="F1" s="48" t="s">
+        <v>330</v>
+      </c>
+      <c r="G1" s="48" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="42" t="s">
+        <v>314</v>
+      </c>
+      <c r="C2" s="42" t="s">
+        <v>282</v>
+      </c>
+      <c r="D2" s="49" t="s">
+        <v>312</v>
+      </c>
+      <c r="E2" s="42" t="s">
+        <v>326</v>
+      </c>
+      <c r="F2" s="42" t="s">
+        <v>327</v>
+      </c>
+      <c r="G2" s="42" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="42" t="s">
+        <v>275</v>
+      </c>
+      <c r="C3" s="42" t="s">
+        <v>313</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="51" t="s">
+        <v>313</v>
+      </c>
+      <c r="F3" s="51" t="s">
+        <v>313</v>
+      </c>
+      <c r="G3" s="51" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15" x14ac:dyDescent="0.3">
+      <c r="A4" s="50" t="s">
+        <v>290</v>
+      </c>
+      <c r="B4" s="44" t="s">
+        <v>315</v>
+      </c>
+      <c r="C4" s="50">
+        <v>100</v>
+      </c>
+      <c r="D4" s="50" t="s">
+        <v>291</v>
+      </c>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15" x14ac:dyDescent="0.3">
+      <c r="A5" s="50" t="s">
+        <v>292</v>
+      </c>
+      <c r="B5" s="44" t="s">
+        <v>316</v>
+      </c>
+      <c r="C5" s="50">
+        <v>100</v>
+      </c>
+      <c r="D5" s="50" t="s">
+        <v>293</v>
+      </c>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15" x14ac:dyDescent="0.3">
+      <c r="A6" s="50" t="s">
+        <v>294</v>
+      </c>
+      <c r="B6" s="44" t="s">
+        <v>317</v>
+      </c>
+      <c r="C6" s="50">
+        <v>3</v>
+      </c>
+      <c r="D6" s="50" t="s">
+        <v>295</v>
+      </c>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15" x14ac:dyDescent="0.3">
+      <c r="A7" s="50" t="s">
+        <v>296</v>
+      </c>
+      <c r="B7" s="44" t="s">
+        <v>318</v>
+      </c>
+      <c r="C7" s="50">
+        <v>3</v>
+      </c>
+      <c r="D7" s="50" t="s">
+        <v>297</v>
+      </c>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15" x14ac:dyDescent="0.3">
+      <c r="A8" s="50" t="s">
+        <v>298</v>
+      </c>
+      <c r="B8" s="44" t="s">
+        <v>319</v>
+      </c>
+      <c r="C8" s="50">
+        <v>10</v>
+      </c>
+      <c r="D8" s="50" t="s">
+        <v>299</v>
+      </c>
+      <c r="E8" s="10"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15" x14ac:dyDescent="0.3">
+      <c r="A9" s="50" t="s">
+        <v>300</v>
+      </c>
+      <c r="B9" s="44" t="s">
+        <v>320</v>
+      </c>
+      <c r="C9" s="50">
+        <v>0</v>
+      </c>
+      <c r="D9" s="50" t="s">
+        <v>301</v>
+      </c>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15" x14ac:dyDescent="0.3">
+      <c r="A10" s="50" t="s">
+        <v>302</v>
+      </c>
+      <c r="B10" s="44" t="s">
+        <v>321</v>
+      </c>
+      <c r="C10" s="50">
+        <v>0</v>
+      </c>
+      <c r="D10" s="50" t="s">
+        <v>303</v>
+      </c>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15" x14ac:dyDescent="0.3">
+      <c r="A11" s="50" t="s">
+        <v>304</v>
+      </c>
+      <c r="B11" s="44" t="s">
+        <v>322</v>
+      </c>
+      <c r="C11" s="50">
+        <v>0</v>
+      </c>
+      <c r="D11" s="50" t="s">
+        <v>305</v>
+      </c>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15" x14ac:dyDescent="0.3">
+      <c r="A12" s="50" t="s">
+        <v>306</v>
+      </c>
+      <c r="B12" s="44" t="s">
+        <v>323</v>
+      </c>
+      <c r="C12" s="50">
+        <v>0</v>
+      </c>
+      <c r="D12" s="50" t="s">
+        <v>307</v>
+      </c>
+      <c r="E12" s="10"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15" x14ac:dyDescent="0.3">
+      <c r="A13" s="50" t="s">
+        <v>308</v>
+      </c>
+      <c r="B13" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="C13" s="50">
+        <v>0</v>
+      </c>
+      <c r="D13" s="50" t="s">
+        <v>309</v>
+      </c>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="15" x14ac:dyDescent="0.3">
+      <c r="A14" s="50" t="s">
+        <v>310</v>
+      </c>
+      <c r="B14" s="44" t="s">
+        <v>325</v>
+      </c>
+      <c r="C14" s="50">
+        <v>0</v>
+      </c>
+      <c r="D14" s="50" t="s">
+        <v>311</v>
+      </c>
+      <c r="E14" s="10"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:AA41"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" ht="14.25" spans="1:27">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2968,9 +3224,9 @@
       <c r="X1" s="15"/>
       <c r="Y1" s="15"/>
       <c r="Z1" s="15"/>
-      <c r="AA1" s="31"/>
-    </row>
-    <row r="2" ht="14.25" spans="1:27">
+      <c r="AA1" s="30"/>
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -3043,17 +3299,17 @@
       <c r="X2" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="Y2" s="32" t="s">
+      <c r="Y2" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="Z2" s="32" t="s">
+      <c r="Z2" s="31" t="s">
         <v>95</v>
       </c>
-      <c r="AA2" s="33" t="s">
+      <c r="AA2" s="32" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="3" ht="14.25" spans="1:27">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>10</v>
       </c>
@@ -3132,11 +3388,11 @@
       <c r="Z3" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="AA3" s="34" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27">
+      <c r="AA3" s="33" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A4" s="7">
         <v>1</v>
       </c>
@@ -3196,7 +3452,7 @@
       <c r="U4" s="8"/>
       <c r="V4" s="8"/>
       <c r="W4" s="23"/>
-      <c r="X4" s="43" t="s">
+      <c r="X4" s="41" t="s">
         <v>98</v>
       </c>
       <c r="Y4" s="8" t="s">
@@ -3209,7 +3465,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="5" spans="1:27">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A5" s="9">
         <v>2</v>
       </c>
@@ -3261,15 +3517,15 @@
       <c r="Q5" s="10">
         <v>0</v>
       </c>
-      <c r="R5" s="25">
+      <c r="R5" s="24">
         <v>0</v>
       </c>
       <c r="S5" s="10"/>
       <c r="T5" s="10"/>
       <c r="U5" s="10"/>
       <c r="V5" s="10"/>
-      <c r="W5" s="26"/>
-      <c r="X5" s="27" t="s">
+      <c r="W5" s="25"/>
+      <c r="X5" s="26" t="s">
         <v>103</v>
       </c>
       <c r="Y5" s="10" t="s">
@@ -3278,11 +3534,11 @@
       <c r="Z5" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="AA5" s="26" t="s">
+      <c r="AA5" s="25" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="6" spans="1:27">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A6" s="9">
         <v>3</v>
       </c>
@@ -3334,15 +3590,15 @@
       <c r="Q6" s="10">
         <v>0</v>
       </c>
-      <c r="R6" s="25">
+      <c r="R6" s="24">
         <v>0</v>
       </c>
       <c r="S6" s="10"/>
       <c r="T6" s="10"/>
       <c r="U6" s="10"/>
       <c r="V6" s="10"/>
-      <c r="W6" s="26"/>
-      <c r="X6" s="27" t="s">
+      <c r="W6" s="25"/>
+      <c r="X6" s="26" t="s">
         <v>106</v>
       </c>
       <c r="Y6" s="10" t="s">
@@ -3351,11 +3607,11 @@
       <c r="Z6" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="AA6" s="26" t="s">
+      <c r="AA6" s="25" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="7" spans="1:27">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A7" s="9">
         <v>4</v>
       </c>
@@ -3407,15 +3663,15 @@
       <c r="Q7" s="10">
         <v>0</v>
       </c>
-      <c r="R7" s="25">
+      <c r="R7" s="24">
         <v>0</v>
       </c>
       <c r="S7" s="10"/>
       <c r="T7" s="10"/>
       <c r="U7" s="10"/>
       <c r="V7" s="10"/>
-      <c r="W7" s="26"/>
-      <c r="X7" s="27" t="s">
+      <c r="W7" s="25"/>
+      <c r="X7" s="26" t="s">
         <v>110</v>
       </c>
       <c r="Y7" s="10" t="s">
@@ -3424,11 +3680,11 @@
       <c r="Z7" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="AA7" s="26" t="s">
+      <c r="AA7" s="25" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="8" spans="1:27">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A8" s="9">
         <v>5</v>
       </c>
@@ -3480,15 +3736,15 @@
       <c r="Q8" s="10">
         <v>0</v>
       </c>
-      <c r="R8" s="25">
+      <c r="R8" s="24">
         <v>0</v>
       </c>
       <c r="S8" s="10"/>
       <c r="T8" s="10"/>
       <c r="U8" s="10"/>
       <c r="V8" s="10"/>
-      <c r="W8" s="26"/>
-      <c r="X8" s="27" t="s">
+      <c r="W8" s="25"/>
+      <c r="X8" s="26" t="s">
         <v>114</v>
       </c>
       <c r="Y8" s="10" t="s">
@@ -3497,11 +3753,11 @@
       <c r="Z8" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="AA8" s="26" t="s">
+      <c r="AA8" s="25" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="9" spans="1:27">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A9" s="9">
         <v>6</v>
       </c>
@@ -3553,15 +3809,15 @@
       <c r="Q9" s="10">
         <v>0</v>
       </c>
-      <c r="R9" s="25">
+      <c r="R9" s="24">
         <v>0</v>
       </c>
       <c r="S9" s="10"/>
       <c r="T9" s="10"/>
       <c r="U9" s="10"/>
       <c r="V9" s="10"/>
-      <c r="W9" s="26"/>
-      <c r="X9" s="27" t="s">
+      <c r="W9" s="25"/>
+      <c r="X9" s="26" t="s">
         <v>118</v>
       </c>
       <c r="Y9" s="10" t="s">
@@ -3570,11 +3826,11 @@
       <c r="Z9" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="AA9" s="26" t="s">
+      <c r="AA9" s="25" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="10" spans="1:27">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A10" s="9">
         <v>7</v>
       </c>
@@ -3626,15 +3882,15 @@
       <c r="Q10" s="10">
         <v>0</v>
       </c>
-      <c r="R10" s="25">
+      <c r="R10" s="24">
         <v>0</v>
       </c>
       <c r="S10" s="10"/>
       <c r="T10" s="10"/>
       <c r="U10" s="10"/>
       <c r="V10" s="10"/>
-      <c r="W10" s="26"/>
-      <c r="X10" s="27" t="s">
+      <c r="W10" s="25"/>
+      <c r="X10" s="26" t="s">
         <v>123</v>
       </c>
       <c r="Y10" s="10" t="s">
@@ -3643,11 +3899,11 @@
       <c r="Z10" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="AA10" s="26" t="s">
+      <c r="AA10" s="25" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="11" spans="1:27">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A11" s="9">
         <v>8</v>
       </c>
@@ -3699,15 +3955,15 @@
       <c r="Q11" s="10">
         <v>0</v>
       </c>
-      <c r="R11" s="25">
+      <c r="R11" s="24">
         <v>0</v>
       </c>
       <c r="S11" s="10"/>
       <c r="T11" s="10"/>
       <c r="U11" s="10"/>
       <c r="V11" s="10"/>
-      <c r="W11" s="26"/>
-      <c r="X11" s="27" t="s">
+      <c r="W11" s="25"/>
+      <c r="X11" s="26" t="s">
         <v>127</v>
       </c>
       <c r="Y11" s="10" t="s">
@@ -3716,11 +3972,11 @@
       <c r="Z11" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="AA11" s="26" t="s">
+      <c r="AA11" s="25" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="12" spans="1:27">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A12" s="9">
         <v>9</v>
       </c>
@@ -3772,15 +4028,15 @@
       <c r="Q12" s="10">
         <v>0</v>
       </c>
-      <c r="R12" s="25">
+      <c r="R12" s="24">
         <v>0</v>
       </c>
       <c r="S12" s="10"/>
       <c r="T12" s="10"/>
       <c r="U12" s="10"/>
       <c r="V12" s="10"/>
-      <c r="W12" s="26"/>
-      <c r="X12" s="27" t="s">
+      <c r="W12" s="25"/>
+      <c r="X12" s="26" t="s">
         <v>132</v>
       </c>
       <c r="Y12" s="10" t="s">
@@ -3789,11 +4045,11 @@
       <c r="Z12" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="AA12" s="26" t="s">
+      <c r="AA12" s="25" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="13" spans="1:27">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A13" s="9">
         <v>10</v>
       </c>
@@ -3845,15 +4101,15 @@
       <c r="Q13" s="10">
         <v>0</v>
       </c>
-      <c r="R13" s="25">
+      <c r="R13" s="24">
         <v>0</v>
       </c>
       <c r="S13" s="10"/>
       <c r="T13" s="10"/>
       <c r="U13" s="10"/>
       <c r="V13" s="10"/>
-      <c r="W13" s="26"/>
-      <c r="X13" s="27" t="s">
+      <c r="W13" s="25"/>
+      <c r="X13" s="26" t="s">
         <v>137</v>
       </c>
       <c r="Y13" s="10" t="s">
@@ -3862,11 +4118,11 @@
       <c r="Z13" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="AA13" s="26" t="s">
+      <c r="AA13" s="25" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="14" spans="1:27">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A14" s="9">
         <v>11</v>
       </c>
@@ -3918,15 +4174,15 @@
       <c r="Q14" s="10">
         <v>0</v>
       </c>
-      <c r="R14" s="25">
+      <c r="R14" s="24">
         <v>0</v>
       </c>
       <c r="S14" s="10"/>
       <c r="T14" s="10"/>
       <c r="U14" s="10"/>
       <c r="V14" s="10"/>
-      <c r="W14" s="26"/>
-      <c r="X14" s="27" t="s">
+      <c r="W14" s="25"/>
+      <c r="X14" s="26" t="s">
         <v>141</v>
       </c>
       <c r="Y14" s="10" t="s">
@@ -3935,11 +4191,11 @@
       <c r="Z14" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="AA14" s="26" t="s">
+      <c r="AA14" s="25" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="15" spans="1:27">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A15" s="9">
         <v>12</v>
       </c>
@@ -3991,15 +4247,15 @@
       <c r="Q15" s="10">
         <v>0</v>
       </c>
-      <c r="R15" s="25">
+      <c r="R15" s="24">
         <v>0</v>
       </c>
       <c r="S15" s="10"/>
       <c r="T15" s="10"/>
       <c r="U15" s="10"/>
       <c r="V15" s="10"/>
-      <c r="W15" s="26"/>
-      <c r="X15" s="27" t="s">
+      <c r="W15" s="25"/>
+      <c r="X15" s="26" t="s">
         <v>146</v>
       </c>
       <c r="Y15" s="10" t="s">
@@ -4008,11 +4264,11 @@
       <c r="Z15" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="AA15" s="26" t="s">
+      <c r="AA15" s="25" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="16" spans="1:27">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A16" s="9">
         <v>13</v>
       </c>
@@ -4064,15 +4320,15 @@
       <c r="Q16" s="10">
         <v>0</v>
       </c>
-      <c r="R16" s="25">
+      <c r="R16" s="24">
         <v>0</v>
       </c>
       <c r="S16" s="10"/>
       <c r="T16" s="10"/>
       <c r="U16" s="10"/>
       <c r="V16" s="10"/>
-      <c r="W16" s="26"/>
-      <c r="X16" s="27" t="s">
+      <c r="W16" s="25"/>
+      <c r="X16" s="26" t="s">
         <v>150</v>
       </c>
       <c r="Y16" s="10" t="s">
@@ -4081,11 +4337,11 @@
       <c r="Z16" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="AA16" s="26" t="s">
+      <c r="AA16" s="25" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="17" spans="1:27">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A17" s="9">
         <v>14</v>
       </c>
@@ -4137,15 +4393,15 @@
       <c r="Q17" s="10">
         <v>0</v>
       </c>
-      <c r="R17" s="25">
+      <c r="R17" s="24">
         <v>0</v>
       </c>
       <c r="S17" s="10"/>
       <c r="T17" s="10"/>
       <c r="U17" s="10"/>
       <c r="V17" s="10"/>
-      <c r="W17" s="26"/>
-      <c r="X17" s="27" t="s">
+      <c r="W17" s="25"/>
+      <c r="X17" s="26" t="s">
         <v>154</v>
       </c>
       <c r="Y17" s="10" t="s">
@@ -4154,11 +4410,11 @@
       <c r="Z17" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="AA17" s="26" t="s">
+      <c r="AA17" s="25" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="18" spans="1:27">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A18" s="9">
         <v>15</v>
       </c>
@@ -4210,15 +4466,15 @@
       <c r="Q18" s="10">
         <v>0</v>
       </c>
-      <c r="R18" s="25">
+      <c r="R18" s="24">
         <v>0</v>
       </c>
       <c r="S18" s="10"/>
       <c r="T18" s="10"/>
       <c r="U18" s="10"/>
       <c r="V18" s="10"/>
-      <c r="W18" s="26"/>
-      <c r="X18" s="27" t="s">
+      <c r="W18" s="25"/>
+      <c r="X18" s="26" t="s">
         <v>159</v>
       </c>
       <c r="Y18" s="10" t="s">
@@ -4227,11 +4483,11 @@
       <c r="Z18" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="AA18" s="26" t="s">
+      <c r="AA18" s="25" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="19" spans="1:27">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A19" s="9">
         <v>16</v>
       </c>
@@ -4283,15 +4539,15 @@
       <c r="Q19" s="10">
         <v>0</v>
       </c>
-      <c r="R19" s="25">
+      <c r="R19" s="24">
         <v>0</v>
       </c>
       <c r="S19" s="10"/>
       <c r="T19" s="10"/>
       <c r="U19" s="10"/>
       <c r="V19" s="10"/>
-      <c r="W19" s="26"/>
-      <c r="X19" s="27" t="s">
+      <c r="W19" s="25"/>
+      <c r="X19" s="26" t="s">
         <v>163</v>
       </c>
       <c r="Y19" s="10" t="s">
@@ -4300,11 +4556,11 @@
       <c r="Z19" s="10" t="s">
         <v>165</v>
       </c>
-      <c r="AA19" s="26" t="s">
+      <c r="AA19" s="25" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="20" spans="1:27">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A20" s="9">
         <v>17</v>
       </c>
@@ -4356,15 +4612,15 @@
       <c r="Q20" s="10">
         <v>0</v>
       </c>
-      <c r="R20" s="25">
+      <c r="R20" s="24">
         <v>0</v>
       </c>
       <c r="S20" s="10"/>
       <c r="T20" s="10"/>
       <c r="U20" s="10"/>
       <c r="V20" s="10"/>
-      <c r="W20" s="26"/>
-      <c r="X20" s="27" t="s">
+      <c r="W20" s="25"/>
+      <c r="X20" s="26" t="s">
         <v>167</v>
       </c>
       <c r="Y20" s="10" t="s">
@@ -4373,11 +4629,11 @@
       <c r="Z20" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="AA20" s="26" t="s">
+      <c r="AA20" s="25" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="21" spans="1:27">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A21" s="9">
         <v>18</v>
       </c>
@@ -4429,15 +4685,15 @@
       <c r="Q21" s="10">
         <v>0</v>
       </c>
-      <c r="R21" s="25">
+      <c r="R21" s="24">
         <v>0</v>
       </c>
       <c r="S21" s="10"/>
       <c r="T21" s="10"/>
       <c r="U21" s="10"/>
       <c r="V21" s="10"/>
-      <c r="W21" s="26"/>
-      <c r="X21" s="27" t="s">
+      <c r="W21" s="25"/>
+      <c r="X21" s="26" t="s">
         <v>171</v>
       </c>
       <c r="Y21" s="10" t="s">
@@ -4446,11 +4702,11 @@
       <c r="Z21" s="10" t="s">
         <v>173</v>
       </c>
-      <c r="AA21" s="26" t="s">
+      <c r="AA21" s="25" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="22" spans="1:27">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A22" s="9">
         <v>19</v>
       </c>
@@ -4502,15 +4758,15 @@
       <c r="Q22" s="10">
         <v>0</v>
       </c>
-      <c r="R22" s="25">
+      <c r="R22" s="24">
         <v>0</v>
       </c>
       <c r="S22" s="10"/>
       <c r="T22" s="10"/>
       <c r="U22" s="10"/>
       <c r="V22" s="10"/>
-      <c r="W22" s="26"/>
-      <c r="X22" s="27" t="s">
+      <c r="W22" s="25"/>
+      <c r="X22" s="26" t="s">
         <v>175</v>
       </c>
       <c r="Y22" s="10" t="s">
@@ -4519,11 +4775,11 @@
       <c r="Z22" s="10" t="s">
         <v>177</v>
       </c>
-      <c r="AA22" s="26" t="s">
+      <c r="AA22" s="25" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="23" spans="1:27">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A23" s="9">
         <v>20</v>
       </c>
@@ -4575,15 +4831,15 @@
       <c r="Q23" s="10">
         <v>0</v>
       </c>
-      <c r="R23" s="25">
+      <c r="R23" s="24">
         <v>0</v>
       </c>
       <c r="S23" s="10"/>
       <c r="T23" s="10"/>
       <c r="U23" s="10"/>
       <c r="V23" s="10"/>
-      <c r="W23" s="26"/>
-      <c r="X23" s="27" t="s">
+      <c r="W23" s="25"/>
+      <c r="X23" s="26" t="s">
         <v>180</v>
       </c>
       <c r="Y23" s="10" t="s">
@@ -4592,11 +4848,11 @@
       <c r="Z23" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="AA23" s="26" t="s">
+      <c r="AA23" s="25" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="24" spans="1:27">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A24" s="9">
         <v>21</v>
       </c>
@@ -4648,15 +4904,15 @@
       <c r="Q24" s="10">
         <v>0</v>
       </c>
-      <c r="R24" s="25">
+      <c r="R24" s="24">
         <v>0</v>
       </c>
       <c r="S24" s="10"/>
       <c r="T24" s="10"/>
       <c r="U24" s="10"/>
       <c r="V24" s="10"/>
-      <c r="W24" s="26"/>
-      <c r="X24" s="27" t="s">
+      <c r="W24" s="25"/>
+      <c r="X24" s="26" t="s">
         <v>185</v>
       </c>
       <c r="Y24" s="10" t="s">
@@ -4665,11 +4921,11 @@
       <c r="Z24" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="AA24" s="26" t="s">
+      <c r="AA24" s="25" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="25" spans="1:27">
+    <row r="25" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A25" s="9">
         <v>22</v>
       </c>
@@ -4721,15 +4977,15 @@
       <c r="Q25" s="10">
         <v>0</v>
       </c>
-      <c r="R25" s="25">
+      <c r="R25" s="24">
         <v>0</v>
       </c>
       <c r="S25" s="10"/>
       <c r="T25" s="10"/>
       <c r="U25" s="10"/>
       <c r="V25" s="10"/>
-      <c r="W25" s="26"/>
-      <c r="X25" s="27" t="s">
+      <c r="W25" s="25"/>
+      <c r="X25" s="26" t="s">
         <v>190</v>
       </c>
       <c r="Y25" s="10" t="s">
@@ -4738,11 +4994,11 @@
       <c r="Z25" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="AA25" s="26" t="s">
+      <c r="AA25" s="25" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="26" spans="1:27">
+    <row r="26" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A26" s="9">
         <v>23</v>
       </c>
@@ -4794,15 +5050,15 @@
       <c r="Q26" s="10">
         <v>0</v>
       </c>
-      <c r="R26" s="25">
+      <c r="R26" s="24">
         <v>0</v>
       </c>
       <c r="S26" s="10"/>
       <c r="T26" s="10"/>
       <c r="U26" s="10"/>
       <c r="V26" s="10"/>
-      <c r="W26" s="26"/>
-      <c r="X26" s="27" t="s">
+      <c r="W26" s="25"/>
+      <c r="X26" s="26" t="s">
         <v>194</v>
       </c>
       <c r="Y26" s="10" t="s">
@@ -4811,11 +5067,11 @@
       <c r="Z26" s="10" t="s">
         <v>196</v>
       </c>
-      <c r="AA26" s="26" t="s">
+      <c r="AA26" s="25" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="27" spans="1:27">
+    <row r="27" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A27" s="9">
         <v>24</v>
       </c>
@@ -4867,15 +5123,15 @@
       <c r="Q27" s="10">
         <v>0</v>
       </c>
-      <c r="R27" s="25">
+      <c r="R27" s="24">
         <v>0</v>
       </c>
       <c r="S27" s="10"/>
       <c r="T27" s="10"/>
       <c r="U27" s="10"/>
       <c r="V27" s="10"/>
-      <c r="W27" s="26"/>
-      <c r="X27" s="27" t="s">
+      <c r="W27" s="25"/>
+      <c r="X27" s="26" t="s">
         <v>199</v>
       </c>
       <c r="Y27" s="10" t="s">
@@ -4884,11 +5140,11 @@
       <c r="Z27" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="AA27" s="26" t="s">
+      <c r="AA27" s="25" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="28" spans="1:27">
+    <row r="28" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A28" s="9">
         <v>25</v>
       </c>
@@ -4940,15 +5196,15 @@
       <c r="Q28" s="10">
         <v>0</v>
       </c>
-      <c r="R28" s="25">
+      <c r="R28" s="24">
         <v>0</v>
       </c>
       <c r="S28" s="10"/>
       <c r="T28" s="10"/>
       <c r="U28" s="10"/>
       <c r="V28" s="10"/>
-      <c r="W28" s="26"/>
-      <c r="X28" s="27" t="s">
+      <c r="W28" s="25"/>
+      <c r="X28" s="26" t="s">
         <v>204</v>
       </c>
       <c r="Y28" s="10" t="s">
@@ -4957,11 +5213,11 @@
       <c r="Z28" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="AA28" s="26" t="s">
+      <c r="AA28" s="25" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="29" spans="1:27">
+    <row r="29" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A29" s="9">
         <v>26</v>
       </c>
@@ -5013,15 +5269,15 @@
       <c r="Q29" s="10">
         <v>0</v>
       </c>
-      <c r="R29" s="25">
+      <c r="R29" s="24">
         <v>0</v>
       </c>
       <c r="S29" s="10"/>
       <c r="T29" s="10"/>
       <c r="U29" s="10"/>
       <c r="V29" s="10"/>
-      <c r="W29" s="26"/>
-      <c r="X29" s="27" t="s">
+      <c r="W29" s="25"/>
+      <c r="X29" s="26" t="s">
         <v>209</v>
       </c>
       <c r="Y29" s="10" t="s">
@@ -5030,11 +5286,11 @@
       <c r="Z29" s="10" t="s">
         <v>211</v>
       </c>
-      <c r="AA29" s="26" t="s">
+      <c r="AA29" s="25" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="30" spans="1:27">
+    <row r="30" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A30" s="9">
         <v>27</v>
       </c>
@@ -5086,15 +5342,15 @@
       <c r="Q30" s="10">
         <v>0</v>
       </c>
-      <c r="R30" s="25">
+      <c r="R30" s="24">
         <v>0</v>
       </c>
       <c r="S30" s="10"/>
       <c r="T30" s="10"/>
       <c r="U30" s="10"/>
       <c r="V30" s="10"/>
-      <c r="W30" s="26"/>
-      <c r="X30" s="27" t="s">
+      <c r="W30" s="25"/>
+      <c r="X30" s="26" t="s">
         <v>214</v>
       </c>
       <c r="Y30" s="10" t="s">
@@ -5103,11 +5359,11 @@
       <c r="Z30" s="10" t="s">
         <v>216</v>
       </c>
-      <c r="AA30" s="26" t="s">
+      <c r="AA30" s="25" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="31" spans="1:27">
+    <row r="31" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A31" s="9">
         <v>28</v>
       </c>
@@ -5159,15 +5415,15 @@
       <c r="Q31" s="10">
         <v>0</v>
       </c>
-      <c r="R31" s="25">
+      <c r="R31" s="24">
         <v>0</v>
       </c>
       <c r="S31" s="10"/>
       <c r="T31" s="10"/>
       <c r="U31" s="10"/>
       <c r="V31" s="10"/>
-      <c r="W31" s="26"/>
-      <c r="X31" s="27" t="s">
+      <c r="W31" s="25"/>
+      <c r="X31" s="26" t="s">
         <v>218</v>
       </c>
       <c r="Y31" s="10" t="s">
@@ -5176,11 +5432,11 @@
       <c r="Z31" s="10" t="s">
         <v>220</v>
       </c>
-      <c r="AA31" s="26" t="s">
+      <c r="AA31" s="25" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="32" spans="1:27">
+    <row r="32" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A32" s="9">
         <v>29</v>
       </c>
@@ -5232,15 +5488,15 @@
       <c r="Q32" s="10">
         <v>0</v>
       </c>
-      <c r="R32" s="25">
+      <c r="R32" s="24">
         <v>0</v>
       </c>
       <c r="S32" s="10"/>
       <c r="T32" s="10"/>
       <c r="U32" s="10"/>
       <c r="V32" s="10"/>
-      <c r="W32" s="26"/>
-      <c r="X32" s="27" t="s">
+      <c r="W32" s="25"/>
+      <c r="X32" s="26" t="s">
         <v>222</v>
       </c>
       <c r="Y32" s="10" t="s">
@@ -5249,11 +5505,11 @@
       <c r="Z32" s="10" t="s">
         <v>224</v>
       </c>
-      <c r="AA32" s="26" t="s">
+      <c r="AA32" s="25" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="33" spans="1:27">
+    <row r="33" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A33" s="9">
         <v>30</v>
       </c>
@@ -5305,15 +5561,15 @@
       <c r="Q33" s="10">
         <v>0</v>
       </c>
-      <c r="R33" s="25">
+      <c r="R33" s="24">
         <v>0</v>
       </c>
       <c r="S33" s="10"/>
       <c r="T33" s="10"/>
       <c r="U33" s="10"/>
       <c r="V33" s="10"/>
-      <c r="W33" s="26"/>
-      <c r="X33" s="27" t="s">
+      <c r="W33" s="25"/>
+      <c r="X33" s="26" t="s">
         <v>227</v>
       </c>
       <c r="Y33" s="10" t="s">
@@ -5322,11 +5578,11 @@
       <c r="Z33" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="AA33" s="26" t="s">
+      <c r="AA33" s="25" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="34" spans="1:27">
+    <row r="34" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A34" s="9">
         <v>31</v>
       </c>
@@ -5378,15 +5634,15 @@
       <c r="Q34" s="10">
         <v>0</v>
       </c>
-      <c r="R34" s="25">
+      <c r="R34" s="24">
         <v>0</v>
       </c>
       <c r="S34" s="10"/>
       <c r="T34" s="10"/>
       <c r="U34" s="10"/>
       <c r="V34" s="10"/>
-      <c r="W34" s="26"/>
-      <c r="X34" s="27" t="s">
+      <c r="W34" s="25"/>
+      <c r="X34" s="26" t="s">
         <v>232</v>
       </c>
       <c r="Y34" s="10" t="s">
@@ -5395,11 +5651,11 @@
       <c r="Z34" s="10" t="s">
         <v>234</v>
       </c>
-      <c r="AA34" s="26" t="s">
+      <c r="AA34" s="25" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="35" spans="1:27">
+    <row r="35" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A35" s="9">
         <v>32</v>
       </c>
@@ -5451,15 +5707,15 @@
       <c r="Q35" s="10">
         <v>0</v>
       </c>
-      <c r="R35" s="25">
+      <c r="R35" s="24">
         <v>0</v>
       </c>
       <c r="S35" s="10"/>
       <c r="T35" s="10"/>
       <c r="U35" s="10"/>
       <c r="V35" s="10"/>
-      <c r="W35" s="26"/>
-      <c r="X35" s="27" t="s">
+      <c r="W35" s="25"/>
+      <c r="X35" s="26" t="s">
         <v>236</v>
       </c>
       <c r="Y35" s="10" t="s">
@@ -5468,11 +5724,11 @@
       <c r="Z35" s="10" t="s">
         <v>238</v>
       </c>
-      <c r="AA35" s="26" t="s">
+      <c r="AA35" s="25" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="36" spans="1:27">
+    <row r="36" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A36" s="9">
         <v>33</v>
       </c>
@@ -5524,15 +5780,15 @@
       <c r="Q36" s="10">
         <v>0</v>
       </c>
-      <c r="R36" s="25">
+      <c r="R36" s="24">
         <v>0</v>
       </c>
       <c r="S36" s="10"/>
       <c r="T36" s="10"/>
       <c r="U36" s="10"/>
       <c r="V36" s="10"/>
-      <c r="W36" s="26"/>
-      <c r="X36" s="27" t="s">
+      <c r="W36" s="25"/>
+      <c r="X36" s="26" t="s">
         <v>241</v>
       </c>
       <c r="Y36" s="10" t="s">
@@ -5541,11 +5797,11 @@
       <c r="Z36" s="10" t="s">
         <v>243</v>
       </c>
-      <c r="AA36" s="26" t="s">
+      <c r="AA36" s="25" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="37" spans="1:27">
+    <row r="37" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A37" s="9">
         <v>34</v>
       </c>
@@ -5597,15 +5853,15 @@
       <c r="Q37" s="10">
         <v>0</v>
       </c>
-      <c r="R37" s="25">
+      <c r="R37" s="24">
         <v>0</v>
       </c>
       <c r="S37" s="10"/>
       <c r="T37" s="10"/>
       <c r="U37" s="10"/>
       <c r="V37" s="10"/>
-      <c r="W37" s="26"/>
-      <c r="X37" s="27" t="s">
+      <c r="W37" s="25"/>
+      <c r="X37" s="26" t="s">
         <v>246</v>
       </c>
       <c r="Y37" s="10" t="s">
@@ -5614,11 +5870,11 @@
       <c r="Z37" s="10" t="s">
         <v>248</v>
       </c>
-      <c r="AA37" s="26" t="s">
+      <c r="AA37" s="25" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="38" spans="1:27">
+    <row r="38" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A38" s="9">
         <v>35</v>
       </c>
@@ -5670,15 +5926,15 @@
       <c r="Q38" s="10">
         <v>0</v>
       </c>
-      <c r="R38" s="25">
+      <c r="R38" s="24">
         <v>0</v>
       </c>
       <c r="S38" s="10"/>
       <c r="T38" s="10"/>
       <c r="U38" s="10"/>
       <c r="V38" s="10"/>
-      <c r="W38" s="26"/>
-      <c r="X38" s="27" t="s">
+      <c r="W38" s="25"/>
+      <c r="X38" s="26" t="s">
         <v>251</v>
       </c>
       <c r="Y38" s="10" t="s">
@@ -5687,11 +5943,11 @@
       <c r="Z38" s="10" t="s">
         <v>253</v>
       </c>
-      <c r="AA38" s="26" t="s">
+      <c r="AA38" s="25" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="39" spans="1:27">
+    <row r="39" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A39" s="9">
         <v>36</v>
       </c>
@@ -5743,15 +5999,15 @@
       <c r="Q39" s="10">
         <v>0</v>
       </c>
-      <c r="R39" s="25">
+      <c r="R39" s="24">
         <v>0</v>
       </c>
       <c r="S39" s="10"/>
       <c r="T39" s="10"/>
       <c r="U39" s="10"/>
       <c r="V39" s="10"/>
-      <c r="W39" s="26"/>
-      <c r="X39" s="27" t="s">
+      <c r="W39" s="25"/>
+      <c r="X39" s="26" t="s">
         <v>256</v>
       </c>
       <c r="Y39" s="10" t="s">
@@ -5760,11 +6016,11 @@
       <c r="Z39" s="10" t="s">
         <v>258</v>
       </c>
-      <c r="AA39" s="26" t="s">
+      <c r="AA39" s="25" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="40" spans="1:27">
+    <row r="40" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A40" s="9">
         <v>37</v>
       </c>
@@ -5816,15 +6072,15 @@
       <c r="Q40" s="10">
         <v>0</v>
       </c>
-      <c r="R40" s="25">
+      <c r="R40" s="24">
         <v>0</v>
       </c>
       <c r="S40" s="10"/>
       <c r="T40" s="10"/>
       <c r="U40" s="10"/>
       <c r="V40" s="10"/>
-      <c r="W40" s="26"/>
-      <c r="X40" s="27" t="s">
+      <c r="W40" s="25"/>
+      <c r="X40" s="26" t="s">
         <v>261</v>
       </c>
       <c r="Y40" s="10" t="s">
@@ -5833,11 +6089,11 @@
       <c r="Z40" s="10" t="s">
         <v>263</v>
       </c>
-      <c r="AA40" s="26" t="s">
+      <c r="AA40" s="25" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="41" ht="14.25" spans="1:27">
+    <row r="41" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A41" s="11">
         <v>38</v>
       </c>
@@ -5889,15 +6145,15 @@
       <c r="Q41" s="12">
         <v>0</v>
       </c>
-      <c r="R41" s="28">
+      <c r="R41" s="27">
         <v>0</v>
       </c>
       <c r="S41" s="12"/>
       <c r="T41" s="12"/>
       <c r="U41" s="12"/>
       <c r="V41" s="12"/>
-      <c r="W41" s="29"/>
-      <c r="X41" s="30" t="s">
+      <c r="W41" s="28"/>
+      <c r="X41" s="29" t="s">
         <v>265</v>
       </c>
       <c r="Y41" s="12" t="s">
@@ -5906,12 +6162,12 @@
       <c r="Z41" s="12" t="s">
         <v>267</v>
       </c>
-      <c r="AA41" s="29" t="s">
+      <c r="AA41" s="28" t="s">
         <v>101</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/xlsdir/配置-总表.xlsx
+++ b/xlsdir/配置-总表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\24102\Documents\project-sx\xlsdir\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1540E82-9635-4A70-A1F5-A54521DC30CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B98A1EB7-638A-4A07-8515-2A960348BB20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="673" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="673" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="combat|战斗" sheetId="31" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="351">
   <si>
     <t>ID</t>
   </si>
@@ -1191,25 +1191,79 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 能量消耗</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 效果ID列表</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 目标类型</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 触发时机</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 持续回合</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 稀有度</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 类别</t>
+    <t>abilityID</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能ID</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>能量消耗</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>效果ID列表</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>触发时机</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>类别</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>cost</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>string[]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>effects</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>trounce_01*trounce_02</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>type</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>trigger</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>target_type</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标类型
+1、自身
+2、对方单体
+3、对方全体</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1296,7 +1350,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="29">
+  <borders count="30">
     <border>
       <left/>
       <right/>
@@ -1670,6 +1724,17 @@
         <color auto="1"/>
       </left>
       <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -1680,7 +1745,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1816,15 +1881,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1834,8 +1890,23 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2500,7 +2571,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="3" width="11.59765625" customWidth="1"/>
@@ -2509,7 +2580,7 @@
     <col min="6" max="6" width="56.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -2528,8 +2599,11 @@
       <c r="F1" s="42" t="s">
         <v>270</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="G1" s="48" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A2" s="34" t="s">
         <v>5</v>
       </c>
@@ -2548,8 +2622,11 @@
       <c r="F2" s="43" t="s">
         <v>269</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G2" s="49" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>10</v>
       </c>
@@ -2568,8 +2645,11 @@
       <c r="F3" s="42" t="s">
         <v>268</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G3" s="48" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
         <v>34</v>
       </c>
@@ -2588,8 +2668,11 @@
       <c r="F4" s="44" t="s">
         <v>272</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G4" s="10" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>37</v>
       </c>
@@ -2608,8 +2691,11 @@
       <c r="F5" s="10" t="s">
         <v>271</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G5" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
         <v>40</v>
       </c>
@@ -2627,6 +2713,9 @@
       </c>
       <c r="F6" s="44" t="s">
         <v>273</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -2637,14 +2726,17 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B33D2148-8412-4B4D-9F87-3CA753CB34C0}">
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="16.73046875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="27.265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.3984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="25.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -2657,43 +2749,52 @@
       <c r="D1" s="4" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="34" t="s">
+      <c r="E1" s="42" t="s">
+        <v>340</v>
+      </c>
+      <c r="F1" s="42" t="s">
+        <v>347</v>
+      </c>
+      <c r="G1" s="42" t="s">
+        <v>346</v>
+      </c>
+      <c r="H1" s="42" t="s">
+        <v>345</v>
+      </c>
+      <c r="I1" s="42" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" s="52" customFormat="1" ht="54" x14ac:dyDescent="0.3">
+      <c r="A2" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="51" t="s">
         <v>274</v>
       </c>
-      <c r="C2" s="42" t="s">
+      <c r="C2" s="51" t="s">
         <v>276</v>
       </c>
-      <c r="D2" s="42" t="s">
+      <c r="D2" s="51" t="s">
         <v>278</v>
       </c>
-      <c r="E2" s="47" t="s">
-        <v>333</v>
-      </c>
-      <c r="F2" s="47" t="s">
-        <v>334</v>
-      </c>
-      <c r="G2" s="47" t="s">
-        <v>335</v>
-      </c>
-      <c r="H2" s="47" t="s">
+      <c r="E2" s="51" t="s">
         <v>336</v>
       </c>
-      <c r="I2" s="47" t="s">
+      <c r="F2" s="53" t="s">
+        <v>348</v>
+      </c>
+      <c r="G2" s="51" t="s">
+        <v>338</v>
+      </c>
+      <c r="H2" s="51" t="s">
+        <v>339</v>
+      </c>
+      <c r="I2" s="51" t="s">
         <v>337</v>
       </c>
-      <c r="J2" s="47" t="s">
-        <v>338</v>
-      </c>
-      <c r="K2" s="47" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>10</v>
       </c>
@@ -2706,38 +2807,101 @@
       <c r="D3" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="E3" s="42" t="s">
+        <v>341</v>
+      </c>
+      <c r="F3" s="42" t="s">
+        <v>275</v>
+      </c>
+      <c r="G3" s="42" t="s">
+        <v>275</v>
+      </c>
+      <c r="H3" s="42" t="s">
+        <v>275</v>
+      </c>
+      <c r="I3" s="42" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
         <v>34</v>
       </c>
+      <c r="B4" s="10"/>
       <c r="C4" s="10" t="s">
         <v>35</v>
       </c>
       <c r="D4" s="10" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="E4" s="10">
+        <v>1</v>
+      </c>
+      <c r="F4" s="10">
+        <v>2</v>
+      </c>
+      <c r="G4" s="10">
+        <v>0</v>
+      </c>
+      <c r="H4" s="44" t="s">
+        <v>349</v>
+      </c>
+      <c r="I4" s="10" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>37</v>
       </c>
+      <c r="B5" s="10"/>
       <c r="C5" s="10" t="s">
         <v>38</v>
       </c>
       <c r="D5" s="10" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="E5" s="10">
+        <v>1</v>
+      </c>
+      <c r="F5" s="10">
+        <v>1</v>
+      </c>
+      <c r="G5" s="10">
+        <v>0</v>
+      </c>
+      <c r="H5" s="44" t="s">
+        <v>350</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
         <v>40</v>
       </c>
+      <c r="B6" s="10"/>
       <c r="C6" s="10" t="s">
         <v>41</v>
       </c>
       <c r="D6" s="10" t="s">
         <v>42</v>
+      </c>
+      <c r="E6" s="10">
+        <v>2</v>
+      </c>
+      <c r="F6" s="10">
+        <v>2</v>
+      </c>
+      <c r="G6" s="10">
+        <v>0</v>
+      </c>
+      <c r="H6" s="44" t="s">
+        <v>349</v>
+      </c>
+      <c r="I6" s="44" t="s">
+        <v>344</v>
       </c>
     </row>
   </sheetData>
@@ -2839,10 +3003,10 @@
         <v>286</v>
       </c>
       <c r="B7" s="10"/>
-      <c r="C7" s="45" t="s">
+      <c r="C7" s="10" t="s">
         <v>284</v>
       </c>
-      <c r="D7" s="46" t="s">
+      <c r="D7" s="44" t="s">
         <v>280</v>
       </c>
     </row>
@@ -2863,25 +3027,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="48" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="48" t="s">
+      <c r="A1" s="45" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="45" t="s">
         <v>287</v>
       </c>
-      <c r="C1" s="48" t="s">
+      <c r="C1" s="45" t="s">
         <v>288</v>
       </c>
-      <c r="D1" s="48" t="s">
+      <c r="D1" s="45" t="s">
         <v>289</v>
       </c>
-      <c r="E1" s="48" t="s">
+      <c r="E1" s="45" t="s">
         <v>331</v>
       </c>
-      <c r="F1" s="48" t="s">
+      <c r="F1" s="45" t="s">
         <v>330</v>
       </c>
-      <c r="G1" s="48" t="s">
+      <c r="G1" s="45" t="s">
         <v>329</v>
       </c>
     </row>
@@ -2895,7 +3059,7 @@
       <c r="C2" s="42" t="s">
         <v>282</v>
       </c>
-      <c r="D2" s="49" t="s">
+      <c r="D2" s="46" t="s">
         <v>312</v>
       </c>
       <c r="E2" s="42" t="s">
@@ -2921,27 +3085,27 @@
       <c r="D3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="51" t="s">
+      <c r="E3" s="42" t="s">
         <v>313</v>
       </c>
-      <c r="F3" s="51" t="s">
+      <c r="F3" s="42" t="s">
         <v>313</v>
       </c>
-      <c r="G3" s="51" t="s">
+      <c r="G3" s="42" t="s">
         <v>332</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15" x14ac:dyDescent="0.3">
-      <c r="A4" s="50" t="s">
+      <c r="A4" s="47" t="s">
         <v>290</v>
       </c>
       <c r="B4" s="44" t="s">
         <v>315</v>
       </c>
-      <c r="C4" s="50">
+      <c r="C4" s="47">
         <v>100</v>
       </c>
-      <c r="D4" s="50" t="s">
+      <c r="D4" s="47" t="s">
         <v>291</v>
       </c>
       <c r="E4" s="10"/>
@@ -2951,16 +3115,16 @@
       </c>
     </row>
     <row r="5" spans="1:7" ht="15" x14ac:dyDescent="0.3">
-      <c r="A5" s="50" t="s">
+      <c r="A5" s="47" t="s">
         <v>292</v>
       </c>
       <c r="B5" s="44" t="s">
         <v>316</v>
       </c>
-      <c r="C5" s="50">
+      <c r="C5" s="47">
         <v>100</v>
       </c>
-      <c r="D5" s="50" t="s">
+      <c r="D5" s="47" t="s">
         <v>293</v>
       </c>
       <c r="E5" s="10"/>
@@ -2970,16 +3134,16 @@
       </c>
     </row>
     <row r="6" spans="1:7" ht="15" x14ac:dyDescent="0.3">
-      <c r="A6" s="50" t="s">
+      <c r="A6" s="47" t="s">
         <v>294</v>
       </c>
       <c r="B6" s="44" t="s">
         <v>317</v>
       </c>
-      <c r="C6" s="50">
+      <c r="C6" s="47">
         <v>3</v>
       </c>
-      <c r="D6" s="50" t="s">
+      <c r="D6" s="47" t="s">
         <v>295</v>
       </c>
       <c r="E6" s="10"/>
@@ -2989,16 +3153,16 @@
       </c>
     </row>
     <row r="7" spans="1:7" ht="15" x14ac:dyDescent="0.3">
-      <c r="A7" s="50" t="s">
+      <c r="A7" s="47" t="s">
         <v>296</v>
       </c>
       <c r="B7" s="44" t="s">
         <v>318</v>
       </c>
-      <c r="C7" s="50">
+      <c r="C7" s="47">
         <v>3</v>
       </c>
-      <c r="D7" s="50" t="s">
+      <c r="D7" s="47" t="s">
         <v>297</v>
       </c>
       <c r="E7" s="10"/>
@@ -3008,16 +3172,16 @@
       </c>
     </row>
     <row r="8" spans="1:7" ht="15" x14ac:dyDescent="0.3">
-      <c r="A8" s="50" t="s">
+      <c r="A8" s="47" t="s">
         <v>298</v>
       </c>
       <c r="B8" s="44" t="s">
         <v>319</v>
       </c>
-      <c r="C8" s="50">
-        <v>10</v>
-      </c>
-      <c r="D8" s="50" t="s">
+      <c r="C8" s="47">
+        <v>10</v>
+      </c>
+      <c r="D8" s="47" t="s">
         <v>299</v>
       </c>
       <c r="E8" s="10"/>
@@ -3027,16 +3191,16 @@
       </c>
     </row>
     <row r="9" spans="1:7" ht="15" x14ac:dyDescent="0.3">
-      <c r="A9" s="50" t="s">
+      <c r="A9" s="47" t="s">
         <v>300</v>
       </c>
       <c r="B9" s="44" t="s">
         <v>320</v>
       </c>
-      <c r="C9" s="50">
-        <v>0</v>
-      </c>
-      <c r="D9" s="50" t="s">
+      <c r="C9" s="47">
+        <v>0</v>
+      </c>
+      <c r="D9" s="47" t="s">
         <v>301</v>
       </c>
       <c r="E9" s="10"/>
@@ -3046,16 +3210,16 @@
       </c>
     </row>
     <row r="10" spans="1:7" ht="15" x14ac:dyDescent="0.3">
-      <c r="A10" s="50" t="s">
+      <c r="A10" s="47" t="s">
         <v>302</v>
       </c>
       <c r="B10" s="44" t="s">
         <v>321</v>
       </c>
-      <c r="C10" s="50">
-        <v>0</v>
-      </c>
-      <c r="D10" s="50" t="s">
+      <c r="C10" s="47">
+        <v>0</v>
+      </c>
+      <c r="D10" s="47" t="s">
         <v>303</v>
       </c>
       <c r="E10" s="10"/>
@@ -3065,16 +3229,16 @@
       </c>
     </row>
     <row r="11" spans="1:7" ht="15" x14ac:dyDescent="0.3">
-      <c r="A11" s="50" t="s">
+      <c r="A11" s="47" t="s">
         <v>304</v>
       </c>
       <c r="B11" s="44" t="s">
         <v>322</v>
       </c>
-      <c r="C11" s="50">
-        <v>0</v>
-      </c>
-      <c r="D11" s="50" t="s">
+      <c r="C11" s="47">
+        <v>0</v>
+      </c>
+      <c r="D11" s="47" t="s">
         <v>305</v>
       </c>
       <c r="E11" s="10"/>
@@ -3084,16 +3248,16 @@
       </c>
     </row>
     <row r="12" spans="1:7" ht="15" x14ac:dyDescent="0.3">
-      <c r="A12" s="50" t="s">
+      <c r="A12" s="47" t="s">
         <v>306</v>
       </c>
       <c r="B12" s="44" t="s">
         <v>323</v>
       </c>
-      <c r="C12" s="50">
-        <v>0</v>
-      </c>
-      <c r="D12" s="50" t="s">
+      <c r="C12" s="47">
+        <v>0</v>
+      </c>
+      <c r="D12" s="47" t="s">
         <v>307</v>
       </c>
       <c r="E12" s="10"/>
@@ -3103,16 +3267,16 @@
       </c>
     </row>
     <row r="13" spans="1:7" ht="15" x14ac:dyDescent="0.3">
-      <c r="A13" s="50" t="s">
+      <c r="A13" s="47" t="s">
         <v>308</v>
       </c>
       <c r="B13" s="44" t="s">
         <v>324</v>
       </c>
-      <c r="C13" s="50">
-        <v>0</v>
-      </c>
-      <c r="D13" s="50" t="s">
+      <c r="C13" s="47">
+        <v>0</v>
+      </c>
+      <c r="D13" s="47" t="s">
         <v>309</v>
       </c>
       <c r="E13" s="10"/>
@@ -3122,16 +3286,16 @@
       </c>
     </row>
     <row r="14" spans="1:7" ht="15" x14ac:dyDescent="0.3">
-      <c r="A14" s="50" t="s">
+      <c r="A14" s="47" t="s">
         <v>310</v>
       </c>
       <c r="B14" s="44" t="s">
         <v>325</v>
       </c>
-      <c r="C14" s="50">
-        <v>0</v>
-      </c>
-      <c r="D14" s="50" t="s">
+      <c r="C14" s="47">
+        <v>0</v>
+      </c>
+      <c r="D14" s="47" t="s">
         <v>311</v>
       </c>
       <c r="E14" s="10"/>

--- a/xlsdir/配置-总表.xlsx
+++ b/xlsdir/配置-总表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\24102\Documents\project-sx\xlsdir\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B98A1EB7-638A-4A07-8515-2A960348BB20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE5FA949-7E6B-4D8E-9F2E-0A30BCC53742}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="673" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="673" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="combat|战斗" sheetId="31" r:id="rId1"/>
@@ -18,11 +18,10 @@
     <sheet name="hero|玩家角色" sheetId="27" r:id="rId3"/>
     <sheet name="monster|魔物" sheetId="28" r:id="rId4"/>
     <sheet name="card|卡牌" sheetId="29" r:id="rId5"/>
-    <sheet name="ability|技能" sheetId="33" r:id="rId6"/>
-    <sheet name="ability_effect|技能效果" sheetId="34" r:id="rId7"/>
-    <sheet name="attribute|属性" sheetId="35" r:id="rId8"/>
-    <sheet name="Sheet1" sheetId="11" r:id="rId9"/>
-    <sheet name="sheet2" sheetId="30" r:id="rId10"/>
+    <sheet name="ability_effect|技能效果" sheetId="34" r:id="rId6"/>
+    <sheet name="attribute|属性" sheetId="35" r:id="rId7"/>
+    <sheet name="Sheet1" sheetId="11" r:id="rId8"/>
+    <sheet name="sheet2" sheetId="30" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'monster|魔物'!$A$1:$B$4</definedName>
@@ -43,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="351">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="346">
   <si>
     <t>ID</t>
   </si>
@@ -988,18 +987,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>技能名</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>ability_name</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能描述</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>effect_name</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -1191,38 +1178,14 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>abilityID</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能ID</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>string</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>能量消耗</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>效果ID列表</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>触发时机</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>类别</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>cost</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>int</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -1240,10 +1203,6 @@
   </si>
   <si>
     <t>type</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>trigger</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
@@ -1263,6 +1222,36 @@
   </si>
   <si>
     <t>技能</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标类型
+0、继承主人
+1、自身
+2、对方单体
+3、对方全体</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>effect_type</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>effect_parameters</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>效果类型
+1、造成伤害
+2、获取护盾
+3、给予BUFF</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>效果参数，根据类型。*号分割
+1、伤害值
+2、护盾值
+3、BUFFID</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -1323,12 +1312,14 @@
       <family val="2"/>
     </font>
     <font>
+      <b/>
       <sz val="9.6"/>
       <color rgb="FF374151"/>
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
     <font>
+      <b/>
       <sz val="9.6"/>
       <color rgb="FF374151"/>
       <name val="宋体"/>
@@ -1350,7 +1341,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="30">
+  <borders count="29">
     <border>
       <left/>
       <right/>
@@ -1724,17 +1715,6 @@
         <color auto="1"/>
       </left>
       <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -1745,7 +1725,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1882,31 +1862,34 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2277,64 +2260,7 @@
         <v>14</v>
       </c>
       <c r="D4" s="10"/>
-      <c r="E4" s="10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="C7:F9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="7" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C7" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="D7">
-        <v>5</v>
-      </c>
-      <c r="E7" t="str">
-        <f t="shared" ref="E7:E9" si="0">C7&amp;"*"&amp;D7</f>
-        <v>strike*5</v>
-      </c>
-    </row>
-    <row r="8" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C8" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D8">
-        <v>4</v>
-      </c>
-      <c r="E8" t="str">
-        <f t="shared" si="0"/>
-        <v>defense*4</v>
-      </c>
-      <c r="F8" t="str">
-        <f>E7&amp;"*"&amp;E8</f>
-        <v>strike*5*defense*4</v>
-      </c>
-    </row>
-    <row r="9" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C9" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="E9" t="str">
-        <f t="shared" si="0"/>
-        <v>trounce*1</v>
-      </c>
-      <c r="F9" t="str">
-        <f>F8&amp;"*"&amp;E9</f>
-        <v>strike*5*defense*4*trounce*1</v>
-      </c>
+      <c r="E4" s="10"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
@@ -2571,16 +2497,19 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="3" width="11.59765625" customWidth="1"/>
     <col min="4" max="4" width="5.86328125" customWidth="1"/>
     <col min="5" max="5" width="24.6640625" customWidth="1"/>
     <col min="6" max="6" width="56.19921875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.3984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.06640625"/>
+    <col min="9" max="9" width="25.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -2599,11 +2528,17 @@
       <c r="F1" s="42" t="s">
         <v>270</v>
       </c>
-      <c r="G1" s="48" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="G1" s="42" t="s">
+        <v>337</v>
+      </c>
+      <c r="H1" s="42" t="s">
+        <v>336</v>
+      </c>
+      <c r="I1" s="42" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="81" x14ac:dyDescent="0.3">
       <c r="A2" s="34" t="s">
         <v>5</v>
       </c>
@@ -2622,11 +2557,17 @@
       <c r="F2" s="43" t="s">
         <v>269</v>
       </c>
-      <c r="G2" s="49" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G2" s="47" t="s">
+        <v>338</v>
+      </c>
+      <c r="H2" s="46" t="s">
+        <v>331</v>
+      </c>
+      <c r="I2" s="46" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>10</v>
       </c>
@@ -2645,11 +2586,17 @@
       <c r="F3" s="42" t="s">
         <v>268</v>
       </c>
-      <c r="G3" s="48" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G3" s="42" t="s">
+        <v>332</v>
+      </c>
+      <c r="H3" s="42" t="s">
+        <v>275</v>
+      </c>
+      <c r="I3" s="42" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
         <v>34</v>
       </c>
@@ -2668,11 +2615,17 @@
       <c r="F4" s="44" t="s">
         <v>272</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="G4" s="10">
+        <v>2</v>
+      </c>
+      <c r="H4" s="44" t="s">
+        <v>339</v>
+      </c>
+      <c r="I4" s="10" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>37</v>
       </c>
@@ -2691,11 +2644,17 @@
       <c r="F5" s="10" t="s">
         <v>271</v>
       </c>
-      <c r="G5" s="10" t="s">
+      <c r="G5" s="10">
+        <v>1</v>
+      </c>
+      <c r="H5" s="44" t="s">
+        <v>340</v>
+      </c>
+      <c r="I5" s="10" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
         <v>40</v>
       </c>
@@ -2714,8 +2673,14 @@
       <c r="F6" s="44" t="s">
         <v>273</v>
       </c>
-      <c r="G6" s="10" t="s">
-        <v>40</v>
+      <c r="G6" s="10">
+        <v>2</v>
+      </c>
+      <c r="H6" s="44" t="s">
+        <v>339</v>
+      </c>
+      <c r="I6" s="44" t="s">
+        <v>335</v>
       </c>
     </row>
   </sheetData>
@@ -2725,18 +2690,18 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B33D2148-8412-4B4D-9F87-3CA753CB34C0}">
-  <dimension ref="A1:I6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A5D68F6-6A69-4994-8A54-CD8F7D229E72}">
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="16.73046875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="27.265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.3984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="25.3984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.3984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.3984375" customWidth="1"/>
+    <col min="6" max="6" width="16.9296875" customWidth="1"/>
+    <col min="7" max="7" width="37.73046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -2744,57 +2709,45 @@
         <v>274</v>
       </c>
       <c r="C1" s="42" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>4</v>
       </c>
       <c r="E1" s="42" t="s">
-        <v>340</v>
-      </c>
-      <c r="F1" s="42" t="s">
-        <v>347</v>
-      </c>
-      <c r="G1" s="42" t="s">
-        <v>346</v>
-      </c>
-      <c r="H1" s="42" t="s">
+        <v>337</v>
+      </c>
+      <c r="F1" s="49" t="s">
+        <v>342</v>
+      </c>
+      <c r="G1" s="49" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="67.5" x14ac:dyDescent="0.3">
+      <c r="A2" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="42" t="s">
+        <v>274</v>
+      </c>
+      <c r="C2" s="42" t="s">
+        <v>279</v>
+      </c>
+      <c r="D2" s="42" t="s">
+        <v>280</v>
+      </c>
+      <c r="E2" s="47" t="s">
+        <v>341</v>
+      </c>
+      <c r="F2" s="50" t="s">
+        <v>344</v>
+      </c>
+      <c r="G2" s="50" t="s">
         <v>345</v>
       </c>
-      <c r="I1" s="42" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" s="52" customFormat="1" ht="54" x14ac:dyDescent="0.3">
-      <c r="A2" s="50" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="51" t="s">
-        <v>274</v>
-      </c>
-      <c r="C2" s="51" t="s">
-        <v>276</v>
-      </c>
-      <c r="D2" s="51" t="s">
-        <v>278</v>
-      </c>
-      <c r="E2" s="51" t="s">
-        <v>336</v>
-      </c>
-      <c r="F2" s="53" t="s">
-        <v>348</v>
-      </c>
-      <c r="G2" s="51" t="s">
-        <v>338</v>
-      </c>
-      <c r="H2" s="51" t="s">
-        <v>339</v>
-      </c>
-      <c r="I2" s="51" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>10</v>
       </c>
@@ -2808,22 +2761,16 @@
         <v>10</v>
       </c>
       <c r="E3" s="42" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="F3" s="42" t="s">
-        <v>275</v>
+        <v>332</v>
       </c>
       <c r="G3" s="42" t="s">
-        <v>275</v>
-      </c>
-      <c r="H3" s="42" t="s">
-        <v>275</v>
-      </c>
-      <c r="I3" s="42" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
         <v>34</v>
       </c>
@@ -2835,22 +2782,16 @@
         <v>36</v>
       </c>
       <c r="E4" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4" s="10">
-        <v>0</v>
-      </c>
-      <c r="H4" s="44" t="s">
-        <v>349</v>
-      </c>
-      <c r="I4" s="10" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>37</v>
       </c>
@@ -2862,47 +2803,54 @@
         <v>39</v>
       </c>
       <c r="E5" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5" s="10">
-        <v>0</v>
-      </c>
-      <c r="H5" s="44" t="s">
-        <v>350</v>
-      </c>
-      <c r="I5" s="10" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="10" t="s">
-        <v>40</v>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="44" t="s">
+        <v>282</v>
       </c>
       <c r="B6" s="10"/>
       <c r="C6" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="D6" s="10" t="s">
-        <v>42</v>
+      <c r="D6" s="44" t="s">
+        <v>278</v>
       </c>
       <c r="E6" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F6" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6" s="10">
-        <v>0</v>
-      </c>
-      <c r="H6" s="44" t="s">
-        <v>349</v>
-      </c>
-      <c r="I6" s="44" t="s">
-        <v>344</v>
-      </c>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="44" t="s">
+        <v>283</v>
+      </c>
+      <c r="B7" s="10"/>
+      <c r="C7" s="10" t="s">
+        <v>281</v>
+      </c>
+      <c r="D7" s="44" t="s">
+        <v>277</v>
+      </c>
+      <c r="E7" s="48">
+        <v>0</v>
+      </c>
+      <c r="F7" s="10">
+        <v>3</v>
+      </c>
+      <c r="G7" s="10"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
@@ -2911,103 +2859,335 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A5D68F6-6A69-4994-8A54-CD8F7D229E72}">
-  <dimension ref="A1:D7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5EA7D5D-311E-4C1E-90F0-7DA998873B51}">
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.3984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="27.265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.86328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="38.73046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="42" t="s">
-        <v>274</v>
-      </c>
-      <c r="C1" s="42" t="s">
+    <row r="1" spans="1:7" ht="15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="51" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="51" t="s">
+        <v>284</v>
+      </c>
+      <c r="C1" s="51" t="s">
+        <v>285</v>
+      </c>
+      <c r="D1" s="51" t="s">
+        <v>328</v>
+      </c>
+      <c r="E1" s="51" t="s">
+        <v>327</v>
+      </c>
+      <c r="F1" s="51" t="s">
+        <v>326</v>
+      </c>
+      <c r="G1" s="51" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="52" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="53" t="s">
+        <v>311</v>
+      </c>
+      <c r="C2" s="53" t="s">
         <v>279</v>
       </c>
-      <c r="D1" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="34" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="42" t="s">
-        <v>274</v>
-      </c>
-      <c r="C2" s="42" t="s">
-        <v>282</v>
-      </c>
-      <c r="D2" s="42" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="42" t="s">
-        <v>274</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="B5" s="10"/>
-      <c r="C5" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="44" t="s">
-        <v>285</v>
-      </c>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="D6" s="44" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="44" t="s">
-        <v>286</v>
-      </c>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10" t="s">
-        <v>284</v>
-      </c>
-      <c r="D7" s="44" t="s">
-        <v>280</v>
+      <c r="D2" s="53" t="s">
+        <v>323</v>
+      </c>
+      <c r="E2" s="53" t="s">
+        <v>324</v>
+      </c>
+      <c r="F2" s="53" t="s">
+        <v>325</v>
+      </c>
+      <c r="G2" s="54" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="53" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="53" t="s">
+        <v>275</v>
+      </c>
+      <c r="C3" s="53" t="s">
+        <v>310</v>
+      </c>
+      <c r="D3" s="53" t="s">
+        <v>310</v>
+      </c>
+      <c r="E3" s="53" t="s">
+        <v>310</v>
+      </c>
+      <c r="F3" s="53" t="s">
+        <v>329</v>
+      </c>
+      <c r="G3" s="53" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15" x14ac:dyDescent="0.3">
+      <c r="A4" s="45" t="s">
+        <v>287</v>
+      </c>
+      <c r="B4" s="44" t="s">
+        <v>312</v>
+      </c>
+      <c r="C4" s="45">
+        <v>100</v>
+      </c>
+      <c r="D4" s="10">
+        <v>0</v>
+      </c>
+      <c r="E4" s="10">
+        <v>0</v>
+      </c>
+      <c r="F4" s="10">
+        <v>1</v>
+      </c>
+      <c r="G4" s="45" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15" x14ac:dyDescent="0.3">
+      <c r="A5" s="45" t="s">
+        <v>289</v>
+      </c>
+      <c r="B5" s="44" t="s">
+        <v>313</v>
+      </c>
+      <c r="C5" s="45">
+        <v>100</v>
+      </c>
+      <c r="D5" s="10">
+        <v>0</v>
+      </c>
+      <c r="E5" s="10">
+        <v>0</v>
+      </c>
+      <c r="F5" s="10">
+        <v>1</v>
+      </c>
+      <c r="G5" s="45" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15" x14ac:dyDescent="0.3">
+      <c r="A6" s="45" t="s">
+        <v>291</v>
+      </c>
+      <c r="B6" s="44" t="s">
+        <v>314</v>
+      </c>
+      <c r="C6" s="45">
+        <v>3</v>
+      </c>
+      <c r="D6" s="10">
+        <v>0</v>
+      </c>
+      <c r="E6" s="10">
+        <v>0</v>
+      </c>
+      <c r="F6" s="10">
+        <v>1</v>
+      </c>
+      <c r="G6" s="45" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15" x14ac:dyDescent="0.3">
+      <c r="A7" s="45" t="s">
+        <v>293</v>
+      </c>
+      <c r="B7" s="44" t="s">
+        <v>315</v>
+      </c>
+      <c r="C7" s="45">
+        <v>3</v>
+      </c>
+      <c r="D7" s="10">
+        <v>0</v>
+      </c>
+      <c r="E7" s="10">
+        <v>0</v>
+      </c>
+      <c r="F7" s="10">
+        <v>1</v>
+      </c>
+      <c r="G7" s="45" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15" x14ac:dyDescent="0.3">
+      <c r="A8" s="45" t="s">
+        <v>295</v>
+      </c>
+      <c r="B8" s="44" t="s">
+        <v>316</v>
+      </c>
+      <c r="C8" s="45">
+        <v>10</v>
+      </c>
+      <c r="D8" s="10">
+        <v>0</v>
+      </c>
+      <c r="E8" s="10">
+        <v>0</v>
+      </c>
+      <c r="F8" s="10">
+        <v>1</v>
+      </c>
+      <c r="G8" s="45" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15" x14ac:dyDescent="0.3">
+      <c r="A9" s="45" t="s">
+        <v>297</v>
+      </c>
+      <c r="B9" s="44" t="s">
+        <v>317</v>
+      </c>
+      <c r="C9" s="45">
+        <v>0</v>
+      </c>
+      <c r="D9" s="10">
+        <v>0</v>
+      </c>
+      <c r="E9" s="10">
+        <v>0</v>
+      </c>
+      <c r="F9" s="10">
+        <v>1</v>
+      </c>
+      <c r="G9" s="45" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15" x14ac:dyDescent="0.3">
+      <c r="A10" s="45" t="s">
+        <v>299</v>
+      </c>
+      <c r="B10" s="44" t="s">
+        <v>318</v>
+      </c>
+      <c r="C10" s="45">
+        <v>0</v>
+      </c>
+      <c r="D10" s="10">
+        <v>0</v>
+      </c>
+      <c r="E10" s="10">
+        <v>0</v>
+      </c>
+      <c r="F10" s="10">
+        <v>1</v>
+      </c>
+      <c r="G10" s="45" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15" x14ac:dyDescent="0.3">
+      <c r="A11" s="45" t="s">
+        <v>301</v>
+      </c>
+      <c r="B11" s="44" t="s">
+        <v>319</v>
+      </c>
+      <c r="C11" s="45">
+        <v>0</v>
+      </c>
+      <c r="D11" s="10">
+        <v>0</v>
+      </c>
+      <c r="E11" s="10">
+        <v>0</v>
+      </c>
+      <c r="F11" s="10">
+        <v>1</v>
+      </c>
+      <c r="G11" s="45" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15" x14ac:dyDescent="0.3">
+      <c r="A12" s="45" t="s">
+        <v>303</v>
+      </c>
+      <c r="B12" s="44" t="s">
+        <v>320</v>
+      </c>
+      <c r="C12" s="45">
+        <v>0</v>
+      </c>
+      <c r="D12" s="10">
+        <v>0</v>
+      </c>
+      <c r="E12" s="10">
+        <v>0</v>
+      </c>
+      <c r="F12" s="10">
+        <v>1</v>
+      </c>
+      <c r="G12" s="45" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15" x14ac:dyDescent="0.3">
+      <c r="A13" s="45" t="s">
+        <v>305</v>
+      </c>
+      <c r="B13" s="44" t="s">
+        <v>321</v>
+      </c>
+      <c r="C13" s="45">
+        <v>0</v>
+      </c>
+      <c r="D13" s="10">
+        <v>0</v>
+      </c>
+      <c r="E13" s="10">
+        <v>0</v>
+      </c>
+      <c r="F13" s="10">
+        <v>1</v>
+      </c>
+      <c r="G13" s="45" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="15" x14ac:dyDescent="0.3">
+      <c r="A14" s="45" t="s">
+        <v>307</v>
+      </c>
+      <c r="B14" s="44" t="s">
+        <v>322</v>
+      </c>
+      <c r="C14" s="45">
+        <v>0</v>
+      </c>
+      <c r="D14" s="10">
+        <v>0</v>
+      </c>
+      <c r="E14" s="10">
+        <v>0</v>
+      </c>
+      <c r="F14" s="10">
+        <v>1</v>
+      </c>
+      <c r="G14" s="45" t="s">
+        <v>308</v>
       </c>
     </row>
   </sheetData>
@@ -3017,300 +3197,6 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5EA7D5D-311E-4C1E-90F0-7DA998873B51}">
-  <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="20.46484375" customWidth="1"/>
-    <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" ht="15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="45" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="45" t="s">
-        <v>287</v>
-      </c>
-      <c r="C1" s="45" t="s">
-        <v>288</v>
-      </c>
-      <c r="D1" s="45" t="s">
-        <v>289</v>
-      </c>
-      <c r="E1" s="45" t="s">
-        <v>331</v>
-      </c>
-      <c r="F1" s="45" t="s">
-        <v>330</v>
-      </c>
-      <c r="G1" s="45" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="34" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="42" t="s">
-        <v>314</v>
-      </c>
-      <c r="C2" s="42" t="s">
-        <v>282</v>
-      </c>
-      <c r="D2" s="46" t="s">
-        <v>312</v>
-      </c>
-      <c r="E2" s="42" t="s">
-        <v>326</v>
-      </c>
-      <c r="F2" s="42" t="s">
-        <v>327</v>
-      </c>
-      <c r="G2" s="42" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="42" t="s">
-        <v>275</v>
-      </c>
-      <c r="C3" s="42" t="s">
-        <v>313</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="42" t="s">
-        <v>313</v>
-      </c>
-      <c r="F3" s="42" t="s">
-        <v>313</v>
-      </c>
-      <c r="G3" s="42" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="15" x14ac:dyDescent="0.3">
-      <c r="A4" s="47" t="s">
-        <v>290</v>
-      </c>
-      <c r="B4" s="44" t="s">
-        <v>315</v>
-      </c>
-      <c r="C4" s="47">
-        <v>100</v>
-      </c>
-      <c r="D4" s="47" t="s">
-        <v>291</v>
-      </c>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="15" x14ac:dyDescent="0.3">
-      <c r="A5" s="47" t="s">
-        <v>292</v>
-      </c>
-      <c r="B5" s="44" t="s">
-        <v>316</v>
-      </c>
-      <c r="C5" s="47">
-        <v>100</v>
-      </c>
-      <c r="D5" s="47" t="s">
-        <v>293</v>
-      </c>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="15" x14ac:dyDescent="0.3">
-      <c r="A6" s="47" t="s">
-        <v>294</v>
-      </c>
-      <c r="B6" s="44" t="s">
-        <v>317</v>
-      </c>
-      <c r="C6" s="47">
-        <v>3</v>
-      </c>
-      <c r="D6" s="47" t="s">
-        <v>295</v>
-      </c>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="15" x14ac:dyDescent="0.3">
-      <c r="A7" s="47" t="s">
-        <v>296</v>
-      </c>
-      <c r="B7" s="44" t="s">
-        <v>318</v>
-      </c>
-      <c r="C7" s="47">
-        <v>3</v>
-      </c>
-      <c r="D7" s="47" t="s">
-        <v>297</v>
-      </c>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="15" x14ac:dyDescent="0.3">
-      <c r="A8" s="47" t="s">
-        <v>298</v>
-      </c>
-      <c r="B8" s="44" t="s">
-        <v>319</v>
-      </c>
-      <c r="C8" s="47">
-        <v>10</v>
-      </c>
-      <c r="D8" s="47" t="s">
-        <v>299</v>
-      </c>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="15" x14ac:dyDescent="0.3">
-      <c r="A9" s="47" t="s">
-        <v>300</v>
-      </c>
-      <c r="B9" s="44" t="s">
-        <v>320</v>
-      </c>
-      <c r="C9" s="47">
-        <v>0</v>
-      </c>
-      <c r="D9" s="47" t="s">
-        <v>301</v>
-      </c>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="15" x14ac:dyDescent="0.3">
-      <c r="A10" s="47" t="s">
-        <v>302</v>
-      </c>
-      <c r="B10" s="44" t="s">
-        <v>321</v>
-      </c>
-      <c r="C10" s="47">
-        <v>0</v>
-      </c>
-      <c r="D10" s="47" t="s">
-        <v>303</v>
-      </c>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="15" x14ac:dyDescent="0.3">
-      <c r="A11" s="47" t="s">
-        <v>304</v>
-      </c>
-      <c r="B11" s="44" t="s">
-        <v>322</v>
-      </c>
-      <c r="C11" s="47">
-        <v>0</v>
-      </c>
-      <c r="D11" s="47" t="s">
-        <v>305</v>
-      </c>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="15" x14ac:dyDescent="0.3">
-      <c r="A12" s="47" t="s">
-        <v>306</v>
-      </c>
-      <c r="B12" s="44" t="s">
-        <v>323</v>
-      </c>
-      <c r="C12" s="47">
-        <v>0</v>
-      </c>
-      <c r="D12" s="47" t="s">
-        <v>307</v>
-      </c>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="15" x14ac:dyDescent="0.3">
-      <c r="A13" s="47" t="s">
-        <v>308</v>
-      </c>
-      <c r="B13" s="44" t="s">
-        <v>324</v>
-      </c>
-      <c r="C13" s="47">
-        <v>0</v>
-      </c>
-      <c r="D13" s="47" t="s">
-        <v>309</v>
-      </c>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="15" x14ac:dyDescent="0.3">
-      <c r="A14" s="47" t="s">
-        <v>310</v>
-      </c>
-      <c r="B14" s="44" t="s">
-        <v>325</v>
-      </c>
-      <c r="C14" s="47">
-        <v>0</v>
-      </c>
-      <c r="D14" s="47" t="s">
-        <v>311</v>
-      </c>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:AA41"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
@@ -6334,4 +6220,59 @@
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="C7:F9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="7" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C7" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7">
+        <v>5</v>
+      </c>
+      <c r="E7" t="str">
+        <f t="shared" ref="E7:E9" si="0">C7&amp;"*"&amp;D7</f>
+        <v>strike*5</v>
+      </c>
+    </row>
+    <row r="8" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C8" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8">
+        <v>4</v>
+      </c>
+      <c r="E8" t="str">
+        <f t="shared" si="0"/>
+        <v>defense*4</v>
+      </c>
+      <c r="F8" t="str">
+        <f>E7&amp;"*"&amp;E8</f>
+        <v>strike*5*defense*4</v>
+      </c>
+    </row>
+    <row r="9" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C9" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9" t="str">
+        <f t="shared" si="0"/>
+        <v>trounce*1</v>
+      </c>
+      <c r="F9" t="str">
+        <f>F8&amp;"*"&amp;E9</f>
+        <v>strike*5*defense*4*trounce*1</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/xlsdir/配置-总表.xlsx
+++ b/xlsdir/配置-总表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\24102\Documents\project-sx\xlsdir\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE5FA949-7E6B-4D8E-9F2E-0A30BCC53742}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2993DBC-3C2D-4BB5-8A68-3BA8A81D7713}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="673" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" tabRatio="673" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="combat|战斗" sheetId="31" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="343">
   <si>
     <t>ID</t>
   </si>
@@ -1182,10 +1182,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>类别</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>int</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -1199,10 +1195,6 @@
   </si>
   <si>
     <t>trounce_01*trounce_02</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>type</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
@@ -1214,14 +1206,6 @@
 1、自身
 2、对方单体
 3、对方全体</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
@@ -1253,6 +1237,10 @@
 2、护盾值
 3、BUFFID</t>
     <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>card_description</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2260,7 +2248,9 @@
         <v>14</v>
       </c>
       <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
+      <c r="E4" s="10" t="s">
+        <v>14</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
@@ -2497,19 +2487,18 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="3" width="11.59765625" customWidth="1"/>
     <col min="4" max="4" width="5.86328125" customWidth="1"/>
     <col min="5" max="5" width="24.6640625" customWidth="1"/>
     <col min="6" max="6" width="56.19921875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.3984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.06640625"/>
-    <col min="9" max="9" width="25.3984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -2522,23 +2511,20 @@
       <c r="D1" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>4</v>
+      <c r="E1" s="42" t="s">
+        <v>342</v>
       </c>
       <c r="F1" s="42" t="s">
         <v>270</v>
       </c>
       <c r="G1" s="42" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="H1" s="42" t="s">
-        <v>336</v>
-      </c>
-      <c r="I1" s="42" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="81" x14ac:dyDescent="0.3">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="54" x14ac:dyDescent="0.3">
       <c r="A2" s="34" t="s">
         <v>5</v>
       </c>
@@ -2558,16 +2544,13 @@
         <v>269</v>
       </c>
       <c r="G2" s="47" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="H2" s="46" t="s">
-        <v>331</v>
-      </c>
-      <c r="I2" s="46" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>10</v>
       </c>
@@ -2587,16 +2570,13 @@
         <v>268</v>
       </c>
       <c r="G3" s="42" t="s">
+        <v>331</v>
+      </c>
+      <c r="H3" s="42" t="s">
         <v>332</v>
       </c>
-      <c r="H3" s="42" t="s">
-        <v>275</v>
-      </c>
-      <c r="I3" s="42" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
         <v>34</v>
       </c>
@@ -2618,14 +2598,11 @@
       <c r="G4" s="10">
         <v>2</v>
       </c>
-      <c r="H4" s="44" t="s">
-        <v>339</v>
-      </c>
-      <c r="I4" s="10" t="s">
+      <c r="H4" s="10" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>37</v>
       </c>
@@ -2647,14 +2624,11 @@
       <c r="G5" s="10">
         <v>1</v>
       </c>
-      <c r="H5" s="44" t="s">
-        <v>340</v>
-      </c>
-      <c r="I5" s="10" t="s">
+      <c r="H5" s="10" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
         <v>40</v>
       </c>
@@ -2677,10 +2651,7 @@
         <v>2</v>
       </c>
       <c r="H6" s="44" t="s">
-        <v>339</v>
-      </c>
-      <c r="I6" s="44" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
   </sheetData>
@@ -2715,13 +2686,13 @@
         <v>4</v>
       </c>
       <c r="E1" s="42" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="F1" s="49" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="G1" s="49" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="67.5" x14ac:dyDescent="0.3">
@@ -2738,13 +2709,13 @@
         <v>280</v>
       </c>
       <c r="E2" s="47" t="s">
+        <v>337</v>
+      </c>
+      <c r="F2" s="50" t="s">
+        <v>340</v>
+      </c>
+      <c r="G2" s="50" t="s">
         <v>341</v>
-      </c>
-      <c r="F2" s="50" t="s">
-        <v>344</v>
-      </c>
-      <c r="G2" s="50" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -2761,13 +2732,13 @@
         <v>10</v>
       </c>
       <c r="E3" s="42" t="s">
+        <v>331</v>
+      </c>
+      <c r="F3" s="42" t="s">
+        <v>331</v>
+      </c>
+      <c r="G3" s="42" t="s">
         <v>332</v>
-      </c>
-      <c r="F3" s="42" t="s">
-        <v>332</v>
-      </c>
-      <c r="G3" s="42" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">

--- a/xlsdir/配置-总表.xlsx
+++ b/xlsdir/配置-总表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\24102\Documents\project-sx\xlsdir\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2993DBC-3C2D-4BB5-8A68-3BA8A81D7713}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B432C9F-B25F-450B-9A31-6E985317D49A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" tabRatio="673" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="673" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="combat|战斗" sheetId="31" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="384">
   <si>
     <t>ID</t>
   </si>
@@ -1225,13 +1225,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>效果类型
-1、造成伤害
-2、获取护盾
-3、给予BUFF</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>效果参数，根据类型。*号分割
 1、伤害值
 2、护盾值
@@ -1241,6 +1234,144 @@
   <si>
     <t>card_description</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>易伤（Vulnerable）</t>
+  </si>
+  <si>
+    <t>弱化（Weak）</t>
+  </si>
+  <si>
+    <t>中毒（Poisoned）</t>
+  </si>
+  <si>
+    <t>燃烧（Burning）</t>
+  </si>
+  <si>
+    <t>强化（Strengthened）</t>
+  </si>
+  <si>
+    <t>再生（Regenerating）</t>
+  </si>
+  <si>
+    <t>流血（Bleeding）</t>
+  </si>
+  <si>
+    <t>充能（Energized）</t>
+  </si>
+  <si>
+    <t>冻结（Frozen）</t>
+  </si>
+  <si>
+    <t>易伤</t>
+  </si>
+  <si>
+    <t>弱化</t>
+  </si>
+  <si>
+    <t>中毒</t>
+  </si>
+  <si>
+    <t>燃烧</t>
+  </si>
+  <si>
+    <t>强化</t>
+  </si>
+  <si>
+    <t>再生</t>
+  </si>
+  <si>
+    <t>流血</t>
+  </si>
+  <si>
+    <t>充能</t>
+  </si>
+  <si>
+    <t>FROZEN</t>
+  </si>
+  <si>
+    <t>冻结</t>
+  </si>
+  <si>
+    <t>VULNERABLE</t>
+  </si>
+  <si>
+    <t>WEAK</t>
+  </si>
+  <si>
+    <t>POISONED</t>
+  </si>
+  <si>
+    <t>BURNING</t>
+  </si>
+  <si>
+    <t>STRENGTHENED</t>
+  </si>
+  <si>
+    <t>REGENERATING</t>
+  </si>
+  <si>
+    <t>BLEEDING</t>
+  </si>
+  <si>
+    <t>ENERGIZED</t>
+  </si>
+  <si>
+    <t>目标受到的伤害增加50%。</t>
+  </si>
+  <si>
+    <t>目标造成的伤害减少25%。</t>
+  </si>
+  <si>
+    <t>在目标的回合开始时，中毒将造成等同于其堆叠数的伤害，并减少1点堆叠数。</t>
+  </si>
+  <si>
+    <t>每回合结束时，目标受到等同于燃烧堆叠数的伤害，然后燃烧堆叠数减半。</t>
+  </si>
+  <si>
+    <t>目标的攻击力增加。</t>
+  </si>
+  <si>
+    <t>每回合结束时，目标受到等同于流血堆叠数的伤害。</t>
+  </si>
+  <si>
+    <t>目标在下一回合获得额外的能量点数。</t>
+  </si>
+  <si>
+    <t>目标在下一回合无法行动。</t>
+  </si>
+  <si>
+    <t>duration</t>
+  </si>
+  <si>
+    <t>持续回合
+0及时
+-1永久</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>VULNERABLE*2</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>效果类型
+1、造成伤害
+2、获得护盾
+3、给予BUFF
+4、特性</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得5点护盾</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标每回合恢复5生命值。</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>shielded</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2512,7 +2643,7 @@
         <v>29</v>
       </c>
       <c r="E1" s="42" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F1" s="42" t="s">
         <v>270</v>
@@ -2624,8 +2755,8 @@
       <c r="G5" s="10">
         <v>1</v>
       </c>
-      <c r="H5" s="10" t="s">
-        <v>37</v>
+      <c r="H5" s="44" t="s">
+        <v>383</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
@@ -2662,17 +2793,18 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A5D68F6-6A69-4994-8A54-CD8F7D229E72}">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.3984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.3984375" customWidth="1"/>
-    <col min="6" max="6" width="16.9296875" customWidth="1"/>
-    <col min="7" max="7" width="37.73046875" customWidth="1"/>
+    <col min="1" max="1" width="13.265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.3984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" customWidth="1"/>
+    <col min="8" max="8" width="71.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -2682,11 +2814,11 @@
       <c r="C1" s="42" t="s">
         <v>276</v>
       </c>
-      <c r="D1" s="4" t="s">
-        <v>4</v>
+      <c r="D1" s="42" t="s">
+        <v>335</v>
       </c>
       <c r="E1" s="42" t="s">
-        <v>335</v>
+        <v>377</v>
       </c>
       <c r="F1" s="49" t="s">
         <v>338</v>
@@ -2694,8 +2826,11 @@
       <c r="G1" s="49" t="s">
         <v>339</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" ht="67.5" x14ac:dyDescent="0.3">
+      <c r="H1" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="81" x14ac:dyDescent="0.3">
       <c r="A2" s="34" t="s">
         <v>5</v>
       </c>
@@ -2705,20 +2840,23 @@
       <c r="C2" s="42" t="s">
         <v>279</v>
       </c>
-      <c r="D2" s="42" t="s">
+      <c r="D2" s="47" t="s">
+        <v>337</v>
+      </c>
+      <c r="E2" s="43" t="s">
+        <v>378</v>
+      </c>
+      <c r="F2" s="50" t="s">
+        <v>380</v>
+      </c>
+      <c r="G2" s="50" t="s">
+        <v>340</v>
+      </c>
+      <c r="H2" s="42" t="s">
         <v>280</v>
       </c>
-      <c r="E2" s="47" t="s">
-        <v>337</v>
-      </c>
-      <c r="F2" s="50" t="s">
-        <v>340</v>
-      </c>
-      <c r="G2" s="50" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>10</v>
       </c>
@@ -2728,10 +2866,10 @@
       <c r="C3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="42" t="s">
+      <c r="D3" s="42" t="s">
+        <v>331</v>
+      </c>
+      <c r="E3" s="49" t="s">
         <v>331</v>
       </c>
       <c r="F3" s="42" t="s">
@@ -2740,8 +2878,11 @@
       <c r="G3" s="42" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H3" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
         <v>34</v>
       </c>
@@ -2749,10 +2890,10 @@
       <c r="C4" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="D4" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="E4" s="10">
+      <c r="D4" s="10">
+        <v>0</v>
+      </c>
+      <c r="E4" s="48">
         <v>0</v>
       </c>
       <c r="F4" s="10">
@@ -2761,29 +2902,35 @@
       <c r="G4" s="10">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="10" t="s">
-        <v>37</v>
+      <c r="H4" s="10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="44" t="s">
+        <v>383</v>
       </c>
       <c r="B5" s="10"/>
-      <c r="C5" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="E5" s="10">
+      <c r="C5" s="44" t="s">
+        <v>322</v>
+      </c>
+      <c r="D5" s="10">
+        <v>1</v>
+      </c>
+      <c r="E5" s="48">
         <v>0</v>
       </c>
       <c r="F5" s="10">
         <v>2</v>
       </c>
-      <c r="G5" s="10">
+      <c r="G5" s="44">
         <v>5</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H5" s="44" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="44" t="s">
         <v>282</v>
       </c>
@@ -2791,10 +2938,10 @@
       <c r="C6" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="D6" s="44" t="s">
-        <v>278</v>
-      </c>
-      <c r="E6" s="10">
+      <c r="D6" s="10">
+        <v>0</v>
+      </c>
+      <c r="E6" s="48">
         <v>0</v>
       </c>
       <c r="F6" s="10">
@@ -2803,8 +2950,11 @@
       <c r="G6" s="10">
         <v>8</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H6" s="44" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="44" t="s">
         <v>283</v>
       </c>
@@ -2812,8 +2962,8 @@
       <c r="C7" s="10" t="s">
         <v>281</v>
       </c>
-      <c r="D7" s="44" t="s">
-        <v>277</v>
+      <c r="D7" s="48">
+        <v>0</v>
       </c>
       <c r="E7" s="48">
         <v>0</v>
@@ -2821,7 +2971,246 @@
       <c r="F7" s="10">
         <v>3</v>
       </c>
-      <c r="G7" s="10"/>
+      <c r="G7" s="44" t="s">
+        <v>379</v>
+      </c>
+      <c r="H7" s="44" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="10" t="s">
+        <v>361</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>342</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>351</v>
+      </c>
+      <c r="D8" s="10">
+        <v>0</v>
+      </c>
+      <c r="E8" s="10">
+        <v>2</v>
+      </c>
+      <c r="F8" s="48">
+        <v>4</v>
+      </c>
+      <c r="G8" s="10">
+        <v>1</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>343</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>352</v>
+      </c>
+      <c r="D9" s="10">
+        <v>0</v>
+      </c>
+      <c r="E9" s="10">
+        <v>1</v>
+      </c>
+      <c r="F9" s="48">
+        <v>4</v>
+      </c>
+      <c r="G9" s="10">
+        <v>2</v>
+      </c>
+      <c r="H9" s="10" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" s="10" t="s">
+        <v>363</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>344</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="D10" s="10">
+        <v>0</v>
+      </c>
+      <c r="E10" s="10">
+        <v>-1</v>
+      </c>
+      <c r="F10" s="48">
+        <v>4</v>
+      </c>
+      <c r="G10" s="10">
+        <v>3</v>
+      </c>
+      <c r="H10" s="10" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="10" t="s">
+        <v>364</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>345</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>354</v>
+      </c>
+      <c r="D11" s="10">
+        <v>0</v>
+      </c>
+      <c r="E11" s="10">
+        <v>-1</v>
+      </c>
+      <c r="F11" s="48">
+        <v>4</v>
+      </c>
+      <c r="G11" s="10">
+        <v>4</v>
+      </c>
+      <c r="H11" s="10" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" s="10" t="s">
+        <v>365</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>346</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>355</v>
+      </c>
+      <c r="D12" s="10">
+        <v>0</v>
+      </c>
+      <c r="E12" s="10">
+        <v>1</v>
+      </c>
+      <c r="F12" s="48">
+        <v>4</v>
+      </c>
+      <c r="G12" s="10">
+        <v>5</v>
+      </c>
+      <c r="H12" s="10" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" s="10" t="s">
+        <v>366</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>347</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>356</v>
+      </c>
+      <c r="D13" s="10">
+        <v>0</v>
+      </c>
+      <c r="E13" s="10">
+        <v>5</v>
+      </c>
+      <c r="F13" s="48">
+        <v>4</v>
+      </c>
+      <c r="G13" s="10">
+        <v>6</v>
+      </c>
+      <c r="H13" s="44" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>348</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>357</v>
+      </c>
+      <c r="D14" s="10">
+        <v>0</v>
+      </c>
+      <c r="E14" s="10">
+        <v>-1</v>
+      </c>
+      <c r="F14" s="48">
+        <v>4</v>
+      </c>
+      <c r="G14" s="10">
+        <v>7</v>
+      </c>
+      <c r="H14" s="10" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" s="10" t="s">
+        <v>368</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>349</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="D15" s="10">
+        <v>0</v>
+      </c>
+      <c r="E15" s="10">
+        <v>1</v>
+      </c>
+      <c r="F15" s="48">
+        <v>4</v>
+      </c>
+      <c r="G15" s="10">
+        <v>8</v>
+      </c>
+      <c r="H15" s="10" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" s="10" t="s">
+        <v>359</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>350</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>360</v>
+      </c>
+      <c r="D16" s="10">
+        <v>0</v>
+      </c>
+      <c r="E16" s="10">
+        <v>1</v>
+      </c>
+      <c r="F16" s="48">
+        <v>4</v>
+      </c>
+      <c r="G16" s="10">
+        <v>9</v>
+      </c>
+      <c r="H16" s="10" t="s">
+        <v>376</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>

--- a/xlsdir/配置-总表.xlsx
+++ b/xlsdir/配置-总表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\24102\Documents\project-sx\xlsdir\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B432C9F-B25F-450B-9A31-6E985317D49A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B5F261B-6C28-4192-B3A9-2020FE6B8D55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="673" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" tabRatio="673" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="combat|战斗" sheetId="31" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="388">
   <si>
     <t>ID</t>
   </si>
@@ -1371,6 +1371,21 @@
   </si>
   <si>
     <t>shielded</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>description</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>play_animation</t>
+  </si>
+  <si>
+    <t>施法者动作</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>items</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -1844,7 +1859,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1988,15 +2003,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -2618,7 +2624,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="3" width="11.59765625" customWidth="1"/>
@@ -2626,10 +2632,11 @@
     <col min="5" max="5" width="24.6640625" customWidth="1"/>
     <col min="6" max="6" width="56.19921875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="25.3984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.06640625"/>
+    <col min="9" max="9" width="25.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -2652,10 +2659,13 @@
         <v>335</v>
       </c>
       <c r="H1" s="42" t="s">
+        <v>385</v>
+      </c>
+      <c r="I1" s="42" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="54" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="54" x14ac:dyDescent="0.3">
       <c r="A2" s="34" t="s">
         <v>5</v>
       </c>
@@ -2677,11 +2687,14 @@
       <c r="G2" s="47" t="s">
         <v>336</v>
       </c>
-      <c r="H2" s="46" t="s">
+      <c r="H2" s="43" t="s">
+        <v>386</v>
+      </c>
+      <c r="I2" s="46" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>10</v>
       </c>
@@ -2704,10 +2717,13 @@
         <v>331</v>
       </c>
       <c r="H3" s="42" t="s">
+        <v>275</v>
+      </c>
+      <c r="I3" s="42" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
         <v>34</v>
       </c>
@@ -2729,11 +2745,12 @@
       <c r="G4" s="10">
         <v>2</v>
       </c>
-      <c r="H4" s="10" t="s">
+      <c r="H4" s="10"/>
+      <c r="I4" s="10" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>37</v>
       </c>
@@ -2756,10 +2773,13 @@
         <v>1</v>
       </c>
       <c r="H5" s="44" t="s">
+        <v>387</v>
+      </c>
+      <c r="I5" s="44" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
         <v>40</v>
       </c>
@@ -2781,9 +2801,40 @@
       <c r="G6" s="10">
         <v>2</v>
       </c>
-      <c r="H6" s="44" t="s">
+      <c r="H6" s="10"/>
+      <c r="I6" s="44" t="s">
         <v>334</v>
       </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H7" s="10"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H8" s="10"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H9" s="10"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H10" s="10"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H11" s="10"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H12" s="10"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H13" s="10"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H14" s="10"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H15" s="10"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H16" s="10"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -2820,14 +2871,14 @@
       <c r="E1" s="42" t="s">
         <v>377</v>
       </c>
-      <c r="F1" s="49" t="s">
+      <c r="F1" s="42" t="s">
         <v>338</v>
       </c>
-      <c r="G1" s="49" t="s">
+      <c r="G1" s="42" t="s">
         <v>339</v>
       </c>
-      <c r="H1" s="4" t="s">
-        <v>4</v>
+      <c r="H1" s="42" t="s">
+        <v>384</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="81" x14ac:dyDescent="0.3">
@@ -2846,10 +2897,10 @@
       <c r="E2" s="43" t="s">
         <v>378</v>
       </c>
-      <c r="F2" s="50" t="s">
+      <c r="F2" s="43" t="s">
         <v>380</v>
       </c>
-      <c r="G2" s="50" t="s">
+      <c r="G2" s="43" t="s">
         <v>340</v>
       </c>
       <c r="H2" s="42" t="s">
@@ -2860,8 +2911,8 @@
       <c r="A3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="42" t="s">
-        <v>274</v>
+      <c r="B3" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>10</v>
@@ -2869,7 +2920,7 @@
       <c r="D3" s="42" t="s">
         <v>331</v>
       </c>
-      <c r="E3" s="49" t="s">
+      <c r="E3" s="42" t="s">
         <v>331</v>
       </c>
       <c r="F3" s="42" t="s">
@@ -2893,7 +2944,7 @@
       <c r="D4" s="10">
         <v>0</v>
       </c>
-      <c r="E4" s="48">
+      <c r="E4" s="10">
         <v>0</v>
       </c>
       <c r="F4" s="10">
@@ -2917,7 +2968,7 @@
       <c r="D5" s="10">
         <v>1</v>
       </c>
-      <c r="E5" s="48">
+      <c r="E5" s="10">
         <v>0</v>
       </c>
       <c r="F5" s="10">
@@ -2941,7 +2992,7 @@
       <c r="D6" s="10">
         <v>0</v>
       </c>
-      <c r="E6" s="48">
+      <c r="E6" s="10">
         <v>0</v>
       </c>
       <c r="F6" s="10">
@@ -2962,10 +3013,10 @@
       <c r="C7" s="10" t="s">
         <v>281</v>
       </c>
-      <c r="D7" s="48">
-        <v>0</v>
-      </c>
-      <c r="E7" s="48">
+      <c r="D7" s="10">
+        <v>0</v>
+      </c>
+      <c r="E7" s="10">
         <v>0</v>
       </c>
       <c r="F7" s="10">
@@ -2994,7 +3045,7 @@
       <c r="E8" s="10">
         <v>2</v>
       </c>
-      <c r="F8" s="48">
+      <c r="F8" s="10">
         <v>4</v>
       </c>
       <c r="G8" s="10">
@@ -3020,7 +3071,7 @@
       <c r="E9" s="10">
         <v>1</v>
       </c>
-      <c r="F9" s="48">
+      <c r="F9" s="10">
         <v>4</v>
       </c>
       <c r="G9" s="10">
@@ -3046,7 +3097,7 @@
       <c r="E10" s="10">
         <v>-1</v>
       </c>
-      <c r="F10" s="48">
+      <c r="F10" s="10">
         <v>4</v>
       </c>
       <c r="G10" s="10">
@@ -3072,7 +3123,7 @@
       <c r="E11" s="10">
         <v>-1</v>
       </c>
-      <c r="F11" s="48">
+      <c r="F11" s="10">
         <v>4</v>
       </c>
       <c r="G11" s="10">
@@ -3098,7 +3149,7 @@
       <c r="E12" s="10">
         <v>1</v>
       </c>
-      <c r="F12" s="48">
+      <c r="F12" s="10">
         <v>4</v>
       </c>
       <c r="G12" s="10">
@@ -3124,7 +3175,7 @@
       <c r="E13" s="10">
         <v>5</v>
       </c>
-      <c r="F13" s="48">
+      <c r="F13" s="10">
         <v>4</v>
       </c>
       <c r="G13" s="10">
@@ -3150,7 +3201,7 @@
       <c r="E14" s="10">
         <v>-1</v>
       </c>
-      <c r="F14" s="48">
+      <c r="F14" s="10">
         <v>4</v>
       </c>
       <c r="G14" s="10">
@@ -3176,7 +3227,7 @@
       <c r="E15" s="10">
         <v>1</v>
       </c>
-      <c r="F15" s="48">
+      <c r="F15" s="10">
         <v>4</v>
       </c>
       <c r="G15" s="10">
@@ -3202,7 +3253,7 @@
       <c r="E16" s="10">
         <v>1</v>
       </c>
-      <c r="F16" s="48">
+      <c r="F16" s="10">
         <v>4</v>
       </c>
       <c r="G16" s="10">
@@ -3229,71 +3280,71 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="51" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="51" t="s">
+      <c r="A1" s="48" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="48" t="s">
         <v>284</v>
       </c>
-      <c r="C1" s="51" t="s">
+      <c r="C1" s="48" t="s">
         <v>285</v>
       </c>
-      <c r="D1" s="51" t="s">
+      <c r="D1" s="48" t="s">
         <v>328</v>
       </c>
-      <c r="E1" s="51" t="s">
+      <c r="E1" s="48" t="s">
         <v>327</v>
       </c>
-      <c r="F1" s="51" t="s">
+      <c r="F1" s="48" t="s">
         <v>326</v>
       </c>
-      <c r="G1" s="51" t="s">
+      <c r="G1" s="48" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="52" t="s">
+      <c r="A2" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="53" t="s">
+      <c r="B2" s="50" t="s">
         <v>311</v>
       </c>
-      <c r="C2" s="53" t="s">
+      <c r="C2" s="50" t="s">
         <v>279</v>
       </c>
-      <c r="D2" s="53" t="s">
+      <c r="D2" s="50" t="s">
         <v>323</v>
       </c>
-      <c r="E2" s="53" t="s">
+      <c r="E2" s="50" t="s">
         <v>324</v>
       </c>
-      <c r="F2" s="53" t="s">
+      <c r="F2" s="50" t="s">
         <v>325</v>
       </c>
-      <c r="G2" s="54" t="s">
+      <c r="G2" s="51" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="53" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="53" t="s">
+      <c r="A3" s="50" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="50" t="s">
         <v>275</v>
       </c>
-      <c r="C3" s="53" t="s">
+      <c r="C3" s="50" t="s">
         <v>310</v>
       </c>
-      <c r="D3" s="53" t="s">
+      <c r="D3" s="50" t="s">
         <v>310</v>
       </c>
-      <c r="E3" s="53" t="s">
+      <c r="E3" s="50" t="s">
         <v>310</v>
       </c>
-      <c r="F3" s="53" t="s">
+      <c r="F3" s="50" t="s">
         <v>329</v>
       </c>
-      <c r="G3" s="53" t="s">
+      <c r="G3" s="50" t="s">
         <v>10</v>
       </c>
     </row>

--- a/xlsdir/配置-总表.xlsx
+++ b/xlsdir/配置-总表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\24102\Documents\project-sx\xlsdir\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B5F261B-6C28-4192-B3A9-2020FE6B8D55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCDB24C4-0E9F-42A6-959F-E24D331C9B07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" tabRatio="673" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="389">
   <si>
     <t>ID</t>
   </si>
@@ -1387,6 +1387,10 @@
   <si>
     <t>items</t>
     <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>attack_01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2632,7 +2636,7 @@
     <col min="5" max="5" width="24.6640625" customWidth="1"/>
     <col min="6" max="6" width="56.19921875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.06640625"/>
+    <col min="8" max="8" width="16.3984375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="25.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2745,7 +2749,9 @@
       <c r="G4" s="10">
         <v>2</v>
       </c>
-      <c r="H4" s="10"/>
+      <c r="H4" s="44" t="s">
+        <v>388</v>
+      </c>
       <c r="I4" s="10" t="s">
         <v>34</v>
       </c>
@@ -2801,7 +2807,9 @@
       <c r="G6" s="10">
         <v>2</v>
       </c>
-      <c r="H6" s="10"/>
+      <c r="H6" s="44" t="s">
+        <v>388</v>
+      </c>
       <c r="I6" s="44" t="s">
         <v>334</v>
       </c>

--- a/xlsdir/配置-总表.xlsx
+++ b/xlsdir/配置-总表.xlsx
@@ -8,20 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\24102\Documents\project-sx\xlsdir\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCDB24C4-0E9F-42A6-959F-E24D331C9B07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2223CB15-51F6-40E5-91FF-3E31D690A49C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" tabRatio="673" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" tabRatio="673" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="combat|战斗" sheetId="31" r:id="rId1"/>
     <sheet name="character|角色" sheetId="32" r:id="rId2"/>
     <sheet name="hero|玩家角色" sheetId="27" r:id="rId3"/>
     <sheet name="monster|魔物" sheetId="28" r:id="rId4"/>
-    <sheet name="card|卡牌" sheetId="29" r:id="rId5"/>
-    <sheet name="ability_effect|技能效果" sheetId="34" r:id="rId6"/>
-    <sheet name="attribute|属性" sheetId="35" r:id="rId7"/>
-    <sheet name="Sheet1" sheetId="11" r:id="rId8"/>
-    <sheet name="sheet2" sheetId="30" r:id="rId9"/>
+    <sheet name="intent|意图" sheetId="38" r:id="rId5"/>
+    <sheet name="card|卡牌" sheetId="29" r:id="rId6"/>
+    <sheet name="ability_effect|技能效果" sheetId="34" r:id="rId7"/>
+    <sheet name="attribute|属性" sheetId="35" r:id="rId8"/>
+    <sheet name="Sheet1" sheetId="11" r:id="rId9"/>
+    <sheet name="sheet2" sheetId="30" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'monster|魔物'!$A$1:$B$4</definedName>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="433">
   <si>
     <t>ID</t>
   </si>
@@ -1390,6 +1391,155 @@
   </si>
   <si>
     <t>attack_01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>意图名</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>type</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>意图类型</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>意图描述</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>des</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>意图图标</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击</t>
+  </si>
+  <si>
+    <t>多重攻击</t>
+  </si>
+  <si>
+    <t>敌人将提升某项能力，如攻击力、防御力或特殊能力。</t>
+  </si>
+  <si>
+    <t>敌人计划施放会削弱玩家能力的效果，如减少玩家的攻击力或防御力。</t>
+  </si>
+  <si>
+    <t>治疗</t>
+  </si>
+  <si>
+    <t>敌人会恢复一定量的生命值。</t>
+  </si>
+  <si>
+    <t>策略</t>
+  </si>
+  <si>
+    <t>敌人将采取某种特殊行动，如召唤援助、准备强力攻击或其他战术动作。</t>
+  </si>
+  <si>
+    <t>逃跑</t>
+  </si>
+  <si>
+    <t>在某些战斗中，敌人可能会试图逃跑，尤其是在遭遇战中</t>
+  </si>
+  <si>
+    <t>ESCAPE</t>
+  </si>
+  <si>
+    <t>ATTACK</t>
+  </si>
+  <si>
+    <t>MULTI_ATTACK</t>
+  </si>
+  <si>
+    <t>DEFEND</t>
+  </si>
+  <si>
+    <t>BUFF</t>
+  </si>
+  <si>
+    <t>DEBUFF</t>
+  </si>
+  <si>
+    <t>HEAL</t>
+  </si>
+  <si>
+    <t>STRATEGY</t>
+  </si>
+  <si>
+    <t>value</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>意图值</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>res://asserts/widgets/Spells/poison_dagger.png</t>
+  </si>
+  <si>
+    <t>res://asserts/widgets/Spells/thorn_vine_spell.png</t>
+  </si>
+  <si>
+    <t>res://asserts/widgets/Spells/healing_spell.png</t>
+  </si>
+  <si>
+    <t>res://asserts/widgets/Debuffs/on_fire_(burning).png</t>
+  </si>
+  <si>
+    <t>res://asserts/widgets/Debuffs/confused.png</t>
+  </si>
+  <si>
+    <t>res://asserts/widgets/Debuffs/disarmed.png</t>
+  </si>
+  <si>
+    <t>res://asserts/widgets/Buffs/lucky_boost.png</t>
+  </si>
+  <si>
+    <t>res://asserts/widgets/Buffs/swiftness.png</t>
+  </si>
+  <si>
+    <t>func</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>意图对应方法</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ATTACK*MULTI_ATTACK*DEFEND</t>
+  </si>
+  <si>
+    <t>intent_pool</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>意图池</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>敌人计划多次攻击。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>敌人打算进行攻击。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>敌人将增加防御力</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1479,7 +1629,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="29">
+  <borders count="30">
     <border>
       <left/>
       <right/>
@@ -1853,6 +2003,17 @@
         <color auto="1"/>
       </left>
       <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -1863,7 +2024,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2019,6 +2180,24 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2399,6 +2578,61 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="C7:F9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="7" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C7" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7">
+        <v>5</v>
+      </c>
+      <c r="E7" t="str">
+        <f t="shared" ref="E7:E9" si="0">C7&amp;"*"&amp;D7</f>
+        <v>strike*5</v>
+      </c>
+    </row>
+    <row r="8" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C8" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8">
+        <v>4</v>
+      </c>
+      <c r="E8" t="str">
+        <f t="shared" si="0"/>
+        <v>defense*4</v>
+      </c>
+      <c r="F8" t="str">
+        <f>E7&amp;"*"&amp;E8</f>
+        <v>strike*5*defense*4</v>
+      </c>
+    </row>
+    <row r="9" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C9" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9" t="str">
+        <f t="shared" si="0"/>
+        <v>trounce*1</v>
+      </c>
+      <c r="F9" t="str">
+        <f>F8&amp;"*"&amp;E9</f>
+        <v>strike*5*defense*4*trounce*1</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E5"/>
@@ -2580,44 +2814,64 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.6640625" customWidth="1"/>
     <col min="2" max="2" width="11.46484375" style="21" customWidth="1"/>
+    <col min="3" max="3" width="28.06640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="35" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="36" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C1" s="52" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="35" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="36" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C2" s="52" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="35" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="36" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C3" s="52" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="37" t="s">
         <v>14</v>
       </c>
       <c r="B4" s="38" t="s">
         <v>15</v>
       </c>
+      <c r="C4" t="s">
+        <v>427</v>
+      </c>
+      <c r="D4" s="44"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D5" s="10"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D6" s="10"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
@@ -2627,6 +2881,251 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D44291C8-9325-4F23-B950-831A2BB11291}">
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="9.06640625" style="55"/>
+    <col min="4" max="4" width="62" customWidth="1"/>
+    <col min="5" max="5" width="54.53125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="42" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="54" t="s">
+        <v>390</v>
+      </c>
+      <c r="D1" s="53" t="s">
+        <v>394</v>
+      </c>
+      <c r="E1" s="53" t="s">
+        <v>270</v>
+      </c>
+      <c r="F1" s="53" t="s">
+        <v>415</v>
+      </c>
+      <c r="G1" s="57" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="42" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="42" t="s">
+        <v>389</v>
+      </c>
+      <c r="C2" s="54" t="s">
+        <v>391</v>
+      </c>
+      <c r="D2" s="53" t="s">
+        <v>393</v>
+      </c>
+      <c r="E2" s="53" t="s">
+        <v>396</v>
+      </c>
+      <c r="F2" s="53" t="s">
+        <v>416</v>
+      </c>
+      <c r="G2" s="57" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="42" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="42" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="54" t="s">
+        <v>392</v>
+      </c>
+      <c r="D3" s="53" t="s">
+        <v>395</v>
+      </c>
+      <c r="E3" s="53" t="s">
+        <v>268</v>
+      </c>
+      <c r="F3" s="53" t="s">
+        <v>392</v>
+      </c>
+      <c r="G3" s="57" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="10" t="s">
+        <v>408</v>
+      </c>
+      <c r="B4" s="44" t="s">
+        <v>397</v>
+      </c>
+      <c r="C4" s="56">
+        <v>1</v>
+      </c>
+      <c r="D4" s="44" t="s">
+        <v>431</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>417</v>
+      </c>
+      <c r="F4" s="10">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="10" t="s">
+        <v>409</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C5" s="56">
+        <v>2</v>
+      </c>
+      <c r="D5" s="44" t="s">
+        <v>430</v>
+      </c>
+      <c r="E5" s="44" t="s">
+        <v>418</v>
+      </c>
+      <c r="F5" s="10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" s="56">
+        <v>3</v>
+      </c>
+      <c r="D6" s="44" t="s">
+        <v>432</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>419</v>
+      </c>
+      <c r="F6" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="10" t="s">
+        <v>411</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>355</v>
+      </c>
+      <c r="C7" s="56">
+        <v>4</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>399</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>420</v>
+      </c>
+      <c r="F7" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="10" t="s">
+        <v>412</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>352</v>
+      </c>
+      <c r="C8" s="56">
+        <v>5</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>400</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="F8" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="10" t="s">
+        <v>413</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>401</v>
+      </c>
+      <c r="C9" s="56">
+        <v>6</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>402</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>423</v>
+      </c>
+      <c r="F9" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="10" t="s">
+        <v>414</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>403</v>
+      </c>
+      <c r="C10" s="56">
+        <v>7</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>404</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>421</v>
+      </c>
+      <c r="F10" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="10" t="s">
+        <v>407</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>405</v>
+      </c>
+      <c r="C11" s="56">
+        <v>8</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>406</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>424</v>
+      </c>
+      <c r="F11" s="10">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:I16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
@@ -2636,7 +3135,7 @@
     <col min="5" max="5" width="24.6640625" customWidth="1"/>
     <col min="6" max="6" width="56.19921875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.3984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11" customWidth="1"/>
     <col min="9" max="9" width="25.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2850,7 +3349,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A5D68F6-6A69-4994-8A54-CD8F7D229E72}">
   <dimension ref="A1:H16"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
@@ -3277,7 +3776,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5EA7D5D-311E-4C1E-90F0-7DA998873B51}">
   <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
@@ -3615,7 +4114,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:AA41"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
@@ -6639,59 +7138,4 @@
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="C7:F9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="7" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C7" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="D7">
-        <v>5</v>
-      </c>
-      <c r="E7" t="str">
-        <f t="shared" ref="E7:E9" si="0">C7&amp;"*"&amp;D7</f>
-        <v>strike*5</v>
-      </c>
-    </row>
-    <row r="8" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C8" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D8">
-        <v>4</v>
-      </c>
-      <c r="E8" t="str">
-        <f t="shared" si="0"/>
-        <v>defense*4</v>
-      </c>
-      <c r="F8" t="str">
-        <f>E7&amp;"*"&amp;E8</f>
-        <v>strike*5*defense*4</v>
-      </c>
-    </row>
-    <row r="9" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C9" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="E9" t="str">
-        <f t="shared" si="0"/>
-        <v>trounce*1</v>
-      </c>
-      <c r="F9" t="str">
-        <f>F8&amp;"*"&amp;E9</f>
-        <v>strike*5*defense*4*trounce*1</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/xlsdir/配置-总表.xlsx
+++ b/xlsdir/配置-总表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="673" firstSheet="3" activeTab="6"/>
+    <workbookView windowWidth="13545" windowHeight="12375" tabRatio="673" firstSheet="3" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="character|角色" sheetId="32" r:id="rId1"/>
@@ -21,12 +21,25 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'monster|魔物'!$A$1:$B$4</definedName>
   </definedNames>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="433">
   <si>
     <t>ID</t>
   </si>
@@ -133,13 +146,43 @@
     <t>intent_pool</t>
   </si>
   <si>
+    <t>enemy_scene</t>
+  </si>
+  <si>
     <t>怪物名</t>
   </si>
   <si>
     <t>意图池</t>
   </si>
   <si>
+    <t>怪物场景</t>
+  </si>
+  <si>
     <t>ATTACK*MULTI_ATTACK*DEFEND</t>
+  </si>
+  <si>
+    <t>flying_eye</t>
+  </si>
+  <si>
+    <t>眼魔</t>
+  </si>
+  <si>
+    <t>goblin</t>
+  </si>
+  <si>
+    <t>地精</t>
+  </si>
+  <si>
+    <t>mushroom</t>
+  </si>
+  <si>
+    <t>蘑菇怪</t>
+  </si>
+  <si>
+    <t>skeleton</t>
+  </si>
+  <si>
+    <t>骷髅怪</t>
   </si>
   <si>
     <t>type</t>
@@ -1424,14 +1467,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1456,14 +1499,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="9.6"/>
       <color rgb="FF374151"/>
       <name val="宋体"/>
@@ -1474,13 +1509,6 @@
       <color rgb="FF374151"/>
       <name val="Segoe UI"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -1827,7 +1855,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="38">
+  <borders count="36">
     <border>
       <left/>
       <right/>
@@ -2177,34 +2205,6 @@
       </right>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -2334,137 +2334,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="28" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="30" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="32" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="33" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="34" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="33" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="35" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="36" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="37" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="32" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="33" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="34" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="35" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2573,70 +2573,61 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1" quotePrefix="1">
@@ -3014,13 +3005,13 @@
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="42" t="s">
+      <c r="C2" s="41" t="s">
         <v>7</v>
       </c>
       <c r="D2" s="5" t="s">
@@ -3095,7 +3086,7 @@
   <sheetData>
     <row r="7" spans="3:5">
       <c r="C7" s="1" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="D7">
         <v>5</v>
@@ -3107,7 +3098,7 @@
     </row>
     <row r="8" spans="3:6">
       <c r="C8" s="1" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="D8">
         <v>4</v>
@@ -3123,7 +3114,7 @@
     </row>
     <row r="9" spans="3:6">
       <c r="C9" s="1" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -3227,7 +3218,7 @@
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultColWidth="8.86666666666667" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="8.33333333333333" style="57" customWidth="1"/>
+    <col min="1" max="1" width="8.33333333333333" style="54" customWidth="1"/>
     <col min="2" max="2" width="11.8666666666667" customWidth="1"/>
     <col min="3" max="3" width="31.4666666666667" customWidth="1"/>
   </cols>
@@ -3245,20 +3236,20 @@
       <c r="D1" s="5"/>
       <c r="E1" s="5"/>
     </row>
-    <row r="2" s="56" customFormat="1" spans="1:5">
-      <c r="A2" s="42" t="s">
+    <row r="2" s="53" customFormat="1" spans="1:5">
+      <c r="A2" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="41" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="42" t="s">
+      <c r="C2" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="D2" s="42" t="s">
+      <c r="D2" s="41" t="s">
         <v>29</v>
       </c>
-      <c r="E2" s="42" t="s">
+      <c r="E2" s="41" t="s">
         <v>30</v>
       </c>
     </row>
@@ -3305,64 +3296,123 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="3"/>
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="7.66666666666667" customWidth="1"/>
+    <col min="1" max="1" width="11.5" customWidth="1"/>
     <col min="2" max="2" width="11.4666666666667" style="21" customWidth="1"/>
     <col min="3" max="3" width="28.0666666666667" customWidth="1"/>
+    <col min="4" max="4" width="14.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="51" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="52" t="s">
+    <row r="1" spans="1:4">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="53" t="s">
+      <c r="C1" s="49" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="51" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="52" t="s">
+      <c r="D1" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="53" t="s">
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="51" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="52" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="53" t="s">
+      <c r="C2" s="49" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2" s="21" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="49" t="s">
         <v>31</v>
       </c>
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="54" t="s">
+      <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="55" t="s">
+      <c r="B4" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="C4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D4" s="40"/>
-    </row>
-    <row r="5" spans="4:4">
-      <c r="D5" s="1"/>
-    </row>
-    <row r="6" spans="4:4">
-      <c r="D6" s="1"/>
+      <c r="C4" s="50" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" s="51" t="str">
+        <f t="shared" ref="D4:D8" si="0">"enemy_"&amp;A4</f>
+        <v>enemy_slime</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="50" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="52" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" s="50"/>
+      <c r="D5" s="51" t="str">
+        <f t="shared" si="0"/>
+        <v>enemy_flying_eye</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="50" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" s="52" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="50"/>
+      <c r="D6" s="51" t="str">
+        <f t="shared" si="0"/>
+        <v>enemy_goblin</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="50" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" s="52" t="s">
+        <v>45</v>
+      </c>
+      <c r="C7" s="50"/>
+      <c r="D7" s="51" t="str">
+        <f t="shared" si="0"/>
+        <v>enemy_mushroom</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="50" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" s="52" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" s="50"/>
+      <c r="D8" s="51" t="str">
+        <f t="shared" si="0"/>
+        <v>enemy_skeleton</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3377,95 +3427,95 @@
   <dimension ref="A1:G11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
-    <col min="3" max="3" width="9.06666666666667" style="46"/>
+    <col min="3" max="3" width="9.06666666666667" style="44"/>
     <col min="4" max="4" width="62" customWidth="1"/>
     <col min="5" max="5" width="54.5333333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="41" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="41" t="s">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="47" t="s">
-        <v>38</v>
-      </c>
-      <c r="D1" s="48" t="s">
-        <v>39</v>
-      </c>
-      <c r="E1" s="48" t="s">
-        <v>40</v>
-      </c>
-      <c r="F1" s="48" t="s">
-        <v>41</v>
-      </c>
-      <c r="G1" s="49" t="s">
-        <v>42</v>
+      <c r="C1" s="45" t="s">
+        <v>48</v>
+      </c>
+      <c r="D1" s="46" t="s">
+        <v>49</v>
+      </c>
+      <c r="E1" s="46" t="s">
+        <v>50</v>
+      </c>
+      <c r="F1" s="46" t="s">
+        <v>51</v>
+      </c>
+      <c r="G1" s="47" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="41" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="41" t="s">
-        <v>43</v>
-      </c>
-      <c r="C2" s="47" t="s">
-        <v>44</v>
-      </c>
-      <c r="D2" s="48" t="s">
-        <v>45</v>
-      </c>
-      <c r="E2" s="48" t="s">
-        <v>46</v>
-      </c>
-      <c r="F2" s="48" t="s">
-        <v>47</v>
-      </c>
-      <c r="G2" s="49" t="s">
-        <v>48</v>
+      <c r="A2" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2" s="45" t="s">
+        <v>54</v>
+      </c>
+      <c r="D2" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="E2" s="46" t="s">
+        <v>56</v>
+      </c>
+      <c r="F2" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="G2" s="47" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="41" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="41" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="47" t="s">
+      <c r="A3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="45" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="48" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="48" t="s">
-        <v>49</v>
-      </c>
-      <c r="F3" s="48" t="s">
+      <c r="D3" s="46" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="46" t="s">
+        <v>59</v>
+      </c>
+      <c r="F3" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="49" t="s">
+      <c r="G3" s="47" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="1" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="B4" s="40" t="s">
-        <v>51</v>
-      </c>
-      <c r="C4" s="50">
+        <v>61</v>
+      </c>
+      <c r="C4" s="48">
         <v>1</v>
       </c>
       <c r="D4" s="40" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="F4" s="1">
         <v>8</v>
@@ -3473,19 +3523,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="1" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C5" s="50">
+        <v>65</v>
+      </c>
+      <c r="C5" s="48">
         <v>2</v>
       </c>
       <c r="D5" s="40" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="E5" s="40" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="F5" s="1">
         <v>3</v>
@@ -3493,19 +3543,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="1" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C6" s="50">
+        <v>69</v>
+      </c>
+      <c r="C6" s="48">
         <v>3</v>
       </c>
       <c r="D6" s="40" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="F6" s="1">
         <v>0</v>
@@ -3513,19 +3563,19 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="1" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C7" s="50">
+        <v>73</v>
+      </c>
+      <c r="C7" s="48">
         <v>4</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="F7" s="1">
         <v>0</v>
@@ -3533,19 +3583,19 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="1" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C8" s="50">
+        <v>77</v>
+      </c>
+      <c r="C8" s="48">
         <v>5</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="F8" s="1">
         <v>0</v>
@@ -3553,19 +3603,19 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="1" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C9" s="50">
+        <v>81</v>
+      </c>
+      <c r="C9" s="48">
         <v>6</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="F9" s="1">
         <v>0</v>
@@ -3573,19 +3623,19 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="1" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C10" s="50">
+        <v>85</v>
+      </c>
+      <c r="C10" s="48">
         <v>7</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="F10" s="1">
         <v>0</v>
@@ -3593,19 +3643,19 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="1" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C11" s="50">
+        <v>89</v>
+      </c>
+      <c r="C11" s="48">
         <v>8</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="F11" s="1">
         <v>0</v>
@@ -3637,57 +3687,57 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="E1" s="41" t="s">
-        <v>85</v>
-      </c>
-      <c r="F1" s="41" t="s">
-        <v>40</v>
-      </c>
-      <c r="G1" s="41" t="s">
-        <v>86</v>
-      </c>
-      <c r="H1" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="I1" s="41" t="s">
-        <v>88</v>
+        <v>94</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="2" ht="54" spans="1:9">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="42" t="s">
-        <v>89</v>
-      </c>
-      <c r="C2" s="42" t="s">
-        <v>90</v>
-      </c>
-      <c r="D2" s="42" t="s">
-        <v>91</v>
+      <c r="B2" s="41" t="s">
+        <v>99</v>
+      </c>
+      <c r="C2" s="41" t="s">
+        <v>100</v>
+      </c>
+      <c r="D2" s="41" t="s">
+        <v>101</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="F2" s="44" t="s">
-        <v>93</v>
-      </c>
-      <c r="G2" s="43" t="s">
-        <v>94</v>
-      </c>
-      <c r="H2" s="44" t="s">
-        <v>95</v>
-      </c>
-      <c r="I2" s="45" t="s">
-        <v>96</v>
+        <v>102</v>
+      </c>
+      <c r="F2" s="41" t="s">
+        <v>103</v>
+      </c>
+      <c r="G2" s="42" t="s">
+        <v>104</v>
+      </c>
+      <c r="H2" s="41" t="s">
+        <v>105</v>
+      </c>
+      <c r="I2" s="43" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -3706,25 +3756,25 @@
       <c r="E3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="41" t="s">
-        <v>49</v>
-      </c>
-      <c r="G3" s="41" t="s">
+      <c r="F3" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="G3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="H3" s="41" t="s">
-        <v>10</v>
-      </c>
-      <c r="I3" s="41" t="s">
+      <c r="H3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="I3" s="5" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="C4" s="1">
         <v>1</v>
@@ -3733,27 +3783,27 @@
         <v>1</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="F4" s="40" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="G4" s="1">
         <v>2</v>
       </c>
       <c r="H4" s="40" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="C5" s="1">
         <v>2</v>
@@ -3762,27 +3812,27 @@
         <v>1</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="G5" s="1">
         <v>1</v>
       </c>
       <c r="H5" s="40" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="I5" s="40" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="C6" s="1">
         <v>1</v>
@@ -3791,19 +3841,19 @@
         <v>2</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="F6" s="40" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="G6" s="1">
         <v>2</v>
       </c>
       <c r="H6" s="40" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="I6" s="40" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -3830,52 +3880,52 @@
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="41" t="s">
-        <v>112</v>
-      </c>
-      <c r="C1" s="41" t="s">
-        <v>113</v>
-      </c>
-      <c r="D1" s="41" t="s">
-        <v>86</v>
-      </c>
-      <c r="E1" s="41" t="s">
-        <v>114</v>
-      </c>
-      <c r="F1" s="41" t="s">
-        <v>115</v>
-      </c>
-      <c r="G1" s="41" t="s">
-        <v>116</v>
-      </c>
-      <c r="H1" s="41" t="s">
+      <c r="B1" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="H1" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" ht="81" spans="1:8">
-      <c r="A2" s="42" t="s">
+    <row r="2" ht="108" spans="1:8">
+      <c r="A2" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="41" t="s">
-        <v>112</v>
-      </c>
-      <c r="C2" s="41" t="s">
-        <v>117</v>
-      </c>
-      <c r="D2" s="43" t="s">
-        <v>118</v>
-      </c>
-      <c r="E2" s="44" t="s">
-        <v>119</v>
-      </c>
-      <c r="F2" s="44" t="s">
-        <v>120</v>
-      </c>
-      <c r="G2" s="44" t="s">
-        <v>121</v>
-      </c>
-      <c r="H2" s="41" t="s">
+      <c r="B2" s="5" t="s">
         <v>122</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="D2" s="42" t="s">
+        <v>128</v>
+      </c>
+      <c r="E2" s="41" t="s">
+        <v>129</v>
+      </c>
+      <c r="F2" s="41" t="s">
+        <v>130</v>
+      </c>
+      <c r="G2" s="41" t="s">
+        <v>131</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -3888,16 +3938,16 @@
       <c r="C3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="41" t="s">
+      <c r="D3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="41" t="s">
+      <c r="E3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="41" t="s">
+      <c r="F3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="41" t="s">
+      <c r="G3" s="5" t="s">
         <v>31</v>
       </c>
       <c r="H3" s="5" t="s">
@@ -3906,11 +3956,11 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="D4" s="1">
         <v>0</v>
@@ -3925,16 +3975,16 @@
         <v>6</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="40" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="40" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="D5" s="1">
         <v>1</v>
@@ -3949,16 +3999,16 @@
         <v>5</v>
       </c>
       <c r="H5" s="40" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="40" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="B6" s="1"/>
       <c r="C6" s="1" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="D6" s="1">
         <v>0</v>
@@ -3973,16 +4023,16 @@
         <v>8</v>
       </c>
       <c r="H6" s="40" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="40" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="B7" s="1"/>
       <c r="C7" s="1" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="D7" s="1">
         <v>0</v>
@@ -3994,21 +4044,21 @@
         <v>3</v>
       </c>
       <c r="G7" s="40" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="H7" s="40" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="1" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="D8" s="1">
         <v>0</v>
@@ -4023,18 +4073,18 @@
         <v>1</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -4049,18 +4099,18 @@
         <v>2</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="D10" s="1">
         <v>0</v>
@@ -4075,18 +4125,18 @@
         <v>3</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="D11" s="1">
         <v>0</v>
@@ -4101,18 +4151,18 @@
         <v>4</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="D12" s="1">
         <v>0</v>
@@ -4127,18 +4177,18 @@
         <v>5</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="D13" s="1">
         <v>0</v>
@@ -4153,18 +4203,18 @@
         <v>6</v>
       </c>
       <c r="H13" s="40" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="D14" s="1">
         <v>0</v>
@@ -4179,18 +4229,18 @@
         <v>7</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -4205,18 +4255,18 @@
         <v>8</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="D16" s="1">
         <v>0</v>
@@ -4231,7 +4281,7 @@
         <v>9</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>
@@ -4256,22 +4306,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="35" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="C1" s="35" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="D1" s="35" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="E1" s="35" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="F1" s="35" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="G1" s="35" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -4279,22 +4329,22 @@
         <v>5</v>
       </c>
       <c r="B2" s="37" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="C2" s="37" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="D2" s="37" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="E2" s="37" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="F2" s="37" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="G2" s="38" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -4305,16 +4355,16 @@
         <v>10</v>
       </c>
       <c r="C3" s="37" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="D3" s="37" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="E3" s="37" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="F3" s="37" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="G3" s="37" t="s">
         <v>10</v>
@@ -4322,10 +4372,10 @@
     </row>
     <row r="4" ht="14.25" spans="1:7">
       <c r="A4" s="39" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="B4" s="40" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="C4" s="39">
         <v>100</v>
@@ -4340,15 +4390,15 @@
         <v>1</v>
       </c>
       <c r="G4" s="39" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
     </row>
     <row r="5" ht="14.25" spans="1:7">
       <c r="A5" s="39" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="B5" s="40" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="C5" s="39">
         <v>100</v>
@@ -4363,15 +4413,15 @@
         <v>1</v>
       </c>
       <c r="G5" s="39" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
     </row>
     <row r="6" ht="14.25" spans="1:7">
       <c r="A6" s="39" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="B6" s="40" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="C6" s="39">
         <v>3</v>
@@ -4386,15 +4436,15 @@
         <v>1</v>
       </c>
       <c r="G6" s="39" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
     </row>
     <row r="7" ht="14.25" spans="1:7">
       <c r="A7" s="39" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="B7" s="40" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="C7" s="39">
         <v>3</v>
@@ -4409,12 +4459,12 @@
         <v>1</v>
       </c>
       <c r="G7" s="39" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
     </row>
     <row r="8" ht="14.25" spans="1:7">
       <c r="A8" s="39" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="B8" s="40" t="s">
         <v>8</v>
@@ -4432,15 +4482,15 @@
         <v>1</v>
       </c>
       <c r="G8" s="39" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
     </row>
     <row r="9" ht="14.25" spans="1:7">
       <c r="A9" s="39" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="B9" s="40" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="C9" s="39">
         <v>0</v>
@@ -4455,15 +4505,15 @@
         <v>1</v>
       </c>
       <c r="G9" s="39" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
     </row>
     <row r="10" ht="14.25" spans="1:7">
       <c r="A10" s="39" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="B10" s="40" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="C10" s="39">
         <v>0</v>
@@ -4478,15 +4528,15 @@
         <v>1</v>
       </c>
       <c r="G10" s="39" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
     </row>
     <row r="11" ht="14.25" spans="1:7">
       <c r="A11" s="39" t="s">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="B11" s="40" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="C11" s="39">
         <v>0</v>
@@ -4501,15 +4551,15 @@
         <v>1</v>
       </c>
       <c r="G11" s="39" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
     </row>
     <row r="12" ht="14.25" spans="1:7">
       <c r="A12" s="39" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="B12" s="40" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="C12" s="39">
         <v>0</v>
@@ -4524,15 +4574,15 @@
         <v>1</v>
       </c>
       <c r="G12" s="39" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
     </row>
     <row r="13" ht="14.25" spans="1:7">
       <c r="A13" s="39" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="B13" s="40" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="C13" s="39">
         <v>0</v>
@@ -4547,15 +4597,15 @@
         <v>1</v>
       </c>
       <c r="G13" s="39" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
     </row>
     <row r="14" ht="14.25" spans="1:7">
       <c r="A14" s="39" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="B14" s="40" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="C14" s="39">
         <v>0</v>
@@ -4570,7 +4620,7 @@
         <v>1</v>
       </c>
       <c r="G14" s="39" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
     </row>
   </sheetData>
@@ -4593,67 +4643,67 @@
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="R1" s="13" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="S1" s="3" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="T1" s="3" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="U1" s="3" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="V1" s="3" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="W1" s="14" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="X1" s="15"/>
       <c r="Y1" s="15"/>
@@ -4665,82 +4715,82 @@
         <v>5</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="O2" s="5" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="P2" s="5" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="Q2" s="5" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="R2" s="16" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="S2" s="5" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="T2" s="5" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="U2" s="5" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="V2" s="5" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="W2" s="17" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="X2" s="18" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="Y2" s="32" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="Z2" s="32" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="AA2" s="33" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
     </row>
     <row r="3" ht="14.25" spans="1:27">
@@ -4831,7 +4881,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="C4" s="9">
         <v>10</v>
@@ -4886,17 +4936,17 @@
       <c r="U4" s="9"/>
       <c r="V4" s="9"/>
       <c r="W4" s="23"/>
-      <c r="X4" s="58" t="s">
-        <v>253</v>
+      <c r="X4" s="55" t="s">
+        <v>263</v>
       </c>
       <c r="Y4" s="9" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="Z4" s="9" t="s">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="AA4" s="23" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
     </row>
     <row r="5" spans="1:27">
@@ -4904,7 +4954,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="C5" s="1">
         <v>10</v>
@@ -4960,16 +5010,16 @@
       <c r="V5" s="1"/>
       <c r="W5" s="26"/>
       <c r="X5" s="27" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="Y5" s="1" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="Z5" s="1" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="AA5" s="26" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
     </row>
     <row r="6" spans="1:27">
@@ -4977,7 +5027,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="C6" s="1">
         <v>10</v>
@@ -5033,16 +5083,16 @@
       <c r="V6" s="1"/>
       <c r="W6" s="26"/>
       <c r="X6" s="27" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="Y6" s="1" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="Z6" s="1" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="AA6" s="26" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
     </row>
     <row r="7" spans="1:27">
@@ -5050,7 +5100,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="C7" s="1">
         <v>10</v>
@@ -5106,16 +5156,16 @@
       <c r="V7" s="1"/>
       <c r="W7" s="26"/>
       <c r="X7" s="27" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="Y7" s="1" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="Z7" s="1" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="AA7" s="26" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
     </row>
     <row r="8" spans="1:27">
@@ -5123,7 +5173,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="C8" s="1">
         <v>10</v>
@@ -5179,16 +5229,16 @@
       <c r="V8" s="1"/>
       <c r="W8" s="26"/>
       <c r="X8" s="27" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="Y8" s="1" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="Z8" s="1" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="AA8" s="26" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
     </row>
     <row r="9" spans="1:27">
@@ -5196,7 +5246,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="C9" s="1">
         <v>10</v>
@@ -5252,16 +5302,16 @@
       <c r="V9" s="1"/>
       <c r="W9" s="26"/>
       <c r="X9" s="27" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="Y9" s="1" t="s">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="Z9" s="1" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="AA9" s="26" t="s">
-        <v>276</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10" spans="1:27">
@@ -5269,7 +5319,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="C10" s="1">
         <v>10</v>
@@ -5325,16 +5375,16 @@
       <c r="V10" s="1"/>
       <c r="W10" s="26"/>
       <c r="X10" s="27" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="Y10" s="1" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="Z10" s="1" t="s">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="AA10" s="26" t="s">
-        <v>281</v>
+        <v>291</v>
       </c>
     </row>
     <row r="11" spans="1:27">
@@ -5342,7 +5392,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="C11" s="1">
         <v>10</v>
@@ -5398,16 +5448,16 @@
       <c r="V11" s="1"/>
       <c r="W11" s="26"/>
       <c r="X11" s="27" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="Y11" s="1" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="Z11" s="1" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="AA11" s="26" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
     </row>
     <row r="12" spans="1:27">
@@ -5415,7 +5465,7 @@
         <v>9</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="C12" s="1">
         <v>10</v>
@@ -5471,16 +5521,16 @@
       <c r="V12" s="1"/>
       <c r="W12" s="26"/>
       <c r="X12" s="27" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="Y12" s="1" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="Z12" s="1" t="s">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="AA12" s="26" t="s">
-        <v>290</v>
+        <v>300</v>
       </c>
     </row>
     <row r="13" spans="1:27">
@@ -5488,7 +5538,7 @@
         <v>10</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>291</v>
+        <v>301</v>
       </c>
       <c r="C13" s="1">
         <v>10</v>
@@ -5544,16 +5594,16 @@
       <c r="V13" s="1"/>
       <c r="W13" s="26"/>
       <c r="X13" s="27" t="s">
-        <v>292</v>
+        <v>302</v>
       </c>
       <c r="Y13" s="1" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="Z13" s="1" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="AA13" s="26" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
     </row>
     <row r="14" spans="1:27">
@@ -5561,7 +5611,7 @@
         <v>11</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="C14" s="1">
         <v>10</v>
@@ -5617,16 +5667,16 @@
       <c r="V14" s="1"/>
       <c r="W14" s="26"/>
       <c r="X14" s="27" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="Y14" s="1" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="Z14" s="1" t="s">
-        <v>298</v>
+        <v>308</v>
       </c>
       <c r="AA14" s="26" t="s">
-        <v>299</v>
+        <v>309</v>
       </c>
     </row>
     <row r="15" spans="1:27">
@@ -5634,7 +5684,7 @@
         <v>12</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="C15" s="1">
         <v>10</v>
@@ -5690,16 +5740,16 @@
       <c r="V15" s="1"/>
       <c r="W15" s="26"/>
       <c r="X15" s="27" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="Y15" s="1" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="Z15" s="1" t="s">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="AA15" s="26" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
     </row>
     <row r="16" spans="1:27">
@@ -5707,7 +5757,7 @@
         <v>13</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="C16" s="1">
         <v>10</v>
@@ -5763,16 +5813,16 @@
       <c r="V16" s="1"/>
       <c r="W16" s="26"/>
       <c r="X16" s="27" t="s">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="Y16" s="1" t="s">
-        <v>306</v>
+        <v>316</v>
       </c>
       <c r="Z16" s="1" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="AA16" s="26" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
     </row>
     <row r="17" spans="1:27">
@@ -5780,7 +5830,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="C17" s="1">
         <v>10</v>
@@ -5836,16 +5886,16 @@
       <c r="V17" s="1"/>
       <c r="W17" s="26"/>
       <c r="X17" s="27" t="s">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c r="Y17" s="1" t="s">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="Z17" s="1" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="AA17" s="26" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
     </row>
     <row r="18" spans="1:27">
@@ -5853,7 +5903,7 @@
         <v>15</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="C18" s="1">
         <v>10</v>
@@ -5909,16 +5959,16 @@
       <c r="V18" s="1"/>
       <c r="W18" s="26"/>
       <c r="X18" s="27" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="Y18" s="1" t="s">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="Z18" s="1" t="s">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="AA18" s="26" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
     </row>
     <row r="19" spans="1:27">
@@ -5926,7 +5976,7 @@
         <v>16</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="C19" s="1">
         <v>10</v>
@@ -5982,16 +6032,16 @@
       <c r="V19" s="1"/>
       <c r="W19" s="26"/>
       <c r="X19" s="27" t="s">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="Y19" s="1" t="s">
-        <v>319</v>
+        <v>329</v>
       </c>
       <c r="Z19" s="1" t="s">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="AA19" s="26" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
     </row>
     <row r="20" spans="1:27">
@@ -5999,7 +6049,7 @@
         <v>17</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>321</v>
+        <v>331</v>
       </c>
       <c r="C20" s="1">
         <v>10</v>
@@ -6055,16 +6105,16 @@
       <c r="V20" s="1"/>
       <c r="W20" s="26"/>
       <c r="X20" s="27" t="s">
-        <v>322</v>
+        <v>332</v>
       </c>
       <c r="Y20" s="1" t="s">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="Z20" s="1" t="s">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="AA20" s="26" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
     </row>
     <row r="21" spans="1:27">
@@ -6072,7 +6122,7 @@
         <v>18</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="C21" s="1">
         <v>10</v>
@@ -6128,16 +6178,16 @@
       <c r="V21" s="1"/>
       <c r="W21" s="26"/>
       <c r="X21" s="27" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="Y21" s="1" t="s">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="Z21" s="1" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="AA21" s="26" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
     </row>
     <row r="22" spans="1:27">
@@ -6145,7 +6195,7 @@
         <v>19</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>329</v>
+        <v>339</v>
       </c>
       <c r="C22" s="1">
         <v>10</v>
@@ -6201,16 +6251,16 @@
       <c r="V22" s="1"/>
       <c r="W22" s="26"/>
       <c r="X22" s="27" t="s">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="Y22" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="Z22" s="1" t="s">
-        <v>332</v>
+        <v>342</v>
       </c>
       <c r="AA22" s="26" t="s">
-        <v>333</v>
+        <v>343</v>
       </c>
     </row>
     <row r="23" spans="1:27">
@@ -6218,7 +6268,7 @@
         <v>20</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="C23" s="1">
         <v>10</v>
@@ -6274,16 +6324,16 @@
       <c r="V23" s="1"/>
       <c r="W23" s="26"/>
       <c r="X23" s="27" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="Y23" s="1" t="s">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="Z23" s="1" t="s">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="AA23" s="26" t="s">
-        <v>338</v>
+        <v>348</v>
       </c>
     </row>
     <row r="24" spans="1:27">
@@ -6291,7 +6341,7 @@
         <v>21</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>339</v>
+        <v>349</v>
       </c>
       <c r="C24" s="1">
         <v>10</v>
@@ -6347,16 +6397,16 @@
       <c r="V24" s="1"/>
       <c r="W24" s="26"/>
       <c r="X24" s="27" t="s">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="Y24" s="1" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="Z24" s="1" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="AA24" s="26" t="s">
-        <v>343</v>
+        <v>353</v>
       </c>
     </row>
     <row r="25" spans="1:27">
@@ -6364,7 +6414,7 @@
         <v>22</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>344</v>
+        <v>354</v>
       </c>
       <c r="C25" s="1">
         <v>10</v>
@@ -6420,16 +6470,16 @@
       <c r="V25" s="1"/>
       <c r="W25" s="26"/>
       <c r="X25" s="27" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="Y25" s="1" t="s">
-        <v>346</v>
+        <v>356</v>
       </c>
       <c r="Z25" s="1" t="s">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="AA25" s="26" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
     </row>
     <row r="26" spans="1:27">
@@ -6437,7 +6487,7 @@
         <v>23</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>348</v>
+        <v>358</v>
       </c>
       <c r="C26" s="1">
         <v>10</v>
@@ -6493,16 +6543,16 @@
       <c r="V26" s="1"/>
       <c r="W26" s="26"/>
       <c r="X26" s="27" t="s">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="Y26" s="1" t="s">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="Z26" s="1" t="s">
-        <v>351</v>
+        <v>361</v>
       </c>
       <c r="AA26" s="26" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
     </row>
     <row r="27" spans="1:27">
@@ -6510,7 +6560,7 @@
         <v>24</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="C27" s="1">
         <v>10</v>
@@ -6566,16 +6616,16 @@
       <c r="V27" s="1"/>
       <c r="W27" s="26"/>
       <c r="X27" s="27" t="s">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="Y27" s="1" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="Z27" s="1" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="AA27" s="26" t="s">
-        <v>357</v>
+        <v>367</v>
       </c>
     </row>
     <row r="28" spans="1:27">
@@ -6583,7 +6633,7 @@
         <v>25</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="C28" s="1">
         <v>10</v>
@@ -6639,16 +6689,16 @@
       <c r="V28" s="1"/>
       <c r="W28" s="26"/>
       <c r="X28" s="27" t="s">
-        <v>359</v>
+        <v>369</v>
       </c>
       <c r="Y28" s="1" t="s">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="Z28" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="AA28" s="26" t="s">
-        <v>362</v>
+        <v>372</v>
       </c>
     </row>
     <row r="29" spans="1:27">
@@ -6656,7 +6706,7 @@
         <v>26</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>363</v>
+        <v>373</v>
       </c>
       <c r="C29" s="1">
         <v>10</v>
@@ -6712,16 +6762,16 @@
       <c r="V29" s="1"/>
       <c r="W29" s="26"/>
       <c r="X29" s="27" t="s">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="Y29" s="1" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="Z29" s="1" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="AA29" s="26" t="s">
-        <v>367</v>
+        <v>377</v>
       </c>
     </row>
     <row r="30" spans="1:27">
@@ -6729,7 +6779,7 @@
         <v>27</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>368</v>
+        <v>378</v>
       </c>
       <c r="C30" s="1">
         <v>10</v>
@@ -6785,16 +6835,16 @@
       <c r="V30" s="1"/>
       <c r="W30" s="26"/>
       <c r="X30" s="27" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="Y30" s="1" t="s">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="Z30" s="1" t="s">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="AA30" s="26" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
     </row>
     <row r="31" spans="1:27">
@@ -6802,7 +6852,7 @@
         <v>28</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="C31" s="1">
         <v>10</v>
@@ -6858,16 +6908,16 @@
       <c r="V31" s="1"/>
       <c r="W31" s="26"/>
       <c r="X31" s="27" t="s">
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="Y31" s="1" t="s">
-        <v>374</v>
+        <v>384</v>
       </c>
       <c r="Z31" s="1" t="s">
-        <v>375</v>
+        <v>385</v>
       </c>
       <c r="AA31" s="26" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
     </row>
     <row r="32" spans="1:27">
@@ -6875,7 +6925,7 @@
         <v>29</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="C32" s="1">
         <v>10</v>
@@ -6931,16 +6981,16 @@
       <c r="V32" s="1"/>
       <c r="W32" s="26"/>
       <c r="X32" s="27" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="Y32" s="1" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="Z32" s="1" t="s">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="AA32" s="26" t="s">
-        <v>380</v>
+        <v>390</v>
       </c>
     </row>
     <row r="33" spans="1:27">
@@ -6948,7 +6998,7 @@
         <v>30</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="C33" s="1">
         <v>10</v>
@@ -7004,16 +7054,16 @@
       <c r="V33" s="1"/>
       <c r="W33" s="26"/>
       <c r="X33" s="27" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="Y33" s="1" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="Z33" s="1" t="s">
-        <v>384</v>
+        <v>394</v>
       </c>
       <c r="AA33" s="26" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
     </row>
     <row r="34" spans="1:27">
@@ -7021,7 +7071,7 @@
         <v>31</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>386</v>
+        <v>396</v>
       </c>
       <c r="C34" s="1">
         <v>10</v>
@@ -7077,16 +7127,16 @@
       <c r="V34" s="1"/>
       <c r="W34" s="26"/>
       <c r="X34" s="27" t="s">
-        <v>387</v>
+        <v>397</v>
       </c>
       <c r="Y34" s="1" t="s">
-        <v>388</v>
+        <v>398</v>
       </c>
       <c r="Z34" s="1" t="s">
-        <v>389</v>
+        <v>399</v>
       </c>
       <c r="AA34" s="26" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
     </row>
     <row r="35" spans="1:27">
@@ -7094,7 +7144,7 @@
         <v>32</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>390</v>
+        <v>400</v>
       </c>
       <c r="C35" s="1">
         <v>10</v>
@@ -7150,16 +7200,16 @@
       <c r="V35" s="1"/>
       <c r="W35" s="26"/>
       <c r="X35" s="27" t="s">
-        <v>391</v>
+        <v>401</v>
       </c>
       <c r="Y35" s="1" t="s">
-        <v>392</v>
+        <v>402</v>
       </c>
       <c r="Z35" s="1" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="AA35" s="26" t="s">
-        <v>394</v>
+        <v>404</v>
       </c>
     </row>
     <row r="36" spans="1:27">
@@ -7167,7 +7217,7 @@
         <v>33</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c r="C36" s="1">
         <v>10</v>
@@ -7223,16 +7273,16 @@
       <c r="V36" s="1"/>
       <c r="W36" s="26"/>
       <c r="X36" s="27" t="s">
-        <v>396</v>
+        <v>406</v>
       </c>
       <c r="Y36" s="1" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="Z36" s="1" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="AA36" s="26" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
     </row>
     <row r="37" spans="1:27">
@@ -7240,7 +7290,7 @@
         <v>34</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="C37" s="1">
         <v>10</v>
@@ -7296,16 +7346,16 @@
       <c r="V37" s="1"/>
       <c r="W37" s="26"/>
       <c r="X37" s="27" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="Y37" s="1" t="s">
-        <v>402</v>
+        <v>412</v>
       </c>
       <c r="Z37" s="1" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="AA37" s="26" t="s">
-        <v>404</v>
+        <v>414</v>
       </c>
     </row>
     <row r="38" spans="1:27">
@@ -7313,7 +7363,7 @@
         <v>35</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="C38" s="1">
         <v>10</v>
@@ -7369,16 +7419,16 @@
       <c r="V38" s="1"/>
       <c r="W38" s="26"/>
       <c r="X38" s="27" t="s">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="Y38" s="1" t="s">
-        <v>407</v>
+        <v>417</v>
       </c>
       <c r="Z38" s="1" t="s">
-        <v>408</v>
+        <v>418</v>
       </c>
       <c r="AA38" s="26" t="s">
-        <v>409</v>
+        <v>419</v>
       </c>
     </row>
     <row r="39" spans="1:27">
@@ -7386,7 +7436,7 @@
         <v>36</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>410</v>
+        <v>420</v>
       </c>
       <c r="C39" s="1">
         <v>10</v>
@@ -7442,16 +7492,16 @@
       <c r="V39" s="1"/>
       <c r="W39" s="26"/>
       <c r="X39" s="27" t="s">
-        <v>411</v>
+        <v>421</v>
       </c>
       <c r="Y39" s="1" t="s">
-        <v>412</v>
+        <v>422</v>
       </c>
       <c r="Z39" s="1" t="s">
-        <v>413</v>
+        <v>423</v>
       </c>
       <c r="AA39" s="26" t="s">
-        <v>414</v>
+        <v>424</v>
       </c>
     </row>
     <row r="40" spans="1:27">
@@ -7459,7 +7509,7 @@
         <v>37</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="C40" s="1">
         <v>10</v>
@@ -7515,16 +7565,16 @@
       <c r="V40" s="1"/>
       <c r="W40" s="26"/>
       <c r="X40" s="27" t="s">
-        <v>416</v>
+        <v>426</v>
       </c>
       <c r="Y40" s="1" t="s">
-        <v>417</v>
+        <v>427</v>
       </c>
       <c r="Z40" s="1" t="s">
-        <v>418</v>
+        <v>428</v>
       </c>
       <c r="AA40" s="26" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
     </row>
     <row r="41" ht="14.25" spans="1:27">
@@ -7532,7 +7582,7 @@
         <v>38</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>419</v>
+        <v>429</v>
       </c>
       <c r="C41" s="12">
         <v>10</v>
@@ -7588,16 +7638,16 @@
       <c r="V41" s="12"/>
       <c r="W41" s="29"/>
       <c r="X41" s="30" t="s">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c r="Y41" s="12" t="s">
-        <v>421</v>
+        <v>431</v>
       </c>
       <c r="Z41" s="12" t="s">
-        <v>422</v>
+        <v>432</v>
       </c>
       <c r="AA41" s="29" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
     </row>
   </sheetData>

--- a/xlsdir/配置-总表.xlsx
+++ b/xlsdir/配置-总表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="13545" windowHeight="12375" tabRatio="673" firstSheet="3" activeTab="3"/>
+    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="673" firstSheet="3"/>
   </bookViews>
   <sheets>
     <sheet name="character|角色" sheetId="32" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="433">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="433">
   <si>
     <t>ID</t>
   </si>
@@ -92,6 +92,30 @@
     <t>一个矮小而丑陋的怪物，生活在森林深处。</t>
   </si>
   <si>
+    <t>flying_eye</t>
+  </si>
+  <si>
+    <t>眼魔</t>
+  </si>
+  <si>
+    <t>goblin</t>
+  </si>
+  <si>
+    <t>地精</t>
+  </si>
+  <si>
+    <t>mushroom</t>
+  </si>
+  <si>
+    <t>蘑菇怪</t>
+  </si>
+  <si>
+    <t>skeleton</t>
+  </si>
+  <si>
+    <t>骷髅怪</t>
+  </si>
+  <si>
     <t>mark_04</t>
   </si>
   <si>
@@ -161,30 +185,6 @@
     <t>ATTACK*MULTI_ATTACK*DEFEND</t>
   </si>
   <si>
-    <t>flying_eye</t>
-  </si>
-  <si>
-    <t>眼魔</t>
-  </si>
-  <si>
-    <t>goblin</t>
-  </si>
-  <si>
-    <t>地精</t>
-  </si>
-  <si>
-    <t>mushroom</t>
-  </si>
-  <si>
-    <t>蘑菇怪</t>
-  </si>
-  <si>
-    <t>skeleton</t>
-  </si>
-  <si>
-    <t>骷髅怪</t>
-  </si>
-  <si>
     <t>type</t>
   </si>
   <si>
@@ -230,7 +230,7 @@
     <t>敌人打算进行攻击。</t>
   </si>
   <si>
-    <t>res://asserts/widgets/Spells/poison_dagger.png</t>
+    <t>res://asserts/textures/widgets/Spells/poison_dagger.png</t>
   </si>
   <si>
     <t>MULTI_ATTACK</t>
@@ -242,7 +242,7 @@
     <t>敌人计划多次攻击。</t>
   </si>
   <si>
-    <t>res://asserts/widgets/Spells/thorn_vine_spell.png</t>
+    <t>res://asserts/textures/widgets/Spells/thorn_vine_spell.png</t>
   </si>
   <si>
     <t>DEFEND</t>
@@ -254,7 +254,7 @@
     <t>敌人将增加防御力</t>
   </si>
   <si>
-    <t>res://asserts/widgets/Spells/healing_spell.png</t>
+    <t>res://asserts/textures/widgets/Spells/healing_spell.png</t>
   </si>
   <si>
     <t>BUFF</t>
@@ -266,7 +266,7 @@
     <t>敌人将提升某项能力，如攻击力、防御力或特殊能力。</t>
   </si>
   <si>
-    <t>res://asserts/widgets/Debuffs/on_fire_(burning).png</t>
+    <t>res://asserts/textures/widgets/Debuffs/on_fire_(burning).png</t>
   </si>
   <si>
     <t>DEBUFF</t>
@@ -278,7 +278,7 @@
     <t>敌人计划施放会削弱玩家能力的效果，如减少玩家的攻击力或防御力。</t>
   </si>
   <si>
-    <t>res://asserts/widgets/Debuffs/disarmed.png</t>
+    <t>res://asserts/textures/widgets/Debuffs/disarmed.png</t>
   </si>
   <si>
     <t>HEAL</t>
@@ -290,7 +290,7 @@
     <t>敌人会恢复一定量的生命值。</t>
   </si>
   <si>
-    <t>res://asserts/widgets/Buffs/lucky_boost.png</t>
+    <t>res://asserts/textures/widgets/Buffs/lucky_boost.png</t>
   </si>
   <si>
     <t>STRATEGY</t>
@@ -302,7 +302,7 @@
     <t>敌人将采取某种特殊行动，如召唤援助、准备强力攻击或其他战术动作。</t>
   </si>
   <si>
-    <t>res://asserts/widgets/Debuffs/confused.png</t>
+    <t>res://asserts/textures/widgets/Debuffs/confused.png</t>
   </si>
   <si>
     <t>ESCAPE</t>
@@ -314,7 +314,7 @@
     <t>在某些战斗中，敌人可能会试图逃跑，尤其是在遭遇战中</t>
   </si>
   <si>
-    <t>res://asserts/widgets/Buffs/swiftness.png</t>
+    <t>res://asserts/textures/widgets/Buffs/swiftness.png</t>
   </si>
   <si>
     <t>card_name</t>
@@ -376,7 +376,7 @@
     <t>造成6点伤害</t>
   </si>
   <si>
-    <t>res://asserts/cards/card_icons/card_strike.png</t>
+    <t>res://asserts/textures/cards/card_icons/card_strike.png</t>
   </si>
   <si>
     <t>attack_01</t>
@@ -388,7 +388,7 @@
     <t>获得5点护甲</t>
   </si>
   <si>
-    <t>res://asserts/cards/card_icons/card_defense.png</t>
+    <t>res://asserts/textures/cards/card_icons/card_defense.png</t>
   </si>
   <si>
     <t>items</t>
@@ -406,7 +406,7 @@
     <t>造成8点伤害，给与2层易伤</t>
   </si>
   <si>
-    <t>res://asserts/cards/card_icons/card_trounce.png</t>
+    <t>res://asserts/textures/cards/card_icons/card_trounce.png</t>
   </si>
   <si>
     <t>trounce_01*trounce_02</t>
@@ -2981,8 +2981,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="4"/>
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="5" max="5" width="37" customWidth="1"/>
   </cols>
@@ -3070,6 +3070,62 @@
       </c>
       <c r="E5" s="1" t="s">
         <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="52" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="1">
+        <v>50</v>
+      </c>
+      <c r="D6" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="50" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="52" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="1">
+        <v>50</v>
+      </c>
+      <c r="D7" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="50" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="52" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="1">
+        <v>50</v>
+      </c>
+      <c r="D8" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="50" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="52" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="1">
+        <v>50</v>
+      </c>
+      <c r="D9" s="1">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -3148,13 +3204,13 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -3162,16 +3218,16 @@
         <v>0</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -3196,14 +3252,14 @@
         <v>1</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="1" t="s">
-        <v>14</v>
+      <c r="E4" s="50" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -3228,10 +3284,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="D1" s="5"/>
       <c r="E1" s="5"/>
@@ -3241,16 +3297,16 @@
         <v>5</v>
       </c>
       <c r="B2" s="41" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="C2" s="41" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D2" s="41" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="E2" s="41" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -3261,7 +3317,7 @@
         <v>10</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>11</v>
@@ -3278,13 +3334,13 @@
         <v>12</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="D4" s="1">
         <v>99</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -3313,10 +3369,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="49" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="D1" s="21" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -3324,13 +3380,13 @@
         <v>0</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C2" s="49" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="D2" s="21" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -3341,7 +3397,7 @@
         <v>10</v>
       </c>
       <c r="C3" s="49" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
@@ -3355,7 +3411,7 @@
         <v>15</v>
       </c>
       <c r="C4" s="50" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="D4" s="51" t="str">
         <f t="shared" ref="D4:D8" si="0">"enemy_"&amp;A4</f>
@@ -3364,10 +3420,10 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="50" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="B5" s="52" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="C5" s="50"/>
       <c r="D5" s="51" t="str">
@@ -3377,10 +3433,10 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="50" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="B6" s="52" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="C6" s="50"/>
       <c r="D6" s="51" t="str">
@@ -3390,10 +3446,10 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="50" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="B7" s="52" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="C7" s="50"/>
       <c r="D7" s="51" t="str">
@@ -3403,10 +3459,10 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="50" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="B8" s="52" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="C8" s="50"/>
       <c r="D8" s="51" t="str">
@@ -3429,7 +3485,7 @@
   <cols>
     <col min="3" max="3" width="9.06666666666667" style="44"/>
     <col min="4" max="4" width="62" customWidth="1"/>
-    <col min="5" max="5" width="54.5333333333333" customWidth="1"/>
+    <col min="5" max="5" width="67.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -3766,7 +3822,7 @@
         <v>10</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -3948,7 +4004,7 @@
         <v>11</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="H3" s="5" t="s">
         <v>10</v>

--- a/xlsdir/配置-总表.xlsx
+++ b/xlsdir/配置-总表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="673" firstSheet="3"/>
+    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="673" firstSheet="3" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="character|角色" sheetId="32" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="433">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="709" uniqueCount="504">
   <si>
     <t>ID</t>
   </si>
@@ -89,7 +89,7 @@
     <t>史莱姆</t>
   </si>
   <si>
-    <t>一个矮小而丑陋的怪物，生活在森林深处。</t>
+    <t>一种黏滑的生物，能够分裂和吸收小型物体。史莱姆的主要攻击方式是覆盖和缠绕。</t>
   </si>
   <si>
     <t>flying_eye</t>
@@ -98,24 +98,36 @@
     <t>眼魔</t>
   </si>
   <si>
+    <t>一种拥有多个眼睛的神秘生物，能够施放不同的魔法效果。以其智慧和远程攻击著称。</t>
+  </si>
+  <si>
     <t>goblin</t>
   </si>
   <si>
     <t>地精</t>
   </si>
   <si>
+    <t>一种小型、狡猾且迅速的生物。擅长使用小刀和陷阱。</t>
+  </si>
+  <si>
     <t>mushroom</t>
   </si>
   <si>
     <t>蘑菇怪</t>
   </si>
   <si>
+    <t>一种生长在森林里的神秘生物，能够释放毒素和治疗药剂。</t>
+  </si>
+  <si>
     <t>skeleton</t>
   </si>
   <si>
     <t>骷髅怪</t>
   </si>
   <si>
+    <t>不死生物，使用古老的武器和盔甲。虽然动作缓慢，但具有较高的防御力。</t>
+  </si>
+  <si>
     <t>mark_04</t>
   </si>
   <si>
@@ -182,12 +194,33 @@
     <t>怪物场景</t>
   </si>
   <si>
-    <t>ATTACK*MULTI_ATTACK*DEFEND</t>
+    <t>split*absorb*entangle</t>
+  </si>
+  <si>
+    <t>destruction_ray*curse_gaze*magic_shield</t>
+  </si>
+  <si>
+    <t>sprint_stab*set_trap*sneak_attack</t>
+  </si>
+  <si>
+    <t>toxin_spray*healing_spore*hallucinogenic_spore</t>
+  </si>
+  <si>
+    <t>heavy_strike*bone_shield*summon_assistance</t>
+  </si>
+  <si>
+    <t>owner</t>
   </si>
   <si>
     <t>type</t>
   </si>
   <si>
+    <t>weight</t>
+  </si>
+  <si>
+    <t>cooldown</t>
+  </si>
+  <si>
     <t>des</t>
   </si>
   <si>
@@ -200,12 +233,21 @@
     <t>func</t>
   </si>
   <si>
+    <t>所属(注释）</t>
+  </si>
+  <si>
     <t>意图名</t>
   </si>
   <si>
     <t>意图类型</t>
   </si>
   <si>
+    <t>权重</t>
+  </si>
+  <si>
+    <t>冷却</t>
+  </si>
+  <si>
     <t>意图描述</t>
   </si>
   <si>
@@ -215,7 +257,10 @@
     <t>意图值</t>
   </si>
   <si>
-    <t>意图对应方法</t>
+    <t>意图方法</t>
+  </si>
+  <si>
+    <t>float</t>
   </si>
   <si>
     <t>texture</t>
@@ -315,6 +360,141 @@
   </si>
   <si>
     <t>res://asserts/textures/widgets/Buffs/swiftness.png</t>
+  </si>
+  <si>
+    <t>split</t>
+  </si>
+  <si>
+    <t>分裂</t>
+  </si>
+  <si>
+    <t>史莱姆分裂成两个较小的实体，增加战斗中的敌人数量。</t>
+  </si>
+  <si>
+    <t>absorb</t>
+  </si>
+  <si>
+    <t>吸收</t>
+  </si>
+  <si>
+    <t>回复一定量的生命值，吸收的量取决于其当前生命值。</t>
+  </si>
+  <si>
+    <t>entangle</t>
+  </si>
+  <si>
+    <t>缠绕</t>
+  </si>
+  <si>
+    <t>降低玩家下一回合的行动点数。</t>
+  </si>
+  <si>
+    <t>destruction_ray</t>
+  </si>
+  <si>
+    <t>破坏射线</t>
+  </si>
+  <si>
+    <t>对玩家造成魔法伤害。</t>
+  </si>
+  <si>
+    <t>curse_gaze</t>
+  </si>
+  <si>
+    <t>诅咒凝视</t>
+  </si>
+  <si>
+    <t>使玩家在下一回合内受到的伤害增加。</t>
+  </si>
+  <si>
+    <t>magic_shield</t>
+  </si>
+  <si>
+    <t>魔法护盾</t>
+  </si>
+  <si>
+    <t>为自己添加一层护盾，抵挡一定量的伤害。</t>
+  </si>
+  <si>
+    <t>sprint_stab</t>
+  </si>
+  <si>
+    <t>疾跑刺击</t>
+  </si>
+  <si>
+    <t>快速冲刺并对玩家造成物理伤害。</t>
+  </si>
+  <si>
+    <t>set_trap</t>
+  </si>
+  <si>
+    <t>布置陷阱</t>
+  </si>
+  <si>
+    <t>下一回合对玩家造成额外伤害。</t>
+  </si>
+  <si>
+    <t>sneak_attack</t>
+  </si>
+  <si>
+    <t>偷袭</t>
+  </si>
+  <si>
+    <t>如果玩家生命值低，造成额外伤害。</t>
+  </si>
+  <si>
+    <t>toxin_spray</t>
+  </si>
+  <si>
+    <t>毒素喷射</t>
+  </si>
+  <si>
+    <t>造成持续性的毒素伤害。</t>
+  </si>
+  <si>
+    <t>healing_spore</t>
+  </si>
+  <si>
+    <t>治疗孢子</t>
+  </si>
+  <si>
+    <t>为自己或其他敌人恢复生命值。</t>
+  </si>
+  <si>
+    <t>hallucinogenic_spore</t>
+  </si>
+  <si>
+    <t>迷幻孢子</t>
+  </si>
+  <si>
+    <t>使玩家在下一回合内混乱，随机选择行动。</t>
+  </si>
+  <si>
+    <t>heavy_strike</t>
+  </si>
+  <si>
+    <t>重击</t>
+  </si>
+  <si>
+    <t>用锋利的武器对玩家造成大量伤害。</t>
+  </si>
+  <si>
+    <t>bone_shield</t>
+  </si>
+  <si>
+    <t>骨盾</t>
+  </si>
+  <si>
+    <t>提高自己的防御力，减少受到的伤害。</t>
+  </si>
+  <si>
+    <t>summon_assistance</t>
+  </si>
+  <si>
+    <t>召唤援助</t>
+  </si>
+  <si>
+    <t>召唤另一个骷髅怪加入战斗</t>
   </si>
   <si>
     <t>card_name</t>
@@ -615,9 +795,6 @@
   </si>
   <si>
     <t>属性描述</t>
-  </si>
-  <si>
-    <t>float</t>
   </si>
   <si>
     <t>bool</t>
@@ -1462,6 +1639,42 @@
   </si>
   <si>
     <t>抹杀者</t>
+  </si>
+  <si>
+    <t>史莱姆（Slime）</t>
+  </si>
+  <si>
+    <t>眼魔（Beholder）</t>
+  </si>
+  <si>
+    <t>哥布林（Goblin）</t>
+  </si>
+  <si>
+    <t>蘑菇精（Mushroom Sprite）</t>
+  </si>
+  <si>
+    <t>split*absorb</t>
+  </si>
+  <si>
+    <t>骷髅怪（Skeleton）</t>
+  </si>
+  <si>
+    <t>destruction_ray*curse_gaze</t>
+  </si>
+  <si>
+    <t>sprint_stab*set_trap</t>
+  </si>
+  <si>
+    <t>意图：</t>
+  </si>
+  <si>
+    <t>toxin_spray*healing_spore</t>
+  </si>
+  <si>
+    <t>heavy_strike*bone_shield</t>
+  </si>
+  <si>
+    <t>描述：</t>
   </si>
 </sst>
 </file>
@@ -1655,7 +1868,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1665,6 +1878,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF7F7F8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.25"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1855,7 +2074,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="36">
+  <borders count="35">
     <border>
       <left/>
       <right/>
@@ -2197,17 +2416,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color auto="1"/>
       </left>
@@ -2340,7 +2548,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="28" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="27" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2352,119 +2560,119 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="32" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="33" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="34" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="35" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="30" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="30" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="32" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="33" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="34" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2606,19 +2814,25 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
@@ -2627,7 +2841,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1" quotePrefix="1">
@@ -3068,15 +3282,15 @@
       <c r="D5" s="1">
         <v>10</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="50" t="s">
+    <row r="6" spans="1:5">
+      <c r="A6" s="52" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="52" t="s">
+      <c r="B6" s="54" t="s">
         <v>18</v>
       </c>
       <c r="C6" s="1">
@@ -3085,13 +3299,16 @@
       <c r="D6" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="50" t="s">
+      <c r="E6" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="52" t="s">
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="52" t="s">
         <v>20</v>
+      </c>
+      <c r="B7" s="54" t="s">
+        <v>21</v>
       </c>
       <c r="C7" s="1">
         <v>50</v>
@@ -3099,13 +3316,16 @@
       <c r="D7" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="50" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="52" t="s">
+      <c r="E7" t="s">
         <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="52" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="54" t="s">
+        <v>24</v>
       </c>
       <c r="C8" s="1">
         <v>50</v>
@@ -3113,19 +3333,25 @@
       <c r="D8" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="50" t="s">
-        <v>23</v>
-      </c>
-      <c r="B9" s="52" t="s">
-        <v>24</v>
+      <c r="E8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" s="54" t="s">
+        <v>27</v>
       </c>
       <c r="C9" s="1">
         <v>50</v>
       </c>
       <c r="D9" s="1">
         <v>10</v>
+      </c>
+      <c r="E9" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -3137,12 +3363,12 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C7:F9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <dimension ref="A7:I66"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
     <row r="7" spans="3:5">
       <c r="C7" s="1" t="s">
-        <v>107</v>
+        <v>167</v>
       </c>
       <c r="D7">
         <v>5</v>
@@ -3154,7 +3380,7 @@
     </row>
     <row r="8" spans="3:6">
       <c r="C8" s="1" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
       <c r="D8">
         <v>4</v>
@@ -3170,7 +3396,7 @@
     </row>
     <row r="9" spans="3:6">
       <c r="C9" s="1" t="s">
-        <v>117</v>
+        <v>177</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -3182,6 +3408,220 @@
       <c r="F9" t="str">
         <f>F8&amp;"*"&amp;E9</f>
         <v>strike*5*defense*4*trounce*1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12">
+        <v>1</v>
+      </c>
+      <c r="B12" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13">
+        <v>2</v>
+      </c>
+      <c r="B13" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14">
+        <v>3</v>
+      </c>
+      <c r="B14" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15">
+        <v>4</v>
+      </c>
+      <c r="B15" t="s">
+        <v>495</v>
+      </c>
+      <c r="F15" t="s">
+        <v>107</v>
+      </c>
+      <c r="H15" t="s">
+        <v>107</v>
+      </c>
+      <c r="I15" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16">
+        <v>5</v>
+      </c>
+      <c r="B16" t="s">
+        <v>497</v>
+      </c>
+      <c r="F16" t="s">
+        <v>496</v>
+      </c>
+      <c r="H16" t="s">
+        <v>116</v>
+      </c>
+      <c r="I16" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="17" spans="6:9">
+      <c r="F17" t="s">
+        <v>51</v>
+      </c>
+      <c r="H17" t="s">
+        <v>125</v>
+      </c>
+      <c r="I17" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9">
+      <c r="B18" t="s">
+        <v>500</v>
+      </c>
+      <c r="F18" t="s">
+        <v>116</v>
+      </c>
+      <c r="H18" t="s">
+        <v>134</v>
+      </c>
+      <c r="I18" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="19" spans="6:9">
+      <c r="F19" t="s">
+        <v>498</v>
+      </c>
+      <c r="H19" t="s">
+        <v>143</v>
+      </c>
+      <c r="I19" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="20" spans="6:8">
+      <c r="F20" t="s">
+        <v>52</v>
+      </c>
+      <c r="H20">
+        <f>IF('intent|意图'!F17='intent|意图'!F16,#REF!&amp;"*"&amp;'intent|意图'!D17,'intent|意图'!D17)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="6:8">
+      <c r="F21" t="s">
+        <v>125</v>
+      </c>
+      <c r="H21">
+        <f>IF('intent|意图'!F18='intent|意图'!F17,H20&amp;"*"&amp;'intent|意图'!D18,'intent|意图'!D18)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="6:8">
+      <c r="F22" t="s">
+        <v>499</v>
+      </c>
+      <c r="H22">
+        <f>IF('intent|意图'!F19='intent|意图'!F18,H21&amp;"*"&amp;'intent|意图'!D19,'intent|意图'!D19)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="6:8">
+      <c r="F23" t="s">
+        <v>53</v>
+      </c>
+      <c r="H23">
+        <f>IF('intent|意图'!F20='intent|意图'!F19,H22&amp;"*"&amp;'intent|意图'!D20,'intent|意图'!D20)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="6:8">
+      <c r="F24" t="s">
+        <v>134</v>
+      </c>
+      <c r="H24">
+        <f>IF('intent|意图'!F21='intent|意图'!F20,H23&amp;"*"&amp;'intent|意图'!D21,'intent|意图'!D21)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="6:8">
+      <c r="F25" t="s">
+        <v>501</v>
+      </c>
+      <c r="H25">
+        <f>IF('intent|意图'!F22='intent|意图'!F21,H24&amp;"*"&amp;'intent|意图'!D22,'intent|意图'!D22)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="6:8">
+      <c r="F26" t="s">
+        <v>54</v>
+      </c>
+      <c r="H26">
+        <f>IF('intent|意图'!F23='intent|意图'!F22,H25&amp;"*"&amp;'intent|意图'!D23,'intent|意图'!D23)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="6:8">
+      <c r="F27" t="s">
+        <v>143</v>
+      </c>
+      <c r="H27">
+        <f>IF('intent|意图'!F24='intent|意图'!F23,H26&amp;"*"&amp;'intent|意图'!D24,'intent|意图'!D24)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="6:8">
+      <c r="F28" t="s">
+        <v>502</v>
+      </c>
+      <c r="H28">
+        <f>IF('intent|意图'!F25='intent|意图'!F24,H27&amp;"*"&amp;'intent|意图'!D25,'intent|意图'!D25)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="6:8">
+      <c r="F29" t="s">
+        <v>55</v>
+      </c>
+      <c r="H29">
+        <f>IF('intent|意图'!F26='intent|意图'!F25,H28&amp;"*"&amp;'intent|意图'!D26,'intent|意图'!D26)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="2:2">
+      <c r="B30" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="42" spans="2:2">
+      <c r="B42" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="50" spans="2:2">
+      <c r="B50" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="54" spans="2:2">
+      <c r="B54" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="62" spans="2:2">
+      <c r="B62" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="66" spans="2:2">
+      <c r="B66" t="s">
+        <v>500</v>
       </c>
     </row>
   </sheetData>
@@ -3204,13 +3644,13 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -3218,16 +3658,16 @@
         <v>0</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -3252,14 +3692,14 @@
         <v>1</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="50" t="s">
-        <v>21</v>
+      <c r="E4" s="52" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -3274,7 +3714,7 @@
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultColWidth="8.86666666666667" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="8.33333333333333" style="54" customWidth="1"/>
+    <col min="1" max="1" width="8.33333333333333" style="56" customWidth="1"/>
     <col min="2" max="2" width="11.8666666666667" customWidth="1"/>
     <col min="3" max="3" width="31.4666666666667" customWidth="1"/>
   </cols>
@@ -3284,29 +3724,29 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D1" s="5"/>
       <c r="E1" s="5"/>
     </row>
-    <row r="2" s="53" customFormat="1" spans="1:5">
+    <row r="2" s="55" customFormat="1" spans="1:5">
       <c r="A2" s="41" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="41" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C2" s="41" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D2" s="41" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E2" s="41" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -3317,7 +3757,7 @@
         <v>10</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>11</v>
@@ -3334,13 +3774,13 @@
         <v>12</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D4" s="1">
         <v>99</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -3357,7 +3797,7 @@
   <cols>
     <col min="1" max="1" width="11.5" customWidth="1"/>
     <col min="2" max="2" width="11.4666666666667" style="21" customWidth="1"/>
-    <col min="3" max="3" width="28.0666666666667" customWidth="1"/>
+    <col min="3" max="3" width="51.5" customWidth="1"/>
     <col min="4" max="4" width="14.125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3368,11 +3808,11 @@
       <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="49" t="s">
-        <v>42</v>
-      </c>
-      <c r="D1" s="21" t="s">
-        <v>43</v>
+      <c r="C1" s="53" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1" s="53" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -3380,13 +3820,13 @@
         <v>0</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C2" s="49" t="s">
-        <v>45</v>
-      </c>
-      <c r="D2" s="21" t="s">
-        <v>46</v>
+        <v>48</v>
+      </c>
+      <c r="C2" s="53" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" s="53" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -3396,10 +3836,10 @@
       <c r="B3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="49" t="s">
-        <v>39</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="C3" s="53" t="s">
+        <v>43</v>
+      </c>
+      <c r="D3" s="52" t="s">
         <v>10</v>
       </c>
     </row>
@@ -3410,62 +3850,70 @@
       <c r="B4" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="50" t="s">
-        <v>47</v>
-      </c>
-      <c r="D4" s="51" t="str">
+      <c r="C4" s="52" t="s">
+        <v>51</v>
+      </c>
+      <c r="D4" s="40" t="str">
         <f t="shared" ref="D4:D8" si="0">"enemy_"&amp;A4</f>
         <v>enemy_slime</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="50" t="s">
+      <c r="A5" s="52" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="52" t="s">
+      <c r="B5" s="54" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="50"/>
-      <c r="D5" s="51" t="str">
+      <c r="C5" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="D5" s="40" t="str">
         <f t="shared" si="0"/>
         <v>enemy_flying_eye</v>
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="50" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="52" t="s">
+      <c r="A6" s="52" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="50"/>
-      <c r="D6" s="51" t="str">
+      <c r="B6" s="54" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="D6" s="40" t="str">
         <f t="shared" si="0"/>
         <v>enemy_goblin</v>
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="50" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" s="52" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" s="50"/>
-      <c r="D7" s="51" t="str">
+      <c r="A7" s="52" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="54" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="52" t="s">
+        <v>54</v>
+      </c>
+      <c r="D7" s="40" t="str">
         <f t="shared" si="0"/>
         <v>enemy_mushroom</v>
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="50" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" s="52" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" s="50"/>
-      <c r="D8" s="51" t="str">
+      <c r="A8" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="54" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="52" t="s">
+        <v>55</v>
+      </c>
+      <c r="D8" s="40" t="str">
         <f t="shared" si="0"/>
         <v>enemy_skeleton</v>
       </c>
@@ -3480,242 +3928,723 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
+  <dimension ref="A1:J26"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="3" max="3" width="9.06666666666667" style="44"/>
-    <col min="4" max="4" width="62" customWidth="1"/>
-    <col min="5" max="5" width="67.125" customWidth="1"/>
+    <col min="1" max="1" width="21.25" customWidth="1"/>
+    <col min="2" max="2" width="9.06666666666667" style="44"/>
+    <col min="4" max="6" width="9.06666666666667" style="44"/>
+    <col min="7" max="7" width="62" customWidth="1"/>
+    <col min="8" max="8" width="67.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:10">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="45" t="s">
-        <v>48</v>
-      </c>
-      <c r="D1" s="46" t="s">
-        <v>49</v>
-      </c>
-      <c r="E1" s="46" t="s">
-        <v>50</v>
-      </c>
-      <c r="F1" s="46" t="s">
-        <v>51</v>
-      </c>
-      <c r="G1" s="47" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
+      <c r="B1" s="45" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="45" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1" s="45" t="s">
+        <v>58</v>
+      </c>
+      <c r="F1" s="45" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1" s="46" t="s">
+        <v>60</v>
+      </c>
+      <c r="H1" s="46" t="s">
+        <v>61</v>
+      </c>
+      <c r="I1" s="46" t="s">
+        <v>62</v>
+      </c>
+      <c r="J1" s="46" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C2" s="45" t="s">
-        <v>54</v>
-      </c>
-      <c r="D2" s="46" t="s">
-        <v>55</v>
-      </c>
-      <c r="E2" s="46" t="s">
-        <v>56</v>
-      </c>
-      <c r="F2" s="46" t="s">
-        <v>57</v>
-      </c>
-      <c r="G2" s="47" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+      <c r="B2" s="45" t="s">
+        <v>64</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D2" s="45" t="s">
+        <v>66</v>
+      </c>
+      <c r="E2" s="45" t="s">
+        <v>67</v>
+      </c>
+      <c r="F2" s="45" t="s">
+        <v>68</v>
+      </c>
+      <c r="G2" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="H2" s="46" t="s">
+        <v>70</v>
+      </c>
+      <c r="I2" s="46" t="s">
+        <v>71</v>
+      </c>
+      <c r="J2" s="46" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="45" t="s">
+      <c r="B3" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="45" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="46" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="46" t="s">
-        <v>59</v>
-      </c>
-      <c r="F3" s="46" t="s">
+      <c r="E3" s="45" t="s">
+        <v>73</v>
+      </c>
+      <c r="F3" s="45" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="47" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+      <c r="G3" s="46" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="46" t="s">
+        <v>74</v>
+      </c>
+      <c r="I3" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="J3" s="46" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B4" s="40" t="s">
-        <v>61</v>
-      </c>
-      <c r="C4" s="48">
-        <v>1</v>
-      </c>
-      <c r="D4" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F4" s="1">
+        <v>75</v>
+      </c>
+      <c r="B4" s="47"/>
+      <c r="C4" s="40" t="s">
+        <v>76</v>
+      </c>
+      <c r="D4" s="47">
+        <v>1</v>
+      </c>
+      <c r="E4" s="47"/>
+      <c r="F4" s="47"/>
+      <c r="G4" s="40" t="s">
+        <v>77</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="I4" s="1">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
+      <c r="J4" s="52"/>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C5" s="48">
+        <v>79</v>
+      </c>
+      <c r="B5" s="47"/>
+      <c r="C5" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D5" s="47">
         <v>2</v>
       </c>
-      <c r="D5" s="40" t="s">
-        <v>66</v>
-      </c>
-      <c r="E5" s="40" t="s">
-        <v>67</v>
-      </c>
-      <c r="F5" s="1">
+      <c r="E5" s="47"/>
+      <c r="F5" s="47"/>
+      <c r="G5" s="40" t="s">
+        <v>81</v>
+      </c>
+      <c r="H5" s="40" t="s">
+        <v>82</v>
+      </c>
+      <c r="I5" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="1:6">
+      <c r="J5" s="52"/>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C6" s="48">
+        <v>83</v>
+      </c>
+      <c r="B6" s="47"/>
+      <c r="C6" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D6" s="47">
         <v>3</v>
       </c>
-      <c r="D6" s="40" t="s">
-        <v>70</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="F6" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+      <c r="E6" s="47"/>
+      <c r="F6" s="47"/>
+      <c r="G6" s="40" t="s">
+        <v>85</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="I6" s="1">
+        <v>0</v>
+      </c>
+      <c r="J6" s="52"/>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C7" s="48">
+        <v>87</v>
+      </c>
+      <c r="B7" s="47"/>
+      <c r="C7" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D7" s="47">
         <v>4</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="F7" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+      <c r="E7" s="47"/>
+      <c r="F7" s="47"/>
+      <c r="G7" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="I7" s="1">
+        <v>0</v>
+      </c>
+      <c r="J7" s="52"/>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C8" s="48">
+        <v>91</v>
+      </c>
+      <c r="B8" s="47"/>
+      <c r="C8" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D8" s="47">
         <v>5</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="F8" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+      <c r="E8" s="47"/>
+      <c r="F8" s="47"/>
+      <c r="G8" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="I8" s="1">
+        <v>0</v>
+      </c>
+      <c r="J8" s="52"/>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="C9" s="48">
+        <v>95</v>
+      </c>
+      <c r="B9" s="47"/>
+      <c r="C9" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D9" s="47">
         <v>6</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F9" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+      <c r="E9" s="47"/>
+      <c r="F9" s="47"/>
+      <c r="G9" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="I9" s="1">
+        <v>0</v>
+      </c>
+      <c r="J9" s="52"/>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="C10" s="48">
+        <v>99</v>
+      </c>
+      <c r="B10" s="47"/>
+      <c r="C10" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D10" s="47">
         <v>7</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="F10" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
+      <c r="E10" s="47"/>
+      <c r="F10" s="47"/>
+      <c r="G10" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="I10" s="1">
+        <v>0</v>
+      </c>
+      <c r="J10" s="52"/>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="C11" s="48">
+        <v>103</v>
+      </c>
+      <c r="B11" s="47"/>
+      <c r="C11" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D11" s="47">
         <v>8</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="F11" s="1">
-        <v>0</v>
-      </c>
+      <c r="E11" s="47"/>
+      <c r="F11" s="47"/>
+      <c r="G11" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="I11" s="1">
+        <v>0</v>
+      </c>
+      <c r="J11" s="52"/>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="48" t="s">
+        <v>107</v>
+      </c>
+      <c r="B12" s="49" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" s="50" t="s">
+        <v>108</v>
+      </c>
+      <c r="D12" s="51"/>
+      <c r="E12" s="51">
+        <v>1</v>
+      </c>
+      <c r="F12" s="51">
+        <v>0</v>
+      </c>
+      <c r="G12" s="50" t="s">
+        <v>109</v>
+      </c>
+      <c r="H12" s="49" t="s">
+        <v>106</v>
+      </c>
+      <c r="I12" s="49">
+        <v>0</v>
+      </c>
+      <c r="J12" s="50"/>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="48" t="s">
+        <v>110</v>
+      </c>
+      <c r="B13" s="49" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="50" t="s">
+        <v>111</v>
+      </c>
+      <c r="D13" s="51"/>
+      <c r="E13" s="51">
+        <v>1</v>
+      </c>
+      <c r="F13" s="51">
+        <v>1</v>
+      </c>
+      <c r="G13" s="50" t="s">
+        <v>112</v>
+      </c>
+      <c r="H13" s="49" t="s">
+        <v>106</v>
+      </c>
+      <c r="I13" s="49">
+        <v>0</v>
+      </c>
+      <c r="J13" s="50"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="48" t="s">
+        <v>113</v>
+      </c>
+      <c r="B14" s="49" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="50" t="s">
+        <v>114</v>
+      </c>
+      <c r="D14" s="51"/>
+      <c r="E14" s="51">
+        <v>1</v>
+      </c>
+      <c r="F14" s="51">
+        <v>3</v>
+      </c>
+      <c r="G14" s="50" t="s">
+        <v>115</v>
+      </c>
+      <c r="H14" s="49" t="s">
+        <v>106</v>
+      </c>
+      <c r="I14" s="49">
+        <v>0</v>
+      </c>
+      <c r="J14" s="50"/>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="48" t="s">
+        <v>116</v>
+      </c>
+      <c r="B15" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="50" t="s">
+        <v>117</v>
+      </c>
+      <c r="D15" s="51"/>
+      <c r="E15" s="51">
+        <v>1</v>
+      </c>
+      <c r="F15" s="51">
+        <v>0</v>
+      </c>
+      <c r="G15" s="50" t="s">
+        <v>118</v>
+      </c>
+      <c r="H15" s="49" t="s">
+        <v>106</v>
+      </c>
+      <c r="I15" s="49">
+        <v>0</v>
+      </c>
+      <c r="J15" s="50"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="48" t="s">
+        <v>119</v>
+      </c>
+      <c r="B16" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="50" t="s">
+        <v>120</v>
+      </c>
+      <c r="D16" s="51"/>
+      <c r="E16" s="51">
+        <v>1</v>
+      </c>
+      <c r="F16" s="51">
+        <v>1</v>
+      </c>
+      <c r="G16" s="50" t="s">
+        <v>121</v>
+      </c>
+      <c r="H16" s="49" t="s">
+        <v>106</v>
+      </c>
+      <c r="I16" s="49">
+        <v>0</v>
+      </c>
+      <c r="J16" s="50"/>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="48" t="s">
+        <v>122</v>
+      </c>
+      <c r="B17" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="50" t="s">
+        <v>123</v>
+      </c>
+      <c r="D17" s="51"/>
+      <c r="E17" s="51">
+        <v>1</v>
+      </c>
+      <c r="F17" s="51">
+        <v>3</v>
+      </c>
+      <c r="G17" s="50" t="s">
+        <v>124</v>
+      </c>
+      <c r="H17" s="49" t="s">
+        <v>106</v>
+      </c>
+      <c r="I17" s="49">
+        <v>0</v>
+      </c>
+      <c r="J17" s="50"/>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="48" t="s">
+        <v>125</v>
+      </c>
+      <c r="B18" s="50" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18" s="50" t="s">
+        <v>126</v>
+      </c>
+      <c r="D18" s="51"/>
+      <c r="E18" s="51">
+        <v>1</v>
+      </c>
+      <c r="F18" s="51">
+        <v>0</v>
+      </c>
+      <c r="G18" s="50" t="s">
+        <v>127</v>
+      </c>
+      <c r="H18" s="49" t="s">
+        <v>106</v>
+      </c>
+      <c r="I18" s="49">
+        <v>0</v>
+      </c>
+      <c r="J18" s="50"/>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="48" t="s">
+        <v>128</v>
+      </c>
+      <c r="B19" s="50" t="s">
+        <v>20</v>
+      </c>
+      <c r="C19" s="50" t="s">
+        <v>129</v>
+      </c>
+      <c r="D19" s="51"/>
+      <c r="E19" s="51">
+        <v>1</v>
+      </c>
+      <c r="F19" s="51">
+        <v>1</v>
+      </c>
+      <c r="G19" s="50" t="s">
+        <v>130</v>
+      </c>
+      <c r="H19" s="49" t="s">
+        <v>106</v>
+      </c>
+      <c r="I19" s="49">
+        <v>0</v>
+      </c>
+      <c r="J19" s="50"/>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="48" t="s">
+        <v>131</v>
+      </c>
+      <c r="B20" s="50" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" s="50" t="s">
+        <v>132</v>
+      </c>
+      <c r="D20" s="51"/>
+      <c r="E20" s="51">
+        <v>1</v>
+      </c>
+      <c r="F20" s="51">
+        <v>3</v>
+      </c>
+      <c r="G20" s="50" t="s">
+        <v>133</v>
+      </c>
+      <c r="H20" s="49" t="s">
+        <v>106</v>
+      </c>
+      <c r="I20" s="49">
+        <v>0</v>
+      </c>
+      <c r="J20" s="50"/>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="48" t="s">
+        <v>134</v>
+      </c>
+      <c r="B21" s="50" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21" s="50" t="s">
+        <v>135</v>
+      </c>
+      <c r="D21" s="51"/>
+      <c r="E21" s="51">
+        <v>1</v>
+      </c>
+      <c r="F21" s="51">
+        <v>0</v>
+      </c>
+      <c r="G21" s="50" t="s">
+        <v>136</v>
+      </c>
+      <c r="H21" s="49" t="s">
+        <v>106</v>
+      </c>
+      <c r="I21" s="49">
+        <v>0</v>
+      </c>
+      <c r="J21" s="50"/>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="48" t="s">
+        <v>137</v>
+      </c>
+      <c r="B22" s="50" t="s">
+        <v>23</v>
+      </c>
+      <c r="C22" s="50" t="s">
+        <v>138</v>
+      </c>
+      <c r="D22" s="51"/>
+      <c r="E22" s="51">
+        <v>1</v>
+      </c>
+      <c r="F22" s="51">
+        <v>1</v>
+      </c>
+      <c r="G22" s="50" t="s">
+        <v>139</v>
+      </c>
+      <c r="H22" s="49" t="s">
+        <v>106</v>
+      </c>
+      <c r="I22" s="49">
+        <v>0</v>
+      </c>
+      <c r="J22" s="50"/>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="B23" s="50" t="s">
+        <v>23</v>
+      </c>
+      <c r="C23" s="50" t="s">
+        <v>141</v>
+      </c>
+      <c r="D23" s="51"/>
+      <c r="E23" s="51">
+        <v>1</v>
+      </c>
+      <c r="F23" s="51">
+        <v>3</v>
+      </c>
+      <c r="G23" s="50" t="s">
+        <v>142</v>
+      </c>
+      <c r="H23" s="49" t="s">
+        <v>106</v>
+      </c>
+      <c r="I23" s="49">
+        <v>0</v>
+      </c>
+      <c r="J23" s="50"/>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="48" t="s">
+        <v>143</v>
+      </c>
+      <c r="B24" s="50" t="s">
+        <v>26</v>
+      </c>
+      <c r="C24" s="50" t="s">
+        <v>144</v>
+      </c>
+      <c r="D24" s="51"/>
+      <c r="E24" s="51">
+        <v>1</v>
+      </c>
+      <c r="F24" s="51">
+        <v>0</v>
+      </c>
+      <c r="G24" s="50" t="s">
+        <v>145</v>
+      </c>
+      <c r="H24" s="49" t="s">
+        <v>106</v>
+      </c>
+      <c r="I24" s="49">
+        <v>0</v>
+      </c>
+      <c r="J24" s="50"/>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="48" t="s">
+        <v>146</v>
+      </c>
+      <c r="B25" s="50" t="s">
+        <v>26</v>
+      </c>
+      <c r="C25" s="50" t="s">
+        <v>147</v>
+      </c>
+      <c r="D25" s="51"/>
+      <c r="E25" s="51">
+        <v>1</v>
+      </c>
+      <c r="F25" s="51">
+        <v>1</v>
+      </c>
+      <c r="G25" s="50" t="s">
+        <v>148</v>
+      </c>
+      <c r="H25" s="49" t="s">
+        <v>106</v>
+      </c>
+      <c r="I25" s="49">
+        <v>0</v>
+      </c>
+      <c r="J25" s="50"/>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="48" t="s">
+        <v>149</v>
+      </c>
+      <c r="B26" s="50" t="s">
+        <v>26</v>
+      </c>
+      <c r="C26" s="50" t="s">
+        <v>150</v>
+      </c>
+      <c r="D26" s="51"/>
+      <c r="E26" s="51">
+        <v>1</v>
+      </c>
+      <c r="F26" s="51">
+        <v>3</v>
+      </c>
+      <c r="G26" s="50" t="s">
+        <v>151</v>
+      </c>
+      <c r="H26" s="49" t="s">
+        <v>106</v>
+      </c>
+      <c r="I26" s="49">
+        <v>0</v>
+      </c>
+      <c r="J26" s="50"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3743,28 +4672,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>92</v>
+        <v>152</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>93</v>
+        <v>153</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>94</v>
+        <v>154</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>95</v>
+        <v>155</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>96</v>
+        <v>156</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>97</v>
+        <v>157</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>98</v>
+        <v>158</v>
       </c>
     </row>
     <row r="2" ht="54" spans="1:9">
@@ -3772,28 +4701,28 @@
         <v>5</v>
       </c>
       <c r="B2" s="41" t="s">
-        <v>99</v>
+        <v>159</v>
       </c>
       <c r="C2" s="41" t="s">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="D2" s="41" t="s">
-        <v>101</v>
+        <v>161</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>102</v>
+        <v>162</v>
       </c>
       <c r="F2" s="41" t="s">
-        <v>103</v>
+        <v>163</v>
       </c>
       <c r="G2" s="42" t="s">
-        <v>104</v>
+        <v>164</v>
       </c>
       <c r="H2" s="41" t="s">
-        <v>105</v>
+        <v>165</v>
       </c>
       <c r="I2" s="43" t="s">
-        <v>106</v>
+        <v>166</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -3813,7 +4742,7 @@
         <v>10</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>11</v>
@@ -3822,15 +4751,15 @@
         <v>10</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>107</v>
+        <v>167</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>108</v>
+        <v>168</v>
       </c>
       <c r="C4" s="1">
         <v>1</v>
@@ -3839,27 +4768,27 @@
         <v>1</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
       <c r="F4" s="40" t="s">
-        <v>110</v>
+        <v>170</v>
       </c>
       <c r="G4" s="1">
         <v>2</v>
       </c>
       <c r="H4" s="40" t="s">
-        <v>111</v>
+        <v>171</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>107</v>
+        <v>167</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="C5" s="1">
         <v>2</v>
@@ -3868,27 +4797,27 @@
         <v>1</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>113</v>
+        <v>173</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>114</v>
+        <v>174</v>
       </c>
       <c r="G5" s="1">
         <v>1</v>
       </c>
       <c r="H5" s="40" t="s">
-        <v>115</v>
+        <v>175</v>
       </c>
       <c r="I5" s="40" t="s">
-        <v>116</v>
+        <v>176</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>117</v>
+        <v>177</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>118</v>
+        <v>178</v>
       </c>
       <c r="C6" s="1">
         <v>1</v>
@@ -3897,19 +4826,19 @@
         <v>2</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>119</v>
+        <v>179</v>
       </c>
       <c r="F6" s="40" t="s">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="G6" s="1">
         <v>2</v>
       </c>
       <c r="H6" s="40" t="s">
-        <v>111</v>
+        <v>171</v>
       </c>
       <c r="I6" s="40" t="s">
-        <v>121</v>
+        <v>181</v>
       </c>
     </row>
   </sheetData>
@@ -3937,22 +4866,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>122</v>
+        <v>182</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>123</v>
+        <v>183</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>96</v>
+        <v>156</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>124</v>
+        <v>184</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>125</v>
+        <v>185</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>126</v>
+        <v>186</v>
       </c>
       <c r="H1" s="5" t="s">
         <v>4</v>
@@ -3963,25 +4892,25 @@
         <v>5</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>122</v>
+        <v>182</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>127</v>
+        <v>187</v>
       </c>
       <c r="D2" s="42" t="s">
-        <v>128</v>
+        <v>188</v>
       </c>
       <c r="E2" s="41" t="s">
-        <v>129</v>
+        <v>189</v>
       </c>
       <c r="F2" s="41" t="s">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="G2" s="41" t="s">
-        <v>131</v>
+        <v>191</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>132</v>
+        <v>192</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -4004,7 +4933,7 @@
         <v>11</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H3" s="5" t="s">
         <v>10</v>
@@ -4012,11 +4941,11 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
-        <v>107</v>
+        <v>167</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1" t="s">
-        <v>108</v>
+        <v>168</v>
       </c>
       <c r="D4" s="1">
         <v>0</v>
@@ -4031,16 +4960,16 @@
         <v>6</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="40" t="s">
-        <v>116</v>
+        <v>176</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="40" t="s">
-        <v>133</v>
+        <v>193</v>
       </c>
       <c r="D5" s="1">
         <v>1</v>
@@ -4055,16 +4984,16 @@
         <v>5</v>
       </c>
       <c r="H5" s="40" t="s">
-        <v>134</v>
+        <v>194</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="40" t="s">
-        <v>135</v>
+        <v>195</v>
       </c>
       <c r="B6" s="1"/>
       <c r="C6" s="1" t="s">
-        <v>118</v>
+        <v>178</v>
       </c>
       <c r="D6" s="1">
         <v>0</v>
@@ -4079,16 +5008,16 @@
         <v>8</v>
       </c>
       <c r="H6" s="40" t="s">
-        <v>136</v>
+        <v>196</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="40" t="s">
-        <v>137</v>
+        <v>197</v>
       </c>
       <c r="B7" s="1"/>
       <c r="C7" s="1" t="s">
-        <v>138</v>
+        <v>198</v>
       </c>
       <c r="D7" s="1">
         <v>0</v>
@@ -4100,21 +5029,21 @@
         <v>3</v>
       </c>
       <c r="G7" s="40" t="s">
-        <v>139</v>
+        <v>199</v>
       </c>
       <c r="H7" s="40" t="s">
-        <v>140</v>
+        <v>200</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="1" t="s">
-        <v>141</v>
+        <v>201</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>142</v>
+        <v>202</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>143</v>
+        <v>203</v>
       </c>
       <c r="D8" s="1">
         <v>0</v>
@@ -4129,18 +5058,18 @@
         <v>1</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>144</v>
+        <v>204</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
-        <v>145</v>
+        <v>205</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>146</v>
+        <v>206</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -4155,18 +5084,18 @@
         <v>2</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>147</v>
+        <v>207</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
-        <v>148</v>
+        <v>208</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>149</v>
+        <v>209</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>150</v>
+        <v>210</v>
       </c>
       <c r="D10" s="1">
         <v>0</v>
@@ -4181,18 +5110,18 @@
         <v>3</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>151</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
-        <v>152</v>
+        <v>212</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>153</v>
+        <v>213</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>154</v>
+        <v>214</v>
       </c>
       <c r="D11" s="1">
         <v>0</v>
@@ -4207,18 +5136,18 @@
         <v>4</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>155</v>
+        <v>215</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
-        <v>156</v>
+        <v>216</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>157</v>
+        <v>217</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="D12" s="1">
         <v>0</v>
@@ -4233,18 +5162,18 @@
         <v>5</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>158</v>
+        <v>218</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1" t="s">
-        <v>159</v>
+        <v>219</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>160</v>
+        <v>220</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>161</v>
+        <v>221</v>
       </c>
       <c r="D13" s="1">
         <v>0</v>
@@ -4259,18 +5188,18 @@
         <v>6</v>
       </c>
       <c r="H13" s="40" t="s">
-        <v>162</v>
+        <v>222</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>163</v>
+        <v>223</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>164</v>
+        <v>224</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>165</v>
+        <v>225</v>
       </c>
       <c r="D14" s="1">
         <v>0</v>
@@ -4285,18 +5214,18 @@
         <v>7</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>166</v>
+        <v>226</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1" t="s">
-        <v>167</v>
+        <v>227</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>168</v>
+        <v>228</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>169</v>
+        <v>229</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -4311,18 +5240,18 @@
         <v>8</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>170</v>
+        <v>230</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1" t="s">
-        <v>171</v>
+        <v>231</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>172</v>
+        <v>232</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>173</v>
+        <v>233</v>
       </c>
       <c r="D16" s="1">
         <v>0</v>
@@ -4337,7 +5266,7 @@
         <v>9</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>174</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -4362,22 +5291,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="35" t="s">
-        <v>175</v>
+        <v>235</v>
       </c>
       <c r="C1" s="35" t="s">
-        <v>176</v>
+        <v>236</v>
       </c>
       <c r="D1" s="35" t="s">
-        <v>177</v>
+        <v>237</v>
       </c>
       <c r="E1" s="35" t="s">
-        <v>178</v>
+        <v>238</v>
       </c>
       <c r="F1" s="35" t="s">
-        <v>179</v>
+        <v>239</v>
       </c>
       <c r="G1" s="35" t="s">
-        <v>180</v>
+        <v>240</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -4385,22 +5314,22 @@
         <v>5</v>
       </c>
       <c r="B2" s="37" t="s">
-        <v>181</v>
+        <v>241</v>
       </c>
       <c r="C2" s="37" t="s">
-        <v>127</v>
+        <v>187</v>
       </c>
       <c r="D2" s="37" t="s">
-        <v>182</v>
+        <v>242</v>
       </c>
       <c r="E2" s="37" t="s">
-        <v>183</v>
+        <v>243</v>
       </c>
       <c r="F2" s="37" t="s">
-        <v>184</v>
+        <v>244</v>
       </c>
       <c r="G2" s="38" t="s">
-        <v>185</v>
+        <v>245</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -4411,16 +5340,16 @@
         <v>10</v>
       </c>
       <c r="C3" s="37" t="s">
-        <v>186</v>
+        <v>73</v>
       </c>
       <c r="D3" s="37" t="s">
-        <v>186</v>
+        <v>73</v>
       </c>
       <c r="E3" s="37" t="s">
-        <v>186</v>
+        <v>73</v>
       </c>
       <c r="F3" s="37" t="s">
-        <v>187</v>
+        <v>246</v>
       </c>
       <c r="G3" s="37" t="s">
         <v>10</v>
@@ -4428,10 +5357,10 @@
     </row>
     <row r="4" ht="14.25" spans="1:7">
       <c r="A4" s="39" t="s">
-        <v>188</v>
+        <v>247</v>
       </c>
       <c r="B4" s="40" t="s">
-        <v>189</v>
+        <v>248</v>
       </c>
       <c r="C4" s="39">
         <v>100</v>
@@ -4446,15 +5375,15 @@
         <v>1</v>
       </c>
       <c r="G4" s="39" t="s">
-        <v>190</v>
+        <v>249</v>
       </c>
     </row>
     <row r="5" ht="14.25" spans="1:7">
       <c r="A5" s="39" t="s">
-        <v>191</v>
+        <v>250</v>
       </c>
       <c r="B5" s="40" t="s">
-        <v>192</v>
+        <v>251</v>
       </c>
       <c r="C5" s="39">
         <v>100</v>
@@ -4469,15 +5398,15 @@
         <v>1</v>
       </c>
       <c r="G5" s="39" t="s">
-        <v>193</v>
+        <v>252</v>
       </c>
     </row>
     <row r="6" ht="14.25" spans="1:7">
       <c r="A6" s="39" t="s">
-        <v>194</v>
+        <v>253</v>
       </c>
       <c r="B6" s="40" t="s">
-        <v>195</v>
+        <v>254</v>
       </c>
       <c r="C6" s="39">
         <v>3</v>
@@ -4492,15 +5421,15 @@
         <v>1</v>
       </c>
       <c r="G6" s="39" t="s">
-        <v>196</v>
+        <v>255</v>
       </c>
     </row>
     <row r="7" ht="14.25" spans="1:7">
       <c r="A7" s="39" t="s">
-        <v>197</v>
+        <v>256</v>
       </c>
       <c r="B7" s="40" t="s">
-        <v>198</v>
+        <v>257</v>
       </c>
       <c r="C7" s="39">
         <v>3</v>
@@ -4515,12 +5444,12 @@
         <v>1</v>
       </c>
       <c r="G7" s="39" t="s">
-        <v>199</v>
+        <v>258</v>
       </c>
     </row>
     <row r="8" ht="14.25" spans="1:7">
       <c r="A8" s="39" t="s">
-        <v>200</v>
+        <v>259</v>
       </c>
       <c r="B8" s="40" t="s">
         <v>8</v>
@@ -4538,15 +5467,15 @@
         <v>1</v>
       </c>
       <c r="G8" s="39" t="s">
-        <v>201</v>
+        <v>260</v>
       </c>
     </row>
     <row r="9" ht="14.25" spans="1:7">
       <c r="A9" s="39" t="s">
-        <v>202</v>
+        <v>261</v>
       </c>
       <c r="B9" s="40" t="s">
-        <v>203</v>
+        <v>262</v>
       </c>
       <c r="C9" s="39">
         <v>0</v>
@@ -4561,15 +5490,15 @@
         <v>1</v>
       </c>
       <c r="G9" s="39" t="s">
-        <v>204</v>
+        <v>263</v>
       </c>
     </row>
     <row r="10" ht="14.25" spans="1:7">
       <c r="A10" s="39" t="s">
-        <v>205</v>
+        <v>264</v>
       </c>
       <c r="B10" s="40" t="s">
-        <v>206</v>
+        <v>265</v>
       </c>
       <c r="C10" s="39">
         <v>0</v>
@@ -4584,15 +5513,15 @@
         <v>1</v>
       </c>
       <c r="G10" s="39" t="s">
-        <v>207</v>
+        <v>266</v>
       </c>
     </row>
     <row r="11" ht="14.25" spans="1:7">
       <c r="A11" s="39" t="s">
-        <v>208</v>
+        <v>267</v>
       </c>
       <c r="B11" s="40" t="s">
-        <v>209</v>
+        <v>268</v>
       </c>
       <c r="C11" s="39">
         <v>0</v>
@@ -4607,15 +5536,15 @@
         <v>1</v>
       </c>
       <c r="G11" s="39" t="s">
-        <v>210</v>
+        <v>269</v>
       </c>
     </row>
     <row r="12" ht="14.25" spans="1:7">
       <c r="A12" s="39" t="s">
-        <v>211</v>
+        <v>270</v>
       </c>
       <c r="B12" s="40" t="s">
-        <v>212</v>
+        <v>271</v>
       </c>
       <c r="C12" s="39">
         <v>0</v>
@@ -4630,15 +5559,15 @@
         <v>1</v>
       </c>
       <c r="G12" s="39" t="s">
-        <v>213</v>
+        <v>272</v>
       </c>
     </row>
     <row r="13" ht="14.25" spans="1:7">
       <c r="A13" s="39" t="s">
-        <v>214</v>
+        <v>273</v>
       </c>
       <c r="B13" s="40" t="s">
-        <v>215</v>
+        <v>274</v>
       </c>
       <c r="C13" s="39">
         <v>0</v>
@@ -4653,15 +5582,15 @@
         <v>1</v>
       </c>
       <c r="G13" s="39" t="s">
-        <v>216</v>
+        <v>275</v>
       </c>
     </row>
     <row r="14" ht="14.25" spans="1:7">
       <c r="A14" s="39" t="s">
-        <v>217</v>
+        <v>276</v>
       </c>
       <c r="B14" s="40" t="s">
-        <v>133</v>
+        <v>193</v>
       </c>
       <c r="C14" s="39">
         <v>0</v>
@@ -4676,7 +5605,7 @@
         <v>1</v>
       </c>
       <c r="G14" s="39" t="s">
-        <v>218</v>
+        <v>277</v>
       </c>
     </row>
   </sheetData>
@@ -4699,67 +5628,67 @@
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>219</v>
+        <v>278</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>220</v>
+        <v>279</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>221</v>
+        <v>280</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>222</v>
+        <v>281</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>223</v>
+        <v>282</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>224</v>
+        <v>283</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>225</v>
+        <v>284</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>226</v>
+        <v>285</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>227</v>
+        <v>286</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>228</v>
+        <v>287</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>229</v>
+        <v>288</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>230</v>
+        <v>289</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>231</v>
+        <v>290</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>232</v>
+        <v>291</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>233</v>
+        <v>292</v>
       </c>
       <c r="R1" s="13" t="s">
-        <v>234</v>
+        <v>293</v>
       </c>
       <c r="S1" s="3" t="s">
-        <v>235</v>
+        <v>294</v>
       </c>
       <c r="T1" s="3" t="s">
-        <v>236</v>
+        <v>295</v>
       </c>
       <c r="U1" s="3" t="s">
-        <v>237</v>
+        <v>296</v>
       </c>
       <c r="V1" s="3" t="s">
-        <v>238</v>
+        <v>297</v>
       </c>
       <c r="W1" s="14" t="s">
-        <v>239</v>
+        <v>298</v>
       </c>
       <c r="X1" s="15"/>
       <c r="Y1" s="15"/>
@@ -4771,82 +5700,82 @@
         <v>5</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>240</v>
+        <v>299</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>189</v>
+        <v>248</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>241</v>
+        <v>300</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>242</v>
+        <v>301</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>243</v>
+        <v>302</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>244</v>
+        <v>303</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>245</v>
+        <v>304</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>246</v>
+        <v>305</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>247</v>
+        <v>306</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>248</v>
+        <v>307</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>249</v>
+        <v>308</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>250</v>
+        <v>309</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>251</v>
+        <v>310</v>
       </c>
       <c r="O2" s="5" t="s">
-        <v>252</v>
+        <v>311</v>
       </c>
       <c r="P2" s="5" t="s">
-        <v>253</v>
+        <v>312</v>
       </c>
       <c r="Q2" s="5" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="R2" s="16" t="s">
-        <v>255</v>
+        <v>314</v>
       </c>
       <c r="S2" s="5" t="s">
-        <v>256</v>
+        <v>315</v>
       </c>
       <c r="T2" s="5" t="s">
-        <v>209</v>
+        <v>268</v>
       </c>
       <c r="U2" s="5" t="s">
-        <v>212</v>
+        <v>271</v>
       </c>
       <c r="V2" s="5" t="s">
-        <v>257</v>
+        <v>316</v>
       </c>
       <c r="W2" s="17" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="X2" s="18" t="s">
-        <v>258</v>
+        <v>317</v>
       </c>
       <c r="Y2" s="32" t="s">
-        <v>259</v>
+        <v>318</v>
       </c>
       <c r="Z2" s="32" t="s">
-        <v>260</v>
+        <v>319</v>
       </c>
       <c r="AA2" s="33" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
     </row>
     <row r="3" ht="14.25" spans="1:27">
@@ -4937,7 +5866,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>262</v>
+        <v>321</v>
       </c>
       <c r="C4" s="9">
         <v>10</v>
@@ -4992,17 +5921,17 @@
       <c r="U4" s="9"/>
       <c r="V4" s="9"/>
       <c r="W4" s="23"/>
-      <c r="X4" s="55" t="s">
-        <v>263</v>
+      <c r="X4" s="57" t="s">
+        <v>322</v>
       </c>
       <c r="Y4" s="9" t="s">
-        <v>264</v>
+        <v>323</v>
       </c>
       <c r="Z4" s="9" t="s">
-        <v>265</v>
+        <v>324</v>
       </c>
       <c r="AA4" s="23" t="s">
-        <v>266</v>
+        <v>325</v>
       </c>
     </row>
     <row r="5" spans="1:27">
@@ -5010,7 +5939,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>267</v>
+        <v>326</v>
       </c>
       <c r="C5" s="1">
         <v>10</v>
@@ -5066,16 +5995,16 @@
       <c r="V5" s="1"/>
       <c r="W5" s="26"/>
       <c r="X5" s="27" t="s">
-        <v>268</v>
+        <v>327</v>
       </c>
       <c r="Y5" s="1" t="s">
-        <v>264</v>
+        <v>323</v>
       </c>
       <c r="Z5" s="1" t="s">
-        <v>269</v>
+        <v>328</v>
       </c>
       <c r="AA5" s="26" t="s">
-        <v>244</v>
+        <v>303</v>
       </c>
     </row>
     <row r="6" spans="1:27">
@@ -5083,7 +6012,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>270</v>
+        <v>329</v>
       </c>
       <c r="C6" s="1">
         <v>10</v>
@@ -5139,16 +6068,16 @@
       <c r="V6" s="1"/>
       <c r="W6" s="26"/>
       <c r="X6" s="27" t="s">
-        <v>271</v>
+        <v>330</v>
       </c>
       <c r="Y6" s="1" t="s">
-        <v>264</v>
+        <v>323</v>
       </c>
       <c r="Z6" s="1" t="s">
-        <v>272</v>
+        <v>331</v>
       </c>
       <c r="AA6" s="26" t="s">
-        <v>273</v>
+        <v>332</v>
       </c>
     </row>
     <row r="7" spans="1:27">
@@ -5156,7 +6085,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>274</v>
+        <v>333</v>
       </c>
       <c r="C7" s="1">
         <v>10</v>
@@ -5212,16 +6141,16 @@
       <c r="V7" s="1"/>
       <c r="W7" s="26"/>
       <c r="X7" s="27" t="s">
-        <v>275</v>
+        <v>334</v>
       </c>
       <c r="Y7" s="1" t="s">
-        <v>264</v>
+        <v>323</v>
       </c>
       <c r="Z7" s="1" t="s">
-        <v>276</v>
+        <v>335</v>
       </c>
       <c r="AA7" s="26" t="s">
-        <v>277</v>
+        <v>336</v>
       </c>
     </row>
     <row r="8" spans="1:27">
@@ -5229,7 +6158,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>278</v>
+        <v>337</v>
       </c>
       <c r="C8" s="1">
         <v>10</v>
@@ -5285,16 +6214,16 @@
       <c r="V8" s="1"/>
       <c r="W8" s="26"/>
       <c r="X8" s="27" t="s">
-        <v>279</v>
+        <v>338</v>
       </c>
       <c r="Y8" s="1" t="s">
-        <v>264</v>
+        <v>323</v>
       </c>
       <c r="Z8" s="1" t="s">
-        <v>280</v>
+        <v>339</v>
       </c>
       <c r="AA8" s="26" t="s">
-        <v>281</v>
+        <v>340</v>
       </c>
     </row>
     <row r="9" spans="1:27">
@@ -5302,7 +6231,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>282</v>
+        <v>341</v>
       </c>
       <c r="C9" s="1">
         <v>10</v>
@@ -5358,16 +6287,16 @@
       <c r="V9" s="1"/>
       <c r="W9" s="26"/>
       <c r="X9" s="27" t="s">
-        <v>283</v>
+        <v>342</v>
       </c>
       <c r="Y9" s="1" t="s">
-        <v>284</v>
+        <v>343</v>
       </c>
       <c r="Z9" s="1" t="s">
-        <v>285</v>
+        <v>344</v>
       </c>
       <c r="AA9" s="26" t="s">
-        <v>286</v>
+        <v>345</v>
       </c>
     </row>
     <row r="10" spans="1:27">
@@ -5375,7 +6304,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>287</v>
+        <v>346</v>
       </c>
       <c r="C10" s="1">
         <v>10</v>
@@ -5431,16 +6360,16 @@
       <c r="V10" s="1"/>
       <c r="W10" s="26"/>
       <c r="X10" s="27" t="s">
-        <v>288</v>
+        <v>347</v>
       </c>
       <c r="Y10" s="1" t="s">
-        <v>289</v>
+        <v>348</v>
       </c>
       <c r="Z10" s="1" t="s">
-        <v>290</v>
+        <v>349</v>
       </c>
       <c r="AA10" s="26" t="s">
-        <v>291</v>
+        <v>350</v>
       </c>
     </row>
     <row r="11" spans="1:27">
@@ -5448,7 +6377,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="C11" s="1">
         <v>10</v>
@@ -5504,16 +6433,16 @@
       <c r="V11" s="1"/>
       <c r="W11" s="26"/>
       <c r="X11" s="27" t="s">
-        <v>292</v>
+        <v>351</v>
       </c>
       <c r="Y11" s="1" t="s">
-        <v>293</v>
+        <v>352</v>
       </c>
       <c r="Z11" s="1" t="s">
-        <v>294</v>
+        <v>353</v>
       </c>
       <c r="AA11" s="26" t="s">
-        <v>295</v>
+        <v>354</v>
       </c>
     </row>
     <row r="12" spans="1:27">
@@ -5521,7 +6450,7 @@
         <v>9</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>296</v>
+        <v>355</v>
       </c>
       <c r="C12" s="1">
         <v>10</v>
@@ -5577,16 +6506,16 @@
       <c r="V12" s="1"/>
       <c r="W12" s="26"/>
       <c r="X12" s="27" t="s">
-        <v>297</v>
+        <v>356</v>
       </c>
       <c r="Y12" s="1" t="s">
-        <v>298</v>
+        <v>357</v>
       </c>
       <c r="Z12" s="1" t="s">
-        <v>299</v>
+        <v>358</v>
       </c>
       <c r="AA12" s="26" t="s">
-        <v>300</v>
+        <v>359</v>
       </c>
     </row>
     <row r="13" spans="1:27">
@@ -5594,7 +6523,7 @@
         <v>10</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>301</v>
+        <v>360</v>
       </c>
       <c r="C13" s="1">
         <v>10</v>
@@ -5650,16 +6579,16 @@
       <c r="V13" s="1"/>
       <c r="W13" s="26"/>
       <c r="X13" s="27" t="s">
-        <v>302</v>
+        <v>361</v>
       </c>
       <c r="Y13" s="1" t="s">
-        <v>293</v>
+        <v>352</v>
       </c>
       <c r="Z13" s="1" t="s">
-        <v>303</v>
+        <v>362</v>
       </c>
       <c r="AA13" s="26" t="s">
-        <v>304</v>
+        <v>363</v>
       </c>
     </row>
     <row r="14" spans="1:27">
@@ -5667,7 +6596,7 @@
         <v>11</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>305</v>
+        <v>364</v>
       </c>
       <c r="C14" s="1">
         <v>10</v>
@@ -5723,16 +6652,16 @@
       <c r="V14" s="1"/>
       <c r="W14" s="26"/>
       <c r="X14" s="27" t="s">
-        <v>306</v>
+        <v>365</v>
       </c>
       <c r="Y14" s="1" t="s">
-        <v>307</v>
+        <v>366</v>
       </c>
       <c r="Z14" s="1" t="s">
-        <v>308</v>
+        <v>367</v>
       </c>
       <c r="AA14" s="26" t="s">
-        <v>309</v>
+        <v>368</v>
       </c>
     </row>
     <row r="15" spans="1:27">
@@ -5740,7 +6669,7 @@
         <v>12</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>310</v>
+        <v>369</v>
       </c>
       <c r="C15" s="1">
         <v>10</v>
@@ -5796,16 +6725,16 @@
       <c r="V15" s="1"/>
       <c r="W15" s="26"/>
       <c r="X15" s="27" t="s">
-        <v>311</v>
+        <v>370</v>
       </c>
       <c r="Y15" s="1" t="s">
-        <v>312</v>
+        <v>371</v>
       </c>
       <c r="Z15" s="1" t="s">
-        <v>313</v>
+        <v>372</v>
       </c>
       <c r="AA15" s="26" t="s">
-        <v>266</v>
+        <v>325</v>
       </c>
     </row>
     <row r="16" spans="1:27">
@@ -5813,7 +6742,7 @@
         <v>13</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>314</v>
+        <v>373</v>
       </c>
       <c r="C16" s="1">
         <v>10</v>
@@ -5869,16 +6798,16 @@
       <c r="V16" s="1"/>
       <c r="W16" s="26"/>
       <c r="X16" s="27" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="Y16" s="1" t="s">
-        <v>316</v>
+        <v>375</v>
       </c>
       <c r="Z16" s="1" t="s">
-        <v>317</v>
+        <v>376</v>
       </c>
       <c r="AA16" s="26" t="s">
-        <v>266</v>
+        <v>325</v>
       </c>
     </row>
     <row r="17" spans="1:27">
@@ -5886,7 +6815,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>318</v>
+        <v>377</v>
       </c>
       <c r="C17" s="1">
         <v>10</v>
@@ -5942,16 +6871,16 @@
       <c r="V17" s="1"/>
       <c r="W17" s="26"/>
       <c r="X17" s="27" t="s">
-        <v>319</v>
+        <v>378</v>
       </c>
       <c r="Y17" s="1" t="s">
-        <v>320</v>
+        <v>379</v>
       </c>
       <c r="Z17" s="1" t="s">
-        <v>321</v>
+        <v>380</v>
       </c>
       <c r="AA17" s="26" t="s">
-        <v>322</v>
+        <v>381</v>
       </c>
     </row>
     <row r="18" spans="1:27">
@@ -5959,7 +6888,7 @@
         <v>15</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>323</v>
+        <v>382</v>
       </c>
       <c r="C18" s="1">
         <v>10</v>
@@ -6015,16 +6944,16 @@
       <c r="V18" s="1"/>
       <c r="W18" s="26"/>
       <c r="X18" s="27" t="s">
-        <v>324</v>
+        <v>383</v>
       </c>
       <c r="Y18" s="1" t="s">
-        <v>325</v>
+        <v>384</v>
       </c>
       <c r="Z18" s="1" t="s">
-        <v>326</v>
+        <v>385</v>
       </c>
       <c r="AA18" s="26" t="s">
-        <v>244</v>
+        <v>303</v>
       </c>
     </row>
     <row r="19" spans="1:27">
@@ -6032,7 +6961,7 @@
         <v>16</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>327</v>
+        <v>386</v>
       </c>
       <c r="C19" s="1">
         <v>10</v>
@@ -6088,16 +7017,16 @@
       <c r="V19" s="1"/>
       <c r="W19" s="26"/>
       <c r="X19" s="27" t="s">
-        <v>328</v>
+        <v>387</v>
       </c>
       <c r="Y19" s="1" t="s">
-        <v>329</v>
+        <v>388</v>
       </c>
       <c r="Z19" s="1" t="s">
-        <v>330</v>
+        <v>389</v>
       </c>
       <c r="AA19" s="26" t="s">
-        <v>266</v>
+        <v>325</v>
       </c>
     </row>
     <row r="20" spans="1:27">
@@ -6105,7 +7034,7 @@
         <v>17</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>331</v>
+        <v>390</v>
       </c>
       <c r="C20" s="1">
         <v>10</v>
@@ -6161,16 +7090,16 @@
       <c r="V20" s="1"/>
       <c r="W20" s="26"/>
       <c r="X20" s="27" t="s">
-        <v>332</v>
+        <v>391</v>
       </c>
       <c r="Y20" s="1" t="s">
-        <v>333</v>
+        <v>392</v>
       </c>
       <c r="Z20" s="1" t="s">
-        <v>334</v>
+        <v>393</v>
       </c>
       <c r="AA20" s="26" t="s">
-        <v>242</v>
+        <v>301</v>
       </c>
     </row>
     <row r="21" spans="1:27">
@@ -6178,7 +7107,7 @@
         <v>18</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>335</v>
+        <v>394</v>
       </c>
       <c r="C21" s="1">
         <v>10</v>
@@ -6234,16 +7163,16 @@
       <c r="V21" s="1"/>
       <c r="W21" s="26"/>
       <c r="X21" s="27" t="s">
-        <v>336</v>
+        <v>395</v>
       </c>
       <c r="Y21" s="1" t="s">
-        <v>337</v>
+        <v>396</v>
       </c>
       <c r="Z21" s="1" t="s">
-        <v>338</v>
+        <v>397</v>
       </c>
       <c r="AA21" s="26" t="s">
-        <v>255</v>
+        <v>314</v>
       </c>
     </row>
     <row r="22" spans="1:27">
@@ -6251,7 +7180,7 @@
         <v>19</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>339</v>
+        <v>398</v>
       </c>
       <c r="C22" s="1">
         <v>10</v>
@@ -6307,16 +7236,16 @@
       <c r="V22" s="1"/>
       <c r="W22" s="26"/>
       <c r="X22" s="27" t="s">
-        <v>340</v>
+        <v>399</v>
       </c>
       <c r="Y22" s="1" t="s">
-        <v>341</v>
+        <v>400</v>
       </c>
       <c r="Z22" s="1" t="s">
-        <v>342</v>
+        <v>401</v>
       </c>
       <c r="AA22" s="26" t="s">
-        <v>343</v>
+        <v>402</v>
       </c>
     </row>
     <row r="23" spans="1:27">
@@ -6324,7 +7253,7 @@
         <v>20</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>344</v>
+        <v>403</v>
       </c>
       <c r="C23" s="1">
         <v>10</v>
@@ -6380,16 +7309,16 @@
       <c r="V23" s="1"/>
       <c r="W23" s="26"/>
       <c r="X23" s="27" t="s">
-        <v>345</v>
+        <v>404</v>
       </c>
       <c r="Y23" s="1" t="s">
-        <v>346</v>
+        <v>405</v>
       </c>
       <c r="Z23" s="1" t="s">
-        <v>347</v>
+        <v>406</v>
       </c>
       <c r="AA23" s="26" t="s">
-        <v>348</v>
+        <v>407</v>
       </c>
     </row>
     <row r="24" spans="1:27">
@@ -6397,7 +7326,7 @@
         <v>21</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>349</v>
+        <v>408</v>
       </c>
       <c r="C24" s="1">
         <v>10</v>
@@ -6453,16 +7382,16 @@
       <c r="V24" s="1"/>
       <c r="W24" s="26"/>
       <c r="X24" s="27" t="s">
-        <v>350</v>
+        <v>409</v>
       </c>
       <c r="Y24" s="1" t="s">
-        <v>351</v>
+        <v>410</v>
       </c>
       <c r="Z24" s="1" t="s">
-        <v>352</v>
+        <v>411</v>
       </c>
       <c r="AA24" s="26" t="s">
-        <v>353</v>
+        <v>412</v>
       </c>
     </row>
     <row r="25" spans="1:27">
@@ -6470,7 +7399,7 @@
         <v>22</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>354</v>
+        <v>413</v>
       </c>
       <c r="C25" s="1">
         <v>10</v>
@@ -6526,16 +7455,16 @@
       <c r="V25" s="1"/>
       <c r="W25" s="26"/>
       <c r="X25" s="27" t="s">
-        <v>355</v>
+        <v>414</v>
       </c>
       <c r="Y25" s="1" t="s">
-        <v>356</v>
+        <v>415</v>
       </c>
       <c r="Z25" s="1" t="s">
-        <v>357</v>
+        <v>416</v>
       </c>
       <c r="AA25" s="26" t="s">
-        <v>249</v>
+        <v>308</v>
       </c>
     </row>
     <row r="26" spans="1:27">
@@ -6543,7 +7472,7 @@
         <v>23</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>358</v>
+        <v>417</v>
       </c>
       <c r="C26" s="1">
         <v>10</v>
@@ -6599,16 +7528,16 @@
       <c r="V26" s="1"/>
       <c r="W26" s="26"/>
       <c r="X26" s="27" t="s">
-        <v>359</v>
+        <v>418</v>
       </c>
       <c r="Y26" s="1" t="s">
-        <v>360</v>
+        <v>419</v>
       </c>
       <c r="Z26" s="1" t="s">
-        <v>361</v>
+        <v>420</v>
       </c>
       <c r="AA26" s="26" t="s">
-        <v>362</v>
+        <v>421</v>
       </c>
     </row>
     <row r="27" spans="1:27">
@@ -6616,7 +7545,7 @@
         <v>24</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>363</v>
+        <v>422</v>
       </c>
       <c r="C27" s="1">
         <v>10</v>
@@ -6672,16 +7601,16 @@
       <c r="V27" s="1"/>
       <c r="W27" s="26"/>
       <c r="X27" s="27" t="s">
-        <v>364</v>
+        <v>423</v>
       </c>
       <c r="Y27" s="1" t="s">
-        <v>365</v>
+        <v>424</v>
       </c>
       <c r="Z27" s="1" t="s">
-        <v>366</v>
+        <v>425</v>
       </c>
       <c r="AA27" s="26" t="s">
-        <v>367</v>
+        <v>426</v>
       </c>
     </row>
     <row r="28" spans="1:27">
@@ -6689,7 +7618,7 @@
         <v>25</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>368</v>
+        <v>427</v>
       </c>
       <c r="C28" s="1">
         <v>10</v>
@@ -6745,16 +7674,16 @@
       <c r="V28" s="1"/>
       <c r="W28" s="26"/>
       <c r="X28" s="27" t="s">
-        <v>369</v>
+        <v>428</v>
       </c>
       <c r="Y28" s="1" t="s">
-        <v>370</v>
+        <v>429</v>
       </c>
       <c r="Z28" s="1" t="s">
-        <v>371</v>
+        <v>430</v>
       </c>
       <c r="AA28" s="26" t="s">
-        <v>372</v>
+        <v>431</v>
       </c>
     </row>
     <row r="29" spans="1:27">
@@ -6762,7 +7691,7 @@
         <v>26</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>373</v>
+        <v>432</v>
       </c>
       <c r="C29" s="1">
         <v>10</v>
@@ -6818,16 +7747,16 @@
       <c r="V29" s="1"/>
       <c r="W29" s="26"/>
       <c r="X29" s="27" t="s">
-        <v>374</v>
+        <v>433</v>
       </c>
       <c r="Y29" s="1" t="s">
-        <v>375</v>
+        <v>434</v>
       </c>
       <c r="Z29" s="1" t="s">
-        <v>376</v>
+        <v>435</v>
       </c>
       <c r="AA29" s="26" t="s">
-        <v>377</v>
+        <v>436</v>
       </c>
     </row>
     <row r="30" spans="1:27">
@@ -6835,7 +7764,7 @@
         <v>27</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>378</v>
+        <v>437</v>
       </c>
       <c r="C30" s="1">
         <v>10</v>
@@ -6891,16 +7820,16 @@
       <c r="V30" s="1"/>
       <c r="W30" s="26"/>
       <c r="X30" s="27" t="s">
-        <v>379</v>
+        <v>438</v>
       </c>
       <c r="Y30" s="1" t="s">
-        <v>380</v>
+        <v>439</v>
       </c>
       <c r="Z30" s="1" t="s">
-        <v>381</v>
+        <v>440</v>
       </c>
       <c r="AA30" s="26" t="s">
-        <v>266</v>
+        <v>325</v>
       </c>
     </row>
     <row r="31" spans="1:27">
@@ -6908,7 +7837,7 @@
         <v>28</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>382</v>
+        <v>441</v>
       </c>
       <c r="C31" s="1">
         <v>10</v>
@@ -6964,16 +7893,16 @@
       <c r="V31" s="1"/>
       <c r="W31" s="26"/>
       <c r="X31" s="27" t="s">
-        <v>383</v>
+        <v>442</v>
       </c>
       <c r="Y31" s="1" t="s">
-        <v>384</v>
+        <v>443</v>
       </c>
       <c r="Z31" s="1" t="s">
-        <v>385</v>
+        <v>444</v>
       </c>
       <c r="AA31" s="26" t="s">
-        <v>266</v>
+        <v>325</v>
       </c>
     </row>
     <row r="32" spans="1:27">
@@ -6981,7 +7910,7 @@
         <v>29</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>386</v>
+        <v>445</v>
       </c>
       <c r="C32" s="1">
         <v>10</v>
@@ -7037,16 +7966,16 @@
       <c r="V32" s="1"/>
       <c r="W32" s="26"/>
       <c r="X32" s="27" t="s">
-        <v>387</v>
+        <v>446</v>
       </c>
       <c r="Y32" s="1" t="s">
-        <v>388</v>
+        <v>447</v>
       </c>
       <c r="Z32" s="1" t="s">
-        <v>389</v>
+        <v>448</v>
       </c>
       <c r="AA32" s="26" t="s">
-        <v>390</v>
+        <v>449</v>
       </c>
     </row>
     <row r="33" spans="1:27">
@@ -7054,7 +7983,7 @@
         <v>30</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>391</v>
+        <v>450</v>
       </c>
       <c r="C33" s="1">
         <v>10</v>
@@ -7110,16 +8039,16 @@
       <c r="V33" s="1"/>
       <c r="W33" s="26"/>
       <c r="X33" s="27" t="s">
-        <v>392</v>
+        <v>451</v>
       </c>
       <c r="Y33" s="1" t="s">
-        <v>393</v>
+        <v>452</v>
       </c>
       <c r="Z33" s="1" t="s">
-        <v>394</v>
+        <v>453</v>
       </c>
       <c r="AA33" s="26" t="s">
-        <v>395</v>
+        <v>454</v>
       </c>
     </row>
     <row r="34" spans="1:27">
@@ -7127,7 +8056,7 @@
         <v>31</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>396</v>
+        <v>455</v>
       </c>
       <c r="C34" s="1">
         <v>10</v>
@@ -7183,16 +8112,16 @@
       <c r="V34" s="1"/>
       <c r="W34" s="26"/>
       <c r="X34" s="27" t="s">
-        <v>397</v>
+        <v>456</v>
       </c>
       <c r="Y34" s="1" t="s">
-        <v>398</v>
+        <v>457</v>
       </c>
       <c r="Z34" s="1" t="s">
-        <v>399</v>
+        <v>458</v>
       </c>
       <c r="AA34" s="26" t="s">
-        <v>266</v>
+        <v>325</v>
       </c>
     </row>
     <row r="35" spans="1:27">
@@ -7200,7 +8129,7 @@
         <v>32</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>400</v>
+        <v>459</v>
       </c>
       <c r="C35" s="1">
         <v>10</v>
@@ -7256,16 +8185,16 @@
       <c r="V35" s="1"/>
       <c r="W35" s="26"/>
       <c r="X35" s="27" t="s">
-        <v>401</v>
+        <v>460</v>
       </c>
       <c r="Y35" s="1" t="s">
-        <v>402</v>
+        <v>461</v>
       </c>
       <c r="Z35" s="1" t="s">
-        <v>403</v>
+        <v>462</v>
       </c>
       <c r="AA35" s="26" t="s">
-        <v>404</v>
+        <v>463</v>
       </c>
     </row>
     <row r="36" spans="1:27">
@@ -7273,7 +8202,7 @@
         <v>33</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>405</v>
+        <v>464</v>
       </c>
       <c r="C36" s="1">
         <v>10</v>
@@ -7329,16 +8258,16 @@
       <c r="V36" s="1"/>
       <c r="W36" s="26"/>
       <c r="X36" s="27" t="s">
-        <v>406</v>
+        <v>465</v>
       </c>
       <c r="Y36" s="1" t="s">
-        <v>407</v>
+        <v>466</v>
       </c>
       <c r="Z36" s="1" t="s">
-        <v>408</v>
+        <v>467</v>
       </c>
       <c r="AA36" s="26" t="s">
-        <v>409</v>
+        <v>468</v>
       </c>
     </row>
     <row r="37" spans="1:27">
@@ -7346,7 +8275,7 @@
         <v>34</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>410</v>
+        <v>469</v>
       </c>
       <c r="C37" s="1">
         <v>10</v>
@@ -7402,16 +8331,16 @@
       <c r="V37" s="1"/>
       <c r="W37" s="26"/>
       <c r="X37" s="27" t="s">
-        <v>411</v>
+        <v>470</v>
       </c>
       <c r="Y37" s="1" t="s">
-        <v>412</v>
+        <v>471</v>
       </c>
       <c r="Z37" s="1" t="s">
-        <v>413</v>
+        <v>472</v>
       </c>
       <c r="AA37" s="26" t="s">
-        <v>414</v>
+        <v>473</v>
       </c>
     </row>
     <row r="38" spans="1:27">
@@ -7419,7 +8348,7 @@
         <v>35</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>415</v>
+        <v>474</v>
       </c>
       <c r="C38" s="1">
         <v>10</v>
@@ -7475,16 +8404,16 @@
       <c r="V38" s="1"/>
       <c r="W38" s="26"/>
       <c r="X38" s="27" t="s">
-        <v>416</v>
+        <v>475</v>
       </c>
       <c r="Y38" s="1" t="s">
-        <v>417</v>
+        <v>476</v>
       </c>
       <c r="Z38" s="1" t="s">
-        <v>418</v>
+        <v>477</v>
       </c>
       <c r="AA38" s="26" t="s">
-        <v>419</v>
+        <v>478</v>
       </c>
     </row>
     <row r="39" spans="1:27">
@@ -7492,7 +8421,7 @@
         <v>36</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>420</v>
+        <v>479</v>
       </c>
       <c r="C39" s="1">
         <v>10</v>
@@ -7548,16 +8477,16 @@
       <c r="V39" s="1"/>
       <c r="W39" s="26"/>
       <c r="X39" s="27" t="s">
-        <v>421</v>
+        <v>480</v>
       </c>
       <c r="Y39" s="1" t="s">
-        <v>422</v>
+        <v>481</v>
       </c>
       <c r="Z39" s="1" t="s">
-        <v>423</v>
+        <v>482</v>
       </c>
       <c r="AA39" s="26" t="s">
-        <v>424</v>
+        <v>483</v>
       </c>
     </row>
     <row r="40" spans="1:27">
@@ -7565,7 +8494,7 @@
         <v>37</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>425</v>
+        <v>484</v>
       </c>
       <c r="C40" s="1">
         <v>10</v>
@@ -7621,16 +8550,16 @@
       <c r="V40" s="1"/>
       <c r="W40" s="26"/>
       <c r="X40" s="27" t="s">
-        <v>426</v>
+        <v>485</v>
       </c>
       <c r="Y40" s="1" t="s">
-        <v>427</v>
+        <v>486</v>
       </c>
       <c r="Z40" s="1" t="s">
-        <v>428</v>
+        <v>487</v>
       </c>
       <c r="AA40" s="26" t="s">
-        <v>251</v>
+        <v>310</v>
       </c>
     </row>
     <row r="41" ht="14.25" spans="1:27">
@@ -7638,7 +8567,7 @@
         <v>38</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>429</v>
+        <v>488</v>
       </c>
       <c r="C41" s="12">
         <v>10</v>
@@ -7694,16 +8623,16 @@
       <c r="V41" s="12"/>
       <c r="W41" s="29"/>
       <c r="X41" s="30" t="s">
-        <v>430</v>
+        <v>489</v>
       </c>
       <c r="Y41" s="12" t="s">
-        <v>431</v>
+        <v>490</v>
       </c>
       <c r="Z41" s="12" t="s">
-        <v>432</v>
+        <v>491</v>
       </c>
       <c r="AA41" s="29" t="s">
-        <v>266</v>
+        <v>325</v>
       </c>
     </row>
   </sheetData>

--- a/xlsdir/配置-总表.xlsx
+++ b/xlsdir/配置-总表.xlsx
@@ -4,15 +4,15 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="673" firstSheet="3" activeTab="4"/>
+    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="673" firstSheet="3" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="character|角色" sheetId="32" r:id="rId1"/>
     <sheet name="combat|战斗" sheetId="31" r:id="rId2"/>
     <sheet name="hero|玩家角色" sheetId="27" r:id="rId3"/>
     <sheet name="monster|魔物" sheetId="28" r:id="rId4"/>
-    <sheet name="intent|意图" sheetId="38" r:id="rId5"/>
-    <sheet name="card|卡牌" sheetId="29" r:id="rId6"/>
+    <sheet name="card|卡牌" sheetId="29" r:id="rId5"/>
+    <sheet name="intent|意图" sheetId="38" r:id="rId6"/>
     <sheet name="ability_effect|技能效果" sheetId="34" r:id="rId7"/>
     <sheet name="attribute|属性" sheetId="35" r:id="rId8"/>
     <sheet name="Sheet1" sheetId="11" r:id="rId9"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="709" uniqueCount="504">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="781" uniqueCount="515">
   <si>
     <t>ID</t>
   </si>
@@ -209,304 +209,19 @@
     <t>heavy_strike*bone_shield*summon_assistance</t>
   </si>
   <si>
-    <t>owner</t>
-  </si>
-  <si>
-    <t>type</t>
-  </si>
-  <si>
-    <t>weight</t>
-  </si>
-  <si>
-    <t>cooldown</t>
-  </si>
-  <si>
-    <t>des</t>
+    <t>card_name</t>
+  </si>
+  <si>
+    <t>card_type</t>
+  </si>
+  <si>
+    <t>cost</t>
+  </si>
+  <si>
+    <t>card_description</t>
   </si>
   <si>
     <t>icon</t>
-  </si>
-  <si>
-    <t>value</t>
-  </si>
-  <si>
-    <t>func</t>
-  </si>
-  <si>
-    <t>所属(注释）</t>
-  </si>
-  <si>
-    <t>意图名</t>
-  </si>
-  <si>
-    <t>意图类型</t>
-  </si>
-  <si>
-    <t>权重</t>
-  </si>
-  <si>
-    <t>冷却</t>
-  </si>
-  <si>
-    <t>意图描述</t>
-  </si>
-  <si>
-    <t>意图图标</t>
-  </si>
-  <si>
-    <t>意图值</t>
-  </si>
-  <si>
-    <t>意图方法</t>
-  </si>
-  <si>
-    <t>float</t>
-  </si>
-  <si>
-    <t>texture</t>
-  </si>
-  <si>
-    <t>ATTACK</t>
-  </si>
-  <si>
-    <t>攻击</t>
-  </si>
-  <si>
-    <t>敌人打算进行攻击。</t>
-  </si>
-  <si>
-    <t>res://asserts/textures/widgets/Spells/poison_dagger.png</t>
-  </si>
-  <si>
-    <t>MULTI_ATTACK</t>
-  </si>
-  <si>
-    <t>多重攻击</t>
-  </si>
-  <si>
-    <t>敌人计划多次攻击。</t>
-  </si>
-  <si>
-    <t>res://asserts/textures/widgets/Spells/thorn_vine_spell.png</t>
-  </si>
-  <si>
-    <t>DEFEND</t>
-  </si>
-  <si>
-    <t>防御</t>
-  </si>
-  <si>
-    <t>敌人将增加防御力</t>
-  </si>
-  <si>
-    <t>res://asserts/textures/widgets/Spells/healing_spell.png</t>
-  </si>
-  <si>
-    <t>BUFF</t>
-  </si>
-  <si>
-    <t>强化</t>
-  </si>
-  <si>
-    <t>敌人将提升某项能力，如攻击力、防御力或特殊能力。</t>
-  </si>
-  <si>
-    <t>res://asserts/textures/widgets/Debuffs/on_fire_(burning).png</t>
-  </si>
-  <si>
-    <t>DEBUFF</t>
-  </si>
-  <si>
-    <t>弱化</t>
-  </si>
-  <si>
-    <t>敌人计划施放会削弱玩家能力的效果，如减少玩家的攻击力或防御力。</t>
-  </si>
-  <si>
-    <t>res://asserts/textures/widgets/Debuffs/disarmed.png</t>
-  </si>
-  <si>
-    <t>HEAL</t>
-  </si>
-  <si>
-    <t>治疗</t>
-  </si>
-  <si>
-    <t>敌人会恢复一定量的生命值。</t>
-  </si>
-  <si>
-    <t>res://asserts/textures/widgets/Buffs/lucky_boost.png</t>
-  </si>
-  <si>
-    <t>STRATEGY</t>
-  </si>
-  <si>
-    <t>策略</t>
-  </si>
-  <si>
-    <t>敌人将采取某种特殊行动，如召唤援助、准备强力攻击或其他战术动作。</t>
-  </si>
-  <si>
-    <t>res://asserts/textures/widgets/Debuffs/confused.png</t>
-  </si>
-  <si>
-    <t>ESCAPE</t>
-  </si>
-  <si>
-    <t>逃跑</t>
-  </si>
-  <si>
-    <t>在某些战斗中，敌人可能会试图逃跑，尤其是在遭遇战中</t>
-  </si>
-  <si>
-    <t>res://asserts/textures/widgets/Buffs/swiftness.png</t>
-  </si>
-  <si>
-    <t>split</t>
-  </si>
-  <si>
-    <t>分裂</t>
-  </si>
-  <si>
-    <t>史莱姆分裂成两个较小的实体，增加战斗中的敌人数量。</t>
-  </si>
-  <si>
-    <t>absorb</t>
-  </si>
-  <si>
-    <t>吸收</t>
-  </si>
-  <si>
-    <t>回复一定量的生命值，吸收的量取决于其当前生命值。</t>
-  </si>
-  <si>
-    <t>entangle</t>
-  </si>
-  <si>
-    <t>缠绕</t>
-  </si>
-  <si>
-    <t>降低玩家下一回合的行动点数。</t>
-  </si>
-  <si>
-    <t>destruction_ray</t>
-  </si>
-  <si>
-    <t>破坏射线</t>
-  </si>
-  <si>
-    <t>对玩家造成魔法伤害。</t>
-  </si>
-  <si>
-    <t>curse_gaze</t>
-  </si>
-  <si>
-    <t>诅咒凝视</t>
-  </si>
-  <si>
-    <t>使玩家在下一回合内受到的伤害增加。</t>
-  </si>
-  <si>
-    <t>magic_shield</t>
-  </si>
-  <si>
-    <t>魔法护盾</t>
-  </si>
-  <si>
-    <t>为自己添加一层护盾，抵挡一定量的伤害。</t>
-  </si>
-  <si>
-    <t>sprint_stab</t>
-  </si>
-  <si>
-    <t>疾跑刺击</t>
-  </si>
-  <si>
-    <t>快速冲刺并对玩家造成物理伤害。</t>
-  </si>
-  <si>
-    <t>set_trap</t>
-  </si>
-  <si>
-    <t>布置陷阱</t>
-  </si>
-  <si>
-    <t>下一回合对玩家造成额外伤害。</t>
-  </si>
-  <si>
-    <t>sneak_attack</t>
-  </si>
-  <si>
-    <t>偷袭</t>
-  </si>
-  <si>
-    <t>如果玩家生命值低，造成额外伤害。</t>
-  </si>
-  <si>
-    <t>toxin_spray</t>
-  </si>
-  <si>
-    <t>毒素喷射</t>
-  </si>
-  <si>
-    <t>造成持续性的毒素伤害。</t>
-  </si>
-  <si>
-    <t>healing_spore</t>
-  </si>
-  <si>
-    <t>治疗孢子</t>
-  </si>
-  <si>
-    <t>为自己或其他敌人恢复生命值。</t>
-  </si>
-  <si>
-    <t>hallucinogenic_spore</t>
-  </si>
-  <si>
-    <t>迷幻孢子</t>
-  </si>
-  <si>
-    <t>使玩家在下一回合内混乱，随机选择行动。</t>
-  </si>
-  <si>
-    <t>heavy_strike</t>
-  </si>
-  <si>
-    <t>重击</t>
-  </si>
-  <si>
-    <t>用锋利的武器对玩家造成大量伤害。</t>
-  </si>
-  <si>
-    <t>bone_shield</t>
-  </si>
-  <si>
-    <t>骨盾</t>
-  </si>
-  <si>
-    <t>提高自己的防御力，减少受到的伤害。</t>
-  </si>
-  <si>
-    <t>summon_assistance</t>
-  </si>
-  <si>
-    <t>召唤援助</t>
-  </si>
-  <si>
-    <t>召唤另一个骷髅怪加入战斗</t>
-  </si>
-  <si>
-    <t>card_name</t>
-  </si>
-  <si>
-    <t>card_type</t>
-  </si>
-  <si>
-    <t>cost</t>
-  </si>
-  <si>
-    <t>card_description</t>
   </si>
   <si>
     <t>target_type</t>
@@ -547,6 +262,9 @@
     <t>效果ID列表</t>
   </si>
   <si>
+    <t>texture</t>
+  </si>
+  <si>
     <t>strike</t>
   </si>
   <si>
@@ -565,6 +283,9 @@
     <t>defense</t>
   </si>
   <si>
+    <t>防御</t>
+  </si>
+  <si>
     <t>获得5点护甲</t>
   </si>
   <si>
@@ -590,6 +311,282 @@
   </si>
   <si>
     <t>trounce_01*trounce_02</t>
+  </si>
+  <si>
+    <t>owner</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>weight</t>
+  </si>
+  <si>
+    <t>cooldown</t>
+  </si>
+  <si>
+    <t>des</t>
+  </si>
+  <si>
+    <t>value</t>
+  </si>
+  <si>
+    <t>func</t>
+  </si>
+  <si>
+    <t>所属(注释）</t>
+  </si>
+  <si>
+    <t>意图名</t>
+  </si>
+  <si>
+    <t>意图类型</t>
+  </si>
+  <si>
+    <t>权重</t>
+  </si>
+  <si>
+    <t>冷却</t>
+  </si>
+  <si>
+    <t>意图描述</t>
+  </si>
+  <si>
+    <t>意图图标</t>
+  </si>
+  <si>
+    <t>意图值</t>
+  </si>
+  <si>
+    <t>意图方法</t>
+  </si>
+  <si>
+    <t>float</t>
+  </si>
+  <si>
+    <t>ATTACK</t>
+  </si>
+  <si>
+    <t>攻击</t>
+  </si>
+  <si>
+    <t>敌人打算进行攻击。</t>
+  </si>
+  <si>
+    <t>res://asserts/textures/widgets/Spells/poison_dagger.png</t>
+  </si>
+  <si>
+    <t>MULTI_ATTACK</t>
+  </si>
+  <si>
+    <t>多重攻击</t>
+  </si>
+  <si>
+    <t>敌人计划多次攻击。</t>
+  </si>
+  <si>
+    <t>res://asserts/textures/widgets/Spells/thorn_vine_spell.png</t>
+  </si>
+  <si>
+    <t>DEFEND</t>
+  </si>
+  <si>
+    <t>敌人将增加防御力</t>
+  </si>
+  <si>
+    <t>res://asserts/textures/widgets/Spells/healing_spell.png</t>
+  </si>
+  <si>
+    <t>BUFF</t>
+  </si>
+  <si>
+    <t>强化</t>
+  </si>
+  <si>
+    <t>敌人将提升某项能力，如攻击力、防御力或特殊能力。</t>
+  </si>
+  <si>
+    <t>res://asserts/textures/widgets/Debuffs/on_fire_(burning).png</t>
+  </si>
+  <si>
+    <t>DEBUFF</t>
+  </si>
+  <si>
+    <t>弱化</t>
+  </si>
+  <si>
+    <t>敌人计划施放会削弱玩家能力的效果，如减少玩家的攻击力或防御力。</t>
+  </si>
+  <si>
+    <t>res://asserts/textures/widgets/Debuffs/disarmed.png</t>
+  </si>
+  <si>
+    <t>HEAL</t>
+  </si>
+  <si>
+    <t>治疗</t>
+  </si>
+  <si>
+    <t>敌人会恢复一定量的生命值。</t>
+  </si>
+  <si>
+    <t>res://asserts/textures/widgets/Buffs/lucky_boost.png</t>
+  </si>
+  <si>
+    <t>STRATEGY</t>
+  </si>
+  <si>
+    <t>策略</t>
+  </si>
+  <si>
+    <t>敌人将采取某种特殊行动，如召唤援助、准备强力攻击或其他战术动作。</t>
+  </si>
+  <si>
+    <t>res://asserts/textures/widgets/Debuffs/confused.png</t>
+  </si>
+  <si>
+    <t>ESCAPE</t>
+  </si>
+  <si>
+    <t>逃跑</t>
+  </si>
+  <si>
+    <t>在某些战斗中，敌人可能会试图逃跑，尤其是在遭遇战中</t>
+  </si>
+  <si>
+    <t>res://asserts/textures/widgets/Buffs/swiftness.png</t>
+  </si>
+  <si>
+    <t>split</t>
+  </si>
+  <si>
+    <t>分裂</t>
+  </si>
+  <si>
+    <t>史莱姆分裂成两个较小的实体，增加战斗中的敌人数量。</t>
+  </si>
+  <si>
+    <t>absorb</t>
+  </si>
+  <si>
+    <t>吸收</t>
+  </si>
+  <si>
+    <t>回复一定量的生命值，吸收的量取决于其当前生命值。</t>
+  </si>
+  <si>
+    <t>entangle</t>
+  </si>
+  <si>
+    <t>缠绕</t>
+  </si>
+  <si>
+    <t>降低玩家下一回合的行动点数。</t>
+  </si>
+  <si>
+    <t>destruction_ray</t>
+  </si>
+  <si>
+    <t>破坏射线</t>
+  </si>
+  <si>
+    <t>对玩家造成魔法伤害。</t>
+  </si>
+  <si>
+    <t>curse_gaze</t>
+  </si>
+  <si>
+    <t>诅咒凝视</t>
+  </si>
+  <si>
+    <t>使玩家在下一回合内受到的伤害增加。</t>
+  </si>
+  <si>
+    <t>magic_shield</t>
+  </si>
+  <si>
+    <t>魔法护盾</t>
+  </si>
+  <si>
+    <t>为自己添加一层护盾，抵挡一定量的伤害。</t>
+  </si>
+  <si>
+    <t>sprint_stab</t>
+  </si>
+  <si>
+    <t>疾跑刺击</t>
+  </si>
+  <si>
+    <t>快速冲刺并对玩家造成物理伤害。</t>
+  </si>
+  <si>
+    <t>set_trap</t>
+  </si>
+  <si>
+    <t>布置陷阱</t>
+  </si>
+  <si>
+    <t>下一回合对玩家造成额外伤害。</t>
+  </si>
+  <si>
+    <t>sneak_attack</t>
+  </si>
+  <si>
+    <t>偷袭</t>
+  </si>
+  <si>
+    <t>如果玩家生命值低，造成额外伤害。</t>
+  </si>
+  <si>
+    <t>toxin_spray</t>
+  </si>
+  <si>
+    <t>毒素喷射</t>
+  </si>
+  <si>
+    <t>造成持续性的毒素伤害。</t>
+  </si>
+  <si>
+    <t>healing_spore</t>
+  </si>
+  <si>
+    <t>治疗孢子</t>
+  </si>
+  <si>
+    <t>为自己或其他敌人恢复生命值。</t>
+  </si>
+  <si>
+    <t>hallucinogenic_spore</t>
+  </si>
+  <si>
+    <t>迷幻孢子</t>
+  </si>
+  <si>
+    <t>玩家获得“混乱”卡牌。</t>
+  </si>
+  <si>
+    <t>heavy_strike</t>
+  </si>
+  <si>
+    <t>重击</t>
+  </si>
+  <si>
+    <t>用锋利的武器对玩家造成大量伤害。</t>
+  </si>
+  <si>
+    <t>bone_shield</t>
+  </si>
+  <si>
+    <t>骨盾</t>
+  </si>
+  <si>
+    <t>summon_assistance</t>
+  </si>
+  <si>
+    <t>召唤援助</t>
+  </si>
+  <si>
+    <t>召唤另一个骷髅怪加入战斗</t>
   </si>
   <si>
     <t>注释</t>
@@ -764,6 +761,45 @@
     <t>目标在下一回合无法行动。</t>
   </si>
   <si>
+    <t>恢复</t>
+  </si>
+  <si>
+    <t>减少玩家下一回合的行动点数。</t>
+  </si>
+  <si>
+    <t>减少行动点数</t>
+  </si>
+  <si>
+    <t>对玩家造成10点伤害</t>
+  </si>
+  <si>
+    <t>伤害</t>
+  </si>
+  <si>
+    <t>获得护盾</t>
+  </si>
+  <si>
+    <t>对玩家造成12点伤害</t>
+  </si>
+  <si>
+    <t>蓄力一回合，下一回合对玩家造成双倍伤害</t>
+  </si>
+  <si>
+    <t>蓄力</t>
+  </si>
+  <si>
+    <t>放毒</t>
+  </si>
+  <si>
+    <t>所有人恢复10点生命值。</t>
+  </si>
+  <si>
+    <t>给与卡牌</t>
+  </si>
+  <si>
+    <t>造成15点伤害</t>
+  </si>
+  <si>
     <t>Name</t>
   </si>
   <si>
@@ -963,9 +999,6 @@
   </si>
   <si>
     <t>生命窃取</t>
-  </si>
-  <si>
-    <t>伤害</t>
   </si>
   <si>
     <t>近战伤害</t>
@@ -1687,7 +1720,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1722,6 +1755,13 @@
       <color rgb="FF374151"/>
       <name val="Segoe UI"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -1868,7 +1908,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1884,6 +1924,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.25"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2542,76 +2594,70 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="27" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="27" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="30" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="30" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="32" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="33" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="34" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="30" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="30" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="32" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="33" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="34" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2620,10 +2666,10 @@
     <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2632,10 +2678,10 @@
     <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2644,10 +2690,10 @@
     <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2656,10 +2702,10 @@
     <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2668,11 +2714,17 @@
     <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2796,47 +2848,71 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -3219,13 +3295,13 @@
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="41" t="s">
+      <c r="A2" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="41" t="s">
+      <c r="C2" s="42" t="s">
         <v>7</v>
       </c>
       <c r="D2" s="5" t="s">
@@ -3287,10 +3363,10 @@
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="52" t="s">
+      <c r="A6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="54" t="s">
+      <c r="B6" s="40" t="s">
         <v>18</v>
       </c>
       <c r="C6" s="1">
@@ -3304,10 +3380,10 @@
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="52" t="s">
+      <c r="A7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="54" t="s">
+      <c r="B7" s="40" t="s">
         <v>21</v>
       </c>
       <c r="C7" s="1">
@@ -3321,10 +3397,10 @@
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="52" t="s">
+      <c r="A8" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="54" t="s">
+      <c r="B8" s="40" t="s">
         <v>24</v>
       </c>
       <c r="C8" s="1">
@@ -3338,10 +3414,10 @@
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="52" t="s">
+      <c r="A9" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="54" t="s">
+      <c r="B9" s="40" t="s">
         <v>27</v>
       </c>
       <c r="C9" s="1">
@@ -3368,7 +3444,7 @@
   <sheetData>
     <row r="7" spans="3:5">
       <c r="C7" s="1" t="s">
-        <v>167</v>
+        <v>73</v>
       </c>
       <c r="D7">
         <v>5</v>
@@ -3380,7 +3456,7 @@
     </row>
     <row r="8" spans="3:6">
       <c r="C8" s="1" t="s">
-        <v>172</v>
+        <v>78</v>
       </c>
       <c r="D8">
         <v>4</v>
@@ -3396,7 +3472,7 @@
     </row>
     <row r="9" spans="3:6">
       <c r="C9" s="1" t="s">
-        <v>177</v>
+        <v>84</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -3415,7 +3491,7 @@
         <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>492</v>
+        <v>503</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -3423,7 +3499,7 @@
         <v>2</v>
       </c>
       <c r="B13" t="s">
-        <v>493</v>
+        <v>504</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -3431,7 +3507,7 @@
         <v>3</v>
       </c>
       <c r="B14" t="s">
-        <v>494</v>
+        <v>505</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -3439,16 +3515,16 @@
         <v>4</v>
       </c>
       <c r="B15" t="s">
-        <v>495</v>
+        <v>506</v>
       </c>
       <c r="F15" t="s">
-        <v>107</v>
+        <v>137</v>
       </c>
       <c r="H15" t="s">
-        <v>107</v>
+        <v>137</v>
       </c>
       <c r="I15" t="s">
-        <v>496</v>
+        <v>507</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -3456,16 +3532,16 @@
         <v>5</v>
       </c>
       <c r="B16" t="s">
-        <v>497</v>
+        <v>508</v>
       </c>
       <c r="F16" t="s">
-        <v>496</v>
+        <v>507</v>
       </c>
       <c r="H16" t="s">
-        <v>116</v>
+        <v>146</v>
       </c>
       <c r="I16" t="s">
-        <v>498</v>
+        <v>509</v>
       </c>
     </row>
     <row r="17" spans="6:9">
@@ -3473,35 +3549,35 @@
         <v>51</v>
       </c>
       <c r="H17" t="s">
-        <v>125</v>
+        <v>155</v>
       </c>
       <c r="I17" t="s">
-        <v>499</v>
+        <v>510</v>
       </c>
     </row>
     <row r="18" spans="2:9">
       <c r="B18" t="s">
-        <v>500</v>
+        <v>511</v>
       </c>
       <c r="F18" t="s">
-        <v>116</v>
+        <v>146</v>
       </c>
       <c r="H18" t="s">
-        <v>134</v>
+        <v>164</v>
       </c>
       <c r="I18" t="s">
-        <v>501</v>
+        <v>512</v>
       </c>
     </row>
     <row r="19" spans="6:9">
       <c r="F19" t="s">
-        <v>498</v>
+        <v>509</v>
       </c>
       <c r="H19" t="s">
-        <v>143</v>
+        <v>173</v>
       </c>
       <c r="I19" t="s">
-        <v>502</v>
+        <v>513</v>
       </c>
     </row>
     <row r="20" spans="6:8">
@@ -3515,7 +3591,7 @@
     </row>
     <row r="21" spans="6:8">
       <c r="F21" t="s">
-        <v>125</v>
+        <v>155</v>
       </c>
       <c r="H21">
         <f>IF('intent|意图'!F18='intent|意图'!F17,H20&amp;"*"&amp;'intent|意图'!D18,'intent|意图'!D18)</f>
@@ -3524,7 +3600,7 @@
     </row>
     <row r="22" spans="6:8">
       <c r="F22" t="s">
-        <v>499</v>
+        <v>510</v>
       </c>
       <c r="H22">
         <f>IF('intent|意图'!F19='intent|意图'!F18,H21&amp;"*"&amp;'intent|意图'!D19,'intent|意图'!D19)</f>
@@ -3542,7 +3618,7 @@
     </row>
     <row r="24" spans="6:8">
       <c r="F24" t="s">
-        <v>134</v>
+        <v>164</v>
       </c>
       <c r="H24">
         <f>IF('intent|意图'!F21='intent|意图'!F20,H23&amp;"*"&amp;'intent|意图'!D21,'intent|意图'!D21)</f>
@@ -3551,7 +3627,7 @@
     </row>
     <row r="25" spans="6:8">
       <c r="F25" t="s">
-        <v>501</v>
+        <v>512</v>
       </c>
       <c r="H25">
         <f>IF('intent|意图'!F22='intent|意图'!F21,H24&amp;"*"&amp;'intent|意图'!D22,'intent|意图'!D22)</f>
@@ -3569,7 +3645,7 @@
     </row>
     <row r="27" spans="6:8">
       <c r="F27" t="s">
-        <v>143</v>
+        <v>173</v>
       </c>
       <c r="H27">
         <f>IF('intent|意图'!F24='intent|意图'!F23,H26&amp;"*"&amp;'intent|意图'!D24,'intent|意图'!D24)</f>
@@ -3578,7 +3654,7 @@
     </row>
     <row r="28" spans="6:8">
       <c r="F28" t="s">
-        <v>502</v>
+        <v>513</v>
       </c>
       <c r="H28">
         <f>IF('intent|意图'!F25='intent|意图'!F24,H27&amp;"*"&amp;'intent|意图'!D25,'intent|意图'!D25)</f>
@@ -3596,32 +3672,32 @@
     </row>
     <row r="30" spans="2:2">
       <c r="B30" t="s">
-        <v>500</v>
+        <v>511</v>
       </c>
     </row>
     <row r="42" spans="2:2">
       <c r="B42" t="s">
-        <v>500</v>
+        <v>511</v>
       </c>
     </row>
     <row r="50" spans="2:2">
       <c r="B50" t="s">
-        <v>503</v>
+        <v>514</v>
       </c>
     </row>
     <row r="54" spans="2:2">
       <c r="B54" t="s">
-        <v>500</v>
+        <v>511</v>
       </c>
     </row>
     <row r="62" spans="2:2">
       <c r="B62" t="s">
-        <v>503</v>
+        <v>514</v>
       </c>
     </row>
     <row r="66" spans="2:2">
       <c r="B66" t="s">
-        <v>500</v>
+        <v>511</v>
       </c>
     </row>
   </sheetData>
@@ -3698,7 +3774,7 @@
         <v>14</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="52" t="s">
+      <c r="E4" s="1" t="s">
         <v>23</v>
       </c>
     </row>
@@ -3714,7 +3790,7 @@
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultColWidth="8.86666666666667" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="8.33333333333333" style="56" customWidth="1"/>
+    <col min="1" max="1" width="8.33333333333333" style="64" customWidth="1"/>
     <col min="2" max="2" width="11.8666666666667" customWidth="1"/>
     <col min="3" max="3" width="31.4666666666667" customWidth="1"/>
   </cols>
@@ -3732,20 +3808,20 @@
       <c r="D1" s="5"/>
       <c r="E1" s="5"/>
     </row>
-    <row r="2" s="55" customFormat="1" spans="1:5">
-      <c r="A2" s="41" t="s">
+    <row r="2" s="63" customFormat="1" spans="1:5">
+      <c r="A2" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="C2" s="41" t="s">
+      <c r="C2" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="D2" s="41" t="s">
+      <c r="D2" s="42" t="s">
         <v>41</v>
       </c>
-      <c r="E2" s="41" t="s">
+      <c r="E2" s="42" t="s">
         <v>42</v>
       </c>
     </row>
@@ -3798,7 +3874,7 @@
     <col min="1" max="1" width="11.5" customWidth="1"/>
     <col min="2" max="2" width="11.4666666666667" style="21" customWidth="1"/>
     <col min="3" max="3" width="51.5" customWidth="1"/>
-    <col min="4" max="4" width="14.125" customWidth="1"/>
+    <col min="4" max="4" width="18.25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -3808,10 +3884,10 @@
       <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="53" t="s">
+      <c r="C1" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="D1" s="53" t="s">
+      <c r="D1" s="5" t="s">
         <v>47</v>
       </c>
     </row>
@@ -3822,10 +3898,10 @@
       <c r="B2" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C2" s="53" t="s">
+      <c r="C2" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="D2" s="53" t="s">
+      <c r="D2" s="5" t="s">
         <v>50</v>
       </c>
     </row>
@@ -3836,10 +3912,10 @@
       <c r="B3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="53" t="s">
+      <c r="C3" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="D3" s="52" t="s">
+      <c r="D3" s="1" t="s">
         <v>10</v>
       </c>
     </row>
@@ -3850,7 +3926,7 @@
       <c r="B4" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="52" t="s">
+      <c r="C4" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D4" s="40" t="str">
@@ -3859,13 +3935,13 @@
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="52" t="s">
+      <c r="A5" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="54" t="s">
+      <c r="B5" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="52" t="s">
+      <c r="C5" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D5" s="40" t="str">
@@ -3874,13 +3950,13 @@
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="52" t="s">
+      <c r="A6" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="54" t="s">
+      <c r="B6" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="52" t="s">
+      <c r="C6" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D6" s="40" t="str">
@@ -3889,13 +3965,13 @@
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="52" t="s">
+      <c r="A7" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="54" t="s">
+      <c r="B7" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="52" t="s">
+      <c r="C7" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D7" s="40" t="str">
@@ -3904,13 +3980,13 @@
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="52" t="s">
+      <c r="A8" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B8" s="54" t="s">
+      <c r="B8" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="52" t="s">
+      <c r="C8" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D8" s="40" t="str">
@@ -3926,733 +4002,6 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:J26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <cols>
-    <col min="1" max="1" width="21.25" customWidth="1"/>
-    <col min="2" max="2" width="9.06666666666667" style="44"/>
-    <col min="4" max="6" width="9.06666666666667" style="44"/>
-    <col min="7" max="7" width="62" customWidth="1"/>
-    <col min="8" max="8" width="67.125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="45" t="s">
-        <v>56</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="45" t="s">
-        <v>57</v>
-      </c>
-      <c r="E1" s="45" t="s">
-        <v>58</v>
-      </c>
-      <c r="F1" s="45" t="s">
-        <v>59</v>
-      </c>
-      <c r="G1" s="46" t="s">
-        <v>60</v>
-      </c>
-      <c r="H1" s="46" t="s">
-        <v>61</v>
-      </c>
-      <c r="I1" s="46" t="s">
-        <v>62</v>
-      </c>
-      <c r="J1" s="46" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="D2" s="45" t="s">
-        <v>66</v>
-      </c>
-      <c r="E2" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="F2" s="45" t="s">
-        <v>68</v>
-      </c>
-      <c r="G2" s="46" t="s">
-        <v>69</v>
-      </c>
-      <c r="H2" s="46" t="s">
-        <v>70</v>
-      </c>
-      <c r="I2" s="46" t="s">
-        <v>71</v>
-      </c>
-      <c r="J2" s="46" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="45" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="45" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="45" t="s">
-        <v>73</v>
-      </c>
-      <c r="F3" s="45" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" s="46" t="s">
-        <v>10</v>
-      </c>
-      <c r="H3" s="46" t="s">
-        <v>74</v>
-      </c>
-      <c r="I3" s="46" t="s">
-        <v>11</v>
-      </c>
-      <c r="J3" s="46" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B4" s="47"/>
-      <c r="C4" s="40" t="s">
-        <v>76</v>
-      </c>
-      <c r="D4" s="47">
-        <v>1</v>
-      </c>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="40" t="s">
-        <v>77</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="I4" s="1">
-        <v>8</v>
-      </c>
-      <c r="J4" s="52"/>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B5" s="47"/>
-      <c r="C5" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D5" s="47">
-        <v>2</v>
-      </c>
-      <c r="E5" s="47"/>
-      <c r="F5" s="47"/>
-      <c r="G5" s="40" t="s">
-        <v>81</v>
-      </c>
-      <c r="H5" s="40" t="s">
-        <v>82</v>
-      </c>
-      <c r="I5" s="1">
-        <v>3</v>
-      </c>
-      <c r="J5" s="52"/>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B6" s="47"/>
-      <c r="C6" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="D6" s="47">
-        <v>3</v>
-      </c>
-      <c r="E6" s="47"/>
-      <c r="F6" s="47"/>
-      <c r="G6" s="40" t="s">
-        <v>85</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="I6" s="1">
-        <v>0</v>
-      </c>
-      <c r="J6" s="52"/>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B7" s="47"/>
-      <c r="C7" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="D7" s="47">
-        <v>4</v>
-      </c>
-      <c r="E7" s="47"/>
-      <c r="F7" s="47"/>
-      <c r="G7" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="I7" s="1">
-        <v>0</v>
-      </c>
-      <c r="J7" s="52"/>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B8" s="47"/>
-      <c r="C8" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="D8" s="47">
-        <v>5</v>
-      </c>
-      <c r="E8" s="47"/>
-      <c r="F8" s="47"/>
-      <c r="G8" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="I8" s="1">
-        <v>0</v>
-      </c>
-      <c r="J8" s="52"/>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B9" s="47"/>
-      <c r="C9" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="D9" s="47">
-        <v>6</v>
-      </c>
-      <c r="E9" s="47"/>
-      <c r="F9" s="47"/>
-      <c r="G9" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="I9" s="1">
-        <v>0</v>
-      </c>
-      <c r="J9" s="52"/>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="B10" s="47"/>
-      <c r="C10" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="D10" s="47">
-        <v>7</v>
-      </c>
-      <c r="E10" s="47"/>
-      <c r="F10" s="47"/>
-      <c r="G10" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="I10" s="1">
-        <v>0</v>
-      </c>
-      <c r="J10" s="52"/>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="B11" s="47"/>
-      <c r="C11" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="D11" s="47">
-        <v>8</v>
-      </c>
-      <c r="E11" s="47"/>
-      <c r="F11" s="47"/>
-      <c r="G11" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="I11" s="1">
-        <v>0</v>
-      </c>
-      <c r="J11" s="52"/>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="48" t="s">
-        <v>107</v>
-      </c>
-      <c r="B12" s="49" t="s">
-        <v>14</v>
-      </c>
-      <c r="C12" s="50" t="s">
-        <v>108</v>
-      </c>
-      <c r="D12" s="51"/>
-      <c r="E12" s="51">
-        <v>1</v>
-      </c>
-      <c r="F12" s="51">
-        <v>0</v>
-      </c>
-      <c r="G12" s="50" t="s">
-        <v>109</v>
-      </c>
-      <c r="H12" s="49" t="s">
-        <v>106</v>
-      </c>
-      <c r="I12" s="49">
-        <v>0</v>
-      </c>
-      <c r="J12" s="50"/>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" s="48" t="s">
-        <v>110</v>
-      </c>
-      <c r="B13" s="49" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13" s="50" t="s">
-        <v>111</v>
-      </c>
-      <c r="D13" s="51"/>
-      <c r="E13" s="51">
-        <v>1</v>
-      </c>
-      <c r="F13" s="51">
-        <v>1</v>
-      </c>
-      <c r="G13" s="50" t="s">
-        <v>112</v>
-      </c>
-      <c r="H13" s="49" t="s">
-        <v>106</v>
-      </c>
-      <c r="I13" s="49">
-        <v>0</v>
-      </c>
-      <c r="J13" s="50"/>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="48" t="s">
-        <v>113</v>
-      </c>
-      <c r="B14" s="49" t="s">
-        <v>14</v>
-      </c>
-      <c r="C14" s="50" t="s">
-        <v>114</v>
-      </c>
-      <c r="D14" s="51"/>
-      <c r="E14" s="51">
-        <v>1</v>
-      </c>
-      <c r="F14" s="51">
-        <v>3</v>
-      </c>
-      <c r="G14" s="50" t="s">
-        <v>115</v>
-      </c>
-      <c r="H14" s="49" t="s">
-        <v>106</v>
-      </c>
-      <c r="I14" s="49">
-        <v>0</v>
-      </c>
-      <c r="J14" s="50"/>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" s="48" t="s">
-        <v>116</v>
-      </c>
-      <c r="B15" s="50" t="s">
-        <v>17</v>
-      </c>
-      <c r="C15" s="50" t="s">
-        <v>117</v>
-      </c>
-      <c r="D15" s="51"/>
-      <c r="E15" s="51">
-        <v>1</v>
-      </c>
-      <c r="F15" s="51">
-        <v>0</v>
-      </c>
-      <c r="G15" s="50" t="s">
-        <v>118</v>
-      </c>
-      <c r="H15" s="49" t="s">
-        <v>106</v>
-      </c>
-      <c r="I15" s="49">
-        <v>0</v>
-      </c>
-      <c r="J15" s="50"/>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="48" t="s">
-        <v>119</v>
-      </c>
-      <c r="B16" s="50" t="s">
-        <v>17</v>
-      </c>
-      <c r="C16" s="50" t="s">
-        <v>120</v>
-      </c>
-      <c r="D16" s="51"/>
-      <c r="E16" s="51">
-        <v>1</v>
-      </c>
-      <c r="F16" s="51">
-        <v>1</v>
-      </c>
-      <c r="G16" s="50" t="s">
-        <v>121</v>
-      </c>
-      <c r="H16" s="49" t="s">
-        <v>106</v>
-      </c>
-      <c r="I16" s="49">
-        <v>0</v>
-      </c>
-      <c r="J16" s="50"/>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17" s="48" t="s">
-        <v>122</v>
-      </c>
-      <c r="B17" s="50" t="s">
-        <v>17</v>
-      </c>
-      <c r="C17" s="50" t="s">
-        <v>123</v>
-      </c>
-      <c r="D17" s="51"/>
-      <c r="E17" s="51">
-        <v>1</v>
-      </c>
-      <c r="F17" s="51">
-        <v>3</v>
-      </c>
-      <c r="G17" s="50" t="s">
-        <v>124</v>
-      </c>
-      <c r="H17" s="49" t="s">
-        <v>106</v>
-      </c>
-      <c r="I17" s="49">
-        <v>0</v>
-      </c>
-      <c r="J17" s="50"/>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="A18" s="48" t="s">
-        <v>125</v>
-      </c>
-      <c r="B18" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="C18" s="50" t="s">
-        <v>126</v>
-      </c>
-      <c r="D18" s="51"/>
-      <c r="E18" s="51">
-        <v>1</v>
-      </c>
-      <c r="F18" s="51">
-        <v>0</v>
-      </c>
-      <c r="G18" s="50" t="s">
-        <v>127</v>
-      </c>
-      <c r="H18" s="49" t="s">
-        <v>106</v>
-      </c>
-      <c r="I18" s="49">
-        <v>0</v>
-      </c>
-      <c r="J18" s="50"/>
-    </row>
-    <row r="19" spans="1:10">
-      <c r="A19" s="48" t="s">
-        <v>128</v>
-      </c>
-      <c r="B19" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="C19" s="50" t="s">
-        <v>129</v>
-      </c>
-      <c r="D19" s="51"/>
-      <c r="E19" s="51">
-        <v>1</v>
-      </c>
-      <c r="F19" s="51">
-        <v>1</v>
-      </c>
-      <c r="G19" s="50" t="s">
-        <v>130</v>
-      </c>
-      <c r="H19" s="49" t="s">
-        <v>106</v>
-      </c>
-      <c r="I19" s="49">
-        <v>0</v>
-      </c>
-      <c r="J19" s="50"/>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="A20" s="48" t="s">
-        <v>131</v>
-      </c>
-      <c r="B20" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="C20" s="50" t="s">
-        <v>132</v>
-      </c>
-      <c r="D20" s="51"/>
-      <c r="E20" s="51">
-        <v>1</v>
-      </c>
-      <c r="F20" s="51">
-        <v>3</v>
-      </c>
-      <c r="G20" s="50" t="s">
-        <v>133</v>
-      </c>
-      <c r="H20" s="49" t="s">
-        <v>106</v>
-      </c>
-      <c r="I20" s="49">
-        <v>0</v>
-      </c>
-      <c r="J20" s="50"/>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="A21" s="48" t="s">
-        <v>134</v>
-      </c>
-      <c r="B21" s="50" t="s">
-        <v>23</v>
-      </c>
-      <c r="C21" s="50" t="s">
-        <v>135</v>
-      </c>
-      <c r="D21" s="51"/>
-      <c r="E21" s="51">
-        <v>1</v>
-      </c>
-      <c r="F21" s="51">
-        <v>0</v>
-      </c>
-      <c r="G21" s="50" t="s">
-        <v>136</v>
-      </c>
-      <c r="H21" s="49" t="s">
-        <v>106</v>
-      </c>
-      <c r="I21" s="49">
-        <v>0</v>
-      </c>
-      <c r="J21" s="50"/>
-    </row>
-    <row r="22" spans="1:10">
-      <c r="A22" s="48" t="s">
-        <v>137</v>
-      </c>
-      <c r="B22" s="50" t="s">
-        <v>23</v>
-      </c>
-      <c r="C22" s="50" t="s">
-        <v>138</v>
-      </c>
-      <c r="D22" s="51"/>
-      <c r="E22" s="51">
-        <v>1</v>
-      </c>
-      <c r="F22" s="51">
-        <v>1</v>
-      </c>
-      <c r="G22" s="50" t="s">
-        <v>139</v>
-      </c>
-      <c r="H22" s="49" t="s">
-        <v>106</v>
-      </c>
-      <c r="I22" s="49">
-        <v>0</v>
-      </c>
-      <c r="J22" s="50"/>
-    </row>
-    <row r="23" spans="1:10">
-      <c r="A23" s="48" t="s">
-        <v>140</v>
-      </c>
-      <c r="B23" s="50" t="s">
-        <v>23</v>
-      </c>
-      <c r="C23" s="50" t="s">
-        <v>141</v>
-      </c>
-      <c r="D23" s="51"/>
-      <c r="E23" s="51">
-        <v>1</v>
-      </c>
-      <c r="F23" s="51">
-        <v>3</v>
-      </c>
-      <c r="G23" s="50" t="s">
-        <v>142</v>
-      </c>
-      <c r="H23" s="49" t="s">
-        <v>106</v>
-      </c>
-      <c r="I23" s="49">
-        <v>0</v>
-      </c>
-      <c r="J23" s="50"/>
-    </row>
-    <row r="24" spans="1:10">
-      <c r="A24" s="48" t="s">
-        <v>143</v>
-      </c>
-      <c r="B24" s="50" t="s">
-        <v>26</v>
-      </c>
-      <c r="C24" s="50" t="s">
-        <v>144</v>
-      </c>
-      <c r="D24" s="51"/>
-      <c r="E24" s="51">
-        <v>1</v>
-      </c>
-      <c r="F24" s="51">
-        <v>0</v>
-      </c>
-      <c r="G24" s="50" t="s">
-        <v>145</v>
-      </c>
-      <c r="H24" s="49" t="s">
-        <v>106</v>
-      </c>
-      <c r="I24" s="49">
-        <v>0</v>
-      </c>
-      <c r="J24" s="50"/>
-    </row>
-    <row r="25" spans="1:10">
-      <c r="A25" s="48" t="s">
-        <v>146</v>
-      </c>
-      <c r="B25" s="50" t="s">
-        <v>26</v>
-      </c>
-      <c r="C25" s="50" t="s">
-        <v>147</v>
-      </c>
-      <c r="D25" s="51"/>
-      <c r="E25" s="51">
-        <v>1</v>
-      </c>
-      <c r="F25" s="51">
-        <v>1</v>
-      </c>
-      <c r="G25" s="50" t="s">
-        <v>148</v>
-      </c>
-      <c r="H25" s="49" t="s">
-        <v>106</v>
-      </c>
-      <c r="I25" s="49">
-        <v>0</v>
-      </c>
-      <c r="J25" s="50"/>
-    </row>
-    <row r="26" spans="1:10">
-      <c r="A26" s="48" t="s">
-        <v>149</v>
-      </c>
-      <c r="B26" s="50" t="s">
-        <v>26</v>
-      </c>
-      <c r="C26" s="50" t="s">
-        <v>150</v>
-      </c>
-      <c r="D26" s="51"/>
-      <c r="E26" s="51">
-        <v>1</v>
-      </c>
-      <c r="F26" s="51">
-        <v>3</v>
-      </c>
-      <c r="G26" s="50" t="s">
-        <v>151</v>
-      </c>
-      <c r="H26" s="49" t="s">
-        <v>106</v>
-      </c>
-      <c r="I26" s="49">
-        <v>0</v>
-      </c>
-      <c r="J26" s="50"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:I6"/>
@@ -4672,57 +4021,57 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>152</v>
+        <v>56</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>153</v>
+        <v>57</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>154</v>
+        <v>58</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>155</v>
+        <v>59</v>
       </c>
       <c r="F1" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="G1" s="5" t="s">
-        <v>156</v>
-      </c>
       <c r="H1" s="5" t="s">
-        <v>157</v>
+        <v>62</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>158</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" ht="54" spans="1:9">
-      <c r="A2" s="41" t="s">
+      <c r="A2" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="41" t="s">
-        <v>159</v>
-      </c>
-      <c r="C2" s="41" t="s">
-        <v>160</v>
-      </c>
-      <c r="D2" s="41" t="s">
-        <v>161</v>
+      <c r="B2" s="42" t="s">
+        <v>64</v>
+      </c>
+      <c r="C2" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="D2" s="42" t="s">
+        <v>66</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="F2" s="41" t="s">
-        <v>163</v>
-      </c>
-      <c r="G2" s="42" t="s">
-        <v>164</v>
-      </c>
-      <c r="H2" s="41" t="s">
-        <v>165</v>
-      </c>
-      <c r="I2" s="43" t="s">
-        <v>166</v>
+        <v>67</v>
+      </c>
+      <c r="F2" s="42" t="s">
+        <v>68</v>
+      </c>
+      <c r="G2" s="43" t="s">
+        <v>69</v>
+      </c>
+      <c r="H2" s="42" t="s">
+        <v>70</v>
+      </c>
+      <c r="I2" s="62" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -4742,7 +4091,7 @@
         <v>10</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>11</v>
@@ -4756,10 +4105,10 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>167</v>
+        <v>73</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>168</v>
+        <v>74</v>
       </c>
       <c r="C4" s="1">
         <v>1</v>
@@ -4768,27 +4117,27 @@
         <v>1</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>169</v>
+        <v>75</v>
       </c>
       <c r="F4" s="40" t="s">
-        <v>170</v>
+        <v>76</v>
       </c>
       <c r="G4" s="1">
         <v>2</v>
       </c>
       <c r="H4" s="40" t="s">
-        <v>171</v>
+        <v>77</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>167</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>172</v>
+        <v>78</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C5" s="1">
         <v>2</v>
@@ -4797,27 +4146,27 @@
         <v>1</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>173</v>
+        <v>80</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>174</v>
+        <v>81</v>
       </c>
       <c r="G5" s="1">
         <v>1</v>
       </c>
       <c r="H5" s="40" t="s">
-        <v>175</v>
+        <v>82</v>
       </c>
       <c r="I5" s="40" t="s">
-        <v>176</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>177</v>
+        <v>84</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>178</v>
+        <v>85</v>
       </c>
       <c r="C6" s="1">
         <v>1</v>
@@ -4826,23 +4175,750 @@
         <v>2</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>179</v>
+        <v>86</v>
       </c>
       <c r="F6" s="40" t="s">
-        <v>180</v>
+        <v>87</v>
       </c>
       <c r="G6" s="1">
         <v>2</v>
       </c>
       <c r="H6" s="40" t="s">
-        <v>171</v>
+        <v>77</v>
       </c>
       <c r="I6" s="40" t="s">
-        <v>181</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:J26"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="21.25" customWidth="1"/>
+    <col min="2" max="2" width="9.06666666666667" style="54"/>
+    <col min="4" max="6" width="9.06666666666667" style="54"/>
+    <col min="7" max="7" width="62" customWidth="1"/>
+    <col min="8" max="8" width="67.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="55" t="s">
+        <v>89</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="55" t="s">
+        <v>90</v>
+      </c>
+      <c r="E1" s="55" t="s">
+        <v>91</v>
+      </c>
+      <c r="F1" s="55" t="s">
+        <v>92</v>
+      </c>
+      <c r="G1" s="56" t="s">
+        <v>93</v>
+      </c>
+      <c r="H1" s="56" t="s">
+        <v>60</v>
+      </c>
+      <c r="I1" s="56" t="s">
+        <v>94</v>
+      </c>
+      <c r="J1" s="56" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="55" t="s">
+        <v>96</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="D2" s="55" t="s">
+        <v>98</v>
+      </c>
+      <c r="E2" s="55" t="s">
+        <v>99</v>
+      </c>
+      <c r="F2" s="55" t="s">
+        <v>100</v>
+      </c>
+      <c r="G2" s="56" t="s">
+        <v>101</v>
+      </c>
+      <c r="H2" s="56" t="s">
+        <v>102</v>
+      </c>
+      <c r="I2" s="56" t="s">
+        <v>103</v>
+      </c>
+      <c r="J2" s="56" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="55" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="55" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="55" t="s">
+        <v>105</v>
+      </c>
+      <c r="F3" s="55" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="56" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="56" t="s">
+        <v>72</v>
+      </c>
+      <c r="I3" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="J3" s="56" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B4" s="57"/>
+      <c r="C4" s="40" t="s">
+        <v>107</v>
+      </c>
+      <c r="D4" s="57">
+        <v>1</v>
+      </c>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="40" t="s">
+        <v>108</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="I4" s="1">
+        <v>8</v>
+      </c>
+      <c r="J4" s="1"/>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B5" s="57"/>
+      <c r="C5" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D5" s="57">
+        <v>2</v>
+      </c>
+      <c r="E5" s="57"/>
+      <c r="F5" s="57"/>
+      <c r="G5" s="40" t="s">
+        <v>112</v>
+      </c>
+      <c r="H5" s="40" t="s">
+        <v>113</v>
+      </c>
+      <c r="I5" s="1">
+        <v>3</v>
+      </c>
+      <c r="J5" s="1"/>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B6" s="57"/>
+      <c r="C6" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D6" s="57">
+        <v>3</v>
+      </c>
+      <c r="E6" s="57"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="40" t="s">
+        <v>115</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="I6" s="1">
+        <v>0</v>
+      </c>
+      <c r="J6" s="1"/>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B7" s="57"/>
+      <c r="C7" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D7" s="57">
+        <v>4</v>
+      </c>
+      <c r="E7" s="57"/>
+      <c r="F7" s="57"/>
+      <c r="G7" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="I7" s="1">
+        <v>0</v>
+      </c>
+      <c r="J7" s="1"/>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B8" s="57"/>
+      <c r="C8" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D8" s="57">
+        <v>5</v>
+      </c>
+      <c r="E8" s="57"/>
+      <c r="F8" s="57"/>
+      <c r="G8" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="I8" s="1">
+        <v>0</v>
+      </c>
+      <c r="J8" s="1"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B9" s="57"/>
+      <c r="C9" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D9" s="57">
+        <v>6</v>
+      </c>
+      <c r="E9" s="57"/>
+      <c r="F9" s="57"/>
+      <c r="G9" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="I9" s="1">
+        <v>0</v>
+      </c>
+      <c r="J9" s="1"/>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B10" s="57"/>
+      <c r="C10" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="D10" s="57">
+        <v>7</v>
+      </c>
+      <c r="E10" s="57"/>
+      <c r="F10" s="57"/>
+      <c r="G10" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="I10" s="1">
+        <v>0</v>
+      </c>
+      <c r="J10" s="1"/>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B11" s="57"/>
+      <c r="C11" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="D11" s="57">
+        <v>8</v>
+      </c>
+      <c r="E11" s="57"/>
+      <c r="F11" s="57"/>
+      <c r="G11" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="I11" s="1">
+        <v>0</v>
+      </c>
+      <c r="J11" s="1"/>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="46" t="s">
+        <v>137</v>
+      </c>
+      <c r="B12" s="47" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" s="47" t="s">
+        <v>138</v>
+      </c>
+      <c r="D12" s="58"/>
+      <c r="E12" s="58">
+        <v>1</v>
+      </c>
+      <c r="F12" s="58">
+        <v>0</v>
+      </c>
+      <c r="G12" s="47" t="s">
+        <v>139</v>
+      </c>
+      <c r="H12" s="47" t="s">
+        <v>136</v>
+      </c>
+      <c r="I12" s="61">
+        <v>0</v>
+      </c>
+      <c r="J12" s="50"/>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="49" t="s">
+        <v>140</v>
+      </c>
+      <c r="B13" s="50" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="50" t="s">
+        <v>141</v>
+      </c>
+      <c r="D13" s="59"/>
+      <c r="E13" s="59">
+        <v>1</v>
+      </c>
+      <c r="F13" s="59">
+        <v>1</v>
+      </c>
+      <c r="G13" s="50" t="s">
+        <v>142</v>
+      </c>
+      <c r="H13" s="50" t="s">
+        <v>136</v>
+      </c>
+      <c r="I13" s="50">
+        <v>0</v>
+      </c>
+      <c r="J13" s="50"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="49" t="s">
+        <v>143</v>
+      </c>
+      <c r="B14" s="50" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="50" t="s">
+        <v>144</v>
+      </c>
+      <c r="D14" s="59"/>
+      <c r="E14" s="59">
+        <v>1</v>
+      </c>
+      <c r="F14" s="59">
+        <v>3</v>
+      </c>
+      <c r="G14" s="50" t="s">
+        <v>145</v>
+      </c>
+      <c r="H14" s="50" t="s">
+        <v>136</v>
+      </c>
+      <c r="I14" s="50">
+        <v>0</v>
+      </c>
+      <c r="J14" s="50"/>
+    </row>
+    <row r="15" s="53" customFormat="1" spans="1:10">
+      <c r="A15" s="51" t="s">
+        <v>146</v>
+      </c>
+      <c r="B15" s="52" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="52" t="s">
+        <v>147</v>
+      </c>
+      <c r="D15" s="60"/>
+      <c r="E15" s="60">
+        <v>1</v>
+      </c>
+      <c r="F15" s="60">
+        <v>0</v>
+      </c>
+      <c r="G15" s="52" t="s">
+        <v>148</v>
+      </c>
+      <c r="H15" s="52" t="s">
+        <v>136</v>
+      </c>
+      <c r="I15" s="52">
+        <v>0</v>
+      </c>
+      <c r="J15" s="52"/>
+    </row>
+    <row r="16" s="53" customFormat="1" spans="1:10">
+      <c r="A16" s="51" t="s">
+        <v>149</v>
+      </c>
+      <c r="B16" s="52" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="52" t="s">
+        <v>150</v>
+      </c>
+      <c r="D16" s="60"/>
+      <c r="E16" s="60">
+        <v>1</v>
+      </c>
+      <c r="F16" s="60">
+        <v>1</v>
+      </c>
+      <c r="G16" s="52" t="s">
+        <v>151</v>
+      </c>
+      <c r="H16" s="52" t="s">
+        <v>136</v>
+      </c>
+      <c r="I16" s="52">
+        <v>0</v>
+      </c>
+      <c r="J16" s="52"/>
+    </row>
+    <row r="17" s="53" customFormat="1" spans="1:10">
+      <c r="A17" s="51" t="s">
+        <v>152</v>
+      </c>
+      <c r="B17" s="52" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="52" t="s">
+        <v>153</v>
+      </c>
+      <c r="D17" s="60"/>
+      <c r="E17" s="60">
+        <v>1</v>
+      </c>
+      <c r="F17" s="60">
+        <v>3</v>
+      </c>
+      <c r="G17" s="52" t="s">
+        <v>154</v>
+      </c>
+      <c r="H17" s="52" t="s">
+        <v>136</v>
+      </c>
+      <c r="I17" s="52">
+        <v>0</v>
+      </c>
+      <c r="J17" s="52"/>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="49" t="s">
+        <v>155</v>
+      </c>
+      <c r="B18" s="50" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18" s="50" t="s">
+        <v>156</v>
+      </c>
+      <c r="D18" s="59"/>
+      <c r="E18" s="59">
+        <v>1</v>
+      </c>
+      <c r="F18" s="59">
+        <v>0</v>
+      </c>
+      <c r="G18" s="50" t="s">
+        <v>157</v>
+      </c>
+      <c r="H18" s="50" t="s">
+        <v>136</v>
+      </c>
+      <c r="I18" s="50">
+        <v>0</v>
+      </c>
+      <c r="J18" s="50"/>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="49" t="s">
+        <v>158</v>
+      </c>
+      <c r="B19" s="50" t="s">
+        <v>20</v>
+      </c>
+      <c r="C19" s="50" t="s">
+        <v>159</v>
+      </c>
+      <c r="D19" s="59"/>
+      <c r="E19" s="59">
+        <v>1</v>
+      </c>
+      <c r="F19" s="59">
+        <v>1</v>
+      </c>
+      <c r="G19" s="50" t="s">
+        <v>160</v>
+      </c>
+      <c r="H19" s="50" t="s">
+        <v>136</v>
+      </c>
+      <c r="I19" s="50">
+        <v>0</v>
+      </c>
+      <c r="J19" s="50"/>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="49" t="s">
+        <v>161</v>
+      </c>
+      <c r="B20" s="50" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" s="50" t="s">
+        <v>162</v>
+      </c>
+      <c r="D20" s="59"/>
+      <c r="E20" s="59">
+        <v>1</v>
+      </c>
+      <c r="F20" s="59">
+        <v>3</v>
+      </c>
+      <c r="G20" s="50" t="s">
+        <v>163</v>
+      </c>
+      <c r="H20" s="50" t="s">
+        <v>136</v>
+      </c>
+      <c r="I20" s="50">
+        <v>0</v>
+      </c>
+      <c r="J20" s="50"/>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="49" t="s">
+        <v>164</v>
+      </c>
+      <c r="B21" s="50" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21" s="50" t="s">
+        <v>165</v>
+      </c>
+      <c r="D21" s="59"/>
+      <c r="E21" s="59">
+        <v>1</v>
+      </c>
+      <c r="F21" s="59">
+        <v>0</v>
+      </c>
+      <c r="G21" s="50" t="s">
+        <v>166</v>
+      </c>
+      <c r="H21" s="50" t="s">
+        <v>136</v>
+      </c>
+      <c r="I21" s="50">
+        <v>0</v>
+      </c>
+      <c r="J21" s="50"/>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="49" t="s">
+        <v>167</v>
+      </c>
+      <c r="B22" s="50" t="s">
+        <v>23</v>
+      </c>
+      <c r="C22" s="50" t="s">
+        <v>168</v>
+      </c>
+      <c r="D22" s="59"/>
+      <c r="E22" s="59">
+        <v>1</v>
+      </c>
+      <c r="F22" s="59">
+        <v>1</v>
+      </c>
+      <c r="G22" s="50" t="s">
+        <v>169</v>
+      </c>
+      <c r="H22" s="50" t="s">
+        <v>136</v>
+      </c>
+      <c r="I22" s="50">
+        <v>0</v>
+      </c>
+      <c r="J22" s="50"/>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="49" t="s">
+        <v>170</v>
+      </c>
+      <c r="B23" s="50" t="s">
+        <v>23</v>
+      </c>
+      <c r="C23" s="50" t="s">
+        <v>171</v>
+      </c>
+      <c r="D23" s="59"/>
+      <c r="E23" s="59">
+        <v>1</v>
+      </c>
+      <c r="F23" s="59">
+        <v>3</v>
+      </c>
+      <c r="G23" s="50" t="s">
+        <v>172</v>
+      </c>
+      <c r="H23" s="50" t="s">
+        <v>136</v>
+      </c>
+      <c r="I23" s="50">
+        <v>0</v>
+      </c>
+      <c r="J23" s="50"/>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="B24" s="50" t="s">
+        <v>26</v>
+      </c>
+      <c r="C24" s="50" t="s">
+        <v>174</v>
+      </c>
+      <c r="D24" s="59"/>
+      <c r="E24" s="59">
+        <v>1</v>
+      </c>
+      <c r="F24" s="59">
+        <v>0</v>
+      </c>
+      <c r="G24" s="50" t="s">
+        <v>175</v>
+      </c>
+      <c r="H24" s="50" t="s">
+        <v>136</v>
+      </c>
+      <c r="I24" s="50">
+        <v>0</v>
+      </c>
+      <c r="J24" s="50"/>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="49" t="s">
+        <v>176</v>
+      </c>
+      <c r="B25" s="50" t="s">
+        <v>26</v>
+      </c>
+      <c r="C25" s="50" t="s">
+        <v>177</v>
+      </c>
+      <c r="D25" s="59"/>
+      <c r="E25" s="59">
+        <v>1</v>
+      </c>
+      <c r="F25" s="59">
+        <v>1</v>
+      </c>
+      <c r="G25" s="52" t="s">
+        <v>154</v>
+      </c>
+      <c r="H25" s="50" t="s">
+        <v>136</v>
+      </c>
+      <c r="I25" s="50">
+        <v>0</v>
+      </c>
+      <c r="J25" s="50"/>
+    </row>
+    <row r="26" s="41" customFormat="1" spans="1:10">
+      <c r="A26" s="46" t="s">
+        <v>178</v>
+      </c>
+      <c r="B26" s="47" t="s">
+        <v>26</v>
+      </c>
+      <c r="C26" s="47" t="s">
+        <v>179</v>
+      </c>
+      <c r="D26" s="58"/>
+      <c r="E26" s="58">
+        <v>1</v>
+      </c>
+      <c r="F26" s="58">
+        <v>3</v>
+      </c>
+      <c r="G26" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="H26" s="47" t="s">
+        <v>136</v>
+      </c>
+      <c r="I26" s="61">
+        <v>0</v>
+      </c>
+      <c r="J26" s="61"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
 </file>
@@ -4850,13 +4926,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <dimension ref="A1:I31"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="13.2666666666667" customWidth="1"/>
-    <col min="3" max="3" width="14.125" customWidth="1"/>
-    <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="1" max="1" width="22.625" customWidth="1"/>
+    <col min="3" max="3" width="9.125" customWidth="1"/>
+    <col min="4" max="4" width="14.125" customWidth="1"/>
+    <col min="6" max="6" width="14.125" customWidth="1"/>
     <col min="7" max="7" width="9.75" customWidth="1"/>
     <col min="8" max="8" width="71.2" customWidth="1"/>
   </cols>
@@ -4866,51 +4942,51 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D1" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="D1" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="E1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>185</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>186</v>
       </c>
       <c r="H1" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" ht="108" spans="1:8">
-      <c r="A2" s="41" t="s">
+      <c r="A2" s="42" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C2" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="D2" s="43" t="s">
         <v>187</v>
       </c>
-      <c r="D2" s="42" t="s">
+      <c r="E2" s="42" t="s">
         <v>188</v>
       </c>
-      <c r="E2" s="41" t="s">
+      <c r="F2" s="42" t="s">
         <v>189</v>
       </c>
-      <c r="F2" s="41" t="s">
+      <c r="G2" s="42" t="s">
         <v>190</v>
       </c>
-      <c r="G2" s="41" t="s">
+      <c r="H2" s="5" t="s">
         <v>191</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -4941,11 +5017,11 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
-        <v>167</v>
+        <v>73</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1" t="s">
-        <v>168</v>
+        <v>74</v>
       </c>
       <c r="D4" s="1">
         <v>0</v>
@@ -4960,16 +5036,16 @@
         <v>6</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>169</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="40" t="s">
-        <v>176</v>
+        <v>83</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="40" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D5" s="1">
         <v>1</v>
@@ -4984,66 +5060,66 @@
         <v>5</v>
       </c>
       <c r="H5" s="40" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="6" s="41" customFormat="1" spans="1:8">
+      <c r="A6" s="44" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="40" t="s">
+      <c r="B6" s="45"/>
+      <c r="C6" s="44" t="s">
+        <v>85</v>
+      </c>
+      <c r="D6" s="45">
+        <v>0</v>
+      </c>
+      <c r="E6" s="45">
+        <v>0</v>
+      </c>
+      <c r="F6" s="45">
+        <v>1</v>
+      </c>
+      <c r="G6" s="45">
+        <v>8</v>
+      </c>
+      <c r="H6" s="44" t="s">
         <v>195</v>
       </c>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="D6" s="1">
-        <v>0</v>
-      </c>
-      <c r="E6" s="1">
-        <v>0</v>
-      </c>
-      <c r="F6" s="1">
-        <v>1</v>
-      </c>
-      <c r="G6" s="1">
-        <v>8</v>
-      </c>
-      <c r="H6" s="40" t="s">
+    </row>
+    <row r="7" s="41" customFormat="1" spans="1:8">
+      <c r="A7" s="44" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="40" t="s">
+      <c r="B7" s="45"/>
+      <c r="C7" s="44" t="s">
         <v>197</v>
       </c>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1" t="s">
+      <c r="D7" s="45">
+        <v>0</v>
+      </c>
+      <c r="E7" s="45">
+        <v>0</v>
+      </c>
+      <c r="F7" s="45">
+        <v>3</v>
+      </c>
+      <c r="G7" s="44" t="s">
         <v>198</v>
       </c>
-      <c r="D7" s="1">
-        <v>0</v>
-      </c>
-      <c r="E7" s="1">
-        <v>0</v>
-      </c>
-      <c r="F7" s="1">
-        <v>3</v>
-      </c>
-      <c r="G7" s="40" t="s">
+      <c r="H7" s="44" t="s">
         <v>199</v>
-      </c>
-      <c r="H7" s="40" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="C8" s="1" t="s">
         <v>202</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>203</v>
       </c>
       <c r="D8" s="1">
         <v>0</v>
@@ -5058,18 +5134,18 @@
         <v>1</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>206</v>
-      </c>
       <c r="C9" s="1" t="s">
-        <v>92</v>
+        <v>122</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -5084,18 +5160,18 @@
         <v>2</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="C10" s="1" t="s">
         <v>209</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>210</v>
       </c>
       <c r="D10" s="1">
         <v>0</v>
@@ -5110,18 +5186,18 @@
         <v>3</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="C11" s="1" t="s">
         <v>213</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>214</v>
       </c>
       <c r="D11" s="1">
         <v>0</v>
@@ -5136,18 +5212,18 @@
         <v>4</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>217</v>
-      </c>
       <c r="C12" s="1" t="s">
-        <v>88</v>
+        <v>118</v>
       </c>
       <c r="D12" s="1">
         <v>0</v>
@@ -5162,18 +5238,18 @@
         <v>5</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="C13" s="1" t="s">
         <v>220</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>221</v>
       </c>
       <c r="D13" s="1">
         <v>0</v>
@@ -5188,18 +5264,18 @@
         <v>6</v>
       </c>
       <c r="H13" s="40" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="C14" s="1" t="s">
         <v>224</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>225</v>
       </c>
       <c r="D14" s="1">
         <v>0</v>
@@ -5214,18 +5290,18 @@
         <v>7</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="C15" s="1" t="s">
         <v>228</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>229</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -5240,18 +5316,18 @@
         <v>8</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="C16" s="1" t="s">
         <v>232</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>233</v>
       </c>
       <c r="D16" s="1">
         <v>0</v>
@@ -5266,7 +5342,343 @@
         <v>9</v>
       </c>
       <c r="H16" s="1" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="46" t="s">
+        <v>137</v>
+      </c>
+      <c r="B17" s="47" t="s">
+        <v>138</v>
+      </c>
+      <c r="C17" s="47" t="s">
+        <v>138</v>
+      </c>
+      <c r="D17" s="1">
+        <v>0</v>
+      </c>
+      <c r="E17" s="48"/>
+      <c r="F17" s="48"/>
+      <c r="G17" s="48"/>
+      <c r="H17" s="47" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" s="49" t="s">
+        <v>140</v>
+      </c>
+      <c r="B18" s="50" t="s">
+        <v>141</v>
+      </c>
+      <c r="C18" s="50" t="s">
+        <v>141</v>
+      </c>
+      <c r="D18" s="1">
+        <v>0</v>
+      </c>
+      <c r="E18" s="48"/>
+      <c r="F18" s="48"/>
+      <c r="G18" s="48"/>
+      <c r="H18" s="50" t="s">
+        <v>142</v>
+      </c>
+      <c r="I18" t="s">
         <v>234</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" s="49" t="s">
+        <v>143</v>
+      </c>
+      <c r="B19" s="50" t="s">
+        <v>144</v>
+      </c>
+      <c r="C19" s="50" t="s">
+        <v>144</v>
+      </c>
+      <c r="D19" s="1">
+        <v>0</v>
+      </c>
+      <c r="E19" s="48"/>
+      <c r="F19" s="48"/>
+      <c r="G19" s="48"/>
+      <c r="H19" s="50" t="s">
+        <v>235</v>
+      </c>
+      <c r="I19" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="51" t="s">
+        <v>146</v>
+      </c>
+      <c r="B20" s="52" t="s">
+        <v>147</v>
+      </c>
+      <c r="C20" s="52" t="s">
+        <v>147</v>
+      </c>
+      <c r="D20" s="1">
+        <v>0</v>
+      </c>
+      <c r="E20" s="48"/>
+      <c r="F20" s="48"/>
+      <c r="G20" s="48"/>
+      <c r="H20" s="52" t="s">
+        <v>237</v>
+      </c>
+      <c r="I20" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="51" t="s">
+        <v>149</v>
+      </c>
+      <c r="B21" s="52" t="s">
+        <v>150</v>
+      </c>
+      <c r="C21" s="52" t="s">
+        <v>150</v>
+      </c>
+      <c r="D21" s="1">
+        <v>0</v>
+      </c>
+      <c r="E21" s="48"/>
+      <c r="F21" s="48"/>
+      <c r="G21" s="48"/>
+      <c r="H21" s="48" t="s">
+        <v>199</v>
+      </c>
+      <c r="I21" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="51" t="s">
+        <v>152</v>
+      </c>
+      <c r="B22" s="52" t="s">
+        <v>153</v>
+      </c>
+      <c r="C22" s="52" t="s">
+        <v>153</v>
+      </c>
+      <c r="D22" s="1">
+        <v>0</v>
+      </c>
+      <c r="E22" s="48"/>
+      <c r="F22" s="48"/>
+      <c r="G22" s="48"/>
+      <c r="H22" s="52" t="s">
+        <v>154</v>
+      </c>
+      <c r="I22" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="49" t="s">
+        <v>155</v>
+      </c>
+      <c r="B23" s="50" t="s">
+        <v>156</v>
+      </c>
+      <c r="C23" s="50" t="s">
+        <v>156</v>
+      </c>
+      <c r="D23" s="1">
+        <v>0</v>
+      </c>
+      <c r="E23" s="48"/>
+      <c r="F23" s="48"/>
+      <c r="G23" s="48"/>
+      <c r="H23" s="50" t="s">
+        <v>240</v>
+      </c>
+      <c r="I23" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" s="49" t="s">
+        <v>158</v>
+      </c>
+      <c r="B24" s="50" t="s">
+        <v>159</v>
+      </c>
+      <c r="C24" s="50" t="s">
+        <v>159</v>
+      </c>
+      <c r="D24" s="1">
+        <v>0</v>
+      </c>
+      <c r="E24" s="48"/>
+      <c r="F24" s="48"/>
+      <c r="G24" s="48"/>
+      <c r="H24" s="50" t="s">
+        <v>241</v>
+      </c>
+      <c r="I24" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" s="49" t="s">
+        <v>161</v>
+      </c>
+      <c r="B25" s="50" t="s">
+        <v>162</v>
+      </c>
+      <c r="C25" s="50" t="s">
+        <v>162</v>
+      </c>
+      <c r="D25" s="1">
+        <v>0</v>
+      </c>
+      <c r="E25" s="48"/>
+      <c r="F25" s="48"/>
+      <c r="G25" s="48"/>
+      <c r="H25" s="47" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" s="49" t="s">
+        <v>164</v>
+      </c>
+      <c r="B26" s="50" t="s">
+        <v>165</v>
+      </c>
+      <c r="C26" s="50" t="s">
+        <v>165</v>
+      </c>
+      <c r="D26" s="1">
+        <v>0</v>
+      </c>
+      <c r="E26" s="48"/>
+      <c r="F26" s="48"/>
+      <c r="G26" s="48"/>
+      <c r="H26" s="50" t="s">
+        <v>166</v>
+      </c>
+      <c r="I26" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" s="49" t="s">
+        <v>167</v>
+      </c>
+      <c r="B27" s="50" t="s">
+        <v>168</v>
+      </c>
+      <c r="C27" s="50" t="s">
+        <v>168</v>
+      </c>
+      <c r="D27" s="1">
+        <v>0</v>
+      </c>
+      <c r="E27" s="48"/>
+      <c r="F27" s="48"/>
+      <c r="G27" s="48"/>
+      <c r="H27" s="50" t="s">
+        <v>244</v>
+      </c>
+      <c r="I27" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" s="49" t="s">
+        <v>170</v>
+      </c>
+      <c r="B28" s="50" t="s">
+        <v>171</v>
+      </c>
+      <c r="C28" s="50" t="s">
+        <v>171</v>
+      </c>
+      <c r="D28" s="1">
+        <v>0</v>
+      </c>
+      <c r="E28" s="48"/>
+      <c r="F28" s="48"/>
+      <c r="G28" s="48"/>
+      <c r="H28" s="50" t="s">
+        <v>172</v>
+      </c>
+      <c r="I28" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="B29" s="50" t="s">
+        <v>174</v>
+      </c>
+      <c r="C29" s="50" t="s">
+        <v>174</v>
+      </c>
+      <c r="D29" s="1">
+        <v>0</v>
+      </c>
+      <c r="E29" s="48"/>
+      <c r="F29" s="48"/>
+      <c r="G29" s="48"/>
+      <c r="H29" s="50" t="s">
+        <v>246</v>
+      </c>
+      <c r="I29" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" s="49" t="s">
+        <v>176</v>
+      </c>
+      <c r="B30" s="50" t="s">
+        <v>177</v>
+      </c>
+      <c r="C30" s="50" t="s">
+        <v>177</v>
+      </c>
+      <c r="D30" s="1">
+        <v>0</v>
+      </c>
+      <c r="E30" s="48"/>
+      <c r="F30" s="48"/>
+      <c r="G30" s="48"/>
+      <c r="H30" s="52" t="s">
+        <v>154</v>
+      </c>
+      <c r="I30" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" s="46" t="s">
+        <v>178</v>
+      </c>
+      <c r="B31" s="47" t="s">
+        <v>179</v>
+      </c>
+      <c r="C31" s="47" t="s">
+        <v>179</v>
+      </c>
+      <c r="D31" s="1">
+        <v>0</v>
+      </c>
+      <c r="E31" s="48"/>
+      <c r="F31" s="48"/>
+      <c r="G31" s="48"/>
+      <c r="H31" s="47" t="s">
+        <v>180</v>
       </c>
     </row>
   </sheetData>
@@ -5291,22 +5703,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="35" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="C1" s="35" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="D1" s="35" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="E1" s="35" t="s">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="F1" s="35" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="G1" s="35" t="s">
-        <v>240</v>
+        <v>252</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -5314,22 +5726,22 @@
         <v>5</v>
       </c>
       <c r="B2" s="37" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="C2" s="37" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D2" s="37" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="E2" s="37" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="F2" s="37" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="G2" s="38" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -5340,16 +5752,16 @@
         <v>10</v>
       </c>
       <c r="C3" s="37" t="s">
-        <v>73</v>
+        <v>105</v>
       </c>
       <c r="D3" s="37" t="s">
-        <v>73</v>
+        <v>105</v>
       </c>
       <c r="E3" s="37" t="s">
-        <v>73</v>
+        <v>105</v>
       </c>
       <c r="F3" s="37" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="G3" s="37" t="s">
         <v>10</v>
@@ -5357,10 +5769,10 @@
     </row>
     <row r="4" ht="14.25" spans="1:7">
       <c r="A4" s="39" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="B4" s="40" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="C4" s="39">
         <v>100</v>
@@ -5375,15 +5787,15 @@
         <v>1</v>
       </c>
       <c r="G4" s="39" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
     </row>
     <row r="5" ht="14.25" spans="1:7">
       <c r="A5" s="39" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="B5" s="40" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="C5" s="39">
         <v>100</v>
@@ -5398,15 +5810,15 @@
         <v>1</v>
       </c>
       <c r="G5" s="39" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
     </row>
     <row r="6" ht="14.25" spans="1:7">
       <c r="A6" s="39" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="B6" s="40" t="s">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="C6" s="39">
         <v>3</v>
@@ -5421,15 +5833,15 @@
         <v>1</v>
       </c>
       <c r="G6" s="39" t="s">
-        <v>255</v>
+        <v>267</v>
       </c>
     </row>
     <row r="7" ht="14.25" spans="1:7">
       <c r="A7" s="39" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="B7" s="40" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="C7" s="39">
         <v>3</v>
@@ -5444,12 +5856,12 @@
         <v>1</v>
       </c>
       <c r="G7" s="39" t="s">
-        <v>258</v>
+        <v>270</v>
       </c>
     </row>
     <row r="8" ht="14.25" spans="1:7">
       <c r="A8" s="39" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="B8" s="40" t="s">
         <v>8</v>
@@ -5467,15 +5879,15 @@
         <v>1</v>
       </c>
       <c r="G8" s="39" t="s">
-        <v>260</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" ht="14.25" spans="1:7">
       <c r="A9" s="39" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="B9" s="40" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="C9" s="39">
         <v>0</v>
@@ -5490,15 +5902,15 @@
         <v>1</v>
       </c>
       <c r="G9" s="39" t="s">
-        <v>263</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10" ht="14.25" spans="1:7">
       <c r="A10" s="39" t="s">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="B10" s="40" t="s">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="C10" s="39">
         <v>0</v>
@@ -5513,15 +5925,15 @@
         <v>1</v>
       </c>
       <c r="G10" s="39" t="s">
-        <v>266</v>
+        <v>278</v>
       </c>
     </row>
     <row r="11" ht="14.25" spans="1:7">
       <c r="A11" s="39" t="s">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="B11" s="40" t="s">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="C11" s="39">
         <v>0</v>
@@ -5536,15 +5948,15 @@
         <v>1</v>
       </c>
       <c r="G11" s="39" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
     </row>
     <row r="12" ht="14.25" spans="1:7">
       <c r="A12" s="39" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="B12" s="40" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="C12" s="39">
         <v>0</v>
@@ -5559,15 +5971,15 @@
         <v>1</v>
       </c>
       <c r="G12" s="39" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
     </row>
     <row r="13" ht="14.25" spans="1:7">
       <c r="A13" s="39" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="B13" s="40" t="s">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="C13" s="39">
         <v>0</v>
@@ -5582,15 +5994,15 @@
         <v>1</v>
       </c>
       <c r="G13" s="39" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
     </row>
     <row r="14" ht="14.25" spans="1:7">
       <c r="A14" s="39" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="B14" s="40" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C14" s="39">
         <v>0</v>
@@ -5605,7 +6017,7 @@
         <v>1</v>
       </c>
       <c r="G14" s="39" t="s">
-        <v>277</v>
+        <v>289</v>
       </c>
     </row>
   </sheetData>
@@ -5628,67 +6040,67 @@
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="R1" s="13" t="s">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="S1" s="3" t="s">
-        <v>294</v>
+        <v>306</v>
       </c>
       <c r="T1" s="3" t="s">
-        <v>295</v>
+        <v>307</v>
       </c>
       <c r="U1" s="3" t="s">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="V1" s="3" t="s">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="W1" s="14" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="X1" s="15"/>
       <c r="Y1" s="15"/>
@@ -5700,82 +6112,82 @@
         <v>5</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>299</v>
+        <v>311</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>300</v>
+        <v>312</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>302</v>
+        <v>238</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>305</v>
+        <v>316</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>306</v>
+        <v>317</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>307</v>
+        <v>318</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>308</v>
+        <v>319</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>310</v>
+        <v>321</v>
       </c>
       <c r="O2" s="5" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="P2" s="5" t="s">
-        <v>312</v>
+        <v>323</v>
       </c>
       <c r="Q2" s="5" t="s">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="R2" s="16" t="s">
-        <v>314</v>
+        <v>325</v>
       </c>
       <c r="S2" s="5" t="s">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="T2" s="5" t="s">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="U2" s="5" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="V2" s="5" t="s">
-        <v>316</v>
+        <v>327</v>
       </c>
       <c r="W2" s="17" t="s">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="X2" s="18" t="s">
-        <v>317</v>
+        <v>328</v>
       </c>
       <c r="Y2" s="32" t="s">
-        <v>318</v>
+        <v>329</v>
       </c>
       <c r="Z2" s="32" t="s">
-        <v>319</v>
+        <v>330</v>
       </c>
       <c r="AA2" s="33" t="s">
-        <v>320</v>
+        <v>331</v>
       </c>
     </row>
     <row r="3" ht="14.25" spans="1:27">
@@ -5866,7 +6278,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>321</v>
+        <v>332</v>
       </c>
       <c r="C4" s="9">
         <v>10</v>
@@ -5921,17 +6333,17 @@
       <c r="U4" s="9"/>
       <c r="V4" s="9"/>
       <c r="W4" s="23"/>
-      <c r="X4" s="57" t="s">
-        <v>322</v>
+      <c r="X4" s="65" t="s">
+        <v>333</v>
       </c>
       <c r="Y4" s="9" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="Z4" s="9" t="s">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="AA4" s="23" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
     </row>
     <row r="5" spans="1:27">
@@ -5939,7 +6351,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="C5" s="1">
         <v>10</v>
@@ -5995,16 +6407,16 @@
       <c r="V5" s="1"/>
       <c r="W5" s="26"/>
       <c r="X5" s="27" t="s">
-        <v>327</v>
+        <v>338</v>
       </c>
       <c r="Y5" s="1" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="Z5" s="1" t="s">
-        <v>328</v>
+        <v>339</v>
       </c>
       <c r="AA5" s="26" t="s">
-        <v>303</v>
+        <v>314</v>
       </c>
     </row>
     <row r="6" spans="1:27">
@@ -6012,7 +6424,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="C6" s="1">
         <v>10</v>
@@ -6068,16 +6480,16 @@
       <c r="V6" s="1"/>
       <c r="W6" s="26"/>
       <c r="X6" s="27" t="s">
-        <v>330</v>
+        <v>341</v>
       </c>
       <c r="Y6" s="1" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="Z6" s="1" t="s">
-        <v>331</v>
+        <v>342</v>
       </c>
       <c r="AA6" s="26" t="s">
-        <v>332</v>
+        <v>343</v>
       </c>
     </row>
     <row r="7" spans="1:27">
@@ -6085,7 +6497,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>333</v>
+        <v>344</v>
       </c>
       <c r="C7" s="1">
         <v>10</v>
@@ -6141,16 +6553,16 @@
       <c r="V7" s="1"/>
       <c r="W7" s="26"/>
       <c r="X7" s="27" t="s">
+        <v>345</v>
+      </c>
+      <c r="Y7" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="Y7" s="1" t="s">
-        <v>323</v>
-      </c>
       <c r="Z7" s="1" t="s">
-        <v>335</v>
+        <v>346</v>
       </c>
       <c r="AA7" s="26" t="s">
-        <v>336</v>
+        <v>347</v>
       </c>
     </row>
     <row r="8" spans="1:27">
@@ -6158,7 +6570,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>337</v>
+        <v>348</v>
       </c>
       <c r="C8" s="1">
         <v>10</v>
@@ -6214,16 +6626,16 @@
       <c r="V8" s="1"/>
       <c r="W8" s="26"/>
       <c r="X8" s="27" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
       <c r="Y8" s="1" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="Z8" s="1" t="s">
-        <v>339</v>
+        <v>350</v>
       </c>
       <c r="AA8" s="26" t="s">
-        <v>340</v>
+        <v>351</v>
       </c>
     </row>
     <row r="9" spans="1:27">
@@ -6231,7 +6643,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>341</v>
+        <v>352</v>
       </c>
       <c r="C9" s="1">
         <v>10</v>
@@ -6287,16 +6699,16 @@
       <c r="V9" s="1"/>
       <c r="W9" s="26"/>
       <c r="X9" s="27" t="s">
-        <v>342</v>
+        <v>353</v>
       </c>
       <c r="Y9" s="1" t="s">
-        <v>343</v>
+        <v>354</v>
       </c>
       <c r="Z9" s="1" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AA9" s="26" t="s">
-        <v>345</v>
+        <v>356</v>
       </c>
     </row>
     <row r="10" spans="1:27">
@@ -6304,7 +6716,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>346</v>
+        <v>357</v>
       </c>
       <c r="C10" s="1">
         <v>10</v>
@@ -6360,16 +6772,16 @@
       <c r="V10" s="1"/>
       <c r="W10" s="26"/>
       <c r="X10" s="27" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="Y10" s="1" t="s">
-        <v>348</v>
+        <v>359</v>
       </c>
       <c r="Z10" s="1" t="s">
-        <v>349</v>
+        <v>360</v>
       </c>
       <c r="AA10" s="26" t="s">
-        <v>350</v>
+        <v>361</v>
       </c>
     </row>
     <row r="11" spans="1:27">
@@ -6377,7 +6789,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="C11" s="1">
         <v>10</v>
@@ -6433,16 +6845,16 @@
       <c r="V11" s="1"/>
       <c r="W11" s="26"/>
       <c r="X11" s="27" t="s">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="Y11" s="1" t="s">
-        <v>352</v>
+        <v>363</v>
       </c>
       <c r="Z11" s="1" t="s">
-        <v>353</v>
+        <v>364</v>
       </c>
       <c r="AA11" s="26" t="s">
-        <v>354</v>
+        <v>365</v>
       </c>
     </row>
     <row r="12" spans="1:27">
@@ -6450,7 +6862,7 @@
         <v>9</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="C12" s="1">
         <v>10</v>
@@ -6506,16 +6918,16 @@
       <c r="V12" s="1"/>
       <c r="W12" s="26"/>
       <c r="X12" s="27" t="s">
-        <v>356</v>
+        <v>367</v>
       </c>
       <c r="Y12" s="1" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
       <c r="Z12" s="1" t="s">
-        <v>358</v>
+        <v>369</v>
       </c>
       <c r="AA12" s="26" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
     </row>
     <row r="13" spans="1:27">
@@ -6523,7 +6935,7 @@
         <v>10</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>360</v>
+        <v>371</v>
       </c>
       <c r="C13" s="1">
         <v>10</v>
@@ -6579,16 +6991,16 @@
       <c r="V13" s="1"/>
       <c r="W13" s="26"/>
       <c r="X13" s="27" t="s">
-        <v>361</v>
+        <v>372</v>
       </c>
       <c r="Y13" s="1" t="s">
-        <v>352</v>
+        <v>363</v>
       </c>
       <c r="Z13" s="1" t="s">
-        <v>362</v>
+        <v>373</v>
       </c>
       <c r="AA13" s="26" t="s">
-        <v>363</v>
+        <v>374</v>
       </c>
     </row>
     <row r="14" spans="1:27">
@@ -6596,7 +7008,7 @@
         <v>11</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="C14" s="1">
         <v>10</v>
@@ -6652,16 +7064,16 @@
       <c r="V14" s="1"/>
       <c r="W14" s="26"/>
       <c r="X14" s="27" t="s">
-        <v>365</v>
+        <v>376</v>
       </c>
       <c r="Y14" s="1" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="Z14" s="1" t="s">
-        <v>367</v>
+        <v>378</v>
       </c>
       <c r="AA14" s="26" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
     </row>
     <row r="15" spans="1:27">
@@ -6669,7 +7081,7 @@
         <v>12</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="C15" s="1">
         <v>10</v>
@@ -6725,16 +7137,16 @@
       <c r="V15" s="1"/>
       <c r="W15" s="26"/>
       <c r="X15" s="27" t="s">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="Y15" s="1" t="s">
-        <v>371</v>
+        <v>382</v>
       </c>
       <c r="Z15" s="1" t="s">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c r="AA15" s="26" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
     </row>
     <row r="16" spans="1:27">
@@ -6742,7 +7154,7 @@
         <v>13</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c r="C16" s="1">
         <v>10</v>
@@ -6798,16 +7210,16 @@
       <c r="V16" s="1"/>
       <c r="W16" s="26"/>
       <c r="X16" s="27" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="Y16" s="1" t="s">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="Z16" s="1" t="s">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="AA16" s="26" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
     </row>
     <row r="17" spans="1:27">
@@ -6815,7 +7227,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="C17" s="1">
         <v>10</v>
@@ -6871,16 +7283,16 @@
       <c r="V17" s="1"/>
       <c r="W17" s="26"/>
       <c r="X17" s="27" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="Y17" s="1" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="Z17" s="1" t="s">
-        <v>380</v>
+        <v>391</v>
       </c>
       <c r="AA17" s="26" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
     </row>
     <row r="18" spans="1:27">
@@ -6888,7 +7300,7 @@
         <v>15</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>382</v>
+        <v>393</v>
       </c>
       <c r="C18" s="1">
         <v>10</v>
@@ -6944,16 +7356,16 @@
       <c r="V18" s="1"/>
       <c r="W18" s="26"/>
       <c r="X18" s="27" t="s">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="Y18" s="1" t="s">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="Z18" s="1" t="s">
-        <v>385</v>
+        <v>396</v>
       </c>
       <c r="AA18" s="26" t="s">
-        <v>303</v>
+        <v>314</v>
       </c>
     </row>
     <row r="19" spans="1:27">
@@ -6961,7 +7373,7 @@
         <v>16</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
       <c r="C19" s="1">
         <v>10</v>
@@ -7017,16 +7429,16 @@
       <c r="V19" s="1"/>
       <c r="W19" s="26"/>
       <c r="X19" s="27" t="s">
-        <v>387</v>
+        <v>398</v>
       </c>
       <c r="Y19" s="1" t="s">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="Z19" s="1" t="s">
-        <v>389</v>
+        <v>400</v>
       </c>
       <c r="AA19" s="26" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
     </row>
     <row r="20" spans="1:27">
@@ -7034,7 +7446,7 @@
         <v>17</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>390</v>
+        <v>401</v>
       </c>
       <c r="C20" s="1">
         <v>10</v>
@@ -7090,16 +7502,16 @@
       <c r="V20" s="1"/>
       <c r="W20" s="26"/>
       <c r="X20" s="27" t="s">
-        <v>391</v>
+        <v>402</v>
       </c>
       <c r="Y20" s="1" t="s">
-        <v>392</v>
+        <v>403</v>
       </c>
       <c r="Z20" s="1" t="s">
-        <v>393</v>
+        <v>404</v>
       </c>
       <c r="AA20" s="26" t="s">
-        <v>301</v>
+        <v>313</v>
       </c>
     </row>
     <row r="21" spans="1:27">
@@ -7107,7 +7519,7 @@
         <v>18</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>394</v>
+        <v>405</v>
       </c>
       <c r="C21" s="1">
         <v>10</v>
@@ -7163,16 +7575,16 @@
       <c r="V21" s="1"/>
       <c r="W21" s="26"/>
       <c r="X21" s="27" t="s">
-        <v>395</v>
+        <v>406</v>
       </c>
       <c r="Y21" s="1" t="s">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="Z21" s="1" t="s">
-        <v>397</v>
+        <v>408</v>
       </c>
       <c r="AA21" s="26" t="s">
-        <v>314</v>
+        <v>325</v>
       </c>
     </row>
     <row r="22" spans="1:27">
@@ -7180,7 +7592,7 @@
         <v>19</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>398</v>
+        <v>409</v>
       </c>
       <c r="C22" s="1">
         <v>10</v>
@@ -7236,16 +7648,16 @@
       <c r="V22" s="1"/>
       <c r="W22" s="26"/>
       <c r="X22" s="27" t="s">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="Y22" s="1" t="s">
-        <v>400</v>
+        <v>411</v>
       </c>
       <c r="Z22" s="1" t="s">
-        <v>401</v>
+        <v>412</v>
       </c>
       <c r="AA22" s="26" t="s">
-        <v>402</v>
+        <v>413</v>
       </c>
     </row>
     <row r="23" spans="1:27">
@@ -7253,7 +7665,7 @@
         <v>20</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>403</v>
+        <v>414</v>
       </c>
       <c r="C23" s="1">
         <v>10</v>
@@ -7309,16 +7721,16 @@
       <c r="V23" s="1"/>
       <c r="W23" s="26"/>
       <c r="X23" s="27" t="s">
-        <v>404</v>
+        <v>415</v>
       </c>
       <c r="Y23" s="1" t="s">
-        <v>405</v>
+        <v>416</v>
       </c>
       <c r="Z23" s="1" t="s">
-        <v>406</v>
+        <v>417</v>
       </c>
       <c r="AA23" s="26" t="s">
-        <v>407</v>
+        <v>418</v>
       </c>
     </row>
     <row r="24" spans="1:27">
@@ -7326,7 +7738,7 @@
         <v>21</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>408</v>
+        <v>419</v>
       </c>
       <c r="C24" s="1">
         <v>10</v>
@@ -7382,16 +7794,16 @@
       <c r="V24" s="1"/>
       <c r="W24" s="26"/>
       <c r="X24" s="27" t="s">
-        <v>409</v>
+        <v>420</v>
       </c>
       <c r="Y24" s="1" t="s">
-        <v>410</v>
+        <v>421</v>
       </c>
       <c r="Z24" s="1" t="s">
-        <v>411</v>
+        <v>422</v>
       </c>
       <c r="AA24" s="26" t="s">
-        <v>412</v>
+        <v>423</v>
       </c>
     </row>
     <row r="25" spans="1:27">
@@ -7399,7 +7811,7 @@
         <v>22</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>413</v>
+        <v>424</v>
       </c>
       <c r="C25" s="1">
         <v>10</v>
@@ -7455,16 +7867,16 @@
       <c r="V25" s="1"/>
       <c r="W25" s="26"/>
       <c r="X25" s="27" t="s">
-        <v>414</v>
+        <v>425</v>
       </c>
       <c r="Y25" s="1" t="s">
-        <v>415</v>
+        <v>426</v>
       </c>
       <c r="Z25" s="1" t="s">
-        <v>416</v>
+        <v>427</v>
       </c>
       <c r="AA25" s="26" t="s">
-        <v>308</v>
+        <v>319</v>
       </c>
     </row>
     <row r="26" spans="1:27">
@@ -7472,7 +7884,7 @@
         <v>23</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>417</v>
+        <v>428</v>
       </c>
       <c r="C26" s="1">
         <v>10</v>
@@ -7528,16 +7940,16 @@
       <c r="V26" s="1"/>
       <c r="W26" s="26"/>
       <c r="X26" s="27" t="s">
-        <v>418</v>
+        <v>429</v>
       </c>
       <c r="Y26" s="1" t="s">
-        <v>419</v>
+        <v>430</v>
       </c>
       <c r="Z26" s="1" t="s">
-        <v>420</v>
+        <v>431</v>
       </c>
       <c r="AA26" s="26" t="s">
-        <v>421</v>
+        <v>432</v>
       </c>
     </row>
     <row r="27" spans="1:27">
@@ -7545,7 +7957,7 @@
         <v>24</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>422</v>
+        <v>433</v>
       </c>
       <c r="C27" s="1">
         <v>10</v>
@@ -7601,16 +8013,16 @@
       <c r="V27" s="1"/>
       <c r="W27" s="26"/>
       <c r="X27" s="27" t="s">
-        <v>423</v>
+        <v>434</v>
       </c>
       <c r="Y27" s="1" t="s">
-        <v>424</v>
+        <v>435</v>
       </c>
       <c r="Z27" s="1" t="s">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="AA27" s="26" t="s">
-        <v>426</v>
+        <v>437</v>
       </c>
     </row>
     <row r="28" spans="1:27">
@@ -7618,7 +8030,7 @@
         <v>25</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="C28" s="1">
         <v>10</v>
@@ -7674,16 +8086,16 @@
       <c r="V28" s="1"/>
       <c r="W28" s="26"/>
       <c r="X28" s="27" t="s">
-        <v>428</v>
+        <v>439</v>
       </c>
       <c r="Y28" s="1" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="Z28" s="1" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="AA28" s="26" t="s">
-        <v>431</v>
+        <v>442</v>
       </c>
     </row>
     <row r="29" spans="1:27">
@@ -7691,7 +8103,7 @@
         <v>26</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>432</v>
+        <v>443</v>
       </c>
       <c r="C29" s="1">
         <v>10</v>
@@ -7747,16 +8159,16 @@
       <c r="V29" s="1"/>
       <c r="W29" s="26"/>
       <c r="X29" s="27" t="s">
-        <v>433</v>
+        <v>444</v>
       </c>
       <c r="Y29" s="1" t="s">
-        <v>434</v>
+        <v>445</v>
       </c>
       <c r="Z29" s="1" t="s">
-        <v>435</v>
+        <v>446</v>
       </c>
       <c r="AA29" s="26" t="s">
-        <v>436</v>
+        <v>447</v>
       </c>
     </row>
     <row r="30" spans="1:27">
@@ -7764,7 +8176,7 @@
         <v>27</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>437</v>
+        <v>448</v>
       </c>
       <c r="C30" s="1">
         <v>10</v>
@@ -7820,16 +8232,16 @@
       <c r="V30" s="1"/>
       <c r="W30" s="26"/>
       <c r="X30" s="27" t="s">
-        <v>438</v>
+        <v>449</v>
       </c>
       <c r="Y30" s="1" t="s">
-        <v>439</v>
+        <v>450</v>
       </c>
       <c r="Z30" s="1" t="s">
-        <v>440</v>
+        <v>451</v>
       </c>
       <c r="AA30" s="26" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
     </row>
     <row r="31" spans="1:27">
@@ -7837,7 +8249,7 @@
         <v>28</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>441</v>
+        <v>452</v>
       </c>
       <c r="C31" s="1">
         <v>10</v>
@@ -7893,16 +8305,16 @@
       <c r="V31" s="1"/>
       <c r="W31" s="26"/>
       <c r="X31" s="27" t="s">
-        <v>442</v>
+        <v>453</v>
       </c>
       <c r="Y31" s="1" t="s">
-        <v>443</v>
+        <v>454</v>
       </c>
       <c r="Z31" s="1" t="s">
-        <v>444</v>
+        <v>455</v>
       </c>
       <c r="AA31" s="26" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
     </row>
     <row r="32" spans="1:27">
@@ -7910,7 +8322,7 @@
         <v>29</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>445</v>
+        <v>456</v>
       </c>
       <c r="C32" s="1">
         <v>10</v>
@@ -7966,16 +8378,16 @@
       <c r="V32" s="1"/>
       <c r="W32" s="26"/>
       <c r="X32" s="27" t="s">
-        <v>446</v>
+        <v>457</v>
       </c>
       <c r="Y32" s="1" t="s">
-        <v>447</v>
+        <v>458</v>
       </c>
       <c r="Z32" s="1" t="s">
-        <v>448</v>
+        <v>459</v>
       </c>
       <c r="AA32" s="26" t="s">
-        <v>449</v>
+        <v>460</v>
       </c>
     </row>
     <row r="33" spans="1:27">
@@ -7983,7 +8395,7 @@
         <v>30</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>450</v>
+        <v>461</v>
       </c>
       <c r="C33" s="1">
         <v>10</v>
@@ -8039,16 +8451,16 @@
       <c r="V33" s="1"/>
       <c r="W33" s="26"/>
       <c r="X33" s="27" t="s">
-        <v>451</v>
+        <v>462</v>
       </c>
       <c r="Y33" s="1" t="s">
-        <v>452</v>
+        <v>463</v>
       </c>
       <c r="Z33" s="1" t="s">
-        <v>453</v>
+        <v>464</v>
       </c>
       <c r="AA33" s="26" t="s">
-        <v>454</v>
+        <v>465</v>
       </c>
     </row>
     <row r="34" spans="1:27">
@@ -8056,7 +8468,7 @@
         <v>31</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>455</v>
+        <v>466</v>
       </c>
       <c r="C34" s="1">
         <v>10</v>
@@ -8112,16 +8524,16 @@
       <c r="V34" s="1"/>
       <c r="W34" s="26"/>
       <c r="X34" s="27" t="s">
-        <v>456</v>
+        <v>467</v>
       </c>
       <c r="Y34" s="1" t="s">
-        <v>457</v>
+        <v>468</v>
       </c>
       <c r="Z34" s="1" t="s">
-        <v>458</v>
+        <v>469</v>
       </c>
       <c r="AA34" s="26" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
     </row>
     <row r="35" spans="1:27">
@@ -8129,7 +8541,7 @@
         <v>32</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>459</v>
+        <v>470</v>
       </c>
       <c r="C35" s="1">
         <v>10</v>
@@ -8185,16 +8597,16 @@
       <c r="V35" s="1"/>
       <c r="W35" s="26"/>
       <c r="X35" s="27" t="s">
-        <v>460</v>
+        <v>471</v>
       </c>
       <c r="Y35" s="1" t="s">
-        <v>461</v>
+        <v>472</v>
       </c>
       <c r="Z35" s="1" t="s">
-        <v>462</v>
+        <v>473</v>
       </c>
       <c r="AA35" s="26" t="s">
-        <v>463</v>
+        <v>474</v>
       </c>
     </row>
     <row r="36" spans="1:27">
@@ -8202,7 +8614,7 @@
         <v>33</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>464</v>
+        <v>475</v>
       </c>
       <c r="C36" s="1">
         <v>10</v>
@@ -8258,16 +8670,16 @@
       <c r="V36" s="1"/>
       <c r="W36" s="26"/>
       <c r="X36" s="27" t="s">
-        <v>465</v>
+        <v>476</v>
       </c>
       <c r="Y36" s="1" t="s">
-        <v>466</v>
+        <v>477</v>
       </c>
       <c r="Z36" s="1" t="s">
-        <v>467</v>
+        <v>478</v>
       </c>
       <c r="AA36" s="26" t="s">
-        <v>468</v>
+        <v>479</v>
       </c>
     </row>
     <row r="37" spans="1:27">
@@ -8275,7 +8687,7 @@
         <v>34</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>469</v>
+        <v>480</v>
       </c>
       <c r="C37" s="1">
         <v>10</v>
@@ -8331,16 +8743,16 @@
       <c r="V37" s="1"/>
       <c r="W37" s="26"/>
       <c r="X37" s="27" t="s">
-        <v>470</v>
+        <v>481</v>
       </c>
       <c r="Y37" s="1" t="s">
-        <v>471</v>
+        <v>482</v>
       </c>
       <c r="Z37" s="1" t="s">
-        <v>472</v>
+        <v>483</v>
       </c>
       <c r="AA37" s="26" t="s">
-        <v>473</v>
+        <v>484</v>
       </c>
     </row>
     <row r="38" spans="1:27">
@@ -8348,7 +8760,7 @@
         <v>35</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>474</v>
+        <v>485</v>
       </c>
       <c r="C38" s="1">
         <v>10</v>
@@ -8404,16 +8816,16 @@
       <c r="V38" s="1"/>
       <c r="W38" s="26"/>
       <c r="X38" s="27" t="s">
-        <v>475</v>
+        <v>486</v>
       </c>
       <c r="Y38" s="1" t="s">
-        <v>476</v>
+        <v>487</v>
       </c>
       <c r="Z38" s="1" t="s">
-        <v>477</v>
+        <v>488</v>
       </c>
       <c r="AA38" s="26" t="s">
-        <v>478</v>
+        <v>489</v>
       </c>
     </row>
     <row r="39" spans="1:27">
@@ -8421,7 +8833,7 @@
         <v>36</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>479</v>
+        <v>490</v>
       </c>
       <c r="C39" s="1">
         <v>10</v>
@@ -8477,16 +8889,16 @@
       <c r="V39" s="1"/>
       <c r="W39" s="26"/>
       <c r="X39" s="27" t="s">
-        <v>480</v>
+        <v>491</v>
       </c>
       <c r="Y39" s="1" t="s">
-        <v>481</v>
+        <v>492</v>
       </c>
       <c r="Z39" s="1" t="s">
-        <v>482</v>
+        <v>493</v>
       </c>
       <c r="AA39" s="26" t="s">
-        <v>483</v>
+        <v>494</v>
       </c>
     </row>
     <row r="40" spans="1:27">
@@ -8494,7 +8906,7 @@
         <v>37</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>484</v>
+        <v>495</v>
       </c>
       <c r="C40" s="1">
         <v>10</v>
@@ -8550,16 +8962,16 @@
       <c r="V40" s="1"/>
       <c r="W40" s="26"/>
       <c r="X40" s="27" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="Y40" s="1" t="s">
-        <v>486</v>
+        <v>497</v>
       </c>
       <c r="Z40" s="1" t="s">
-        <v>487</v>
+        <v>498</v>
       </c>
       <c r="AA40" s="26" t="s">
-        <v>310</v>
+        <v>321</v>
       </c>
     </row>
     <row r="41" ht="14.25" spans="1:27">
@@ -8567,7 +8979,7 @@
         <v>38</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>488</v>
+        <v>499</v>
       </c>
       <c r="C41" s="12">
         <v>10</v>
@@ -8623,16 +9035,16 @@
       <c r="V41" s="12"/>
       <c r="W41" s="29"/>
       <c r="X41" s="30" t="s">
-        <v>489</v>
+        <v>500</v>
       </c>
       <c r="Y41" s="12" t="s">
-        <v>490</v>
+        <v>501</v>
       </c>
       <c r="Z41" s="12" t="s">
-        <v>491</v>
+        <v>502</v>
       </c>
       <c r="AA41" s="29" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
     </row>
   </sheetData>

--- a/xlsdir/配置-总表.xlsx
+++ b/xlsdir/配置-总表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="673" firstSheet="3" activeTab="6"/>
+    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="673" firstSheet="3" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="character|角色" sheetId="32" r:id="rId1"/>
@@ -12,11 +12,12 @@
     <sheet name="hero|玩家角色" sheetId="27" r:id="rId3"/>
     <sheet name="monster|魔物" sheetId="28" r:id="rId4"/>
     <sheet name="card|卡牌" sheetId="29" r:id="rId5"/>
-    <sheet name="intent|意图" sheetId="38" r:id="rId6"/>
-    <sheet name="ability_effect|技能效果" sheetId="34" r:id="rId7"/>
-    <sheet name="attribute|属性" sheetId="35" r:id="rId8"/>
-    <sheet name="Sheet1" sheetId="11" r:id="rId9"/>
-    <sheet name="sheet2" sheetId="30" r:id="rId10"/>
+    <sheet name="buff|增益" sheetId="39" r:id="rId6"/>
+    <sheet name="intent|意图" sheetId="38" r:id="rId7"/>
+    <sheet name="ability_effect|技能效果" sheetId="34" r:id="rId8"/>
+    <sheet name="attribute|属性" sheetId="35" r:id="rId9"/>
+    <sheet name="Sheet1" sheetId="11" r:id="rId10"/>
+    <sheet name="sheet2" sheetId="30" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'monster|魔物'!$A$1:$B$4</definedName>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="781" uniqueCount="515">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="810" uniqueCount="535">
   <si>
     <t>ID</t>
   </si>
@@ -231,6 +232,9 @@
   </si>
   <si>
     <t>effects</t>
+  </si>
+  <si>
+    <t>buff_des</t>
   </si>
   <si>
     <t>卡牌名</t>
@@ -262,6 +266,9 @@
     <t>效果ID列表</t>
   </si>
   <si>
+    <t>BUFF描述</t>
+  </si>
+  <si>
     <t>texture</t>
   </si>
   <si>
@@ -286,7 +293,7 @@
     <t>防御</t>
   </si>
   <si>
-    <t>获得5点护甲</t>
+    <t>获得5点[color=yellow]格挡[/color]</t>
   </si>
   <si>
     <t>res://asserts/textures/cards/card_icons/card_defense.png</t>
@@ -298,13 +305,16 @@
     <t>shielded</t>
   </si>
   <si>
+    <t>block</t>
+  </si>
+  <si>
     <t>trounce</t>
   </si>
   <si>
     <t>痛击</t>
   </si>
   <si>
-    <t>造成8点伤害，给与2层易伤</t>
+    <t>造成8点伤害，给与2层[color=yellow]易伤[/color]</t>
   </si>
   <si>
     <t>res://asserts/textures/cards/card_icons/card_trounce.png</t>
@@ -313,6 +323,51 @@
     <t>trounce_01*trounce_02</t>
   </si>
   <si>
+    <t>vulnerable</t>
+  </si>
+  <si>
+    <t>效果名</t>
+  </si>
+  <si>
+    <t>格挡</t>
+  </si>
+  <si>
+    <t>持续到下一个回合开始之前，格挡伤害</t>
+  </si>
+  <si>
+    <t>易伤</t>
+  </si>
+  <si>
+    <t>使目标收到的攻击伤害增加</t>
+  </si>
+  <si>
+    <t>weak</t>
+  </si>
+  <si>
+    <t>虚弱</t>
+  </si>
+  <si>
+    <t>降低目标的攻击伤害</t>
+  </si>
+  <si>
+    <t>poison</t>
+  </si>
+  <si>
+    <t>中毒</t>
+  </si>
+  <si>
+    <t>每个回合结束时，根据层数对目标造成伤害</t>
+  </si>
+  <si>
+    <t>entangled</t>
+  </si>
+  <si>
+    <t>缠绕</t>
+  </si>
+  <si>
+    <t>目标在下一个回合无法攻击</t>
+  </si>
+  <si>
     <t>owner</t>
   </si>
   <si>
@@ -373,7 +428,7 @@
     <t>敌人打算进行攻击。</t>
   </si>
   <si>
-    <t>res://asserts/textures/widgets/Spells/poison_dagger.png</t>
+    <t>res://asserts/textures/widgets/Buffs/poison_dagger.png</t>
   </si>
   <si>
     <t>MULTI_ATTACK</t>
@@ -385,7 +440,7 @@
     <t>敌人计划多次攻击。</t>
   </si>
   <si>
-    <t>res://asserts/textures/widgets/Spells/thorn_vine_spell.png</t>
+    <t>res://asserts/textures/widgets/Buffs/thorn_vine_spell.png</t>
   </si>
   <si>
     <t>DEFEND</t>
@@ -394,7 +449,7 @@
     <t>敌人将增加防御力</t>
   </si>
   <si>
-    <t>res://asserts/textures/widgets/Spells/healing_spell.png</t>
+    <t>res://asserts/textures/widgets/Buffs/healing_spell.png</t>
   </si>
   <si>
     <t>BUFF</t>
@@ -406,7 +461,7 @@
     <t>敌人将提升某项能力，如攻击力、防御力或特殊能力。</t>
   </si>
   <si>
-    <t>res://asserts/textures/widgets/Debuffs/on_fire_(burning).png</t>
+    <t>res://asserts/textures/widgets/Buffs/on_fire_(burning).png</t>
   </si>
   <si>
     <t>DEBUFF</t>
@@ -418,7 +473,7 @@
     <t>敌人计划施放会削弱玩家能力的效果，如减少玩家的攻击力或防御力。</t>
   </si>
   <si>
-    <t>res://asserts/textures/widgets/Debuffs/disarmed.png</t>
+    <t>res://asserts/textures/widgets/Buffs/disarmed.png</t>
   </si>
   <si>
     <t>HEAL</t>
@@ -442,7 +497,7 @@
     <t>敌人将采取某种特殊行动，如召唤援助、准备强力攻击或其他战术动作。</t>
   </si>
   <si>
-    <t>res://asserts/textures/widgets/Debuffs/confused.png</t>
+    <t>res://asserts/textures/widgets/Buffs/confused.png</t>
   </si>
   <si>
     <t>ESCAPE</t>
@@ -460,10 +515,13 @@
     <t>split</t>
   </si>
   <si>
-    <t>分裂</t>
-  </si>
-  <si>
-    <t>史莱姆分裂成两个较小的实体，增加战斗中的敌人数量。</t>
+    <t>脆弱</t>
+  </si>
+  <si>
+    <t>目标下一回合获得的护甲值降低25%</t>
+  </si>
+  <si>
+    <t>res://asserts/textures/widgets/Buffs/ghost_form_(physical_damage_immunity).png</t>
   </si>
   <si>
     <t>absorb</t>
@@ -475,15 +533,45 @@
     <t>回复一定量的生命值，吸收的量取决于其当前生命值。</t>
   </si>
   <si>
+    <t>res://asserts/textures/widgets/Buffs/summoning_spell.png</t>
+  </si>
+  <si>
     <t>entangle</t>
   </si>
   <si>
-    <t>缠绕</t>
-  </si>
-  <si>
     <t>降低玩家下一回合的行动点数。</t>
   </si>
   <si>
+    <t>toxin_spray</t>
+  </si>
+  <si>
+    <t>毒素喷射</t>
+  </si>
+  <si>
+    <t>造成持续性的毒素伤害。</t>
+  </si>
+  <si>
+    <t>res://asserts/textures/widgets/Buffs/poisoned.png</t>
+  </si>
+  <si>
+    <t>healing_spore</t>
+  </si>
+  <si>
+    <t>治疗孢子</t>
+  </si>
+  <si>
+    <t>为自己或其他敌人恢复生命值。</t>
+  </si>
+  <si>
+    <t>hallucinogenic_spore</t>
+  </si>
+  <si>
+    <t>迷幻孢子</t>
+  </si>
+  <si>
+    <t>玩家获得“混乱”卡牌。</t>
+  </si>
+  <si>
     <t>destruction_ray</t>
   </si>
   <si>
@@ -536,33 +624,6 @@
   </si>
   <si>
     <t>如果玩家生命值低，造成额外伤害。</t>
-  </si>
-  <si>
-    <t>toxin_spray</t>
-  </si>
-  <si>
-    <t>毒素喷射</t>
-  </si>
-  <si>
-    <t>造成持续性的毒素伤害。</t>
-  </si>
-  <si>
-    <t>healing_spore</t>
-  </si>
-  <si>
-    <t>治疗孢子</t>
-  </si>
-  <si>
-    <t>为自己或其他敌人恢复生命值。</t>
-  </si>
-  <si>
-    <t>hallucinogenic_spore</t>
-  </si>
-  <si>
-    <t>迷幻孢子</t>
-  </si>
-  <si>
-    <t>玩家获得“混乱”卡牌。</t>
   </si>
   <si>
     <t>heavy_strike</t>
@@ -665,9 +726,6 @@
     <t>易伤（Vulnerable）</t>
   </si>
   <si>
-    <t>易伤</t>
-  </si>
-  <si>
     <t>目标受到的伤害增加50%。</t>
   </si>
   <si>
@@ -686,9 +744,6 @@
     <t>中毒（Poisoned）</t>
   </si>
   <si>
-    <t>中毒</t>
-  </si>
-  <si>
     <t>在目标的回合开始时，中毒将造成等同于其堆叠数的伤害，并减少1点堆叠数。</t>
   </si>
   <si>
@@ -761,6 +816,12 @@
     <t>目标在下一回合无法行动。</t>
   </si>
   <si>
+    <t>分裂</t>
+  </si>
+  <si>
+    <t>史莱姆分裂成两个较小的实体，增加战斗中的敌人数量。</t>
+  </si>
+  <si>
     <t>恢复</t>
   </si>
   <si>
@@ -770,6 +831,15 @@
     <t>减少行动点数</t>
   </si>
   <si>
+    <t>放毒</t>
+  </si>
+  <si>
+    <t>所有人恢复10点生命值。</t>
+  </si>
+  <si>
+    <t>给与卡牌</t>
+  </si>
+  <si>
     <t>对玩家造成10点伤害</t>
   </si>
   <si>
@@ -786,15 +856,6 @@
   </si>
   <si>
     <t>蓄力</t>
-  </si>
-  <si>
-    <t>放毒</t>
-  </si>
-  <si>
-    <t>所有人恢复10点生命值。</t>
-  </si>
-  <si>
-    <t>给与卡牌</t>
   </si>
   <si>
     <t>造成15点伤害</t>
@@ -1908,7 +1969,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1923,13 +1984,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.25"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="2" tint="-0.1"/>
+        <fgColor theme="3" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2600,7 +2667,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="27" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="27" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2624,16 +2691,16 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="30" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="30" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="32" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="30" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="30" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="32" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="33" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -2642,89 +2709,89 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="34" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2851,6 +2918,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -2860,22 +2930,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2884,7 +2942,22 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2899,16 +2972,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3295,13 +3374,13 @@
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="42" t="s">
+      <c r="C2" s="43" t="s">
         <v>7</v>
       </c>
       <c r="D2" s="5" t="s">
@@ -3439,12 +3518,3039 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
+  <dimension ref="A1:AA41"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetData>
+    <row r="1" ht="14.25" spans="1:27">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="R1" s="13" t="s">
+        <v>325</v>
+      </c>
+      <c r="S1" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="T1" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="U1" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="V1" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="W1" s="14" t="s">
+        <v>330</v>
+      </c>
+      <c r="X1" s="15"/>
+      <c r="Y1" s="15"/>
+      <c r="Z1" s="15"/>
+      <c r="AA1" s="31"/>
+    </row>
+    <row r="2" ht="14.25" spans="1:27">
+      <c r="A2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>337</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>338</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="O2" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="P2" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="Q2" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="R2" s="16" t="s">
+        <v>345</v>
+      </c>
+      <c r="S2" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="T2" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="U2" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="V2" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="W2" s="17" t="s">
+        <v>344</v>
+      </c>
+      <c r="X2" s="18" t="s">
+        <v>348</v>
+      </c>
+      <c r="Y2" s="32" t="s">
+        <v>349</v>
+      </c>
+      <c r="Z2" s="32" t="s">
+        <v>350</v>
+      </c>
+      <c r="AA2" s="33" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="3" ht="14.25" spans="1:27">
+      <c r="A3" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="L3" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="M3" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="N3" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="O3" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="P3" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q3" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="R3" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="S3" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="T3" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="U3" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="V3" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="W3" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="X3" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y3" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z3" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA3" s="34" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27">
+      <c r="A4" s="8">
+        <v>1</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>352</v>
+      </c>
+      <c r="C4" s="9">
+        <v>10</v>
+      </c>
+      <c r="D4" s="9">
+        <v>0</v>
+      </c>
+      <c r="E4" s="9">
+        <v>0</v>
+      </c>
+      <c r="F4" s="9">
+        <v>10</v>
+      </c>
+      <c r="G4" s="9">
+        <v>0</v>
+      </c>
+      <c r="H4" s="9">
+        <v>0</v>
+      </c>
+      <c r="I4" s="9">
+        <v>0</v>
+      </c>
+      <c r="J4" s="9">
+        <v>2</v>
+      </c>
+      <c r="K4" s="9">
+        <v>1</v>
+      </c>
+      <c r="L4" s="9">
+        <v>0</v>
+      </c>
+      <c r="M4" s="9">
+        <v>0</v>
+      </c>
+      <c r="N4" s="9">
+        <v>0</v>
+      </c>
+      <c r="O4" s="9">
+        <v>0</v>
+      </c>
+      <c r="P4" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="9">
+        <v>0</v>
+      </c>
+      <c r="R4" s="22">
+        <v>0</v>
+      </c>
+      <c r="S4" s="9"/>
+      <c r="T4" s="9"/>
+      <c r="U4" s="9"/>
+      <c r="V4" s="9"/>
+      <c r="W4" s="23"/>
+      <c r="X4" s="69" t="s">
+        <v>353</v>
+      </c>
+      <c r="Y4" s="9" t="s">
+        <v>354</v>
+      </c>
+      <c r="Z4" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="AA4" s="23" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27">
+      <c r="A5" s="10">
+        <v>2</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="C5" s="1">
+        <v>10</v>
+      </c>
+      <c r="D5" s="1">
+        <v>0</v>
+      </c>
+      <c r="E5" s="1">
+        <v>0</v>
+      </c>
+      <c r="F5" s="1">
+        <v>10</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0</v>
+      </c>
+      <c r="H5" s="1">
+        <v>0</v>
+      </c>
+      <c r="I5" s="1">
+        <v>0</v>
+      </c>
+      <c r="J5" s="1">
+        <v>2</v>
+      </c>
+      <c r="K5" s="1">
+        <v>1</v>
+      </c>
+      <c r="L5" s="1">
+        <v>0</v>
+      </c>
+      <c r="M5" s="1">
+        <v>0</v>
+      </c>
+      <c r="N5" s="1">
+        <v>0</v>
+      </c>
+      <c r="O5" s="1">
+        <v>0</v>
+      </c>
+      <c r="P5" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="1">
+        <v>0</v>
+      </c>
+      <c r="R5" s="25">
+        <v>0</v>
+      </c>
+      <c r="S5" s="1"/>
+      <c r="T5" s="1"/>
+      <c r="U5" s="1"/>
+      <c r="V5" s="1"/>
+      <c r="W5" s="26"/>
+      <c r="X5" s="27" t="s">
+        <v>358</v>
+      </c>
+      <c r="Y5" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="Z5" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="AA5" s="26" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27">
+      <c r="A6" s="10">
+        <v>3</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="C6" s="1">
+        <v>10</v>
+      </c>
+      <c r="D6" s="1">
+        <v>0</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0</v>
+      </c>
+      <c r="F6" s="1">
+        <v>10</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0</v>
+      </c>
+      <c r="H6" s="1">
+        <v>0</v>
+      </c>
+      <c r="I6" s="1">
+        <v>0</v>
+      </c>
+      <c r="J6" s="1">
+        <v>2</v>
+      </c>
+      <c r="K6" s="1">
+        <v>1</v>
+      </c>
+      <c r="L6" s="1">
+        <v>0</v>
+      </c>
+      <c r="M6" s="1">
+        <v>0</v>
+      </c>
+      <c r="N6" s="1">
+        <v>0</v>
+      </c>
+      <c r="O6" s="1">
+        <v>0</v>
+      </c>
+      <c r="P6" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>0</v>
+      </c>
+      <c r="R6" s="25">
+        <v>0</v>
+      </c>
+      <c r="S6" s="1"/>
+      <c r="T6" s="1"/>
+      <c r="U6" s="1"/>
+      <c r="V6" s="1"/>
+      <c r="W6" s="26"/>
+      <c r="X6" s="27" t="s">
+        <v>361</v>
+      </c>
+      <c r="Y6" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="Z6" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="AA6" s="26" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27">
+      <c r="A7" s="10">
+        <v>4</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="C7" s="1">
+        <v>10</v>
+      </c>
+      <c r="D7" s="1">
+        <v>0</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0</v>
+      </c>
+      <c r="F7" s="1">
+        <v>10</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0</v>
+      </c>
+      <c r="H7" s="1">
+        <v>0</v>
+      </c>
+      <c r="I7" s="1">
+        <v>0</v>
+      </c>
+      <c r="J7" s="1">
+        <v>2</v>
+      </c>
+      <c r="K7" s="1">
+        <v>1</v>
+      </c>
+      <c r="L7" s="1">
+        <v>0</v>
+      </c>
+      <c r="M7" s="1">
+        <v>0</v>
+      </c>
+      <c r="N7" s="1">
+        <v>0</v>
+      </c>
+      <c r="O7" s="1">
+        <v>0</v>
+      </c>
+      <c r="P7" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>0</v>
+      </c>
+      <c r="R7" s="25">
+        <v>0</v>
+      </c>
+      <c r="S7" s="1"/>
+      <c r="T7" s="1"/>
+      <c r="U7" s="1"/>
+      <c r="V7" s="1"/>
+      <c r="W7" s="26"/>
+      <c r="X7" s="27" t="s">
+        <v>365</v>
+      </c>
+      <c r="Y7" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="Z7" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="AA7" s="26" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27">
+      <c r="A8" s="10">
+        <v>5</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="C8" s="1">
+        <v>10</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0</v>
+      </c>
+      <c r="E8" s="1">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1">
+        <v>10</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0</v>
+      </c>
+      <c r="H8" s="1">
+        <v>0</v>
+      </c>
+      <c r="I8" s="1">
+        <v>0</v>
+      </c>
+      <c r="J8" s="1">
+        <v>2</v>
+      </c>
+      <c r="K8" s="1">
+        <v>1</v>
+      </c>
+      <c r="L8" s="1">
+        <v>0</v>
+      </c>
+      <c r="M8" s="1">
+        <v>0</v>
+      </c>
+      <c r="N8" s="1">
+        <v>0</v>
+      </c>
+      <c r="O8" s="1">
+        <v>0</v>
+      </c>
+      <c r="P8" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>0</v>
+      </c>
+      <c r="R8" s="25">
+        <v>0</v>
+      </c>
+      <c r="S8" s="1"/>
+      <c r="T8" s="1"/>
+      <c r="U8" s="1"/>
+      <c r="V8" s="1"/>
+      <c r="W8" s="26"/>
+      <c r="X8" s="27" t="s">
+        <v>369</v>
+      </c>
+      <c r="Y8" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="Z8" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="AA8" s="26" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27">
+      <c r="A9" s="10">
+        <v>6</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="C9" s="1">
+        <v>10</v>
+      </c>
+      <c r="D9" s="1">
+        <v>0</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0</v>
+      </c>
+      <c r="F9" s="1">
+        <v>10</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0</v>
+      </c>
+      <c r="H9" s="1">
+        <v>0</v>
+      </c>
+      <c r="I9" s="1">
+        <v>0</v>
+      </c>
+      <c r="J9" s="1">
+        <v>2</v>
+      </c>
+      <c r="K9" s="1">
+        <v>1</v>
+      </c>
+      <c r="L9" s="1">
+        <v>0</v>
+      </c>
+      <c r="M9" s="1">
+        <v>0</v>
+      </c>
+      <c r="N9" s="1">
+        <v>0</v>
+      </c>
+      <c r="O9" s="1">
+        <v>0</v>
+      </c>
+      <c r="P9" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>0</v>
+      </c>
+      <c r="R9" s="25">
+        <v>0</v>
+      </c>
+      <c r="S9" s="1"/>
+      <c r="T9" s="1"/>
+      <c r="U9" s="1"/>
+      <c r="V9" s="1"/>
+      <c r="W9" s="26"/>
+      <c r="X9" s="27" t="s">
+        <v>373</v>
+      </c>
+      <c r="Y9" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="Z9" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="AA9" s="26" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27">
+      <c r="A10" s="10">
+        <v>7</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="C10" s="1">
+        <v>10</v>
+      </c>
+      <c r="D10" s="1">
+        <v>0</v>
+      </c>
+      <c r="E10" s="1">
+        <v>0</v>
+      </c>
+      <c r="F10" s="1">
+        <v>10</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0</v>
+      </c>
+      <c r="H10" s="1">
+        <v>0</v>
+      </c>
+      <c r="I10" s="1">
+        <v>0</v>
+      </c>
+      <c r="J10" s="1">
+        <v>2</v>
+      </c>
+      <c r="K10" s="1">
+        <v>1</v>
+      </c>
+      <c r="L10" s="1">
+        <v>0</v>
+      </c>
+      <c r="M10" s="1">
+        <v>0</v>
+      </c>
+      <c r="N10" s="1">
+        <v>0</v>
+      </c>
+      <c r="O10" s="1">
+        <v>0</v>
+      </c>
+      <c r="P10" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>0</v>
+      </c>
+      <c r="R10" s="25">
+        <v>0</v>
+      </c>
+      <c r="S10" s="1"/>
+      <c r="T10" s="1"/>
+      <c r="U10" s="1"/>
+      <c r="V10" s="1"/>
+      <c r="W10" s="26"/>
+      <c r="X10" s="27" t="s">
+        <v>378</v>
+      </c>
+      <c r="Y10" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="Z10" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="AA10" s="26" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27">
+      <c r="A11" s="10">
+        <v>8</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="C11" s="1">
+        <v>10</v>
+      </c>
+      <c r="D11" s="1">
+        <v>0</v>
+      </c>
+      <c r="E11" s="1">
+        <v>0</v>
+      </c>
+      <c r="F11" s="1">
+        <v>10</v>
+      </c>
+      <c r="G11" s="1">
+        <v>0</v>
+      </c>
+      <c r="H11" s="1">
+        <v>0</v>
+      </c>
+      <c r="I11" s="1">
+        <v>0</v>
+      </c>
+      <c r="J11" s="1">
+        <v>2</v>
+      </c>
+      <c r="K11" s="1">
+        <v>1</v>
+      </c>
+      <c r="L11" s="1">
+        <v>0</v>
+      </c>
+      <c r="M11" s="1">
+        <v>0</v>
+      </c>
+      <c r="N11" s="1">
+        <v>0</v>
+      </c>
+      <c r="O11" s="1">
+        <v>0</v>
+      </c>
+      <c r="P11" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>0</v>
+      </c>
+      <c r="R11" s="25">
+        <v>0</v>
+      </c>
+      <c r="S11" s="1"/>
+      <c r="T11" s="1"/>
+      <c r="U11" s="1"/>
+      <c r="V11" s="1"/>
+      <c r="W11" s="26"/>
+      <c r="X11" s="27" t="s">
+        <v>382</v>
+      </c>
+      <c r="Y11" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="Z11" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="AA11" s="26" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27">
+      <c r="A12" s="10">
+        <v>9</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="C12" s="1">
+        <v>10</v>
+      </c>
+      <c r="D12" s="1">
+        <v>0</v>
+      </c>
+      <c r="E12" s="1">
+        <v>0</v>
+      </c>
+      <c r="F12" s="1">
+        <v>10</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0</v>
+      </c>
+      <c r="H12" s="1">
+        <v>0</v>
+      </c>
+      <c r="I12" s="1">
+        <v>0</v>
+      </c>
+      <c r="J12" s="1">
+        <v>2</v>
+      </c>
+      <c r="K12" s="1">
+        <v>1</v>
+      </c>
+      <c r="L12" s="1">
+        <v>0</v>
+      </c>
+      <c r="M12" s="1">
+        <v>0</v>
+      </c>
+      <c r="N12" s="1">
+        <v>0</v>
+      </c>
+      <c r="O12" s="1">
+        <v>0</v>
+      </c>
+      <c r="P12" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>0</v>
+      </c>
+      <c r="R12" s="25">
+        <v>0</v>
+      </c>
+      <c r="S12" s="1"/>
+      <c r="T12" s="1"/>
+      <c r="U12" s="1"/>
+      <c r="V12" s="1"/>
+      <c r="W12" s="26"/>
+      <c r="X12" s="27" t="s">
+        <v>387</v>
+      </c>
+      <c r="Y12" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="Z12" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="AA12" s="26" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27">
+      <c r="A13" s="10">
+        <v>10</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="C13" s="1">
+        <v>10</v>
+      </c>
+      <c r="D13" s="1">
+        <v>0</v>
+      </c>
+      <c r="E13" s="1">
+        <v>0</v>
+      </c>
+      <c r="F13" s="1">
+        <v>10</v>
+      </c>
+      <c r="G13" s="1">
+        <v>0</v>
+      </c>
+      <c r="H13" s="1">
+        <v>0</v>
+      </c>
+      <c r="I13" s="1">
+        <v>0</v>
+      </c>
+      <c r="J13" s="1">
+        <v>2</v>
+      </c>
+      <c r="K13" s="1">
+        <v>1</v>
+      </c>
+      <c r="L13" s="1">
+        <v>0</v>
+      </c>
+      <c r="M13" s="1">
+        <v>0</v>
+      </c>
+      <c r="N13" s="1">
+        <v>0</v>
+      </c>
+      <c r="O13" s="1">
+        <v>0</v>
+      </c>
+      <c r="P13" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="1">
+        <v>0</v>
+      </c>
+      <c r="R13" s="25">
+        <v>0</v>
+      </c>
+      <c r="S13" s="1"/>
+      <c r="T13" s="1"/>
+      <c r="U13" s="1"/>
+      <c r="V13" s="1"/>
+      <c r="W13" s="26"/>
+      <c r="X13" s="27" t="s">
+        <v>392</v>
+      </c>
+      <c r="Y13" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="Z13" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="AA13" s="26" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27">
+      <c r="A14" s="10">
+        <v>11</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="C14" s="1">
+        <v>10</v>
+      </c>
+      <c r="D14" s="1">
+        <v>0</v>
+      </c>
+      <c r="E14" s="1">
+        <v>0</v>
+      </c>
+      <c r="F14" s="1">
+        <v>10</v>
+      </c>
+      <c r="G14" s="1">
+        <v>0</v>
+      </c>
+      <c r="H14" s="1">
+        <v>0</v>
+      </c>
+      <c r="I14" s="1">
+        <v>0</v>
+      </c>
+      <c r="J14" s="1">
+        <v>2</v>
+      </c>
+      <c r="K14" s="1">
+        <v>1</v>
+      </c>
+      <c r="L14" s="1">
+        <v>0</v>
+      </c>
+      <c r="M14" s="1">
+        <v>0</v>
+      </c>
+      <c r="N14" s="1">
+        <v>0</v>
+      </c>
+      <c r="O14" s="1">
+        <v>0</v>
+      </c>
+      <c r="P14" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="1">
+        <v>0</v>
+      </c>
+      <c r="R14" s="25">
+        <v>0</v>
+      </c>
+      <c r="S14" s="1"/>
+      <c r="T14" s="1"/>
+      <c r="U14" s="1"/>
+      <c r="V14" s="1"/>
+      <c r="W14" s="26"/>
+      <c r="X14" s="27" t="s">
+        <v>396</v>
+      </c>
+      <c r="Y14" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="Z14" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="AA14" s="26" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27">
+      <c r="A15" s="10">
+        <v>12</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="C15" s="1">
+        <v>10</v>
+      </c>
+      <c r="D15" s="1">
+        <v>0</v>
+      </c>
+      <c r="E15" s="1">
+        <v>0</v>
+      </c>
+      <c r="F15" s="1">
+        <v>10</v>
+      </c>
+      <c r="G15" s="1">
+        <v>0</v>
+      </c>
+      <c r="H15" s="1">
+        <v>0</v>
+      </c>
+      <c r="I15" s="1">
+        <v>0</v>
+      </c>
+      <c r="J15" s="1">
+        <v>2</v>
+      </c>
+      <c r="K15" s="1">
+        <v>1</v>
+      </c>
+      <c r="L15" s="1">
+        <v>0</v>
+      </c>
+      <c r="M15" s="1">
+        <v>0</v>
+      </c>
+      <c r="N15" s="1">
+        <v>0</v>
+      </c>
+      <c r="O15" s="1">
+        <v>0</v>
+      </c>
+      <c r="P15" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="1">
+        <v>0</v>
+      </c>
+      <c r="R15" s="25">
+        <v>0</v>
+      </c>
+      <c r="S15" s="1"/>
+      <c r="T15" s="1"/>
+      <c r="U15" s="1"/>
+      <c r="V15" s="1"/>
+      <c r="W15" s="26"/>
+      <c r="X15" s="27" t="s">
+        <v>401</v>
+      </c>
+      <c r="Y15" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="Z15" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="AA15" s="26" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27">
+      <c r="A16" s="10">
+        <v>13</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="C16" s="1">
+        <v>10</v>
+      </c>
+      <c r="D16" s="1">
+        <v>0</v>
+      </c>
+      <c r="E16" s="1">
+        <v>0</v>
+      </c>
+      <c r="F16" s="1">
+        <v>10</v>
+      </c>
+      <c r="G16" s="1">
+        <v>0</v>
+      </c>
+      <c r="H16" s="1">
+        <v>0</v>
+      </c>
+      <c r="I16" s="1">
+        <v>0</v>
+      </c>
+      <c r="J16" s="1">
+        <v>2</v>
+      </c>
+      <c r="K16" s="1">
+        <v>1</v>
+      </c>
+      <c r="L16" s="1">
+        <v>0</v>
+      </c>
+      <c r="M16" s="1">
+        <v>0</v>
+      </c>
+      <c r="N16" s="1">
+        <v>0</v>
+      </c>
+      <c r="O16" s="1">
+        <v>0</v>
+      </c>
+      <c r="P16" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="1">
+        <v>0</v>
+      </c>
+      <c r="R16" s="25">
+        <v>0</v>
+      </c>
+      <c r="S16" s="1"/>
+      <c r="T16" s="1"/>
+      <c r="U16" s="1"/>
+      <c r="V16" s="1"/>
+      <c r="W16" s="26"/>
+      <c r="X16" s="27" t="s">
+        <v>405</v>
+      </c>
+      <c r="Y16" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="Z16" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="AA16" s="26" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="17" spans="1:27">
+      <c r="A17" s="10">
+        <v>14</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="C17" s="1">
+        <v>10</v>
+      </c>
+      <c r="D17" s="1">
+        <v>0</v>
+      </c>
+      <c r="E17" s="1">
+        <v>0</v>
+      </c>
+      <c r="F17" s="1">
+        <v>10</v>
+      </c>
+      <c r="G17" s="1">
+        <v>0</v>
+      </c>
+      <c r="H17" s="1">
+        <v>0</v>
+      </c>
+      <c r="I17" s="1">
+        <v>0</v>
+      </c>
+      <c r="J17" s="1">
+        <v>2</v>
+      </c>
+      <c r="K17" s="1">
+        <v>1</v>
+      </c>
+      <c r="L17" s="1">
+        <v>0</v>
+      </c>
+      <c r="M17" s="1">
+        <v>0</v>
+      </c>
+      <c r="N17" s="1">
+        <v>0</v>
+      </c>
+      <c r="O17" s="1">
+        <v>0</v>
+      </c>
+      <c r="P17" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="1">
+        <v>0</v>
+      </c>
+      <c r="R17" s="25">
+        <v>0</v>
+      </c>
+      <c r="S17" s="1"/>
+      <c r="T17" s="1"/>
+      <c r="U17" s="1"/>
+      <c r="V17" s="1"/>
+      <c r="W17" s="26"/>
+      <c r="X17" s="27" t="s">
+        <v>409</v>
+      </c>
+      <c r="Y17" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="Z17" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="AA17" s="26" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="18" spans="1:27">
+      <c r="A18" s="10">
+        <v>15</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="C18" s="1">
+        <v>10</v>
+      </c>
+      <c r="D18" s="1">
+        <v>0</v>
+      </c>
+      <c r="E18" s="1">
+        <v>0</v>
+      </c>
+      <c r="F18" s="1">
+        <v>10</v>
+      </c>
+      <c r="G18" s="1">
+        <v>0</v>
+      </c>
+      <c r="H18" s="1">
+        <v>0</v>
+      </c>
+      <c r="I18" s="1">
+        <v>0</v>
+      </c>
+      <c r="J18" s="1">
+        <v>2</v>
+      </c>
+      <c r="K18" s="1">
+        <v>1</v>
+      </c>
+      <c r="L18" s="1">
+        <v>0</v>
+      </c>
+      <c r="M18" s="1">
+        <v>0</v>
+      </c>
+      <c r="N18" s="1">
+        <v>0</v>
+      </c>
+      <c r="O18" s="1">
+        <v>0</v>
+      </c>
+      <c r="P18" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="1">
+        <v>0</v>
+      </c>
+      <c r="R18" s="25">
+        <v>0</v>
+      </c>
+      <c r="S18" s="1"/>
+      <c r="T18" s="1"/>
+      <c r="U18" s="1"/>
+      <c r="V18" s="1"/>
+      <c r="W18" s="26"/>
+      <c r="X18" s="27" t="s">
+        <v>414</v>
+      </c>
+      <c r="Y18" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="Z18" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="AA18" s="26" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="19" spans="1:27">
+      <c r="A19" s="10">
+        <v>16</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="C19" s="1">
+        <v>10</v>
+      </c>
+      <c r="D19" s="1">
+        <v>0</v>
+      </c>
+      <c r="E19" s="1">
+        <v>0</v>
+      </c>
+      <c r="F19" s="1">
+        <v>10</v>
+      </c>
+      <c r="G19" s="1">
+        <v>0</v>
+      </c>
+      <c r="H19" s="1">
+        <v>0</v>
+      </c>
+      <c r="I19" s="1">
+        <v>0</v>
+      </c>
+      <c r="J19" s="1">
+        <v>2</v>
+      </c>
+      <c r="K19" s="1">
+        <v>1</v>
+      </c>
+      <c r="L19" s="1">
+        <v>0</v>
+      </c>
+      <c r="M19" s="1">
+        <v>0</v>
+      </c>
+      <c r="N19" s="1">
+        <v>0</v>
+      </c>
+      <c r="O19" s="1">
+        <v>0</v>
+      </c>
+      <c r="P19" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="1">
+        <v>0</v>
+      </c>
+      <c r="R19" s="25">
+        <v>0</v>
+      </c>
+      <c r="S19" s="1"/>
+      <c r="T19" s="1"/>
+      <c r="U19" s="1"/>
+      <c r="V19" s="1"/>
+      <c r="W19" s="26"/>
+      <c r="X19" s="27" t="s">
+        <v>418</v>
+      </c>
+      <c r="Y19" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="Z19" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="AA19" s="26" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="20" spans="1:27">
+      <c r="A20" s="10">
+        <v>17</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="C20" s="1">
+        <v>10</v>
+      </c>
+      <c r="D20" s="1">
+        <v>0</v>
+      </c>
+      <c r="E20" s="1">
+        <v>0</v>
+      </c>
+      <c r="F20" s="1">
+        <v>10</v>
+      </c>
+      <c r="G20" s="1">
+        <v>0</v>
+      </c>
+      <c r="H20" s="1">
+        <v>0</v>
+      </c>
+      <c r="I20" s="1">
+        <v>0</v>
+      </c>
+      <c r="J20" s="1">
+        <v>2</v>
+      </c>
+      <c r="K20" s="1">
+        <v>1</v>
+      </c>
+      <c r="L20" s="1">
+        <v>0</v>
+      </c>
+      <c r="M20" s="1">
+        <v>0</v>
+      </c>
+      <c r="N20" s="1">
+        <v>0</v>
+      </c>
+      <c r="O20" s="1">
+        <v>0</v>
+      </c>
+      <c r="P20" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="1">
+        <v>0</v>
+      </c>
+      <c r="R20" s="25">
+        <v>0</v>
+      </c>
+      <c r="S20" s="1"/>
+      <c r="T20" s="1"/>
+      <c r="U20" s="1"/>
+      <c r="V20" s="1"/>
+      <c r="W20" s="26"/>
+      <c r="X20" s="27" t="s">
+        <v>422</v>
+      </c>
+      <c r="Y20" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="Z20" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="AA20" s="26" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="21" spans="1:27">
+      <c r="A21" s="10">
+        <v>18</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="C21" s="1">
+        <v>10</v>
+      </c>
+      <c r="D21" s="1">
+        <v>0</v>
+      </c>
+      <c r="E21" s="1">
+        <v>0</v>
+      </c>
+      <c r="F21" s="1">
+        <v>10</v>
+      </c>
+      <c r="G21" s="1">
+        <v>0</v>
+      </c>
+      <c r="H21" s="1">
+        <v>0</v>
+      </c>
+      <c r="I21" s="1">
+        <v>0</v>
+      </c>
+      <c r="J21" s="1">
+        <v>2</v>
+      </c>
+      <c r="K21" s="1">
+        <v>1</v>
+      </c>
+      <c r="L21" s="1">
+        <v>0</v>
+      </c>
+      <c r="M21" s="1">
+        <v>0</v>
+      </c>
+      <c r="N21" s="1">
+        <v>0</v>
+      </c>
+      <c r="O21" s="1">
+        <v>0</v>
+      </c>
+      <c r="P21" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="1">
+        <v>0</v>
+      </c>
+      <c r="R21" s="25">
+        <v>0</v>
+      </c>
+      <c r="S21" s="1"/>
+      <c r="T21" s="1"/>
+      <c r="U21" s="1"/>
+      <c r="V21" s="1"/>
+      <c r="W21" s="26"/>
+      <c r="X21" s="27" t="s">
+        <v>426</v>
+      </c>
+      <c r="Y21" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="Z21" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="AA21" s="26" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="22" spans="1:27">
+      <c r="A22" s="10">
+        <v>19</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="C22" s="1">
+        <v>10</v>
+      </c>
+      <c r="D22" s="1">
+        <v>0</v>
+      </c>
+      <c r="E22" s="1">
+        <v>0</v>
+      </c>
+      <c r="F22" s="1">
+        <v>10</v>
+      </c>
+      <c r="G22" s="1">
+        <v>0</v>
+      </c>
+      <c r="H22" s="1">
+        <v>0</v>
+      </c>
+      <c r="I22" s="1">
+        <v>0</v>
+      </c>
+      <c r="J22" s="1">
+        <v>2</v>
+      </c>
+      <c r="K22" s="1">
+        <v>1</v>
+      </c>
+      <c r="L22" s="1">
+        <v>0</v>
+      </c>
+      <c r="M22" s="1">
+        <v>0</v>
+      </c>
+      <c r="N22" s="1">
+        <v>0</v>
+      </c>
+      <c r="O22" s="1">
+        <v>0</v>
+      </c>
+      <c r="P22" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="1">
+        <v>0</v>
+      </c>
+      <c r="R22" s="25">
+        <v>0</v>
+      </c>
+      <c r="S22" s="1"/>
+      <c r="T22" s="1"/>
+      <c r="U22" s="1"/>
+      <c r="V22" s="1"/>
+      <c r="W22" s="26"/>
+      <c r="X22" s="27" t="s">
+        <v>430</v>
+      </c>
+      <c r="Y22" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="Z22" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="AA22" s="26" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="23" spans="1:27">
+      <c r="A23" s="10">
+        <v>20</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C23" s="1">
+        <v>10</v>
+      </c>
+      <c r="D23" s="1">
+        <v>0</v>
+      </c>
+      <c r="E23" s="1">
+        <v>0</v>
+      </c>
+      <c r="F23" s="1">
+        <v>10</v>
+      </c>
+      <c r="G23" s="1">
+        <v>0</v>
+      </c>
+      <c r="H23" s="1">
+        <v>0</v>
+      </c>
+      <c r="I23" s="1">
+        <v>0</v>
+      </c>
+      <c r="J23" s="1">
+        <v>2</v>
+      </c>
+      <c r="K23" s="1">
+        <v>1</v>
+      </c>
+      <c r="L23" s="1">
+        <v>0</v>
+      </c>
+      <c r="M23" s="1">
+        <v>0</v>
+      </c>
+      <c r="N23" s="1">
+        <v>0</v>
+      </c>
+      <c r="O23" s="1">
+        <v>0</v>
+      </c>
+      <c r="P23" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="1">
+        <v>0</v>
+      </c>
+      <c r="R23" s="25">
+        <v>0</v>
+      </c>
+      <c r="S23" s="1"/>
+      <c r="T23" s="1"/>
+      <c r="U23" s="1"/>
+      <c r="V23" s="1"/>
+      <c r="W23" s="26"/>
+      <c r="X23" s="27" t="s">
+        <v>435</v>
+      </c>
+      <c r="Y23" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="Z23" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="AA23" s="26" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="24" spans="1:27">
+      <c r="A24" s="10">
+        <v>21</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="C24" s="1">
+        <v>10</v>
+      </c>
+      <c r="D24" s="1">
+        <v>0</v>
+      </c>
+      <c r="E24" s="1">
+        <v>0</v>
+      </c>
+      <c r="F24" s="1">
+        <v>10</v>
+      </c>
+      <c r="G24" s="1">
+        <v>0</v>
+      </c>
+      <c r="H24" s="1">
+        <v>0</v>
+      </c>
+      <c r="I24" s="1">
+        <v>0</v>
+      </c>
+      <c r="J24" s="1">
+        <v>2</v>
+      </c>
+      <c r="K24" s="1">
+        <v>1</v>
+      </c>
+      <c r="L24" s="1">
+        <v>0</v>
+      </c>
+      <c r="M24" s="1">
+        <v>0</v>
+      </c>
+      <c r="N24" s="1">
+        <v>0</v>
+      </c>
+      <c r="O24" s="1">
+        <v>0</v>
+      </c>
+      <c r="P24" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="1">
+        <v>0</v>
+      </c>
+      <c r="R24" s="25">
+        <v>0</v>
+      </c>
+      <c r="S24" s="1"/>
+      <c r="T24" s="1"/>
+      <c r="U24" s="1"/>
+      <c r="V24" s="1"/>
+      <c r="W24" s="26"/>
+      <c r="X24" s="27" t="s">
+        <v>440</v>
+      </c>
+      <c r="Y24" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="Z24" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="AA24" s="26" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="25" spans="1:27">
+      <c r="A25" s="10">
+        <v>22</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="C25" s="1">
+        <v>10</v>
+      </c>
+      <c r="D25" s="1">
+        <v>0</v>
+      </c>
+      <c r="E25" s="1">
+        <v>0</v>
+      </c>
+      <c r="F25" s="1">
+        <v>10</v>
+      </c>
+      <c r="G25" s="1">
+        <v>0</v>
+      </c>
+      <c r="H25" s="1">
+        <v>0</v>
+      </c>
+      <c r="I25" s="1">
+        <v>0</v>
+      </c>
+      <c r="J25" s="1">
+        <v>2</v>
+      </c>
+      <c r="K25" s="1">
+        <v>1</v>
+      </c>
+      <c r="L25" s="1">
+        <v>0</v>
+      </c>
+      <c r="M25" s="1">
+        <v>0</v>
+      </c>
+      <c r="N25" s="1">
+        <v>0</v>
+      </c>
+      <c r="O25" s="1">
+        <v>0</v>
+      </c>
+      <c r="P25" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="1">
+        <v>0</v>
+      </c>
+      <c r="R25" s="25">
+        <v>0</v>
+      </c>
+      <c r="S25" s="1"/>
+      <c r="T25" s="1"/>
+      <c r="U25" s="1"/>
+      <c r="V25" s="1"/>
+      <c r="W25" s="26"/>
+      <c r="X25" s="27" t="s">
+        <v>445</v>
+      </c>
+      <c r="Y25" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="Z25" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="AA25" s="26" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="26" spans="1:27">
+      <c r="A26" s="10">
+        <v>23</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="C26" s="1">
+        <v>10</v>
+      </c>
+      <c r="D26" s="1">
+        <v>0</v>
+      </c>
+      <c r="E26" s="1">
+        <v>0</v>
+      </c>
+      <c r="F26" s="1">
+        <v>10</v>
+      </c>
+      <c r="G26" s="1">
+        <v>0</v>
+      </c>
+      <c r="H26" s="1">
+        <v>0</v>
+      </c>
+      <c r="I26" s="1">
+        <v>0</v>
+      </c>
+      <c r="J26" s="1">
+        <v>2</v>
+      </c>
+      <c r="K26" s="1">
+        <v>1</v>
+      </c>
+      <c r="L26" s="1">
+        <v>0</v>
+      </c>
+      <c r="M26" s="1">
+        <v>0</v>
+      </c>
+      <c r="N26" s="1">
+        <v>0</v>
+      </c>
+      <c r="O26" s="1">
+        <v>0</v>
+      </c>
+      <c r="P26" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="1">
+        <v>0</v>
+      </c>
+      <c r="R26" s="25">
+        <v>0</v>
+      </c>
+      <c r="S26" s="1"/>
+      <c r="T26" s="1"/>
+      <c r="U26" s="1"/>
+      <c r="V26" s="1"/>
+      <c r="W26" s="26"/>
+      <c r="X26" s="27" t="s">
+        <v>449</v>
+      </c>
+      <c r="Y26" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="Z26" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="AA26" s="26" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="27" spans="1:27">
+      <c r="A27" s="10">
+        <v>24</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="C27" s="1">
+        <v>10</v>
+      </c>
+      <c r="D27" s="1">
+        <v>0</v>
+      </c>
+      <c r="E27" s="1">
+        <v>0</v>
+      </c>
+      <c r="F27" s="1">
+        <v>10</v>
+      </c>
+      <c r="G27" s="1">
+        <v>0</v>
+      </c>
+      <c r="H27" s="1">
+        <v>0</v>
+      </c>
+      <c r="I27" s="1">
+        <v>0</v>
+      </c>
+      <c r="J27" s="1">
+        <v>2</v>
+      </c>
+      <c r="K27" s="1">
+        <v>1</v>
+      </c>
+      <c r="L27" s="1">
+        <v>0</v>
+      </c>
+      <c r="M27" s="1">
+        <v>0</v>
+      </c>
+      <c r="N27" s="1">
+        <v>0</v>
+      </c>
+      <c r="O27" s="1">
+        <v>0</v>
+      </c>
+      <c r="P27" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="1">
+        <v>0</v>
+      </c>
+      <c r="R27" s="25">
+        <v>0</v>
+      </c>
+      <c r="S27" s="1"/>
+      <c r="T27" s="1"/>
+      <c r="U27" s="1"/>
+      <c r="V27" s="1"/>
+      <c r="W27" s="26"/>
+      <c r="X27" s="27" t="s">
+        <v>454</v>
+      </c>
+      <c r="Y27" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="Z27" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="AA27" s="26" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="28" spans="1:27">
+      <c r="A28" s="10">
+        <v>25</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="C28" s="1">
+        <v>10</v>
+      </c>
+      <c r="D28" s="1">
+        <v>0</v>
+      </c>
+      <c r="E28" s="1">
+        <v>0</v>
+      </c>
+      <c r="F28" s="1">
+        <v>10</v>
+      </c>
+      <c r="G28" s="1">
+        <v>0</v>
+      </c>
+      <c r="H28" s="1">
+        <v>0</v>
+      </c>
+      <c r="I28" s="1">
+        <v>0</v>
+      </c>
+      <c r="J28" s="1">
+        <v>2</v>
+      </c>
+      <c r="K28" s="1">
+        <v>1</v>
+      </c>
+      <c r="L28" s="1">
+        <v>0</v>
+      </c>
+      <c r="M28" s="1">
+        <v>0</v>
+      </c>
+      <c r="N28" s="1">
+        <v>0</v>
+      </c>
+      <c r="O28" s="1">
+        <v>0</v>
+      </c>
+      <c r="P28" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="1">
+        <v>0</v>
+      </c>
+      <c r="R28" s="25">
+        <v>0</v>
+      </c>
+      <c r="S28" s="1"/>
+      <c r="T28" s="1"/>
+      <c r="U28" s="1"/>
+      <c r="V28" s="1"/>
+      <c r="W28" s="26"/>
+      <c r="X28" s="27" t="s">
+        <v>459</v>
+      </c>
+      <c r="Y28" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="Z28" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="AA28" s="26" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="29" spans="1:27">
+      <c r="A29" s="10">
+        <v>26</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="C29" s="1">
+        <v>10</v>
+      </c>
+      <c r="D29" s="1">
+        <v>0</v>
+      </c>
+      <c r="E29" s="1">
+        <v>0</v>
+      </c>
+      <c r="F29" s="1">
+        <v>10</v>
+      </c>
+      <c r="G29" s="1">
+        <v>0</v>
+      </c>
+      <c r="H29" s="1">
+        <v>0</v>
+      </c>
+      <c r="I29" s="1">
+        <v>0</v>
+      </c>
+      <c r="J29" s="1">
+        <v>2</v>
+      </c>
+      <c r="K29" s="1">
+        <v>1</v>
+      </c>
+      <c r="L29" s="1">
+        <v>0</v>
+      </c>
+      <c r="M29" s="1">
+        <v>0</v>
+      </c>
+      <c r="N29" s="1">
+        <v>0</v>
+      </c>
+      <c r="O29" s="1">
+        <v>0</v>
+      </c>
+      <c r="P29" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="1">
+        <v>0</v>
+      </c>
+      <c r="R29" s="25">
+        <v>0</v>
+      </c>
+      <c r="S29" s="1"/>
+      <c r="T29" s="1"/>
+      <c r="U29" s="1"/>
+      <c r="V29" s="1"/>
+      <c r="W29" s="26"/>
+      <c r="X29" s="27" t="s">
+        <v>464</v>
+      </c>
+      <c r="Y29" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="Z29" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="AA29" s="26" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="30" spans="1:27">
+      <c r="A30" s="10">
+        <v>27</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="C30" s="1">
+        <v>10</v>
+      </c>
+      <c r="D30" s="1">
+        <v>0</v>
+      </c>
+      <c r="E30" s="1">
+        <v>0</v>
+      </c>
+      <c r="F30" s="1">
+        <v>10</v>
+      </c>
+      <c r="G30" s="1">
+        <v>0</v>
+      </c>
+      <c r="H30" s="1">
+        <v>0</v>
+      </c>
+      <c r="I30" s="1">
+        <v>0</v>
+      </c>
+      <c r="J30" s="1">
+        <v>2</v>
+      </c>
+      <c r="K30" s="1">
+        <v>1</v>
+      </c>
+      <c r="L30" s="1">
+        <v>0</v>
+      </c>
+      <c r="M30" s="1">
+        <v>0</v>
+      </c>
+      <c r="N30" s="1">
+        <v>0</v>
+      </c>
+      <c r="O30" s="1">
+        <v>0</v>
+      </c>
+      <c r="P30" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="1">
+        <v>0</v>
+      </c>
+      <c r="R30" s="25">
+        <v>0</v>
+      </c>
+      <c r="S30" s="1"/>
+      <c r="T30" s="1"/>
+      <c r="U30" s="1"/>
+      <c r="V30" s="1"/>
+      <c r="W30" s="26"/>
+      <c r="X30" s="27" t="s">
+        <v>469</v>
+      </c>
+      <c r="Y30" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="Z30" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="AA30" s="26" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="31" spans="1:27">
+      <c r="A31" s="10">
+        <v>28</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="C31" s="1">
+        <v>10</v>
+      </c>
+      <c r="D31" s="1">
+        <v>0</v>
+      </c>
+      <c r="E31" s="1">
+        <v>0</v>
+      </c>
+      <c r="F31" s="1">
+        <v>10</v>
+      </c>
+      <c r="G31" s="1">
+        <v>0</v>
+      </c>
+      <c r="H31" s="1">
+        <v>0</v>
+      </c>
+      <c r="I31" s="1">
+        <v>0</v>
+      </c>
+      <c r="J31" s="1">
+        <v>2</v>
+      </c>
+      <c r="K31" s="1">
+        <v>1</v>
+      </c>
+      <c r="L31" s="1">
+        <v>0</v>
+      </c>
+      <c r="M31" s="1">
+        <v>0</v>
+      </c>
+      <c r="N31" s="1">
+        <v>0</v>
+      </c>
+      <c r="O31" s="1">
+        <v>0</v>
+      </c>
+      <c r="P31" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="1">
+        <v>0</v>
+      </c>
+      <c r="R31" s="25">
+        <v>0</v>
+      </c>
+      <c r="S31" s="1"/>
+      <c r="T31" s="1"/>
+      <c r="U31" s="1"/>
+      <c r="V31" s="1"/>
+      <c r="W31" s="26"/>
+      <c r="X31" s="27" t="s">
+        <v>473</v>
+      </c>
+      <c r="Y31" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="Z31" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="AA31" s="26" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="32" spans="1:27">
+      <c r="A32" s="10">
+        <v>29</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="C32" s="1">
+        <v>10</v>
+      </c>
+      <c r="D32" s="1">
+        <v>0</v>
+      </c>
+      <c r="E32" s="1">
+        <v>0</v>
+      </c>
+      <c r="F32" s="1">
+        <v>10</v>
+      </c>
+      <c r="G32" s="1">
+        <v>0</v>
+      </c>
+      <c r="H32" s="1">
+        <v>0</v>
+      </c>
+      <c r="I32" s="1">
+        <v>0</v>
+      </c>
+      <c r="J32" s="1">
+        <v>2</v>
+      </c>
+      <c r="K32" s="1">
+        <v>1</v>
+      </c>
+      <c r="L32" s="1">
+        <v>0</v>
+      </c>
+      <c r="M32" s="1">
+        <v>0</v>
+      </c>
+      <c r="N32" s="1">
+        <v>0</v>
+      </c>
+      <c r="O32" s="1">
+        <v>0</v>
+      </c>
+      <c r="P32" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="1">
+        <v>0</v>
+      </c>
+      <c r="R32" s="25">
+        <v>0</v>
+      </c>
+      <c r="S32" s="1"/>
+      <c r="T32" s="1"/>
+      <c r="U32" s="1"/>
+      <c r="V32" s="1"/>
+      <c r="W32" s="26"/>
+      <c r="X32" s="27" t="s">
+        <v>477</v>
+      </c>
+      <c r="Y32" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="Z32" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="AA32" s="26" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="33" spans="1:27">
+      <c r="A33" s="10">
+        <v>30</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="C33" s="1">
+        <v>10</v>
+      </c>
+      <c r="D33" s="1">
+        <v>0</v>
+      </c>
+      <c r="E33" s="1">
+        <v>0</v>
+      </c>
+      <c r="F33" s="1">
+        <v>10</v>
+      </c>
+      <c r="G33" s="1">
+        <v>0</v>
+      </c>
+      <c r="H33" s="1">
+        <v>0</v>
+      </c>
+      <c r="I33" s="1">
+        <v>0</v>
+      </c>
+      <c r="J33" s="1">
+        <v>2</v>
+      </c>
+      <c r="K33" s="1">
+        <v>1</v>
+      </c>
+      <c r="L33" s="1">
+        <v>0</v>
+      </c>
+      <c r="M33" s="1">
+        <v>0</v>
+      </c>
+      <c r="N33" s="1">
+        <v>0</v>
+      </c>
+      <c r="O33" s="1">
+        <v>0</v>
+      </c>
+      <c r="P33" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="1">
+        <v>0</v>
+      </c>
+      <c r="R33" s="25">
+        <v>0</v>
+      </c>
+      <c r="S33" s="1"/>
+      <c r="T33" s="1"/>
+      <c r="U33" s="1"/>
+      <c r="V33" s="1"/>
+      <c r="W33" s="26"/>
+      <c r="X33" s="27" t="s">
+        <v>482</v>
+      </c>
+      <c r="Y33" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="Z33" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="AA33" s="26" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="34" spans="1:27">
+      <c r="A34" s="10">
+        <v>31</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="C34" s="1">
+        <v>10</v>
+      </c>
+      <c r="D34" s="1">
+        <v>0</v>
+      </c>
+      <c r="E34" s="1">
+        <v>0</v>
+      </c>
+      <c r="F34" s="1">
+        <v>10</v>
+      </c>
+      <c r="G34" s="1">
+        <v>0</v>
+      </c>
+      <c r="H34" s="1">
+        <v>0</v>
+      </c>
+      <c r="I34" s="1">
+        <v>0</v>
+      </c>
+      <c r="J34" s="1">
+        <v>2</v>
+      </c>
+      <c r="K34" s="1">
+        <v>1</v>
+      </c>
+      <c r="L34" s="1">
+        <v>0</v>
+      </c>
+      <c r="M34" s="1">
+        <v>0</v>
+      </c>
+      <c r="N34" s="1">
+        <v>0</v>
+      </c>
+      <c r="O34" s="1">
+        <v>0</v>
+      </c>
+      <c r="P34" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="1">
+        <v>0</v>
+      </c>
+      <c r="R34" s="25">
+        <v>0</v>
+      </c>
+      <c r="S34" s="1"/>
+      <c r="T34" s="1"/>
+      <c r="U34" s="1"/>
+      <c r="V34" s="1"/>
+      <c r="W34" s="26"/>
+      <c r="X34" s="27" t="s">
+        <v>487</v>
+      </c>
+      <c r="Y34" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="Z34" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="AA34" s="26" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="35" spans="1:27">
+      <c r="A35" s="10">
+        <v>32</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="C35" s="1">
+        <v>10</v>
+      </c>
+      <c r="D35" s="1">
+        <v>0</v>
+      </c>
+      <c r="E35" s="1">
+        <v>0</v>
+      </c>
+      <c r="F35" s="1">
+        <v>10</v>
+      </c>
+      <c r="G35" s="1">
+        <v>0</v>
+      </c>
+      <c r="H35" s="1">
+        <v>0</v>
+      </c>
+      <c r="I35" s="1">
+        <v>0</v>
+      </c>
+      <c r="J35" s="1">
+        <v>2</v>
+      </c>
+      <c r="K35" s="1">
+        <v>1</v>
+      </c>
+      <c r="L35" s="1">
+        <v>0</v>
+      </c>
+      <c r="M35" s="1">
+        <v>0</v>
+      </c>
+      <c r="N35" s="1">
+        <v>0</v>
+      </c>
+      <c r="O35" s="1">
+        <v>0</v>
+      </c>
+      <c r="P35" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="1">
+        <v>0</v>
+      </c>
+      <c r="R35" s="25">
+        <v>0</v>
+      </c>
+      <c r="S35" s="1"/>
+      <c r="T35" s="1"/>
+      <c r="U35" s="1"/>
+      <c r="V35" s="1"/>
+      <c r="W35" s="26"/>
+      <c r="X35" s="27" t="s">
+        <v>491</v>
+      </c>
+      <c r="Y35" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="Z35" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="AA35" s="26" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="36" spans="1:27">
+      <c r="A36" s="10">
+        <v>33</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="C36" s="1">
+        <v>10</v>
+      </c>
+      <c r="D36" s="1">
+        <v>0</v>
+      </c>
+      <c r="E36" s="1">
+        <v>0</v>
+      </c>
+      <c r="F36" s="1">
+        <v>10</v>
+      </c>
+      <c r="G36" s="1">
+        <v>0</v>
+      </c>
+      <c r="H36" s="1">
+        <v>0</v>
+      </c>
+      <c r="I36" s="1">
+        <v>0</v>
+      </c>
+      <c r="J36" s="1">
+        <v>2</v>
+      </c>
+      <c r="K36" s="1">
+        <v>1</v>
+      </c>
+      <c r="L36" s="1">
+        <v>0</v>
+      </c>
+      <c r="M36" s="1">
+        <v>0</v>
+      </c>
+      <c r="N36" s="1">
+        <v>0</v>
+      </c>
+      <c r="O36" s="1">
+        <v>0</v>
+      </c>
+      <c r="P36" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="1">
+        <v>0</v>
+      </c>
+      <c r="R36" s="25">
+        <v>0</v>
+      </c>
+      <c r="S36" s="1"/>
+      <c r="T36" s="1"/>
+      <c r="U36" s="1"/>
+      <c r="V36" s="1"/>
+      <c r="W36" s="26"/>
+      <c r="X36" s="27" t="s">
+        <v>496</v>
+      </c>
+      <c r="Y36" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="Z36" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="AA36" s="26" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="37" spans="1:27">
+      <c r="A37" s="10">
+        <v>34</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="C37" s="1">
+        <v>10</v>
+      </c>
+      <c r="D37" s="1">
+        <v>0</v>
+      </c>
+      <c r="E37" s="1">
+        <v>0</v>
+      </c>
+      <c r="F37" s="1">
+        <v>10</v>
+      </c>
+      <c r="G37" s="1">
+        <v>0</v>
+      </c>
+      <c r="H37" s="1">
+        <v>0</v>
+      </c>
+      <c r="I37" s="1">
+        <v>0</v>
+      </c>
+      <c r="J37" s="1">
+        <v>2</v>
+      </c>
+      <c r="K37" s="1">
+        <v>1</v>
+      </c>
+      <c r="L37" s="1">
+        <v>0</v>
+      </c>
+      <c r="M37" s="1">
+        <v>0</v>
+      </c>
+      <c r="N37" s="1">
+        <v>0</v>
+      </c>
+      <c r="O37" s="1">
+        <v>0</v>
+      </c>
+      <c r="P37" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="1">
+        <v>0</v>
+      </c>
+      <c r="R37" s="25">
+        <v>0</v>
+      </c>
+      <c r="S37" s="1"/>
+      <c r="T37" s="1"/>
+      <c r="U37" s="1"/>
+      <c r="V37" s="1"/>
+      <c r="W37" s="26"/>
+      <c r="X37" s="27" t="s">
+        <v>501</v>
+      </c>
+      <c r="Y37" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="Z37" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="AA37" s="26" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="38" spans="1:27">
+      <c r="A38" s="10">
+        <v>35</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="C38" s="1">
+        <v>10</v>
+      </c>
+      <c r="D38" s="1">
+        <v>0</v>
+      </c>
+      <c r="E38" s="1">
+        <v>0</v>
+      </c>
+      <c r="F38" s="1">
+        <v>10</v>
+      </c>
+      <c r="G38" s="1">
+        <v>0</v>
+      </c>
+      <c r="H38" s="1">
+        <v>0</v>
+      </c>
+      <c r="I38" s="1">
+        <v>0</v>
+      </c>
+      <c r="J38" s="1">
+        <v>2</v>
+      </c>
+      <c r="K38" s="1">
+        <v>1</v>
+      </c>
+      <c r="L38" s="1">
+        <v>0</v>
+      </c>
+      <c r="M38" s="1">
+        <v>0</v>
+      </c>
+      <c r="N38" s="1">
+        <v>0</v>
+      </c>
+      <c r="O38" s="1">
+        <v>0</v>
+      </c>
+      <c r="P38" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="1">
+        <v>0</v>
+      </c>
+      <c r="R38" s="25">
+        <v>0</v>
+      </c>
+      <c r="S38" s="1"/>
+      <c r="T38" s="1"/>
+      <c r="U38" s="1"/>
+      <c r="V38" s="1"/>
+      <c r="W38" s="26"/>
+      <c r="X38" s="27" t="s">
+        <v>506</v>
+      </c>
+      <c r="Y38" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="Z38" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="AA38" s="26" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="39" spans="1:27">
+      <c r="A39" s="10">
+        <v>36</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="C39" s="1">
+        <v>10</v>
+      </c>
+      <c r="D39" s="1">
+        <v>0</v>
+      </c>
+      <c r="E39" s="1">
+        <v>0</v>
+      </c>
+      <c r="F39" s="1">
+        <v>10</v>
+      </c>
+      <c r="G39" s="1">
+        <v>0</v>
+      </c>
+      <c r="H39" s="1">
+        <v>0</v>
+      </c>
+      <c r="I39" s="1">
+        <v>0</v>
+      </c>
+      <c r="J39" s="1">
+        <v>2</v>
+      </c>
+      <c r="K39" s="1">
+        <v>1</v>
+      </c>
+      <c r="L39" s="1">
+        <v>0</v>
+      </c>
+      <c r="M39" s="1">
+        <v>0</v>
+      </c>
+      <c r="N39" s="1">
+        <v>0</v>
+      </c>
+      <c r="O39" s="1">
+        <v>0</v>
+      </c>
+      <c r="P39" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="1">
+        <v>0</v>
+      </c>
+      <c r="R39" s="25">
+        <v>0</v>
+      </c>
+      <c r="S39" s="1"/>
+      <c r="T39" s="1"/>
+      <c r="U39" s="1"/>
+      <c r="V39" s="1"/>
+      <c r="W39" s="26"/>
+      <c r="X39" s="27" t="s">
+        <v>511</v>
+      </c>
+      <c r="Y39" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="Z39" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="AA39" s="26" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="40" spans="1:27">
+      <c r="A40" s="10">
+        <v>37</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="C40" s="1">
+        <v>10</v>
+      </c>
+      <c r="D40" s="1">
+        <v>0</v>
+      </c>
+      <c r="E40" s="1">
+        <v>0</v>
+      </c>
+      <c r="F40" s="1">
+        <v>10</v>
+      </c>
+      <c r="G40" s="1">
+        <v>0</v>
+      </c>
+      <c r="H40" s="1">
+        <v>0</v>
+      </c>
+      <c r="I40" s="1">
+        <v>0</v>
+      </c>
+      <c r="J40" s="1">
+        <v>2</v>
+      </c>
+      <c r="K40" s="1">
+        <v>1</v>
+      </c>
+      <c r="L40" s="1">
+        <v>0</v>
+      </c>
+      <c r="M40" s="1">
+        <v>0</v>
+      </c>
+      <c r="N40" s="1">
+        <v>0</v>
+      </c>
+      <c r="O40" s="1">
+        <v>0</v>
+      </c>
+      <c r="P40" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q40" s="1">
+        <v>0</v>
+      </c>
+      <c r="R40" s="25">
+        <v>0</v>
+      </c>
+      <c r="S40" s="1"/>
+      <c r="T40" s="1"/>
+      <c r="U40" s="1"/>
+      <c r="V40" s="1"/>
+      <c r="W40" s="26"/>
+      <c r="X40" s="27" t="s">
+        <v>516</v>
+      </c>
+      <c r="Y40" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="Z40" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="AA40" s="26" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="41" ht="14.25" spans="1:27">
+      <c r="A41" s="11">
+        <v>38</v>
+      </c>
+      <c r="B41" s="12" t="s">
+        <v>519</v>
+      </c>
+      <c r="C41" s="12">
+        <v>10</v>
+      </c>
+      <c r="D41" s="12">
+        <v>0</v>
+      </c>
+      <c r="E41" s="12">
+        <v>0</v>
+      </c>
+      <c r="F41" s="12">
+        <v>10</v>
+      </c>
+      <c r="G41" s="12">
+        <v>0</v>
+      </c>
+      <c r="H41" s="12">
+        <v>0</v>
+      </c>
+      <c r="I41" s="12">
+        <v>0</v>
+      </c>
+      <c r="J41" s="12">
+        <v>2</v>
+      </c>
+      <c r="K41" s="12">
+        <v>1</v>
+      </c>
+      <c r="L41" s="12">
+        <v>0</v>
+      </c>
+      <c r="M41" s="12">
+        <v>0</v>
+      </c>
+      <c r="N41" s="12">
+        <v>0</v>
+      </c>
+      <c r="O41" s="12">
+        <v>0</v>
+      </c>
+      <c r="P41" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="12">
+        <v>0</v>
+      </c>
+      <c r="R41" s="28">
+        <v>0</v>
+      </c>
+      <c r="S41" s="12"/>
+      <c r="T41" s="12"/>
+      <c r="U41" s="12"/>
+      <c r="V41" s="12"/>
+      <c r="W41" s="29"/>
+      <c r="X41" s="30" t="s">
+        <v>520</v>
+      </c>
+      <c r="Y41" s="12" t="s">
+        <v>521</v>
+      </c>
+      <c r="Z41" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="AA41" s="29" t="s">
+        <v>356</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A7:I66"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
     <row r="7" spans="3:5">
       <c r="C7" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D7">
         <v>5</v>
@@ -3456,7 +6562,7 @@
     </row>
     <row r="8" spans="3:6">
       <c r="C8" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D8">
         <v>4</v>
@@ -3472,7 +6578,7 @@
     </row>
     <row r="9" spans="3:6">
       <c r="C9" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -3491,7 +6597,7 @@
         <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -3499,7 +6605,7 @@
         <v>2</v>
       </c>
       <c r="B13" t="s">
-        <v>504</v>
+        <v>524</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -3507,7 +6613,7 @@
         <v>3</v>
       </c>
       <c r="B14" t="s">
-        <v>505</v>
+        <v>525</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -3515,16 +6621,16 @@
         <v>4</v>
       </c>
       <c r="B15" t="s">
-        <v>506</v>
+        <v>526</v>
       </c>
       <c r="F15" t="s">
-        <v>137</v>
+        <v>155</v>
       </c>
       <c r="H15" t="s">
-        <v>137</v>
+        <v>155</v>
       </c>
       <c r="I15" t="s">
-        <v>507</v>
+        <v>527</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -3532,16 +6638,16 @@
         <v>5</v>
       </c>
       <c r="B16" t="s">
-        <v>508</v>
+        <v>528</v>
       </c>
       <c r="F16" t="s">
-        <v>507</v>
+        <v>527</v>
       </c>
       <c r="H16" t="s">
-        <v>146</v>
+        <v>175</v>
       </c>
       <c r="I16" t="s">
-        <v>509</v>
+        <v>529</v>
       </c>
     </row>
     <row r="17" spans="6:9">
@@ -3549,35 +6655,35 @@
         <v>51</v>
       </c>
       <c r="H17" t="s">
-        <v>155</v>
+        <v>184</v>
       </c>
       <c r="I17" t="s">
-        <v>510</v>
+        <v>530</v>
       </c>
     </row>
     <row r="18" spans="2:9">
       <c r="B18" t="s">
-        <v>511</v>
+        <v>531</v>
       </c>
       <c r="F18" t="s">
-        <v>146</v>
+        <v>175</v>
       </c>
       <c r="H18" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I18" t="s">
-        <v>512</v>
+        <v>532</v>
       </c>
     </row>
     <row r="19" spans="6:9">
       <c r="F19" t="s">
-        <v>509</v>
+        <v>529</v>
       </c>
       <c r="H19" t="s">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="I19" t="s">
-        <v>513</v>
+        <v>533</v>
       </c>
     </row>
     <row r="20" spans="6:8">
@@ -3585,25 +6691,25 @@
         <v>52</v>
       </c>
       <c r="H20">
-        <f>IF('intent|意图'!F17='intent|意图'!F16,#REF!&amp;"*"&amp;'intent|意图'!D17,'intent|意图'!D17)</f>
+        <f>IF('intent|意图'!F20='intent|意图'!F19,#REF!&amp;"*"&amp;'intent|意图'!D20,'intent|意图'!D20)</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="6:8">
       <c r="F21" t="s">
-        <v>155</v>
+        <v>184</v>
       </c>
       <c r="H21">
-        <f>IF('intent|意图'!F18='intent|意图'!F17,H20&amp;"*"&amp;'intent|意图'!D18,'intent|意图'!D18)</f>
+        <f>IF('intent|意图'!F21='intent|意图'!F20,H20&amp;"*"&amp;'intent|意图'!D21,'intent|意图'!D21)</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="6:8">
       <c r="F22" t="s">
-        <v>510</v>
+        <v>530</v>
       </c>
       <c r="H22">
-        <f>IF('intent|意图'!F19='intent|意图'!F18,H21&amp;"*"&amp;'intent|意图'!D19,'intent|意图'!D19)</f>
+        <f>IF('intent|意图'!F22='intent|意图'!F21,H21&amp;"*"&amp;'intent|意图'!D22,'intent|意图'!D22)</f>
         <v>0</v>
       </c>
     </row>
@@ -3612,25 +6718,25 @@
         <v>53</v>
       </c>
       <c r="H23">
-        <f>IF('intent|意图'!F20='intent|意图'!F19,H22&amp;"*"&amp;'intent|意图'!D20,'intent|意图'!D20)</f>
+        <f>IF('intent|意图'!F23='intent|意图'!F22,H22&amp;"*"&amp;'intent|意图'!D23,'intent|意图'!D23)</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="6:8">
       <c r="F24" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H24">
-        <f>IF('intent|意图'!F21='intent|意图'!F20,H23&amp;"*"&amp;'intent|意图'!D21,'intent|意图'!D21)</f>
+        <f>IF('intent|意图'!F15='intent|意图'!F23,H23&amp;"*"&amp;'intent|意图'!D15,'intent|意图'!D15)</f>
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="6:8">
       <c r="F25" t="s">
-        <v>512</v>
+        <v>532</v>
       </c>
       <c r="H25">
-        <f>IF('intent|意图'!F22='intent|意图'!F21,H24&amp;"*"&amp;'intent|意图'!D22,'intent|意图'!D22)</f>
+        <f>IF('intent|意图'!F16='intent|意图'!F15,H24&amp;"*"&amp;'intent|意图'!D16,'intent|意图'!D16)</f>
         <v>0</v>
       </c>
     </row>
@@ -3639,22 +6745,22 @@
         <v>54</v>
       </c>
       <c r="H26">
-        <f>IF('intent|意图'!F23='intent|意图'!F22,H25&amp;"*"&amp;'intent|意图'!D23,'intent|意图'!D23)</f>
+        <f>IF('intent|意图'!F17='intent|意图'!F16,H25&amp;"*"&amp;'intent|意图'!D17,'intent|意图'!D17)</f>
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="6:8">
       <c r="F27" t="s">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="H27">
-        <f>IF('intent|意图'!F24='intent|意图'!F23,H26&amp;"*"&amp;'intent|意图'!D24,'intent|意图'!D24)</f>
+        <f>IF('intent|意图'!F24='intent|意图'!F17,H26&amp;"*"&amp;'intent|意图'!D24,'intent|意图'!D24)</f>
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="6:8">
       <c r="F28" t="s">
-        <v>513</v>
+        <v>533</v>
       </c>
       <c r="H28">
         <f>IF('intent|意图'!F25='intent|意图'!F24,H27&amp;"*"&amp;'intent|意图'!D25,'intent|意图'!D25)</f>
@@ -3672,32 +6778,32 @@
     </row>
     <row r="30" spans="2:2">
       <c r="B30" t="s">
-        <v>511</v>
+        <v>531</v>
       </c>
     </row>
     <row r="42" spans="2:2">
       <c r="B42" t="s">
-        <v>511</v>
+        <v>531</v>
       </c>
     </row>
     <row r="50" spans="2:2">
       <c r="B50" t="s">
-        <v>514</v>
+        <v>534</v>
       </c>
     </row>
     <row r="54" spans="2:2">
       <c r="B54" t="s">
-        <v>511</v>
+        <v>531</v>
       </c>
     </row>
     <row r="62" spans="2:2">
       <c r="B62" t="s">
-        <v>514</v>
+        <v>534</v>
       </c>
     </row>
     <row r="66" spans="2:2">
       <c r="B66" t="s">
-        <v>511</v>
+        <v>531</v>
       </c>
     </row>
   </sheetData>
@@ -3790,7 +6896,7 @@
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultColWidth="8.86666666666667" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="8.33333333333333" style="64" customWidth="1"/>
+    <col min="1" max="1" width="8.33333333333333" style="68" customWidth="1"/>
     <col min="2" max="2" width="11.8666666666667" customWidth="1"/>
     <col min="3" max="3" width="31.4666666666667" customWidth="1"/>
   </cols>
@@ -3808,20 +6914,20 @@
       <c r="D1" s="5"/>
       <c r="E1" s="5"/>
     </row>
-    <row r="2" s="63" customFormat="1" spans="1:5">
-      <c r="A2" s="42" t="s">
+    <row r="2" s="67" customFormat="1" spans="1:5">
+      <c r="A2" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="C2" s="42" t="s">
+      <c r="C2" s="43" t="s">
         <v>40</v>
       </c>
-      <c r="D2" s="42" t="s">
+      <c r="D2" s="43" t="s">
         <v>41</v>
       </c>
-      <c r="E2" s="42" t="s">
+      <c r="E2" s="43" t="s">
         <v>42</v>
       </c>
     </row>
@@ -4004,19 +7110,20 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5"/>
   <cols>
     <col min="2" max="3" width="11.6" customWidth="1"/>
     <col min="4" max="4" width="5.86666666666667" customWidth="1"/>
-    <col min="5" max="5" width="25.625" customWidth="1"/>
-    <col min="6" max="6" width="56.2" customWidth="1"/>
+    <col min="5" max="5" width="50" customWidth="1"/>
+    <col min="6" max="6" width="62.625" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
     <col min="8" max="8" width="11" customWidth="1"/>
     <col min="9" max="9" width="25.4" customWidth="1"/>
+    <col min="10" max="10" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -4044,37 +7151,43 @@
       <c r="I1" s="5" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="2" ht="54" spans="1:9">
-      <c r="A2" s="42" t="s">
+      <c r="J1" s="21" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2" ht="54" spans="1:10">
+      <c r="A2" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="42" t="s">
-        <v>64</v>
-      </c>
-      <c r="C2" s="42" t="s">
+      <c r="B2" s="43" t="s">
         <v>65</v>
       </c>
-      <c r="D2" s="42" t="s">
+      <c r="C2" s="43" t="s">
         <v>66</v>
       </c>
+      <c r="D2" s="43" t="s">
+        <v>67</v>
+      </c>
       <c r="E2" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F2" s="42" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="43" t="s">
+      <c r="F2" s="43" t="s">
         <v>69</v>
       </c>
-      <c r="H2" s="42" t="s">
+      <c r="G2" s="44" t="s">
         <v>70</v>
       </c>
-      <c r="I2" s="62" t="s">
+      <c r="H2" s="43" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="3" spans="1:9">
+      <c r="I2" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="J2" s="21" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" s="5" t="s">
         <v>10</v>
       </c>
@@ -4091,7 +7204,7 @@
         <v>10</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>11</v>
@@ -4102,13 +7215,16 @@
       <c r="I3" s="5" t="s">
         <v>43</v>
       </c>
+      <c r="J3" s="21" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C4" s="1">
         <v>1</v>
@@ -4117,27 +7233,27 @@
         <v>1</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F4" s="40" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G4" s="1">
         <v>2</v>
       </c>
       <c r="H4" s="40" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C5" s="1">
         <v>2</v>
@@ -4146,27 +7262,30 @@
         <v>1</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G5" s="1">
         <v>1</v>
       </c>
       <c r="H5" s="40" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I5" s="40" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
+        <v>85</v>
+      </c>
+      <c r="J5" s="65" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C6" s="1">
         <v>1</v>
@@ -4175,19 +7294,22 @@
         <v>2</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F6" s="40" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="G6" s="1">
         <v>2</v>
       </c>
       <c r="H6" s="40" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I6" s="40" t="s">
-        <v>88</v>
+        <v>91</v>
+      </c>
+      <c r="J6" s="65" t="s">
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -4199,12 +7321,116 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="2"/>
+  <cols>
+    <col min="1" max="1" width="11.5" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="64" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="43" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="43" t="s">
+        <v>93</v>
+      </c>
+      <c r="C2" s="64" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="64" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="65" t="s">
+        <v>86</v>
+      </c>
+      <c r="B4" s="65" t="s">
+        <v>94</v>
+      </c>
+      <c r="C4" s="65" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="65" t="s">
+        <v>92</v>
+      </c>
+      <c r="B5" s="65" t="s">
+        <v>96</v>
+      </c>
+      <c r="C5" s="65" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="65" t="s">
+        <v>98</v>
+      </c>
+      <c r="B6" s="65" t="s">
+        <v>99</v>
+      </c>
+      <c r="C6" s="65" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="65" t="s">
+        <v>101</v>
+      </c>
+      <c r="B7" s="65" t="s">
+        <v>102</v>
+      </c>
+      <c r="C7" s="65" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="65" t="s">
+        <v>104</v>
+      </c>
+      <c r="B8" s="65" t="s">
+        <v>105</v>
+      </c>
+      <c r="C8" s="65" t="s">
+        <v>106</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:J26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="21.25" customWidth="1"/>
-    <col min="2" max="2" width="9.06666666666667" style="54"/>
-    <col min="4" max="6" width="9.06666666666667" style="54"/>
+    <col min="2" max="2" width="9.06666666666667" style="56"/>
+    <col min="4" max="6" width="9.06666666666667" style="56"/>
     <col min="7" max="7" width="62" customWidth="1"/>
     <col min="8" max="8" width="67.125" customWidth="1"/>
   </cols>
@@ -4213,116 +7439,116 @@
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="55" t="s">
-        <v>89</v>
+      <c r="B1" s="57" t="s">
+        <v>107</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="55" t="s">
-        <v>90</v>
-      </c>
-      <c r="E1" s="55" t="s">
-        <v>91</v>
-      </c>
-      <c r="F1" s="55" t="s">
-        <v>92</v>
-      </c>
-      <c r="G1" s="56" t="s">
-        <v>93</v>
-      </c>
-      <c r="H1" s="56" t="s">
+      <c r="D1" s="57" t="s">
+        <v>108</v>
+      </c>
+      <c r="E1" s="57" t="s">
+        <v>109</v>
+      </c>
+      <c r="F1" s="57" t="s">
+        <v>110</v>
+      </c>
+      <c r="G1" s="58" t="s">
+        <v>111</v>
+      </c>
+      <c r="H1" s="58" t="s">
         <v>60</v>
       </c>
-      <c r="I1" s="56" t="s">
-        <v>94</v>
-      </c>
-      <c r="J1" s="56" t="s">
-        <v>95</v>
+      <c r="I1" s="58" t="s">
+        <v>112</v>
+      </c>
+      <c r="J1" s="58" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="55" t="s">
-        <v>96</v>
+      <c r="B2" s="57" t="s">
+        <v>114</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="D2" s="55" t="s">
-        <v>98</v>
-      </c>
-      <c r="E2" s="55" t="s">
-        <v>99</v>
-      </c>
-      <c r="F2" s="55" t="s">
-        <v>100</v>
-      </c>
-      <c r="G2" s="56" t="s">
-        <v>101</v>
-      </c>
-      <c r="H2" s="56" t="s">
-        <v>102</v>
-      </c>
-      <c r="I2" s="56" t="s">
-        <v>103</v>
-      </c>
-      <c r="J2" s="56" t="s">
-        <v>104</v>
+        <v>115</v>
+      </c>
+      <c r="D2" s="57" t="s">
+        <v>116</v>
+      </c>
+      <c r="E2" s="57" t="s">
+        <v>117</v>
+      </c>
+      <c r="F2" s="57" t="s">
+        <v>118</v>
+      </c>
+      <c r="G2" s="58" t="s">
+        <v>119</v>
+      </c>
+      <c r="H2" s="58" t="s">
+        <v>120</v>
+      </c>
+      <c r="I2" s="58" t="s">
+        <v>121</v>
+      </c>
+      <c r="J2" s="58" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="55" t="s">
+      <c r="B3" s="57" t="s">
         <v>10</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="55" t="s">
+      <c r="D3" s="57" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="55" t="s">
-        <v>105</v>
-      </c>
-      <c r="F3" s="55" t="s">
+      <c r="E3" s="57" t="s">
+        <v>123</v>
+      </c>
+      <c r="F3" s="57" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="56" t="s">
-        <v>10</v>
-      </c>
-      <c r="H3" s="56" t="s">
-        <v>72</v>
-      </c>
-      <c r="I3" s="56" t="s">
+      <c r="G3" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="58" t="s">
+        <v>74</v>
+      </c>
+      <c r="I3" s="58" t="s">
         <v>11</v>
       </c>
-      <c r="J3" s="56" t="s">
+      <c r="J3" s="58" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="B4" s="57"/>
+        <v>124</v>
+      </c>
+      <c r="B4" s="59"/>
       <c r="C4" s="40" t="s">
-        <v>107</v>
-      </c>
-      <c r="D4" s="57">
-        <v>1</v>
-      </c>
-      <c r="E4" s="57"/>
-      <c r="F4" s="57"/>
+        <v>125</v>
+      </c>
+      <c r="D4" s="59">
+        <v>1</v>
+      </c>
+      <c r="E4" s="59"/>
+      <c r="F4" s="59"/>
       <c r="G4" s="40" t="s">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="I4" s="1">
         <v>8</v>
@@ -4331,22 +7557,22 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="B5" s="57"/>
+        <v>128</v>
+      </c>
+      <c r="B5" s="59"/>
       <c r="C5" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="D5" s="57">
+        <v>129</v>
+      </c>
+      <c r="D5" s="59">
         <v>2</v>
       </c>
-      <c r="E5" s="57"/>
-      <c r="F5" s="57"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="59"/>
       <c r="G5" s="40" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="H5" s="40" t="s">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="I5" s="1">
         <v>3</v>
@@ -4355,22 +7581,22 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="B6" s="57"/>
+        <v>132</v>
+      </c>
+      <c r="B6" s="59"/>
       <c r="C6" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="D6" s="57">
+        <v>81</v>
+      </c>
+      <c r="D6" s="59">
         <v>3</v>
       </c>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
+      <c r="E6" s="59"/>
+      <c r="F6" s="59"/>
       <c r="G6" s="40" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="I6" s="1">
         <v>0</v>
@@ -4379,22 +7605,22 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="B7" s="57"/>
+        <v>135</v>
+      </c>
+      <c r="B7" s="59"/>
       <c r="C7" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="D7" s="57">
+        <v>136</v>
+      </c>
+      <c r="D7" s="59">
         <v>4</v>
       </c>
-      <c r="E7" s="57"/>
-      <c r="F7" s="57"/>
+      <c r="E7" s="59"/>
+      <c r="F7" s="59"/>
       <c r="G7" s="1" t="s">
-        <v>119</v>
+        <v>137</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>120</v>
+        <v>138</v>
       </c>
       <c r="I7" s="1">
         <v>0</v>
@@ -4403,22 +7629,22 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="B8" s="57"/>
+        <v>139</v>
+      </c>
+      <c r="B8" s="59"/>
       <c r="C8" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="D8" s="57">
+        <v>140</v>
+      </c>
+      <c r="D8" s="59">
         <v>5</v>
       </c>
-      <c r="E8" s="57"/>
-      <c r="F8" s="57"/>
+      <c r="E8" s="59"/>
+      <c r="F8" s="59"/>
       <c r="G8" s="1" t="s">
-        <v>123</v>
+        <v>141</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="I8" s="1">
         <v>0</v>
@@ -4427,22 +7653,22 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B9" s="57"/>
+        <v>143</v>
+      </c>
+      <c r="B9" s="59"/>
       <c r="C9" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="D9" s="57">
+        <v>144</v>
+      </c>
+      <c r="D9" s="59">
         <v>6</v>
       </c>
-      <c r="E9" s="57"/>
-      <c r="F9" s="57"/>
+      <c r="E9" s="59"/>
+      <c r="F9" s="59"/>
       <c r="G9" s="1" t="s">
-        <v>127</v>
+        <v>145</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>128</v>
+        <v>146</v>
       </c>
       <c r="I9" s="1">
         <v>0</v>
@@ -4451,22 +7677,22 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="B10" s="57"/>
+        <v>147</v>
+      </c>
+      <c r="B10" s="59"/>
       <c r="C10" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="D10" s="57">
+        <v>148</v>
+      </c>
+      <c r="D10" s="59">
         <v>7</v>
       </c>
-      <c r="E10" s="57"/>
-      <c r="F10" s="57"/>
+      <c r="E10" s="59"/>
+      <c r="F10" s="59"/>
       <c r="G10" s="1" t="s">
-        <v>131</v>
+        <v>149</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>132</v>
+        <v>150</v>
       </c>
       <c r="I10" s="1">
         <v>0</v>
@@ -4475,22 +7701,22 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B11" s="57"/>
+        <v>151</v>
+      </c>
+      <c r="B11" s="59"/>
       <c r="C11" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="D11" s="57">
+        <v>152</v>
+      </c>
+      <c r="D11" s="59">
         <v>8</v>
       </c>
-      <c r="E11" s="57"/>
-      <c r="F11" s="57"/>
+      <c r="E11" s="59"/>
+      <c r="F11" s="59"/>
       <c r="G11" s="1" t="s">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>136</v>
+        <v>154</v>
       </c>
       <c r="I11" s="1">
         <v>0</v>
@@ -4499,423 +7725,423 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="46" t="s">
-        <v>137</v>
+        <v>155</v>
       </c>
       <c r="B12" s="47" t="s">
         <v>14</v>
       </c>
       <c r="C12" s="47" t="s">
-        <v>138</v>
-      </c>
-      <c r="D12" s="58"/>
-      <c r="E12" s="58">
-        <v>1</v>
-      </c>
-      <c r="F12" s="58">
+        <v>156</v>
+      </c>
+      <c r="D12" s="60"/>
+      <c r="E12" s="60">
+        <v>1</v>
+      </c>
+      <c r="F12" s="60">
         <v>0</v>
       </c>
       <c r="G12" s="47" t="s">
-        <v>139</v>
+        <v>157</v>
       </c>
       <c r="H12" s="47" t="s">
-        <v>136</v>
-      </c>
-      <c r="I12" s="61">
-        <v>0</v>
-      </c>
-      <c r="J12" s="50"/>
+        <v>158</v>
+      </c>
+      <c r="I12" s="47">
+        <v>0</v>
+      </c>
+      <c r="J12" s="49"/>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="49" t="s">
-        <v>140</v>
-      </c>
-      <c r="B13" s="50" t="s">
+      <c r="A13" s="48" t="s">
+        <v>159</v>
+      </c>
+      <c r="B13" s="49" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="50" t="s">
-        <v>141</v>
-      </c>
-      <c r="D13" s="59"/>
-      <c r="E13" s="59">
-        <v>1</v>
-      </c>
-      <c r="F13" s="59">
-        <v>1</v>
-      </c>
-      <c r="G13" s="50" t="s">
-        <v>142</v>
-      </c>
-      <c r="H13" s="50" t="s">
-        <v>136</v>
-      </c>
-      <c r="I13" s="50">
-        <v>0</v>
-      </c>
-      <c r="J13" s="50"/>
+      <c r="C13" s="49" t="s">
+        <v>160</v>
+      </c>
+      <c r="D13" s="61"/>
+      <c r="E13" s="61">
+        <v>1</v>
+      </c>
+      <c r="F13" s="61">
+        <v>1</v>
+      </c>
+      <c r="G13" s="49" t="s">
+        <v>161</v>
+      </c>
+      <c r="H13" s="49" t="s">
+        <v>162</v>
+      </c>
+      <c r="I13" s="49">
+        <v>0</v>
+      </c>
+      <c r="J13" s="49"/>
     </row>
     <row r="14" spans="1:10">
-      <c r="A14" s="49" t="s">
-        <v>143</v>
-      </c>
-      <c r="B14" s="50" t="s">
+      <c r="A14" s="48" t="s">
+        <v>163</v>
+      </c>
+      <c r="B14" s="49" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="50" t="s">
-        <v>144</v>
-      </c>
-      <c r="D14" s="59"/>
-      <c r="E14" s="59">
-        <v>1</v>
-      </c>
-      <c r="F14" s="59">
+      <c r="C14" s="49" t="s">
+        <v>105</v>
+      </c>
+      <c r="D14" s="61"/>
+      <c r="E14" s="61">
+        <v>1</v>
+      </c>
+      <c r="F14" s="61">
         <v>3</v>
       </c>
-      <c r="G14" s="50" t="s">
-        <v>145</v>
-      </c>
-      <c r="H14" s="50" t="s">
-        <v>136</v>
-      </c>
-      <c r="I14" s="50">
-        <v>0</v>
-      </c>
-      <c r="J14" s="50"/>
-    </row>
-    <row r="15" s="53" customFormat="1" spans="1:10">
-      <c r="A15" s="51" t="s">
+      <c r="G14" s="49" t="s">
+        <v>164</v>
+      </c>
+      <c r="H14" s="49" t="s">
+        <v>131</v>
+      </c>
+      <c r="I14" s="49">
+        <v>0</v>
+      </c>
+      <c r="J14" s="49"/>
+    </row>
+    <row r="15" s="42" customFormat="1" spans="1:10">
+      <c r="A15" s="50" t="s">
+        <v>165</v>
+      </c>
+      <c r="B15" s="51" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" s="51" t="s">
+        <v>166</v>
+      </c>
+      <c r="D15" s="62"/>
+      <c r="E15" s="62">
+        <v>1</v>
+      </c>
+      <c r="F15" s="62">
+        <v>0</v>
+      </c>
+      <c r="G15" s="51" t="s">
+        <v>167</v>
+      </c>
+      <c r="H15" s="51" t="s">
+        <v>168</v>
+      </c>
+      <c r="I15" s="51">
+        <v>0</v>
+      </c>
+      <c r="J15" s="51"/>
+    </row>
+    <row r="16" s="42" customFormat="1" spans="1:10">
+      <c r="A16" s="50" t="s">
+        <v>169</v>
+      </c>
+      <c r="B16" s="51" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" s="51" t="s">
+        <v>170</v>
+      </c>
+      <c r="D16" s="62"/>
+      <c r="E16" s="62">
+        <v>1</v>
+      </c>
+      <c r="F16" s="62">
+        <v>1</v>
+      </c>
+      <c r="G16" s="51" t="s">
+        <v>171</v>
+      </c>
+      <c r="H16" s="51" t="s">
         <v>146</v>
       </c>
-      <c r="B15" s="52" t="s">
+      <c r="I16" s="51">
+        <v>0</v>
+      </c>
+      <c r="J16" s="51"/>
+    </row>
+    <row r="17" s="42" customFormat="1" spans="1:10">
+      <c r="A17" s="50" t="s">
+        <v>172</v>
+      </c>
+      <c r="B17" s="51" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" s="51" t="s">
+        <v>173</v>
+      </c>
+      <c r="D17" s="62"/>
+      <c r="E17" s="62">
+        <v>1</v>
+      </c>
+      <c r="F17" s="62">
+        <v>3</v>
+      </c>
+      <c r="G17" s="51" t="s">
+        <v>174</v>
+      </c>
+      <c r="H17" s="51" t="s">
+        <v>150</v>
+      </c>
+      <c r="I17" s="51">
+        <v>0</v>
+      </c>
+      <c r="J17" s="51"/>
+    </row>
+    <row r="18" s="55" customFormat="1" spans="1:10">
+      <c r="A18" s="53" t="s">
+        <v>175</v>
+      </c>
+      <c r="B18" s="54" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="52" t="s">
-        <v>147</v>
-      </c>
-      <c r="D15" s="60"/>
-      <c r="E15" s="60">
-        <v>1</v>
-      </c>
-      <c r="F15" s="60">
-        <v>0</v>
-      </c>
-      <c r="G15" s="52" t="s">
-        <v>148</v>
-      </c>
-      <c r="H15" s="52" t="s">
-        <v>136</v>
-      </c>
-      <c r="I15" s="52">
-        <v>0</v>
-      </c>
-      <c r="J15" s="52"/>
-    </row>
-    <row r="16" s="53" customFormat="1" spans="1:10">
-      <c r="A16" s="51" t="s">
-        <v>149</v>
-      </c>
-      <c r="B16" s="52" t="s">
+      <c r="C18" s="54" t="s">
+        <v>176</v>
+      </c>
+      <c r="D18" s="63"/>
+      <c r="E18" s="63">
+        <v>1</v>
+      </c>
+      <c r="F18" s="63">
+        <v>0</v>
+      </c>
+      <c r="G18" s="54" t="s">
+        <v>177</v>
+      </c>
+      <c r="H18" s="54" t="s">
+        <v>154</v>
+      </c>
+      <c r="I18" s="54">
+        <v>0</v>
+      </c>
+      <c r="J18" s="54"/>
+    </row>
+    <row r="19" s="55" customFormat="1" spans="1:10">
+      <c r="A19" s="53" t="s">
+        <v>178</v>
+      </c>
+      <c r="B19" s="54" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="52" t="s">
-        <v>150</v>
-      </c>
-      <c r="D16" s="60"/>
-      <c r="E16" s="60">
-        <v>1</v>
-      </c>
-      <c r="F16" s="60">
-        <v>1</v>
-      </c>
-      <c r="G16" s="52" t="s">
-        <v>151</v>
-      </c>
-      <c r="H16" s="52" t="s">
-        <v>136</v>
-      </c>
-      <c r="I16" s="52">
-        <v>0</v>
-      </c>
-      <c r="J16" s="52"/>
-    </row>
-    <row r="17" s="53" customFormat="1" spans="1:10">
-      <c r="A17" s="51" t="s">
-        <v>152</v>
-      </c>
-      <c r="B17" s="52" t="s">
+      <c r="C19" s="54" t="s">
+        <v>179</v>
+      </c>
+      <c r="D19" s="63"/>
+      <c r="E19" s="63">
+        <v>1</v>
+      </c>
+      <c r="F19" s="63">
+        <v>1</v>
+      </c>
+      <c r="G19" s="54" t="s">
+        <v>180</v>
+      </c>
+      <c r="H19" s="54" t="s">
+        <v>154</v>
+      </c>
+      <c r="I19" s="54">
+        <v>0</v>
+      </c>
+      <c r="J19" s="54"/>
+    </row>
+    <row r="20" s="55" customFormat="1" spans="1:10">
+      <c r="A20" s="53" t="s">
+        <v>181</v>
+      </c>
+      <c r="B20" s="54" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="52" t="s">
-        <v>153</v>
-      </c>
-      <c r="D17" s="60"/>
-      <c r="E17" s="60">
-        <v>1</v>
-      </c>
-      <c r="F17" s="60">
+      <c r="C20" s="54" t="s">
+        <v>182</v>
+      </c>
+      <c r="D20" s="63"/>
+      <c r="E20" s="63">
+        <v>1</v>
+      </c>
+      <c r="F20" s="63">
         <v>3</v>
       </c>
-      <c r="G17" s="52" t="s">
+      <c r="G20" s="54" t="s">
+        <v>183</v>
+      </c>
+      <c r="H20" s="54" t="s">
         <v>154</v>
       </c>
-      <c r="H17" s="52" t="s">
-        <v>136</v>
-      </c>
-      <c r="I17" s="52">
-        <v>0</v>
-      </c>
-      <c r="J17" s="52"/>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="A18" s="49" t="s">
-        <v>155</v>
-      </c>
-      <c r="B18" s="50" t="s">
+      <c r="I20" s="54">
+        <v>0</v>
+      </c>
+      <c r="J20" s="54"/>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="48" t="s">
+        <v>184</v>
+      </c>
+      <c r="B21" s="49" t="s">
         <v>20</v>
       </c>
-      <c r="C18" s="50" t="s">
-        <v>156</v>
-      </c>
-      <c r="D18" s="59"/>
-      <c r="E18" s="59">
-        <v>1</v>
-      </c>
-      <c r="F18" s="59">
-        <v>0</v>
-      </c>
-      <c r="G18" s="50" t="s">
-        <v>157</v>
-      </c>
-      <c r="H18" s="50" t="s">
-        <v>136</v>
-      </c>
-      <c r="I18" s="50">
-        <v>0</v>
-      </c>
-      <c r="J18" s="50"/>
-    </row>
-    <row r="19" spans="1:10">
-      <c r="A19" s="49" t="s">
-        <v>158</v>
-      </c>
-      <c r="B19" s="50" t="s">
+      <c r="C21" s="49" t="s">
+        <v>185</v>
+      </c>
+      <c r="D21" s="61"/>
+      <c r="E21" s="61">
+        <v>1</v>
+      </c>
+      <c r="F21" s="61">
+        <v>0</v>
+      </c>
+      <c r="G21" s="49" t="s">
+        <v>186</v>
+      </c>
+      <c r="H21" s="49" t="s">
+        <v>154</v>
+      </c>
+      <c r="I21" s="49">
+        <v>0</v>
+      </c>
+      <c r="J21" s="49"/>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="48" t="s">
+        <v>187</v>
+      </c>
+      <c r="B22" s="49" t="s">
         <v>20</v>
       </c>
-      <c r="C19" s="50" t="s">
-        <v>159</v>
-      </c>
-      <c r="D19" s="59"/>
-      <c r="E19" s="59">
-        <v>1</v>
-      </c>
-      <c r="F19" s="59">
-        <v>1</v>
-      </c>
-      <c r="G19" s="50" t="s">
-        <v>160</v>
-      </c>
-      <c r="H19" s="50" t="s">
-        <v>136</v>
-      </c>
-      <c r="I19" s="50">
-        <v>0</v>
-      </c>
-      <c r="J19" s="50"/>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="A20" s="49" t="s">
-        <v>161</v>
-      </c>
-      <c r="B20" s="50" t="s">
+      <c r="C22" s="49" t="s">
+        <v>188</v>
+      </c>
+      <c r="D22" s="61"/>
+      <c r="E22" s="61">
+        <v>1</v>
+      </c>
+      <c r="F22" s="61">
+        <v>1</v>
+      </c>
+      <c r="G22" s="49" t="s">
+        <v>189</v>
+      </c>
+      <c r="H22" s="49" t="s">
+        <v>154</v>
+      </c>
+      <c r="I22" s="49">
+        <v>0</v>
+      </c>
+      <c r="J22" s="49"/>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="48" t="s">
+        <v>190</v>
+      </c>
+      <c r="B23" s="49" t="s">
         <v>20</v>
       </c>
-      <c r="C20" s="50" t="s">
-        <v>162</v>
-      </c>
-      <c r="D20" s="59"/>
-      <c r="E20" s="59">
-        <v>1</v>
-      </c>
-      <c r="F20" s="59">
+      <c r="C23" s="49" t="s">
+        <v>191</v>
+      </c>
+      <c r="D23" s="61"/>
+      <c r="E23" s="61">
+        <v>1</v>
+      </c>
+      <c r="F23" s="61">
         <v>3</v>
       </c>
-      <c r="G20" s="50" t="s">
-        <v>163</v>
-      </c>
-      <c r="H20" s="50" t="s">
-        <v>136</v>
-      </c>
-      <c r="I20" s="50">
-        <v>0</v>
-      </c>
-      <c r="J20" s="50"/>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="A21" s="49" t="s">
-        <v>164</v>
-      </c>
-      <c r="B21" s="50" t="s">
-        <v>23</v>
-      </c>
-      <c r="C21" s="50" t="s">
-        <v>165</v>
-      </c>
-      <c r="D21" s="59"/>
-      <c r="E21" s="59">
-        <v>1</v>
-      </c>
-      <c r="F21" s="59">
-        <v>0</v>
-      </c>
-      <c r="G21" s="50" t="s">
-        <v>166</v>
-      </c>
-      <c r="H21" s="50" t="s">
-        <v>136</v>
-      </c>
-      <c r="I21" s="50">
-        <v>0</v>
-      </c>
-      <c r="J21" s="50"/>
-    </row>
-    <row r="22" spans="1:10">
-      <c r="A22" s="49" t="s">
-        <v>167</v>
-      </c>
-      <c r="B22" s="50" t="s">
-        <v>23</v>
-      </c>
-      <c r="C22" s="50" t="s">
-        <v>168</v>
-      </c>
-      <c r="D22" s="59"/>
-      <c r="E22" s="59">
-        <v>1</v>
-      </c>
-      <c r="F22" s="59">
-        <v>1</v>
-      </c>
-      <c r="G22" s="50" t="s">
-        <v>169</v>
-      </c>
-      <c r="H22" s="50" t="s">
-        <v>136</v>
-      </c>
-      <c r="I22" s="50">
-        <v>0</v>
-      </c>
-      <c r="J22" s="50"/>
-    </row>
-    <row r="23" spans="1:10">
-      <c r="A23" s="49" t="s">
-        <v>170</v>
-      </c>
-      <c r="B23" s="50" t="s">
-        <v>23</v>
-      </c>
-      <c r="C23" s="50" t="s">
-        <v>171</v>
-      </c>
-      <c r="D23" s="59"/>
-      <c r="E23" s="59">
-        <v>1</v>
-      </c>
-      <c r="F23" s="59">
-        <v>3</v>
-      </c>
-      <c r="G23" s="50" t="s">
-        <v>172</v>
-      </c>
-      <c r="H23" s="50" t="s">
-        <v>136</v>
-      </c>
-      <c r="I23" s="50">
-        <v>0</v>
-      </c>
-      <c r="J23" s="50"/>
+      <c r="G23" s="49" t="s">
+        <v>192</v>
+      </c>
+      <c r="H23" s="49" t="s">
+        <v>154</v>
+      </c>
+      <c r="I23" s="49">
+        <v>0</v>
+      </c>
+      <c r="J23" s="49"/>
     </row>
     <row r="24" spans="1:10">
-      <c r="A24" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="B24" s="50" t="s">
+      <c r="A24" s="48" t="s">
+        <v>193</v>
+      </c>
+      <c r="B24" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="C24" s="50" t="s">
-        <v>174</v>
-      </c>
-      <c r="D24" s="59"/>
-      <c r="E24" s="59">
-        <v>1</v>
-      </c>
-      <c r="F24" s="59">
-        <v>0</v>
-      </c>
-      <c r="G24" s="50" t="s">
-        <v>175</v>
-      </c>
-      <c r="H24" s="50" t="s">
-        <v>136</v>
-      </c>
-      <c r="I24" s="50">
-        <v>0</v>
-      </c>
-      <c r="J24" s="50"/>
+      <c r="C24" s="49" t="s">
+        <v>194</v>
+      </c>
+      <c r="D24" s="61"/>
+      <c r="E24" s="61">
+        <v>1</v>
+      </c>
+      <c r="F24" s="61">
+        <v>0</v>
+      </c>
+      <c r="G24" s="49" t="s">
+        <v>195</v>
+      </c>
+      <c r="H24" s="49" t="s">
+        <v>154</v>
+      </c>
+      <c r="I24" s="49">
+        <v>0</v>
+      </c>
+      <c r="J24" s="49"/>
     </row>
     <row r="25" spans="1:10">
-      <c r="A25" s="49" t="s">
-        <v>176</v>
-      </c>
-      <c r="B25" s="50" t="s">
+      <c r="A25" s="48" t="s">
+        <v>196</v>
+      </c>
+      <c r="B25" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="C25" s="50" t="s">
-        <v>177</v>
-      </c>
-      <c r="D25" s="59"/>
-      <c r="E25" s="59">
-        <v>1</v>
-      </c>
-      <c r="F25" s="59">
-        <v>1</v>
-      </c>
-      <c r="G25" s="52" t="s">
+      <c r="C25" s="49" t="s">
+        <v>197</v>
+      </c>
+      <c r="D25" s="61"/>
+      <c r="E25" s="61">
+        <v>1</v>
+      </c>
+      <c r="F25" s="61">
+        <v>1</v>
+      </c>
+      <c r="G25" s="54" t="s">
+        <v>183</v>
+      </c>
+      <c r="H25" s="49" t="s">
         <v>154</v>
       </c>
-      <c r="H25" s="50" t="s">
-        <v>136</v>
-      </c>
-      <c r="I25" s="50">
-        <v>0</v>
-      </c>
-      <c r="J25" s="50"/>
+      <c r="I25" s="49">
+        <v>0</v>
+      </c>
+      <c r="J25" s="49"/>
     </row>
     <row r="26" s="41" customFormat="1" spans="1:10">
       <c r="A26" s="46" t="s">
-        <v>178</v>
+        <v>198</v>
       </c>
       <c r="B26" s="47" t="s">
         <v>26</v>
       </c>
       <c r="C26" s="47" t="s">
-        <v>179</v>
-      </c>
-      <c r="D26" s="58"/>
-      <c r="E26" s="58">
-        <v>1</v>
-      </c>
-      <c r="F26" s="58">
+        <v>199</v>
+      </c>
+      <c r="D26" s="60"/>
+      <c r="E26" s="60">
+        <v>1</v>
+      </c>
+      <c r="F26" s="60">
         <v>3</v>
       </c>
       <c r="G26" s="47" t="s">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="H26" s="47" t="s">
-        <v>136</v>
-      </c>
-      <c r="I26" s="61">
-        <v>0</v>
-      </c>
-      <c r="J26" s="61"/>
+        <v>154</v>
+      </c>
+      <c r="I26" s="47">
+        <v>0</v>
+      </c>
+      <c r="J26" s="47"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4923,7 +8149,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:I31"/>
@@ -4942,51 +8168,51 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>181</v>
+        <v>201</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>182</v>
+        <v>202</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>61</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>183</v>
+        <v>203</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>185</v>
+        <v>205</v>
       </c>
       <c r="H1" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" ht="108" spans="1:8">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="43" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>181</v>
+        <v>201</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="D2" s="43" t="s">
-        <v>187</v>
-      </c>
-      <c r="E2" s="42" t="s">
-        <v>188</v>
-      </c>
-      <c r="F2" s="42" t="s">
-        <v>189</v>
-      </c>
-      <c r="G2" s="42" t="s">
-        <v>190</v>
+        <v>206</v>
+      </c>
+      <c r="D2" s="44" t="s">
+        <v>207</v>
+      </c>
+      <c r="E2" s="43" t="s">
+        <v>208</v>
+      </c>
+      <c r="F2" s="43" t="s">
+        <v>209</v>
+      </c>
+      <c r="G2" s="43" t="s">
+        <v>210</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>191</v>
+        <v>211</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -5017,11 +8243,11 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D4" s="1">
         <v>0</v>
@@ -5036,16 +8262,16 @@
         <v>6</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="40" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="40" t="s">
-        <v>192</v>
+        <v>212</v>
       </c>
       <c r="D5" s="1">
         <v>1</v>
@@ -5060,16 +8286,16 @@
         <v>5</v>
       </c>
       <c r="H5" s="40" t="s">
-        <v>193</v>
+        <v>213</v>
       </c>
     </row>
     <row r="6" s="41" customFormat="1" spans="1:8">
-      <c r="A6" s="44" t="s">
-        <v>194</v>
+      <c r="A6" s="45" t="s">
+        <v>214</v>
       </c>
       <c r="B6" s="45"/>
-      <c r="C6" s="44" t="s">
-        <v>85</v>
+      <c r="C6" s="45" t="s">
+        <v>88</v>
       </c>
       <c r="D6" s="45">
         <v>0</v>
@@ -5083,17 +8309,17 @@
       <c r="G6" s="45">
         <v>8</v>
       </c>
-      <c r="H6" s="44" t="s">
-        <v>195</v>
+      <c r="H6" s="45" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="7" s="41" customFormat="1" spans="1:8">
-      <c r="A7" s="44" t="s">
-        <v>196</v>
+      <c r="A7" s="45" t="s">
+        <v>216</v>
       </c>
       <c r="B7" s="45"/>
-      <c r="C7" s="44" t="s">
-        <v>197</v>
+      <c r="C7" s="45" t="s">
+        <v>217</v>
       </c>
       <c r="D7" s="45">
         <v>0</v>
@@ -5104,22 +8330,22 @@
       <c r="F7" s="45">
         <v>3</v>
       </c>
-      <c r="G7" s="44" t="s">
-        <v>198</v>
-      </c>
-      <c r="H7" s="44" t="s">
-        <v>199</v>
+      <c r="G7" s="45" t="s">
+        <v>218</v>
+      </c>
+      <c r="H7" s="45" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="1" t="s">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>202</v>
+        <v>96</v>
       </c>
       <c r="D8" s="1">
         <v>0</v>
@@ -5134,18 +8360,18 @@
         <v>1</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>203</v>
+        <v>222</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
-        <v>204</v>
+        <v>223</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>205</v>
+        <v>224</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -5160,18 +8386,18 @@
         <v>2</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>206</v>
+        <v>225</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
-        <v>207</v>
+        <v>226</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>208</v>
+        <v>227</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>209</v>
+        <v>102</v>
       </c>
       <c r="D10" s="1">
         <v>0</v>
@@ -5186,18 +8412,18 @@
         <v>3</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>210</v>
+        <v>228</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
-        <v>211</v>
+        <v>229</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>212</v>
+        <v>230</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>213</v>
+        <v>231</v>
       </c>
       <c r="D11" s="1">
         <v>0</v>
@@ -5212,18 +8438,18 @@
         <v>4</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>214</v>
+        <v>232</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
-        <v>215</v>
+        <v>233</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>216</v>
+        <v>234</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="D12" s="1">
         <v>0</v>
@@ -5238,18 +8464,18 @@
         <v>5</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>217</v>
+        <v>235</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1" t="s">
-        <v>218</v>
+        <v>236</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>220</v>
+        <v>238</v>
       </c>
       <c r="D13" s="1">
         <v>0</v>
@@ -5264,18 +8490,18 @@
         <v>6</v>
       </c>
       <c r="H13" s="40" t="s">
-        <v>221</v>
+        <v>239</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>222</v>
+        <v>240</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>223</v>
+        <v>241</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>224</v>
+        <v>242</v>
       </c>
       <c r="D14" s="1">
         <v>0</v>
@@ -5290,18 +8516,18 @@
         <v>7</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>225</v>
+        <v>243</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1" t="s">
-        <v>226</v>
+        <v>244</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>227</v>
+        <v>245</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>228</v>
+        <v>246</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -5316,18 +8542,18 @@
         <v>8</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>231</v>
+        <v>249</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>232</v>
+        <v>250</v>
       </c>
       <c r="D16" s="1">
         <v>0</v>
@@ -5342,343 +8568,343 @@
         <v>9</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>233</v>
+        <v>251</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="46" t="s">
-        <v>137</v>
+        <v>155</v>
       </c>
       <c r="B17" s="47" t="s">
-        <v>138</v>
+        <v>252</v>
       </c>
       <c r="C17" s="47" t="s">
-        <v>138</v>
+        <v>252</v>
       </c>
       <c r="D17" s="1">
         <v>0</v>
       </c>
-      <c r="E17" s="48"/>
-      <c r="F17" s="48"/>
-      <c r="G17" s="48"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
       <c r="H17" s="47" t="s">
-        <v>139</v>
+        <v>253</v>
       </c>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="49" t="s">
-        <v>140</v>
-      </c>
-      <c r="B18" s="50" t="s">
-        <v>141</v>
-      </c>
-      <c r="C18" s="50" t="s">
-        <v>141</v>
+      <c r="A18" s="48" t="s">
+        <v>159</v>
+      </c>
+      <c r="B18" s="49" t="s">
+        <v>160</v>
+      </c>
+      <c r="C18" s="49" t="s">
+        <v>160</v>
       </c>
       <c r="D18" s="1">
         <v>0</v>
       </c>
-      <c r="E18" s="48"/>
-      <c r="F18" s="48"/>
-      <c r="G18" s="48"/>
-      <c r="H18" s="50" t="s">
-        <v>142</v>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="49" t="s">
+        <v>161</v>
       </c>
       <c r="I18" t="s">
-        <v>234</v>
+        <v>254</v>
       </c>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="49" t="s">
-        <v>143</v>
-      </c>
-      <c r="B19" s="50" t="s">
-        <v>144</v>
-      </c>
-      <c r="C19" s="50" t="s">
-        <v>144</v>
+      <c r="A19" s="48" t="s">
+        <v>163</v>
+      </c>
+      <c r="B19" s="49" t="s">
+        <v>105</v>
+      </c>
+      <c r="C19" s="49" t="s">
+        <v>105</v>
       </c>
       <c r="D19" s="1">
         <v>0</v>
       </c>
-      <c r="E19" s="48"/>
-      <c r="F19" s="48"/>
-      <c r="G19" s="48"/>
-      <c r="H19" s="50" t="s">
-        <v>235</v>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="49" t="s">
+        <v>255</v>
       </c>
       <c r="I19" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9">
-      <c r="A20" s="51" t="s">
-        <v>146</v>
-      </c>
-      <c r="B20" s="52" t="s">
-        <v>147</v>
-      </c>
-      <c r="C20" s="52" t="s">
-        <v>147</v>
-      </c>
-      <c r="D20" s="1">
-        <v>0</v>
-      </c>
-      <c r="E20" s="48"/>
-      <c r="F20" s="48"/>
-      <c r="G20" s="48"/>
-      <c r="H20" s="52" t="s">
-        <v>237</v>
-      </c>
-      <c r="I20" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9">
-      <c r="A21" s="51" t="s">
-        <v>149</v>
-      </c>
-      <c r="B21" s="52" t="s">
-        <v>150</v>
-      </c>
-      <c r="C21" s="52" t="s">
-        <v>150</v>
-      </c>
-      <c r="D21" s="1">
-        <v>0</v>
-      </c>
-      <c r="E21" s="48"/>
-      <c r="F21" s="48"/>
-      <c r="G21" s="48"/>
-      <c r="H21" s="48" t="s">
-        <v>199</v>
-      </c>
-      <c r="I21" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9">
-      <c r="A22" s="51" t="s">
-        <v>152</v>
-      </c>
-      <c r="B22" s="52" t="s">
-        <v>153</v>
-      </c>
-      <c r="C22" s="52" t="s">
-        <v>153</v>
-      </c>
-      <c r="D22" s="1">
-        <v>0</v>
-      </c>
-      <c r="E22" s="48"/>
-      <c r="F22" s="48"/>
-      <c r="G22" s="48"/>
-      <c r="H22" s="52" t="s">
-        <v>154</v>
-      </c>
-      <c r="I22" t="s">
-        <v>239</v>
+        <v>256</v>
+      </c>
+    </row>
+    <row r="20" s="42" customFormat="1" spans="1:9">
+      <c r="A20" s="50" t="s">
+        <v>165</v>
+      </c>
+      <c r="B20" s="51" t="s">
+        <v>166</v>
+      </c>
+      <c r="C20" s="51" t="s">
+        <v>166</v>
+      </c>
+      <c r="D20" s="52">
+        <v>0</v>
+      </c>
+      <c r="E20" s="52"/>
+      <c r="F20" s="52"/>
+      <c r="G20" s="52"/>
+      <c r="H20" s="51" t="s">
+        <v>167</v>
+      </c>
+      <c r="I20" s="42" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="21" s="42" customFormat="1" spans="1:9">
+      <c r="A21" s="50" t="s">
+        <v>169</v>
+      </c>
+      <c r="B21" s="51" t="s">
+        <v>170</v>
+      </c>
+      <c r="C21" s="51" t="s">
+        <v>170</v>
+      </c>
+      <c r="D21" s="52">
+        <v>0</v>
+      </c>
+      <c r="E21" s="52"/>
+      <c r="F21" s="52"/>
+      <c r="G21" s="52"/>
+      <c r="H21" s="51" t="s">
+        <v>258</v>
+      </c>
+      <c r="I21" s="42" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="22" s="42" customFormat="1" spans="1:9">
+      <c r="A22" s="50" t="s">
+        <v>172</v>
+      </c>
+      <c r="B22" s="51" t="s">
+        <v>173</v>
+      </c>
+      <c r="C22" s="51" t="s">
+        <v>173</v>
+      </c>
+      <c r="D22" s="52">
+        <v>0</v>
+      </c>
+      <c r="E22" s="52"/>
+      <c r="F22" s="52"/>
+      <c r="G22" s="52"/>
+      <c r="H22" s="51" t="s">
+        <v>174</v>
+      </c>
+      <c r="I22" s="42" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="49" t="s">
-        <v>155</v>
-      </c>
-      <c r="B23" s="50" t="s">
-        <v>156</v>
-      </c>
-      <c r="C23" s="50" t="s">
-        <v>156</v>
+      <c r="A23" s="53" t="s">
+        <v>175</v>
+      </c>
+      <c r="B23" s="54" t="s">
+        <v>176</v>
+      </c>
+      <c r="C23" s="54" t="s">
+        <v>176</v>
       </c>
       <c r="D23" s="1">
         <v>0</v>
       </c>
-      <c r="E23" s="48"/>
-      <c r="F23" s="48"/>
-      <c r="G23" s="48"/>
-      <c r="H23" s="50" t="s">
-        <v>240</v>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="54" t="s">
+        <v>260</v>
       </c>
       <c r="I23" t="s">
-        <v>238</v>
+        <v>261</v>
       </c>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="49" t="s">
-        <v>158</v>
-      </c>
-      <c r="B24" s="50" t="s">
-        <v>159</v>
-      </c>
-      <c r="C24" s="50" t="s">
-        <v>159</v>
+      <c r="A24" s="53" t="s">
+        <v>178</v>
+      </c>
+      <c r="B24" s="54" t="s">
+        <v>179</v>
+      </c>
+      <c r="C24" s="54" t="s">
+        <v>179</v>
       </c>
       <c r="D24" s="1">
         <v>0</v>
       </c>
-      <c r="E24" s="48"/>
-      <c r="F24" s="48"/>
-      <c r="G24" s="48"/>
-      <c r="H24" s="50" t="s">
-        <v>241</v>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1" t="s">
+        <v>219</v>
       </c>
       <c r="I24" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8">
-      <c r="A25" s="49" t="s">
-        <v>161</v>
-      </c>
-      <c r="B25" s="50" t="s">
-        <v>162</v>
-      </c>
-      <c r="C25" s="50" t="s">
-        <v>162</v>
+        <v>96</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="53" t="s">
+        <v>181</v>
+      </c>
+      <c r="B25" s="54" t="s">
+        <v>182</v>
+      </c>
+      <c r="C25" s="54" t="s">
+        <v>182</v>
       </c>
       <c r="D25" s="1">
         <v>0</v>
       </c>
-      <c r="E25" s="48"/>
-      <c r="F25" s="48"/>
-      <c r="G25" s="48"/>
-      <c r="H25" s="47" t="s">
-        <v>163</v>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="54" t="s">
+        <v>183</v>
+      </c>
+      <c r="I25" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" s="49" t="s">
-        <v>164</v>
-      </c>
-      <c r="B26" s="50" t="s">
-        <v>165</v>
-      </c>
-      <c r="C26" s="50" t="s">
-        <v>165</v>
+      <c r="A26" s="48" t="s">
+        <v>184</v>
+      </c>
+      <c r="B26" s="49" t="s">
+        <v>185</v>
+      </c>
+      <c r="C26" s="49" t="s">
+        <v>185</v>
       </c>
       <c r="D26" s="1">
         <v>0</v>
       </c>
-      <c r="E26" s="48"/>
-      <c r="F26" s="48"/>
-      <c r="G26" s="48"/>
-      <c r="H26" s="50" t="s">
-        <v>166</v>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="49" t="s">
+        <v>263</v>
       </c>
       <c r="I26" t="s">
-        <v>243</v>
+        <v>261</v>
       </c>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="49" t="s">
-        <v>167</v>
-      </c>
-      <c r="B27" s="50" t="s">
-        <v>168</v>
-      </c>
-      <c r="C27" s="50" t="s">
-        <v>168</v>
+      <c r="A27" s="48" t="s">
+        <v>187</v>
+      </c>
+      <c r="B27" s="49" t="s">
+        <v>188</v>
+      </c>
+      <c r="C27" s="49" t="s">
+        <v>188</v>
       </c>
       <c r="D27" s="1">
         <v>0</v>
       </c>
-      <c r="E27" s="48"/>
-      <c r="F27" s="48"/>
-      <c r="G27" s="48"/>
-      <c r="H27" s="50" t="s">
-        <v>244</v>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="49" t="s">
+        <v>264</v>
       </c>
       <c r="I27" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9">
-      <c r="A28" s="49" t="s">
-        <v>170</v>
-      </c>
-      <c r="B28" s="50" t="s">
-        <v>171</v>
-      </c>
-      <c r="C28" s="50" t="s">
-        <v>171</v>
+        <v>265</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" s="48" t="s">
+        <v>190</v>
+      </c>
+      <c r="B28" s="49" t="s">
+        <v>191</v>
+      </c>
+      <c r="C28" s="49" t="s">
+        <v>191</v>
       </c>
       <c r="D28" s="1">
         <v>0</v>
       </c>
-      <c r="E28" s="48"/>
-      <c r="F28" s="48"/>
-      <c r="G28" s="48"/>
-      <c r="H28" s="50" t="s">
-        <v>172</v>
-      </c>
-      <c r="I28" t="s">
-        <v>245</v>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="47" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="29" spans="1:9">
-      <c r="A29" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="B29" s="50" t="s">
-        <v>174</v>
-      </c>
-      <c r="C29" s="50" t="s">
-        <v>174</v>
+      <c r="A29" s="48" t="s">
+        <v>193</v>
+      </c>
+      <c r="B29" s="49" t="s">
+        <v>194</v>
+      </c>
+      <c r="C29" s="49" t="s">
+        <v>194</v>
       </c>
       <c r="D29" s="1">
         <v>0</v>
       </c>
-      <c r="E29" s="48"/>
-      <c r="F29" s="48"/>
-      <c r="G29" s="48"/>
-      <c r="H29" s="50" t="s">
-        <v>246</v>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="49" t="s">
+        <v>266</v>
       </c>
       <c r="I29" t="s">
-        <v>238</v>
+        <v>261</v>
       </c>
     </row>
     <row r="30" spans="1:9">
-      <c r="A30" s="49" t="s">
-        <v>176</v>
-      </c>
-      <c r="B30" s="50" t="s">
-        <v>177</v>
-      </c>
-      <c r="C30" s="50" t="s">
-        <v>177</v>
+      <c r="A30" s="48" t="s">
+        <v>196</v>
+      </c>
+      <c r="B30" s="49" t="s">
+        <v>197</v>
+      </c>
+      <c r="C30" s="49" t="s">
+        <v>197</v>
       </c>
       <c r="D30" s="1">
         <v>0</v>
       </c>
-      <c r="E30" s="48"/>
-      <c r="F30" s="48"/>
-      <c r="G30" s="48"/>
-      <c r="H30" s="52" t="s">
-        <v>154</v>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="54" t="s">
+        <v>183</v>
       </c>
       <c r="I30" t="s">
-        <v>239</v>
+        <v>262</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="46" t="s">
-        <v>178</v>
+        <v>198</v>
       </c>
       <c r="B31" s="47" t="s">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="C31" s="47" t="s">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="D31" s="1">
         <v>0</v>
       </c>
-      <c r="E31" s="48"/>
-      <c r="F31" s="48"/>
-      <c r="G31" s="48"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
       <c r="H31" s="47" t="s">
-        <v>180</v>
+        <v>200</v>
       </c>
     </row>
   </sheetData>
@@ -5687,7 +8913,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G14"/>
@@ -5703,22 +8929,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="35" t="s">
-        <v>247</v>
+        <v>267</v>
       </c>
       <c r="C1" s="35" t="s">
-        <v>248</v>
+        <v>268</v>
       </c>
       <c r="D1" s="35" t="s">
-        <v>249</v>
+        <v>269</v>
       </c>
       <c r="E1" s="35" t="s">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="F1" s="35" t="s">
-        <v>251</v>
+        <v>271</v>
       </c>
       <c r="G1" s="35" t="s">
-        <v>252</v>
+        <v>272</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -5726,22 +8952,22 @@
         <v>5</v>
       </c>
       <c r="B2" s="37" t="s">
-        <v>253</v>
+        <v>273</v>
       </c>
       <c r="C2" s="37" t="s">
-        <v>186</v>
+        <v>206</v>
       </c>
       <c r="D2" s="37" t="s">
-        <v>254</v>
+        <v>274</v>
       </c>
       <c r="E2" s="37" t="s">
-        <v>255</v>
+        <v>275</v>
       </c>
       <c r="F2" s="37" t="s">
-        <v>256</v>
+        <v>276</v>
       </c>
       <c r="G2" s="38" t="s">
-        <v>257</v>
+        <v>277</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -5752,16 +8978,16 @@
         <v>10</v>
       </c>
       <c r="C3" s="37" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="D3" s="37" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="E3" s="37" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="F3" s="37" t="s">
-        <v>258</v>
+        <v>278</v>
       </c>
       <c r="G3" s="37" t="s">
         <v>10</v>
@@ -5769,10 +8995,10 @@
     </row>
     <row r="4" ht="14.25" spans="1:7">
       <c r="A4" s="39" t="s">
-        <v>259</v>
+        <v>279</v>
       </c>
       <c r="B4" s="40" t="s">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="C4" s="39">
         <v>100</v>
@@ -5787,15 +9013,15 @@
         <v>1</v>
       </c>
       <c r="G4" s="39" t="s">
-        <v>261</v>
+        <v>281</v>
       </c>
     </row>
     <row r="5" ht="14.25" spans="1:7">
       <c r="A5" s="39" t="s">
-        <v>262</v>
+        <v>282</v>
       </c>
       <c r="B5" s="40" t="s">
-        <v>263</v>
+        <v>283</v>
       </c>
       <c r="C5" s="39">
         <v>100</v>
@@ -5810,15 +9036,15 @@
         <v>1</v>
       </c>
       <c r="G5" s="39" t="s">
-        <v>264</v>
+        <v>284</v>
       </c>
     </row>
     <row r="6" ht="14.25" spans="1:7">
       <c r="A6" s="39" t="s">
-        <v>265</v>
+        <v>285</v>
       </c>
       <c r="B6" s="40" t="s">
-        <v>266</v>
+        <v>286</v>
       </c>
       <c r="C6" s="39">
         <v>3</v>
@@ -5833,15 +9059,15 @@
         <v>1</v>
       </c>
       <c r="G6" s="39" t="s">
-        <v>267</v>
+        <v>287</v>
       </c>
     </row>
     <row r="7" ht="14.25" spans="1:7">
       <c r="A7" s="39" t="s">
-        <v>268</v>
+        <v>288</v>
       </c>
       <c r="B7" s="40" t="s">
-        <v>269</v>
+        <v>289</v>
       </c>
       <c r="C7" s="39">
         <v>3</v>
@@ -5856,12 +9082,12 @@
         <v>1</v>
       </c>
       <c r="G7" s="39" t="s">
-        <v>270</v>
+        <v>290</v>
       </c>
     </row>
     <row r="8" ht="14.25" spans="1:7">
       <c r="A8" s="39" t="s">
-        <v>271</v>
+        <v>291</v>
       </c>
       <c r="B8" s="40" t="s">
         <v>8</v>
@@ -5879,15 +9105,15 @@
         <v>1</v>
       </c>
       <c r="G8" s="39" t="s">
-        <v>272</v>
+        <v>292</v>
       </c>
     </row>
     <row r="9" ht="14.25" spans="1:7">
       <c r="A9" s="39" t="s">
-        <v>273</v>
+        <v>293</v>
       </c>
       <c r="B9" s="40" t="s">
-        <v>274</v>
+        <v>294</v>
       </c>
       <c r="C9" s="39">
         <v>0</v>
@@ -5902,15 +9128,15 @@
         <v>1</v>
       </c>
       <c r="G9" s="39" t="s">
-        <v>275</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10" ht="14.25" spans="1:7">
       <c r="A10" s="39" t="s">
-        <v>276</v>
+        <v>296</v>
       </c>
       <c r="B10" s="40" t="s">
-        <v>277</v>
+        <v>297</v>
       </c>
       <c r="C10" s="39">
         <v>0</v>
@@ -5925,15 +9151,15 @@
         <v>1</v>
       </c>
       <c r="G10" s="39" t="s">
-        <v>278</v>
+        <v>298</v>
       </c>
     </row>
     <row r="11" ht="14.25" spans="1:7">
       <c r="A11" s="39" t="s">
-        <v>279</v>
+        <v>299</v>
       </c>
       <c r="B11" s="40" t="s">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="C11" s="39">
         <v>0</v>
@@ -5948,15 +9174,15 @@
         <v>1</v>
       </c>
       <c r="G11" s="39" t="s">
-        <v>281</v>
+        <v>301</v>
       </c>
     </row>
     <row r="12" ht="14.25" spans="1:7">
       <c r="A12" s="39" t="s">
-        <v>282</v>
+        <v>302</v>
       </c>
       <c r="B12" s="40" t="s">
-        <v>283</v>
+        <v>303</v>
       </c>
       <c r="C12" s="39">
         <v>0</v>
@@ -5971,15 +9197,15 @@
         <v>1</v>
       </c>
       <c r="G12" s="39" t="s">
-        <v>284</v>
+        <v>304</v>
       </c>
     </row>
     <row r="13" ht="14.25" spans="1:7">
       <c r="A13" s="39" t="s">
-        <v>285</v>
+        <v>305</v>
       </c>
       <c r="B13" s="40" t="s">
-        <v>286</v>
+        <v>306</v>
       </c>
       <c r="C13" s="39">
         <v>0</v>
@@ -5994,15 +9220,15 @@
         <v>1</v>
       </c>
       <c r="G13" s="39" t="s">
-        <v>287</v>
+        <v>307</v>
       </c>
     </row>
     <row r="14" ht="14.25" spans="1:7">
       <c r="A14" s="39" t="s">
-        <v>288</v>
+        <v>308</v>
       </c>
       <c r="B14" s="40" t="s">
-        <v>192</v>
+        <v>212</v>
       </c>
       <c r="C14" s="39">
         <v>0</v>
@@ -6017,3038 +9243,11 @@
         <v>1</v>
       </c>
       <c r="G14" s="39" t="s">
-        <v>289</v>
+        <v>309</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:AA41"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData>
-    <row r="1" ht="14.25" spans="1:27">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="P1" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="Q1" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="R1" s="13" t="s">
-        <v>305</v>
-      </c>
-      <c r="S1" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="T1" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="U1" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="V1" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="W1" s="14" t="s">
-        <v>310</v>
-      </c>
-      <c r="X1" s="15"/>
-      <c r="Y1" s="15"/>
-      <c r="Z1" s="15"/>
-      <c r="AA1" s="31"/>
-    </row>
-    <row r="2" ht="14.25" spans="1:27">
-      <c r="A2" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>313</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>238</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>314</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>316</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>317</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>318</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>319</v>
-      </c>
-      <c r="M2" s="5" t="s">
-        <v>320</v>
-      </c>
-      <c r="N2" s="5" t="s">
-        <v>321</v>
-      </c>
-      <c r="O2" s="5" t="s">
-        <v>322</v>
-      </c>
-      <c r="P2" s="5" t="s">
-        <v>323</v>
-      </c>
-      <c r="Q2" s="5" t="s">
-        <v>324</v>
-      </c>
-      <c r="R2" s="16" t="s">
-        <v>325</v>
-      </c>
-      <c r="S2" s="5" t="s">
-        <v>326</v>
-      </c>
-      <c r="T2" s="5" t="s">
-        <v>280</v>
-      </c>
-      <c r="U2" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="V2" s="5" t="s">
-        <v>327</v>
-      </c>
-      <c r="W2" s="17" t="s">
-        <v>324</v>
-      </c>
-      <c r="X2" s="18" t="s">
-        <v>328</v>
-      </c>
-      <c r="Y2" s="32" t="s">
-        <v>329</v>
-      </c>
-      <c r="Z2" s="32" t="s">
-        <v>330</v>
-      </c>
-      <c r="AA2" s="33" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="3" ht="14.25" spans="1:27">
-      <c r="A3" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="K3" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="L3" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="M3" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="N3" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="O3" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="P3" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q3" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="R3" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="S3" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="T3" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="U3" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="V3" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="W3" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="X3" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y3" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="Z3" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA3" s="34" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27">
-      <c r="A4" s="8">
-        <v>1</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>332</v>
-      </c>
-      <c r="C4" s="9">
-        <v>10</v>
-      </c>
-      <c r="D4" s="9">
-        <v>0</v>
-      </c>
-      <c r="E4" s="9">
-        <v>0</v>
-      </c>
-      <c r="F4" s="9">
-        <v>10</v>
-      </c>
-      <c r="G4" s="9">
-        <v>0</v>
-      </c>
-      <c r="H4" s="9">
-        <v>0</v>
-      </c>
-      <c r="I4" s="9">
-        <v>0</v>
-      </c>
-      <c r="J4" s="9">
-        <v>2</v>
-      </c>
-      <c r="K4" s="9">
-        <v>1</v>
-      </c>
-      <c r="L4" s="9">
-        <v>0</v>
-      </c>
-      <c r="M4" s="9">
-        <v>0</v>
-      </c>
-      <c r="N4" s="9">
-        <v>0</v>
-      </c>
-      <c r="O4" s="9">
-        <v>0</v>
-      </c>
-      <c r="P4" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="9">
-        <v>0</v>
-      </c>
-      <c r="R4" s="22">
-        <v>0</v>
-      </c>
-      <c r="S4" s="9"/>
-      <c r="T4" s="9"/>
-      <c r="U4" s="9"/>
-      <c r="V4" s="9"/>
-      <c r="W4" s="23"/>
-      <c r="X4" s="65" t="s">
-        <v>333</v>
-      </c>
-      <c r="Y4" s="9" t="s">
-        <v>334</v>
-      </c>
-      <c r="Z4" s="9" t="s">
-        <v>335</v>
-      </c>
-      <c r="AA4" s="23" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27">
-      <c r="A5" s="10">
-        <v>2</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="C5" s="1">
-        <v>10</v>
-      </c>
-      <c r="D5" s="1">
-        <v>0</v>
-      </c>
-      <c r="E5" s="1">
-        <v>0</v>
-      </c>
-      <c r="F5" s="1">
-        <v>10</v>
-      </c>
-      <c r="G5" s="1">
-        <v>0</v>
-      </c>
-      <c r="H5" s="1">
-        <v>0</v>
-      </c>
-      <c r="I5" s="1">
-        <v>0</v>
-      </c>
-      <c r="J5" s="1">
-        <v>2</v>
-      </c>
-      <c r="K5" s="1">
-        <v>1</v>
-      </c>
-      <c r="L5" s="1">
-        <v>0</v>
-      </c>
-      <c r="M5" s="1">
-        <v>0</v>
-      </c>
-      <c r="N5" s="1">
-        <v>0</v>
-      </c>
-      <c r="O5" s="1">
-        <v>0</v>
-      </c>
-      <c r="P5" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="1">
-        <v>0</v>
-      </c>
-      <c r="R5" s="25">
-        <v>0</v>
-      </c>
-      <c r="S5" s="1"/>
-      <c r="T5" s="1"/>
-      <c r="U5" s="1"/>
-      <c r="V5" s="1"/>
-      <c r="W5" s="26"/>
-      <c r="X5" s="27" t="s">
-        <v>338</v>
-      </c>
-      <c r="Y5" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="Z5" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="AA5" s="26" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27">
-      <c r="A6" s="10">
-        <v>3</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="C6" s="1">
-        <v>10</v>
-      </c>
-      <c r="D6" s="1">
-        <v>0</v>
-      </c>
-      <c r="E6" s="1">
-        <v>0</v>
-      </c>
-      <c r="F6" s="1">
-        <v>10</v>
-      </c>
-      <c r="G6" s="1">
-        <v>0</v>
-      </c>
-      <c r="H6" s="1">
-        <v>0</v>
-      </c>
-      <c r="I6" s="1">
-        <v>0</v>
-      </c>
-      <c r="J6" s="1">
-        <v>2</v>
-      </c>
-      <c r="K6" s="1">
-        <v>1</v>
-      </c>
-      <c r="L6" s="1">
-        <v>0</v>
-      </c>
-      <c r="M6" s="1">
-        <v>0</v>
-      </c>
-      <c r="N6" s="1">
-        <v>0</v>
-      </c>
-      <c r="O6" s="1">
-        <v>0</v>
-      </c>
-      <c r="P6" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="1">
-        <v>0</v>
-      </c>
-      <c r="R6" s="25">
-        <v>0</v>
-      </c>
-      <c r="S6" s="1"/>
-      <c r="T6" s="1"/>
-      <c r="U6" s="1"/>
-      <c r="V6" s="1"/>
-      <c r="W6" s="26"/>
-      <c r="X6" s="27" t="s">
-        <v>341</v>
-      </c>
-      <c r="Y6" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="Z6" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="AA6" s="26" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27">
-      <c r="A7" s="10">
-        <v>4</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="C7" s="1">
-        <v>10</v>
-      </c>
-      <c r="D7" s="1">
-        <v>0</v>
-      </c>
-      <c r="E7" s="1">
-        <v>0</v>
-      </c>
-      <c r="F7" s="1">
-        <v>10</v>
-      </c>
-      <c r="G7" s="1">
-        <v>0</v>
-      </c>
-      <c r="H7" s="1">
-        <v>0</v>
-      </c>
-      <c r="I7" s="1">
-        <v>0</v>
-      </c>
-      <c r="J7" s="1">
-        <v>2</v>
-      </c>
-      <c r="K7" s="1">
-        <v>1</v>
-      </c>
-      <c r="L7" s="1">
-        <v>0</v>
-      </c>
-      <c r="M7" s="1">
-        <v>0</v>
-      </c>
-      <c r="N7" s="1">
-        <v>0</v>
-      </c>
-      <c r="O7" s="1">
-        <v>0</v>
-      </c>
-      <c r="P7" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="1">
-        <v>0</v>
-      </c>
-      <c r="R7" s="25">
-        <v>0</v>
-      </c>
-      <c r="S7" s="1"/>
-      <c r="T7" s="1"/>
-      <c r="U7" s="1"/>
-      <c r="V7" s="1"/>
-      <c r="W7" s="26"/>
-      <c r="X7" s="27" t="s">
-        <v>345</v>
-      </c>
-      <c r="Y7" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="Z7" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="AA7" s="26" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27">
-      <c r="A8" s="10">
-        <v>5</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="C8" s="1">
-        <v>10</v>
-      </c>
-      <c r="D8" s="1">
-        <v>0</v>
-      </c>
-      <c r="E8" s="1">
-        <v>0</v>
-      </c>
-      <c r="F8" s="1">
-        <v>10</v>
-      </c>
-      <c r="G8" s="1">
-        <v>0</v>
-      </c>
-      <c r="H8" s="1">
-        <v>0</v>
-      </c>
-      <c r="I8" s="1">
-        <v>0</v>
-      </c>
-      <c r="J8" s="1">
-        <v>2</v>
-      </c>
-      <c r="K8" s="1">
-        <v>1</v>
-      </c>
-      <c r="L8" s="1">
-        <v>0</v>
-      </c>
-      <c r="M8" s="1">
-        <v>0</v>
-      </c>
-      <c r="N8" s="1">
-        <v>0</v>
-      </c>
-      <c r="O8" s="1">
-        <v>0</v>
-      </c>
-      <c r="P8" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="1">
-        <v>0</v>
-      </c>
-      <c r="R8" s="25">
-        <v>0</v>
-      </c>
-      <c r="S8" s="1"/>
-      <c r="T8" s="1"/>
-      <c r="U8" s="1"/>
-      <c r="V8" s="1"/>
-      <c r="W8" s="26"/>
-      <c r="X8" s="27" t="s">
-        <v>349</v>
-      </c>
-      <c r="Y8" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="Z8" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="AA8" s="26" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27">
-      <c r="A9" s="10">
-        <v>6</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="C9" s="1">
-        <v>10</v>
-      </c>
-      <c r="D9" s="1">
-        <v>0</v>
-      </c>
-      <c r="E9" s="1">
-        <v>0</v>
-      </c>
-      <c r="F9" s="1">
-        <v>10</v>
-      </c>
-      <c r="G9" s="1">
-        <v>0</v>
-      </c>
-      <c r="H9" s="1">
-        <v>0</v>
-      </c>
-      <c r="I9" s="1">
-        <v>0</v>
-      </c>
-      <c r="J9" s="1">
-        <v>2</v>
-      </c>
-      <c r="K9" s="1">
-        <v>1</v>
-      </c>
-      <c r="L9" s="1">
-        <v>0</v>
-      </c>
-      <c r="M9" s="1">
-        <v>0</v>
-      </c>
-      <c r="N9" s="1">
-        <v>0</v>
-      </c>
-      <c r="O9" s="1">
-        <v>0</v>
-      </c>
-      <c r="P9" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="1">
-        <v>0</v>
-      </c>
-      <c r="R9" s="25">
-        <v>0</v>
-      </c>
-      <c r="S9" s="1"/>
-      <c r="T9" s="1"/>
-      <c r="U9" s="1"/>
-      <c r="V9" s="1"/>
-      <c r="W9" s="26"/>
-      <c r="X9" s="27" t="s">
-        <v>353</v>
-      </c>
-      <c r="Y9" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="Z9" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="AA9" s="26" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27">
-      <c r="A10" s="10">
-        <v>7</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="C10" s="1">
-        <v>10</v>
-      </c>
-      <c r="D10" s="1">
-        <v>0</v>
-      </c>
-      <c r="E10" s="1">
-        <v>0</v>
-      </c>
-      <c r="F10" s="1">
-        <v>10</v>
-      </c>
-      <c r="G10" s="1">
-        <v>0</v>
-      </c>
-      <c r="H10" s="1">
-        <v>0</v>
-      </c>
-      <c r="I10" s="1">
-        <v>0</v>
-      </c>
-      <c r="J10" s="1">
-        <v>2</v>
-      </c>
-      <c r="K10" s="1">
-        <v>1</v>
-      </c>
-      <c r="L10" s="1">
-        <v>0</v>
-      </c>
-      <c r="M10" s="1">
-        <v>0</v>
-      </c>
-      <c r="N10" s="1">
-        <v>0</v>
-      </c>
-      <c r="O10" s="1">
-        <v>0</v>
-      </c>
-      <c r="P10" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="1">
-        <v>0</v>
-      </c>
-      <c r="R10" s="25">
-        <v>0</v>
-      </c>
-      <c r="S10" s="1"/>
-      <c r="T10" s="1"/>
-      <c r="U10" s="1"/>
-      <c r="V10" s="1"/>
-      <c r="W10" s="26"/>
-      <c r="X10" s="27" t="s">
-        <v>358</v>
-      </c>
-      <c r="Y10" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="Z10" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="AA10" s="26" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27">
-      <c r="A11" s="10">
-        <v>8</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="C11" s="1">
-        <v>10</v>
-      </c>
-      <c r="D11" s="1">
-        <v>0</v>
-      </c>
-      <c r="E11" s="1">
-        <v>0</v>
-      </c>
-      <c r="F11" s="1">
-        <v>10</v>
-      </c>
-      <c r="G11" s="1">
-        <v>0</v>
-      </c>
-      <c r="H11" s="1">
-        <v>0</v>
-      </c>
-      <c r="I11" s="1">
-        <v>0</v>
-      </c>
-      <c r="J11" s="1">
-        <v>2</v>
-      </c>
-      <c r="K11" s="1">
-        <v>1</v>
-      </c>
-      <c r="L11" s="1">
-        <v>0</v>
-      </c>
-      <c r="M11" s="1">
-        <v>0</v>
-      </c>
-      <c r="N11" s="1">
-        <v>0</v>
-      </c>
-      <c r="O11" s="1">
-        <v>0</v>
-      </c>
-      <c r="P11" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="1">
-        <v>0</v>
-      </c>
-      <c r="R11" s="25">
-        <v>0</v>
-      </c>
-      <c r="S11" s="1"/>
-      <c r="T11" s="1"/>
-      <c r="U11" s="1"/>
-      <c r="V11" s="1"/>
-      <c r="W11" s="26"/>
-      <c r="X11" s="27" t="s">
-        <v>362</v>
-      </c>
-      <c r="Y11" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="Z11" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="AA11" s="26" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27">
-      <c r="A12" s="10">
-        <v>9</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>366</v>
-      </c>
-      <c r="C12" s="1">
-        <v>10</v>
-      </c>
-      <c r="D12" s="1">
-        <v>0</v>
-      </c>
-      <c r="E12" s="1">
-        <v>0</v>
-      </c>
-      <c r="F12" s="1">
-        <v>10</v>
-      </c>
-      <c r="G12" s="1">
-        <v>0</v>
-      </c>
-      <c r="H12" s="1">
-        <v>0</v>
-      </c>
-      <c r="I12" s="1">
-        <v>0</v>
-      </c>
-      <c r="J12" s="1">
-        <v>2</v>
-      </c>
-      <c r="K12" s="1">
-        <v>1</v>
-      </c>
-      <c r="L12" s="1">
-        <v>0</v>
-      </c>
-      <c r="M12" s="1">
-        <v>0</v>
-      </c>
-      <c r="N12" s="1">
-        <v>0</v>
-      </c>
-      <c r="O12" s="1">
-        <v>0</v>
-      </c>
-      <c r="P12" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="1">
-        <v>0</v>
-      </c>
-      <c r="R12" s="25">
-        <v>0</v>
-      </c>
-      <c r="S12" s="1"/>
-      <c r="T12" s="1"/>
-      <c r="U12" s="1"/>
-      <c r="V12" s="1"/>
-      <c r="W12" s="26"/>
-      <c r="X12" s="27" t="s">
-        <v>367</v>
-      </c>
-      <c r="Y12" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="Z12" s="1" t="s">
-        <v>369</v>
-      </c>
-      <c r="AA12" s="26" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27">
-      <c r="A13" s="10">
-        <v>10</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>371</v>
-      </c>
-      <c r="C13" s="1">
-        <v>10</v>
-      </c>
-      <c r="D13" s="1">
-        <v>0</v>
-      </c>
-      <c r="E13" s="1">
-        <v>0</v>
-      </c>
-      <c r="F13" s="1">
-        <v>10</v>
-      </c>
-      <c r="G13" s="1">
-        <v>0</v>
-      </c>
-      <c r="H13" s="1">
-        <v>0</v>
-      </c>
-      <c r="I13" s="1">
-        <v>0</v>
-      </c>
-      <c r="J13" s="1">
-        <v>2</v>
-      </c>
-      <c r="K13" s="1">
-        <v>1</v>
-      </c>
-      <c r="L13" s="1">
-        <v>0</v>
-      </c>
-      <c r="M13" s="1">
-        <v>0</v>
-      </c>
-      <c r="N13" s="1">
-        <v>0</v>
-      </c>
-      <c r="O13" s="1">
-        <v>0</v>
-      </c>
-      <c r="P13" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="1">
-        <v>0</v>
-      </c>
-      <c r="R13" s="25">
-        <v>0</v>
-      </c>
-      <c r="S13" s="1"/>
-      <c r="T13" s="1"/>
-      <c r="U13" s="1"/>
-      <c r="V13" s="1"/>
-      <c r="W13" s="26"/>
-      <c r="X13" s="27" t="s">
-        <v>372</v>
-      </c>
-      <c r="Y13" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="Z13" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="AA13" s="26" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27">
-      <c r="A14" s="10">
-        <v>11</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>375</v>
-      </c>
-      <c r="C14" s="1">
-        <v>10</v>
-      </c>
-      <c r="D14" s="1">
-        <v>0</v>
-      </c>
-      <c r="E14" s="1">
-        <v>0</v>
-      </c>
-      <c r="F14" s="1">
-        <v>10</v>
-      </c>
-      <c r="G14" s="1">
-        <v>0</v>
-      </c>
-      <c r="H14" s="1">
-        <v>0</v>
-      </c>
-      <c r="I14" s="1">
-        <v>0</v>
-      </c>
-      <c r="J14" s="1">
-        <v>2</v>
-      </c>
-      <c r="K14" s="1">
-        <v>1</v>
-      </c>
-      <c r="L14" s="1">
-        <v>0</v>
-      </c>
-      <c r="M14" s="1">
-        <v>0</v>
-      </c>
-      <c r="N14" s="1">
-        <v>0</v>
-      </c>
-      <c r="O14" s="1">
-        <v>0</v>
-      </c>
-      <c r="P14" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="1">
-        <v>0</v>
-      </c>
-      <c r="R14" s="25">
-        <v>0</v>
-      </c>
-      <c r="S14" s="1"/>
-      <c r="T14" s="1"/>
-      <c r="U14" s="1"/>
-      <c r="V14" s="1"/>
-      <c r="W14" s="26"/>
-      <c r="X14" s="27" t="s">
-        <v>376</v>
-      </c>
-      <c r="Y14" s="1" t="s">
-        <v>377</v>
-      </c>
-      <c r="Z14" s="1" t="s">
-        <v>378</v>
-      </c>
-      <c r="AA14" s="26" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27">
-      <c r="A15" s="10">
-        <v>12</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="C15" s="1">
-        <v>10</v>
-      </c>
-      <c r="D15" s="1">
-        <v>0</v>
-      </c>
-      <c r="E15" s="1">
-        <v>0</v>
-      </c>
-      <c r="F15" s="1">
-        <v>10</v>
-      </c>
-      <c r="G15" s="1">
-        <v>0</v>
-      </c>
-      <c r="H15" s="1">
-        <v>0</v>
-      </c>
-      <c r="I15" s="1">
-        <v>0</v>
-      </c>
-      <c r="J15" s="1">
-        <v>2</v>
-      </c>
-      <c r="K15" s="1">
-        <v>1</v>
-      </c>
-      <c r="L15" s="1">
-        <v>0</v>
-      </c>
-      <c r="M15" s="1">
-        <v>0</v>
-      </c>
-      <c r="N15" s="1">
-        <v>0</v>
-      </c>
-      <c r="O15" s="1">
-        <v>0</v>
-      </c>
-      <c r="P15" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="1">
-        <v>0</v>
-      </c>
-      <c r="R15" s="25">
-        <v>0</v>
-      </c>
-      <c r="S15" s="1"/>
-      <c r="T15" s="1"/>
-      <c r="U15" s="1"/>
-      <c r="V15" s="1"/>
-      <c r="W15" s="26"/>
-      <c r="X15" s="27" t="s">
-        <v>381</v>
-      </c>
-      <c r="Y15" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="Z15" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="AA15" s="26" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="16" spans="1:27">
-      <c r="A16" s="10">
-        <v>13</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="C16" s="1">
-        <v>10</v>
-      </c>
-      <c r="D16" s="1">
-        <v>0</v>
-      </c>
-      <c r="E16" s="1">
-        <v>0</v>
-      </c>
-      <c r="F16" s="1">
-        <v>10</v>
-      </c>
-      <c r="G16" s="1">
-        <v>0</v>
-      </c>
-      <c r="H16" s="1">
-        <v>0</v>
-      </c>
-      <c r="I16" s="1">
-        <v>0</v>
-      </c>
-      <c r="J16" s="1">
-        <v>2</v>
-      </c>
-      <c r="K16" s="1">
-        <v>1</v>
-      </c>
-      <c r="L16" s="1">
-        <v>0</v>
-      </c>
-      <c r="M16" s="1">
-        <v>0</v>
-      </c>
-      <c r="N16" s="1">
-        <v>0</v>
-      </c>
-      <c r="O16" s="1">
-        <v>0</v>
-      </c>
-      <c r="P16" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="1">
-        <v>0</v>
-      </c>
-      <c r="R16" s="25">
-        <v>0</v>
-      </c>
-      <c r="S16" s="1"/>
-      <c r="T16" s="1"/>
-      <c r="U16" s="1"/>
-      <c r="V16" s="1"/>
-      <c r="W16" s="26"/>
-      <c r="X16" s="27" t="s">
-        <v>385</v>
-      </c>
-      <c r="Y16" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="Z16" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="AA16" s="26" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="17" spans="1:27">
-      <c r="A17" s="10">
-        <v>14</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="C17" s="1">
-        <v>10</v>
-      </c>
-      <c r="D17" s="1">
-        <v>0</v>
-      </c>
-      <c r="E17" s="1">
-        <v>0</v>
-      </c>
-      <c r="F17" s="1">
-        <v>10</v>
-      </c>
-      <c r="G17" s="1">
-        <v>0</v>
-      </c>
-      <c r="H17" s="1">
-        <v>0</v>
-      </c>
-      <c r="I17" s="1">
-        <v>0</v>
-      </c>
-      <c r="J17" s="1">
-        <v>2</v>
-      </c>
-      <c r="K17" s="1">
-        <v>1</v>
-      </c>
-      <c r="L17" s="1">
-        <v>0</v>
-      </c>
-      <c r="M17" s="1">
-        <v>0</v>
-      </c>
-      <c r="N17" s="1">
-        <v>0</v>
-      </c>
-      <c r="O17" s="1">
-        <v>0</v>
-      </c>
-      <c r="P17" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="1">
-        <v>0</v>
-      </c>
-      <c r="R17" s="25">
-        <v>0</v>
-      </c>
-      <c r="S17" s="1"/>
-      <c r="T17" s="1"/>
-      <c r="U17" s="1"/>
-      <c r="V17" s="1"/>
-      <c r="W17" s="26"/>
-      <c r="X17" s="27" t="s">
-        <v>389</v>
-      </c>
-      <c r="Y17" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="Z17" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="AA17" s="26" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="18" spans="1:27">
-      <c r="A18" s="10">
-        <v>15</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="C18" s="1">
-        <v>10</v>
-      </c>
-      <c r="D18" s="1">
-        <v>0</v>
-      </c>
-      <c r="E18" s="1">
-        <v>0</v>
-      </c>
-      <c r="F18" s="1">
-        <v>10</v>
-      </c>
-      <c r="G18" s="1">
-        <v>0</v>
-      </c>
-      <c r="H18" s="1">
-        <v>0</v>
-      </c>
-      <c r="I18" s="1">
-        <v>0</v>
-      </c>
-      <c r="J18" s="1">
-        <v>2</v>
-      </c>
-      <c r="K18" s="1">
-        <v>1</v>
-      </c>
-      <c r="L18" s="1">
-        <v>0</v>
-      </c>
-      <c r="M18" s="1">
-        <v>0</v>
-      </c>
-      <c r="N18" s="1">
-        <v>0</v>
-      </c>
-      <c r="O18" s="1">
-        <v>0</v>
-      </c>
-      <c r="P18" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="1">
-        <v>0</v>
-      </c>
-      <c r="R18" s="25">
-        <v>0</v>
-      </c>
-      <c r="S18" s="1"/>
-      <c r="T18" s="1"/>
-      <c r="U18" s="1"/>
-      <c r="V18" s="1"/>
-      <c r="W18" s="26"/>
-      <c r="X18" s="27" t="s">
-        <v>394</v>
-      </c>
-      <c r="Y18" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="Z18" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="AA18" s="26" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="19" spans="1:27">
-      <c r="A19" s="10">
-        <v>16</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="C19" s="1">
-        <v>10</v>
-      </c>
-      <c r="D19" s="1">
-        <v>0</v>
-      </c>
-      <c r="E19" s="1">
-        <v>0</v>
-      </c>
-      <c r="F19" s="1">
-        <v>10</v>
-      </c>
-      <c r="G19" s="1">
-        <v>0</v>
-      </c>
-      <c r="H19" s="1">
-        <v>0</v>
-      </c>
-      <c r="I19" s="1">
-        <v>0</v>
-      </c>
-      <c r="J19" s="1">
-        <v>2</v>
-      </c>
-      <c r="K19" s="1">
-        <v>1</v>
-      </c>
-      <c r="L19" s="1">
-        <v>0</v>
-      </c>
-      <c r="M19" s="1">
-        <v>0</v>
-      </c>
-      <c r="N19" s="1">
-        <v>0</v>
-      </c>
-      <c r="O19" s="1">
-        <v>0</v>
-      </c>
-      <c r="P19" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="1">
-        <v>0</v>
-      </c>
-      <c r="R19" s="25">
-        <v>0</v>
-      </c>
-      <c r="S19" s="1"/>
-      <c r="T19" s="1"/>
-      <c r="U19" s="1"/>
-      <c r="V19" s="1"/>
-      <c r="W19" s="26"/>
-      <c r="X19" s="27" t="s">
-        <v>398</v>
-      </c>
-      <c r="Y19" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="Z19" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="AA19" s="26" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="20" spans="1:27">
-      <c r="A20" s="10">
-        <v>17</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="C20" s="1">
-        <v>10</v>
-      </c>
-      <c r="D20" s="1">
-        <v>0</v>
-      </c>
-      <c r="E20" s="1">
-        <v>0</v>
-      </c>
-      <c r="F20" s="1">
-        <v>10</v>
-      </c>
-      <c r="G20" s="1">
-        <v>0</v>
-      </c>
-      <c r="H20" s="1">
-        <v>0</v>
-      </c>
-      <c r="I20" s="1">
-        <v>0</v>
-      </c>
-      <c r="J20" s="1">
-        <v>2</v>
-      </c>
-      <c r="K20" s="1">
-        <v>1</v>
-      </c>
-      <c r="L20" s="1">
-        <v>0</v>
-      </c>
-      <c r="M20" s="1">
-        <v>0</v>
-      </c>
-      <c r="N20" s="1">
-        <v>0</v>
-      </c>
-      <c r="O20" s="1">
-        <v>0</v>
-      </c>
-      <c r="P20" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="1">
-        <v>0</v>
-      </c>
-      <c r="R20" s="25">
-        <v>0</v>
-      </c>
-      <c r="S20" s="1"/>
-      <c r="T20" s="1"/>
-      <c r="U20" s="1"/>
-      <c r="V20" s="1"/>
-      <c r="W20" s="26"/>
-      <c r="X20" s="27" t="s">
-        <v>402</v>
-      </c>
-      <c r="Y20" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="Z20" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="AA20" s="26" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="21" spans="1:27">
-      <c r="A21" s="10">
-        <v>18</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="C21" s="1">
-        <v>10</v>
-      </c>
-      <c r="D21" s="1">
-        <v>0</v>
-      </c>
-      <c r="E21" s="1">
-        <v>0</v>
-      </c>
-      <c r="F21" s="1">
-        <v>10</v>
-      </c>
-      <c r="G21" s="1">
-        <v>0</v>
-      </c>
-      <c r="H21" s="1">
-        <v>0</v>
-      </c>
-      <c r="I21" s="1">
-        <v>0</v>
-      </c>
-      <c r="J21" s="1">
-        <v>2</v>
-      </c>
-      <c r="K21" s="1">
-        <v>1</v>
-      </c>
-      <c r="L21" s="1">
-        <v>0</v>
-      </c>
-      <c r="M21" s="1">
-        <v>0</v>
-      </c>
-      <c r="N21" s="1">
-        <v>0</v>
-      </c>
-      <c r="O21" s="1">
-        <v>0</v>
-      </c>
-      <c r="P21" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="1">
-        <v>0</v>
-      </c>
-      <c r="R21" s="25">
-        <v>0</v>
-      </c>
-      <c r="S21" s="1"/>
-      <c r="T21" s="1"/>
-      <c r="U21" s="1"/>
-      <c r="V21" s="1"/>
-      <c r="W21" s="26"/>
-      <c r="X21" s="27" t="s">
-        <v>406</v>
-      </c>
-      <c r="Y21" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="Z21" s="1" t="s">
-        <v>408</v>
-      </c>
-      <c r="AA21" s="26" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="22" spans="1:27">
-      <c r="A22" s="10">
-        <v>19</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>409</v>
-      </c>
-      <c r="C22" s="1">
-        <v>10</v>
-      </c>
-      <c r="D22" s="1">
-        <v>0</v>
-      </c>
-      <c r="E22" s="1">
-        <v>0</v>
-      </c>
-      <c r="F22" s="1">
-        <v>10</v>
-      </c>
-      <c r="G22" s="1">
-        <v>0</v>
-      </c>
-      <c r="H22" s="1">
-        <v>0</v>
-      </c>
-      <c r="I22" s="1">
-        <v>0</v>
-      </c>
-      <c r="J22" s="1">
-        <v>2</v>
-      </c>
-      <c r="K22" s="1">
-        <v>1</v>
-      </c>
-      <c r="L22" s="1">
-        <v>0</v>
-      </c>
-      <c r="M22" s="1">
-        <v>0</v>
-      </c>
-      <c r="N22" s="1">
-        <v>0</v>
-      </c>
-      <c r="O22" s="1">
-        <v>0</v>
-      </c>
-      <c r="P22" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="1">
-        <v>0</v>
-      </c>
-      <c r="R22" s="25">
-        <v>0</v>
-      </c>
-      <c r="S22" s="1"/>
-      <c r="T22" s="1"/>
-      <c r="U22" s="1"/>
-      <c r="V22" s="1"/>
-      <c r="W22" s="26"/>
-      <c r="X22" s="27" t="s">
-        <v>410</v>
-      </c>
-      <c r="Y22" s="1" t="s">
-        <v>411</v>
-      </c>
-      <c r="Z22" s="1" t="s">
-        <v>412</v>
-      </c>
-      <c r="AA22" s="26" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="23" spans="1:27">
-      <c r="A23" s="10">
-        <v>20</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="C23" s="1">
-        <v>10</v>
-      </c>
-      <c r="D23" s="1">
-        <v>0</v>
-      </c>
-      <c r="E23" s="1">
-        <v>0</v>
-      </c>
-      <c r="F23" s="1">
-        <v>10</v>
-      </c>
-      <c r="G23" s="1">
-        <v>0</v>
-      </c>
-      <c r="H23" s="1">
-        <v>0</v>
-      </c>
-      <c r="I23" s="1">
-        <v>0</v>
-      </c>
-      <c r="J23" s="1">
-        <v>2</v>
-      </c>
-      <c r="K23" s="1">
-        <v>1</v>
-      </c>
-      <c r="L23" s="1">
-        <v>0</v>
-      </c>
-      <c r="M23" s="1">
-        <v>0</v>
-      </c>
-      <c r="N23" s="1">
-        <v>0</v>
-      </c>
-      <c r="O23" s="1">
-        <v>0</v>
-      </c>
-      <c r="P23" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q23" s="1">
-        <v>0</v>
-      </c>
-      <c r="R23" s="25">
-        <v>0</v>
-      </c>
-      <c r="S23" s="1"/>
-      <c r="T23" s="1"/>
-      <c r="U23" s="1"/>
-      <c r="V23" s="1"/>
-      <c r="W23" s="26"/>
-      <c r="X23" s="27" t="s">
-        <v>415</v>
-      </c>
-      <c r="Y23" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="Z23" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="AA23" s="26" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="24" spans="1:27">
-      <c r="A24" s="10">
-        <v>21</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>419</v>
-      </c>
-      <c r="C24" s="1">
-        <v>10</v>
-      </c>
-      <c r="D24" s="1">
-        <v>0</v>
-      </c>
-      <c r="E24" s="1">
-        <v>0</v>
-      </c>
-      <c r="F24" s="1">
-        <v>10</v>
-      </c>
-      <c r="G24" s="1">
-        <v>0</v>
-      </c>
-      <c r="H24" s="1">
-        <v>0</v>
-      </c>
-      <c r="I24" s="1">
-        <v>0</v>
-      </c>
-      <c r="J24" s="1">
-        <v>2</v>
-      </c>
-      <c r="K24" s="1">
-        <v>1</v>
-      </c>
-      <c r="L24" s="1">
-        <v>0</v>
-      </c>
-      <c r="M24" s="1">
-        <v>0</v>
-      </c>
-      <c r="N24" s="1">
-        <v>0</v>
-      </c>
-      <c r="O24" s="1">
-        <v>0</v>
-      </c>
-      <c r="P24" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="1">
-        <v>0</v>
-      </c>
-      <c r="R24" s="25">
-        <v>0</v>
-      </c>
-      <c r="S24" s="1"/>
-      <c r="T24" s="1"/>
-      <c r="U24" s="1"/>
-      <c r="V24" s="1"/>
-      <c r="W24" s="26"/>
-      <c r="X24" s="27" t="s">
-        <v>420</v>
-      </c>
-      <c r="Y24" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="Z24" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="AA24" s="26" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="25" spans="1:27">
-      <c r="A25" s="10">
-        <v>22</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>424</v>
-      </c>
-      <c r="C25" s="1">
-        <v>10</v>
-      </c>
-      <c r="D25" s="1">
-        <v>0</v>
-      </c>
-      <c r="E25" s="1">
-        <v>0</v>
-      </c>
-      <c r="F25" s="1">
-        <v>10</v>
-      </c>
-      <c r="G25" s="1">
-        <v>0</v>
-      </c>
-      <c r="H25" s="1">
-        <v>0</v>
-      </c>
-      <c r="I25" s="1">
-        <v>0</v>
-      </c>
-      <c r="J25" s="1">
-        <v>2</v>
-      </c>
-      <c r="K25" s="1">
-        <v>1</v>
-      </c>
-      <c r="L25" s="1">
-        <v>0</v>
-      </c>
-      <c r="M25" s="1">
-        <v>0</v>
-      </c>
-      <c r="N25" s="1">
-        <v>0</v>
-      </c>
-      <c r="O25" s="1">
-        <v>0</v>
-      </c>
-      <c r="P25" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="1">
-        <v>0</v>
-      </c>
-      <c r="R25" s="25">
-        <v>0</v>
-      </c>
-      <c r="S25" s="1"/>
-      <c r="T25" s="1"/>
-      <c r="U25" s="1"/>
-      <c r="V25" s="1"/>
-      <c r="W25" s="26"/>
-      <c r="X25" s="27" t="s">
-        <v>425</v>
-      </c>
-      <c r="Y25" s="1" t="s">
-        <v>426</v>
-      </c>
-      <c r="Z25" s="1" t="s">
-        <v>427</v>
-      </c>
-      <c r="AA25" s="26" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="26" spans="1:27">
-      <c r="A26" s="10">
-        <v>23</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>428</v>
-      </c>
-      <c r="C26" s="1">
-        <v>10</v>
-      </c>
-      <c r="D26" s="1">
-        <v>0</v>
-      </c>
-      <c r="E26" s="1">
-        <v>0</v>
-      </c>
-      <c r="F26" s="1">
-        <v>10</v>
-      </c>
-      <c r="G26" s="1">
-        <v>0</v>
-      </c>
-      <c r="H26" s="1">
-        <v>0</v>
-      </c>
-      <c r="I26" s="1">
-        <v>0</v>
-      </c>
-      <c r="J26" s="1">
-        <v>2</v>
-      </c>
-      <c r="K26" s="1">
-        <v>1</v>
-      </c>
-      <c r="L26" s="1">
-        <v>0</v>
-      </c>
-      <c r="M26" s="1">
-        <v>0</v>
-      </c>
-      <c r="N26" s="1">
-        <v>0</v>
-      </c>
-      <c r="O26" s="1">
-        <v>0</v>
-      </c>
-      <c r="P26" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="1">
-        <v>0</v>
-      </c>
-      <c r="R26" s="25">
-        <v>0</v>
-      </c>
-      <c r="S26" s="1"/>
-      <c r="T26" s="1"/>
-      <c r="U26" s="1"/>
-      <c r="V26" s="1"/>
-      <c r="W26" s="26"/>
-      <c r="X26" s="27" t="s">
-        <v>429</v>
-      </c>
-      <c r="Y26" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="Z26" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="AA26" s="26" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="27" spans="1:27">
-      <c r="A27" s="10">
-        <v>24</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="C27" s="1">
-        <v>10</v>
-      </c>
-      <c r="D27" s="1">
-        <v>0</v>
-      </c>
-      <c r="E27" s="1">
-        <v>0</v>
-      </c>
-      <c r="F27" s="1">
-        <v>10</v>
-      </c>
-      <c r="G27" s="1">
-        <v>0</v>
-      </c>
-      <c r="H27" s="1">
-        <v>0</v>
-      </c>
-      <c r="I27" s="1">
-        <v>0</v>
-      </c>
-      <c r="J27" s="1">
-        <v>2</v>
-      </c>
-      <c r="K27" s="1">
-        <v>1</v>
-      </c>
-      <c r="L27" s="1">
-        <v>0</v>
-      </c>
-      <c r="M27" s="1">
-        <v>0</v>
-      </c>
-      <c r="N27" s="1">
-        <v>0</v>
-      </c>
-      <c r="O27" s="1">
-        <v>0</v>
-      </c>
-      <c r="P27" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="1">
-        <v>0</v>
-      </c>
-      <c r="R27" s="25">
-        <v>0</v>
-      </c>
-      <c r="S27" s="1"/>
-      <c r="T27" s="1"/>
-      <c r="U27" s="1"/>
-      <c r="V27" s="1"/>
-      <c r="W27" s="26"/>
-      <c r="X27" s="27" t="s">
-        <v>434</v>
-      </c>
-      <c r="Y27" s="1" t="s">
-        <v>435</v>
-      </c>
-      <c r="Z27" s="1" t="s">
-        <v>436</v>
-      </c>
-      <c r="AA27" s="26" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="28" spans="1:27">
-      <c r="A28" s="10">
-        <v>25</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="C28" s="1">
-        <v>10</v>
-      </c>
-      <c r="D28" s="1">
-        <v>0</v>
-      </c>
-      <c r="E28" s="1">
-        <v>0</v>
-      </c>
-      <c r="F28" s="1">
-        <v>10</v>
-      </c>
-      <c r="G28" s="1">
-        <v>0</v>
-      </c>
-      <c r="H28" s="1">
-        <v>0</v>
-      </c>
-      <c r="I28" s="1">
-        <v>0</v>
-      </c>
-      <c r="J28" s="1">
-        <v>2</v>
-      </c>
-      <c r="K28" s="1">
-        <v>1</v>
-      </c>
-      <c r="L28" s="1">
-        <v>0</v>
-      </c>
-      <c r="M28" s="1">
-        <v>0</v>
-      </c>
-      <c r="N28" s="1">
-        <v>0</v>
-      </c>
-      <c r="O28" s="1">
-        <v>0</v>
-      </c>
-      <c r="P28" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q28" s="1">
-        <v>0</v>
-      </c>
-      <c r="R28" s="25">
-        <v>0</v>
-      </c>
-      <c r="S28" s="1"/>
-      <c r="T28" s="1"/>
-      <c r="U28" s="1"/>
-      <c r="V28" s="1"/>
-      <c r="W28" s="26"/>
-      <c r="X28" s="27" t="s">
-        <v>439</v>
-      </c>
-      <c r="Y28" s="1" t="s">
-        <v>440</v>
-      </c>
-      <c r="Z28" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="AA28" s="26" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="29" spans="1:27">
-      <c r="A29" s="10">
-        <v>26</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="C29" s="1">
-        <v>10</v>
-      </c>
-      <c r="D29" s="1">
-        <v>0</v>
-      </c>
-      <c r="E29" s="1">
-        <v>0</v>
-      </c>
-      <c r="F29" s="1">
-        <v>10</v>
-      </c>
-      <c r="G29" s="1">
-        <v>0</v>
-      </c>
-      <c r="H29" s="1">
-        <v>0</v>
-      </c>
-      <c r="I29" s="1">
-        <v>0</v>
-      </c>
-      <c r="J29" s="1">
-        <v>2</v>
-      </c>
-      <c r="K29" s="1">
-        <v>1</v>
-      </c>
-      <c r="L29" s="1">
-        <v>0</v>
-      </c>
-      <c r="M29" s="1">
-        <v>0</v>
-      </c>
-      <c r="N29" s="1">
-        <v>0</v>
-      </c>
-      <c r="O29" s="1">
-        <v>0</v>
-      </c>
-      <c r="P29" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="1">
-        <v>0</v>
-      </c>
-      <c r="R29" s="25">
-        <v>0</v>
-      </c>
-      <c r="S29" s="1"/>
-      <c r="T29" s="1"/>
-      <c r="U29" s="1"/>
-      <c r="V29" s="1"/>
-      <c r="W29" s="26"/>
-      <c r="X29" s="27" t="s">
-        <v>444</v>
-      </c>
-      <c r="Y29" s="1" t="s">
-        <v>445</v>
-      </c>
-      <c r="Z29" s="1" t="s">
-        <v>446</v>
-      </c>
-      <c r="AA29" s="26" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="30" spans="1:27">
-      <c r="A30" s="10">
-        <v>27</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>448</v>
-      </c>
-      <c r="C30" s="1">
-        <v>10</v>
-      </c>
-      <c r="D30" s="1">
-        <v>0</v>
-      </c>
-      <c r="E30" s="1">
-        <v>0</v>
-      </c>
-      <c r="F30" s="1">
-        <v>10</v>
-      </c>
-      <c r="G30" s="1">
-        <v>0</v>
-      </c>
-      <c r="H30" s="1">
-        <v>0</v>
-      </c>
-      <c r="I30" s="1">
-        <v>0</v>
-      </c>
-      <c r="J30" s="1">
-        <v>2</v>
-      </c>
-      <c r="K30" s="1">
-        <v>1</v>
-      </c>
-      <c r="L30" s="1">
-        <v>0</v>
-      </c>
-      <c r="M30" s="1">
-        <v>0</v>
-      </c>
-      <c r="N30" s="1">
-        <v>0</v>
-      </c>
-      <c r="O30" s="1">
-        <v>0</v>
-      </c>
-      <c r="P30" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q30" s="1">
-        <v>0</v>
-      </c>
-      <c r="R30" s="25">
-        <v>0</v>
-      </c>
-      <c r="S30" s="1"/>
-      <c r="T30" s="1"/>
-      <c r="U30" s="1"/>
-      <c r="V30" s="1"/>
-      <c r="W30" s="26"/>
-      <c r="X30" s="27" t="s">
-        <v>449</v>
-      </c>
-      <c r="Y30" s="1" t="s">
-        <v>450</v>
-      </c>
-      <c r="Z30" s="1" t="s">
-        <v>451</v>
-      </c>
-      <c r="AA30" s="26" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="31" spans="1:27">
-      <c r="A31" s="10">
-        <v>28</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>452</v>
-      </c>
-      <c r="C31" s="1">
-        <v>10</v>
-      </c>
-      <c r="D31" s="1">
-        <v>0</v>
-      </c>
-      <c r="E31" s="1">
-        <v>0</v>
-      </c>
-      <c r="F31" s="1">
-        <v>10</v>
-      </c>
-      <c r="G31" s="1">
-        <v>0</v>
-      </c>
-      <c r="H31" s="1">
-        <v>0</v>
-      </c>
-      <c r="I31" s="1">
-        <v>0</v>
-      </c>
-      <c r="J31" s="1">
-        <v>2</v>
-      </c>
-      <c r="K31" s="1">
-        <v>1</v>
-      </c>
-      <c r="L31" s="1">
-        <v>0</v>
-      </c>
-      <c r="M31" s="1">
-        <v>0</v>
-      </c>
-      <c r="N31" s="1">
-        <v>0</v>
-      </c>
-      <c r="O31" s="1">
-        <v>0</v>
-      </c>
-      <c r="P31" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q31" s="1">
-        <v>0</v>
-      </c>
-      <c r="R31" s="25">
-        <v>0</v>
-      </c>
-      <c r="S31" s="1"/>
-      <c r="T31" s="1"/>
-      <c r="U31" s="1"/>
-      <c r="V31" s="1"/>
-      <c r="W31" s="26"/>
-      <c r="X31" s="27" t="s">
-        <v>453</v>
-      </c>
-      <c r="Y31" s="1" t="s">
-        <v>454</v>
-      </c>
-      <c r="Z31" s="1" t="s">
-        <v>455</v>
-      </c>
-      <c r="AA31" s="26" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="32" spans="1:27">
-      <c r="A32" s="10">
-        <v>29</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>456</v>
-      </c>
-      <c r="C32" s="1">
-        <v>10</v>
-      </c>
-      <c r="D32" s="1">
-        <v>0</v>
-      </c>
-      <c r="E32" s="1">
-        <v>0</v>
-      </c>
-      <c r="F32" s="1">
-        <v>10</v>
-      </c>
-      <c r="G32" s="1">
-        <v>0</v>
-      </c>
-      <c r="H32" s="1">
-        <v>0</v>
-      </c>
-      <c r="I32" s="1">
-        <v>0</v>
-      </c>
-      <c r="J32" s="1">
-        <v>2</v>
-      </c>
-      <c r="K32" s="1">
-        <v>1</v>
-      </c>
-      <c r="L32" s="1">
-        <v>0</v>
-      </c>
-      <c r="M32" s="1">
-        <v>0</v>
-      </c>
-      <c r="N32" s="1">
-        <v>0</v>
-      </c>
-      <c r="O32" s="1">
-        <v>0</v>
-      </c>
-      <c r="P32" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="1">
-        <v>0</v>
-      </c>
-      <c r="R32" s="25">
-        <v>0</v>
-      </c>
-      <c r="S32" s="1"/>
-      <c r="T32" s="1"/>
-      <c r="U32" s="1"/>
-      <c r="V32" s="1"/>
-      <c r="W32" s="26"/>
-      <c r="X32" s="27" t="s">
-        <v>457</v>
-      </c>
-      <c r="Y32" s="1" t="s">
-        <v>458</v>
-      </c>
-      <c r="Z32" s="1" t="s">
-        <v>459</v>
-      </c>
-      <c r="AA32" s="26" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="33" spans="1:27">
-      <c r="A33" s="10">
-        <v>30</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>461</v>
-      </c>
-      <c r="C33" s="1">
-        <v>10</v>
-      </c>
-      <c r="D33" s="1">
-        <v>0</v>
-      </c>
-      <c r="E33" s="1">
-        <v>0</v>
-      </c>
-      <c r="F33" s="1">
-        <v>10</v>
-      </c>
-      <c r="G33" s="1">
-        <v>0</v>
-      </c>
-      <c r="H33" s="1">
-        <v>0</v>
-      </c>
-      <c r="I33" s="1">
-        <v>0</v>
-      </c>
-      <c r="J33" s="1">
-        <v>2</v>
-      </c>
-      <c r="K33" s="1">
-        <v>1</v>
-      </c>
-      <c r="L33" s="1">
-        <v>0</v>
-      </c>
-      <c r="M33" s="1">
-        <v>0</v>
-      </c>
-      <c r="N33" s="1">
-        <v>0</v>
-      </c>
-      <c r="O33" s="1">
-        <v>0</v>
-      </c>
-      <c r="P33" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q33" s="1">
-        <v>0</v>
-      </c>
-      <c r="R33" s="25">
-        <v>0</v>
-      </c>
-      <c r="S33" s="1"/>
-      <c r="T33" s="1"/>
-      <c r="U33" s="1"/>
-      <c r="V33" s="1"/>
-      <c r="W33" s="26"/>
-      <c r="X33" s="27" t="s">
-        <v>462</v>
-      </c>
-      <c r="Y33" s="1" t="s">
-        <v>463</v>
-      </c>
-      <c r="Z33" s="1" t="s">
-        <v>464</v>
-      </c>
-      <c r="AA33" s="26" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="34" spans="1:27">
-      <c r="A34" s="10">
-        <v>31</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>466</v>
-      </c>
-      <c r="C34" s="1">
-        <v>10</v>
-      </c>
-      <c r="D34" s="1">
-        <v>0</v>
-      </c>
-      <c r="E34" s="1">
-        <v>0</v>
-      </c>
-      <c r="F34" s="1">
-        <v>10</v>
-      </c>
-      <c r="G34" s="1">
-        <v>0</v>
-      </c>
-      <c r="H34" s="1">
-        <v>0</v>
-      </c>
-      <c r="I34" s="1">
-        <v>0</v>
-      </c>
-      <c r="J34" s="1">
-        <v>2</v>
-      </c>
-      <c r="K34" s="1">
-        <v>1</v>
-      </c>
-      <c r="L34" s="1">
-        <v>0</v>
-      </c>
-      <c r="M34" s="1">
-        <v>0</v>
-      </c>
-      <c r="N34" s="1">
-        <v>0</v>
-      </c>
-      <c r="O34" s="1">
-        <v>0</v>
-      </c>
-      <c r="P34" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q34" s="1">
-        <v>0</v>
-      </c>
-      <c r="R34" s="25">
-        <v>0</v>
-      </c>
-      <c r="S34" s="1"/>
-      <c r="T34" s="1"/>
-      <c r="U34" s="1"/>
-      <c r="V34" s="1"/>
-      <c r="W34" s="26"/>
-      <c r="X34" s="27" t="s">
-        <v>467</v>
-      </c>
-      <c r="Y34" s="1" t="s">
-        <v>468</v>
-      </c>
-      <c r="Z34" s="1" t="s">
-        <v>469</v>
-      </c>
-      <c r="AA34" s="26" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="35" spans="1:27">
-      <c r="A35" s="10">
-        <v>32</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>470</v>
-      </c>
-      <c r="C35" s="1">
-        <v>10</v>
-      </c>
-      <c r="D35" s="1">
-        <v>0</v>
-      </c>
-      <c r="E35" s="1">
-        <v>0</v>
-      </c>
-      <c r="F35" s="1">
-        <v>10</v>
-      </c>
-      <c r="G35" s="1">
-        <v>0</v>
-      </c>
-      <c r="H35" s="1">
-        <v>0</v>
-      </c>
-      <c r="I35" s="1">
-        <v>0</v>
-      </c>
-      <c r="J35" s="1">
-        <v>2</v>
-      </c>
-      <c r="K35" s="1">
-        <v>1</v>
-      </c>
-      <c r="L35" s="1">
-        <v>0</v>
-      </c>
-      <c r="M35" s="1">
-        <v>0</v>
-      </c>
-      <c r="N35" s="1">
-        <v>0</v>
-      </c>
-      <c r="O35" s="1">
-        <v>0</v>
-      </c>
-      <c r="P35" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q35" s="1">
-        <v>0</v>
-      </c>
-      <c r="R35" s="25">
-        <v>0</v>
-      </c>
-      <c r="S35" s="1"/>
-      <c r="T35" s="1"/>
-      <c r="U35" s="1"/>
-      <c r="V35" s="1"/>
-      <c r="W35" s="26"/>
-      <c r="X35" s="27" t="s">
-        <v>471</v>
-      </c>
-      <c r="Y35" s="1" t="s">
-        <v>472</v>
-      </c>
-      <c r="Z35" s="1" t="s">
-        <v>473</v>
-      </c>
-      <c r="AA35" s="26" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="36" spans="1:27">
-      <c r="A36" s="10">
-        <v>33</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>475</v>
-      </c>
-      <c r="C36" s="1">
-        <v>10</v>
-      </c>
-      <c r="D36" s="1">
-        <v>0</v>
-      </c>
-      <c r="E36" s="1">
-        <v>0</v>
-      </c>
-      <c r="F36" s="1">
-        <v>10</v>
-      </c>
-      <c r="G36" s="1">
-        <v>0</v>
-      </c>
-      <c r="H36" s="1">
-        <v>0</v>
-      </c>
-      <c r="I36" s="1">
-        <v>0</v>
-      </c>
-      <c r="J36" s="1">
-        <v>2</v>
-      </c>
-      <c r="K36" s="1">
-        <v>1</v>
-      </c>
-      <c r="L36" s="1">
-        <v>0</v>
-      </c>
-      <c r="M36" s="1">
-        <v>0</v>
-      </c>
-      <c r="N36" s="1">
-        <v>0</v>
-      </c>
-      <c r="O36" s="1">
-        <v>0</v>
-      </c>
-      <c r="P36" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q36" s="1">
-        <v>0</v>
-      </c>
-      <c r="R36" s="25">
-        <v>0</v>
-      </c>
-      <c r="S36" s="1"/>
-      <c r="T36" s="1"/>
-      <c r="U36" s="1"/>
-      <c r="V36" s="1"/>
-      <c r="W36" s="26"/>
-      <c r="X36" s="27" t="s">
-        <v>476</v>
-      </c>
-      <c r="Y36" s="1" t="s">
-        <v>477</v>
-      </c>
-      <c r="Z36" s="1" t="s">
-        <v>478</v>
-      </c>
-      <c r="AA36" s="26" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="37" spans="1:27">
-      <c r="A37" s="10">
-        <v>34</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>480</v>
-      </c>
-      <c r="C37" s="1">
-        <v>10</v>
-      </c>
-      <c r="D37" s="1">
-        <v>0</v>
-      </c>
-      <c r="E37" s="1">
-        <v>0</v>
-      </c>
-      <c r="F37" s="1">
-        <v>10</v>
-      </c>
-      <c r="G37" s="1">
-        <v>0</v>
-      </c>
-      <c r="H37" s="1">
-        <v>0</v>
-      </c>
-      <c r="I37" s="1">
-        <v>0</v>
-      </c>
-      <c r="J37" s="1">
-        <v>2</v>
-      </c>
-      <c r="K37" s="1">
-        <v>1</v>
-      </c>
-      <c r="L37" s="1">
-        <v>0</v>
-      </c>
-      <c r="M37" s="1">
-        <v>0</v>
-      </c>
-      <c r="N37" s="1">
-        <v>0</v>
-      </c>
-      <c r="O37" s="1">
-        <v>0</v>
-      </c>
-      <c r="P37" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q37" s="1">
-        <v>0</v>
-      </c>
-      <c r="R37" s="25">
-        <v>0</v>
-      </c>
-      <c r="S37" s="1"/>
-      <c r="T37" s="1"/>
-      <c r="U37" s="1"/>
-      <c r="V37" s="1"/>
-      <c r="W37" s="26"/>
-      <c r="X37" s="27" t="s">
-        <v>481</v>
-      </c>
-      <c r="Y37" s="1" t="s">
-        <v>482</v>
-      </c>
-      <c r="Z37" s="1" t="s">
-        <v>483</v>
-      </c>
-      <c r="AA37" s="26" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="38" spans="1:27">
-      <c r="A38" s="10">
-        <v>35</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>485</v>
-      </c>
-      <c r="C38" s="1">
-        <v>10</v>
-      </c>
-      <c r="D38" s="1">
-        <v>0</v>
-      </c>
-      <c r="E38" s="1">
-        <v>0</v>
-      </c>
-      <c r="F38" s="1">
-        <v>10</v>
-      </c>
-      <c r="G38" s="1">
-        <v>0</v>
-      </c>
-      <c r="H38" s="1">
-        <v>0</v>
-      </c>
-      <c r="I38" s="1">
-        <v>0</v>
-      </c>
-      <c r="J38" s="1">
-        <v>2</v>
-      </c>
-      <c r="K38" s="1">
-        <v>1</v>
-      </c>
-      <c r="L38" s="1">
-        <v>0</v>
-      </c>
-      <c r="M38" s="1">
-        <v>0</v>
-      </c>
-      <c r="N38" s="1">
-        <v>0</v>
-      </c>
-      <c r="O38" s="1">
-        <v>0</v>
-      </c>
-      <c r="P38" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q38" s="1">
-        <v>0</v>
-      </c>
-      <c r="R38" s="25">
-        <v>0</v>
-      </c>
-      <c r="S38" s="1"/>
-      <c r="T38" s="1"/>
-      <c r="U38" s="1"/>
-      <c r="V38" s="1"/>
-      <c r="W38" s="26"/>
-      <c r="X38" s="27" t="s">
-        <v>486</v>
-      </c>
-      <c r="Y38" s="1" t="s">
-        <v>487</v>
-      </c>
-      <c r="Z38" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="AA38" s="26" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="39" spans="1:27">
-      <c r="A39" s="10">
-        <v>36</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>490</v>
-      </c>
-      <c r="C39" s="1">
-        <v>10</v>
-      </c>
-      <c r="D39" s="1">
-        <v>0</v>
-      </c>
-      <c r="E39" s="1">
-        <v>0</v>
-      </c>
-      <c r="F39" s="1">
-        <v>10</v>
-      </c>
-      <c r="G39" s="1">
-        <v>0</v>
-      </c>
-      <c r="H39" s="1">
-        <v>0</v>
-      </c>
-      <c r="I39" s="1">
-        <v>0</v>
-      </c>
-      <c r="J39" s="1">
-        <v>2</v>
-      </c>
-      <c r="K39" s="1">
-        <v>1</v>
-      </c>
-      <c r="L39" s="1">
-        <v>0</v>
-      </c>
-      <c r="M39" s="1">
-        <v>0</v>
-      </c>
-      <c r="N39" s="1">
-        <v>0</v>
-      </c>
-      <c r="O39" s="1">
-        <v>0</v>
-      </c>
-      <c r="P39" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q39" s="1">
-        <v>0</v>
-      </c>
-      <c r="R39" s="25">
-        <v>0</v>
-      </c>
-      <c r="S39" s="1"/>
-      <c r="T39" s="1"/>
-      <c r="U39" s="1"/>
-      <c r="V39" s="1"/>
-      <c r="W39" s="26"/>
-      <c r="X39" s="27" t="s">
-        <v>491</v>
-      </c>
-      <c r="Y39" s="1" t="s">
-        <v>492</v>
-      </c>
-      <c r="Z39" s="1" t="s">
-        <v>493</v>
-      </c>
-      <c r="AA39" s="26" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="40" spans="1:27">
-      <c r="A40" s="10">
-        <v>37</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>495</v>
-      </c>
-      <c r="C40" s="1">
-        <v>10</v>
-      </c>
-      <c r="D40" s="1">
-        <v>0</v>
-      </c>
-      <c r="E40" s="1">
-        <v>0</v>
-      </c>
-      <c r="F40" s="1">
-        <v>10</v>
-      </c>
-      <c r="G40" s="1">
-        <v>0</v>
-      </c>
-      <c r="H40" s="1">
-        <v>0</v>
-      </c>
-      <c r="I40" s="1">
-        <v>0</v>
-      </c>
-      <c r="J40" s="1">
-        <v>2</v>
-      </c>
-      <c r="K40" s="1">
-        <v>1</v>
-      </c>
-      <c r="L40" s="1">
-        <v>0</v>
-      </c>
-      <c r="M40" s="1">
-        <v>0</v>
-      </c>
-      <c r="N40" s="1">
-        <v>0</v>
-      </c>
-      <c r="O40" s="1">
-        <v>0</v>
-      </c>
-      <c r="P40" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q40" s="1">
-        <v>0</v>
-      </c>
-      <c r="R40" s="25">
-        <v>0</v>
-      </c>
-      <c r="S40" s="1"/>
-      <c r="T40" s="1"/>
-      <c r="U40" s="1"/>
-      <c r="V40" s="1"/>
-      <c r="W40" s="26"/>
-      <c r="X40" s="27" t="s">
-        <v>496</v>
-      </c>
-      <c r="Y40" s="1" t="s">
-        <v>497</v>
-      </c>
-      <c r="Z40" s="1" t="s">
-        <v>498</v>
-      </c>
-      <c r="AA40" s="26" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="41" ht="14.25" spans="1:27">
-      <c r="A41" s="11">
-        <v>38</v>
-      </c>
-      <c r="B41" s="12" t="s">
-        <v>499</v>
-      </c>
-      <c r="C41" s="12">
-        <v>10</v>
-      </c>
-      <c r="D41" s="12">
-        <v>0</v>
-      </c>
-      <c r="E41" s="12">
-        <v>0</v>
-      </c>
-      <c r="F41" s="12">
-        <v>10</v>
-      </c>
-      <c r="G41" s="12">
-        <v>0</v>
-      </c>
-      <c r="H41" s="12">
-        <v>0</v>
-      </c>
-      <c r="I41" s="12">
-        <v>0</v>
-      </c>
-      <c r="J41" s="12">
-        <v>2</v>
-      </c>
-      <c r="K41" s="12">
-        <v>1</v>
-      </c>
-      <c r="L41" s="12">
-        <v>0</v>
-      </c>
-      <c r="M41" s="12">
-        <v>0</v>
-      </c>
-      <c r="N41" s="12">
-        <v>0</v>
-      </c>
-      <c r="O41" s="12">
-        <v>0</v>
-      </c>
-      <c r="P41" s="12">
-        <v>0</v>
-      </c>
-      <c r="Q41" s="12">
-        <v>0</v>
-      </c>
-      <c r="R41" s="28">
-        <v>0</v>
-      </c>
-      <c r="S41" s="12"/>
-      <c r="T41" s="12"/>
-      <c r="U41" s="12"/>
-      <c r="V41" s="12"/>
-      <c r="W41" s="29"/>
-      <c r="X41" s="30" t="s">
-        <v>500</v>
-      </c>
-      <c r="Y41" s="12" t="s">
-        <v>501</v>
-      </c>
-      <c r="Z41" s="12" t="s">
-        <v>502</v>
-      </c>
-      <c r="AA41" s="29" t="s">
-        <v>336</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
 </file>
--- a/xlsdir/配置-总表.xlsx
+++ b/xlsdir/配置-总表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="673" firstSheet="3" activeTab="5"/>
+    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="673" firstSheet="3" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="character|角色" sheetId="32" r:id="rId1"/>
@@ -12,8 +12,8 @@
     <sheet name="hero|玩家角色" sheetId="27" r:id="rId3"/>
     <sheet name="monster|魔物" sheetId="28" r:id="rId4"/>
     <sheet name="card|卡牌" sheetId="29" r:id="rId5"/>
-    <sheet name="buff|增益" sheetId="39" r:id="rId6"/>
-    <sheet name="intent|意图" sheetId="38" r:id="rId7"/>
+    <sheet name="intent|意图" sheetId="38" r:id="rId6"/>
+    <sheet name="buff|增益" sheetId="39" r:id="rId7"/>
     <sheet name="ability_effect|技能效果" sheetId="34" r:id="rId8"/>
     <sheet name="attribute|属性" sheetId="35" r:id="rId9"/>
     <sheet name="Sheet1" sheetId="11" r:id="rId10"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="810" uniqueCount="535">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="834" uniqueCount="548">
   <si>
     <t>ID</t>
   </si>
@@ -326,21 +326,353 @@
     <t>vulnerable</t>
   </si>
   <si>
+    <t>owner</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>weight</t>
+  </si>
+  <si>
+    <t>cooldown</t>
+  </si>
+  <si>
+    <t>des</t>
+  </si>
+  <si>
+    <t>value</t>
+  </si>
+  <si>
+    <t>func</t>
+  </si>
+  <si>
+    <t>所属(注释）</t>
+  </si>
+  <si>
+    <t>意图名</t>
+  </si>
+  <si>
+    <t>意图类型</t>
+  </si>
+  <si>
+    <t>权重</t>
+  </si>
+  <si>
+    <t>冷却</t>
+  </si>
+  <si>
+    <t>意图描述</t>
+  </si>
+  <si>
+    <t>意图图标</t>
+  </si>
+  <si>
+    <t>意图值</t>
+  </si>
+  <si>
+    <t>意图方法</t>
+  </si>
+  <si>
+    <t>float</t>
+  </si>
+  <si>
+    <t>ATTACK</t>
+  </si>
+  <si>
+    <t>攻击</t>
+  </si>
+  <si>
+    <t>敌人打算进行攻击。</t>
+  </si>
+  <si>
+    <t>res://asserts/textures/widgets/Buffs/poison_dagger.png</t>
+  </si>
+  <si>
+    <t>MULTI_ATTACK</t>
+  </si>
+  <si>
+    <t>多重攻击</t>
+  </si>
+  <si>
+    <t>敌人计划多次攻击。</t>
+  </si>
+  <si>
+    <t>res://asserts/textures/widgets/Buffs/thorn_vine_spell.png</t>
+  </si>
+  <si>
+    <t>DEFEND</t>
+  </si>
+  <si>
+    <t>敌人将增加防御力</t>
+  </si>
+  <si>
+    <t>res://asserts/textures/widgets/Buffs/healing_spell.png</t>
+  </si>
+  <si>
+    <t>BUFF</t>
+  </si>
+  <si>
+    <t>强化</t>
+  </si>
+  <si>
+    <t>敌人将提升某项能力，如攻击力、防御力或特殊能力。</t>
+  </si>
+  <si>
+    <t>res://asserts/textures/widgets/Buffs/on_fire_(burning).png</t>
+  </si>
+  <si>
+    <t>DEBUFF</t>
+  </si>
+  <si>
+    <t>弱化</t>
+  </si>
+  <si>
+    <t>敌人计划施放会削弱玩家能力的效果，如减少玩家的攻击力或防御力。</t>
+  </si>
+  <si>
+    <t>res://asserts/textures/widgets/Buffs/disarmed.png</t>
+  </si>
+  <si>
+    <t>HEAL</t>
+  </si>
+  <si>
+    <t>治疗</t>
+  </si>
+  <si>
+    <t>敌人会恢复一定量的生命值。</t>
+  </si>
+  <si>
+    <t>res://asserts/textures/widgets/Buffs/lucky_boost.png</t>
+  </si>
+  <si>
+    <t>STRATEGY</t>
+  </si>
+  <si>
+    <t>策略</t>
+  </si>
+  <si>
+    <t>敌人将采取某种特殊行动，如召唤援助、准备强力攻击或其他战术动作。</t>
+  </si>
+  <si>
+    <t>res://asserts/textures/widgets/Buffs/confused.png</t>
+  </si>
+  <si>
+    <t>ESCAPE</t>
+  </si>
+  <si>
+    <t>逃跑</t>
+  </si>
+  <si>
+    <t>在某些战斗中，敌人可能会试图逃跑，尤其是在遭遇战中</t>
+  </si>
+  <si>
+    <t>res://asserts/textures/widgets/Buffs/swiftness.png</t>
+  </si>
+  <si>
+    <t>split</t>
+  </si>
+  <si>
+    <t>脆弱</t>
+  </si>
+  <si>
+    <t>目标下一回合获得的护甲值降低25%</t>
+  </si>
+  <si>
+    <t>res://asserts/textures/widgets/Buffs/ghost_form_(physical_damage_immunity).png</t>
+  </si>
+  <si>
+    <t>absorb</t>
+  </si>
+  <si>
+    <t>吸收</t>
+  </si>
+  <si>
+    <t>回复一定量的生命值，吸收的量取决于其当前生命值。</t>
+  </si>
+  <si>
+    <t>res://asserts/textures/widgets/Buffs/summoning_spell.png</t>
+  </si>
+  <si>
+    <t>entangle</t>
+  </si>
+  <si>
+    <t>缠绕</t>
+  </si>
+  <si>
+    <t>降低玩家下一回合的行动点数。</t>
+  </si>
+  <si>
+    <t>toxin_spray</t>
+  </si>
+  <si>
+    <t>毒素喷射</t>
+  </si>
+  <si>
+    <t>造成持续性的毒素伤害。</t>
+  </si>
+  <si>
+    <t>res://asserts/textures/widgets/Buffs/poisoned.png</t>
+  </si>
+  <si>
+    <t>healing_spore</t>
+  </si>
+  <si>
+    <t>治疗孢子</t>
+  </si>
+  <si>
+    <t>为自己或其他敌人恢复生命值。</t>
+  </si>
+  <si>
+    <t>hallucinogenic_spore</t>
+  </si>
+  <si>
+    <t>迷幻孢子</t>
+  </si>
+  <si>
+    <t>玩家获得“混乱”卡牌。</t>
+  </si>
+  <si>
+    <t>destruction_ray</t>
+  </si>
+  <si>
+    <t>破坏射线</t>
+  </si>
+  <si>
+    <t>对玩家造成魔法伤害。</t>
+  </si>
+  <si>
+    <t>curse_gaze</t>
+  </si>
+  <si>
+    <t>诅咒凝视</t>
+  </si>
+  <si>
+    <t>使玩家在下一回合内受到的伤害增加。</t>
+  </si>
+  <si>
+    <t>magic_shield</t>
+  </si>
+  <si>
+    <t>魔法护盾</t>
+  </si>
+  <si>
+    <t>为自己添加一层护盾，抵挡一定量的伤害。</t>
+  </si>
+  <si>
+    <t>sprint_stab</t>
+  </si>
+  <si>
+    <t>疾跑刺击</t>
+  </si>
+  <si>
+    <t>快速冲刺并对玩家造成物理伤害。</t>
+  </si>
+  <si>
+    <t>set_trap</t>
+  </si>
+  <si>
+    <t>布置陷阱</t>
+  </si>
+  <si>
+    <t>下一回合对玩家造成额外伤害。</t>
+  </si>
+  <si>
+    <t>sneak_attack</t>
+  </si>
+  <si>
+    <t>偷袭</t>
+  </si>
+  <si>
+    <t>如果玩家生命值低，造成额外伤害。</t>
+  </si>
+  <si>
+    <t>heavy_strike</t>
+  </si>
+  <si>
+    <t>重击</t>
+  </si>
+  <si>
+    <t>用锋利的武器对玩家造成大量伤害。</t>
+  </si>
+  <si>
+    <t>bone_shield</t>
+  </si>
+  <si>
+    <t>骨盾</t>
+  </si>
+  <si>
+    <t>summon_assistance</t>
+  </si>
+  <si>
+    <t>召唤援助</t>
+  </si>
+  <si>
+    <t>召唤另一个骷髅怪加入战斗</t>
+  </si>
+  <si>
+    <t>duration</t>
+  </si>
+  <si>
     <t>效果名</t>
   </si>
   <si>
+    <t>持续类型
+1永久
+2持续回合</t>
+  </si>
+  <si>
+    <t>图标</t>
+  </si>
+  <si>
     <t>格挡</t>
   </si>
   <si>
     <t>持续到下一个回合开始之前，格挡伤害</t>
   </si>
   <si>
+    <t>res://asserts/textures/widgets/Buffs/fortify_spell.png</t>
+  </si>
+  <si>
+    <t>strength</t>
+  </si>
+  <si>
+    <t>力量</t>
+  </si>
+  <si>
+    <t>增加角色攻击卡牌造成的伤害</t>
+  </si>
+  <si>
+    <t>dexterity</t>
+  </si>
+  <si>
+    <t>敏捷</t>
+  </si>
+  <si>
+    <t>增加每次或格挡时的格挡量</t>
+  </si>
+  <si>
+    <t>regen</t>
+  </si>
+  <si>
+    <t>再生</t>
+  </si>
+  <si>
+    <t>每回合结束时恢复一定量的生命值</t>
+  </si>
+  <si>
     <t>易伤</t>
   </si>
   <si>
     <t>使目标收到的攻击伤害增加</t>
   </si>
   <si>
+    <t>VULNERABLE</t>
+  </si>
+  <si>
+    <t>res://asserts/textures/widgets/Buffs/defense_down.png</t>
+  </si>
+  <si>
     <t>weak</t>
   </si>
   <si>
@@ -359,304 +691,25 @@
     <t>每个回合结束时，根据层数对目标造成伤害</t>
   </si>
   <si>
+    <t>frail</t>
+  </si>
+  <si>
+    <t>摧残</t>
+  </si>
+  <si>
+    <t>减少从所有来源获得的格挡值</t>
+  </si>
+  <si>
     <t>entangled</t>
   </si>
   <si>
-    <t>缠绕</t>
-  </si>
-  <si>
     <t>目标在下一个回合无法攻击</t>
   </si>
   <si>
-    <t>owner</t>
-  </si>
-  <si>
-    <t>type</t>
-  </si>
-  <si>
-    <t>weight</t>
-  </si>
-  <si>
-    <t>cooldown</t>
-  </si>
-  <si>
-    <t>des</t>
-  </si>
-  <si>
-    <t>value</t>
-  </si>
-  <si>
-    <t>func</t>
-  </si>
-  <si>
-    <t>所属(注释）</t>
-  </si>
-  <si>
-    <t>意图名</t>
-  </si>
-  <si>
-    <t>意图类型</t>
-  </si>
-  <si>
-    <t>权重</t>
-  </si>
-  <si>
-    <t>冷却</t>
-  </si>
-  <si>
-    <t>意图描述</t>
-  </si>
-  <si>
-    <t>意图图标</t>
-  </si>
-  <si>
-    <t>意图值</t>
-  </si>
-  <si>
-    <t>意图方法</t>
-  </si>
-  <si>
-    <t>float</t>
-  </si>
-  <si>
-    <t>ATTACK</t>
-  </si>
-  <si>
-    <t>攻击</t>
-  </si>
-  <si>
-    <t>敌人打算进行攻击。</t>
-  </si>
-  <si>
-    <t>res://asserts/textures/widgets/Buffs/poison_dagger.png</t>
-  </si>
-  <si>
-    <t>MULTI_ATTACK</t>
-  </si>
-  <si>
-    <t>多重攻击</t>
-  </si>
-  <si>
-    <t>敌人计划多次攻击。</t>
-  </si>
-  <si>
-    <t>res://asserts/textures/widgets/Buffs/thorn_vine_spell.png</t>
-  </si>
-  <si>
-    <t>DEFEND</t>
-  </si>
-  <si>
-    <t>敌人将增加防御力</t>
-  </si>
-  <si>
-    <t>res://asserts/textures/widgets/Buffs/healing_spell.png</t>
-  </si>
-  <si>
-    <t>BUFF</t>
-  </si>
-  <si>
-    <t>强化</t>
-  </si>
-  <si>
-    <t>敌人将提升某项能力，如攻击力、防御力或特殊能力。</t>
-  </si>
-  <si>
-    <t>res://asserts/textures/widgets/Buffs/on_fire_(burning).png</t>
-  </si>
-  <si>
-    <t>DEBUFF</t>
-  </si>
-  <si>
-    <t>弱化</t>
-  </si>
-  <si>
-    <t>敌人计划施放会削弱玩家能力的效果，如减少玩家的攻击力或防御力。</t>
-  </si>
-  <si>
-    <t>res://asserts/textures/widgets/Buffs/disarmed.png</t>
-  </si>
-  <si>
-    <t>HEAL</t>
-  </si>
-  <si>
-    <t>治疗</t>
-  </si>
-  <si>
-    <t>敌人会恢复一定量的生命值。</t>
-  </si>
-  <si>
-    <t>res://asserts/textures/widgets/Buffs/lucky_boost.png</t>
-  </si>
-  <si>
-    <t>STRATEGY</t>
-  </si>
-  <si>
-    <t>策略</t>
-  </si>
-  <si>
-    <t>敌人将采取某种特殊行动，如召唤援助、准备强力攻击或其他战术动作。</t>
-  </si>
-  <si>
-    <t>res://asserts/textures/widgets/Buffs/confused.png</t>
-  </si>
-  <si>
-    <t>ESCAPE</t>
-  </si>
-  <si>
-    <t>逃跑</t>
-  </si>
-  <si>
-    <t>在某些战斗中，敌人可能会试图逃跑，尤其是在遭遇战中</t>
-  </si>
-  <si>
-    <t>res://asserts/textures/widgets/Buffs/swiftness.png</t>
-  </si>
-  <si>
-    <t>split</t>
-  </si>
-  <si>
-    <t>脆弱</t>
-  </si>
-  <si>
-    <t>目标下一回合获得的护甲值降低25%</t>
-  </si>
-  <si>
-    <t>res://asserts/textures/widgets/Buffs/ghost_form_(physical_damage_immunity).png</t>
-  </si>
-  <si>
-    <t>absorb</t>
-  </si>
-  <si>
-    <t>吸收</t>
-  </si>
-  <si>
-    <t>回复一定量的生命值，吸收的量取决于其当前生命值。</t>
-  </si>
-  <si>
-    <t>res://asserts/textures/widgets/Buffs/summoning_spell.png</t>
-  </si>
-  <si>
-    <t>entangle</t>
-  </si>
-  <si>
-    <t>降低玩家下一回合的行动点数。</t>
-  </si>
-  <si>
-    <t>toxin_spray</t>
-  </si>
-  <si>
-    <t>毒素喷射</t>
-  </si>
-  <si>
-    <t>造成持续性的毒素伤害。</t>
-  </si>
-  <si>
-    <t>res://asserts/textures/widgets/Buffs/poisoned.png</t>
-  </si>
-  <si>
-    <t>healing_spore</t>
-  </si>
-  <si>
-    <t>治疗孢子</t>
-  </si>
-  <si>
-    <t>为自己或其他敌人恢复生命值。</t>
-  </si>
-  <si>
-    <t>hallucinogenic_spore</t>
-  </si>
-  <si>
-    <t>迷幻孢子</t>
-  </si>
-  <si>
-    <t>玩家获得“混乱”卡牌。</t>
-  </si>
-  <si>
-    <t>destruction_ray</t>
-  </si>
-  <si>
-    <t>破坏射线</t>
-  </si>
-  <si>
-    <t>对玩家造成魔法伤害。</t>
-  </si>
-  <si>
-    <t>curse_gaze</t>
-  </si>
-  <si>
-    <t>诅咒凝视</t>
-  </si>
-  <si>
-    <t>使玩家在下一回合内受到的伤害增加。</t>
-  </si>
-  <si>
-    <t>magic_shield</t>
-  </si>
-  <si>
-    <t>魔法护盾</t>
-  </si>
-  <si>
-    <t>为自己添加一层护盾，抵挡一定量的伤害。</t>
-  </si>
-  <si>
-    <t>sprint_stab</t>
-  </si>
-  <si>
-    <t>疾跑刺击</t>
-  </si>
-  <si>
-    <t>快速冲刺并对玩家造成物理伤害。</t>
-  </si>
-  <si>
-    <t>set_trap</t>
-  </si>
-  <si>
-    <t>布置陷阱</t>
-  </si>
-  <si>
-    <t>下一回合对玩家造成额外伤害。</t>
-  </si>
-  <si>
-    <t>sneak_attack</t>
-  </si>
-  <si>
-    <t>偷袭</t>
-  </si>
-  <si>
-    <t>如果玩家生命值低，造成额外伤害。</t>
-  </si>
-  <si>
-    <t>heavy_strike</t>
-  </si>
-  <si>
-    <t>重击</t>
-  </si>
-  <si>
-    <t>用锋利的武器对玩家造成大量伤害。</t>
-  </si>
-  <si>
-    <t>bone_shield</t>
-  </si>
-  <si>
-    <t>骨盾</t>
-  </si>
-  <si>
-    <t>summon_assistance</t>
-  </si>
-  <si>
-    <t>召唤援助</t>
-  </si>
-  <si>
-    <t>召唤另一个骷髅怪加入战斗</t>
-  </si>
-  <si>
     <t>注释</t>
   </si>
   <si>
     <t>effect_name</t>
-  </si>
-  <si>
-    <t>duration</t>
   </si>
   <si>
     <t>effect_type</t>
@@ -714,15 +767,12 @@
     <t>给予易伤</t>
   </si>
   <si>
-    <t>VULNERABLE*2</t>
+    <t>vulnerable*2</t>
   </si>
   <si>
     <t>给与2层易伤</t>
   </si>
   <si>
-    <t>VULNERABLE</t>
-  </si>
-  <si>
     <t>易伤（Vulnerable）</t>
   </si>
   <si>
@@ -774,9 +824,6 @@
     <t>再生（Regenerating）</t>
   </si>
   <si>
-    <t>再生</t>
-  </si>
-  <si>
     <t>目标每回合恢复5生命值。</t>
   </si>
   <si>
@@ -960,16 +1007,10 @@
     <t>Strength</t>
   </si>
   <si>
-    <t>力量</t>
-  </si>
-  <si>
     <t>增加角色攻击力的强化值</t>
   </si>
   <si>
     <t>Dexterity</t>
-  </si>
-  <si>
-    <t>敏捷</t>
   </si>
   <si>
     <t>影响角色行动速度或攻击速度的属性</t>
@@ -1996,13 +2037,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.6"/>
+        <fgColor theme="2" tint="-0.1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="2" tint="-0.1"/>
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2791,7 +2832,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2942,22 +2983,43 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2966,9 +3028,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2978,20 +3037,11 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -3529,67 +3579,67 @@
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>310</v>
+        <v>323</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>311</v>
+        <v>324</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>312</v>
+        <v>325</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>313</v>
+        <v>326</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>314</v>
+        <v>327</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>315</v>
+        <v>328</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>316</v>
+        <v>329</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>317</v>
+        <v>330</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>318</v>
+        <v>331</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>319</v>
+        <v>332</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>320</v>
+        <v>333</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>321</v>
+        <v>334</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>322</v>
+        <v>335</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>324</v>
+        <v>337</v>
       </c>
       <c r="R1" s="13" t="s">
-        <v>325</v>
+        <v>338</v>
       </c>
       <c r="S1" s="3" t="s">
-        <v>326</v>
+        <v>339</v>
       </c>
       <c r="T1" s="3" t="s">
-        <v>327</v>
+        <v>340</v>
       </c>
       <c r="U1" s="3" t="s">
-        <v>328</v>
+        <v>341</v>
       </c>
       <c r="V1" s="3" t="s">
-        <v>329</v>
+        <v>342</v>
       </c>
       <c r="W1" s="14" t="s">
-        <v>330</v>
+        <v>343</v>
       </c>
       <c r="X1" s="15"/>
       <c r="Y1" s="15"/>
@@ -3601,82 +3651,82 @@
         <v>5</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>331</v>
+        <v>344</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>280</v>
+        <v>295</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>332</v>
+        <v>345</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>333</v>
+        <v>346</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>261</v>
+        <v>276</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>334</v>
+        <v>347</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>335</v>
+        <v>348</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>336</v>
+        <v>349</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>337</v>
+        <v>350</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>338</v>
+        <v>351</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>339</v>
+        <v>352</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>340</v>
+        <v>353</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>341</v>
+        <v>354</v>
       </c>
       <c r="O2" s="5" t="s">
-        <v>342</v>
+        <v>355</v>
       </c>
       <c r="P2" s="5" t="s">
-        <v>343</v>
+        <v>356</v>
       </c>
       <c r="Q2" s="5" t="s">
-        <v>344</v>
+        <v>357</v>
       </c>
       <c r="R2" s="16" t="s">
-        <v>345</v>
+        <v>358</v>
       </c>
       <c r="S2" s="5" t="s">
-        <v>346</v>
+        <v>359</v>
       </c>
       <c r="T2" s="5" t="s">
-        <v>300</v>
+        <v>196</v>
       </c>
       <c r="U2" s="5" t="s">
-        <v>303</v>
+        <v>199</v>
       </c>
       <c r="V2" s="5" t="s">
-        <v>347</v>
+        <v>360</v>
       </c>
       <c r="W2" s="17" t="s">
-        <v>344</v>
+        <v>357</v>
       </c>
       <c r="X2" s="18" t="s">
-        <v>348</v>
+        <v>361</v>
       </c>
       <c r="Y2" s="32" t="s">
-        <v>349</v>
+        <v>362</v>
       </c>
       <c r="Z2" s="32" t="s">
-        <v>350</v>
+        <v>363</v>
       </c>
       <c r="AA2" s="33" t="s">
-        <v>351</v>
+        <v>364</v>
       </c>
     </row>
     <row r="3" ht="14.25" spans="1:27">
@@ -3767,7 +3817,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>352</v>
+        <v>365</v>
       </c>
       <c r="C4" s="9">
         <v>10</v>
@@ -3822,17 +3872,17 @@
       <c r="U4" s="9"/>
       <c r="V4" s="9"/>
       <c r="W4" s="23"/>
-      <c r="X4" s="69" t="s">
-        <v>353</v>
+      <c r="X4" s="72" t="s">
+        <v>366</v>
       </c>
       <c r="Y4" s="9" t="s">
-        <v>354</v>
+        <v>367</v>
       </c>
       <c r="Z4" s="9" t="s">
-        <v>355</v>
+        <v>368</v>
       </c>
       <c r="AA4" s="23" t="s">
-        <v>356</v>
+        <v>369</v>
       </c>
     </row>
     <row r="5" spans="1:27">
@@ -3840,7 +3890,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>357</v>
+        <v>370</v>
       </c>
       <c r="C5" s="1">
         <v>10</v>
@@ -3896,16 +3946,16 @@
       <c r="V5" s="1"/>
       <c r="W5" s="26"/>
       <c r="X5" s="27" t="s">
-        <v>358</v>
+        <v>371</v>
       </c>
       <c r="Y5" s="1" t="s">
-        <v>354</v>
+        <v>367</v>
       </c>
       <c r="Z5" s="1" t="s">
-        <v>359</v>
+        <v>372</v>
       </c>
       <c r="AA5" s="26" t="s">
-        <v>334</v>
+        <v>347</v>
       </c>
     </row>
     <row r="6" spans="1:27">
@@ -3913,7 +3963,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>360</v>
+        <v>373</v>
       </c>
       <c r="C6" s="1">
         <v>10</v>
@@ -3969,16 +4019,16 @@
       <c r="V6" s="1"/>
       <c r="W6" s="26"/>
       <c r="X6" s="27" t="s">
-        <v>361</v>
+        <v>374</v>
       </c>
       <c r="Y6" s="1" t="s">
-        <v>354</v>
+        <v>367</v>
       </c>
       <c r="Z6" s="1" t="s">
-        <v>362</v>
+        <v>375</v>
       </c>
       <c r="AA6" s="26" t="s">
-        <v>363</v>
+        <v>376</v>
       </c>
     </row>
     <row r="7" spans="1:27">
@@ -3986,7 +4036,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>364</v>
+        <v>377</v>
       </c>
       <c r="C7" s="1">
         <v>10</v>
@@ -4042,16 +4092,16 @@
       <c r="V7" s="1"/>
       <c r="W7" s="26"/>
       <c r="X7" s="27" t="s">
-        <v>365</v>
+        <v>378</v>
       </c>
       <c r="Y7" s="1" t="s">
-        <v>354</v>
+        <v>367</v>
       </c>
       <c r="Z7" s="1" t="s">
-        <v>366</v>
+        <v>379</v>
       </c>
       <c r="AA7" s="26" t="s">
-        <v>367</v>
+        <v>380</v>
       </c>
     </row>
     <row r="8" spans="1:27">
@@ -4059,7 +4109,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>368</v>
+        <v>381</v>
       </c>
       <c r="C8" s="1">
         <v>10</v>
@@ -4115,16 +4165,16 @@
       <c r="V8" s="1"/>
       <c r="W8" s="26"/>
       <c r="X8" s="27" t="s">
-        <v>369</v>
+        <v>382</v>
       </c>
       <c r="Y8" s="1" t="s">
-        <v>354</v>
+        <v>367</v>
       </c>
       <c r="Z8" s="1" t="s">
-        <v>370</v>
+        <v>383</v>
       </c>
       <c r="AA8" s="26" t="s">
-        <v>371</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9" spans="1:27">
@@ -4132,7 +4182,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>372</v>
+        <v>385</v>
       </c>
       <c r="C9" s="1">
         <v>10</v>
@@ -4188,16 +4238,16 @@
       <c r="V9" s="1"/>
       <c r="W9" s="26"/>
       <c r="X9" s="27" t="s">
-        <v>373</v>
+        <v>386</v>
       </c>
       <c r="Y9" s="1" t="s">
-        <v>374</v>
+        <v>387</v>
       </c>
       <c r="Z9" s="1" t="s">
-        <v>375</v>
+        <v>388</v>
       </c>
       <c r="AA9" s="26" t="s">
-        <v>376</v>
+        <v>389</v>
       </c>
     </row>
     <row r="10" spans="1:27">
@@ -4205,7 +4255,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>377</v>
+        <v>390</v>
       </c>
       <c r="C10" s="1">
         <v>10</v>
@@ -4261,16 +4311,16 @@
       <c r="V10" s="1"/>
       <c r="W10" s="26"/>
       <c r="X10" s="27" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="Y10" s="1" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="Z10" s="1" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="AA10" s="26" t="s">
-        <v>381</v>
+        <v>394</v>
       </c>
     </row>
     <row r="11" spans="1:27">
@@ -4278,7 +4328,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>344</v>
+        <v>357</v>
       </c>
       <c r="C11" s="1">
         <v>10</v>
@@ -4334,16 +4384,16 @@
       <c r="V11" s="1"/>
       <c r="W11" s="26"/>
       <c r="X11" s="27" t="s">
-        <v>382</v>
+        <v>395</v>
       </c>
       <c r="Y11" s="1" t="s">
-        <v>383</v>
+        <v>396</v>
       </c>
       <c r="Z11" s="1" t="s">
-        <v>384</v>
+        <v>397</v>
       </c>
       <c r="AA11" s="26" t="s">
-        <v>385</v>
+        <v>398</v>
       </c>
     </row>
     <row r="12" spans="1:27">
@@ -4351,7 +4401,7 @@
         <v>9</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>386</v>
+        <v>399</v>
       </c>
       <c r="C12" s="1">
         <v>10</v>
@@ -4407,16 +4457,16 @@
       <c r="V12" s="1"/>
       <c r="W12" s="26"/>
       <c r="X12" s="27" t="s">
-        <v>387</v>
+        <v>400</v>
       </c>
       <c r="Y12" s="1" t="s">
-        <v>388</v>
+        <v>401</v>
       </c>
       <c r="Z12" s="1" t="s">
-        <v>389</v>
+        <v>402</v>
       </c>
       <c r="AA12" s="26" t="s">
-        <v>390</v>
+        <v>403</v>
       </c>
     </row>
     <row r="13" spans="1:27">
@@ -4424,7 +4474,7 @@
         <v>10</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>391</v>
+        <v>404</v>
       </c>
       <c r="C13" s="1">
         <v>10</v>
@@ -4480,16 +4530,16 @@
       <c r="V13" s="1"/>
       <c r="W13" s="26"/>
       <c r="X13" s="27" t="s">
-        <v>392</v>
+        <v>405</v>
       </c>
       <c r="Y13" s="1" t="s">
-        <v>383</v>
+        <v>396</v>
       </c>
       <c r="Z13" s="1" t="s">
-        <v>393</v>
+        <v>406</v>
       </c>
       <c r="AA13" s="26" t="s">
-        <v>394</v>
+        <v>407</v>
       </c>
     </row>
     <row r="14" spans="1:27">
@@ -4497,7 +4547,7 @@
         <v>11</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>395</v>
+        <v>408</v>
       </c>
       <c r="C14" s="1">
         <v>10</v>
@@ -4553,16 +4603,16 @@
       <c r="V14" s="1"/>
       <c r="W14" s="26"/>
       <c r="X14" s="27" t="s">
-        <v>396</v>
+        <v>409</v>
       </c>
       <c r="Y14" s="1" t="s">
-        <v>397</v>
+        <v>410</v>
       </c>
       <c r="Z14" s="1" t="s">
-        <v>398</v>
+        <v>411</v>
       </c>
       <c r="AA14" s="26" t="s">
-        <v>399</v>
+        <v>412</v>
       </c>
     </row>
     <row r="15" spans="1:27">
@@ -4570,7 +4620,7 @@
         <v>12</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>400</v>
+        <v>413</v>
       </c>
       <c r="C15" s="1">
         <v>10</v>
@@ -4626,16 +4676,16 @@
       <c r="V15" s="1"/>
       <c r="W15" s="26"/>
       <c r="X15" s="27" t="s">
-        <v>401</v>
+        <v>414</v>
       </c>
       <c r="Y15" s="1" t="s">
-        <v>402</v>
+        <v>415</v>
       </c>
       <c r="Z15" s="1" t="s">
-        <v>403</v>
+        <v>416</v>
       </c>
       <c r="AA15" s="26" t="s">
-        <v>356</v>
+        <v>369</v>
       </c>
     </row>
     <row r="16" spans="1:27">
@@ -4643,7 +4693,7 @@
         <v>13</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>404</v>
+        <v>417</v>
       </c>
       <c r="C16" s="1">
         <v>10</v>
@@ -4699,16 +4749,16 @@
       <c r="V16" s="1"/>
       <c r="W16" s="26"/>
       <c r="X16" s="27" t="s">
-        <v>405</v>
+        <v>418</v>
       </c>
       <c r="Y16" s="1" t="s">
-        <v>406</v>
+        <v>419</v>
       </c>
       <c r="Z16" s="1" t="s">
-        <v>407</v>
+        <v>420</v>
       </c>
       <c r="AA16" s="26" t="s">
-        <v>356</v>
+        <v>369</v>
       </c>
     </row>
     <row r="17" spans="1:27">
@@ -4716,7 +4766,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>408</v>
+        <v>421</v>
       </c>
       <c r="C17" s="1">
         <v>10</v>
@@ -4772,16 +4822,16 @@
       <c r="V17" s="1"/>
       <c r="W17" s="26"/>
       <c r="X17" s="27" t="s">
-        <v>409</v>
+        <v>422</v>
       </c>
       <c r="Y17" s="1" t="s">
-        <v>410</v>
+        <v>423</v>
       </c>
       <c r="Z17" s="1" t="s">
-        <v>411</v>
+        <v>424</v>
       </c>
       <c r="AA17" s="26" t="s">
-        <v>412</v>
+        <v>425</v>
       </c>
     </row>
     <row r="18" spans="1:27">
@@ -4789,7 +4839,7 @@
         <v>15</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>413</v>
+        <v>426</v>
       </c>
       <c r="C18" s="1">
         <v>10</v>
@@ -4845,16 +4895,16 @@
       <c r="V18" s="1"/>
       <c r="W18" s="26"/>
       <c r="X18" s="27" t="s">
-        <v>414</v>
+        <v>427</v>
       </c>
       <c r="Y18" s="1" t="s">
-        <v>415</v>
+        <v>428</v>
       </c>
       <c r="Z18" s="1" t="s">
-        <v>416</v>
+        <v>429</v>
       </c>
       <c r="AA18" s="26" t="s">
-        <v>334</v>
+        <v>347</v>
       </c>
     </row>
     <row r="19" spans="1:27">
@@ -4862,7 +4912,7 @@
         <v>16</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
       <c r="C19" s="1">
         <v>10</v>
@@ -4918,16 +4968,16 @@
       <c r="V19" s="1"/>
       <c r="W19" s="26"/>
       <c r="X19" s="27" t="s">
-        <v>418</v>
+        <v>431</v>
       </c>
       <c r="Y19" s="1" t="s">
-        <v>419</v>
+        <v>432</v>
       </c>
       <c r="Z19" s="1" t="s">
-        <v>420</v>
+        <v>433</v>
       </c>
       <c r="AA19" s="26" t="s">
-        <v>356</v>
+        <v>369</v>
       </c>
     </row>
     <row r="20" spans="1:27">
@@ -4935,7 +4985,7 @@
         <v>17</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>421</v>
+        <v>434</v>
       </c>
       <c r="C20" s="1">
         <v>10</v>
@@ -4991,16 +5041,16 @@
       <c r="V20" s="1"/>
       <c r="W20" s="26"/>
       <c r="X20" s="27" t="s">
-        <v>422</v>
+        <v>435</v>
       </c>
       <c r="Y20" s="1" t="s">
-        <v>423</v>
+        <v>436</v>
       </c>
       <c r="Z20" s="1" t="s">
-        <v>424</v>
+        <v>437</v>
       </c>
       <c r="AA20" s="26" t="s">
-        <v>333</v>
+        <v>346</v>
       </c>
     </row>
     <row r="21" spans="1:27">
@@ -5008,7 +5058,7 @@
         <v>18</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>425</v>
+        <v>438</v>
       </c>
       <c r="C21" s="1">
         <v>10</v>
@@ -5064,16 +5114,16 @@
       <c r="V21" s="1"/>
       <c r="W21" s="26"/>
       <c r="X21" s="27" t="s">
-        <v>426</v>
+        <v>439</v>
       </c>
       <c r="Y21" s="1" t="s">
-        <v>427</v>
+        <v>440</v>
       </c>
       <c r="Z21" s="1" t="s">
-        <v>428</v>
+        <v>441</v>
       </c>
       <c r="AA21" s="26" t="s">
-        <v>345</v>
+        <v>358</v>
       </c>
     </row>
     <row r="22" spans="1:27">
@@ -5081,7 +5131,7 @@
         <v>19</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>429</v>
+        <v>442</v>
       </c>
       <c r="C22" s="1">
         <v>10</v>
@@ -5137,16 +5187,16 @@
       <c r="V22" s="1"/>
       <c r="W22" s="26"/>
       <c r="X22" s="27" t="s">
-        <v>430</v>
+        <v>443</v>
       </c>
       <c r="Y22" s="1" t="s">
-        <v>431</v>
+        <v>444</v>
       </c>
       <c r="Z22" s="1" t="s">
-        <v>432</v>
+        <v>445</v>
       </c>
       <c r="AA22" s="26" t="s">
-        <v>433</v>
+        <v>446</v>
       </c>
     </row>
     <row r="23" spans="1:27">
@@ -5154,7 +5204,7 @@
         <v>20</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>434</v>
+        <v>447</v>
       </c>
       <c r="C23" s="1">
         <v>10</v>
@@ -5210,16 +5260,16 @@
       <c r="V23" s="1"/>
       <c r="W23" s="26"/>
       <c r="X23" s="27" t="s">
-        <v>435</v>
+        <v>448</v>
       </c>
       <c r="Y23" s="1" t="s">
-        <v>436</v>
+        <v>449</v>
       </c>
       <c r="Z23" s="1" t="s">
-        <v>437</v>
+        <v>450</v>
       </c>
       <c r="AA23" s="26" t="s">
-        <v>438</v>
+        <v>451</v>
       </c>
     </row>
     <row r="24" spans="1:27">
@@ -5227,7 +5277,7 @@
         <v>21</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>439</v>
+        <v>452</v>
       </c>
       <c r="C24" s="1">
         <v>10</v>
@@ -5283,16 +5333,16 @@
       <c r="V24" s="1"/>
       <c r="W24" s="26"/>
       <c r="X24" s="27" t="s">
-        <v>440</v>
+        <v>453</v>
       </c>
       <c r="Y24" s="1" t="s">
-        <v>441</v>
+        <v>454</v>
       </c>
       <c r="Z24" s="1" t="s">
-        <v>442</v>
+        <v>455</v>
       </c>
       <c r="AA24" s="26" t="s">
-        <v>443</v>
+        <v>456</v>
       </c>
     </row>
     <row r="25" spans="1:27">
@@ -5300,7 +5350,7 @@
         <v>22</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>444</v>
+        <v>457</v>
       </c>
       <c r="C25" s="1">
         <v>10</v>
@@ -5356,16 +5406,16 @@
       <c r="V25" s="1"/>
       <c r="W25" s="26"/>
       <c r="X25" s="27" t="s">
-        <v>445</v>
+        <v>458</v>
       </c>
       <c r="Y25" s="1" t="s">
-        <v>446</v>
+        <v>459</v>
       </c>
       <c r="Z25" s="1" t="s">
-        <v>447</v>
+        <v>460</v>
       </c>
       <c r="AA25" s="26" t="s">
-        <v>339</v>
+        <v>352</v>
       </c>
     </row>
     <row r="26" spans="1:27">
@@ -5373,7 +5423,7 @@
         <v>23</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>448</v>
+        <v>461</v>
       </c>
       <c r="C26" s="1">
         <v>10</v>
@@ -5429,16 +5479,16 @@
       <c r="V26" s="1"/>
       <c r="W26" s="26"/>
       <c r="X26" s="27" t="s">
-        <v>449</v>
+        <v>462</v>
       </c>
       <c r="Y26" s="1" t="s">
-        <v>450</v>
+        <v>463</v>
       </c>
       <c r="Z26" s="1" t="s">
-        <v>451</v>
+        <v>464</v>
       </c>
       <c r="AA26" s="26" t="s">
-        <v>452</v>
+        <v>465</v>
       </c>
     </row>
     <row r="27" spans="1:27">
@@ -5446,7 +5496,7 @@
         <v>24</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>453</v>
+        <v>466</v>
       </c>
       <c r="C27" s="1">
         <v>10</v>
@@ -5502,16 +5552,16 @@
       <c r="V27" s="1"/>
       <c r="W27" s="26"/>
       <c r="X27" s="27" t="s">
-        <v>454</v>
+        <v>467</v>
       </c>
       <c r="Y27" s="1" t="s">
-        <v>455</v>
+        <v>468</v>
       </c>
       <c r="Z27" s="1" t="s">
-        <v>456</v>
+        <v>469</v>
       </c>
       <c r="AA27" s="26" t="s">
-        <v>457</v>
+        <v>470</v>
       </c>
     </row>
     <row r="28" spans="1:27">
@@ -5519,7 +5569,7 @@
         <v>25</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>458</v>
+        <v>471</v>
       </c>
       <c r="C28" s="1">
         <v>10</v>
@@ -5575,16 +5625,16 @@
       <c r="V28" s="1"/>
       <c r="W28" s="26"/>
       <c r="X28" s="27" t="s">
-        <v>459</v>
+        <v>472</v>
       </c>
       <c r="Y28" s="1" t="s">
-        <v>460</v>
+        <v>473</v>
       </c>
       <c r="Z28" s="1" t="s">
-        <v>461</v>
+        <v>474</v>
       </c>
       <c r="AA28" s="26" t="s">
-        <v>462</v>
+        <v>475</v>
       </c>
     </row>
     <row r="29" spans="1:27">
@@ -5592,7 +5642,7 @@
         <v>26</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>463</v>
+        <v>476</v>
       </c>
       <c r="C29" s="1">
         <v>10</v>
@@ -5648,16 +5698,16 @@
       <c r="V29" s="1"/>
       <c r="W29" s="26"/>
       <c r="X29" s="27" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="Y29" s="1" t="s">
-        <v>465</v>
+        <v>478</v>
       </c>
       <c r="Z29" s="1" t="s">
-        <v>466</v>
+        <v>479</v>
       </c>
       <c r="AA29" s="26" t="s">
-        <v>467</v>
+        <v>480</v>
       </c>
     </row>
     <row r="30" spans="1:27">
@@ -5665,7 +5715,7 @@
         <v>27</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>468</v>
+        <v>481</v>
       </c>
       <c r="C30" s="1">
         <v>10</v>
@@ -5721,16 +5771,16 @@
       <c r="V30" s="1"/>
       <c r="W30" s="26"/>
       <c r="X30" s="27" t="s">
-        <v>469</v>
+        <v>482</v>
       </c>
       <c r="Y30" s="1" t="s">
-        <v>470</v>
+        <v>483</v>
       </c>
       <c r="Z30" s="1" t="s">
-        <v>471</v>
+        <v>484</v>
       </c>
       <c r="AA30" s="26" t="s">
-        <v>356</v>
+        <v>369</v>
       </c>
     </row>
     <row r="31" spans="1:27">
@@ -5738,7 +5788,7 @@
         <v>28</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>472</v>
+        <v>485</v>
       </c>
       <c r="C31" s="1">
         <v>10</v>
@@ -5794,16 +5844,16 @@
       <c r="V31" s="1"/>
       <c r="W31" s="26"/>
       <c r="X31" s="27" t="s">
-        <v>473</v>
+        <v>486</v>
       </c>
       <c r="Y31" s="1" t="s">
-        <v>474</v>
+        <v>487</v>
       </c>
       <c r="Z31" s="1" t="s">
-        <v>475</v>
+        <v>488</v>
       </c>
       <c r="AA31" s="26" t="s">
-        <v>356</v>
+        <v>369</v>
       </c>
     </row>
     <row r="32" spans="1:27">
@@ -5811,7 +5861,7 @@
         <v>29</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>476</v>
+        <v>489</v>
       </c>
       <c r="C32" s="1">
         <v>10</v>
@@ -5867,16 +5917,16 @@
       <c r="V32" s="1"/>
       <c r="W32" s="26"/>
       <c r="X32" s="27" t="s">
-        <v>477</v>
+        <v>490</v>
       </c>
       <c r="Y32" s="1" t="s">
-        <v>478</v>
+        <v>491</v>
       </c>
       <c r="Z32" s="1" t="s">
-        <v>479</v>
+        <v>492</v>
       </c>
       <c r="AA32" s="26" t="s">
-        <v>480</v>
+        <v>493</v>
       </c>
     </row>
     <row r="33" spans="1:27">
@@ -5884,7 +5934,7 @@
         <v>30</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>481</v>
+        <v>494</v>
       </c>
       <c r="C33" s="1">
         <v>10</v>
@@ -5940,16 +5990,16 @@
       <c r="V33" s="1"/>
       <c r="W33" s="26"/>
       <c r="X33" s="27" t="s">
-        <v>482</v>
+        <v>495</v>
       </c>
       <c r="Y33" s="1" t="s">
-        <v>483</v>
+        <v>496</v>
       </c>
       <c r="Z33" s="1" t="s">
-        <v>484</v>
+        <v>497</v>
       </c>
       <c r="AA33" s="26" t="s">
-        <v>485</v>
+        <v>498</v>
       </c>
     </row>
     <row r="34" spans="1:27">
@@ -5957,7 +6007,7 @@
         <v>31</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>486</v>
+        <v>499</v>
       </c>
       <c r="C34" s="1">
         <v>10</v>
@@ -6013,16 +6063,16 @@
       <c r="V34" s="1"/>
       <c r="W34" s="26"/>
       <c r="X34" s="27" t="s">
-        <v>487</v>
+        <v>500</v>
       </c>
       <c r="Y34" s="1" t="s">
-        <v>488</v>
+        <v>501</v>
       </c>
       <c r="Z34" s="1" t="s">
-        <v>489</v>
+        <v>502</v>
       </c>
       <c r="AA34" s="26" t="s">
-        <v>356</v>
+        <v>369</v>
       </c>
     </row>
     <row r="35" spans="1:27">
@@ -6030,7 +6080,7 @@
         <v>32</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>490</v>
+        <v>503</v>
       </c>
       <c r="C35" s="1">
         <v>10</v>
@@ -6086,16 +6136,16 @@
       <c r="V35" s="1"/>
       <c r="W35" s="26"/>
       <c r="X35" s="27" t="s">
-        <v>491</v>
+        <v>504</v>
       </c>
       <c r="Y35" s="1" t="s">
-        <v>492</v>
+        <v>505</v>
       </c>
       <c r="Z35" s="1" t="s">
-        <v>493</v>
+        <v>506</v>
       </c>
       <c r="AA35" s="26" t="s">
-        <v>494</v>
+        <v>507</v>
       </c>
     </row>
     <row r="36" spans="1:27">
@@ -6103,7 +6153,7 @@
         <v>33</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>495</v>
+        <v>508</v>
       </c>
       <c r="C36" s="1">
         <v>10</v>
@@ -6159,16 +6209,16 @@
       <c r="V36" s="1"/>
       <c r="W36" s="26"/>
       <c r="X36" s="27" t="s">
-        <v>496</v>
+        <v>509</v>
       </c>
       <c r="Y36" s="1" t="s">
-        <v>497</v>
+        <v>510</v>
       </c>
       <c r="Z36" s="1" t="s">
-        <v>498</v>
+        <v>511</v>
       </c>
       <c r="AA36" s="26" t="s">
-        <v>499</v>
+        <v>512</v>
       </c>
     </row>
     <row r="37" spans="1:27">
@@ -6176,7 +6226,7 @@
         <v>34</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>500</v>
+        <v>513</v>
       </c>
       <c r="C37" s="1">
         <v>10</v>
@@ -6232,16 +6282,16 @@
       <c r="V37" s="1"/>
       <c r="W37" s="26"/>
       <c r="X37" s="27" t="s">
-        <v>501</v>
+        <v>514</v>
       </c>
       <c r="Y37" s="1" t="s">
-        <v>502</v>
+        <v>515</v>
       </c>
       <c r="Z37" s="1" t="s">
-        <v>503</v>
+        <v>516</v>
       </c>
       <c r="AA37" s="26" t="s">
-        <v>504</v>
+        <v>517</v>
       </c>
     </row>
     <row r="38" spans="1:27">
@@ -6249,7 +6299,7 @@
         <v>35</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>505</v>
+        <v>518</v>
       </c>
       <c r="C38" s="1">
         <v>10</v>
@@ -6305,16 +6355,16 @@
       <c r="V38" s="1"/>
       <c r="W38" s="26"/>
       <c r="X38" s="27" t="s">
-        <v>506</v>
+        <v>519</v>
       </c>
       <c r="Y38" s="1" t="s">
-        <v>507</v>
+        <v>520</v>
       </c>
       <c r="Z38" s="1" t="s">
-        <v>508</v>
+        <v>521</v>
       </c>
       <c r="AA38" s="26" t="s">
-        <v>509</v>
+        <v>522</v>
       </c>
     </row>
     <row r="39" spans="1:27">
@@ -6322,7 +6372,7 @@
         <v>36</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>510</v>
+        <v>523</v>
       </c>
       <c r="C39" s="1">
         <v>10</v>
@@ -6378,16 +6428,16 @@
       <c r="V39" s="1"/>
       <c r="W39" s="26"/>
       <c r="X39" s="27" t="s">
-        <v>511</v>
+        <v>524</v>
       </c>
       <c r="Y39" s="1" t="s">
-        <v>512</v>
+        <v>525</v>
       </c>
       <c r="Z39" s="1" t="s">
-        <v>513</v>
+        <v>526</v>
       </c>
       <c r="AA39" s="26" t="s">
-        <v>514</v>
+        <v>527</v>
       </c>
     </row>
     <row r="40" spans="1:27">
@@ -6395,7 +6445,7 @@
         <v>37</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>515</v>
+        <v>528</v>
       </c>
       <c r="C40" s="1">
         <v>10</v>
@@ -6451,16 +6501,16 @@
       <c r="V40" s="1"/>
       <c r="W40" s="26"/>
       <c r="X40" s="27" t="s">
-        <v>516</v>
+        <v>529</v>
       </c>
       <c r="Y40" s="1" t="s">
-        <v>517</v>
+        <v>530</v>
       </c>
       <c r="Z40" s="1" t="s">
-        <v>518</v>
+        <v>531</v>
       </c>
       <c r="AA40" s="26" t="s">
-        <v>341</v>
+        <v>354</v>
       </c>
     </row>
     <row r="41" ht="14.25" spans="1:27">
@@ -6468,7 +6518,7 @@
         <v>38</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>519</v>
+        <v>532</v>
       </c>
       <c r="C41" s="12">
         <v>10</v>
@@ -6524,16 +6574,16 @@
       <c r="V41" s="12"/>
       <c r="W41" s="29"/>
       <c r="X41" s="30" t="s">
-        <v>520</v>
+        <v>533</v>
       </c>
       <c r="Y41" s="12" t="s">
-        <v>521</v>
+        <v>534</v>
       </c>
       <c r="Z41" s="12" t="s">
-        <v>522</v>
+        <v>535</v>
       </c>
       <c r="AA41" s="29" t="s">
-        <v>356</v>
+        <v>369</v>
       </c>
     </row>
   </sheetData>
@@ -6597,7 +6647,7 @@
         <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>523</v>
+        <v>536</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -6605,7 +6655,7 @@
         <v>2</v>
       </c>
       <c r="B13" t="s">
-        <v>524</v>
+        <v>537</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -6613,7 +6663,7 @@
         <v>3</v>
       </c>
       <c r="B14" t="s">
-        <v>525</v>
+        <v>538</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -6621,16 +6671,16 @@
         <v>4</v>
       </c>
       <c r="B15" t="s">
-        <v>526</v>
+        <v>539</v>
       </c>
       <c r="F15" t="s">
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="H15" t="s">
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="I15" t="s">
-        <v>527</v>
+        <v>540</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -6638,16 +6688,16 @@
         <v>5</v>
       </c>
       <c r="B16" t="s">
-        <v>528</v>
+        <v>541</v>
       </c>
       <c r="F16" t="s">
-        <v>527</v>
+        <v>540</v>
       </c>
       <c r="H16" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="I16" t="s">
-        <v>529</v>
+        <v>542</v>
       </c>
     </row>
     <row r="17" spans="6:9">
@@ -6655,35 +6705,35 @@
         <v>51</v>
       </c>
       <c r="H17" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="I17" t="s">
-        <v>530</v>
+        <v>543</v>
       </c>
     </row>
     <row r="18" spans="2:9">
       <c r="B18" t="s">
-        <v>531</v>
+        <v>544</v>
       </c>
       <c r="F18" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="H18" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="I18" t="s">
-        <v>532</v>
+        <v>545</v>
       </c>
     </row>
     <row r="19" spans="6:9">
       <c r="F19" t="s">
-        <v>529</v>
+        <v>542</v>
       </c>
       <c r="H19" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="I19" t="s">
-        <v>533</v>
+        <v>546</v>
       </c>
     </row>
     <row r="20" spans="6:8">
@@ -6697,7 +6747,7 @@
     </row>
     <row r="21" spans="6:8">
       <c r="F21" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="H21">
         <f>IF('intent|意图'!F21='intent|意图'!F20,H20&amp;"*"&amp;'intent|意图'!D21,'intent|意图'!D21)</f>
@@ -6706,7 +6756,7 @@
     </row>
     <row r="22" spans="6:8">
       <c r="F22" t="s">
-        <v>530</v>
+        <v>543</v>
       </c>
       <c r="H22">
         <f>IF('intent|意图'!F22='intent|意图'!F21,H21&amp;"*"&amp;'intent|意图'!D22,'intent|意图'!D22)</f>
@@ -6724,7 +6774,7 @@
     </row>
     <row r="24" spans="6:8">
       <c r="F24" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="H24">
         <f>IF('intent|意图'!F15='intent|意图'!F23,H23&amp;"*"&amp;'intent|意图'!D15,'intent|意图'!D15)</f>
@@ -6733,7 +6783,7 @@
     </row>
     <row r="25" spans="6:8">
       <c r="F25" t="s">
-        <v>532</v>
+        <v>545</v>
       </c>
       <c r="H25">
         <f>IF('intent|意图'!F16='intent|意图'!F15,H24&amp;"*"&amp;'intent|意图'!D16,'intent|意图'!D16)</f>
@@ -6751,7 +6801,7 @@
     </row>
     <row r="27" spans="6:8">
       <c r="F27" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="H27">
         <f>IF('intent|意图'!F24='intent|意图'!F17,H26&amp;"*"&amp;'intent|意图'!D24,'intent|意图'!D24)</f>
@@ -6760,7 +6810,7 @@
     </row>
     <row r="28" spans="6:8">
       <c r="F28" t="s">
-        <v>533</v>
+        <v>546</v>
       </c>
       <c r="H28">
         <f>IF('intent|意图'!F25='intent|意图'!F24,H27&amp;"*"&amp;'intent|意图'!D25,'intent|意图'!D25)</f>
@@ -6778,32 +6828,32 @@
     </row>
     <row r="30" spans="2:2">
       <c r="B30" t="s">
-        <v>531</v>
+        <v>544</v>
       </c>
     </row>
     <row r="42" spans="2:2">
       <c r="B42" t="s">
-        <v>531</v>
+        <v>544</v>
       </c>
     </row>
     <row r="50" spans="2:2">
       <c r="B50" t="s">
-        <v>534</v>
+        <v>547</v>
       </c>
     </row>
     <row r="54" spans="2:2">
       <c r="B54" t="s">
-        <v>531</v>
+        <v>544</v>
       </c>
     </row>
     <row r="62" spans="2:2">
       <c r="B62" t="s">
-        <v>534</v>
+        <v>547</v>
       </c>
     </row>
     <row r="66" spans="2:2">
       <c r="B66" t="s">
-        <v>531</v>
+        <v>544</v>
       </c>
     </row>
   </sheetData>
@@ -6896,7 +6946,7 @@
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultColWidth="8.86666666666667" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="8.33333333333333" style="68" customWidth="1"/>
+    <col min="1" max="1" width="8.33333333333333" style="71" customWidth="1"/>
     <col min="2" max="2" width="11.8666666666667" customWidth="1"/>
     <col min="3" max="3" width="31.4666666666667" customWidth="1"/>
   </cols>
@@ -6914,7 +6964,7 @@
       <c r="D1" s="5"/>
       <c r="E1" s="5"/>
     </row>
-    <row r="2" s="67" customFormat="1" spans="1:5">
+    <row r="2" s="70" customFormat="1" spans="1:5">
       <c r="A2" s="43" t="s">
         <v>5</v>
       </c>
@@ -7180,7 +7230,7 @@
       <c r="H2" s="43" t="s">
         <v>71</v>
       </c>
-      <c r="I2" s="66" t="s">
+      <c r="I2" s="57" t="s">
         <v>72</v>
       </c>
       <c r="J2" s="21" t="s">
@@ -7276,7 +7326,7 @@
       <c r="I5" s="40" t="s">
         <v>85</v>
       </c>
-      <c r="J5" s="65" t="s">
+      <c r="J5" s="1" t="s">
         <v>86</v>
       </c>
     </row>
@@ -7308,7 +7358,7 @@
       <c r="I6" s="40" t="s">
         <v>91</v>
       </c>
-      <c r="J6" s="65" t="s">
+      <c r="J6" s="1" t="s">
         <v>92</v>
       </c>
     </row>
@@ -7321,103 +7371,726 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="2"/>
+  <dimension ref="A1:J26"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="11.5" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="1" max="1" width="21.25" customWidth="1"/>
+    <col min="2" max="2" width="9.06666666666667" style="63"/>
+    <col min="4" max="6" width="9.06666666666667" style="63"/>
+    <col min="7" max="7" width="62" customWidth="1"/>
+    <col min="8" max="8" width="67.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:10">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="64" t="s">
+        <v>93</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="64" t="s">
+      <c r="D1" s="64" t="s">
+        <v>94</v>
+      </c>
+      <c r="E1" s="64" t="s">
+        <v>95</v>
+      </c>
+      <c r="F1" s="64" t="s">
+        <v>96</v>
+      </c>
+      <c r="G1" s="56" t="s">
+        <v>97</v>
+      </c>
+      <c r="H1" s="56" t="s">
+        <v>60</v>
+      </c>
+      <c r="I1" s="56" t="s">
+        <v>98</v>
+      </c>
+      <c r="J1" s="56" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="64" t="s">
+        <v>100</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="D2" s="64" t="s">
+        <v>102</v>
+      </c>
+      <c r="E2" s="64" t="s">
+        <v>103</v>
+      </c>
+      <c r="F2" s="64" t="s">
+        <v>104</v>
+      </c>
+      <c r="G2" s="56" t="s">
+        <v>105</v>
+      </c>
+      <c r="H2" s="56" t="s">
+        <v>106</v>
+      </c>
+      <c r="I2" s="56" t="s">
+        <v>107</v>
+      </c>
+      <c r="J2" s="56" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="64" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="64" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="64" t="s">
+        <v>109</v>
+      </c>
+      <c r="F3" s="64" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="56" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="56" t="s">
+        <v>74</v>
+      </c>
+      <c r="I3" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="J3" s="56" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B4" s="65"/>
+      <c r="C4" s="40" t="s">
+        <v>111</v>
+      </c>
+      <c r="D4" s="65">
+        <v>1</v>
+      </c>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="40" t="s">
+        <v>112</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="I4" s="1">
+        <v>8</v>
+      </c>
+      <c r="J4" s="1"/>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B5" s="65"/>
+      <c r="C5" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D5" s="65">
+        <v>2</v>
+      </c>
+      <c r="E5" s="65"/>
+      <c r="F5" s="65"/>
+      <c r="G5" s="40" t="s">
+        <v>116</v>
+      </c>
+      <c r="H5" s="40" t="s">
+        <v>117</v>
+      </c>
+      <c r="I5" s="1">
+        <v>3</v>
+      </c>
+      <c r="J5" s="1"/>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B6" s="65"/>
+      <c r="C6" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D6" s="65">
+        <v>3</v>
+      </c>
+      <c r="E6" s="65"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="40" t="s">
+        <v>119</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="I6" s="1">
+        <v>0</v>
+      </c>
+      <c r="J6" s="1"/>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B7" s="65"/>
+      <c r="C7" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D7" s="65">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="43" t="s">
+      <c r="E7" s="65"/>
+      <c r="F7" s="65"/>
+      <c r="G7" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="I7" s="1">
+        <v>0</v>
+      </c>
+      <c r="J7" s="1"/>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B8" s="65"/>
+      <c r="C8" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D8" s="65">
         <v>5</v>
       </c>
-      <c r="B2" s="43" t="s">
-        <v>93</v>
-      </c>
-      <c r="C2" s="64" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="64" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="65" t="s">
-        <v>86</v>
-      </c>
-      <c r="B4" s="65" t="s">
-        <v>94</v>
-      </c>
-      <c r="C4" s="65" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="65" t="s">
-        <v>92</v>
-      </c>
-      <c r="B5" s="65" t="s">
-        <v>96</v>
-      </c>
-      <c r="C5" s="65" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="65" t="s">
-        <v>98</v>
-      </c>
-      <c r="B6" s="65" t="s">
-        <v>99</v>
-      </c>
-      <c r="C6" s="65" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="65" t="s">
-        <v>101</v>
-      </c>
-      <c r="B7" s="65" t="s">
-        <v>102</v>
-      </c>
-      <c r="C7" s="65" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="65" t="s">
-        <v>104</v>
-      </c>
-      <c r="B8" s="65" t="s">
-        <v>105</v>
-      </c>
-      <c r="C8" s="65" t="s">
-        <v>106</v>
-      </c>
+      <c r="E8" s="65"/>
+      <c r="F8" s="65"/>
+      <c r="G8" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="I8" s="1">
+        <v>0</v>
+      </c>
+      <c r="J8" s="1"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B9" s="65"/>
+      <c r="C9" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="D9" s="65">
+        <v>6</v>
+      </c>
+      <c r="E9" s="65"/>
+      <c r="F9" s="65"/>
+      <c r="G9" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="I9" s="1">
+        <v>0</v>
+      </c>
+      <c r="J9" s="1"/>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B10" s="65"/>
+      <c r="C10" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="D10" s="65">
+        <v>7</v>
+      </c>
+      <c r="E10" s="65"/>
+      <c r="F10" s="65"/>
+      <c r="G10" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="I10" s="1">
+        <v>0</v>
+      </c>
+      <c r="J10" s="1"/>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B11" s="65"/>
+      <c r="C11" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D11" s="65">
+        <v>8</v>
+      </c>
+      <c r="E11" s="65"/>
+      <c r="F11" s="65"/>
+      <c r="G11" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="I11" s="1">
+        <v>0</v>
+      </c>
+      <c r="J11" s="1"/>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="46" t="s">
+        <v>141</v>
+      </c>
+      <c r="B12" s="47" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" s="47" t="s">
+        <v>142</v>
+      </c>
+      <c r="D12" s="66"/>
+      <c r="E12" s="66">
+        <v>1</v>
+      </c>
+      <c r="F12" s="66">
+        <v>0</v>
+      </c>
+      <c r="G12" s="47" t="s">
+        <v>143</v>
+      </c>
+      <c r="H12" s="47" t="s">
+        <v>144</v>
+      </c>
+      <c r="I12" s="47">
+        <v>0</v>
+      </c>
+      <c r="J12" s="49"/>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="48" t="s">
+        <v>145</v>
+      </c>
+      <c r="B13" s="49" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="49" t="s">
+        <v>146</v>
+      </c>
+      <c r="D13" s="67"/>
+      <c r="E13" s="67">
+        <v>1</v>
+      </c>
+      <c r="F13" s="67">
+        <v>1</v>
+      </c>
+      <c r="G13" s="49" t="s">
+        <v>147</v>
+      </c>
+      <c r="H13" s="49" t="s">
+        <v>148</v>
+      </c>
+      <c r="I13" s="49">
+        <v>0</v>
+      </c>
+      <c r="J13" s="49"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="48" t="s">
+        <v>149</v>
+      </c>
+      <c r="B14" s="49" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="49" t="s">
+        <v>150</v>
+      </c>
+      <c r="D14" s="67"/>
+      <c r="E14" s="67">
+        <v>1</v>
+      </c>
+      <c r="F14" s="67">
+        <v>3</v>
+      </c>
+      <c r="G14" s="49" t="s">
+        <v>151</v>
+      </c>
+      <c r="H14" s="49" t="s">
+        <v>117</v>
+      </c>
+      <c r="I14" s="49">
+        <v>0</v>
+      </c>
+      <c r="J14" s="49"/>
+    </row>
+    <row r="15" s="42" customFormat="1" spans="1:10">
+      <c r="A15" s="50" t="s">
+        <v>152</v>
+      </c>
+      <c r="B15" s="51" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" s="51" t="s">
+        <v>153</v>
+      </c>
+      <c r="D15" s="68"/>
+      <c r="E15" s="68">
+        <v>1</v>
+      </c>
+      <c r="F15" s="68">
+        <v>0</v>
+      </c>
+      <c r="G15" s="51" t="s">
+        <v>154</v>
+      </c>
+      <c r="H15" s="51" t="s">
+        <v>155</v>
+      </c>
+      <c r="I15" s="51">
+        <v>0</v>
+      </c>
+      <c r="J15" s="51"/>
+    </row>
+    <row r="16" s="42" customFormat="1" spans="1:10">
+      <c r="A16" s="50" t="s">
+        <v>156</v>
+      </c>
+      <c r="B16" s="51" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" s="51" t="s">
+        <v>157</v>
+      </c>
+      <c r="D16" s="68"/>
+      <c r="E16" s="68">
+        <v>1</v>
+      </c>
+      <c r="F16" s="68">
+        <v>1</v>
+      </c>
+      <c r="G16" s="51" t="s">
+        <v>158</v>
+      </c>
+      <c r="H16" s="51" t="s">
+        <v>132</v>
+      </c>
+      <c r="I16" s="51">
+        <v>0</v>
+      </c>
+      <c r="J16" s="51"/>
+    </row>
+    <row r="17" s="42" customFormat="1" spans="1:10">
+      <c r="A17" s="50" t="s">
+        <v>159</v>
+      </c>
+      <c r="B17" s="51" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" s="51" t="s">
+        <v>160</v>
+      </c>
+      <c r="D17" s="68"/>
+      <c r="E17" s="68">
+        <v>1</v>
+      </c>
+      <c r="F17" s="68">
+        <v>3</v>
+      </c>
+      <c r="G17" s="51" t="s">
+        <v>161</v>
+      </c>
+      <c r="H17" s="51" t="s">
+        <v>136</v>
+      </c>
+      <c r="I17" s="51">
+        <v>0</v>
+      </c>
+      <c r="J17" s="51"/>
+    </row>
+    <row r="18" s="62" customFormat="1" spans="1:10">
+      <c r="A18" s="52" t="s">
+        <v>162</v>
+      </c>
+      <c r="B18" s="53" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" s="53" t="s">
+        <v>163</v>
+      </c>
+      <c r="D18" s="69"/>
+      <c r="E18" s="69">
+        <v>1</v>
+      </c>
+      <c r="F18" s="69">
+        <v>0</v>
+      </c>
+      <c r="G18" s="53" t="s">
+        <v>164</v>
+      </c>
+      <c r="H18" s="53" t="s">
+        <v>140</v>
+      </c>
+      <c r="I18" s="53">
+        <v>0</v>
+      </c>
+      <c r="J18" s="53"/>
+    </row>
+    <row r="19" s="62" customFormat="1" spans="1:10">
+      <c r="A19" s="52" t="s">
+        <v>165</v>
+      </c>
+      <c r="B19" s="53" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" s="53" t="s">
+        <v>166</v>
+      </c>
+      <c r="D19" s="69"/>
+      <c r="E19" s="69">
+        <v>1</v>
+      </c>
+      <c r="F19" s="69">
+        <v>1</v>
+      </c>
+      <c r="G19" s="53" t="s">
+        <v>167</v>
+      </c>
+      <c r="H19" s="53" t="s">
+        <v>140</v>
+      </c>
+      <c r="I19" s="53">
+        <v>0</v>
+      </c>
+      <c r="J19" s="53"/>
+    </row>
+    <row r="20" s="62" customFormat="1" spans="1:10">
+      <c r="A20" s="52" t="s">
+        <v>168</v>
+      </c>
+      <c r="B20" s="53" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" s="53" t="s">
+        <v>169</v>
+      </c>
+      <c r="D20" s="69"/>
+      <c r="E20" s="69">
+        <v>1</v>
+      </c>
+      <c r="F20" s="69">
+        <v>3</v>
+      </c>
+      <c r="G20" s="53" t="s">
+        <v>170</v>
+      </c>
+      <c r="H20" s="53" t="s">
+        <v>140</v>
+      </c>
+      <c r="I20" s="53">
+        <v>0</v>
+      </c>
+      <c r="J20" s="53"/>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="48" t="s">
+        <v>171</v>
+      </c>
+      <c r="B21" s="49" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="49" t="s">
+        <v>172</v>
+      </c>
+      <c r="D21" s="67"/>
+      <c r="E21" s="67">
+        <v>1</v>
+      </c>
+      <c r="F21" s="67">
+        <v>0</v>
+      </c>
+      <c r="G21" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="H21" s="49" t="s">
+        <v>140</v>
+      </c>
+      <c r="I21" s="49">
+        <v>0</v>
+      </c>
+      <c r="J21" s="49"/>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="48" t="s">
+        <v>174</v>
+      </c>
+      <c r="B22" s="49" t="s">
+        <v>20</v>
+      </c>
+      <c r="C22" s="49" t="s">
+        <v>175</v>
+      </c>
+      <c r="D22" s="67"/>
+      <c r="E22" s="67">
+        <v>1</v>
+      </c>
+      <c r="F22" s="67">
+        <v>1</v>
+      </c>
+      <c r="G22" s="49" t="s">
+        <v>176</v>
+      </c>
+      <c r="H22" s="49" t="s">
+        <v>140</v>
+      </c>
+      <c r="I22" s="49">
+        <v>0</v>
+      </c>
+      <c r="J22" s="49"/>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="48" t="s">
+        <v>177</v>
+      </c>
+      <c r="B23" s="49" t="s">
+        <v>20</v>
+      </c>
+      <c r="C23" s="49" t="s">
+        <v>178</v>
+      </c>
+      <c r="D23" s="67"/>
+      <c r="E23" s="67">
+        <v>1</v>
+      </c>
+      <c r="F23" s="67">
+        <v>3</v>
+      </c>
+      <c r="G23" s="49" t="s">
+        <v>179</v>
+      </c>
+      <c r="H23" s="49" t="s">
+        <v>140</v>
+      </c>
+      <c r="I23" s="49">
+        <v>0</v>
+      </c>
+      <c r="J23" s="49"/>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="48" t="s">
+        <v>180</v>
+      </c>
+      <c r="B24" s="49" t="s">
+        <v>26</v>
+      </c>
+      <c r="C24" s="49" t="s">
+        <v>181</v>
+      </c>
+      <c r="D24" s="67"/>
+      <c r="E24" s="67">
+        <v>1</v>
+      </c>
+      <c r="F24" s="67">
+        <v>0</v>
+      </c>
+      <c r="G24" s="49" t="s">
+        <v>182</v>
+      </c>
+      <c r="H24" s="49" t="s">
+        <v>140</v>
+      </c>
+      <c r="I24" s="49">
+        <v>0</v>
+      </c>
+      <c r="J24" s="49"/>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="48" t="s">
+        <v>183</v>
+      </c>
+      <c r="B25" s="49" t="s">
+        <v>26</v>
+      </c>
+      <c r="C25" s="49" t="s">
+        <v>184</v>
+      </c>
+      <c r="D25" s="67"/>
+      <c r="E25" s="67">
+        <v>1</v>
+      </c>
+      <c r="F25" s="67">
+        <v>1</v>
+      </c>
+      <c r="G25" s="53" t="s">
+        <v>170</v>
+      </c>
+      <c r="H25" s="49" t="s">
+        <v>140</v>
+      </c>
+      <c r="I25" s="49">
+        <v>0</v>
+      </c>
+      <c r="J25" s="49"/>
+    </row>
+    <row r="26" s="41" customFormat="1" spans="1:10">
+      <c r="A26" s="46" t="s">
+        <v>185</v>
+      </c>
+      <c r="B26" s="47" t="s">
+        <v>26</v>
+      </c>
+      <c r="C26" s="47" t="s">
+        <v>186</v>
+      </c>
+      <c r="D26" s="66"/>
+      <c r="E26" s="66">
+        <v>1</v>
+      </c>
+      <c r="F26" s="66">
+        <v>3</v>
+      </c>
+      <c r="G26" s="47" t="s">
+        <v>187</v>
+      </c>
+      <c r="H26" s="47" t="s">
+        <v>140</v>
+      </c>
+      <c r="I26" s="47">
+        <v>0</v>
+      </c>
+      <c r="J26" s="47"/>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
 </file>
@@ -7425,726 +8098,256 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:F26"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="21.25" customWidth="1"/>
-    <col min="2" max="2" width="9.06666666666667" style="56"/>
-    <col min="4" max="6" width="9.06666666666667" style="56"/>
-    <col min="7" max="7" width="62" customWidth="1"/>
-    <col min="8" max="8" width="67.125" customWidth="1"/>
+    <col min="1" max="1" width="11.5" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="11.875" customWidth="1"/>
+    <col min="5" max="5" width="10.375" customWidth="1"/>
+    <col min="6" max="6" width="67.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:6">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="57" t="s">
-        <v>107</v>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="57" t="s">
-        <v>108</v>
-      </c>
-      <c r="E1" s="57" t="s">
-        <v>109</v>
-      </c>
-      <c r="F1" s="57" t="s">
-        <v>110</v>
-      </c>
-      <c r="G1" s="58" t="s">
-        <v>111</v>
-      </c>
-      <c r="H1" s="58" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="E1" s="55" t="s">
+        <v>188</v>
+      </c>
+      <c r="F1" s="56" t="s">
         <v>60</v>
       </c>
-      <c r="I1" s="58" t="s">
-        <v>112</v>
-      </c>
-      <c r="J1" s="58" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="57" t="s">
-        <v>114</v>
+    </row>
+    <row r="2" ht="40.5" spans="1:6">
+      <c r="A2" s="43" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="43" t="s">
+        <v>189</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>115</v>
+        <v>9</v>
       </c>
       <c r="D2" s="57" t="s">
-        <v>116</v>
-      </c>
-      <c r="E2" s="57" t="s">
-        <v>117</v>
-      </c>
-      <c r="F2" s="57" t="s">
-        <v>118</v>
-      </c>
-      <c r="G2" s="58" t="s">
-        <v>119</v>
-      </c>
-      <c r="H2" s="58" t="s">
-        <v>120</v>
-      </c>
-      <c r="I2" s="58" t="s">
-        <v>121</v>
-      </c>
-      <c r="J2" s="58" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
+        <v>72</v>
+      </c>
+      <c r="E2" s="58" t="s">
+        <v>190</v>
+      </c>
+      <c r="F2" s="56" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="57" t="s">
+      <c r="B3" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="57" t="s">
+      <c r="D3" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E3" s="55" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="57" t="s">
-        <v>123</v>
-      </c>
-      <c r="F3" s="57" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" s="58" t="s">
-        <v>10</v>
-      </c>
-      <c r="H3" s="58" t="s">
+      <c r="F3" s="56" t="s">
         <v>74</v>
       </c>
-      <c r="I3" s="58" t="s">
-        <v>11</v>
-      </c>
-      <c r="J3" s="58" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="B4" s="59"/>
-      <c r="C4" s="40" t="s">
-        <v>125</v>
-      </c>
-      <c r="D4" s="59">
-        <v>1</v>
-      </c>
-      <c r="E4" s="59"/>
-      <c r="F4" s="59"/>
-      <c r="G4" s="40" t="s">
-        <v>126</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="I4" s="1">
-        <v>8</v>
-      </c>
-      <c r="J4" s="1"/>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B5" s="59"/>
-      <c r="C5" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="D5" s="59">
+    </row>
+    <row r="4" s="54" customFormat="1" spans="1:6">
+      <c r="A4" s="59" t="s">
+        <v>86</v>
+      </c>
+      <c r="B4" s="59" t="s">
+        <v>192</v>
+      </c>
+      <c r="C4" s="59" t="s">
+        <v>193</v>
+      </c>
+      <c r="D4" s="60"/>
+      <c r="E4" s="60">
         <v>2</v>
       </c>
-      <c r="E5" s="59"/>
-      <c r="F5" s="59"/>
-      <c r="G5" s="40" t="s">
-        <v>130</v>
-      </c>
-      <c r="H5" s="40" t="s">
-        <v>131</v>
-      </c>
-      <c r="I5" s="1">
-        <v>3</v>
-      </c>
-      <c r="J5" s="1"/>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="B6" s="59"/>
-      <c r="C6" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="D6" s="59">
-        <v>3</v>
-      </c>
-      <c r="E6" s="59"/>
-      <c r="F6" s="59"/>
-      <c r="G6" s="40" t="s">
-        <v>133</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="I6" s="1">
-        <v>0</v>
-      </c>
-      <c r="J6" s="1"/>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="B7" s="59"/>
-      <c r="C7" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="D7" s="59">
-        <v>4</v>
-      </c>
-      <c r="E7" s="59"/>
-      <c r="F7" s="59"/>
-      <c r="G7" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="I7" s="1">
-        <v>0</v>
-      </c>
-      <c r="J7" s="1"/>
-    </row>
-    <row r="8" spans="1:10">
+      <c r="F4" s="1" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="5" s="54" customFormat="1" spans="1:6">
+      <c r="A5" s="60" t="s">
+        <v>195</v>
+      </c>
+      <c r="B5" s="60" t="s">
+        <v>196</v>
+      </c>
+      <c r="C5" s="60" t="s">
+        <v>197</v>
+      </c>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
+      <c r="F5" s="40"/>
+    </row>
+    <row r="6" s="54" customFormat="1" spans="1:6">
+      <c r="A6" s="60" t="s">
+        <v>198</v>
+      </c>
+      <c r="B6" s="60" t="s">
+        <v>199</v>
+      </c>
+      <c r="C6" s="60" t="s">
+        <v>200</v>
+      </c>
+      <c r="D6" s="60"/>
+      <c r="E6" s="60"/>
+      <c r="F6" s="1"/>
+    </row>
+    <row r="7" s="54" customFormat="1" spans="1:6">
+      <c r="A7" s="60" t="s">
+        <v>201</v>
+      </c>
+      <c r="B7" s="60" t="s">
+        <v>202</v>
+      </c>
+      <c r="C7" s="60" t="s">
+        <v>203</v>
+      </c>
+      <c r="D7" s="60"/>
+      <c r="E7" s="60"/>
+      <c r="F7" s="1"/>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="B8" s="59"/>
+        <v>92</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>204</v>
+      </c>
       <c r="C8" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="D8" s="59">
-        <v>5</v>
-      </c>
-      <c r="E8" s="59"/>
-      <c r="F8" s="59"/>
-      <c r="G8" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="I8" s="1">
-        <v>0</v>
-      </c>
-      <c r="J8" s="1"/>
-    </row>
-    <row r="9" spans="1:10">
+        <v>205</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="E8" s="61">
+        <v>2</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="B9" s="59"/>
+        <v>208</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>209</v>
+      </c>
       <c r="C9" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="D9" s="59">
-        <v>6</v>
-      </c>
-      <c r="E9" s="59"/>
-      <c r="F9" s="59"/>
-      <c r="G9" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="I9" s="1">
-        <v>0</v>
-      </c>
-      <c r="J9" s="1"/>
-    </row>
-    <row r="10" spans="1:10">
+        <v>210</v>
+      </c>
+      <c r="D9" s="61"/>
+      <c r="E9" s="61"/>
+      <c r="F9" s="1"/>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="B10" s="59"/>
+        <v>211</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>212</v>
+      </c>
       <c r="C10" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="D10" s="59">
-        <v>7</v>
-      </c>
-      <c r="E10" s="59"/>
-      <c r="F10" s="59"/>
-      <c r="G10" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="H10" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="D10" s="61"/>
+      <c r="E10" s="61"/>
+      <c r="F10" s="1"/>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="D11" s="61"/>
+      <c r="E11" s="61"/>
+      <c r="F11" s="1"/>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="I10" s="1">
-        <v>0</v>
-      </c>
-      <c r="J10" s="1"/>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="B11" s="59"/>
-      <c r="C11" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="D11" s="59">
-        <v>8</v>
-      </c>
-      <c r="E11" s="59"/>
-      <c r="F11" s="59"/>
-      <c r="G11" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="I11" s="1">
-        <v>0</v>
-      </c>
-      <c r="J11" s="1"/>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="46" t="s">
-        <v>155</v>
-      </c>
-      <c r="B12" s="47" t="s">
-        <v>14</v>
-      </c>
-      <c r="C12" s="47" t="s">
-        <v>156</v>
-      </c>
-      <c r="D12" s="60"/>
-      <c r="E12" s="60">
-        <v>1</v>
-      </c>
-      <c r="F12" s="60">
-        <v>0</v>
-      </c>
-      <c r="G12" s="47" t="s">
-        <v>157</v>
-      </c>
-      <c r="H12" s="47" t="s">
-        <v>158</v>
-      </c>
-      <c r="I12" s="47">
-        <v>0</v>
-      </c>
-      <c r="J12" s="49"/>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" s="48" t="s">
-        <v>159</v>
-      </c>
-      <c r="B13" s="49" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13" s="49" t="s">
-        <v>160</v>
-      </c>
-      <c r="D13" s="61"/>
-      <c r="E13" s="61">
-        <v>1</v>
-      </c>
-      <c r="F13" s="61">
-        <v>1</v>
-      </c>
-      <c r="G13" s="49" t="s">
-        <v>161</v>
-      </c>
-      <c r="H13" s="49" t="s">
-        <v>162</v>
-      </c>
-      <c r="I13" s="49">
-        <v>0</v>
-      </c>
-      <c r="J13" s="49"/>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="48" t="s">
-        <v>163</v>
-      </c>
-      <c r="B14" s="49" t="s">
-        <v>14</v>
-      </c>
-      <c r="C14" s="49" t="s">
-        <v>105</v>
-      </c>
-      <c r="D14" s="61"/>
-      <c r="E14" s="61">
-        <v>1</v>
-      </c>
-      <c r="F14" s="61">
-        <v>3</v>
-      </c>
-      <c r="G14" s="49" t="s">
-        <v>164</v>
-      </c>
-      <c r="H14" s="49" t="s">
-        <v>131</v>
-      </c>
-      <c r="I14" s="49">
-        <v>0</v>
-      </c>
-      <c r="J14" s="49"/>
-    </row>
-    <row r="15" s="42" customFormat="1" spans="1:10">
-      <c r="A15" s="50" t="s">
-        <v>165</v>
-      </c>
-      <c r="B15" s="51" t="s">
-        <v>23</v>
-      </c>
-      <c r="C15" s="51" t="s">
-        <v>166</v>
-      </c>
-      <c r="D15" s="62"/>
-      <c r="E15" s="62">
-        <v>1</v>
-      </c>
-      <c r="F15" s="62">
-        <v>0</v>
-      </c>
-      <c r="G15" s="51" t="s">
-        <v>167</v>
-      </c>
-      <c r="H15" s="51" t="s">
-        <v>168</v>
-      </c>
-      <c r="I15" s="51">
-        <v>0</v>
-      </c>
-      <c r="J15" s="51"/>
-    </row>
-    <row r="16" s="42" customFormat="1" spans="1:10">
-      <c r="A16" s="50" t="s">
-        <v>169</v>
-      </c>
-      <c r="B16" s="51" t="s">
-        <v>23</v>
-      </c>
-      <c r="C16" s="51" t="s">
-        <v>170</v>
-      </c>
-      <c r="D16" s="62"/>
-      <c r="E16" s="62">
-        <v>1</v>
-      </c>
-      <c r="F16" s="62">
-        <v>1</v>
-      </c>
-      <c r="G16" s="51" t="s">
-        <v>171</v>
-      </c>
-      <c r="H16" s="51" t="s">
-        <v>146</v>
-      </c>
-      <c r="I16" s="51">
-        <v>0</v>
-      </c>
-      <c r="J16" s="51"/>
-    </row>
-    <row r="17" s="42" customFormat="1" spans="1:10">
-      <c r="A17" s="50" t="s">
-        <v>172</v>
-      </c>
-      <c r="B17" s="51" t="s">
-        <v>23</v>
-      </c>
-      <c r="C17" s="51" t="s">
-        <v>173</v>
-      </c>
-      <c r="D17" s="62"/>
-      <c r="E17" s="62">
-        <v>1</v>
-      </c>
-      <c r="F17" s="62">
-        <v>3</v>
-      </c>
-      <c r="G17" s="51" t="s">
-        <v>174</v>
-      </c>
-      <c r="H17" s="51" t="s">
-        <v>150</v>
-      </c>
-      <c r="I17" s="51">
-        <v>0</v>
-      </c>
-      <c r="J17" s="51"/>
-    </row>
-    <row r="18" s="55" customFormat="1" spans="1:10">
-      <c r="A18" s="53" t="s">
-        <v>175</v>
-      </c>
-      <c r="B18" s="54" t="s">
-        <v>17</v>
-      </c>
-      <c r="C18" s="54" t="s">
-        <v>176</v>
-      </c>
-      <c r="D18" s="63"/>
-      <c r="E18" s="63">
-        <v>1</v>
-      </c>
-      <c r="F18" s="63">
-        <v>0</v>
-      </c>
-      <c r="G18" s="54" t="s">
-        <v>177</v>
-      </c>
-      <c r="H18" s="54" t="s">
-        <v>154</v>
-      </c>
-      <c r="I18" s="54">
-        <v>0</v>
-      </c>
-      <c r="J18" s="54"/>
-    </row>
-    <row r="19" s="55" customFormat="1" spans="1:10">
-      <c r="A19" s="53" t="s">
-        <v>178</v>
-      </c>
-      <c r="B19" s="54" t="s">
-        <v>17</v>
-      </c>
-      <c r="C19" s="54" t="s">
-        <v>179</v>
-      </c>
-      <c r="D19" s="63"/>
-      <c r="E19" s="63">
-        <v>1</v>
-      </c>
-      <c r="F19" s="63">
-        <v>1</v>
-      </c>
-      <c r="G19" s="54" t="s">
-        <v>180</v>
-      </c>
-      <c r="H19" s="54" t="s">
-        <v>154</v>
-      </c>
-      <c r="I19" s="54">
-        <v>0</v>
-      </c>
-      <c r="J19" s="54"/>
-    </row>
-    <row r="20" s="55" customFormat="1" spans="1:10">
-      <c r="A20" s="53" t="s">
-        <v>181</v>
-      </c>
-      <c r="B20" s="54" t="s">
-        <v>17</v>
-      </c>
-      <c r="C20" s="54" t="s">
-        <v>182</v>
-      </c>
-      <c r="D20" s="63"/>
-      <c r="E20" s="63">
-        <v>1</v>
-      </c>
-      <c r="F20" s="63">
-        <v>3</v>
-      </c>
-      <c r="G20" s="54" t="s">
-        <v>183</v>
-      </c>
-      <c r="H20" s="54" t="s">
-        <v>154</v>
-      </c>
-      <c r="I20" s="54">
-        <v>0</v>
-      </c>
-      <c r="J20" s="54"/>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="A21" s="48" t="s">
-        <v>184</v>
-      </c>
-      <c r="B21" s="49" t="s">
-        <v>20</v>
-      </c>
-      <c r="C21" s="49" t="s">
-        <v>185</v>
-      </c>
-      <c r="D21" s="61"/>
-      <c r="E21" s="61">
-        <v>1</v>
-      </c>
-      <c r="F21" s="61">
-        <v>0</v>
-      </c>
-      <c r="G21" s="49" t="s">
-        <v>186</v>
-      </c>
-      <c r="H21" s="49" t="s">
-        <v>154</v>
-      </c>
-      <c r="I21" s="49">
-        <v>0</v>
-      </c>
-      <c r="J21" s="49"/>
-    </row>
-    <row r="22" spans="1:10">
-      <c r="A22" s="48" t="s">
-        <v>187</v>
-      </c>
-      <c r="B22" s="49" t="s">
-        <v>20</v>
-      </c>
-      <c r="C22" s="49" t="s">
-        <v>188</v>
-      </c>
-      <c r="D22" s="61"/>
-      <c r="E22" s="61">
-        <v>1</v>
-      </c>
-      <c r="F22" s="61">
-        <v>1</v>
-      </c>
-      <c r="G22" s="49" t="s">
-        <v>189</v>
-      </c>
-      <c r="H22" s="49" t="s">
-        <v>154</v>
-      </c>
-      <c r="I22" s="49">
-        <v>0</v>
-      </c>
-      <c r="J22" s="49"/>
-    </row>
-    <row r="23" spans="1:10">
-      <c r="A23" s="48" t="s">
-        <v>190</v>
-      </c>
-      <c r="B23" s="49" t="s">
-        <v>20</v>
-      </c>
-      <c r="C23" s="49" t="s">
-        <v>191</v>
-      </c>
-      <c r="D23" s="61"/>
-      <c r="E23" s="61">
-        <v>1</v>
-      </c>
-      <c r="F23" s="61">
-        <v>3</v>
-      </c>
-      <c r="G23" s="49" t="s">
-        <v>192</v>
-      </c>
-      <c r="H23" s="49" t="s">
-        <v>154</v>
-      </c>
-      <c r="I23" s="49">
-        <v>0</v>
-      </c>
-      <c r="J23" s="49"/>
-    </row>
-    <row r="24" spans="1:10">
-      <c r="A24" s="48" t="s">
-        <v>193</v>
-      </c>
-      <c r="B24" s="49" t="s">
-        <v>26</v>
-      </c>
-      <c r="C24" s="49" t="s">
-        <v>194</v>
-      </c>
-      <c r="D24" s="61"/>
-      <c r="E24" s="61">
-        <v>1</v>
-      </c>
-      <c r="F24" s="61">
-        <v>0</v>
-      </c>
-      <c r="G24" s="49" t="s">
-        <v>195</v>
-      </c>
-      <c r="H24" s="49" t="s">
-        <v>154</v>
-      </c>
-      <c r="I24" s="49">
-        <v>0</v>
-      </c>
-      <c r="J24" s="49"/>
-    </row>
-    <row r="25" spans="1:10">
-      <c r="A25" s="48" t="s">
-        <v>196</v>
-      </c>
-      <c r="B25" s="49" t="s">
-        <v>26</v>
-      </c>
-      <c r="C25" s="49" t="s">
-        <v>197</v>
-      </c>
-      <c r="D25" s="61"/>
-      <c r="E25" s="61">
-        <v>1</v>
-      </c>
-      <c r="F25" s="61">
-        <v>1</v>
-      </c>
-      <c r="G25" s="54" t="s">
-        <v>183</v>
-      </c>
-      <c r="H25" s="49" t="s">
-        <v>154</v>
-      </c>
-      <c r="I25" s="49">
-        <v>0</v>
-      </c>
-      <c r="J25" s="49"/>
-    </row>
-    <row r="26" s="41" customFormat="1" spans="1:10">
-      <c r="A26" s="46" t="s">
-        <v>198</v>
-      </c>
-      <c r="B26" s="47" t="s">
-        <v>26</v>
-      </c>
-      <c r="C26" s="47" t="s">
-        <v>199</v>
-      </c>
-      <c r="D26" s="60"/>
-      <c r="E26" s="60">
-        <v>1</v>
-      </c>
-      <c r="F26" s="60">
-        <v>3</v>
-      </c>
-      <c r="G26" s="47" t="s">
-        <v>200</v>
-      </c>
-      <c r="H26" s="47" t="s">
-        <v>154</v>
-      </c>
-      <c r="I26" s="47">
-        <v>0</v>
-      </c>
-      <c r="J26" s="47"/>
+      <c r="C12" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="D12" s="61"/>
+      <c r="E12" s="61"/>
+      <c r="F12" s="47"/>
+    </row>
+    <row r="13" spans="6:6">
+      <c r="F13" s="49"/>
+    </row>
+    <row r="14" spans="6:6">
+      <c r="F14" s="49"/>
+    </row>
+    <row r="15" spans="6:6">
+      <c r="F15" s="51"/>
+    </row>
+    <row r="16" spans="6:6">
+      <c r="F16" s="51"/>
+    </row>
+    <row r="17" spans="6:6">
+      <c r="F17" s="51"/>
+    </row>
+    <row r="18" spans="6:6">
+      <c r="F18" s="53"/>
+    </row>
+    <row r="19" spans="6:6">
+      <c r="F19" s="53"/>
+    </row>
+    <row r="20" spans="6:6">
+      <c r="F20" s="53"/>
+    </row>
+    <row r="21" spans="6:6">
+      <c r="F21" s="49"/>
+    </row>
+    <row r="22" spans="6:6">
+      <c r="F22" s="49"/>
+    </row>
+    <row r="23" spans="6:6">
+      <c r="F23" s="49"/>
+    </row>
+    <row r="24" spans="6:6">
+      <c r="F24" s="49"/>
+    </row>
+    <row r="25" spans="6:6">
+      <c r="F25" s="49"/>
+    </row>
+    <row r="26" spans="6:6">
+      <c r="F26" s="47"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
 </file>
@@ -8159,7 +8362,7 @@
     <col min="3" max="3" width="9.125" customWidth="1"/>
     <col min="4" max="4" width="14.125" customWidth="1"/>
     <col min="6" max="6" width="14.125" customWidth="1"/>
-    <col min="7" max="7" width="9.75" customWidth="1"/>
+    <col min="7" max="7" width="14.375" customWidth="1"/>
     <col min="8" max="8" width="71.2" customWidth="1"/>
   </cols>
   <sheetData>
@@ -8168,22 +8371,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>201</v>
+        <v>219</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>202</v>
+        <v>220</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>61</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>203</v>
+        <v>188</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>204</v>
+        <v>221</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>205</v>
+        <v>222</v>
       </c>
       <c r="H1" s="5" t="s">
         <v>4</v>
@@ -8194,25 +8397,25 @@
         <v>5</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>201</v>
+        <v>219</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="D2" s="44" t="s">
-        <v>207</v>
+        <v>224</v>
       </c>
       <c r="E2" s="43" t="s">
-        <v>208</v>
+        <v>225</v>
       </c>
       <c r="F2" s="43" t="s">
-        <v>209</v>
+        <v>226</v>
       </c>
       <c r="G2" s="43" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -8271,7 +8474,7 @@
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="40" t="s">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="D5" s="1">
         <v>1</v>
@@ -8286,12 +8489,12 @@
         <v>5</v>
       </c>
       <c r="H5" s="40" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
     </row>
     <row r="6" s="41" customFormat="1" spans="1:8">
       <c r="A6" s="45" t="s">
-        <v>214</v>
+        <v>231</v>
       </c>
       <c r="B6" s="45"/>
       <c r="C6" s="45" t="s">
@@ -8310,16 +8513,16 @@
         <v>8</v>
       </c>
       <c r="H6" s="45" t="s">
-        <v>215</v>
+        <v>232</v>
       </c>
     </row>
     <row r="7" s="41" customFormat="1" spans="1:8">
       <c r="A7" s="45" t="s">
-        <v>216</v>
+        <v>233</v>
       </c>
       <c r="B7" s="45"/>
       <c r="C7" s="45" t="s">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="D7" s="45">
         <v>0</v>
@@ -8331,21 +8534,21 @@
         <v>3</v>
       </c>
       <c r="G7" s="45" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="H7" s="45" t="s">
-        <v>219</v>
+        <v>236</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="1" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>221</v>
+        <v>237</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>96</v>
+        <v>204</v>
       </c>
       <c r="D8" s="1">
         <v>0</v>
@@ -8360,18 +8563,18 @@
         <v>1</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>222</v>
+        <v>238</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
-        <v>223</v>
+        <v>239</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>224</v>
+        <v>240</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -8386,18 +8589,18 @@
         <v>2</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>225</v>
+        <v>241</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
-        <v>226</v>
+        <v>242</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>227</v>
+        <v>243</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>102</v>
+        <v>212</v>
       </c>
       <c r="D10" s="1">
         <v>0</v>
@@ -8412,18 +8615,18 @@
         <v>3</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>228</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>230</v>
+        <v>246</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>231</v>
+        <v>247</v>
       </c>
       <c r="D11" s="1">
         <v>0</v>
@@ -8438,18 +8641,18 @@
         <v>4</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>232</v>
+        <v>248</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>234</v>
+        <v>250</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="D12" s="1">
         <v>0</v>
@@ -8464,18 +8667,18 @@
         <v>5</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>235</v>
+        <v>251</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1" t="s">
-        <v>236</v>
+        <v>252</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>237</v>
+        <v>253</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>238</v>
+        <v>202</v>
       </c>
       <c r="D13" s="1">
         <v>0</v>
@@ -8490,18 +8693,18 @@
         <v>6</v>
       </c>
       <c r="H13" s="40" t="s">
-        <v>239</v>
+        <v>254</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>240</v>
+        <v>255</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>241</v>
+        <v>256</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>242</v>
+        <v>257</v>
       </c>
       <c r="D14" s="1">
         <v>0</v>
@@ -8516,18 +8719,18 @@
         <v>7</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>243</v>
+        <v>258</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1" t="s">
-        <v>244</v>
+        <v>259</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>245</v>
+        <v>260</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>246</v>
+        <v>261</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -8542,18 +8745,18 @@
         <v>8</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>247</v>
+        <v>262</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1" t="s">
-        <v>248</v>
+        <v>263</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>249</v>
+        <v>264</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>250</v>
+        <v>265</v>
       </c>
       <c r="D16" s="1">
         <v>0</v>
@@ -8568,18 +8771,18 @@
         <v>9</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>251</v>
+        <v>266</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="46" t="s">
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="B17" s="47" t="s">
-        <v>252</v>
+        <v>267</v>
       </c>
       <c r="C17" s="47" t="s">
-        <v>252</v>
+        <v>267</v>
       </c>
       <c r="D17" s="1">
         <v>0</v>
@@ -8588,18 +8791,18 @@
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
       <c r="H17" s="47" t="s">
-        <v>253</v>
+        <v>268</v>
       </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="48" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="B18" s="49" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="C18" s="49" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="D18" s="1">
         <v>0</v>
@@ -8608,21 +8811,21 @@
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
       <c r="H18" s="49" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="I18" t="s">
-        <v>254</v>
+        <v>269</v>
       </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="48" t="s">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="B19" s="49" t="s">
-        <v>105</v>
+        <v>150</v>
       </c>
       <c r="C19" s="49" t="s">
-        <v>105</v>
+        <v>150</v>
       </c>
       <c r="D19" s="1">
         <v>0</v>
@@ -8631,90 +8834,90 @@
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
       <c r="H19" s="49" t="s">
-        <v>255</v>
+        <v>270</v>
       </c>
       <c r="I19" t="s">
-        <v>256</v>
+        <v>271</v>
       </c>
     </row>
     <row r="20" s="42" customFormat="1" spans="1:9">
       <c r="A20" s="50" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="B20" s="51" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="C20" s="51" t="s">
-        <v>166</v>
-      </c>
-      <c r="D20" s="52">
-        <v>0</v>
-      </c>
-      <c r="E20" s="52"/>
-      <c r="F20" s="52"/>
-      <c r="G20" s="52"/>
+        <v>153</v>
+      </c>
+      <c r="D20" s="51">
+        <v>0</v>
+      </c>
+      <c r="E20" s="51"/>
+      <c r="F20" s="51"/>
+      <c r="G20" s="51"/>
       <c r="H20" s="51" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
       <c r="I20" s="42" t="s">
-        <v>257</v>
+        <v>272</v>
       </c>
     </row>
     <row r="21" s="42" customFormat="1" spans="1:9">
       <c r="A21" s="50" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="B21" s="51" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="C21" s="51" t="s">
-        <v>170</v>
-      </c>
-      <c r="D21" s="52">
-        <v>0</v>
-      </c>
-      <c r="E21" s="52"/>
-      <c r="F21" s="52"/>
-      <c r="G21" s="52"/>
+        <v>157</v>
+      </c>
+      <c r="D21" s="51">
+        <v>0</v>
+      </c>
+      <c r="E21" s="51"/>
+      <c r="F21" s="51"/>
+      <c r="G21" s="51"/>
       <c r="H21" s="51" t="s">
-        <v>258</v>
+        <v>273</v>
       </c>
       <c r="I21" s="42" t="s">
-        <v>254</v>
+        <v>269</v>
       </c>
     </row>
     <row r="22" s="42" customFormat="1" spans="1:9">
       <c r="A22" s="50" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="B22" s="51" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="C22" s="51" t="s">
-        <v>173</v>
-      </c>
-      <c r="D22" s="52">
-        <v>0</v>
-      </c>
-      <c r="E22" s="52"/>
-      <c r="F22" s="52"/>
-      <c r="G22" s="52"/>
+        <v>160</v>
+      </c>
+      <c r="D22" s="51">
+        <v>0</v>
+      </c>
+      <c r="E22" s="51"/>
+      <c r="F22" s="51"/>
+      <c r="G22" s="51"/>
       <c r="H22" s="51" t="s">
-        <v>174</v>
+        <v>161</v>
       </c>
       <c r="I22" s="42" t="s">
-        <v>259</v>
+        <v>274</v>
       </c>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="53" t="s">
-        <v>175</v>
-      </c>
-      <c r="B23" s="54" t="s">
-        <v>176</v>
-      </c>
-      <c r="C23" s="54" t="s">
-        <v>176</v>
+      <c r="A23" s="52" t="s">
+        <v>162</v>
+      </c>
+      <c r="B23" s="53" t="s">
+        <v>163</v>
+      </c>
+      <c r="C23" s="53" t="s">
+        <v>163</v>
       </c>
       <c r="D23" s="1">
         <v>0</v>
@@ -8722,22 +8925,22 @@
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
-      <c r="H23" s="54" t="s">
-        <v>260</v>
+      <c r="H23" s="53" t="s">
+        <v>275</v>
       </c>
       <c r="I23" t="s">
-        <v>261</v>
+        <v>276</v>
       </c>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="53" t="s">
-        <v>178</v>
-      </c>
-      <c r="B24" s="54" t="s">
-        <v>179</v>
-      </c>
-      <c r="C24" s="54" t="s">
-        <v>179</v>
+      <c r="A24" s="52" t="s">
+        <v>165</v>
+      </c>
+      <c r="B24" s="53" t="s">
+        <v>166</v>
+      </c>
+      <c r="C24" s="53" t="s">
+        <v>166</v>
       </c>
       <c r="D24" s="1">
         <v>0</v>
@@ -8746,21 +8949,21 @@
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
       <c r="H24" s="1" t="s">
-        <v>219</v>
+        <v>236</v>
       </c>
       <c r="I24" t="s">
-        <v>96</v>
+        <v>204</v>
       </c>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="53" t="s">
-        <v>181</v>
-      </c>
-      <c r="B25" s="54" t="s">
-        <v>182</v>
-      </c>
-      <c r="C25" s="54" t="s">
-        <v>182</v>
+      <c r="A25" s="52" t="s">
+        <v>168</v>
+      </c>
+      <c r="B25" s="53" t="s">
+        <v>169</v>
+      </c>
+      <c r="C25" s="53" t="s">
+        <v>169</v>
       </c>
       <c r="D25" s="1">
         <v>0</v>
@@ -8768,22 +8971,22 @@
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
-      <c r="H25" s="54" t="s">
-        <v>183</v>
+      <c r="H25" s="53" t="s">
+        <v>170</v>
       </c>
       <c r="I25" t="s">
-        <v>262</v>
+        <v>277</v>
       </c>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="48" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="B26" s="49" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="C26" s="49" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="D26" s="1">
         <v>0</v>
@@ -8792,21 +8995,21 @@
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
       <c r="H26" s="49" t="s">
-        <v>263</v>
+        <v>278</v>
       </c>
       <c r="I26" t="s">
-        <v>261</v>
+        <v>276</v>
       </c>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="48" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="B27" s="49" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="C27" s="49" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="D27" s="1">
         <v>0</v>
@@ -8815,21 +9018,21 @@
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
       <c r="H27" s="49" t="s">
-        <v>264</v>
+        <v>279</v>
       </c>
       <c r="I27" t="s">
-        <v>265</v>
+        <v>280</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="48" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="B28" s="49" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="C28" s="49" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="D28" s="1">
         <v>0</v>
@@ -8838,18 +9041,18 @@
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
       <c r="H28" s="47" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="48" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="B29" s="49" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="C29" s="49" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="D29" s="1">
         <v>0</v>
@@ -8858,21 +9061,21 @@
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
       <c r="H29" s="49" t="s">
-        <v>266</v>
+        <v>281</v>
       </c>
       <c r="I29" t="s">
-        <v>261</v>
+        <v>276</v>
       </c>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="48" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="B30" s="49" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="C30" s="49" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="D30" s="1">
         <v>0</v>
@@ -8880,22 +9083,22 @@
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
-      <c r="H30" s="54" t="s">
-        <v>183</v>
+      <c r="H30" s="53" t="s">
+        <v>170</v>
       </c>
       <c r="I30" t="s">
-        <v>262</v>
+        <v>277</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="46" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="B31" s="47" t="s">
-        <v>199</v>
+        <v>186</v>
       </c>
       <c r="C31" s="47" t="s">
-        <v>199</v>
+        <v>186</v>
       </c>
       <c r="D31" s="1">
         <v>0</v>
@@ -8904,7 +9107,7 @@
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
       <c r="H31" s="47" t="s">
-        <v>200</v>
+        <v>187</v>
       </c>
     </row>
   </sheetData>
@@ -8929,22 +9132,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="35" t="s">
-        <v>267</v>
+        <v>282</v>
       </c>
       <c r="C1" s="35" t="s">
-        <v>268</v>
+        <v>283</v>
       </c>
       <c r="D1" s="35" t="s">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="E1" s="35" t="s">
-        <v>270</v>
+        <v>285</v>
       </c>
       <c r="F1" s="35" t="s">
-        <v>271</v>
+        <v>286</v>
       </c>
       <c r="G1" s="35" t="s">
-        <v>272</v>
+        <v>287</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -8952,22 +9155,22 @@
         <v>5</v>
       </c>
       <c r="B2" s="37" t="s">
-        <v>273</v>
+        <v>288</v>
       </c>
       <c r="C2" s="37" t="s">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="D2" s="37" t="s">
-        <v>274</v>
+        <v>289</v>
       </c>
       <c r="E2" s="37" t="s">
-        <v>275</v>
+        <v>290</v>
       </c>
       <c r="F2" s="37" t="s">
-        <v>276</v>
+        <v>291</v>
       </c>
       <c r="G2" s="38" t="s">
-        <v>277</v>
+        <v>292</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -8978,16 +9181,16 @@
         <v>10</v>
       </c>
       <c r="C3" s="37" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="D3" s="37" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="E3" s="37" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="F3" s="37" t="s">
-        <v>278</v>
+        <v>293</v>
       </c>
       <c r="G3" s="37" t="s">
         <v>10</v>
@@ -8995,10 +9198,10 @@
     </row>
     <row r="4" ht="14.25" spans="1:7">
       <c r="A4" s="39" t="s">
-        <v>279</v>
+        <v>294</v>
       </c>
       <c r="B4" s="40" t="s">
-        <v>280</v>
+        <v>295</v>
       </c>
       <c r="C4" s="39">
         <v>100</v>
@@ -9013,15 +9216,15 @@
         <v>1</v>
       </c>
       <c r="G4" s="39" t="s">
-        <v>281</v>
+        <v>296</v>
       </c>
     </row>
     <row r="5" ht="14.25" spans="1:7">
       <c r="A5" s="39" t="s">
-        <v>282</v>
+        <v>297</v>
       </c>
       <c r="B5" s="40" t="s">
-        <v>283</v>
+        <v>298</v>
       </c>
       <c r="C5" s="39">
         <v>100</v>
@@ -9036,15 +9239,15 @@
         <v>1</v>
       </c>
       <c r="G5" s="39" t="s">
-        <v>284</v>
+        <v>299</v>
       </c>
     </row>
     <row r="6" ht="14.25" spans="1:7">
       <c r="A6" s="39" t="s">
-        <v>285</v>
+        <v>300</v>
       </c>
       <c r="B6" s="40" t="s">
-        <v>286</v>
+        <v>301</v>
       </c>
       <c r="C6" s="39">
         <v>3</v>
@@ -9059,15 +9262,15 @@
         <v>1</v>
       </c>
       <c r="G6" s="39" t="s">
-        <v>287</v>
+        <v>302</v>
       </c>
     </row>
     <row r="7" ht="14.25" spans="1:7">
       <c r="A7" s="39" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="B7" s="40" t="s">
-        <v>289</v>
+        <v>304</v>
       </c>
       <c r="C7" s="39">
         <v>3</v>
@@ -9082,12 +9285,12 @@
         <v>1</v>
       </c>
       <c r="G7" s="39" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
     </row>
     <row r="8" ht="14.25" spans="1:7">
       <c r="A8" s="39" t="s">
-        <v>291</v>
+        <v>306</v>
       </c>
       <c r="B8" s="40" t="s">
         <v>8</v>
@@ -9105,15 +9308,15 @@
         <v>1</v>
       </c>
       <c r="G8" s="39" t="s">
-        <v>292</v>
+        <v>307</v>
       </c>
     </row>
     <row r="9" ht="14.25" spans="1:7">
       <c r="A9" s="39" t="s">
-        <v>293</v>
+        <v>308</v>
       </c>
       <c r="B9" s="40" t="s">
-        <v>294</v>
+        <v>309</v>
       </c>
       <c r="C9" s="39">
         <v>0</v>
@@ -9128,15 +9331,15 @@
         <v>1</v>
       </c>
       <c r="G9" s="39" t="s">
-        <v>295</v>
+        <v>310</v>
       </c>
     </row>
     <row r="10" ht="14.25" spans="1:7">
       <c r="A10" s="39" t="s">
-        <v>296</v>
+        <v>311</v>
       </c>
       <c r="B10" s="40" t="s">
-        <v>297</v>
+        <v>312</v>
       </c>
       <c r="C10" s="39">
         <v>0</v>
@@ -9151,15 +9354,15 @@
         <v>1</v>
       </c>
       <c r="G10" s="39" t="s">
-        <v>298</v>
+        <v>313</v>
       </c>
     </row>
     <row r="11" ht="14.25" spans="1:7">
       <c r="A11" s="39" t="s">
-        <v>299</v>
+        <v>314</v>
       </c>
       <c r="B11" s="40" t="s">
-        <v>300</v>
+        <v>196</v>
       </c>
       <c r="C11" s="39">
         <v>0</v>
@@ -9174,15 +9377,15 @@
         <v>1</v>
       </c>
       <c r="G11" s="39" t="s">
-        <v>301</v>
+        <v>315</v>
       </c>
     </row>
     <row r="12" ht="14.25" spans="1:7">
       <c r="A12" s="39" t="s">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="B12" s="40" t="s">
-        <v>303</v>
+        <v>199</v>
       </c>
       <c r="C12" s="39">
         <v>0</v>
@@ -9197,15 +9400,15 @@
         <v>1</v>
       </c>
       <c r="G12" s="39" t="s">
-        <v>304</v>
+        <v>317</v>
       </c>
     </row>
     <row r="13" ht="14.25" spans="1:7">
       <c r="A13" s="39" t="s">
-        <v>305</v>
+        <v>318</v>
       </c>
       <c r="B13" s="40" t="s">
-        <v>306</v>
+        <v>319</v>
       </c>
       <c r="C13" s="39">
         <v>0</v>
@@ -9220,15 +9423,15 @@
         <v>1</v>
       </c>
       <c r="G13" s="39" t="s">
-        <v>307</v>
+        <v>320</v>
       </c>
     </row>
     <row r="14" ht="14.25" spans="1:7">
       <c r="A14" s="39" t="s">
-        <v>308</v>
+        <v>321</v>
       </c>
       <c r="B14" s="40" t="s">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="C14" s="39">
         <v>0</v>
@@ -9243,7 +9446,7 @@
         <v>1</v>
       </c>
       <c r="G14" s="39" t="s">
-        <v>309</v>
+        <v>322</v>
       </c>
     </row>
   </sheetData>

--- a/xlsdir/配置-总表.xlsx
+++ b/xlsdir/配置-总表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="673" firstSheet="3" activeTab="6"/>
+    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="673" firstSheet="3" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="character|角色" sheetId="32" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="834" uniqueCount="548">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="865" uniqueCount="557">
   <si>
     <t>ID</t>
   </si>
@@ -180,34 +180,34 @@
     <t>燃烧之血，战斗结束时恢复6点生命。</t>
   </si>
   <si>
+    <t>enemy_scene</t>
+  </si>
+  <si>
     <t>intent_pool</t>
   </si>
   <si>
-    <t>enemy_scene</t>
-  </si>
-  <si>
     <t>怪物名</t>
   </si>
   <si>
+    <t>怪物场景</t>
+  </si>
+  <si>
     <t>意图池</t>
   </si>
   <si>
-    <t>怪物场景</t>
-  </si>
-  <si>
-    <t>split*absorb*entangle</t>
+    <t>split*absorb*entangle*attack_5</t>
+  </si>
+  <si>
+    <t>toxin_spray*healing_spore*hallucinogenic_spore*attack_8</t>
+  </si>
+  <si>
+    <t>heavy_strike*bone_shield*summon_assistance</t>
   </si>
   <si>
     <t>destruction_ray*curse_gaze*magic_shield</t>
   </si>
   <si>
     <t>sprint_stab*set_trap*sneak_attack</t>
-  </si>
-  <si>
-    <t>toxin_spray*healing_spore*hallucinogenic_spore</t>
-  </si>
-  <si>
-    <t>heavy_strike*bone_shield*summon_assistance</t>
   </si>
   <si>
     <t>card_name</t>
@@ -344,9 +344,6 @@
     <t>value</t>
   </si>
   <si>
-    <t>func</t>
-  </si>
-  <si>
     <t>所属(注释）</t>
   </si>
   <si>
@@ -371,7 +368,7 @@
     <t>意图值</t>
   </si>
   <si>
-    <t>意图方法</t>
+    <t>意图效果</t>
   </si>
   <si>
     <t>float</t>
@@ -470,13 +467,19 @@
     <t>res://asserts/textures/widgets/Buffs/swiftness.png</t>
   </si>
   <si>
+    <t>attack_5</t>
+  </si>
+  <si>
+    <t>敌人打算进行攻击,造成5点伤害</t>
+  </si>
+  <si>
     <t>split</t>
   </si>
   <si>
     <t>脆弱</t>
   </si>
   <si>
-    <t>目标下一回合获得的护甲值降低25%</t>
+    <t>敌人打算释放一个负面效果的法术</t>
   </si>
   <si>
     <t>res://asserts/textures/widgets/Buffs/ghost_form_(physical_damage_immunity).png</t>
@@ -488,9 +491,6 @@
     <t>吸收</t>
   </si>
   <si>
-    <t>回复一定量的生命值，吸收的量取决于其当前生命值。</t>
-  </si>
-  <si>
     <t>res://asserts/textures/widgets/Buffs/summoning_spell.png</t>
   </si>
   <si>
@@ -500,7 +500,10 @@
     <t>缠绕</t>
   </si>
   <si>
-    <t>降低玩家下一回合的行动点数。</t>
+    <t>attack_8</t>
+  </si>
+  <si>
+    <t>敌人打算进行攻击,造成8点伤害</t>
   </si>
   <si>
     <t>toxin_spray</t>
@@ -509,9 +512,6 @@
     <t>毒素喷射</t>
   </si>
   <si>
-    <t>造成持续性的毒素伤害。</t>
-  </si>
-  <si>
     <t>res://asserts/textures/widgets/Buffs/poisoned.png</t>
   </si>
   <si>
@@ -521,18 +521,12 @@
     <t>治疗孢子</t>
   </si>
   <si>
-    <t>为自己或其他敌人恢复生命值。</t>
-  </si>
-  <si>
     <t>hallucinogenic_spore</t>
   </si>
   <si>
     <t>迷幻孢子</t>
   </si>
   <si>
-    <t>玩家获得“混乱”卡牌。</t>
-  </si>
-  <si>
     <t>destruction_ray</t>
   </si>
   <si>
@@ -611,10 +605,22 @@
     <t>召唤另一个骷髅怪加入战斗</t>
   </si>
   <si>
-    <t>duration</t>
+    <t>buff_type</t>
+  </si>
+  <si>
+    <t>duration_type</t>
+  </si>
+  <si>
+    <t>callback_type</t>
   </si>
   <si>
     <t>效果名</t>
+  </si>
+  <si>
+    <t>类型
+1可堆叠
+2固定
+3短时</t>
   </si>
   <si>
     <t>持续类型
@@ -622,6 +628,19 @@
 2持续回合</t>
   </si>
   <si>
+    <t>回调类型
+1回合开始
+2回合结束
+3攻击前
+4攻击后
+5受到伤害前
+6受到伤害后
+7释放技能前
+8释放技能后
+9被治疗时
+10使用卡牌时</t>
+  </si>
+  <si>
     <t>图标</t>
   </si>
   <si>
@@ -667,12 +686,12 @@
     <t>使目标收到的攻击伤害增加</t>
   </si>
   <si>
+    <t>res://asserts/textures/widgets/Buffs/defense_down.png</t>
+  </si>
+  <si>
     <t>VULNERABLE</t>
   </si>
   <si>
-    <t>res://asserts/textures/widgets/Buffs/defense_down.png</t>
-  </si>
-  <si>
     <t>weak</t>
   </si>
   <si>
@@ -710,6 +729,9 @@
   </si>
   <si>
     <t>effect_name</t>
+  </si>
+  <si>
+    <t>duration</t>
   </si>
   <si>
     <t>effect_type</t>
@@ -737,7 +759,7 @@
 1、造成伤害
 2、获得护盾
 3、给予BUFF
-4、特性</t>
+4、易伤</t>
   </si>
   <si>
     <t>效果参数，根据类型。*号分割
@@ -869,6 +891,9 @@
     <t>史莱姆分裂成两个较小的实体，增加战斗中的敌人数量。</t>
   </si>
   <si>
+    <t>回复一定量的生命值，吸收的量取决于其当前生命值。</t>
+  </si>
+  <si>
     <t>恢复</t>
   </si>
   <si>
@@ -878,12 +903,18 @@
     <t>减少行动点数</t>
   </si>
   <si>
+    <t>造成持续性的毒素伤害。</t>
+  </si>
+  <si>
     <t>放毒</t>
   </si>
   <si>
     <t>所有人恢复10点生命值。</t>
   </si>
   <si>
+    <t>玩家获得“混乱”卡牌。</t>
+  </si>
+  <si>
     <t>给与卡牌</t>
   </si>
   <si>
@@ -906,6 +937,9 @@
   </si>
   <si>
     <t>造成15点伤害</t>
+  </si>
+  <si>
+    <t>造成5点伤害</t>
   </si>
   <si>
     <t>Name</t>
@@ -1797,6 +1831,9 @@
     <t>destruction_ray*curse_gaze</t>
   </si>
   <si>
+    <t>split*absorb*entangle</t>
+  </si>
+  <si>
     <t>sprint_stab*set_trap</t>
   </si>
   <si>
@@ -1807,6 +1844,9 @@
   </si>
   <si>
     <t>heavy_strike*bone_shield</t>
+  </si>
+  <si>
+    <t>toxin_spray*healing_spore*hallucinogenic_spore</t>
   </si>
   <si>
     <t>描述：</t>
@@ -2832,7 +2872,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2998,25 +3038,13 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
@@ -3579,67 +3607,67 @@
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="R1" s="13" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="S1" s="3" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="T1" s="3" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="U1" s="3" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="V1" s="3" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="W1" s="14" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="X1" s="15"/>
       <c r="Y1" s="15"/>
@@ -3651,82 +3679,82 @@
         <v>5</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="O2" s="5" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="P2" s="5" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="Q2" s="5" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="R2" s="16" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="S2" s="5" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="T2" s="5" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="U2" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="V2" s="5" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="W2" s="17" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="X2" s="18" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="Y2" s="32" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="Z2" s="32" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="AA2" s="33" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
     </row>
     <row r="3" ht="14.25" spans="1:27">
@@ -3817,7 +3845,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="C4" s="9">
         <v>10</v>
@@ -3872,17 +3900,17 @@
       <c r="U4" s="9"/>
       <c r="V4" s="9"/>
       <c r="W4" s="23"/>
-      <c r="X4" s="72" t="s">
-        <v>366</v>
+      <c r="X4" s="68" t="s">
+        <v>373</v>
       </c>
       <c r="Y4" s="9" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="Z4" s="9" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="AA4" s="23" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
     </row>
     <row r="5" spans="1:27">
@@ -3890,7 +3918,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="C5" s="1">
         <v>10</v>
@@ -3946,16 +3974,16 @@
       <c r="V5" s="1"/>
       <c r="W5" s="26"/>
       <c r="X5" s="27" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="Y5" s="1" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="Z5" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="AA5" s="26" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
     </row>
     <row r="6" spans="1:27">
@@ -3963,7 +3991,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="C6" s="1">
         <v>10</v>
@@ -4019,16 +4047,16 @@
       <c r="V6" s="1"/>
       <c r="W6" s="26"/>
       <c r="X6" s="27" t="s">
+        <v>381</v>
+      </c>
+      <c r="Y6" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="Y6" s="1" t="s">
-        <v>367</v>
-      </c>
       <c r="Z6" s="1" t="s">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="AA6" s="26" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
     </row>
     <row r="7" spans="1:27">
@@ -4036,7 +4064,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="C7" s="1">
         <v>10</v>
@@ -4092,16 +4120,16 @@
       <c r="V7" s="1"/>
       <c r="W7" s="26"/>
       <c r="X7" s="27" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="Y7" s="1" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="Z7" s="1" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="AA7" s="26" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
     </row>
     <row r="8" spans="1:27">
@@ -4109,7 +4137,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="C8" s="1">
         <v>10</v>
@@ -4165,16 +4193,16 @@
       <c r="V8" s="1"/>
       <c r="W8" s="26"/>
       <c r="X8" s="27" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="Y8" s="1" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="Z8" s="1" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="AA8" s="26" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
     </row>
     <row r="9" spans="1:27">
@@ -4182,7 +4210,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="C9" s="1">
         <v>10</v>
@@ -4238,16 +4266,16 @@
       <c r="V9" s="1"/>
       <c r="W9" s="26"/>
       <c r="X9" s="27" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="Y9" s="1" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="Z9" s="1" t="s">
-        <v>388</v>
+        <v>395</v>
       </c>
       <c r="AA9" s="26" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
     </row>
     <row r="10" spans="1:27">
@@ -4255,7 +4283,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="C10" s="1">
         <v>10</v>
@@ -4311,16 +4339,16 @@
       <c r="V10" s="1"/>
       <c r="W10" s="26"/>
       <c r="X10" s="27" t="s">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="Y10" s="1" t="s">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="Z10" s="1" t="s">
-        <v>393</v>
+        <v>400</v>
       </c>
       <c r="AA10" s="26" t="s">
-        <v>394</v>
+        <v>401</v>
       </c>
     </row>
     <row r="11" spans="1:27">
@@ -4328,7 +4356,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="C11" s="1">
         <v>10</v>
@@ -4384,16 +4412,16 @@
       <c r="V11" s="1"/>
       <c r="W11" s="26"/>
       <c r="X11" s="27" t="s">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="Y11" s="1" t="s">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="Z11" s="1" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="AA11" s="26" t="s">
-        <v>398</v>
+        <v>405</v>
       </c>
     </row>
     <row r="12" spans="1:27">
@@ -4401,7 +4429,7 @@
         <v>9</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="C12" s="1">
         <v>10</v>
@@ -4457,16 +4485,16 @@
       <c r="V12" s="1"/>
       <c r="W12" s="26"/>
       <c r="X12" s="27" t="s">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="Y12" s="1" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="Z12" s="1" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="AA12" s="26" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
     </row>
     <row r="13" spans="1:27">
@@ -4474,7 +4502,7 @@
         <v>10</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="C13" s="1">
         <v>10</v>
@@ -4530,16 +4558,16 @@
       <c r="V13" s="1"/>
       <c r="W13" s="26"/>
       <c r="X13" s="27" t="s">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="Y13" s="1" t="s">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="Z13" s="1" t="s">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="AA13" s="26" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
     </row>
     <row r="14" spans="1:27">
@@ -4547,7 +4575,7 @@
         <v>11</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="C14" s="1">
         <v>10</v>
@@ -4603,16 +4631,16 @@
       <c r="V14" s="1"/>
       <c r="W14" s="26"/>
       <c r="X14" s="27" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="Y14" s="1" t="s">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="Z14" s="1" t="s">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="AA14" s="26" t="s">
-        <v>412</v>
+        <v>419</v>
       </c>
     </row>
     <row r="15" spans="1:27">
@@ -4620,7 +4648,7 @@
         <v>12</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="C15" s="1">
         <v>10</v>
@@ -4676,16 +4704,16 @@
       <c r="V15" s="1"/>
       <c r="W15" s="26"/>
       <c r="X15" s="27" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="Y15" s="1" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="Z15" s="1" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="AA15" s="26" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
     </row>
     <row r="16" spans="1:27">
@@ -4693,7 +4721,7 @@
         <v>13</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C16" s="1">
         <v>10</v>
@@ -4749,16 +4777,16 @@
       <c r="V16" s="1"/>
       <c r="W16" s="26"/>
       <c r="X16" s="27" t="s">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="Y16" s="1" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="Z16" s="1" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="AA16" s="26" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
     </row>
     <row r="17" spans="1:27">
@@ -4766,7 +4794,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="C17" s="1">
         <v>10</v>
@@ -4822,16 +4850,16 @@
       <c r="V17" s="1"/>
       <c r="W17" s="26"/>
       <c r="X17" s="27" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="Y17" s="1" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="Z17" s="1" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="AA17" s="26" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
     </row>
     <row r="18" spans="1:27">
@@ -4839,7 +4867,7 @@
         <v>15</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="C18" s="1">
         <v>10</v>
@@ -4895,16 +4923,16 @@
       <c r="V18" s="1"/>
       <c r="W18" s="26"/>
       <c r="X18" s="27" t="s">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="Y18" s="1" t="s">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="Z18" s="1" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="AA18" s="26" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
     </row>
     <row r="19" spans="1:27">
@@ -4912,7 +4940,7 @@
         <v>16</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c r="C19" s="1">
         <v>10</v>
@@ -4968,16 +4996,16 @@
       <c r="V19" s="1"/>
       <c r="W19" s="26"/>
       <c r="X19" s="27" t="s">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="Y19" s="1" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="Z19" s="1" t="s">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="AA19" s="26" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
     </row>
     <row r="20" spans="1:27">
@@ -4985,7 +5013,7 @@
         <v>17</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="C20" s="1">
         <v>10</v>
@@ -5041,16 +5069,16 @@
       <c r="V20" s="1"/>
       <c r="W20" s="26"/>
       <c r="X20" s="27" t="s">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="Y20" s="1" t="s">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c r="Z20" s="1" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="AA20" s="26" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
     </row>
     <row r="21" spans="1:27">
@@ -5058,7 +5086,7 @@
         <v>18</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="C21" s="1">
         <v>10</v>
@@ -5114,16 +5142,16 @@
       <c r="V21" s="1"/>
       <c r="W21" s="26"/>
       <c r="X21" s="27" t="s">
-        <v>439</v>
+        <v>446</v>
       </c>
       <c r="Y21" s="1" t="s">
-        <v>440</v>
+        <v>447</v>
       </c>
       <c r="Z21" s="1" t="s">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="AA21" s="26" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
     </row>
     <row r="22" spans="1:27">
@@ -5131,7 +5159,7 @@
         <v>19</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="C22" s="1">
         <v>10</v>
@@ -5187,16 +5215,16 @@
       <c r="V22" s="1"/>
       <c r="W22" s="26"/>
       <c r="X22" s="27" t="s">
-        <v>443</v>
+        <v>450</v>
       </c>
       <c r="Y22" s="1" t="s">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="Z22" s="1" t="s">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="AA22" s="26" t="s">
-        <v>446</v>
+        <v>453</v>
       </c>
     </row>
     <row r="23" spans="1:27">
@@ -5204,7 +5232,7 @@
         <v>20</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="C23" s="1">
         <v>10</v>
@@ -5260,16 +5288,16 @@
       <c r="V23" s="1"/>
       <c r="W23" s="26"/>
       <c r="X23" s="27" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="Y23" s="1" t="s">
-        <v>449</v>
+        <v>456</v>
       </c>
       <c r="Z23" s="1" t="s">
-        <v>450</v>
+        <v>457</v>
       </c>
       <c r="AA23" s="26" t="s">
-        <v>451</v>
+        <v>458</v>
       </c>
     </row>
     <row r="24" spans="1:27">
@@ -5277,7 +5305,7 @@
         <v>21</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>452</v>
+        <v>459</v>
       </c>
       <c r="C24" s="1">
         <v>10</v>
@@ -5333,16 +5361,16 @@
       <c r="V24" s="1"/>
       <c r="W24" s="26"/>
       <c r="X24" s="27" t="s">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="Y24" s="1" t="s">
-        <v>454</v>
+        <v>461</v>
       </c>
       <c r="Z24" s="1" t="s">
-        <v>455</v>
+        <v>462</v>
       </c>
       <c r="AA24" s="26" t="s">
-        <v>456</v>
+        <v>463</v>
       </c>
     </row>
     <row r="25" spans="1:27">
@@ -5350,7 +5378,7 @@
         <v>22</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="C25" s="1">
         <v>10</v>
@@ -5406,16 +5434,16 @@
       <c r="V25" s="1"/>
       <c r="W25" s="26"/>
       <c r="X25" s="27" t="s">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="Y25" s="1" t="s">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="Z25" s="1" t="s">
-        <v>460</v>
+        <v>467</v>
       </c>
       <c r="AA25" s="26" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
     </row>
     <row r="26" spans="1:27">
@@ -5423,7 +5451,7 @@
         <v>23</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>461</v>
+        <v>468</v>
       </c>
       <c r="C26" s="1">
         <v>10</v>
@@ -5479,16 +5507,16 @@
       <c r="V26" s="1"/>
       <c r="W26" s="26"/>
       <c r="X26" s="27" t="s">
-        <v>462</v>
+        <v>469</v>
       </c>
       <c r="Y26" s="1" t="s">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="Z26" s="1" t="s">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="AA26" s="26" t="s">
-        <v>465</v>
+        <v>472</v>
       </c>
     </row>
     <row r="27" spans="1:27">
@@ -5496,7 +5524,7 @@
         <v>24</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>466</v>
+        <v>473</v>
       </c>
       <c r="C27" s="1">
         <v>10</v>
@@ -5552,16 +5580,16 @@
       <c r="V27" s="1"/>
       <c r="W27" s="26"/>
       <c r="X27" s="27" t="s">
-        <v>467</v>
+        <v>474</v>
       </c>
       <c r="Y27" s="1" t="s">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="Z27" s="1" t="s">
-        <v>469</v>
+        <v>476</v>
       </c>
       <c r="AA27" s="26" t="s">
-        <v>470</v>
+        <v>477</v>
       </c>
     </row>
     <row r="28" spans="1:27">
@@ -5569,7 +5597,7 @@
         <v>25</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>471</v>
+        <v>478</v>
       </c>
       <c r="C28" s="1">
         <v>10</v>
@@ -5625,16 +5653,16 @@
       <c r="V28" s="1"/>
       <c r="W28" s="26"/>
       <c r="X28" s="27" t="s">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="Y28" s="1" t="s">
-        <v>473</v>
+        <v>480</v>
       </c>
       <c r="Z28" s="1" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="AA28" s="26" t="s">
-        <v>475</v>
+        <v>482</v>
       </c>
     </row>
     <row r="29" spans="1:27">
@@ -5642,7 +5670,7 @@
         <v>26</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>476</v>
+        <v>483</v>
       </c>
       <c r="C29" s="1">
         <v>10</v>
@@ -5698,16 +5726,16 @@
       <c r="V29" s="1"/>
       <c r="W29" s="26"/>
       <c r="X29" s="27" t="s">
-        <v>477</v>
+        <v>484</v>
       </c>
       <c r="Y29" s="1" t="s">
-        <v>478</v>
+        <v>485</v>
       </c>
       <c r="Z29" s="1" t="s">
-        <v>479</v>
+        <v>486</v>
       </c>
       <c r="AA29" s="26" t="s">
-        <v>480</v>
+        <v>487</v>
       </c>
     </row>
     <row r="30" spans="1:27">
@@ -5715,7 +5743,7 @@
         <v>27</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>481</v>
+        <v>488</v>
       </c>
       <c r="C30" s="1">
         <v>10</v>
@@ -5771,16 +5799,16 @@
       <c r="V30" s="1"/>
       <c r="W30" s="26"/>
       <c r="X30" s="27" t="s">
-        <v>482</v>
+        <v>489</v>
       </c>
       <c r="Y30" s="1" t="s">
-        <v>483</v>
+        <v>490</v>
       </c>
       <c r="Z30" s="1" t="s">
-        <v>484</v>
+        <v>491</v>
       </c>
       <c r="AA30" s="26" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
     </row>
     <row r="31" spans="1:27">
@@ -5788,7 +5816,7 @@
         <v>28</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>485</v>
+        <v>492</v>
       </c>
       <c r="C31" s="1">
         <v>10</v>
@@ -5844,16 +5872,16 @@
       <c r="V31" s="1"/>
       <c r="W31" s="26"/>
       <c r="X31" s="27" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="Y31" s="1" t="s">
-        <v>487</v>
+        <v>494</v>
       </c>
       <c r="Z31" s="1" t="s">
-        <v>488</v>
+        <v>495</v>
       </c>
       <c r="AA31" s="26" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
     </row>
     <row r="32" spans="1:27">
@@ -5861,7 +5889,7 @@
         <v>29</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>489</v>
+        <v>496</v>
       </c>
       <c r="C32" s="1">
         <v>10</v>
@@ -5917,16 +5945,16 @@
       <c r="V32" s="1"/>
       <c r="W32" s="26"/>
       <c r="X32" s="27" t="s">
-        <v>490</v>
+        <v>497</v>
       </c>
       <c r="Y32" s="1" t="s">
-        <v>491</v>
+        <v>498</v>
       </c>
       <c r="Z32" s="1" t="s">
-        <v>492</v>
+        <v>499</v>
       </c>
       <c r="AA32" s="26" t="s">
-        <v>493</v>
+        <v>500</v>
       </c>
     </row>
     <row r="33" spans="1:27">
@@ -5934,7 +5962,7 @@
         <v>30</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>494</v>
+        <v>501</v>
       </c>
       <c r="C33" s="1">
         <v>10</v>
@@ -5990,16 +6018,16 @@
       <c r="V33" s="1"/>
       <c r="W33" s="26"/>
       <c r="X33" s="27" t="s">
-        <v>495</v>
+        <v>502</v>
       </c>
       <c r="Y33" s="1" t="s">
-        <v>496</v>
+        <v>503</v>
       </c>
       <c r="Z33" s="1" t="s">
-        <v>497</v>
+        <v>504</v>
       </c>
       <c r="AA33" s="26" t="s">
-        <v>498</v>
+        <v>505</v>
       </c>
     </row>
     <row r="34" spans="1:27">
@@ -6007,7 +6035,7 @@
         <v>31</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>499</v>
+        <v>506</v>
       </c>
       <c r="C34" s="1">
         <v>10</v>
@@ -6063,16 +6091,16 @@
       <c r="V34" s="1"/>
       <c r="W34" s="26"/>
       <c r="X34" s="27" t="s">
-        <v>500</v>
+        <v>507</v>
       </c>
       <c r="Y34" s="1" t="s">
-        <v>501</v>
+        <v>508</v>
       </c>
       <c r="Z34" s="1" t="s">
-        <v>502</v>
+        <v>509</v>
       </c>
       <c r="AA34" s="26" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
     </row>
     <row r="35" spans="1:27">
@@ -6080,7 +6108,7 @@
         <v>32</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>503</v>
+        <v>510</v>
       </c>
       <c r="C35" s="1">
         <v>10</v>
@@ -6136,16 +6164,16 @@
       <c r="V35" s="1"/>
       <c r="W35" s="26"/>
       <c r="X35" s="27" t="s">
-        <v>504</v>
+        <v>511</v>
       </c>
       <c r="Y35" s="1" t="s">
-        <v>505</v>
+        <v>512</v>
       </c>
       <c r="Z35" s="1" t="s">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="AA35" s="26" t="s">
-        <v>507</v>
+        <v>514</v>
       </c>
     </row>
     <row r="36" spans="1:27">
@@ -6153,7 +6181,7 @@
         <v>33</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>508</v>
+        <v>515</v>
       </c>
       <c r="C36" s="1">
         <v>10</v>
@@ -6209,16 +6237,16 @@
       <c r="V36" s="1"/>
       <c r="W36" s="26"/>
       <c r="X36" s="27" t="s">
-        <v>509</v>
+        <v>516</v>
       </c>
       <c r="Y36" s="1" t="s">
-        <v>510</v>
+        <v>517</v>
       </c>
       <c r="Z36" s="1" t="s">
-        <v>511</v>
+        <v>518</v>
       </c>
       <c r="AA36" s="26" t="s">
-        <v>512</v>
+        <v>519</v>
       </c>
     </row>
     <row r="37" spans="1:27">
@@ -6226,7 +6254,7 @@
         <v>34</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>513</v>
+        <v>520</v>
       </c>
       <c r="C37" s="1">
         <v>10</v>
@@ -6282,16 +6310,16 @@
       <c r="V37" s="1"/>
       <c r="W37" s="26"/>
       <c r="X37" s="27" t="s">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="Y37" s="1" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="Z37" s="1" t="s">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="AA37" s="26" t="s">
-        <v>517</v>
+        <v>524</v>
       </c>
     </row>
     <row r="38" spans="1:27">
@@ -6299,7 +6327,7 @@
         <v>35</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="C38" s="1">
         <v>10</v>
@@ -6355,16 +6383,16 @@
       <c r="V38" s="1"/>
       <c r="W38" s="26"/>
       <c r="X38" s="27" t="s">
-        <v>519</v>
+        <v>526</v>
       </c>
       <c r="Y38" s="1" t="s">
-        <v>520</v>
+        <v>527</v>
       </c>
       <c r="Z38" s="1" t="s">
-        <v>521</v>
+        <v>528</v>
       </c>
       <c r="AA38" s="26" t="s">
-        <v>522</v>
+        <v>529</v>
       </c>
     </row>
     <row r="39" spans="1:27">
@@ -6372,7 +6400,7 @@
         <v>36</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>523</v>
+        <v>530</v>
       </c>
       <c r="C39" s="1">
         <v>10</v>
@@ -6428,16 +6456,16 @@
       <c r="V39" s="1"/>
       <c r="W39" s="26"/>
       <c r="X39" s="27" t="s">
-        <v>524</v>
+        <v>531</v>
       </c>
       <c r="Y39" s="1" t="s">
-        <v>525</v>
+        <v>532</v>
       </c>
       <c r="Z39" s="1" t="s">
-        <v>526</v>
+        <v>533</v>
       </c>
       <c r="AA39" s="26" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
     </row>
     <row r="40" spans="1:27">
@@ -6445,7 +6473,7 @@
         <v>37</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="C40" s="1">
         <v>10</v>
@@ -6501,16 +6529,16 @@
       <c r="V40" s="1"/>
       <c r="W40" s="26"/>
       <c r="X40" s="27" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="Y40" s="1" t="s">
-        <v>530</v>
+        <v>537</v>
       </c>
       <c r="Z40" s="1" t="s">
-        <v>531</v>
+        <v>538</v>
       </c>
       <c r="AA40" s="26" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
     </row>
     <row r="41" ht="14.25" spans="1:27">
@@ -6518,7 +6546,7 @@
         <v>38</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>532</v>
+        <v>539</v>
       </c>
       <c r="C41" s="12">
         <v>10</v>
@@ -6574,16 +6602,16 @@
       <c r="V41" s="12"/>
       <c r="W41" s="29"/>
       <c r="X41" s="30" t="s">
-        <v>533</v>
+        <v>540</v>
       </c>
       <c r="Y41" s="12" t="s">
-        <v>534</v>
+        <v>541</v>
       </c>
       <c r="Z41" s="12" t="s">
-        <v>535</v>
+        <v>542</v>
       </c>
       <c r="AA41" s="29" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
     </row>
   </sheetData>
@@ -6647,7 +6675,7 @@
         <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>536</v>
+        <v>543</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -6655,7 +6683,7 @@
         <v>2</v>
       </c>
       <c r="B13" t="s">
-        <v>537</v>
+        <v>544</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -6663,7 +6691,7 @@
         <v>3</v>
       </c>
       <c r="B14" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -6671,16 +6699,16 @@
         <v>4</v>
       </c>
       <c r="B15" t="s">
-        <v>539</v>
+        <v>546</v>
       </c>
       <c r="F15" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H15" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I15" t="s">
-        <v>540</v>
+        <v>547</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -6688,172 +6716,172 @@
         <v>5</v>
       </c>
       <c r="B16" t="s">
-        <v>541</v>
+        <v>548</v>
       </c>
       <c r="F16" t="s">
-        <v>540</v>
+        <v>547</v>
       </c>
       <c r="H16" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="I16" t="s">
-        <v>542</v>
+        <v>549</v>
       </c>
     </row>
     <row r="17" spans="6:9">
       <c r="F17" t="s">
-        <v>51</v>
+        <v>550</v>
       </c>
       <c r="H17" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="I17" t="s">
-        <v>543</v>
+        <v>551</v>
       </c>
     </row>
     <row r="18" spans="2:9">
       <c r="B18" t="s">
-        <v>544</v>
+        <v>552</v>
       </c>
       <c r="F18" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="H18" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I18" t="s">
-        <v>545</v>
+        <v>553</v>
       </c>
     </row>
     <row r="19" spans="6:9">
       <c r="F19" t="s">
-        <v>542</v>
+        <v>549</v>
       </c>
       <c r="H19" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I19" t="s">
-        <v>546</v>
+        <v>554</v>
       </c>
     </row>
     <row r="20" spans="6:8">
       <c r="F20" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H20">
-        <f>IF('intent|意图'!F20='intent|意图'!F19,#REF!&amp;"*"&amp;'intent|意图'!D20,'intent|意图'!D20)</f>
+        <f>IF('intent|意图'!F22='intent|意图'!F21,#REF!&amp;"*"&amp;'intent|意图'!D22,'intent|意图'!D22)</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="6:8">
       <c r="F21" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H21">
-        <f>IF('intent|意图'!F21='intent|意图'!F20,H20&amp;"*"&amp;'intent|意图'!D21,'intent|意图'!D21)</f>
+        <f>IF('intent|意图'!F23='intent|意图'!F22,H20&amp;"*"&amp;'intent|意图'!D23,'intent|意图'!D23)</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="6:8">
       <c r="F22" t="s">
-        <v>543</v>
+        <v>551</v>
       </c>
       <c r="H22">
-        <f>IF('intent|意图'!F22='intent|意图'!F21,H21&amp;"*"&amp;'intent|意图'!D22,'intent|意图'!D22)</f>
+        <f>IF('intent|意图'!F24='intent|意图'!F23,H21&amp;"*"&amp;'intent|意图'!D24,'intent|意图'!D24)</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="6:8">
       <c r="F23" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H23">
-        <f>IF('intent|意图'!F23='intent|意图'!F22,H22&amp;"*"&amp;'intent|意图'!D23,'intent|意图'!D23)</f>
+        <f>IF('intent|意图'!F25='intent|意图'!F24,H22&amp;"*"&amp;'intent|意图'!D25,'intent|意图'!D25)</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="6:8">
       <c r="F24" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H24">
-        <f>IF('intent|意图'!F15='intent|意图'!F23,H23&amp;"*"&amp;'intent|意图'!D15,'intent|意图'!D15)</f>
+        <f>IF('intent|意图'!F17='intent|意图'!F25,H23&amp;"*"&amp;'intent|意图'!D17,'intent|意图'!D17)</f>
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="6:8">
       <c r="F25" t="s">
-        <v>545</v>
+        <v>553</v>
       </c>
       <c r="H25">
-        <f>IF('intent|意图'!F16='intent|意图'!F15,H24&amp;"*"&amp;'intent|意图'!D16,'intent|意图'!D16)</f>
+        <f>IF('intent|意图'!F18='intent|意图'!F17,H24&amp;"*"&amp;'intent|意图'!D18,'intent|意图'!D18)</f>
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="6:8">
       <c r="F26" t="s">
-        <v>54</v>
+        <v>555</v>
       </c>
       <c r="H26">
-        <f>IF('intent|意图'!F17='intent|意图'!F16,H25&amp;"*"&amp;'intent|意图'!D17,'intent|意图'!D17)</f>
+        <f>IF('intent|意图'!F19='intent|意图'!F18,H25&amp;"*"&amp;'intent|意图'!D19,'intent|意图'!D19)</f>
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="6:8">
       <c r="F27" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H27">
-        <f>IF('intent|意图'!F24='intent|意图'!F17,H26&amp;"*"&amp;'intent|意图'!D24,'intent|意图'!D24)</f>
+        <f>IF('intent|意图'!F26='intent|意图'!F19,H26&amp;"*"&amp;'intent|意图'!D26,'intent|意图'!D26)</f>
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="6:8">
       <c r="F28" t="s">
-        <v>546</v>
+        <v>554</v>
       </c>
       <c r="H28">
-        <f>IF('intent|意图'!F25='intent|意图'!F24,H27&amp;"*"&amp;'intent|意图'!D25,'intent|意图'!D25)</f>
+        <f>IF('intent|意图'!F27='intent|意图'!F26,H27&amp;"*"&amp;'intent|意图'!D27,'intent|意图'!D27)</f>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="6:8">
       <c r="F29" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H29">
-        <f>IF('intent|意图'!F26='intent|意图'!F25,H28&amp;"*"&amp;'intent|意图'!D26,'intent|意图'!D26)</f>
+        <f>IF('intent|意图'!F28='intent|意图'!F27,H28&amp;"*"&amp;'intent|意图'!D28,'intent|意图'!D28)</f>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="2:2">
       <c r="B30" t="s">
-        <v>544</v>
+        <v>552</v>
       </c>
     </row>
     <row r="42" spans="2:2">
       <c r="B42" t="s">
-        <v>544</v>
+        <v>552</v>
       </c>
     </row>
     <row r="50" spans="2:2">
       <c r="B50" t="s">
-        <v>547</v>
+        <v>556</v>
       </c>
     </row>
     <row r="54" spans="2:2">
       <c r="B54" t="s">
-        <v>544</v>
+        <v>552</v>
       </c>
     </row>
     <row r="62" spans="2:2">
       <c r="B62" t="s">
-        <v>547</v>
+        <v>556</v>
       </c>
     </row>
     <row r="66" spans="2:2">
       <c r="B66" t="s">
-        <v>544</v>
+        <v>552</v>
       </c>
     </row>
   </sheetData>
@@ -6946,7 +6974,7 @@
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultColWidth="8.86666666666667" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="8.33333333333333" style="71" customWidth="1"/>
+    <col min="1" max="1" width="8.33333333333333" style="67" customWidth="1"/>
     <col min="2" max="2" width="11.8666666666667" customWidth="1"/>
     <col min="3" max="3" width="31.4666666666667" customWidth="1"/>
   </cols>
@@ -6964,7 +6992,7 @@
       <c r="D1" s="5"/>
       <c r="E1" s="5"/>
     </row>
-    <row r="2" s="70" customFormat="1" spans="1:5">
+    <row r="2" s="66" customFormat="1" spans="1:5">
       <c r="A2" s="43" t="s">
         <v>5</v>
       </c>
@@ -7029,8 +7057,8 @@
   <cols>
     <col min="1" max="1" width="11.5" customWidth="1"/>
     <col min="2" max="2" width="11.4666666666667" style="21" customWidth="1"/>
-    <col min="3" max="3" width="51.5" customWidth="1"/>
-    <col min="4" max="4" width="18.25" customWidth="1"/>
+    <col min="3" max="3" width="18.25" customWidth="1"/>
+    <col min="4" max="4" width="61.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -7068,11 +7096,11 @@
       <c r="B3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>43</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -7082,72 +7110,72 @@
       <c r="B4" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="40" t="str">
+        <f>"enemy_"&amp;A4</f>
+        <v>enemy_slime</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="D4" s="40" t="str">
-        <f t="shared" ref="D4:D8" si="0">"enemy_"&amp;A4</f>
-        <v>enemy_slime</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="B5" s="40" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="40" t="str">
+        <f>"enemy_"&amp;A5</f>
+        <v>enemy_mushroom</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="D5" s="40" t="str">
-        <f t="shared" si="0"/>
-        <v>enemy_flying_eye</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B6" s="40" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="40" t="str">
+        <f>"enemy_"&amp;A6</f>
+        <v>enemy_skeleton</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="D6" s="40" t="str">
-        <f t="shared" si="0"/>
-        <v>enemy_goblin</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B7" s="40" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="40" t="str">
+        <f>"enemy_"&amp;A7</f>
+        <v>enemy_flying_eye</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>54</v>
-      </c>
-      <c r="D7" s="40" t="str">
-        <f t="shared" si="0"/>
-        <v>enemy_mushroom</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B8" s="40" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="40" t="str">
+        <f>"enemy_"&amp;A8</f>
+        <v>enemy_goblin</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="D8" s="40" t="str">
-        <f t="shared" si="0"/>
-        <v>enemy_skeleton</v>
       </c>
     </row>
   </sheetData>
@@ -7230,7 +7258,7 @@
       <c r="H2" s="43" t="s">
         <v>71</v>
       </c>
-      <c r="I2" s="57" t="s">
+      <c r="I2" s="56" t="s">
         <v>72</v>
       </c>
       <c r="J2" s="21" t="s">
@@ -7371,723 +7399,833 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="21.25" customWidth="1"/>
-    <col min="2" max="2" width="9.06666666666667" style="63"/>
-    <col min="4" max="6" width="9.06666666666667" style="63"/>
-    <col min="7" max="7" width="62" customWidth="1"/>
-    <col min="8" max="8" width="67.125" customWidth="1"/>
+    <col min="2" max="2" width="9.06666666666667" style="59"/>
+    <col min="4" max="7" width="9.06666666666667" style="59"/>
+    <col min="8" max="8" width="62" customWidth="1"/>
+    <col min="9" max="9" width="67.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="64" t="s">
+      <c r="B1" s="60" t="s">
         <v>93</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="64" t="s">
+      <c r="D1" s="60" t="s">
         <v>94</v>
       </c>
-      <c r="E1" s="64" t="s">
+      <c r="E1" s="60" t="s">
         <v>95</v>
       </c>
-      <c r="F1" s="64" t="s">
+      <c r="F1" s="60" t="s">
         <v>96</v>
       </c>
-      <c r="G1" s="56" t="s">
+      <c r="G1" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="H1" s="55" t="s">
         <v>97</v>
       </c>
-      <c r="H1" s="56" t="s">
+      <c r="I1" s="55" t="s">
         <v>60</v>
       </c>
-      <c r="I1" s="56" t="s">
+      <c r="J1" s="55" t="s">
         <v>98</v>
       </c>
-      <c r="J1" s="56" t="s">
+      <c r="K1" s="55" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="2" ht="27" spans="1:11">
+      <c r="A2" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="60" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="64" t="s">
+      <c r="C2" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="D2" s="60" t="s">
         <v>101</v>
       </c>
-      <c r="D2" s="64" t="s">
+      <c r="E2" s="60" t="s">
         <v>102</v>
       </c>
-      <c r="E2" s="64" t="s">
+      <c r="F2" s="60" t="s">
         <v>103</v>
       </c>
-      <c r="F2" s="64" t="s">
+      <c r="G2" s="43" t="s">
+        <v>71</v>
+      </c>
+      <c r="H2" s="55" t="s">
         <v>104</v>
       </c>
-      <c r="G2" s="56" t="s">
+      <c r="I2" s="55" t="s">
         <v>105</v>
       </c>
-      <c r="H2" s="56" t="s">
+      <c r="J2" s="55" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="56" t="s">
+      <c r="K2" s="55" t="s">
         <v>107</v>
       </c>
-      <c r="J2" s="56" t="s">
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="60" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="60" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="60" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="64" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="64" t="s">
+      <c r="F3" s="60" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="64" t="s">
+      <c r="G3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="55" t="s">
+        <v>10</v>
+      </c>
+      <c r="I3" s="55" t="s">
+        <v>74</v>
+      </c>
+      <c r="J3" s="55" t="s">
+        <v>11</v>
+      </c>
+      <c r="K3" s="55" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="F3" s="64" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" s="56" t="s">
-        <v>10</v>
-      </c>
-      <c r="H3" s="56" t="s">
-        <v>74</v>
-      </c>
-      <c r="I3" s="56" t="s">
-        <v>11</v>
-      </c>
-      <c r="J3" s="56" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="1" t="s">
+      <c r="B4" s="61"/>
+      <c r="C4" s="40" t="s">
         <v>110</v>
       </c>
-      <c r="B4" s="65"/>
-      <c r="C4" s="40" t="s">
+      <c r="D4" s="61">
+        <v>1</v>
+      </c>
+      <c r="E4" s="61"/>
+      <c r="F4" s="61"/>
+      <c r="G4" s="61"/>
+      <c r="H4" s="40" t="s">
         <v>111</v>
       </c>
-      <c r="D4" s="65">
-        <v>1</v>
-      </c>
-      <c r="E4" s="65"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="40" t="s">
+      <c r="I4" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="J4" s="1">
+        <v>8</v>
+      </c>
+      <c r="K4" s="1"/>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="I4" s="1">
-        <v>8</v>
-      </c>
-      <c r="J4" s="1"/>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="1" t="s">
+      <c r="B5" s="61"/>
+      <c r="C5" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B5" s="65"/>
-      <c r="C5" s="1" t="s">
+      <c r="D5" s="61">
+        <v>2</v>
+      </c>
+      <c r="E5" s="61"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="61"/>
+      <c r="H5" s="40" t="s">
         <v>115</v>
       </c>
-      <c r="D5" s="65">
-        <v>2</v>
-      </c>
-      <c r="E5" s="65"/>
-      <c r="F5" s="65"/>
-      <c r="G5" s="40" t="s">
+      <c r="I5" s="40" t="s">
         <v>116</v>
       </c>
-      <c r="H5" s="40" t="s">
+      <c r="J5" s="1">
+        <v>3</v>
+      </c>
+      <c r="K5" s="1"/>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="I5" s="1">
-        <v>3</v>
-      </c>
-      <c r="J5" s="1"/>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="B6" s="65"/>
+      <c r="B6" s="61"/>
       <c r="C6" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="D6" s="65">
+      <c r="D6" s="61">
         <v>3</v>
       </c>
-      <c r="E6" s="65"/>
-      <c r="F6" s="65"/>
-      <c r="G6" s="40" t="s">
+      <c r="E6" s="61"/>
+      <c r="F6" s="61"/>
+      <c r="G6" s="61"/>
+      <c r="H6" s="40" t="s">
+        <v>118</v>
+      </c>
+      <c r="I6" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="J6" s="1">
+        <v>0</v>
+      </c>
+      <c r="K6" s="1"/>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="I6" s="1">
-        <v>0</v>
-      </c>
-      <c r="J6" s="1"/>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="1" t="s">
+      <c r="B7" s="61"/>
+      <c r="C7" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B7" s="65"/>
-      <c r="C7" s="1" t="s">
+      <c r="D7" s="61">
+        <v>4</v>
+      </c>
+      <c r="E7" s="61"/>
+      <c r="F7" s="61"/>
+      <c r="G7" s="61"/>
+      <c r="H7" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="D7" s="65">
-        <v>4</v>
-      </c>
-      <c r="E7" s="65"/>
-      <c r="F7" s="65"/>
-      <c r="G7" s="1" t="s">
+      <c r="I7" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="J7" s="1">
+        <v>0</v>
+      </c>
+      <c r="K7" s="1"/>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="I7" s="1">
-        <v>0</v>
-      </c>
-      <c r="J7" s="1"/>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="1" t="s">
+      <c r="B8" s="61"/>
+      <c r="C8" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="B8" s="65"/>
-      <c r="C8" s="1" t="s">
+      <c r="D8" s="61">
+        <v>5</v>
+      </c>
+      <c r="E8" s="61"/>
+      <c r="F8" s="61"/>
+      <c r="G8" s="61"/>
+      <c r="H8" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="D8" s="65">
+      <c r="I8" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="J8" s="1">
+        <v>0</v>
+      </c>
+      <c r="K8" s="1"/>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B9" s="61"/>
+      <c r="C9" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D9" s="61">
+        <v>6</v>
+      </c>
+      <c r="E9" s="61"/>
+      <c r="F9" s="61"/>
+      <c r="G9" s="61"/>
+      <c r="H9" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="J9" s="1">
+        <v>0</v>
+      </c>
+      <c r="K9" s="1"/>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B10" s="61"/>
+      <c r="C10" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D10" s="61">
+        <v>7</v>
+      </c>
+      <c r="E10" s="61"/>
+      <c r="F10" s="61"/>
+      <c r="G10" s="61"/>
+      <c r="H10" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="J10" s="1">
+        <v>0</v>
+      </c>
+      <c r="K10" s="1"/>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B11" s="61"/>
+      <c r="C11" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D11" s="61">
+        <v>8</v>
+      </c>
+      <c r="E11" s="61"/>
+      <c r="F11" s="61"/>
+      <c r="G11" s="61"/>
+      <c r="H11" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="J11" s="1">
+        <v>0</v>
+      </c>
+      <c r="K11" s="1"/>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B12" s="61"/>
+      <c r="C12" s="40" t="s">
+        <v>110</v>
+      </c>
+      <c r="D12" s="61">
+        <v>1</v>
+      </c>
+      <c r="E12" s="61">
+        <v>2</v>
+      </c>
+      <c r="F12" s="61">
+        <v>0</v>
+      </c>
+      <c r="G12" s="61" t="s">
+        <v>3</v>
+      </c>
+      <c r="H12" s="40" t="s">
+        <v>141</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="J12" s="1">
         <v>5</v>
       </c>
-      <c r="E8" s="65"/>
-      <c r="F8" s="65"/>
-      <c r="G8" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="I8" s="1">
-        <v>0</v>
-      </c>
-      <c r="J8" s="1"/>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="B9" s="65"/>
-      <c r="C9" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="D9" s="65">
-        <v>6</v>
-      </c>
-      <c r="E9" s="65"/>
-      <c r="F9" s="65"/>
-      <c r="G9" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="I9" s="1">
-        <v>0</v>
-      </c>
-      <c r="J9" s="1"/>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B10" s="65"/>
-      <c r="C10" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="D10" s="65">
-        <v>7</v>
-      </c>
-      <c r="E10" s="65"/>
-      <c r="F10" s="65"/>
-      <c r="G10" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="I10" s="1">
-        <v>0</v>
-      </c>
-      <c r="J10" s="1"/>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="B11" s="65"/>
-      <c r="C11" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="D11" s="65">
-        <v>8</v>
-      </c>
-      <c r="E11" s="65"/>
-      <c r="F11" s="65"/>
-      <c r="G11" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="H11" s="1" t="s">
+      <c r="K12" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="I11" s="1">
-        <v>0</v>
-      </c>
-      <c r="J11" s="1"/>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="46" t="s">
-        <v>141</v>
-      </c>
-      <c r="B12" s="47" t="s">
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" s="46" t="s">
+        <v>142</v>
+      </c>
+      <c r="B13" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="47" t="s">
-        <v>142</v>
-      </c>
-      <c r="D12" s="66"/>
-      <c r="E12" s="66">
-        <v>1</v>
-      </c>
-      <c r="F12" s="66">
-        <v>0</v>
-      </c>
-      <c r="G12" s="47" t="s">
+      <c r="C13" s="47" t="s">
         <v>143</v>
       </c>
-      <c r="H12" s="47" t="s">
+      <c r="D13" s="62"/>
+      <c r="E13" s="62">
+        <v>2</v>
+      </c>
+      <c r="F13" s="62">
+        <v>0</v>
+      </c>
+      <c r="G13" s="61" t="s">
+        <v>3</v>
+      </c>
+      <c r="H13" s="47" t="s">
         <v>144</v>
       </c>
-      <c r="I12" s="47">
-        <v>0</v>
-      </c>
-      <c r="J12" s="49"/>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" s="48" t="s">
+      <c r="I13" s="47" t="s">
         <v>145</v>
       </c>
-      <c r="B13" s="49" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13" s="49" t="s">
+      <c r="J13" s="47">
+        <v>0</v>
+      </c>
+      <c r="K13" s="49"/>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" s="48" t="s">
         <v>146</v>
-      </c>
-      <c r="D13" s="67"/>
-      <c r="E13" s="67">
-        <v>1</v>
-      </c>
-      <c r="F13" s="67">
-        <v>1</v>
-      </c>
-      <c r="G13" s="49" t="s">
-        <v>147</v>
-      </c>
-      <c r="H13" s="49" t="s">
-        <v>148</v>
-      </c>
-      <c r="I13" s="49">
-        <v>0</v>
-      </c>
-      <c r="J13" s="49"/>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="48" t="s">
-        <v>149</v>
       </c>
       <c r="B14" s="49" t="s">
         <v>14</v>
       </c>
       <c r="C14" s="49" t="s">
+        <v>147</v>
+      </c>
+      <c r="D14" s="63"/>
+      <c r="E14" s="63">
+        <v>2</v>
+      </c>
+      <c r="F14" s="63">
+        <v>1</v>
+      </c>
+      <c r="G14" s="61" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="49" t="s">
+        <v>144</v>
+      </c>
+      <c r="I14" s="49" t="s">
+        <v>148</v>
+      </c>
+      <c r="J14" s="49">
+        <v>0</v>
+      </c>
+      <c r="K14" s="49"/>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" s="48" t="s">
+        <v>149</v>
+      </c>
+      <c r="B15" s="49" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" s="49" t="s">
         <v>150</v>
       </c>
-      <c r="D14" s="67"/>
-      <c r="E14" s="67">
-        <v>1</v>
-      </c>
-      <c r="F14" s="67">
+      <c r="D15" s="63"/>
+      <c r="E15" s="63">
+        <v>1</v>
+      </c>
+      <c r="F15" s="63">
         <v>3</v>
       </c>
-      <c r="G14" s="49" t="s">
+      <c r="G15" s="61" t="s">
+        <v>3</v>
+      </c>
+      <c r="H15" s="49" t="s">
+        <v>144</v>
+      </c>
+      <c r="I15" s="49" t="s">
+        <v>116</v>
+      </c>
+      <c r="J15" s="49">
+        <v>0</v>
+      </c>
+      <c r="K15" s="49"/>
+    </row>
+    <row r="16" customFormat="1" spans="1:11">
+      <c r="A16" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="H14" s="49" t="s">
-        <v>117</v>
-      </c>
-      <c r="I14" s="49">
-        <v>0</v>
-      </c>
-      <c r="J14" s="49"/>
-    </row>
-    <row r="15" s="42" customFormat="1" spans="1:10">
-      <c r="A15" s="50" t="s">
+      <c r="B16" s="61"/>
+      <c r="C16" s="40" t="s">
+        <v>110</v>
+      </c>
+      <c r="D16" s="61">
+        <v>1</v>
+      </c>
+      <c r="E16" s="61">
+        <v>2</v>
+      </c>
+      <c r="F16" s="61">
+        <v>0</v>
+      </c>
+      <c r="G16" s="61" t="s">
+        <v>3</v>
+      </c>
+      <c r="H16" s="40" t="s">
         <v>152</v>
       </c>
-      <c r="B15" s="51" t="s">
-        <v>23</v>
-      </c>
-      <c r="C15" s="51" t="s">
+      <c r="I16" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="J16" s="1">
+        <v>8</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="17" s="42" customFormat="1" spans="1:11">
+      <c r="A17" s="50" t="s">
         <v>153</v>
-      </c>
-      <c r="D15" s="68"/>
-      <c r="E15" s="68">
-        <v>1</v>
-      </c>
-      <c r="F15" s="68">
-        <v>0</v>
-      </c>
-      <c r="G15" s="51" t="s">
-        <v>154</v>
-      </c>
-      <c r="H15" s="51" t="s">
-        <v>155</v>
-      </c>
-      <c r="I15" s="51">
-        <v>0</v>
-      </c>
-      <c r="J15" s="51"/>
-    </row>
-    <row r="16" s="42" customFormat="1" spans="1:10">
-      <c r="A16" s="50" t="s">
-        <v>156</v>
-      </c>
-      <c r="B16" s="51" t="s">
-        <v>23</v>
-      </c>
-      <c r="C16" s="51" t="s">
-        <v>157</v>
-      </c>
-      <c r="D16" s="68"/>
-      <c r="E16" s="68">
-        <v>1</v>
-      </c>
-      <c r="F16" s="68">
-        <v>1</v>
-      </c>
-      <c r="G16" s="51" t="s">
-        <v>158</v>
-      </c>
-      <c r="H16" s="51" t="s">
-        <v>132</v>
-      </c>
-      <c r="I16" s="51">
-        <v>0</v>
-      </c>
-      <c r="J16" s="51"/>
-    </row>
-    <row r="17" s="42" customFormat="1" spans="1:10">
-      <c r="A17" s="50" t="s">
-        <v>159</v>
       </c>
       <c r="B17" s="51" t="s">
         <v>23</v>
       </c>
       <c r="C17" s="51" t="s">
+        <v>154</v>
+      </c>
+      <c r="D17" s="64"/>
+      <c r="E17" s="64">
+        <v>2</v>
+      </c>
+      <c r="F17" s="64">
+        <v>0</v>
+      </c>
+      <c r="G17" s="61" t="s">
+        <v>3</v>
+      </c>
+      <c r="H17" s="51" t="s">
+        <v>144</v>
+      </c>
+      <c r="I17" s="51" t="s">
+        <v>155</v>
+      </c>
+      <c r="J17" s="51">
+        <v>0</v>
+      </c>
+      <c r="K17" s="51"/>
+    </row>
+    <row r="18" s="42" customFormat="1" spans="1:11">
+      <c r="A18" s="50" t="s">
+        <v>156</v>
+      </c>
+      <c r="B18" s="51" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" s="51" t="s">
+        <v>157</v>
+      </c>
+      <c r="D18" s="64"/>
+      <c r="E18" s="64">
+        <v>2</v>
+      </c>
+      <c r="F18" s="64">
+        <v>1</v>
+      </c>
+      <c r="G18" s="61" t="s">
+        <v>3</v>
+      </c>
+      <c r="H18" s="51" t="s">
+        <v>144</v>
+      </c>
+      <c r="I18" s="51" t="s">
+        <v>131</v>
+      </c>
+      <c r="J18" s="51">
+        <v>0</v>
+      </c>
+      <c r="K18" s="51"/>
+    </row>
+    <row r="19" s="42" customFormat="1" spans="1:11">
+      <c r="A19" s="50" t="s">
+        <v>158</v>
+      </c>
+      <c r="B19" s="51" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" s="51" t="s">
+        <v>159</v>
+      </c>
+      <c r="D19" s="64"/>
+      <c r="E19" s="64">
+        <v>1</v>
+      </c>
+      <c r="F19" s="64">
+        <v>3</v>
+      </c>
+      <c r="G19" s="61" t="s">
+        <v>3</v>
+      </c>
+      <c r="H19" s="51" t="s">
+        <v>144</v>
+      </c>
+      <c r="I19" s="51" t="s">
+        <v>135</v>
+      </c>
+      <c r="J19" s="51">
+        <v>0</v>
+      </c>
+      <c r="K19" s="51"/>
+    </row>
+    <row r="20" s="58" customFormat="1" spans="1:11">
+      <c r="A20" s="52" t="s">
         <v>160</v>
-      </c>
-      <c r="D17" s="68"/>
-      <c r="E17" s="68">
-        <v>1</v>
-      </c>
-      <c r="F17" s="68">
-        <v>3</v>
-      </c>
-      <c r="G17" s="51" t="s">
-        <v>161</v>
-      </c>
-      <c r="H17" s="51" t="s">
-        <v>136</v>
-      </c>
-      <c r="I17" s="51">
-        <v>0</v>
-      </c>
-      <c r="J17" s="51"/>
-    </row>
-    <row r="18" s="62" customFormat="1" spans="1:10">
-      <c r="A18" s="52" t="s">
-        <v>162</v>
-      </c>
-      <c r="B18" s="53" t="s">
-        <v>17</v>
-      </c>
-      <c r="C18" s="53" t="s">
-        <v>163</v>
-      </c>
-      <c r="D18" s="69"/>
-      <c r="E18" s="69">
-        <v>1</v>
-      </c>
-      <c r="F18" s="69">
-        <v>0</v>
-      </c>
-      <c r="G18" s="53" t="s">
-        <v>164</v>
-      </c>
-      <c r="H18" s="53" t="s">
-        <v>140</v>
-      </c>
-      <c r="I18" s="53">
-        <v>0</v>
-      </c>
-      <c r="J18" s="53"/>
-    </row>
-    <row r="19" s="62" customFormat="1" spans="1:10">
-      <c r="A19" s="52" t="s">
-        <v>165</v>
-      </c>
-      <c r="B19" s="53" t="s">
-        <v>17</v>
-      </c>
-      <c r="C19" s="53" t="s">
-        <v>166</v>
-      </c>
-      <c r="D19" s="69"/>
-      <c r="E19" s="69">
-        <v>1</v>
-      </c>
-      <c r="F19" s="69">
-        <v>1</v>
-      </c>
-      <c r="G19" s="53" t="s">
-        <v>167</v>
-      </c>
-      <c r="H19" s="53" t="s">
-        <v>140</v>
-      </c>
-      <c r="I19" s="53">
-        <v>0</v>
-      </c>
-      <c r="J19" s="53"/>
-    </row>
-    <row r="20" s="62" customFormat="1" spans="1:10">
-      <c r="A20" s="52" t="s">
-        <v>168</v>
       </c>
       <c r="B20" s="53" t="s">
         <v>17</v>
       </c>
       <c r="C20" s="53" t="s">
+        <v>161</v>
+      </c>
+      <c r="D20" s="65"/>
+      <c r="E20" s="65">
+        <v>1</v>
+      </c>
+      <c r="F20" s="65">
+        <v>0</v>
+      </c>
+      <c r="G20" s="65"/>
+      <c r="H20" s="53" t="s">
+        <v>162</v>
+      </c>
+      <c r="I20" s="53" t="s">
+        <v>139</v>
+      </c>
+      <c r="J20" s="53">
+        <v>0</v>
+      </c>
+      <c r="K20" s="53"/>
+    </row>
+    <row r="21" s="58" customFormat="1" spans="1:11">
+      <c r="A21" s="52" t="s">
+        <v>163</v>
+      </c>
+      <c r="B21" s="53" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" s="53" t="s">
+        <v>164</v>
+      </c>
+      <c r="D21" s="65"/>
+      <c r="E21" s="65">
+        <v>1</v>
+      </c>
+      <c r="F21" s="65">
+        <v>1</v>
+      </c>
+      <c r="G21" s="65"/>
+      <c r="H21" s="53" t="s">
+        <v>165</v>
+      </c>
+      <c r="I21" s="53" t="s">
+        <v>139</v>
+      </c>
+      <c r="J21" s="53">
+        <v>0</v>
+      </c>
+      <c r="K21" s="53"/>
+    </row>
+    <row r="22" s="58" customFormat="1" spans="1:11">
+      <c r="A22" s="52" t="s">
+        <v>166</v>
+      </c>
+      <c r="B22" s="53" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22" s="53" t="s">
+        <v>167</v>
+      </c>
+      <c r="D22" s="65"/>
+      <c r="E22" s="65">
+        <v>1</v>
+      </c>
+      <c r="F22" s="65">
+        <v>3</v>
+      </c>
+      <c r="G22" s="65"/>
+      <c r="H22" s="53" t="s">
+        <v>168</v>
+      </c>
+      <c r="I22" s="53" t="s">
+        <v>139</v>
+      </c>
+      <c r="J22" s="53">
+        <v>0</v>
+      </c>
+      <c r="K22" s="53"/>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" s="48" t="s">
         <v>169</v>
-      </c>
-      <c r="D20" s="69"/>
-      <c r="E20" s="69">
-        <v>1</v>
-      </c>
-      <c r="F20" s="69">
-        <v>3</v>
-      </c>
-      <c r="G20" s="53" t="s">
-        <v>170</v>
-      </c>
-      <c r="H20" s="53" t="s">
-        <v>140</v>
-      </c>
-      <c r="I20" s="53">
-        <v>0</v>
-      </c>
-      <c r="J20" s="53"/>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="A21" s="48" t="s">
-        <v>171</v>
-      </c>
-      <c r="B21" s="49" t="s">
-        <v>20</v>
-      </c>
-      <c r="C21" s="49" t="s">
-        <v>172</v>
-      </c>
-      <c r="D21" s="67"/>
-      <c r="E21" s="67">
-        <v>1</v>
-      </c>
-      <c r="F21" s="67">
-        <v>0</v>
-      </c>
-      <c r="G21" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="H21" s="49" t="s">
-        <v>140</v>
-      </c>
-      <c r="I21" s="49">
-        <v>0</v>
-      </c>
-      <c r="J21" s="49"/>
-    </row>
-    <row r="22" spans="1:10">
-      <c r="A22" s="48" t="s">
-        <v>174</v>
-      </c>
-      <c r="B22" s="49" t="s">
-        <v>20</v>
-      </c>
-      <c r="C22" s="49" t="s">
-        <v>175</v>
-      </c>
-      <c r="D22" s="67"/>
-      <c r="E22" s="67">
-        <v>1</v>
-      </c>
-      <c r="F22" s="67">
-        <v>1</v>
-      </c>
-      <c r="G22" s="49" t="s">
-        <v>176</v>
-      </c>
-      <c r="H22" s="49" t="s">
-        <v>140</v>
-      </c>
-      <c r="I22" s="49">
-        <v>0</v>
-      </c>
-      <c r="J22" s="49"/>
-    </row>
-    <row r="23" spans="1:10">
-      <c r="A23" s="48" t="s">
-        <v>177</v>
       </c>
       <c r="B23" s="49" t="s">
         <v>20</v>
       </c>
       <c r="C23" s="49" t="s">
+        <v>170</v>
+      </c>
+      <c r="D23" s="63"/>
+      <c r="E23" s="63">
+        <v>1</v>
+      </c>
+      <c r="F23" s="63">
+        <v>0</v>
+      </c>
+      <c r="G23" s="63"/>
+      <c r="H23" s="49" t="s">
+        <v>171</v>
+      </c>
+      <c r="I23" s="49" t="s">
+        <v>139</v>
+      </c>
+      <c r="J23" s="49">
+        <v>0</v>
+      </c>
+      <c r="K23" s="49"/>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" s="48" t="s">
+        <v>172</v>
+      </c>
+      <c r="B24" s="49" t="s">
+        <v>20</v>
+      </c>
+      <c r="C24" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="D24" s="63"/>
+      <c r="E24" s="63">
+        <v>1</v>
+      </c>
+      <c r="F24" s="63">
+        <v>1</v>
+      </c>
+      <c r="G24" s="63"/>
+      <c r="H24" s="49" t="s">
+        <v>174</v>
+      </c>
+      <c r="I24" s="49" t="s">
+        <v>139</v>
+      </c>
+      <c r="J24" s="49">
+        <v>0</v>
+      </c>
+      <c r="K24" s="49"/>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" s="48" t="s">
+        <v>175</v>
+      </c>
+      <c r="B25" s="49" t="s">
+        <v>20</v>
+      </c>
+      <c r="C25" s="49" t="s">
+        <v>176</v>
+      </c>
+      <c r="D25" s="63"/>
+      <c r="E25" s="63">
+        <v>1</v>
+      </c>
+      <c r="F25" s="63">
+        <v>3</v>
+      </c>
+      <c r="G25" s="63"/>
+      <c r="H25" s="49" t="s">
+        <v>177</v>
+      </c>
+      <c r="I25" s="49" t="s">
+        <v>139</v>
+      </c>
+      <c r="J25" s="49">
+        <v>0</v>
+      </c>
+      <c r="K25" s="49"/>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" s="48" t="s">
         <v>178</v>
       </c>
-      <c r="D23" s="67"/>
-      <c r="E23" s="67">
-        <v>1</v>
-      </c>
-      <c r="F23" s="67">
+      <c r="B26" s="49" t="s">
+        <v>26</v>
+      </c>
+      <c r="C26" s="49" t="s">
+        <v>179</v>
+      </c>
+      <c r="D26" s="63"/>
+      <c r="E26" s="63">
+        <v>1</v>
+      </c>
+      <c r="F26" s="63">
+        <v>0</v>
+      </c>
+      <c r="G26" s="63"/>
+      <c r="H26" s="49" t="s">
+        <v>180</v>
+      </c>
+      <c r="I26" s="49" t="s">
+        <v>139</v>
+      </c>
+      <c r="J26" s="49">
+        <v>0</v>
+      </c>
+      <c r="K26" s="49"/>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" s="48" t="s">
+        <v>181</v>
+      </c>
+      <c r="B27" s="49" t="s">
+        <v>26</v>
+      </c>
+      <c r="C27" s="49" t="s">
+        <v>182</v>
+      </c>
+      <c r="D27" s="63"/>
+      <c r="E27" s="63">
+        <v>1</v>
+      </c>
+      <c r="F27" s="63">
+        <v>1</v>
+      </c>
+      <c r="G27" s="63"/>
+      <c r="H27" s="53" t="s">
+        <v>168</v>
+      </c>
+      <c r="I27" s="49" t="s">
+        <v>139</v>
+      </c>
+      <c r="J27" s="49">
+        <v>0</v>
+      </c>
+      <c r="K27" s="49"/>
+    </row>
+    <row r="28" s="41" customFormat="1" spans="1:11">
+      <c r="A28" s="46" t="s">
+        <v>183</v>
+      </c>
+      <c r="B28" s="47" t="s">
+        <v>26</v>
+      </c>
+      <c r="C28" s="47" t="s">
+        <v>184</v>
+      </c>
+      <c r="D28" s="62"/>
+      <c r="E28" s="62">
+        <v>1</v>
+      </c>
+      <c r="F28" s="62">
         <v>3</v>
       </c>
-      <c r="G23" s="49" t="s">
-        <v>179</v>
-      </c>
-      <c r="H23" s="49" t="s">
-        <v>140</v>
-      </c>
-      <c r="I23" s="49">
-        <v>0</v>
-      </c>
-      <c r="J23" s="49"/>
-    </row>
-    <row r="24" spans="1:10">
-      <c r="A24" s="48" t="s">
-        <v>180</v>
-      </c>
-      <c r="B24" s="49" t="s">
-        <v>26</v>
-      </c>
-      <c r="C24" s="49" t="s">
-        <v>181</v>
-      </c>
-      <c r="D24" s="67"/>
-      <c r="E24" s="67">
-        <v>1</v>
-      </c>
-      <c r="F24" s="67">
-        <v>0</v>
-      </c>
-      <c r="G24" s="49" t="s">
-        <v>182</v>
-      </c>
-      <c r="H24" s="49" t="s">
-        <v>140</v>
-      </c>
-      <c r="I24" s="49">
-        <v>0</v>
-      </c>
-      <c r="J24" s="49"/>
-    </row>
-    <row r="25" spans="1:10">
-      <c r="A25" s="48" t="s">
-        <v>183</v>
-      </c>
-      <c r="B25" s="49" t="s">
-        <v>26</v>
-      </c>
-      <c r="C25" s="49" t="s">
-        <v>184</v>
-      </c>
-      <c r="D25" s="67"/>
-      <c r="E25" s="67">
-        <v>1</v>
-      </c>
-      <c r="F25" s="67">
-        <v>1</v>
-      </c>
-      <c r="G25" s="53" t="s">
-        <v>170</v>
-      </c>
-      <c r="H25" s="49" t="s">
-        <v>140</v>
-      </c>
-      <c r="I25" s="49">
-        <v>0</v>
-      </c>
-      <c r="J25" s="49"/>
-    </row>
-    <row r="26" s="41" customFormat="1" spans="1:10">
-      <c r="A26" s="46" t="s">
+      <c r="G28" s="62"/>
+      <c r="H28" s="47" t="s">
         <v>185</v>
       </c>
-      <c r="B26" s="47" t="s">
-        <v>26</v>
-      </c>
-      <c r="C26" s="47" t="s">
-        <v>186</v>
-      </c>
-      <c r="D26" s="66"/>
-      <c r="E26" s="66">
-        <v>1</v>
-      </c>
-      <c r="F26" s="66">
-        <v>3</v>
-      </c>
-      <c r="G26" s="47" t="s">
-        <v>187</v>
-      </c>
-      <c r="H26" s="47" t="s">
-        <v>140</v>
-      </c>
-      <c r="I26" s="47">
-        <v>0</v>
-      </c>
-      <c r="J26" s="47"/>
+      <c r="I28" s="47" t="s">
+        <v>139</v>
+      </c>
+      <c r="J28" s="47">
+        <v>0</v>
+      </c>
+      <c r="K28" s="47"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8098,17 +8236,18 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <dimension ref="A1:H12"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="11.5" customWidth="1"/>
     <col min="3" max="3" width="40" customWidth="1"/>
     <col min="4" max="4" width="11.875" customWidth="1"/>
-    <col min="5" max="5" width="10.375" customWidth="1"/>
-    <col min="6" max="6" width="67.125" customWidth="1"/>
+    <col min="5" max="6" width="16.625" customWidth="1"/>
+    <col min="7" max="7" width="67.125" customWidth="1"/>
+    <col min="8" max="8" width="11.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:8">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -8119,16 +8258,22 @@
         <v>4</v>
       </c>
       <c r="D1" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="G1" s="55" t="s">
+        <v>60</v>
+      </c>
+      <c r="H1" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="E1" s="55" t="s">
-        <v>188</v>
-      </c>
-      <c r="F1" s="56" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="2" ht="40.5" spans="1:6">
+    </row>
+    <row r="2" ht="148.5" spans="1:8">
       <c r="A2" s="43" t="s">
         <v>5</v>
       </c>
@@ -8138,17 +8283,23 @@
       <c r="C2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="57" t="s">
+      <c r="D2" s="44" t="s">
+        <v>190</v>
+      </c>
+      <c r="E2" s="43" t="s">
+        <v>191</v>
+      </c>
+      <c r="F2" s="43" t="s">
+        <v>192</v>
+      </c>
+      <c r="G2" s="55" t="s">
+        <v>193</v>
+      </c>
+      <c r="H2" s="56" t="s">
         <v>72</v>
       </c>
-      <c r="E2" s="58" t="s">
-        <v>190</v>
-      </c>
-      <c r="F2" s="56" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="5" t="s">
         <v>10</v>
       </c>
@@ -8159,192 +8310,178 @@
         <v>10</v>
       </c>
       <c r="D3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="55" t="s">
+        <v>74</v>
+      </c>
+      <c r="H3" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E3" s="55" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="56" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="4" s="54" customFormat="1" spans="1:6">
-      <c r="A4" s="59" t="s">
+    </row>
+    <row r="4" s="54" customFormat="1" spans="1:8">
+      <c r="A4" s="57" t="s">
         <v>86</v>
       </c>
-      <c r="B4" s="59" t="s">
-        <v>192</v>
-      </c>
-      <c r="C4" s="59" t="s">
-        <v>193</v>
-      </c>
-      <c r="D4" s="60"/>
-      <c r="E4" s="60">
+      <c r="B4" s="57" t="s">
+        <v>194</v>
+      </c>
+      <c r="C4" s="57" t="s">
+        <v>195</v>
+      </c>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57">
         <v>2</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="5" s="54" customFormat="1" spans="1:6">
-      <c r="A5" s="60" t="s">
-        <v>195</v>
-      </c>
-      <c r="B5" s="60" t="s">
+      <c r="F4" s="57"/>
+      <c r="G4" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="C5" s="60" t="s">
+      <c r="H4" s="57"/>
+    </row>
+    <row r="5" s="54" customFormat="1" spans="1:8">
+      <c r="A5" s="57" t="s">
         <v>197</v>
       </c>
-      <c r="D5" s="60"/>
-      <c r="E5" s="60"/>
-      <c r="F5" s="40"/>
-    </row>
-    <row r="6" s="54" customFormat="1" spans="1:6">
-      <c r="A6" s="60" t="s">
+      <c r="B5" s="57" t="s">
         <v>198</v>
       </c>
-      <c r="B6" s="60" t="s">
+      <c r="C5" s="57" t="s">
         <v>199</v>
       </c>
-      <c r="C6" s="60" t="s">
+      <c r="D5" s="57"/>
+      <c r="E5" s="57"/>
+      <c r="F5" s="57"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="57"/>
+    </row>
+    <row r="6" s="54" customFormat="1" spans="1:8">
+      <c r="A6" s="57" t="s">
         <v>200</v>
       </c>
-      <c r="D6" s="60"/>
-      <c r="E6" s="60"/>
-      <c r="F6" s="1"/>
-    </row>
-    <row r="7" s="54" customFormat="1" spans="1:6">
-      <c r="A7" s="60" t="s">
+      <c r="B6" s="57" t="s">
         <v>201</v>
       </c>
-      <c r="B7" s="60" t="s">
+      <c r="C6" s="57" t="s">
         <v>202</v>
       </c>
-      <c r="C7" s="60" t="s">
+      <c r="D6" s="57"/>
+      <c r="E6" s="57"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="57"/>
+    </row>
+    <row r="7" s="54" customFormat="1" spans="1:8">
+      <c r="A7" s="57" t="s">
         <v>203</v>
       </c>
-      <c r="D7" s="60"/>
-      <c r="E7" s="60"/>
-      <c r="F7" s="1"/>
-    </row>
-    <row r="8" spans="1:6">
+      <c r="B7" s="57" t="s">
+        <v>204</v>
+      </c>
+      <c r="C7" s="57" t="s">
+        <v>205</v>
+      </c>
+      <c r="D7" s="57"/>
+      <c r="E7" s="57"/>
+      <c r="F7" s="57"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="57"/>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" s="1" t="s">
         <v>92</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="E8" s="61">
+        <v>207</v>
+      </c>
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
+      <c r="E8" s="1">
         <v>2</v>
       </c>
-      <c r="F8" s="1" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+      <c r="F8" s="1">
+        <v>5</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="D9" s="61"/>
-      <c r="E9" s="61"/>
+        <v>212</v>
+      </c>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
       <c r="F9" s="1"/>
-    </row>
-    <row r="10" spans="1:6">
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="D10" s="61"/>
-      <c r="E10" s="61"/>
+        <v>215</v>
+      </c>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
       <c r="F10" s="1"/>
-    </row>
-    <row r="11" spans="1:6">
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="D11" s="61"/>
-      <c r="E11" s="61"/>
+        <v>218</v>
+      </c>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
       <c r="F11" s="1"/>
-    </row>
-    <row r="12" spans="1:6">
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>150</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="D12" s="61"/>
-      <c r="E12" s="61"/>
-      <c r="F12" s="47"/>
-    </row>
-    <row r="13" spans="6:6">
-      <c r="F13" s="49"/>
-    </row>
-    <row r="14" spans="6:6">
-      <c r="F14" s="49"/>
-    </row>
-    <row r="15" spans="6:6">
-      <c r="F15" s="51"/>
-    </row>
-    <row r="16" spans="6:6">
-      <c r="F16" s="51"/>
-    </row>
-    <row r="17" spans="6:6">
-      <c r="F17" s="51"/>
-    </row>
-    <row r="18" spans="6:6">
-      <c r="F18" s="53"/>
-    </row>
-    <row r="19" spans="6:6">
-      <c r="F19" s="53"/>
-    </row>
-    <row r="20" spans="6:6">
-      <c r="F20" s="53"/>
-    </row>
-    <row r="21" spans="6:6">
-      <c r="F21" s="49"/>
-    </row>
-    <row r="22" spans="6:6">
-      <c r="F22" s="49"/>
-    </row>
-    <row r="23" spans="6:6">
-      <c r="F23" s="49"/>
-    </row>
-    <row r="24" spans="6:6">
-      <c r="F24" s="49"/>
-    </row>
-    <row r="25" spans="6:6">
-      <c r="F25" s="49"/>
-    </row>
-    <row r="26" spans="6:6">
-      <c r="F26" s="47"/>
+        <v>220</v>
+      </c>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="47"/>
+      <c r="H12" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8355,7 +8492,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="22.625" customWidth="1"/>
@@ -8371,51 +8508,51 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>61</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>188</v>
+        <v>223</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="H1" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" ht="108" spans="1:8">
+    <row r="2" ht="81" spans="1:8">
       <c r="A2" s="43" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D2" s="44" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E2" s="43" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F2" s="43" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="G2" s="43" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -8474,7 +8611,7 @@
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="40" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="D5" s="1">
         <v>1</v>
@@ -8489,12 +8626,12 @@
         <v>5</v>
       </c>
       <c r="H5" s="40" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
     </row>
     <row r="6" s="41" customFormat="1" spans="1:8">
       <c r="A6" s="45" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B6" s="45"/>
       <c r="C6" s="45" t="s">
@@ -8513,16 +8650,16 @@
         <v>8</v>
       </c>
       <c r="H6" s="45" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="7" s="41" customFormat="1" spans="1:8">
       <c r="A7" s="45" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B7" s="45"/>
       <c r="C7" s="45" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="D7" s="45">
         <v>0</v>
@@ -8534,21 +8671,21 @@
         <v>3</v>
       </c>
       <c r="G7" s="45" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="H7" s="45" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>206</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>204</v>
       </c>
       <c r="D8" s="1">
         <v>0</v>
@@ -8563,18 +8700,18 @@
         <v>1</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -8582,25 +8719,23 @@
       <c r="E9" s="1">
         <v>1</v>
       </c>
-      <c r="F9" s="1">
-        <v>4</v>
-      </c>
+      <c r="F9" s="1"/>
       <c r="G9" s="1">
         <v>2</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D10" s="1">
         <v>0</v>
@@ -8608,25 +8743,23 @@
       <c r="E10" s="1">
         <v>-1</v>
       </c>
-      <c r="F10" s="1">
-        <v>4</v>
-      </c>
+      <c r="F10" s="1"/>
       <c r="G10" s="1">
         <v>3</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="D11" s="1">
         <v>0</v>
@@ -8634,25 +8767,23 @@
       <c r="E11" s="1">
         <v>-1</v>
       </c>
-      <c r="F11" s="1">
-        <v>4</v>
-      </c>
+      <c r="F11" s="1"/>
       <c r="G11" s="1">
         <v>4</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D12" s="1">
         <v>0</v>
@@ -8660,25 +8791,23 @@
       <c r="E12" s="1">
         <v>1</v>
       </c>
-      <c r="F12" s="1">
-        <v>4</v>
-      </c>
+      <c r="F12" s="1"/>
       <c r="G12" s="1">
         <v>5</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D13" s="1">
         <v>0</v>
@@ -8686,25 +8815,23 @@
       <c r="E13" s="1">
         <v>5</v>
       </c>
-      <c r="F13" s="1">
-        <v>4</v>
-      </c>
+      <c r="F13" s="1"/>
       <c r="G13" s="1">
         <v>6</v>
       </c>
       <c r="H13" s="40" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="D14" s="1">
         <v>0</v>
@@ -8712,25 +8839,23 @@
       <c r="E14" s="1">
         <v>-1</v>
       </c>
-      <c r="F14" s="1">
-        <v>4</v>
-      </c>
+      <c r="F14" s="1"/>
       <c r="G14" s="1">
         <v>7</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -8738,25 +8863,23 @@
       <c r="E15" s="1">
         <v>1</v>
       </c>
-      <c r="F15" s="1">
-        <v>4</v>
-      </c>
+      <c r="F15" s="1"/>
       <c r="G15" s="1">
         <v>8</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="D16" s="1">
         <v>0</v>
@@ -8764,25 +8887,23 @@
       <c r="E16" s="1">
         <v>1</v>
       </c>
-      <c r="F16" s="1">
-        <v>4</v>
-      </c>
+      <c r="F16" s="1"/>
       <c r="G16" s="1">
         <v>9</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="46" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B17" s="47" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="C17" s="47" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="D17" s="1">
         <v>0</v>
@@ -8791,18 +8912,18 @@
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
       <c r="H17" s="47" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="48" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B18" s="49" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C18" s="49" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D18" s="1">
         <v>0</v>
@@ -8811,10 +8932,10 @@
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
       <c r="H18" s="49" t="s">
-        <v>147</v>
+        <v>272</v>
       </c>
       <c r="I18" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -8834,21 +8955,21 @@
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
       <c r="H19" s="49" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="I19" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
     </row>
     <row r="20" s="42" customFormat="1" spans="1:9">
       <c r="A20" s="50" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B20" s="51" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C20" s="51" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D20" s="51">
         <v>0</v>
@@ -8857,10 +8978,10 @@
       <c r="F20" s="51"/>
       <c r="G20" s="51"/>
       <c r="H20" s="51" t="s">
-        <v>154</v>
+        <v>276</v>
       </c>
       <c r="I20" s="42" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
     </row>
     <row r="21" s="42" customFormat="1" spans="1:9">
@@ -8880,21 +9001,21 @@
       <c r="F21" s="51"/>
       <c r="G21" s="51"/>
       <c r="H21" s="51" t="s">
+        <v>278</v>
+      </c>
+      <c r="I21" s="42" t="s">
         <v>273</v>
-      </c>
-      <c r="I21" s="42" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="22" s="42" customFormat="1" spans="1:9">
       <c r="A22" s="50" t="s">
+        <v>158</v>
+      </c>
+      <c r="B22" s="51" t="s">
         <v>159</v>
       </c>
-      <c r="B22" s="51" t="s">
-        <v>160</v>
-      </c>
       <c r="C22" s="51" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D22" s="51">
         <v>0</v>
@@ -8903,21 +9024,21 @@
       <c r="F22" s="51"/>
       <c r="G22" s="51"/>
       <c r="H22" s="51" t="s">
-        <v>161</v>
+        <v>279</v>
       </c>
       <c r="I22" s="42" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="52" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B23" s="53" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C23" s="53" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D23" s="1">
         <v>0</v>
@@ -8926,21 +9047,21 @@
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
       <c r="H23" s="53" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="I23" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="52" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B24" s="53" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C24" s="53" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D24" s="1">
         <v>0</v>
@@ -8949,21 +9070,21 @@
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
       <c r="H24" s="1" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="I24" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="52" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B25" s="53" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C25" s="53" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D25" s="1">
         <v>0</v>
@@ -8972,21 +9093,21 @@
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
       <c r="H25" s="53" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="I25" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="48" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B26" s="49" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C26" s="49" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D26" s="1">
         <v>0</v>
@@ -8995,21 +9116,21 @@
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
       <c r="H26" s="49" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="I26" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="48" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B27" s="49" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C27" s="49" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D27" s="1">
         <v>0</v>
@@ -9018,21 +9139,21 @@
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
       <c r="H27" s="49" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="I27" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="48" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B28" s="49" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C28" s="49" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D28" s="1">
         <v>0</v>
@@ -9041,18 +9162,18 @@
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
       <c r="H28" s="47" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="48" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B29" s="49" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C29" s="49" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D29" s="1">
         <v>0</v>
@@ -9061,21 +9182,21 @@
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
       <c r="H29" s="49" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="I29" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="48" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B30" s="49" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C30" s="49" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D30" s="1">
         <v>0</v>
@@ -9084,21 +9205,21 @@
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
       <c r="H30" s="53" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="I30" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="46" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B31" s="47" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C31" s="47" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D31" s="1">
         <v>0</v>
@@ -9107,7 +9228,51 @@
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
       <c r="H31" s="47" t="s">
-        <v>187</v>
+        <v>185</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" s="40" t="s">
+        <v>140</v>
+      </c>
+      <c r="B32" s="1"/>
+      <c r="C32" s="40"/>
+      <c r="D32" s="1">
+        <v>1</v>
+      </c>
+      <c r="E32" s="1">
+        <v>0</v>
+      </c>
+      <c r="F32" s="1">
+        <v>1</v>
+      </c>
+      <c r="G32" s="40">
+        <v>5</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" s="40" t="s">
+        <v>151</v>
+      </c>
+      <c r="B33" s="1"/>
+      <c r="C33" s="40"/>
+      <c r="D33" s="1">
+        <v>1</v>
+      </c>
+      <c r="E33" s="1">
+        <v>0</v>
+      </c>
+      <c r="F33" s="1">
+        <v>1</v>
+      </c>
+      <c r="G33" s="40">
+        <v>8</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>235</v>
       </c>
     </row>
   </sheetData>
@@ -9132,22 +9297,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="35" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="C1" s="35" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="D1" s="35" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="E1" s="35" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="F1" s="35" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="G1" s="35" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -9155,22 +9320,22 @@
         <v>5</v>
       </c>
       <c r="B2" s="37" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="C2" s="37" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D2" s="37" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="E2" s="37" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="F2" s="37" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="G2" s="38" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -9181,16 +9346,16 @@
         <v>10</v>
       </c>
       <c r="C3" s="37" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D3" s="37" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E3" s="37" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F3" s="37" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="G3" s="37" t="s">
         <v>10</v>
@@ -9198,10 +9363,10 @@
     </row>
     <row r="4" ht="14.25" spans="1:7">
       <c r="A4" s="39" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="B4" s="40" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="C4" s="39">
         <v>100</v>
@@ -9216,15 +9381,15 @@
         <v>1</v>
       </c>
       <c r="G4" s="39" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
     </row>
     <row r="5" ht="14.25" spans="1:7">
       <c r="A5" s="39" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="B5" s="40" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="C5" s="39">
         <v>100</v>
@@ -9239,15 +9404,15 @@
         <v>1</v>
       </c>
       <c r="G5" s="39" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
     </row>
     <row r="6" ht="14.25" spans="1:7">
       <c r="A6" s="39" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="B6" s="40" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="C6" s="39">
         <v>3</v>
@@ -9262,15 +9427,15 @@
         <v>1</v>
       </c>
       <c r="G6" s="39" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
     </row>
     <row r="7" ht="14.25" spans="1:7">
       <c r="A7" s="39" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="B7" s="40" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="C7" s="39">
         <v>3</v>
@@ -9285,12 +9450,12 @@
         <v>1</v>
       </c>
       <c r="G7" s="39" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
     </row>
     <row r="8" ht="14.25" spans="1:7">
       <c r="A8" s="39" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="B8" s="40" t="s">
         <v>8</v>
@@ -9308,15 +9473,15 @@
         <v>1</v>
       </c>
       <c r="G8" s="39" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
     </row>
     <row r="9" ht="14.25" spans="1:7">
       <c r="A9" s="39" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="B9" s="40" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="C9" s="39">
         <v>0</v>
@@ -9331,15 +9496,15 @@
         <v>1</v>
       </c>
       <c r="G9" s="39" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
     </row>
     <row r="10" ht="14.25" spans="1:7">
       <c r="A10" s="39" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="B10" s="40" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="C10" s="39">
         <v>0</v>
@@ -9354,15 +9519,15 @@
         <v>1</v>
       </c>
       <c r="G10" s="39" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
     </row>
     <row r="11" ht="14.25" spans="1:7">
       <c r="A11" s="39" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="B11" s="40" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C11" s="39">
         <v>0</v>
@@ -9377,15 +9542,15 @@
         <v>1</v>
       </c>
       <c r="G11" s="39" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
     </row>
     <row r="12" ht="14.25" spans="1:7">
       <c r="A12" s="39" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="B12" s="40" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C12" s="39">
         <v>0</v>
@@ -9400,15 +9565,15 @@
         <v>1</v>
       </c>
       <c r="G12" s="39" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
     </row>
     <row r="13" ht="14.25" spans="1:7">
       <c r="A13" s="39" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="B13" s="40" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="C13" s="39">
         <v>0</v>
@@ -9423,15 +9588,15 @@
         <v>1</v>
       </c>
       <c r="G13" s="39" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
     </row>
     <row r="14" ht="14.25" spans="1:7">
       <c r="A14" s="39" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="B14" s="40" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C14" s="39">
         <v>0</v>
@@ -9446,7 +9611,7 @@
         <v>1</v>
       </c>
       <c r="G14" s="39" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
   </sheetData>

--- a/xlsdir/配置-总表.xlsx
+++ b/xlsdir/配置-总表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="673" firstSheet="3" activeTab="5"/>
+    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="673" firstSheet="3" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="character|角色" sheetId="32" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="865" uniqueCount="557">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="873" uniqueCount="562">
   <si>
     <t>ID</t>
   </si>
@@ -302,7 +302,7 @@
     <t>items</t>
   </si>
   <si>
-    <t>shielded</t>
+    <t>shielded_5</t>
   </si>
   <si>
     <t>block</t>
@@ -605,6 +605,9 @@
     <t>召唤另一个骷髅怪加入战斗</t>
   </si>
   <si>
+    <t>is_stacked</t>
+  </si>
+  <si>
     <t>buff_type</t>
   </si>
   <si>
@@ -617,15 +620,17 @@
     <t>效果名</t>
   </si>
   <si>
+    <t>能否堆叠</t>
+  </si>
+  <si>
     <t>类型
-1可堆叠
-2固定
-3短时</t>
+1数值型
+2状态型</t>
   </si>
   <si>
     <t>持续类型
 1永久
-2持续回合</t>
+2持续回合（状态型每回合减少堆叠数，数值型只能持续一回合）</t>
   </si>
   <si>
     <t>回调类型
@@ -644,6 +649,9 @@
     <t>图标</t>
   </si>
   <si>
+    <t>bool</t>
+  </si>
+  <si>
     <t>格挡</t>
   </si>
   <si>
@@ -651,6 +659,9 @@
   </si>
   <si>
     <t>res://asserts/textures/widgets/Buffs/fortify_spell.png</t>
+  </si>
+  <si>
+    <t>shielded</t>
   </si>
   <si>
     <t>strength</t>
@@ -777,6 +788,12 @@
     <t>获得5点护盾</t>
   </si>
   <si>
+    <t>护盾*5</t>
+  </si>
+  <si>
+    <t>block*5</t>
+  </si>
+  <si>
     <t>trounce_01</t>
   </si>
   <si>
@@ -973,9 +990,6 @@
   </si>
   <si>
     <t>属性描述</t>
-  </si>
-  <si>
-    <t>bool</t>
   </si>
   <si>
     <t>MaxHealth</t>
@@ -2872,7 +2886,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3041,12 +3055,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
@@ -3070,6 +3084,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -3607,67 +3627,67 @@
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="R1" s="13" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="S1" s="3" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="T1" s="3" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="U1" s="3" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="V1" s="3" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="W1" s="14" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="X1" s="15"/>
       <c r="Y1" s="15"/>
@@ -3679,82 +3699,82 @@
         <v>5</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="O2" s="5" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="P2" s="5" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="Q2" s="5" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="R2" s="16" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="S2" s="5" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="T2" s="5" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="U2" s="5" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="V2" s="5" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="W2" s="17" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="X2" s="18" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="Y2" s="32" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="Z2" s="32" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="AA2" s="33" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
     </row>
     <row r="3" ht="14.25" spans="1:27">
@@ -3845,7 +3865,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="C4" s="9">
         <v>10</v>
@@ -3900,17 +3920,17 @@
       <c r="U4" s="9"/>
       <c r="V4" s="9"/>
       <c r="W4" s="23"/>
-      <c r="X4" s="68" t="s">
-        <v>373</v>
+      <c r="X4" s="70" t="s">
+        <v>378</v>
       </c>
       <c r="Y4" s="9" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="Z4" s="9" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="AA4" s="23" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
     </row>
     <row r="5" spans="1:27">
@@ -3918,7 +3938,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="C5" s="1">
         <v>10</v>
@@ -3974,16 +3994,16 @@
       <c r="V5" s="1"/>
       <c r="W5" s="26"/>
       <c r="X5" s="27" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="Y5" s="1" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="Z5" s="1" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="AA5" s="26" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
     </row>
     <row r="6" spans="1:27">
@@ -3991,7 +4011,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="C6" s="1">
         <v>10</v>
@@ -4047,16 +4067,16 @@
       <c r="V6" s="1"/>
       <c r="W6" s="26"/>
       <c r="X6" s="27" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="Y6" s="1" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="Z6" s="1" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="AA6" s="26" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
     </row>
     <row r="7" spans="1:27">
@@ -4064,7 +4084,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="C7" s="1">
         <v>10</v>
@@ -4120,16 +4140,16 @@
       <c r="V7" s="1"/>
       <c r="W7" s="26"/>
       <c r="X7" s="27" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="Y7" s="1" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="Z7" s="1" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="AA7" s="26" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
     </row>
     <row r="8" spans="1:27">
@@ -4137,7 +4157,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="C8" s="1">
         <v>10</v>
@@ -4193,16 +4213,16 @@
       <c r="V8" s="1"/>
       <c r="W8" s="26"/>
       <c r="X8" s="27" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="Y8" s="1" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="Z8" s="1" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="AA8" s="26" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="9" spans="1:27">
@@ -4210,7 +4230,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="C9" s="1">
         <v>10</v>
@@ -4266,16 +4286,16 @@
       <c r="V9" s="1"/>
       <c r="W9" s="26"/>
       <c r="X9" s="27" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="Y9" s="1" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="Z9" s="1" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="AA9" s="26" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
     </row>
     <row r="10" spans="1:27">
@@ -4283,7 +4303,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="C10" s="1">
         <v>10</v>
@@ -4339,16 +4359,16 @@
       <c r="V10" s="1"/>
       <c r="W10" s="26"/>
       <c r="X10" s="27" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="Y10" s="1" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="Z10" s="1" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="AA10" s="26" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
     </row>
     <row r="11" spans="1:27">
@@ -4356,7 +4376,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="C11" s="1">
         <v>10</v>
@@ -4412,16 +4432,16 @@
       <c r="V11" s="1"/>
       <c r="W11" s="26"/>
       <c r="X11" s="27" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="Y11" s="1" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="Z11" s="1" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="AA11" s="26" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
     </row>
     <row r="12" spans="1:27">
@@ -4429,7 +4449,7 @@
         <v>9</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="C12" s="1">
         <v>10</v>
@@ -4485,16 +4505,16 @@
       <c r="V12" s="1"/>
       <c r="W12" s="26"/>
       <c r="X12" s="27" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="Y12" s="1" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="Z12" s="1" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="AA12" s="26" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
     </row>
     <row r="13" spans="1:27">
@@ -4502,7 +4522,7 @@
         <v>10</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="C13" s="1">
         <v>10</v>
@@ -4558,16 +4578,16 @@
       <c r="V13" s="1"/>
       <c r="W13" s="26"/>
       <c r="X13" s="27" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="Y13" s="1" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="Z13" s="1" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="AA13" s="26" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
     </row>
     <row r="14" spans="1:27">
@@ -4575,7 +4595,7 @@
         <v>11</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C14" s="1">
         <v>10</v>
@@ -4631,16 +4651,16 @@
       <c r="V14" s="1"/>
       <c r="W14" s="26"/>
       <c r="X14" s="27" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="Y14" s="1" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="Z14" s="1" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="AA14" s="26" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
     </row>
     <row r="15" spans="1:27">
@@ -4648,7 +4668,7 @@
         <v>12</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="C15" s="1">
         <v>10</v>
@@ -4704,16 +4724,16 @@
       <c r="V15" s="1"/>
       <c r="W15" s="26"/>
       <c r="X15" s="27" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="Y15" s="1" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="Z15" s="1" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="AA15" s="26" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
     </row>
     <row r="16" spans="1:27">
@@ -4721,7 +4741,7 @@
         <v>13</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="C16" s="1">
         <v>10</v>
@@ -4777,16 +4797,16 @@
       <c r="V16" s="1"/>
       <c r="W16" s="26"/>
       <c r="X16" s="27" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="Y16" s="1" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="Z16" s="1" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="AA16" s="26" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
     </row>
     <row r="17" spans="1:27">
@@ -4794,7 +4814,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="C17" s="1">
         <v>10</v>
@@ -4850,16 +4870,16 @@
       <c r="V17" s="1"/>
       <c r="W17" s="26"/>
       <c r="X17" s="27" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="Y17" s="1" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="Z17" s="1" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="AA17" s="26" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
     </row>
     <row r="18" spans="1:27">
@@ -4867,7 +4887,7 @@
         <v>15</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="C18" s="1">
         <v>10</v>
@@ -4923,16 +4943,16 @@
       <c r="V18" s="1"/>
       <c r="W18" s="26"/>
       <c r="X18" s="27" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="Y18" s="1" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="Z18" s="1" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="AA18" s="26" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
     </row>
     <row r="19" spans="1:27">
@@ -4940,7 +4960,7 @@
         <v>16</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="C19" s="1">
         <v>10</v>
@@ -4996,16 +5016,16 @@
       <c r="V19" s="1"/>
       <c r="W19" s="26"/>
       <c r="X19" s="27" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="Y19" s="1" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="Z19" s="1" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="AA19" s="26" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
     </row>
     <row r="20" spans="1:27">
@@ -5013,7 +5033,7 @@
         <v>17</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="C20" s="1">
         <v>10</v>
@@ -5069,16 +5089,16 @@
       <c r="V20" s="1"/>
       <c r="W20" s="26"/>
       <c r="X20" s="27" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="Y20" s="1" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="Z20" s="1" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="AA20" s="26" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
     </row>
     <row r="21" spans="1:27">
@@ -5086,7 +5106,7 @@
         <v>18</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="C21" s="1">
         <v>10</v>
@@ -5142,16 +5162,16 @@
       <c r="V21" s="1"/>
       <c r="W21" s="26"/>
       <c r="X21" s="27" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="Y21" s="1" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="Z21" s="1" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="AA21" s="26" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
     </row>
     <row r="22" spans="1:27">
@@ -5159,7 +5179,7 @@
         <v>19</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="C22" s="1">
         <v>10</v>
@@ -5215,16 +5235,16 @@
       <c r="V22" s="1"/>
       <c r="W22" s="26"/>
       <c r="X22" s="27" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="Y22" s="1" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="Z22" s="1" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="AA22" s="26" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
     </row>
     <row r="23" spans="1:27">
@@ -5232,7 +5252,7 @@
         <v>20</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="C23" s="1">
         <v>10</v>
@@ -5288,16 +5308,16 @@
       <c r="V23" s="1"/>
       <c r="W23" s="26"/>
       <c r="X23" s="27" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="Y23" s="1" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="Z23" s="1" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="AA23" s="26" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
     </row>
     <row r="24" spans="1:27">
@@ -5305,7 +5325,7 @@
         <v>21</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="C24" s="1">
         <v>10</v>
@@ -5361,16 +5381,16 @@
       <c r="V24" s="1"/>
       <c r="W24" s="26"/>
       <c r="X24" s="27" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="Y24" s="1" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="Z24" s="1" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="AA24" s="26" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
     </row>
     <row r="25" spans="1:27">
@@ -5378,7 +5398,7 @@
         <v>22</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="C25" s="1">
         <v>10</v>
@@ -5434,16 +5454,16 @@
       <c r="V25" s="1"/>
       <c r="W25" s="26"/>
       <c r="X25" s="27" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="Y25" s="1" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="Z25" s="1" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="AA25" s="26" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
     </row>
     <row r="26" spans="1:27">
@@ -5451,7 +5471,7 @@
         <v>23</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="C26" s="1">
         <v>10</v>
@@ -5507,16 +5527,16 @@
       <c r="V26" s="1"/>
       <c r="W26" s="26"/>
       <c r="X26" s="27" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="Y26" s="1" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="Z26" s="1" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="AA26" s="26" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
     </row>
     <row r="27" spans="1:27">
@@ -5524,7 +5544,7 @@
         <v>24</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="C27" s="1">
         <v>10</v>
@@ -5580,16 +5600,16 @@
       <c r="V27" s="1"/>
       <c r="W27" s="26"/>
       <c r="X27" s="27" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="Y27" s="1" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="Z27" s="1" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="AA27" s="26" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
     </row>
     <row r="28" spans="1:27">
@@ -5597,7 +5617,7 @@
         <v>25</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="C28" s="1">
         <v>10</v>
@@ -5653,16 +5673,16 @@
       <c r="V28" s="1"/>
       <c r="W28" s="26"/>
       <c r="X28" s="27" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="Y28" s="1" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="Z28" s="1" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="AA28" s="26" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
     </row>
     <row r="29" spans="1:27">
@@ -5670,7 +5690,7 @@
         <v>26</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="C29" s="1">
         <v>10</v>
@@ -5726,16 +5746,16 @@
       <c r="V29" s="1"/>
       <c r="W29" s="26"/>
       <c r="X29" s="27" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="Y29" s="1" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="Z29" s="1" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="AA29" s="26" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
     </row>
     <row r="30" spans="1:27">
@@ -5743,7 +5763,7 @@
         <v>27</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="C30" s="1">
         <v>10</v>
@@ -5799,16 +5819,16 @@
       <c r="V30" s="1"/>
       <c r="W30" s="26"/>
       <c r="X30" s="27" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="Y30" s="1" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="Z30" s="1" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="AA30" s="26" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
     </row>
     <row r="31" spans="1:27">
@@ -5816,7 +5836,7 @@
         <v>28</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="C31" s="1">
         <v>10</v>
@@ -5872,16 +5892,16 @@
       <c r="V31" s="1"/>
       <c r="W31" s="26"/>
       <c r="X31" s="27" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="Y31" s="1" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="Z31" s="1" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="AA31" s="26" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
     </row>
     <row r="32" spans="1:27">
@@ -5889,7 +5909,7 @@
         <v>29</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="C32" s="1">
         <v>10</v>
@@ -5945,16 +5965,16 @@
       <c r="V32" s="1"/>
       <c r="W32" s="26"/>
       <c r="X32" s="27" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="Y32" s="1" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="Z32" s="1" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="AA32" s="26" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
     </row>
     <row r="33" spans="1:27">
@@ -5962,7 +5982,7 @@
         <v>30</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="C33" s="1">
         <v>10</v>
@@ -6018,16 +6038,16 @@
       <c r="V33" s="1"/>
       <c r="W33" s="26"/>
       <c r="X33" s="27" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="Y33" s="1" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="Z33" s="1" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="AA33" s="26" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
     </row>
     <row r="34" spans="1:27">
@@ -6035,7 +6055,7 @@
         <v>31</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="C34" s="1">
         <v>10</v>
@@ -6091,16 +6111,16 @@
       <c r="V34" s="1"/>
       <c r="W34" s="26"/>
       <c r="X34" s="27" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="Y34" s="1" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="Z34" s="1" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="AA34" s="26" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
     </row>
     <row r="35" spans="1:27">
@@ -6108,7 +6128,7 @@
         <v>32</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="C35" s="1">
         <v>10</v>
@@ -6164,16 +6184,16 @@
       <c r="V35" s="1"/>
       <c r="W35" s="26"/>
       <c r="X35" s="27" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="Y35" s="1" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="Z35" s="1" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="AA35" s="26" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
     </row>
     <row r="36" spans="1:27">
@@ -6181,7 +6201,7 @@
         <v>33</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="C36" s="1">
         <v>10</v>
@@ -6237,16 +6257,16 @@
       <c r="V36" s="1"/>
       <c r="W36" s="26"/>
       <c r="X36" s="27" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="Y36" s="1" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="Z36" s="1" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="AA36" s="26" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
     </row>
     <row r="37" spans="1:27">
@@ -6254,7 +6274,7 @@
         <v>34</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="C37" s="1">
         <v>10</v>
@@ -6310,16 +6330,16 @@
       <c r="V37" s="1"/>
       <c r="W37" s="26"/>
       <c r="X37" s="27" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="Y37" s="1" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="Z37" s="1" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="AA37" s="26" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
     </row>
     <row r="38" spans="1:27">
@@ -6327,7 +6347,7 @@
         <v>35</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="C38" s="1">
         <v>10</v>
@@ -6383,16 +6403,16 @@
       <c r="V38" s="1"/>
       <c r="W38" s="26"/>
       <c r="X38" s="27" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="Y38" s="1" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="Z38" s="1" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="AA38" s="26" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
     </row>
     <row r="39" spans="1:27">
@@ -6400,7 +6420,7 @@
         <v>36</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="C39" s="1">
         <v>10</v>
@@ -6456,16 +6476,16 @@
       <c r="V39" s="1"/>
       <c r="W39" s="26"/>
       <c r="X39" s="27" t="s">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="Y39" s="1" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="Z39" s="1" t="s">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="AA39" s="26" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
     </row>
     <row r="40" spans="1:27">
@@ -6473,7 +6493,7 @@
         <v>37</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="C40" s="1">
         <v>10</v>
@@ -6529,16 +6549,16 @@
       <c r="V40" s="1"/>
       <c r="W40" s="26"/>
       <c r="X40" s="27" t="s">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="Y40" s="1" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="Z40" s="1" t="s">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="AA40" s="26" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
     </row>
     <row r="41" ht="14.25" spans="1:27">
@@ -6546,7 +6566,7 @@
         <v>38</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="C41" s="12">
         <v>10</v>
@@ -6602,16 +6622,16 @@
       <c r="V41" s="12"/>
       <c r="W41" s="29"/>
       <c r="X41" s="30" t="s">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="Y41" s="12" t="s">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="Z41" s="12" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="AA41" s="29" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
     </row>
   </sheetData>
@@ -6675,7 +6695,7 @@
         <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>543</v>
+        <v>548</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -6683,7 +6703,7 @@
         <v>2</v>
       </c>
       <c r="B13" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -6691,7 +6711,7 @@
         <v>3</v>
       </c>
       <c r="B14" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -6699,7 +6719,7 @@
         <v>4</v>
       </c>
       <c r="B15" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="F15" t="s">
         <v>142</v>
@@ -6708,7 +6728,7 @@
         <v>142</v>
       </c>
       <c r="I15" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -6716,32 +6736,32 @@
         <v>5</v>
       </c>
       <c r="B16" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="F16" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="H16" t="s">
         <v>160</v>
       </c>
       <c r="I16" t="s">
-        <v>549</v>
+        <v>554</v>
       </c>
     </row>
     <row r="17" spans="6:9">
       <c r="F17" t="s">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="H17" t="s">
         <v>169</v>
       </c>
       <c r="I17" t="s">
-        <v>551</v>
+        <v>556</v>
       </c>
     </row>
     <row r="18" spans="2:9">
       <c r="B18" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="F18" t="s">
         <v>160</v>
@@ -6750,18 +6770,18 @@
         <v>153</v>
       </c>
       <c r="I18" t="s">
-        <v>553</v>
+        <v>558</v>
       </c>
     </row>
     <row r="19" spans="6:9">
       <c r="F19" t="s">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="H19" t="s">
         <v>178</v>
       </c>
       <c r="I19" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
     </row>
     <row r="20" spans="6:8">
@@ -6784,7 +6804,7 @@
     </row>
     <row r="22" spans="6:8">
       <c r="F22" t="s">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="H22">
         <f>IF('intent|意图'!F24='intent|意图'!F23,H21&amp;"*"&amp;'intent|意图'!D24,'intent|意图'!D24)</f>
@@ -6811,7 +6831,7 @@
     </row>
     <row r="25" spans="6:8">
       <c r="F25" t="s">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="H25">
         <f>IF('intent|意图'!F18='intent|意图'!F17,H24&amp;"*"&amp;'intent|意图'!D18,'intent|意图'!D18)</f>
@@ -6820,7 +6840,7 @@
     </row>
     <row r="26" spans="6:8">
       <c r="F26" t="s">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="H26">
         <f>IF('intent|意图'!F19='intent|意图'!F18,H25&amp;"*"&amp;'intent|意图'!D19,'intent|意图'!D19)</f>
@@ -6838,7 +6858,7 @@
     </row>
     <row r="28" spans="6:8">
       <c r="F28" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="H28">
         <f>IF('intent|意图'!F27='intent|意图'!F26,H27&amp;"*"&amp;'intent|意图'!D27,'intent|意图'!D27)</f>
@@ -6856,32 +6876,32 @@
     </row>
     <row r="30" spans="2:2">
       <c r="B30" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
     </row>
     <row r="42" spans="2:2">
       <c r="B42" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
     </row>
     <row r="50" spans="2:2">
       <c r="B50" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
     </row>
     <row r="54" spans="2:2">
       <c r="B54" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
     </row>
     <row r="62" spans="2:2">
       <c r="B62" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
     </row>
     <row r="66" spans="2:2">
       <c r="B66" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
     </row>
   </sheetData>
@@ -6974,7 +6994,7 @@
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultColWidth="8.86666666666667" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="8.33333333333333" style="67" customWidth="1"/>
+    <col min="1" max="1" width="8.33333333333333" style="69" customWidth="1"/>
     <col min="2" max="2" width="11.8666666666667" customWidth="1"/>
     <col min="3" max="3" width="31.4666666666667" customWidth="1"/>
   </cols>
@@ -6992,7 +7012,7 @@
       <c r="D1" s="5"/>
       <c r="E1" s="5"/>
     </row>
-    <row r="2" s="66" customFormat="1" spans="1:5">
+    <row r="2" s="68" customFormat="1" spans="1:5">
       <c r="A2" s="43" t="s">
         <v>5</v>
       </c>
@@ -7229,7 +7249,7 @@
       <c r="I1" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="J1" s="21" t="s">
+      <c r="J1" s="66" t="s">
         <v>64</v>
       </c>
     </row>
@@ -7258,10 +7278,10 @@
       <c r="H2" s="43" t="s">
         <v>71</v>
       </c>
-      <c r="I2" s="56" t="s">
+      <c r="I2" s="57" t="s">
         <v>72</v>
       </c>
-      <c r="J2" s="21" t="s">
+      <c r="J2" s="66" t="s">
         <v>73</v>
       </c>
     </row>
@@ -7293,11 +7313,11 @@
       <c r="I3" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="J3" s="21" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
+      <c r="J3" s="66" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
         <v>75</v>
       </c>
@@ -7325,6 +7345,7 @@
       <c r="I4" s="1" t="s">
         <v>75</v>
       </c>
+      <c r="J4" s="67"/>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="1" t="s">
@@ -8236,18 +8257,21 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <dimension ref="A1:I12"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="11.5" customWidth="1"/>
+    <col min="2" max="2" width="8.125" customWidth="1"/>
     <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="11.875" customWidth="1"/>
-    <col min="5" max="6" width="16.625" customWidth="1"/>
-    <col min="7" max="7" width="67.125" customWidth="1"/>
-    <col min="8" max="8" width="11.875" customWidth="1"/>
+    <col min="4" max="4" width="9.5" customWidth="1"/>
+    <col min="5" max="5" width="11.875" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="7" max="7" width="16" customWidth="1"/>
+    <col min="8" max="8" width="67.125" customWidth="1"/>
+    <col min="9" max="9" width="11.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -8266,40 +8290,46 @@
       <c r="F1" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="G1" s="55" t="s">
+      <c r="G1" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="H1" s="55" t="s">
         <v>60</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="I1" s="5" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="2" ht="148.5" spans="1:8">
+    <row r="2" ht="148.5" spans="1:9">
       <c r="A2" s="43" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="43" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="44" t="s">
-        <v>190</v>
+      <c r="D2" s="5" t="s">
+        <v>191</v>
       </c>
       <c r="E2" s="43" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F2" s="43" t="s">
-        <v>192</v>
-      </c>
-      <c r="G2" s="55" t="s">
         <v>193</v>
       </c>
-      <c r="H2" s="56" t="s">
+      <c r="G2" s="43" t="s">
+        <v>194</v>
+      </c>
+      <c r="H2" s="55" t="s">
+        <v>195</v>
+      </c>
+      <c r="I2" s="57" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:9">
       <c r="A3" s="5" t="s">
         <v>10</v>
       </c>
@@ -8310,7 +8340,7 @@
         <v>10</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>11</v>
+        <v>196</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>11</v>
@@ -8318,90 +8348,111 @@
       <c r="F3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="55" t="s">
+      <c r="G3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3" s="55" t="s">
         <v>74</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="I3" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="4" s="54" customFormat="1" spans="1:8">
-      <c r="A4" s="57" t="s">
+    <row r="4" s="54" customFormat="1" spans="1:9">
+      <c r="A4" s="56" t="s">
         <v>86</v>
       </c>
-      <c r="B4" s="57" t="s">
-        <v>194</v>
-      </c>
-      <c r="C4" s="57" t="s">
-        <v>195</v>
-      </c>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57">
+      <c r="B4" s="56" t="s">
+        <v>197</v>
+      </c>
+      <c r="C4" s="56" t="s">
+        <v>198</v>
+      </c>
+      <c r="D4" s="56">
+        <v>1</v>
+      </c>
+      <c r="E4" s="56">
+        <v>1</v>
+      </c>
+      <c r="F4" s="56">
         <v>2</v>
       </c>
-      <c r="F4" s="57"/>
-      <c r="G4" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="H4" s="57"/>
-    </row>
-    <row r="5" s="54" customFormat="1" spans="1:8">
-      <c r="A5" s="57" t="s">
-        <v>197</v>
-      </c>
-      <c r="B5" s="57" t="s">
-        <v>198</v>
-      </c>
-      <c r="C5" s="57" t="s">
+      <c r="G4" s="56">
+        <v>5</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="D5" s="57"/>
-      <c r="E5" s="57"/>
-      <c r="F5" s="57"/>
-      <c r="G5" s="40"/>
-      <c r="H5" s="57"/>
-    </row>
-    <row r="6" s="54" customFormat="1" spans="1:8">
-      <c r="A6" s="57" t="s">
+      <c r="I4" s="40" t="s">
         <v>200</v>
       </c>
-      <c r="B6" s="57" t="s">
+    </row>
+    <row r="5" s="54" customFormat="1" spans="1:9">
+      <c r="A5" s="56" t="s">
         <v>201</v>
       </c>
-      <c r="C6" s="57" t="s">
+      <c r="B5" s="56" t="s">
         <v>202</v>
       </c>
-      <c r="D6" s="57"/>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="57"/>
-    </row>
-    <row r="7" s="54" customFormat="1" spans="1:8">
-      <c r="A7" s="57" t="s">
+      <c r="C5" s="56" t="s">
         <v>203</v>
       </c>
-      <c r="B7" s="57" t="s">
+      <c r="D5" s="56">
+        <v>1</v>
+      </c>
+      <c r="E5" s="56"/>
+      <c r="F5" s="56"/>
+      <c r="G5" s="56"/>
+      <c r="H5" s="40"/>
+      <c r="I5" s="56"/>
+    </row>
+    <row r="6" s="54" customFormat="1" spans="1:9">
+      <c r="A6" s="56" t="s">
         <v>204</v>
       </c>
-      <c r="C7" s="57" t="s">
+      <c r="B6" s="56" t="s">
         <v>205</v>
       </c>
-      <c r="D7" s="57"/>
-      <c r="E7" s="57"/>
-      <c r="F7" s="57"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="57"/>
-    </row>
-    <row r="8" spans="1:8">
+      <c r="C6" s="56" t="s">
+        <v>206</v>
+      </c>
+      <c r="D6" s="56">
+        <v>1</v>
+      </c>
+      <c r="E6" s="56"/>
+      <c r="F6" s="56"/>
+      <c r="G6" s="56"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="56"/>
+    </row>
+    <row r="7" s="54" customFormat="1" spans="1:9">
+      <c r="A7" s="56" t="s">
+        <v>207</v>
+      </c>
+      <c r="B7" s="56" t="s">
+        <v>208</v>
+      </c>
+      <c r="C7" s="56" t="s">
+        <v>209</v>
+      </c>
+      <c r="D7" s="56">
+        <v>1</v>
+      </c>
+      <c r="E7" s="56"/>
+      <c r="F7" s="56"/>
+      <c r="G7" s="56"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="56"/>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
         <v>92</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="D8" s="1">
         <v>1</v>
@@ -8410,78 +8461,93 @@
         <v>2</v>
       </c>
       <c r="F8" s="1">
+        <v>2</v>
+      </c>
+      <c r="G8" s="1">
         <v>5</v>
       </c>
-      <c r="G8" s="1" t="s">
-        <v>208</v>
-      </c>
       <c r="H8" s="1" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
+        <v>212</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="D9" s="1"/>
+        <v>216</v>
+      </c>
+      <c r="D9" s="1">
+        <v>0</v>
+      </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
-    </row>
-    <row r="10" spans="1:8">
+      <c r="I9" s="1"/>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="D10" s="1"/>
+        <v>219</v>
+      </c>
+      <c r="D10" s="1">
+        <v>0</v>
+      </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
-    </row>
-    <row r="11" spans="1:8">
+      <c r="I10" s="1"/>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="D11" s="1"/>
+        <v>222</v>
+      </c>
+      <c r="D11" s="1">
+        <v>0</v>
+      </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
-    </row>
-    <row r="12" spans="1:8">
+      <c r="I11" s="1"/>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="1" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>150</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="D12" s="1"/>
+        <v>224</v>
+      </c>
+      <c r="D12" s="1">
+        <v>0</v>
+      </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
-      <c r="G12" s="47"/>
-      <c r="H12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="47"/>
+      <c r="I12" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8492,7 +8558,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="22.625" customWidth="1"/>
@@ -8508,22 +8574,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>61</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="H1" s="5" t="s">
         <v>4</v>
@@ -8534,25 +8600,25 @@
         <v>5</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="D2" s="44" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="E2" s="43" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="F2" s="43" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="G2" s="43" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -8607,11 +8673,11 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="40" t="s">
-        <v>85</v>
+        <v>200</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="40" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="D5" s="1">
         <v>1</v>
@@ -8626,40 +8692,40 @@
         <v>5</v>
       </c>
       <c r="H5" s="40" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="6" s="41" customFormat="1" spans="1:8">
-      <c r="A6" s="45" t="s">
-        <v>234</v>
-      </c>
-      <c r="B6" s="45"/>
-      <c r="C6" s="45" t="s">
-        <v>88</v>
-      </c>
-      <c r="D6" s="45">
-        <v>0</v>
-      </c>
-      <c r="E6" s="45">
-        <v>0</v>
-      </c>
-      <c r="F6" s="45">
-        <v>1</v>
-      </c>
-      <c r="G6" s="45">
-        <v>8</v>
-      </c>
-      <c r="H6" s="45" t="s">
-        <v>235</v>
+        <v>237</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="40" t="s">
+        <v>85</v>
+      </c>
+      <c r="B6" s="1"/>
+      <c r="C6" s="40" t="s">
+        <v>238</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0</v>
+      </c>
+      <c r="F6" s="1">
+        <v>3</v>
+      </c>
+      <c r="G6" s="40" t="s">
+        <v>239</v>
+      </c>
+      <c r="H6" s="40" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="7" s="41" customFormat="1" spans="1:8">
       <c r="A7" s="45" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B7" s="45"/>
       <c r="C7" s="45" t="s">
-        <v>237</v>
+        <v>88</v>
       </c>
       <c r="D7" s="45">
         <v>0</v>
@@ -8668,98 +8734,98 @@
         <v>0</v>
       </c>
       <c r="F7" s="45">
+        <v>1</v>
+      </c>
+      <c r="G7" s="45">
+        <v>8</v>
+      </c>
+      <c r="H7" s="45" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="8" s="41" customFormat="1" spans="1:8">
+      <c r="A8" s="45" t="s">
+        <v>242</v>
+      </c>
+      <c r="B8" s="45"/>
+      <c r="C8" s="45" t="s">
+        <v>243</v>
+      </c>
+      <c r="D8" s="45">
+        <v>0</v>
+      </c>
+      <c r="E8" s="45">
+        <v>0</v>
+      </c>
+      <c r="F8" s="45">
         <v>3</v>
       </c>
-      <c r="G7" s="45" t="s">
-        <v>238</v>
-      </c>
-      <c r="H7" s="45" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="D8" s="1">
-        <v>0</v>
-      </c>
-      <c r="E8" s="1">
-        <v>2</v>
-      </c>
-      <c r="F8" s="1">
-        <v>4</v>
-      </c>
-      <c r="G8" s="1">
-        <v>1</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>241</v>
+      <c r="G8" s="45" t="s">
+        <v>244</v>
+      </c>
+      <c r="H8" s="45" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
-        <v>242</v>
+        <v>213</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>125</v>
+        <v>210</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
       </c>
       <c r="E9" s="1">
-        <v>1</v>
-      </c>
-      <c r="F9" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="F9" s="1">
+        <v>4</v>
+      </c>
       <c r="G9" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>214</v>
+        <v>125</v>
       </c>
       <c r="D10" s="1">
         <v>0</v>
       </c>
       <c r="E10" s="1">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="F10" s="1"/>
       <c r="G10" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>250</v>
+        <v>218</v>
       </c>
       <c r="D11" s="1">
         <v>0</v>
@@ -8769,117 +8835,117 @@
       </c>
       <c r="F11" s="1"/>
       <c r="G11" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>121</v>
+        <v>256</v>
       </c>
       <c r="D12" s="1">
         <v>0</v>
       </c>
       <c r="E12" s="1">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="F12" s="1"/>
       <c r="G12" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>204</v>
+        <v>121</v>
       </c>
       <c r="D13" s="1">
         <v>0</v>
       </c>
       <c r="E13" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F13" s="1"/>
       <c r="G13" s="1">
-        <v>6</v>
-      </c>
-      <c r="H13" s="40" t="s">
-        <v>257</v>
+        <v>5</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>260</v>
+        <v>208</v>
       </c>
       <c r="D14" s="1">
         <v>0</v>
       </c>
       <c r="E14" s="1">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F14" s="1"/>
       <c r="G14" s="1">
-        <v>7</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>261</v>
+        <v>6</v>
+      </c>
+      <c r="H14" s="40" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
       </c>
       <c r="E15" s="1">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D16" s="1">
         <v>0</v>
@@ -8889,41 +8955,45 @@
       </c>
       <c r="F16" s="1"/>
       <c r="G16" s="1">
+        <v>8</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="D17" s="1">
+        <v>0</v>
+      </c>
+      <c r="E17" s="1">
+        <v>1</v>
+      </c>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1">
         <v>9</v>
       </c>
-      <c r="H16" s="1" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8">
-      <c r="A17" s="46" t="s">
+      <c r="H17" s="1" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" s="46" t="s">
         <v>142</v>
       </c>
-      <c r="B17" s="47" t="s">
-        <v>270</v>
-      </c>
-      <c r="C17" s="47" t="s">
-        <v>270</v>
-      </c>
-      <c r="D17" s="1">
-        <v>0</v>
-      </c>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="47" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9">
-      <c r="A18" s="48" t="s">
-        <v>146</v>
-      </c>
-      <c r="B18" s="49" t="s">
-        <v>147</v>
-      </c>
-      <c r="C18" s="49" t="s">
-        <v>147</v>
+      <c r="B18" s="47" t="s">
+        <v>276</v>
+      </c>
+      <c r="C18" s="47" t="s">
+        <v>276</v>
       </c>
       <c r="D18" s="1">
         <v>0</v>
@@ -8931,22 +9001,19 @@
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
-      <c r="H18" s="49" t="s">
-        <v>272</v>
-      </c>
-      <c r="I18" t="s">
-        <v>273</v>
+      <c r="H18" s="47" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="48" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B19" s="49" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C19" s="49" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D19" s="1">
         <v>0</v>
@@ -8955,44 +9022,44 @@
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
       <c r="H19" s="49" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="I19" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="20" s="42" customFormat="1" spans="1:9">
-      <c r="A20" s="50" t="s">
-        <v>153</v>
-      </c>
-      <c r="B20" s="51" t="s">
-        <v>154</v>
-      </c>
-      <c r="C20" s="51" t="s">
-        <v>154</v>
-      </c>
-      <c r="D20" s="51">
-        <v>0</v>
-      </c>
-      <c r="E20" s="51"/>
-      <c r="F20" s="51"/>
-      <c r="G20" s="51"/>
-      <c r="H20" s="51" t="s">
-        <v>276</v>
-      </c>
-      <c r="I20" s="42" t="s">
-        <v>277</v>
+        <v>279</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="48" t="s">
+        <v>149</v>
+      </c>
+      <c r="B20" s="49" t="s">
+        <v>150</v>
+      </c>
+      <c r="C20" s="49" t="s">
+        <v>150</v>
+      </c>
+      <c r="D20" s="1">
+        <v>0</v>
+      </c>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="49" t="s">
+        <v>280</v>
+      </c>
+      <c r="I20" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="21" s="42" customFormat="1" spans="1:9">
       <c r="A21" s="50" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B21" s="51" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C21" s="51" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D21" s="51">
         <v>0</v>
@@ -9001,21 +9068,21 @@
       <c r="F21" s="51"/>
       <c r="G21" s="51"/>
       <c r="H21" s="51" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="I21" s="42" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
     </row>
     <row r="22" s="42" customFormat="1" spans="1:9">
       <c r="A22" s="50" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B22" s="51" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C22" s="51" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D22" s="51">
         <v>0</v>
@@ -9024,44 +9091,44 @@
       <c r="F22" s="51"/>
       <c r="G22" s="51"/>
       <c r="H22" s="51" t="s">
+        <v>284</v>
+      </c>
+      <c r="I22" s="42" t="s">
         <v>279</v>
       </c>
-      <c r="I22" s="42" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9">
-      <c r="A23" s="52" t="s">
-        <v>160</v>
-      </c>
-      <c r="B23" s="53" t="s">
-        <v>161</v>
-      </c>
-      <c r="C23" s="53" t="s">
-        <v>161</v>
-      </c>
-      <c r="D23" s="1">
-        <v>0</v>
-      </c>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
-      <c r="H23" s="53" t="s">
-        <v>281</v>
-      </c>
-      <c r="I23" t="s">
-        <v>282</v>
+    </row>
+    <row r="23" s="42" customFormat="1" spans="1:9">
+      <c r="A23" s="50" t="s">
+        <v>158</v>
+      </c>
+      <c r="B23" s="51" t="s">
+        <v>159</v>
+      </c>
+      <c r="C23" s="51" t="s">
+        <v>159</v>
+      </c>
+      <c r="D23" s="51">
+        <v>0</v>
+      </c>
+      <c r="E23" s="51"/>
+      <c r="F23" s="51"/>
+      <c r="G23" s="51"/>
+      <c r="H23" s="51" t="s">
+        <v>285</v>
+      </c>
+      <c r="I23" s="42" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="52" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B24" s="53" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C24" s="53" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D24" s="1">
         <v>0</v>
@@ -9069,22 +9136,22 @@
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
-      <c r="H24" s="1" t="s">
-        <v>239</v>
+      <c r="H24" s="53" t="s">
+        <v>287</v>
       </c>
       <c r="I24" t="s">
-        <v>206</v>
+        <v>288</v>
       </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="52" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B25" s="53" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C25" s="53" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D25" s="1">
         <v>0</v>
@@ -9092,22 +9159,22 @@
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
-      <c r="H25" s="53" t="s">
-        <v>168</v>
+      <c r="H25" s="1" t="s">
+        <v>245</v>
       </c>
       <c r="I25" t="s">
-        <v>283</v>
+        <v>210</v>
       </c>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" s="48" t="s">
-        <v>169</v>
-      </c>
-      <c r="B26" s="49" t="s">
-        <v>170</v>
-      </c>
-      <c r="C26" s="49" t="s">
-        <v>170</v>
+      <c r="A26" s="52" t="s">
+        <v>166</v>
+      </c>
+      <c r="B26" s="53" t="s">
+        <v>167</v>
+      </c>
+      <c r="C26" s="53" t="s">
+        <v>167</v>
       </c>
       <c r="D26" s="1">
         <v>0</v>
@@ -9115,22 +9182,22 @@
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
-      <c r="H26" s="49" t="s">
-        <v>284</v>
+      <c r="H26" s="53" t="s">
+        <v>168</v>
       </c>
       <c r="I26" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="48" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B27" s="49" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C27" s="49" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D27" s="1">
         <v>0</v>
@@ -9139,21 +9206,21 @@
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
       <c r="H27" s="49" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="I27" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
       <c r="A28" s="48" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B28" s="49" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C28" s="49" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D28" s="1">
         <v>0</v>
@@ -9161,19 +9228,22 @@
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
-      <c r="H28" s="47" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9">
+      <c r="H28" s="49" t="s">
+        <v>291</v>
+      </c>
+      <c r="I28" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
       <c r="A29" s="48" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="B29" s="49" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C29" s="49" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D29" s="1">
         <v>0</v>
@@ -9181,22 +9251,19 @@
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
-      <c r="H29" s="49" t="s">
-        <v>287</v>
-      </c>
-      <c r="I29" t="s">
-        <v>282</v>
+      <c r="H29" s="47" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="48" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B30" s="49" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C30" s="49" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D30" s="1">
         <v>0</v>
@@ -9204,22 +9271,22 @@
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
-      <c r="H30" s="53" t="s">
-        <v>168</v>
+      <c r="H30" s="49" t="s">
+        <v>293</v>
       </c>
       <c r="I30" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8">
-      <c r="A31" s="46" t="s">
-        <v>183</v>
-      </c>
-      <c r="B31" s="47" t="s">
-        <v>184</v>
-      </c>
-      <c r="C31" s="47" t="s">
-        <v>184</v>
+        <v>288</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" s="48" t="s">
+        <v>181</v>
+      </c>
+      <c r="B31" s="49" t="s">
+        <v>182</v>
+      </c>
+      <c r="C31" s="49" t="s">
+        <v>182</v>
       </c>
       <c r="D31" s="1">
         <v>0</v>
@@ -9227,35 +9294,36 @@
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
-      <c r="H31" s="47" t="s">
+      <c r="H31" s="53" t="s">
+        <v>168</v>
+      </c>
+      <c r="I31" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" s="46" t="s">
+        <v>183</v>
+      </c>
+      <c r="B32" s="47" t="s">
+        <v>184</v>
+      </c>
+      <c r="C32" s="47" t="s">
+        <v>184</v>
+      </c>
+      <c r="D32" s="1">
+        <v>0</v>
+      </c>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="47" t="s">
         <v>185</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8">
-      <c r="A32" s="40" t="s">
-        <v>140</v>
-      </c>
-      <c r="B32" s="1"/>
-      <c r="C32" s="40"/>
-      <c r="D32" s="1">
-        <v>1</v>
-      </c>
-      <c r="E32" s="1">
-        <v>0</v>
-      </c>
-      <c r="F32" s="1">
-        <v>1</v>
-      </c>
-      <c r="G32" s="40">
-        <v>5</v>
-      </c>
-      <c r="H32" s="1" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="40" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="B33" s="1"/>
       <c r="C33" s="40"/>
@@ -9269,10 +9337,32 @@
         <v>1</v>
       </c>
       <c r="G33" s="40">
+        <v>5</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" s="40" t="s">
+        <v>151</v>
+      </c>
+      <c r="B34" s="1"/>
+      <c r="C34" s="40"/>
+      <c r="D34" s="1">
+        <v>1</v>
+      </c>
+      <c r="E34" s="1">
+        <v>0</v>
+      </c>
+      <c r="F34" s="1">
+        <v>1</v>
+      </c>
+      <c r="G34" s="40">
         <v>8</v>
       </c>
-      <c r="H33" s="1" t="s">
-        <v>235</v>
+      <c r="H34" s="1" t="s">
+        <v>241</v>
       </c>
     </row>
   </sheetData>
@@ -9297,22 +9387,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="35" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="C1" s="35" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="D1" s="35" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="E1" s="35" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="F1" s="35" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="G1" s="35" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -9320,22 +9410,22 @@
         <v>5</v>
       </c>
       <c r="B2" s="37" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="C2" s="37" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="D2" s="37" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="E2" s="37" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="F2" s="37" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="G2" s="38" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -9355,7 +9445,7 @@
         <v>108</v>
       </c>
       <c r="F3" s="37" t="s">
-        <v>300</v>
+        <v>196</v>
       </c>
       <c r="G3" s="37" t="s">
         <v>10</v>
@@ -9363,10 +9453,10 @@
     </row>
     <row r="4" ht="14.25" spans="1:7">
       <c r="A4" s="39" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="B4" s="40" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="C4" s="39">
         <v>100</v>
@@ -9381,15 +9471,15 @@
         <v>1</v>
       </c>
       <c r="G4" s="39" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
     </row>
     <row r="5" ht="14.25" spans="1:7">
       <c r="A5" s="39" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="B5" s="40" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="C5" s="39">
         <v>100</v>
@@ -9404,15 +9494,15 @@
         <v>1</v>
       </c>
       <c r="G5" s="39" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
     </row>
     <row r="6" ht="14.25" spans="1:7">
       <c r="A6" s="39" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="B6" s="40" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="C6" s="39">
         <v>3</v>
@@ -9427,15 +9517,15 @@
         <v>1</v>
       </c>
       <c r="G6" s="39" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="7" ht="14.25" spans="1:7">
       <c r="A7" s="39" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="B7" s="40" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="C7" s="39">
         <v>3</v>
@@ -9450,12 +9540,12 @@
         <v>1</v>
       </c>
       <c r="G7" s="39" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
     </row>
     <row r="8" ht="14.25" spans="1:7">
       <c r="A8" s="39" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="B8" s="40" t="s">
         <v>8</v>
@@ -9473,15 +9563,15 @@
         <v>1</v>
       </c>
       <c r="G8" s="39" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
     </row>
     <row r="9" ht="14.25" spans="1:7">
       <c r="A9" s="39" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="B9" s="40" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="C9" s="39">
         <v>0</v>
@@ -9496,15 +9586,15 @@
         <v>1</v>
       </c>
       <c r="G9" s="39" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
     </row>
     <row r="10" ht="14.25" spans="1:7">
       <c r="A10" s="39" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="B10" s="40" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="C10" s="39">
         <v>0</v>
@@ -9519,15 +9609,15 @@
         <v>1</v>
       </c>
       <c r="G10" s="39" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
     </row>
     <row r="11" ht="14.25" spans="1:7">
       <c r="A11" s="39" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="B11" s="40" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="C11" s="39">
         <v>0</v>
@@ -9542,15 +9632,15 @@
         <v>1</v>
       </c>
       <c r="G11" s="39" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12" ht="14.25" spans="1:7">
       <c r="A12" s="39" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="B12" s="40" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="C12" s="39">
         <v>0</v>
@@ -9565,15 +9655,15 @@
         <v>1</v>
       </c>
       <c r="G12" s="39" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
     </row>
     <row r="13" ht="14.25" spans="1:7">
       <c r="A13" s="39" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="B13" s="40" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="C13" s="39">
         <v>0</v>
@@ -9588,15 +9678,15 @@
         <v>1</v>
       </c>
       <c r="G13" s="39" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
     </row>
     <row r="14" ht="14.25" spans="1:7">
       <c r="A14" s="39" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="B14" s="40" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C14" s="39">
         <v>0</v>
@@ -9611,7 +9701,7 @@
         <v>1</v>
       </c>
       <c r="G14" s="39" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
     </row>
   </sheetData>

--- a/xlsdir/配置-总表.xlsx
+++ b/xlsdir/配置-总表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="673" firstSheet="3" activeTab="6"/>
+    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="673" firstSheet="3" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="character|角色" sheetId="32" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="873" uniqueCount="562">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="858" uniqueCount="557">
   <si>
     <t>ID</t>
   </si>
@@ -652,18 +652,6 @@
     <t>bool</t>
   </si>
   <si>
-    <t>格挡</t>
-  </si>
-  <si>
-    <t>持续到下一个回合开始之前，格挡伤害</t>
-  </si>
-  <si>
-    <t>res://asserts/textures/widgets/Buffs/fortify_spell.png</t>
-  </si>
-  <si>
-    <t>shielded</t>
-  </si>
-  <si>
     <t>strength</t>
   </si>
   <si>
@@ -782,298 +770,295 @@
     <t>技能效果描述</t>
   </si>
   <si>
+    <t>护盾*5</t>
+  </si>
+  <si>
+    <t>获得5点护盾</t>
+  </si>
+  <si>
+    <t>trounce_01</t>
+  </si>
+  <si>
+    <t>造成8点伤害</t>
+  </si>
+  <si>
+    <t>trounce_02</t>
+  </si>
+  <si>
+    <t>给予易伤</t>
+  </si>
+  <si>
+    <t>vulnerable*2</t>
+  </si>
+  <si>
+    <t>给与2层易伤</t>
+  </si>
+  <si>
+    <t>易伤（Vulnerable）</t>
+  </si>
+  <si>
+    <t>目标受到的伤害增加50%。</t>
+  </si>
+  <si>
+    <t>WEAK</t>
+  </si>
+  <si>
+    <t>弱化（Weak）</t>
+  </si>
+  <si>
+    <t>目标造成的伤害减少25%。</t>
+  </si>
+  <si>
+    <t>POISONED</t>
+  </si>
+  <si>
+    <t>中毒（Poisoned）</t>
+  </si>
+  <si>
+    <t>在目标的回合开始时，中毒将造成等同于其堆叠数的伤害，并减少1点堆叠数。</t>
+  </si>
+  <si>
+    <t>BURNING</t>
+  </si>
+  <si>
+    <t>燃烧（Burning）</t>
+  </si>
+  <si>
+    <t>燃烧</t>
+  </si>
+  <si>
+    <t>每回合结束时，目标受到等同于燃烧堆叠数的伤害，然后燃烧堆叠数减半。</t>
+  </si>
+  <si>
+    <t>STRENGTHENED</t>
+  </si>
+  <si>
+    <t>强化（Strengthened）</t>
+  </si>
+  <si>
+    <t>目标的攻击力增加。</t>
+  </si>
+  <si>
+    <t>REGENERATING</t>
+  </si>
+  <si>
+    <t>再生（Regenerating）</t>
+  </si>
+  <si>
+    <t>目标每回合恢复5生命值。</t>
+  </si>
+  <si>
+    <t>BLEEDING</t>
+  </si>
+  <si>
+    <t>流血（Bleeding）</t>
+  </si>
+  <si>
+    <t>流血</t>
+  </si>
+  <si>
+    <t>每回合结束时，目标受到等同于流血堆叠数的伤害。</t>
+  </si>
+  <si>
+    <t>ENERGIZED</t>
+  </si>
+  <si>
+    <t>充能（Energized）</t>
+  </si>
+  <si>
+    <t>充能</t>
+  </si>
+  <si>
+    <t>目标在下一回合获得额外的能量点数。</t>
+  </si>
+  <si>
+    <t>FROZEN</t>
+  </si>
+  <si>
+    <t>冻结（Frozen）</t>
+  </si>
+  <si>
+    <t>冻结</t>
+  </si>
+  <si>
+    <t>目标在下一回合无法行动。</t>
+  </si>
+  <si>
+    <t>分裂</t>
+  </si>
+  <si>
+    <t>史莱姆分裂成两个较小的实体，增加战斗中的敌人数量。</t>
+  </si>
+  <si>
+    <t>回复一定量的生命值，吸收的量取决于其当前生命值。</t>
+  </si>
+  <si>
+    <t>恢复</t>
+  </si>
+  <si>
+    <t>减少玩家下一回合的行动点数。</t>
+  </si>
+  <si>
+    <t>减少行动点数</t>
+  </si>
+  <si>
+    <t>造成持续性的毒素伤害。</t>
+  </si>
+  <si>
+    <t>放毒</t>
+  </si>
+  <si>
+    <t>所有人恢复10点生命值。</t>
+  </si>
+  <si>
+    <t>玩家获得“混乱”卡牌。</t>
+  </si>
+  <si>
+    <t>给与卡牌</t>
+  </si>
+  <si>
+    <t>对玩家造成10点伤害</t>
+  </si>
+  <si>
+    <t>伤害</t>
+  </si>
+  <si>
+    <t>获得护盾</t>
+  </si>
+  <si>
+    <t>对玩家造成12点伤害</t>
+  </si>
+  <si>
+    <t>蓄力一回合，下一回合对玩家造成双倍伤害</t>
+  </si>
+  <si>
+    <t>蓄力</t>
+  </si>
+  <si>
+    <t>造成15点伤害</t>
+  </si>
+  <si>
+    <t>造成5点伤害</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>BaseValue</t>
+  </si>
+  <si>
+    <t>min</t>
+  </si>
+  <si>
+    <t>max</t>
+  </si>
+  <si>
+    <t>visibility</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>属性名</t>
+  </si>
+  <si>
+    <t>最小值</t>
+  </si>
+  <si>
+    <t>最大值</t>
+  </si>
+  <si>
+    <t>可见性</t>
+  </si>
+  <si>
+    <t>属性描述</t>
+  </si>
+  <si>
+    <t>MaxHealth</t>
+  </si>
+  <si>
+    <t>最大生命值</t>
+  </si>
+  <si>
+    <t>角色的最大生命值</t>
+  </si>
+  <si>
+    <t>CurrentHealth</t>
+  </si>
+  <si>
+    <t>当前生命值</t>
+  </si>
+  <si>
+    <t>角色当前的生命值</t>
+  </si>
+  <si>
+    <t>MaxEnergy</t>
+  </si>
+  <si>
+    <t>最大能量值</t>
+  </si>
+  <si>
+    <t>角色可以累积的最大能量值</t>
+  </si>
+  <si>
+    <t>CurrentEnergy</t>
+  </si>
+  <si>
+    <t>当前能量值</t>
+  </si>
+  <si>
+    <t>角色当前的能量值</t>
+  </si>
+  <si>
+    <t>BaseAttack</t>
+  </si>
+  <si>
+    <t>角色基础的攻击力</t>
+  </si>
+  <si>
+    <t>BaseDefense</t>
+  </si>
+  <si>
+    <t>防御力</t>
+  </si>
+  <si>
+    <t>角色基础的防御值</t>
+  </si>
+  <si>
+    <t>Gold</t>
+  </si>
+  <si>
+    <t>金币</t>
+  </si>
+  <si>
+    <t>角色持有的金币数量</t>
+  </si>
+  <si>
+    <t>Strength</t>
+  </si>
+  <si>
+    <t>增加角色攻击力的强化值</t>
+  </si>
+  <si>
+    <t>Dexterity</t>
+  </si>
+  <si>
+    <t>影响角色行动速度或攻击速度的属性</t>
+  </si>
+  <si>
+    <t>MagicPower</t>
+  </si>
+  <si>
+    <t>魔法</t>
+  </si>
+  <si>
+    <t>影响角色魔法或特殊技能效果的属性</t>
+  </si>
+  <si>
+    <t>Shield</t>
+  </si>
+  <si>
     <t>护盾</t>
-  </si>
-  <si>
-    <t>获得5点护盾</t>
-  </si>
-  <si>
-    <t>护盾*5</t>
-  </si>
-  <si>
-    <t>block*5</t>
-  </si>
-  <si>
-    <t>trounce_01</t>
-  </si>
-  <si>
-    <t>造成8点伤害</t>
-  </si>
-  <si>
-    <t>trounce_02</t>
-  </si>
-  <si>
-    <t>给予易伤</t>
-  </si>
-  <si>
-    <t>vulnerable*2</t>
-  </si>
-  <si>
-    <t>给与2层易伤</t>
-  </si>
-  <si>
-    <t>易伤（Vulnerable）</t>
-  </si>
-  <si>
-    <t>目标受到的伤害增加50%。</t>
-  </si>
-  <si>
-    <t>WEAK</t>
-  </si>
-  <si>
-    <t>弱化（Weak）</t>
-  </si>
-  <si>
-    <t>目标造成的伤害减少25%。</t>
-  </si>
-  <si>
-    <t>POISONED</t>
-  </si>
-  <si>
-    <t>中毒（Poisoned）</t>
-  </si>
-  <si>
-    <t>在目标的回合开始时，中毒将造成等同于其堆叠数的伤害，并减少1点堆叠数。</t>
-  </si>
-  <si>
-    <t>BURNING</t>
-  </si>
-  <si>
-    <t>燃烧（Burning）</t>
-  </si>
-  <si>
-    <t>燃烧</t>
-  </si>
-  <si>
-    <t>每回合结束时，目标受到等同于燃烧堆叠数的伤害，然后燃烧堆叠数减半。</t>
-  </si>
-  <si>
-    <t>STRENGTHENED</t>
-  </si>
-  <si>
-    <t>强化（Strengthened）</t>
-  </si>
-  <si>
-    <t>目标的攻击力增加。</t>
-  </si>
-  <si>
-    <t>REGENERATING</t>
-  </si>
-  <si>
-    <t>再生（Regenerating）</t>
-  </si>
-  <si>
-    <t>目标每回合恢复5生命值。</t>
-  </si>
-  <si>
-    <t>BLEEDING</t>
-  </si>
-  <si>
-    <t>流血（Bleeding）</t>
-  </si>
-  <si>
-    <t>流血</t>
-  </si>
-  <si>
-    <t>每回合结束时，目标受到等同于流血堆叠数的伤害。</t>
-  </si>
-  <si>
-    <t>ENERGIZED</t>
-  </si>
-  <si>
-    <t>充能（Energized）</t>
-  </si>
-  <si>
-    <t>充能</t>
-  </si>
-  <si>
-    <t>目标在下一回合获得额外的能量点数。</t>
-  </si>
-  <si>
-    <t>FROZEN</t>
-  </si>
-  <si>
-    <t>冻结（Frozen）</t>
-  </si>
-  <si>
-    <t>冻结</t>
-  </si>
-  <si>
-    <t>目标在下一回合无法行动。</t>
-  </si>
-  <si>
-    <t>分裂</t>
-  </si>
-  <si>
-    <t>史莱姆分裂成两个较小的实体，增加战斗中的敌人数量。</t>
-  </si>
-  <si>
-    <t>回复一定量的生命值，吸收的量取决于其当前生命值。</t>
-  </si>
-  <si>
-    <t>恢复</t>
-  </si>
-  <si>
-    <t>减少玩家下一回合的行动点数。</t>
-  </si>
-  <si>
-    <t>减少行动点数</t>
-  </si>
-  <si>
-    <t>造成持续性的毒素伤害。</t>
-  </si>
-  <si>
-    <t>放毒</t>
-  </si>
-  <si>
-    <t>所有人恢复10点生命值。</t>
-  </si>
-  <si>
-    <t>玩家获得“混乱”卡牌。</t>
-  </si>
-  <si>
-    <t>给与卡牌</t>
-  </si>
-  <si>
-    <t>对玩家造成10点伤害</t>
-  </si>
-  <si>
-    <t>伤害</t>
-  </si>
-  <si>
-    <t>获得护盾</t>
-  </si>
-  <si>
-    <t>对玩家造成12点伤害</t>
-  </si>
-  <si>
-    <t>蓄力一回合，下一回合对玩家造成双倍伤害</t>
-  </si>
-  <si>
-    <t>蓄力</t>
-  </si>
-  <si>
-    <t>造成15点伤害</t>
-  </si>
-  <si>
-    <t>造成5点伤害</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>BaseValue</t>
-  </si>
-  <si>
-    <t>min</t>
-  </si>
-  <si>
-    <t>max</t>
-  </si>
-  <si>
-    <t>visibility</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>属性名</t>
-  </si>
-  <si>
-    <t>最小值</t>
-  </si>
-  <si>
-    <t>最大值</t>
-  </si>
-  <si>
-    <t>可见性</t>
-  </si>
-  <si>
-    <t>属性描述</t>
-  </si>
-  <si>
-    <t>MaxHealth</t>
-  </si>
-  <si>
-    <t>最大生命值</t>
-  </si>
-  <si>
-    <t>角色的最大生命值</t>
-  </si>
-  <si>
-    <t>CurrentHealth</t>
-  </si>
-  <si>
-    <t>当前生命值</t>
-  </si>
-  <si>
-    <t>角色当前的生命值</t>
-  </si>
-  <si>
-    <t>MaxEnergy</t>
-  </si>
-  <si>
-    <t>最大能量值</t>
-  </si>
-  <si>
-    <t>角色可以累积的最大能量值</t>
-  </si>
-  <si>
-    <t>CurrentEnergy</t>
-  </si>
-  <si>
-    <t>当前能量值</t>
-  </si>
-  <si>
-    <t>角色当前的能量值</t>
-  </si>
-  <si>
-    <t>BaseAttack</t>
-  </si>
-  <si>
-    <t>角色基础的攻击力</t>
-  </si>
-  <si>
-    <t>BaseDefense</t>
-  </si>
-  <si>
-    <t>防御力</t>
-  </si>
-  <si>
-    <t>角色基础的防御值</t>
-  </si>
-  <si>
-    <t>Gold</t>
-  </si>
-  <si>
-    <t>金币</t>
-  </si>
-  <si>
-    <t>角色持有的金币数量</t>
-  </si>
-  <si>
-    <t>Strength</t>
-  </si>
-  <si>
-    <t>增加角色攻击力的强化值</t>
-  </si>
-  <si>
-    <t>Dexterity</t>
-  </si>
-  <si>
-    <t>影响角色行动速度或攻击速度的属性</t>
-  </si>
-  <si>
-    <t>MagicPower</t>
-  </si>
-  <si>
-    <t>魔法</t>
-  </si>
-  <si>
-    <t>影响角色魔法或特殊技能效果的属性</t>
-  </si>
-  <si>
-    <t>Shield</t>
   </si>
   <si>
     <t>充当额外生命值的保护层</t>
@@ -3627,67 +3612,67 @@
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="P1" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="Q1" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="R1" s="13" t="s">
         <v>345</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="S1" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="T1" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="U1" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="V1" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="R1" s="13" t="s">
+      <c r="W1" s="14" t="s">
         <v>350</v>
-      </c>
-      <c r="S1" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="T1" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="U1" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="V1" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="W1" s="14" t="s">
-        <v>355</v>
       </c>
       <c r="X1" s="15"/>
       <c r="Y1" s="15"/>
@@ -3699,82 +3684,82 @@
         <v>5</v>
       </c>
       <c r="B2" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>354</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="I2" s="5" t="s">
         <v>356</v>
       </c>
-      <c r="C2" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="D2" s="5" t="s">
+      <c r="J2" s="5" t="s">
         <v>357</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="K2" s="5" t="s">
         <v>358</v>
       </c>
-      <c r="F2" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="G2" s="5" t="s">
+      <c r="L2" s="5" t="s">
         <v>359</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="M2" s="5" t="s">
         <v>360</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="N2" s="5" t="s">
         <v>361</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="O2" s="5" t="s">
         <v>362</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="P2" s="5" t="s">
         <v>363</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="Q2" s="5" t="s">
         <v>364</v>
       </c>
-      <c r="M2" s="5" t="s">
+      <c r="R2" s="16" t="s">
         <v>365</v>
       </c>
-      <c r="N2" s="5" t="s">
+      <c r="S2" s="5" t="s">
         <v>366</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="T2" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="U2" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="V2" s="5" t="s">
         <v>367</v>
       </c>
-      <c r="P2" s="5" t="s">
+      <c r="W2" s="17" t="s">
+        <v>364</v>
+      </c>
+      <c r="X2" s="18" t="s">
         <v>368</v>
       </c>
-      <c r="Q2" s="5" t="s">
+      <c r="Y2" s="32" t="s">
         <v>369</v>
       </c>
-      <c r="R2" s="16" t="s">
+      <c r="Z2" s="32" t="s">
         <v>370</v>
       </c>
-      <c r="S2" s="5" t="s">
+      <c r="AA2" s="33" t="s">
         <v>371</v>
-      </c>
-      <c r="T2" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="U2" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="V2" s="5" t="s">
-        <v>372</v>
-      </c>
-      <c r="W2" s="17" t="s">
-        <v>369</v>
-      </c>
-      <c r="X2" s="18" t="s">
-        <v>373</v>
-      </c>
-      <c r="Y2" s="32" t="s">
-        <v>374</v>
-      </c>
-      <c r="Z2" s="32" t="s">
-        <v>375</v>
-      </c>
-      <c r="AA2" s="33" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="3" ht="14.25" spans="1:27">
@@ -3865,7 +3850,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="C4" s="9">
         <v>10</v>
@@ -3921,16 +3906,16 @@
       <c r="V4" s="9"/>
       <c r="W4" s="23"/>
       <c r="X4" s="70" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="Y4" s="9" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="Z4" s="9" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="AA4" s="23" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
     </row>
     <row r="5" spans="1:27">
@@ -3938,7 +3923,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="C5" s="1">
         <v>10</v>
@@ -3994,16 +3979,16 @@
       <c r="V5" s="1"/>
       <c r="W5" s="26"/>
       <c r="X5" s="27" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="Y5" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="Z5" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="Z5" s="1" t="s">
-        <v>384</v>
-      </c>
       <c r="AA5" s="26" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
     </row>
     <row r="6" spans="1:27">
@@ -4011,7 +3996,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="C6" s="1">
         <v>10</v>
@@ -4067,16 +4052,16 @@
       <c r="V6" s="1"/>
       <c r="W6" s="26"/>
       <c r="X6" s="27" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="Y6" s="1" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="Z6" s="1" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="AA6" s="26" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
     </row>
     <row r="7" spans="1:27">
@@ -4084,7 +4069,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="C7" s="1">
         <v>10</v>
@@ -4140,16 +4125,16 @@
       <c r="V7" s="1"/>
       <c r="W7" s="26"/>
       <c r="X7" s="27" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="Y7" s="1" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="Z7" s="1" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="AA7" s="26" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
     </row>
     <row r="8" spans="1:27">
@@ -4157,7 +4142,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="C8" s="1">
         <v>10</v>
@@ -4213,16 +4198,16 @@
       <c r="V8" s="1"/>
       <c r="W8" s="26"/>
       <c r="X8" s="27" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="Y8" s="1" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="Z8" s="1" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="AA8" s="26" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
     </row>
     <row r="9" spans="1:27">
@@ -4230,7 +4215,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="C9" s="1">
         <v>10</v>
@@ -4286,16 +4271,16 @@
       <c r="V9" s="1"/>
       <c r="W9" s="26"/>
       <c r="X9" s="27" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="Y9" s="1" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="Z9" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="AA9" s="26" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
     </row>
     <row r="10" spans="1:27">
@@ -4303,7 +4288,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="C10" s="1">
         <v>10</v>
@@ -4359,16 +4344,16 @@
       <c r="V10" s="1"/>
       <c r="W10" s="26"/>
       <c r="X10" s="27" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="Y10" s="1" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="Z10" s="1" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="AA10" s="26" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
     </row>
     <row r="11" spans="1:27">
@@ -4376,7 +4361,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="C11" s="1">
         <v>10</v>
@@ -4432,16 +4417,16 @@
       <c r="V11" s="1"/>
       <c r="W11" s="26"/>
       <c r="X11" s="27" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="Y11" s="1" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="Z11" s="1" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="AA11" s="26" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
     </row>
     <row r="12" spans="1:27">
@@ -4449,7 +4434,7 @@
         <v>9</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="C12" s="1">
         <v>10</v>
@@ -4505,16 +4490,16 @@
       <c r="V12" s="1"/>
       <c r="W12" s="26"/>
       <c r="X12" s="27" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="Y12" s="1" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="Z12" s="1" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="AA12" s="26" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
     </row>
     <row r="13" spans="1:27">
@@ -4522,7 +4507,7 @@
         <v>10</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="C13" s="1">
         <v>10</v>
@@ -4578,16 +4563,16 @@
       <c r="V13" s="1"/>
       <c r="W13" s="26"/>
       <c r="X13" s="27" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="Y13" s="1" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="Z13" s="1" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="AA13" s="26" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
     </row>
     <row r="14" spans="1:27">
@@ -4595,7 +4580,7 @@
         <v>11</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="C14" s="1">
         <v>10</v>
@@ -4651,16 +4636,16 @@
       <c r="V14" s="1"/>
       <c r="W14" s="26"/>
       <c r="X14" s="27" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="Y14" s="1" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="Z14" s="1" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="AA14" s="26" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
     </row>
     <row r="15" spans="1:27">
@@ -4668,7 +4653,7 @@
         <v>12</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="C15" s="1">
         <v>10</v>
@@ -4724,16 +4709,16 @@
       <c r="V15" s="1"/>
       <c r="W15" s="26"/>
       <c r="X15" s="27" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="Y15" s="1" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="Z15" s="1" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="AA15" s="26" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
     </row>
     <row r="16" spans="1:27">
@@ -4741,7 +4726,7 @@
         <v>13</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="C16" s="1">
         <v>10</v>
@@ -4797,16 +4782,16 @@
       <c r="V16" s="1"/>
       <c r="W16" s="26"/>
       <c r="X16" s="27" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="Y16" s="1" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="Z16" s="1" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="AA16" s="26" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
     </row>
     <row r="17" spans="1:27">
@@ -4814,7 +4799,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="C17" s="1">
         <v>10</v>
@@ -4870,16 +4855,16 @@
       <c r="V17" s="1"/>
       <c r="W17" s="26"/>
       <c r="X17" s="27" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="Y17" s="1" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="Z17" s="1" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="AA17" s="26" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
     </row>
     <row r="18" spans="1:27">
@@ -4887,7 +4872,7 @@
         <v>15</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="C18" s="1">
         <v>10</v>
@@ -4943,16 +4928,16 @@
       <c r="V18" s="1"/>
       <c r="W18" s="26"/>
       <c r="X18" s="27" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="Y18" s="1" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="Z18" s="1" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="AA18" s="26" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
     </row>
     <row r="19" spans="1:27">
@@ -4960,7 +4945,7 @@
         <v>16</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="C19" s="1">
         <v>10</v>
@@ -5016,16 +5001,16 @@
       <c r="V19" s="1"/>
       <c r="W19" s="26"/>
       <c r="X19" s="27" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="Y19" s="1" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="Z19" s="1" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="AA19" s="26" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
     </row>
     <row r="20" spans="1:27">
@@ -5033,7 +5018,7 @@
         <v>17</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="C20" s="1">
         <v>10</v>
@@ -5089,16 +5074,16 @@
       <c r="V20" s="1"/>
       <c r="W20" s="26"/>
       <c r="X20" s="27" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="Y20" s="1" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="Z20" s="1" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="AA20" s="26" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
     </row>
     <row r="21" spans="1:27">
@@ -5106,7 +5091,7 @@
         <v>18</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="C21" s="1">
         <v>10</v>
@@ -5162,16 +5147,16 @@
       <c r="V21" s="1"/>
       <c r="W21" s="26"/>
       <c r="X21" s="27" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="Y21" s="1" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="Z21" s="1" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="AA21" s="26" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
     </row>
     <row r="22" spans="1:27">
@@ -5179,7 +5164,7 @@
         <v>19</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="C22" s="1">
         <v>10</v>
@@ -5235,16 +5220,16 @@
       <c r="V22" s="1"/>
       <c r="W22" s="26"/>
       <c r="X22" s="27" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="Y22" s="1" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="Z22" s="1" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="AA22" s="26" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
     </row>
     <row r="23" spans="1:27">
@@ -5252,7 +5237,7 @@
         <v>20</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="C23" s="1">
         <v>10</v>
@@ -5308,16 +5293,16 @@
       <c r="V23" s="1"/>
       <c r="W23" s="26"/>
       <c r="X23" s="27" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="Y23" s="1" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="Z23" s="1" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="AA23" s="26" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
     </row>
     <row r="24" spans="1:27">
@@ -5325,7 +5310,7 @@
         <v>21</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="C24" s="1">
         <v>10</v>
@@ -5381,16 +5366,16 @@
       <c r="V24" s="1"/>
       <c r="W24" s="26"/>
       <c r="X24" s="27" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="Y24" s="1" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="Z24" s="1" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="AA24" s="26" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
     </row>
     <row r="25" spans="1:27">
@@ -5398,7 +5383,7 @@
         <v>22</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="C25" s="1">
         <v>10</v>
@@ -5454,16 +5439,16 @@
       <c r="V25" s="1"/>
       <c r="W25" s="26"/>
       <c r="X25" s="27" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="Y25" s="1" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="Z25" s="1" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="AA25" s="26" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
     </row>
     <row r="26" spans="1:27">
@@ -5471,7 +5456,7 @@
         <v>23</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="C26" s="1">
         <v>10</v>
@@ -5527,16 +5512,16 @@
       <c r="V26" s="1"/>
       <c r="W26" s="26"/>
       <c r="X26" s="27" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="Y26" s="1" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="Z26" s="1" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="AA26" s="26" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
     </row>
     <row r="27" spans="1:27">
@@ -5544,7 +5529,7 @@
         <v>24</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="C27" s="1">
         <v>10</v>
@@ -5600,16 +5585,16 @@
       <c r="V27" s="1"/>
       <c r="W27" s="26"/>
       <c r="X27" s="27" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="Y27" s="1" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="Z27" s="1" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="AA27" s="26" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
     </row>
     <row r="28" spans="1:27">
@@ -5617,7 +5602,7 @@
         <v>25</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="C28" s="1">
         <v>10</v>
@@ -5673,16 +5658,16 @@
       <c r="V28" s="1"/>
       <c r="W28" s="26"/>
       <c r="X28" s="27" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="Y28" s="1" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="Z28" s="1" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="AA28" s="26" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
     </row>
     <row r="29" spans="1:27">
@@ -5690,7 +5675,7 @@
         <v>26</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="C29" s="1">
         <v>10</v>
@@ -5746,16 +5731,16 @@
       <c r="V29" s="1"/>
       <c r="W29" s="26"/>
       <c r="X29" s="27" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="Y29" s="1" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="Z29" s="1" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="AA29" s="26" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
     </row>
     <row r="30" spans="1:27">
@@ -5763,7 +5748,7 @@
         <v>27</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="C30" s="1">
         <v>10</v>
@@ -5819,16 +5804,16 @@
       <c r="V30" s="1"/>
       <c r="W30" s="26"/>
       <c r="X30" s="27" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="Y30" s="1" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="Z30" s="1" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="AA30" s="26" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
     </row>
     <row r="31" spans="1:27">
@@ -5836,7 +5821,7 @@
         <v>28</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="C31" s="1">
         <v>10</v>
@@ -5892,16 +5877,16 @@
       <c r="V31" s="1"/>
       <c r="W31" s="26"/>
       <c r="X31" s="27" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="Y31" s="1" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="Z31" s="1" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="AA31" s="26" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
     </row>
     <row r="32" spans="1:27">
@@ -5909,7 +5894,7 @@
         <v>29</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="C32" s="1">
         <v>10</v>
@@ -5965,16 +5950,16 @@
       <c r="V32" s="1"/>
       <c r="W32" s="26"/>
       <c r="X32" s="27" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="Y32" s="1" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="Z32" s="1" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="AA32" s="26" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
     </row>
     <row r="33" spans="1:27">
@@ -5982,7 +5967,7 @@
         <v>30</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="C33" s="1">
         <v>10</v>
@@ -6038,16 +6023,16 @@
       <c r="V33" s="1"/>
       <c r="W33" s="26"/>
       <c r="X33" s="27" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="Y33" s="1" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="Z33" s="1" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="AA33" s="26" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
     </row>
     <row r="34" spans="1:27">
@@ -6055,7 +6040,7 @@
         <v>31</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="C34" s="1">
         <v>10</v>
@@ -6111,16 +6096,16 @@
       <c r="V34" s="1"/>
       <c r="W34" s="26"/>
       <c r="X34" s="27" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="Y34" s="1" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="Z34" s="1" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="AA34" s="26" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
     </row>
     <row r="35" spans="1:27">
@@ -6128,7 +6113,7 @@
         <v>32</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="C35" s="1">
         <v>10</v>
@@ -6184,16 +6169,16 @@
       <c r="V35" s="1"/>
       <c r="W35" s="26"/>
       <c r="X35" s="27" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="Y35" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="Z35" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="AA35" s="26" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
     </row>
     <row r="36" spans="1:27">
@@ -6201,7 +6186,7 @@
         <v>33</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="C36" s="1">
         <v>10</v>
@@ -6257,16 +6242,16 @@
       <c r="V36" s="1"/>
       <c r="W36" s="26"/>
       <c r="X36" s="27" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="Y36" s="1" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="Z36" s="1" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="AA36" s="26" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
     </row>
     <row r="37" spans="1:27">
@@ -6274,7 +6259,7 @@
         <v>34</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="C37" s="1">
         <v>10</v>
@@ -6330,16 +6315,16 @@
       <c r="V37" s="1"/>
       <c r="W37" s="26"/>
       <c r="X37" s="27" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="Y37" s="1" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="Z37" s="1" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="AA37" s="26" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
     </row>
     <row r="38" spans="1:27">
@@ -6347,7 +6332,7 @@
         <v>35</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="C38" s="1">
         <v>10</v>
@@ -6403,16 +6388,16 @@
       <c r="V38" s="1"/>
       <c r="W38" s="26"/>
       <c r="X38" s="27" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="Y38" s="1" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="Z38" s="1" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="AA38" s="26" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
     </row>
     <row r="39" spans="1:27">
@@ -6420,7 +6405,7 @@
         <v>36</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="C39" s="1">
         <v>10</v>
@@ -6476,16 +6461,16 @@
       <c r="V39" s="1"/>
       <c r="W39" s="26"/>
       <c r="X39" s="27" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="Y39" s="1" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="Z39" s="1" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="AA39" s="26" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
     </row>
     <row r="40" spans="1:27">
@@ -6493,7 +6478,7 @@
         <v>37</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="C40" s="1">
         <v>10</v>
@@ -6549,16 +6534,16 @@
       <c r="V40" s="1"/>
       <c r="W40" s="26"/>
       <c r="X40" s="27" t="s">
-        <v>541</v>
+        <v>536</v>
       </c>
       <c r="Y40" s="1" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="Z40" s="1" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="AA40" s="26" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
     </row>
     <row r="41" ht="14.25" spans="1:27">
@@ -6566,7 +6551,7 @@
         <v>38</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="C41" s="12">
         <v>10</v>
@@ -6622,16 +6607,16 @@
       <c r="V41" s="12"/>
       <c r="W41" s="29"/>
       <c r="X41" s="30" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="Y41" s="12" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="Z41" s="12" t="s">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="AA41" s="29" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
     </row>
   </sheetData>
@@ -6695,7 +6680,7 @@
         <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>548</v>
+        <v>543</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -6703,7 +6688,7 @@
         <v>2</v>
       </c>
       <c r="B13" t="s">
-        <v>549</v>
+        <v>544</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -6711,7 +6696,7 @@
         <v>3</v>
       </c>
       <c r="B14" t="s">
-        <v>550</v>
+        <v>545</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -6719,7 +6704,7 @@
         <v>4</v>
       </c>
       <c r="B15" t="s">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="F15" t="s">
         <v>142</v>
@@ -6728,7 +6713,7 @@
         <v>142</v>
       </c>
       <c r="I15" t="s">
-        <v>552</v>
+        <v>547</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -6736,32 +6721,32 @@
         <v>5</v>
       </c>
       <c r="B16" t="s">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="F16" t="s">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="H16" t="s">
         <v>160</v>
       </c>
       <c r="I16" t="s">
-        <v>554</v>
+        <v>549</v>
       </c>
     </row>
     <row r="17" spans="6:9">
       <c r="F17" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="H17" t="s">
         <v>169</v>
       </c>
       <c r="I17" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
     </row>
     <row r="18" spans="2:9">
       <c r="B18" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="F18" t="s">
         <v>160</v>
@@ -6770,18 +6755,18 @@
         <v>153</v>
       </c>
       <c r="I18" t="s">
-        <v>558</v>
+        <v>553</v>
       </c>
     </row>
     <row r="19" spans="6:9">
       <c r="F19" t="s">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="H19" t="s">
         <v>178</v>
       </c>
       <c r="I19" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
     </row>
     <row r="20" spans="6:8">
@@ -6804,7 +6789,7 @@
     </row>
     <row r="22" spans="6:8">
       <c r="F22" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="H22">
         <f>IF('intent|意图'!F24='intent|意图'!F23,H21&amp;"*"&amp;'intent|意图'!D24,'intent|意图'!D24)</f>
@@ -6831,7 +6816,7 @@
     </row>
     <row r="25" spans="6:8">
       <c r="F25" t="s">
-        <v>558</v>
+        <v>553</v>
       </c>
       <c r="H25">
         <f>IF('intent|意图'!F18='intent|意图'!F17,H24&amp;"*"&amp;'intent|意图'!D18,'intent|意图'!D18)</f>
@@ -6840,7 +6825,7 @@
     </row>
     <row r="26" spans="6:8">
       <c r="F26" t="s">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="H26">
         <f>IF('intent|意图'!F19='intent|意图'!F18,H25&amp;"*"&amp;'intent|意图'!D19,'intent|意图'!D19)</f>
@@ -6858,7 +6843,7 @@
     </row>
     <row r="28" spans="6:8">
       <c r="F28" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="H28">
         <f>IF('intent|意图'!F27='intent|意图'!F26,H27&amp;"*"&amp;'intent|意图'!D27,'intent|意图'!D27)</f>
@@ -6876,32 +6861,32 @@
     </row>
     <row r="30" spans="2:2">
       <c r="B30" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
     </row>
     <row r="42" spans="2:2">
       <c r="B42" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
     </row>
     <row r="50" spans="2:2">
       <c r="B50" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
     </row>
     <row r="54" spans="2:2">
       <c r="B54" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
     </row>
     <row r="62" spans="2:2">
       <c r="B62" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
     </row>
     <row r="66" spans="2:2">
       <c r="B66" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
     </row>
   </sheetData>
@@ -7785,9 +7770,7 @@
       <c r="F13" s="62">
         <v>0</v>
       </c>
-      <c r="G13" s="61" t="s">
-        <v>3</v>
-      </c>
+      <c r="G13" s="61"/>
       <c r="H13" s="47" t="s">
         <v>144</v>
       </c>
@@ -7816,9 +7799,7 @@
       <c r="F14" s="63">
         <v>1</v>
       </c>
-      <c r="G14" s="61" t="s">
-        <v>3</v>
-      </c>
+      <c r="G14" s="61"/>
       <c r="H14" s="49" t="s">
         <v>144</v>
       </c>
@@ -7847,9 +7828,7 @@
       <c r="F15" s="63">
         <v>3</v>
       </c>
-      <c r="G15" s="61" t="s">
-        <v>3</v>
-      </c>
+      <c r="G15" s="61"/>
       <c r="H15" s="49" t="s">
         <v>144</v>
       </c>
@@ -7911,9 +7890,7 @@
       <c r="F17" s="64">
         <v>0</v>
       </c>
-      <c r="G17" s="61" t="s">
-        <v>3</v>
-      </c>
+      <c r="G17" s="61"/>
       <c r="H17" s="51" t="s">
         <v>144</v>
       </c>
@@ -7942,9 +7919,7 @@
       <c r="F18" s="64">
         <v>1</v>
       </c>
-      <c r="G18" s="61" t="s">
-        <v>3</v>
-      </c>
+      <c r="G18" s="61"/>
       <c r="H18" s="51" t="s">
         <v>144</v>
       </c>
@@ -7973,9 +7948,7 @@
       <c r="F19" s="64">
         <v>3</v>
       </c>
-      <c r="G19" s="61" t="s">
-        <v>3</v>
-      </c>
+      <c r="G19" s="61"/>
       <c r="H19" s="51" t="s">
         <v>144</v>
       </c>
@@ -8257,7 +8230,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="11.5" customWidth="1"/>
@@ -8360,42 +8333,32 @@
     </row>
     <row r="4" s="54" customFormat="1" spans="1:9">
       <c r="A4" s="56" t="s">
-        <v>86</v>
+        <v>197</v>
       </c>
       <c r="B4" s="56" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C4" s="56" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D4" s="56">
         <v>1</v>
       </c>
-      <c r="E4" s="56">
-        <v>1</v>
-      </c>
-      <c r="F4" s="56">
-        <v>2</v>
-      </c>
-      <c r="G4" s="56">
-        <v>5</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="I4" s="40" t="s">
-        <v>200</v>
-      </c>
+      <c r="E4" s="56"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="40"/>
+      <c r="I4" s="56"/>
     </row>
     <row r="5" s="54" customFormat="1" spans="1:9">
       <c r="A5" s="56" t="s">
+        <v>200</v>
+      </c>
+      <c r="B5" s="56" t="s">
         <v>201</v>
       </c>
-      <c r="B5" s="56" t="s">
+      <c r="C5" s="56" t="s">
         <v>202</v>
-      </c>
-      <c r="C5" s="56" t="s">
-        <v>203</v>
       </c>
       <c r="D5" s="56">
         <v>1</v>
@@ -8403,18 +8366,18 @@
       <c r="E5" s="56"/>
       <c r="F5" s="56"/>
       <c r="G5" s="56"/>
-      <c r="H5" s="40"/>
+      <c r="H5" s="1"/>
       <c r="I5" s="56"/>
     </row>
     <row r="6" s="54" customFormat="1" spans="1:9">
       <c r="A6" s="56" t="s">
+        <v>203</v>
+      </c>
+      <c r="B6" s="56" t="s">
         <v>204</v>
       </c>
-      <c r="B6" s="56" t="s">
+      <c r="C6" s="56" t="s">
         <v>205</v>
-      </c>
-      <c r="C6" s="56" t="s">
-        <v>206</v>
       </c>
       <c r="D6" s="56">
         <v>1</v>
@@ -8425,63 +8388,63 @@
       <c r="H6" s="1"/>
       <c r="I6" s="56"/>
     </row>
-    <row r="7" s="54" customFormat="1" spans="1:9">
-      <c r="A7" s="56" t="s">
+    <row r="7" spans="1:9">
+      <c r="A7" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B7" s="56" t="s">
+      <c r="D7" s="1">
+        <v>1</v>
+      </c>
+      <c r="E7" s="1">
+        <v>2</v>
+      </c>
+      <c r="F7" s="1">
+        <v>2</v>
+      </c>
+      <c r="G7" s="1">
+        <v>5</v>
+      </c>
+      <c r="H7" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="C7" s="56" t="s">
+      <c r="I7" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="D7" s="56">
-        <v>1</v>
-      </c>
-      <c r="E7" s="56"/>
-      <c r="F7" s="56"/>
-      <c r="G7" s="56"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="56"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>92</v>
+        <v>210</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D8" s="1">
-        <v>1</v>
-      </c>
-      <c r="E8" s="1">
-        <v>2</v>
-      </c>
-      <c r="F8" s="1">
-        <v>2</v>
-      </c>
-      <c r="G8" s="1">
-        <v>5</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>213</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>215</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>216</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -8494,13 +8457,13 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="C10" s="1" t="s">
         <v>218</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>219</v>
       </c>
       <c r="D10" s="1">
         <v>0</v>
@@ -8513,13 +8476,13 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>220</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>222</v>
       </c>
       <c r="D11" s="1">
         <v>0</v>
@@ -8527,27 +8490,8 @@
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
+      <c r="H11" s="47"/>
       <c r="I11" s="1"/>
-    </row>
-    <row r="12" spans="1:9">
-      <c r="A12" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="D12" s="1">
-        <v>0</v>
-      </c>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="47"/>
-      <c r="I12" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8558,7 +8502,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="22.625" customWidth="1"/>
@@ -8574,22 +8518,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>61</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="H1" s="5" t="s">
         <v>4</v>
@@ -8600,25 +8544,25 @@
         <v>5</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="C2" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="D2" s="44" t="s">
+        <v>227</v>
+      </c>
+      <c r="E2" s="43" t="s">
+        <v>228</v>
+      </c>
+      <c r="F2" s="43" t="s">
+        <v>229</v>
+      </c>
+      <c r="G2" s="43" t="s">
         <v>230</v>
       </c>
-      <c r="D2" s="44" t="s">
+      <c r="H2" s="5" t="s">
         <v>231</v>
-      </c>
-      <c r="E2" s="43" t="s">
-        <v>232</v>
-      </c>
-      <c r="F2" s="43" t="s">
-        <v>233</v>
-      </c>
-      <c r="G2" s="43" t="s">
-        <v>234</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -8673,11 +8617,11 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="40" t="s">
-        <v>200</v>
+        <v>85</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="40" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="D5" s="1">
         <v>1</v>
@@ -8692,40 +8636,40 @@
         <v>5</v>
       </c>
       <c r="H5" s="40" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="40" t="s">
-        <v>85</v>
-      </c>
-      <c r="B6" s="1"/>
-      <c r="C6" s="40" t="s">
-        <v>238</v>
-      </c>
-      <c r="D6" s="1">
-        <v>1</v>
-      </c>
-      <c r="E6" s="1">
-        <v>0</v>
-      </c>
-      <c r="F6" s="1">
-        <v>3</v>
-      </c>
-      <c r="G6" s="40" t="s">
-        <v>239</v>
-      </c>
-      <c r="H6" s="40" t="s">
-        <v>237</v>
+        <v>233</v>
+      </c>
+    </row>
+    <row r="6" s="41" customFormat="1" spans="1:8">
+      <c r="A6" s="45" t="s">
+        <v>234</v>
+      </c>
+      <c r="B6" s="45"/>
+      <c r="C6" s="45" t="s">
+        <v>88</v>
+      </c>
+      <c r="D6" s="45">
+        <v>0</v>
+      </c>
+      <c r="E6" s="45">
+        <v>0</v>
+      </c>
+      <c r="F6" s="45">
+        <v>1</v>
+      </c>
+      <c r="G6" s="45">
+        <v>8</v>
+      </c>
+      <c r="H6" s="45" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="7" s="41" customFormat="1" spans="1:8">
       <c r="A7" s="45" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="B7" s="45"/>
       <c r="C7" s="45" t="s">
-        <v>88</v>
+        <v>237</v>
       </c>
       <c r="D7" s="45">
         <v>0</v>
@@ -8734,98 +8678,98 @@
         <v>0</v>
       </c>
       <c r="F7" s="45">
-        <v>1</v>
-      </c>
-      <c r="G7" s="45">
-        <v>8</v>
+        <v>3</v>
+      </c>
+      <c r="G7" s="45" t="s">
+        <v>238</v>
       </c>
       <c r="H7" s="45" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0</v>
+      </c>
+      <c r="E8" s="1">
+        <v>2</v>
+      </c>
+      <c r="F8" s="1">
+        <v>4</v>
+      </c>
+      <c r="G8" s="1">
+        <v>1</v>
+      </c>
+      <c r="H8" s="1" t="s">
         <v>241</v>
-      </c>
-    </row>
-    <row r="8" s="41" customFormat="1" spans="1:8">
-      <c r="A8" s="45" t="s">
-        <v>242</v>
-      </c>
-      <c r="B8" s="45"/>
-      <c r="C8" s="45" t="s">
-        <v>243</v>
-      </c>
-      <c r="D8" s="45">
-        <v>0</v>
-      </c>
-      <c r="E8" s="45">
-        <v>0</v>
-      </c>
-      <c r="F8" s="45">
-        <v>3</v>
-      </c>
-      <c r="G8" s="45" t="s">
-        <v>244</v>
-      </c>
-      <c r="H8" s="45" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
-        <v>213</v>
+        <v>242</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>210</v>
+        <v>125</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
       </c>
       <c r="E9" s="1">
+        <v>1</v>
+      </c>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1">
         <v>2</v>
       </c>
-      <c r="F9" s="1">
-        <v>4</v>
-      </c>
-      <c r="G9" s="1">
-        <v>1</v>
-      </c>
       <c r="H9" s="1" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>125</v>
+        <v>214</v>
       </c>
       <c r="D10" s="1">
         <v>0</v>
       </c>
       <c r="E10" s="1">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="F10" s="1"/>
       <c r="G10" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>218</v>
+        <v>250</v>
       </c>
       <c r="D11" s="1">
         <v>0</v>
@@ -8835,117 +8779,117 @@
       </c>
       <c r="F11" s="1"/>
       <c r="G11" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>256</v>
+        <v>121</v>
       </c>
       <c r="D12" s="1">
         <v>0</v>
       </c>
       <c r="E12" s="1">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="F12" s="1"/>
       <c r="G12" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>121</v>
+        <v>204</v>
       </c>
       <c r="D13" s="1">
         <v>0</v>
       </c>
       <c r="E13" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F13" s="1"/>
       <c r="G13" s="1">
-        <v>5</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>260</v>
+        <v>6</v>
+      </c>
+      <c r="H13" s="40" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>208</v>
+        <v>260</v>
       </c>
       <c r="D14" s="1">
         <v>0</v>
       </c>
       <c r="E14" s="1">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="F14" s="1"/>
       <c r="G14" s="1">
-        <v>6</v>
-      </c>
-      <c r="H14" s="40" t="s">
-        <v>263</v>
+        <v>7</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>266</v>
-      </c>
       <c r="D15" s="1">
         <v>0</v>
       </c>
       <c r="E15" s="1">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>268</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>270</v>
       </c>
       <c r="D16" s="1">
         <v>0</v>
@@ -8955,45 +8899,41 @@
       </c>
       <c r="F16" s="1"/>
       <c r="G16" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H16" s="1" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="46" t="s">
+        <v>142</v>
+      </c>
+      <c r="B17" s="47" t="s">
+        <v>270</v>
+      </c>
+      <c r="C17" s="47" t="s">
+        <v>270</v>
+      </c>
+      <c r="D17" s="1">
+        <v>0</v>
+      </c>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="47" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
-      <c r="A17" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="D17" s="1">
-        <v>0</v>
-      </c>
-      <c r="E17" s="1">
-        <v>1</v>
-      </c>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1">
-        <v>9</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8">
-      <c r="A18" s="46" t="s">
-        <v>142</v>
-      </c>
-      <c r="B18" s="47" t="s">
-        <v>276</v>
-      </c>
-      <c r="C18" s="47" t="s">
-        <v>276</v>
+    <row r="18" spans="1:9">
+      <c r="A18" s="48" t="s">
+        <v>146</v>
+      </c>
+      <c r="B18" s="49" t="s">
+        <v>147</v>
+      </c>
+      <c r="C18" s="49" t="s">
+        <v>147</v>
       </c>
       <c r="D18" s="1">
         <v>0</v>
@@ -9001,19 +8941,22 @@
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
-      <c r="H18" s="47" t="s">
-        <v>277</v>
+      <c r="H18" s="49" t="s">
+        <v>272</v>
+      </c>
+      <c r="I18" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="48" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B19" s="49" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C19" s="49" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D19" s="1">
         <v>0</v>
@@ -9022,44 +8965,44 @@
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
       <c r="H19" s="49" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="I19" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9">
-      <c r="A20" s="48" t="s">
-        <v>149</v>
-      </c>
-      <c r="B20" s="49" t="s">
-        <v>150</v>
-      </c>
-      <c r="C20" s="49" t="s">
-        <v>150</v>
-      </c>
-      <c r="D20" s="1">
-        <v>0</v>
-      </c>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="49" t="s">
-        <v>280</v>
-      </c>
-      <c r="I20" t="s">
-        <v>281</v>
+        <v>275</v>
+      </c>
+    </row>
+    <row r="20" s="42" customFormat="1" spans="1:9">
+      <c r="A20" s="50" t="s">
+        <v>153</v>
+      </c>
+      <c r="B20" s="51" t="s">
+        <v>154</v>
+      </c>
+      <c r="C20" s="51" t="s">
+        <v>154</v>
+      </c>
+      <c r="D20" s="51">
+        <v>0</v>
+      </c>
+      <c r="E20" s="51"/>
+      <c r="F20" s="51"/>
+      <c r="G20" s="51"/>
+      <c r="H20" s="51" t="s">
+        <v>276</v>
+      </c>
+      <c r="I20" s="42" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="21" s="42" customFormat="1" spans="1:9">
       <c r="A21" s="50" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B21" s="51" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C21" s="51" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D21" s="51">
         <v>0</v>
@@ -9068,21 +9011,21 @@
       <c r="F21" s="51"/>
       <c r="G21" s="51"/>
       <c r="H21" s="51" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="I21" s="42" t="s">
-        <v>283</v>
+        <v>273</v>
       </c>
     </row>
     <row r="22" s="42" customFormat="1" spans="1:9">
       <c r="A22" s="50" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B22" s="51" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C22" s="51" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D22" s="51">
         <v>0</v>
@@ -9091,44 +9034,44 @@
       <c r="F22" s="51"/>
       <c r="G22" s="51"/>
       <c r="H22" s="51" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="I22" s="42" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="23" s="42" customFormat="1" spans="1:9">
-      <c r="A23" s="50" t="s">
-        <v>158</v>
-      </c>
-      <c r="B23" s="51" t="s">
-        <v>159</v>
-      </c>
-      <c r="C23" s="51" t="s">
-        <v>159</v>
-      </c>
-      <c r="D23" s="51">
-        <v>0</v>
-      </c>
-      <c r="E23" s="51"/>
-      <c r="F23" s="51"/>
-      <c r="G23" s="51"/>
-      <c r="H23" s="51" t="s">
-        <v>285</v>
-      </c>
-      <c r="I23" s="42" t="s">
-        <v>286</v>
+        <v>280</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="52" t="s">
+        <v>160</v>
+      </c>
+      <c r="B23" s="53" t="s">
+        <v>161</v>
+      </c>
+      <c r="C23" s="53" t="s">
+        <v>161</v>
+      </c>
+      <c r="D23" s="1">
+        <v>0</v>
+      </c>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="53" t="s">
+        <v>281</v>
+      </c>
+      <c r="I23" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="52" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B24" s="53" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C24" s="53" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="D24" s="1">
         <v>0</v>
@@ -9136,22 +9079,22 @@
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
-      <c r="H24" s="53" t="s">
-        <v>287</v>
+      <c r="H24" s="1" t="s">
+        <v>239</v>
       </c>
       <c r="I24" t="s">
-        <v>288</v>
+        <v>206</v>
       </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="52" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B25" s="53" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C25" s="53" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="D25" s="1">
         <v>0</v>
@@ -9159,22 +9102,22 @@
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
-      <c r="H25" s="1" t="s">
-        <v>245</v>
+      <c r="H25" s="53" t="s">
+        <v>168</v>
       </c>
       <c r="I25" t="s">
-        <v>210</v>
+        <v>283</v>
       </c>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" s="52" t="s">
-        <v>166</v>
-      </c>
-      <c r="B26" s="53" t="s">
-        <v>167</v>
-      </c>
-      <c r="C26" s="53" t="s">
-        <v>167</v>
+      <c r="A26" s="48" t="s">
+        <v>169</v>
+      </c>
+      <c r="B26" s="49" t="s">
+        <v>170</v>
+      </c>
+      <c r="C26" s="49" t="s">
+        <v>170</v>
       </c>
       <c r="D26" s="1">
         <v>0</v>
@@ -9182,22 +9125,22 @@
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
-      <c r="H26" s="53" t="s">
-        <v>168</v>
+      <c r="H26" s="49" t="s">
+        <v>284</v>
       </c>
       <c r="I26" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="48" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B27" s="49" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C27" s="49" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="D27" s="1">
         <v>0</v>
@@ -9206,21 +9149,21 @@
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
       <c r="H27" s="49" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="I27" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
       <c r="A28" s="48" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B28" s="49" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C28" s="49" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D28" s="1">
         <v>0</v>
@@ -9228,22 +9171,19 @@
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
-      <c r="H28" s="49" t="s">
-        <v>291</v>
-      </c>
-      <c r="I28" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8">
+      <c r="H28" s="47" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
       <c r="A29" s="48" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B29" s="49" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C29" s="49" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D29" s="1">
         <v>0</v>
@@ -9251,19 +9191,22 @@
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
-      <c r="H29" s="47" t="s">
-        <v>177</v>
+      <c r="H29" s="49" t="s">
+        <v>287</v>
+      </c>
+      <c r="I29" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="48" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B30" s="49" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C30" s="49" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="D30" s="1">
         <v>0</v>
@@ -9271,22 +9214,22 @@
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
-      <c r="H30" s="49" t="s">
-        <v>293</v>
+      <c r="H30" s="53" t="s">
+        <v>168</v>
       </c>
       <c r="I30" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9">
-      <c r="A31" s="48" t="s">
-        <v>181</v>
-      </c>
-      <c r="B31" s="49" t="s">
-        <v>182</v>
-      </c>
-      <c r="C31" s="49" t="s">
-        <v>182</v>
+        <v>283</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" s="46" t="s">
+        <v>183</v>
+      </c>
+      <c r="B31" s="47" t="s">
+        <v>184</v>
+      </c>
+      <c r="C31" s="47" t="s">
+        <v>184</v>
       </c>
       <c r="D31" s="1">
         <v>0</v>
@@ -9294,36 +9237,35 @@
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
-      <c r="H31" s="53" t="s">
-        <v>168</v>
-      </c>
-      <c r="I31" t="s">
-        <v>289</v>
+      <c r="H31" s="47" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="32" spans="1:8">
-      <c r="A32" s="46" t="s">
-        <v>183</v>
-      </c>
-      <c r="B32" s="47" t="s">
-        <v>184</v>
-      </c>
-      <c r="C32" s="47" t="s">
-        <v>184</v>
-      </c>
+      <c r="A32" s="40" t="s">
+        <v>140</v>
+      </c>
+      <c r="B32" s="1"/>
+      <c r="C32" s="40"/>
       <c r="D32" s="1">
-        <v>0</v>
-      </c>
-      <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
-      <c r="G32" s="1"/>
-      <c r="H32" s="47" t="s">
-        <v>185</v>
+        <v>1</v>
+      </c>
+      <c r="E32" s="1">
+        <v>0</v>
+      </c>
+      <c r="F32" s="1">
+        <v>1</v>
+      </c>
+      <c r="G32" s="40">
+        <v>5</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="40" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="B33" s="1"/>
       <c r="C33" s="40"/>
@@ -9337,32 +9279,10 @@
         <v>1</v>
       </c>
       <c r="G33" s="40">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8">
-      <c r="A34" s="40" t="s">
-        <v>151</v>
-      </c>
-      <c r="B34" s="1"/>
-      <c r="C34" s="40"/>
-      <c r="D34" s="1">
-        <v>1</v>
-      </c>
-      <c r="E34" s="1">
-        <v>0</v>
-      </c>
-      <c r="F34" s="1">
-        <v>1</v>
-      </c>
-      <c r="G34" s="40">
-        <v>8</v>
-      </c>
-      <c r="H34" s="1" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
     </row>
   </sheetData>
@@ -9387,22 +9307,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="35" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="C1" s="35" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="D1" s="35" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="E1" s="35" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="F1" s="35" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="G1" s="35" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -9410,22 +9330,22 @@
         <v>5</v>
       </c>
       <c r="B2" s="37" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="C2" s="37" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="D2" s="37" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="E2" s="37" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="F2" s="37" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="G2" s="38" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -9453,10 +9373,10 @@
     </row>
     <row r="4" ht="14.25" spans="1:7">
       <c r="A4" s="39" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="B4" s="40" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="C4" s="39">
         <v>100</v>
@@ -9471,15 +9391,15 @@
         <v>1</v>
       </c>
       <c r="G4" s="39" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
     </row>
     <row r="5" ht="14.25" spans="1:7">
       <c r="A5" s="39" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="B5" s="40" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="C5" s="39">
         <v>100</v>
@@ -9494,15 +9414,15 @@
         <v>1</v>
       </c>
       <c r="G5" s="39" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
     </row>
     <row r="6" ht="14.25" spans="1:7">
       <c r="A6" s="39" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="B6" s="40" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="C6" s="39">
         <v>3</v>
@@ -9517,15 +9437,15 @@
         <v>1</v>
       </c>
       <c r="G6" s="39" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
     </row>
     <row r="7" ht="14.25" spans="1:7">
       <c r="A7" s="39" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="B7" s="40" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="C7" s="39">
         <v>3</v>
@@ -9540,12 +9460,12 @@
         <v>1</v>
       </c>
       <c r="G7" s="39" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
     </row>
     <row r="8" ht="14.25" spans="1:7">
       <c r="A8" s="39" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="B8" s="40" t="s">
         <v>8</v>
@@ -9563,15 +9483,15 @@
         <v>1</v>
       </c>
       <c r="G8" s="39" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
     </row>
     <row r="9" ht="14.25" spans="1:7">
       <c r="A9" s="39" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="B9" s="40" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="C9" s="39">
         <v>0</v>
@@ -9586,15 +9506,15 @@
         <v>1</v>
       </c>
       <c r="G9" s="39" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
     </row>
     <row r="10" ht="14.25" spans="1:7">
       <c r="A10" s="39" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="B10" s="40" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="C10" s="39">
         <v>0</v>
@@ -9609,15 +9529,15 @@
         <v>1</v>
       </c>
       <c r="G10" s="39" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="11" ht="14.25" spans="1:7">
       <c r="A11" s="39" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="B11" s="40" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="C11" s="39">
         <v>0</v>
@@ -9632,15 +9552,15 @@
         <v>1</v>
       </c>
       <c r="G11" s="39" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
     </row>
     <row r="12" ht="14.25" spans="1:7">
       <c r="A12" s="39" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="B12" s="40" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="C12" s="39">
         <v>0</v>
@@ -9655,15 +9575,15 @@
         <v>1</v>
       </c>
       <c r="G12" s="39" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
     </row>
     <row r="13" ht="14.25" spans="1:7">
       <c r="A13" s="39" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="B13" s="40" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="C13" s="39">
         <v>0</v>
@@ -9678,15 +9598,15 @@
         <v>1</v>
       </c>
       <c r="G13" s="39" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
     </row>
     <row r="14" ht="14.25" spans="1:7">
       <c r="A14" s="39" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="B14" s="40" t="s">
-        <v>236</v>
+        <v>328</v>
       </c>
       <c r="C14" s="39">
         <v>0</v>
@@ -9701,7 +9621,7 @@
         <v>1</v>
       </c>
       <c r="G14" s="39" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
     </row>
   </sheetData>

--- a/xlsdir/配置-总表.xlsx
+++ b/xlsdir/配置-总表.xlsx
@@ -4,11 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="673" firstSheet="3" activeTab="5"/>
+    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="673" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="character|角色" sheetId="32" r:id="rId1"/>
-    <sheet name="combat|战斗" sheetId="31" r:id="rId2"/>
+    <sheet name="combat|战斗" sheetId="31" r:id="rId1"/>
+    <sheet name="character|角色" sheetId="32" r:id="rId2"/>
     <sheet name="hero|玩家角色" sheetId="27" r:id="rId3"/>
     <sheet name="monster|魔物" sheetId="28" r:id="rId4"/>
     <sheet name="card|卡牌" sheetId="29" r:id="rId5"/>
@@ -48,6 +48,39 @@
     <t>name</t>
   </si>
   <si>
+    <t>mark_04</t>
+  </si>
+  <si>
+    <t>mark_05</t>
+  </si>
+  <si>
+    <t>mark_06</t>
+  </si>
+  <si>
+    <t>战斗名</t>
+  </si>
+  <si>
+    <t>位置1</t>
+  </si>
+  <si>
+    <t>位置2</t>
+  </si>
+  <si>
+    <t>位置3</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>测试用</t>
+  </si>
+  <si>
+    <t>slime</t>
+  </si>
+  <si>
+    <t>mushroom</t>
+  </si>
+  <si>
     <t>health</t>
   </si>
   <si>
@@ -72,9 +105,6 @@
     <t>描述</t>
   </si>
   <si>
-    <t>string</t>
-  </si>
-  <si>
     <t>int</t>
   </si>
   <si>
@@ -84,15 +114,18 @@
     <t>铁甲军团残留下的士兵，他出卖自己的灵魂，获得了恶魔的力量。</t>
   </si>
   <si>
-    <t>slime</t>
-  </si>
-  <si>
     <t>史莱姆</t>
   </si>
   <si>
     <t>一种黏滑的生物，能够分裂和吸收小型物体。史莱姆的主要攻击方式是覆盖和缠绕。</t>
   </si>
   <si>
+    <t>蘑菇怪</t>
+  </si>
+  <si>
+    <t>一种生长在森林里的神秘生物，能够释放毒素和治疗药剂。</t>
+  </si>
+  <si>
     <t>flying_eye</t>
   </si>
   <si>
@@ -111,15 +144,6 @@
     <t>一种小型、狡猾且迅速的生物。擅长使用小刀和陷阱。</t>
   </si>
   <si>
-    <t>mushroom</t>
-  </si>
-  <si>
-    <t>蘑菇怪</t>
-  </si>
-  <si>
-    <t>一种生长在森林里的神秘生物，能够释放毒素和治疗药剂。</t>
-  </si>
-  <si>
     <t>skeleton</t>
   </si>
   <si>
@@ -127,30 +151,6 @@
   </si>
   <si>
     <t>不死生物，使用古老的武器和盔甲。虽然动作缓慢，但具有较高的防御力。</t>
-  </si>
-  <si>
-    <t>mark_04</t>
-  </si>
-  <si>
-    <t>mark_05</t>
-  </si>
-  <si>
-    <t>mark_06</t>
-  </si>
-  <si>
-    <t>战斗名</t>
-  </si>
-  <si>
-    <t>位置1</t>
-  </si>
-  <si>
-    <t>位置2</t>
-  </si>
-  <si>
-    <t>位置3</t>
-  </si>
-  <si>
-    <t>测试用</t>
   </si>
   <si>
     <t>hero_name</t>
@@ -1861,7 +1861,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1898,6 +1898,14 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
@@ -2741,137 +2749,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="27" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="30" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="30" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="32" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="33" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="34" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="30" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="30" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="32" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="33" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="34" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3080,6 +3088,12 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1" quotePrefix="1">
@@ -3433,11 +3447,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
-  <cols>
-    <col min="5" max="5" width="37" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="4"/>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="5" t="s">
@@ -3457,37 +3468,37 @@
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="43" t="s">
+      <c r="A2" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="43" t="s">
+      <c r="C2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="43" t="s">
+      <c r="D2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="E2" s="5" t="s">
         <v>8</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -3495,101 +3506,14 @@
         <v>1</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="C4" s="1">
-        <v>80</v>
-      </c>
-      <c r="D4" s="1">
-        <v>0</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="1">
-        <v>50</v>
-      </c>
-      <c r="D5" s="1">
-        <v>10</v>
-      </c>
-      <c r="E5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="40" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="1">
-        <v>50</v>
-      </c>
-      <c r="D6" s="1">
-        <v>10</v>
-      </c>
-      <c r="E6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" s="40" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" s="1">
-        <v>50</v>
-      </c>
-      <c r="D7" s="1">
-        <v>10</v>
-      </c>
-      <c r="E7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" s="40" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" s="1">
-        <v>50</v>
-      </c>
-      <c r="D8" s="1">
-        <v>10</v>
-      </c>
-      <c r="E8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9" s="40" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" s="1">
-        <v>50</v>
-      </c>
-      <c r="D9" s="1">
-        <v>10</v>
-      </c>
-      <c r="E9" t="s">
-        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -3681,7 +3605,7 @@
     </row>
     <row r="2" ht="14.25" spans="1:27">
       <c r="A2" s="4" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>351</v>
@@ -3764,85 +3688,85 @@
     </row>
     <row r="3" ht="14.25" spans="1:27">
       <c r="A3" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="L3" s="7" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="N3" s="7" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="O3" s="7" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="P3" s="7" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="Q3" s="7" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="R3" s="19" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="S3" s="7" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="T3" s="7" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="U3" s="7" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="V3" s="7" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="W3" s="20" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="X3" s="21" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y3" s="21" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z3" s="21" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA3" s="34" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:27">
@@ -3905,7 +3829,7 @@
       <c r="U4" s="9"/>
       <c r="V4" s="9"/>
       <c r="W4" s="23"/>
-      <c r="X4" s="70" t="s">
+      <c r="X4" s="72" t="s">
         <v>373</v>
       </c>
       <c r="Y4" s="9" t="s">
@@ -6898,8 +6822,11 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="4"/>
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <cols>
+    <col min="5" max="5" width="79.625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="5" t="s">
@@ -6909,47 +6836,47 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>30</v>
+        <v>13</v>
+      </c>
+      <c r="D1" s="70" t="s">
+        <v>14</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>34</v>
+      <c r="A2" s="43" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="43" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="43" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="70" t="s">
+        <v>19</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>10</v>
+        <v>21</v>
+      </c>
+      <c r="D3" s="70" t="s">
+        <v>21</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -6957,14 +6884,101 @@
         <v>1</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="1"/>
+        <v>22</v>
+      </c>
+      <c r="C4" s="1">
+        <v>80</v>
+      </c>
+      <c r="D4" s="71">
+        <v>0</v>
+      </c>
       <c r="E4" s="1" t="s">
         <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="1">
+        <v>30</v>
+      </c>
+      <c r="D5" s="71">
+        <v>10</v>
+      </c>
+      <c r="E5" s="67" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="40" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="1">
+        <v>50</v>
+      </c>
+      <c r="D6" s="71">
+        <v>10</v>
+      </c>
+      <c r="E6" s="67" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="40" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="1">
+        <v>50</v>
+      </c>
+      <c r="D7" s="71">
+        <v>10</v>
+      </c>
+      <c r="E7" s="67" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" s="40" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="1">
+        <v>50</v>
+      </c>
+      <c r="D8" s="71">
+        <v>10</v>
+      </c>
+      <c r="E8" s="67" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="1">
+        <v>50</v>
+      </c>
+      <c r="D9" s="71">
+        <v>10</v>
+      </c>
+      <c r="E9" s="67" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -6999,7 +7013,7 @@
     </row>
     <row r="2" s="68" customFormat="1" spans="1:5">
       <c r="A2" s="43" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="B2" s="43" t="s">
         <v>39</v>
@@ -7016,19 +7030,19 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>43</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -7036,7 +7050,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>44</v>
@@ -7096,13 +7110,13 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>43</v>
@@ -7110,10 +7124,10 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B4" s="40" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C4" s="40" t="str">
         <f>"enemy_"&amp;A4</f>
@@ -7125,10 +7139,10 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="B5" s="40" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C5" s="40" t="str">
         <f>"enemy_"&amp;A5</f>
@@ -7140,10 +7154,10 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="B6" s="40" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="C6" s="40" t="str">
         <f>"enemy_"&amp;A6</f>
@@ -7155,10 +7169,10 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="B7" s="40" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="C7" s="40" t="str">
         <f>"enemy_"&amp;A7</f>
@@ -7170,10 +7184,10 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="B8" s="40" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="C8" s="40" t="str">
         <f>"enemy_"&amp;A8</f>
@@ -7240,7 +7254,7 @@
     </row>
     <row r="2" ht="54" spans="1:10">
       <c r="A2" s="43" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="B2" s="43" t="s">
         <v>65</v>
@@ -7272,34 +7286,34 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>74</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I3" s="5" t="s">
         <v>43</v>
       </c>
       <c r="J3" s="66" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -7487,34 +7501,34 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" s="60" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D3" s="60" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="E3" s="60" t="s">
         <v>108</v>
       </c>
       <c r="F3" s="60" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H3" s="55" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I3" s="55" t="s">
         <v>74</v>
       </c>
       <c r="J3" s="55" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="K3" s="55" t="s">
         <v>43</v>
@@ -7738,7 +7752,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="61" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="H12" s="40" t="s">
         <v>141</v>
@@ -7758,7 +7772,7 @@
         <v>142</v>
       </c>
       <c r="B13" s="47" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C13" s="47" t="s">
         <v>143</v>
@@ -7787,7 +7801,7 @@
         <v>146</v>
       </c>
       <c r="B14" s="49" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C14" s="49" t="s">
         <v>147</v>
@@ -7816,7 +7830,7 @@
         <v>149</v>
       </c>
       <c r="B15" s="49" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C15" s="49" t="s">
         <v>150</v>
@@ -7858,7 +7872,7 @@
         <v>0</v>
       </c>
       <c r="G16" s="61" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="H16" s="40" t="s">
         <v>152</v>
@@ -7878,7 +7892,7 @@
         <v>153</v>
       </c>
       <c r="B17" s="51" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="C17" s="51" t="s">
         <v>154</v>
@@ -7907,7 +7921,7 @@
         <v>156</v>
       </c>
       <c r="B18" s="51" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="C18" s="51" t="s">
         <v>157</v>
@@ -7936,7 +7950,7 @@
         <v>158</v>
       </c>
       <c r="B19" s="51" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="C19" s="51" t="s">
         <v>159</v>
@@ -7965,7 +7979,7 @@
         <v>160</v>
       </c>
       <c r="B20" s="53" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="C20" s="53" t="s">
         <v>161</v>
@@ -7994,7 +8008,7 @@
         <v>163</v>
       </c>
       <c r="B21" s="53" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="C21" s="53" t="s">
         <v>164</v>
@@ -8023,7 +8037,7 @@
         <v>166</v>
       </c>
       <c r="B22" s="53" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="C22" s="53" t="s">
         <v>167</v>
@@ -8052,7 +8066,7 @@
         <v>169</v>
       </c>
       <c r="B23" s="49" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="C23" s="49" t="s">
         <v>170</v>
@@ -8081,7 +8095,7 @@
         <v>172</v>
       </c>
       <c r="B24" s="49" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="C24" s="49" t="s">
         <v>173</v>
@@ -8110,7 +8124,7 @@
         <v>175</v>
       </c>
       <c r="B25" s="49" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="C25" s="49" t="s">
         <v>176</v>
@@ -8139,7 +8153,7 @@
         <v>178</v>
       </c>
       <c r="B26" s="49" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="C26" s="49" t="s">
         <v>179</v>
@@ -8168,7 +8182,7 @@
         <v>181</v>
       </c>
       <c r="B27" s="49" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="C27" s="49" t="s">
         <v>182</v>
@@ -8197,7 +8211,7 @@
         <v>183</v>
       </c>
       <c r="B28" s="47" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="C28" s="47" t="s">
         <v>184</v>
@@ -8252,7 +8266,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>186</v>
@@ -8275,13 +8289,13 @@
     </row>
     <row r="2" ht="148.5" spans="1:9">
       <c r="A2" s="43" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="B2" s="43" t="s">
         <v>190</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>191</v>
@@ -8304,25 +8318,25 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>196</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H3" s="55" t="s">
         <v>74</v>
@@ -8536,12 +8550,12 @@
         <v>225</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" ht="81" spans="1:8">
       <c r="A2" s="43" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>221</v>
@@ -8567,28 +8581,28 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>43</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -9327,7 +9341,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="36" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="B2" s="37" t="s">
         <v>295</v>
@@ -9350,10 +9364,10 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="37" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" s="37" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C3" s="37" t="s">
         <v>108</v>
@@ -9368,7 +9382,7 @@
         <v>196</v>
       </c>
       <c r="G3" s="37" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" ht="14.25" spans="1:7">
@@ -9468,7 +9482,7 @@
         <v>312</v>
       </c>
       <c r="B8" s="40" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C8" s="39">
         <v>10</v>

--- a/xlsdir/配置-总表.xlsx
+++ b/xlsdir/配置-总表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="673" activeTab="1"/>
+    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="673" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="combat|战斗" sheetId="31" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="858" uniqueCount="557">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="861" uniqueCount="559">
   <si>
     <t>ID</t>
   </si>
@@ -652,6 +652,12 @@
     <t>bool</t>
   </si>
   <si>
+    <t>格挡</t>
+  </si>
+  <si>
+    <t>格挡部分伤害</t>
+  </si>
+  <si>
     <t>strength</t>
   </si>
   <si>
@@ -682,7 +688,7 @@
     <t>易伤</t>
   </si>
   <si>
-    <t>使目标收到的攻击伤害增加</t>
+    <t>使目标受到的攻击伤害增加</t>
   </si>
   <si>
     <t>res://asserts/textures/widgets/Buffs/defense_down.png</t>
@@ -2879,7 +2885,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3046,6 +3052,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1">
@@ -3536,67 +3545,67 @@
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="R1" s="13" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="S1" s="3" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="T1" s="3" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="U1" s="3" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="V1" s="3" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="W1" s="14" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="X1" s="15"/>
       <c r="Y1" s="15"/>
@@ -3608,82 +3617,82 @@
         <v>16</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="O2" s="5" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="P2" s="5" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="Q2" s="5" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="R2" s="16" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="S2" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="T2" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="U2" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="V2" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="W2" s="17" t="s">
         <v>366</v>
       </c>
-      <c r="T2" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="U2" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="V2" s="5" t="s">
-        <v>367</v>
-      </c>
-      <c r="W2" s="17" t="s">
-        <v>364</v>
-      </c>
       <c r="X2" s="18" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="Y2" s="32" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="Z2" s="32" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AA2" s="33" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="3" ht="14.25" spans="1:27">
@@ -3774,7 +3783,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C4" s="9">
         <v>10</v>
@@ -3829,17 +3838,17 @@
       <c r="U4" s="9"/>
       <c r="V4" s="9"/>
       <c r="W4" s="23"/>
-      <c r="X4" s="72" t="s">
-        <v>373</v>
+      <c r="X4" s="73" t="s">
+        <v>375</v>
       </c>
       <c r="Y4" s="9" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="Z4" s="9" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AA4" s="23" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="5" spans="1:27">
@@ -3847,7 +3856,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C5" s="1">
         <v>10</v>
@@ -3903,16 +3912,16 @@
       <c r="V5" s="1"/>
       <c r="W5" s="26"/>
       <c r="X5" s="27" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="Y5" s="1" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="Z5" s="1" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AA5" s="26" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="6" spans="1:27">
@@ -3920,7 +3929,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C6" s="1">
         <v>10</v>
@@ -3976,16 +3985,16 @@
       <c r="V6" s="1"/>
       <c r="W6" s="26"/>
       <c r="X6" s="27" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="Y6" s="1" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="Z6" s="1" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AA6" s="26" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="7" spans="1:27">
@@ -3993,7 +4002,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C7" s="1">
         <v>10</v>
@@ -4049,16 +4058,16 @@
       <c r="V7" s="1"/>
       <c r="W7" s="26"/>
       <c r="X7" s="27" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="Y7" s="1" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="Z7" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AA7" s="26" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="8" spans="1:27">
@@ -4066,7 +4075,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C8" s="1">
         <v>10</v>
@@ -4122,16 +4131,16 @@
       <c r="V8" s="1"/>
       <c r="W8" s="26"/>
       <c r="X8" s="27" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="Y8" s="1" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="Z8" s="1" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AA8" s="26" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="9" spans="1:27">
@@ -4139,7 +4148,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C9" s="1">
         <v>10</v>
@@ -4195,16 +4204,16 @@
       <c r="V9" s="1"/>
       <c r="W9" s="26"/>
       <c r="X9" s="27" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="Y9" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="Z9" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AA9" s="26" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="10" spans="1:27">
@@ -4212,7 +4221,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C10" s="1">
         <v>10</v>
@@ -4268,16 +4277,16 @@
       <c r="V10" s="1"/>
       <c r="W10" s="26"/>
       <c r="X10" s="27" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="Y10" s="1" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="Z10" s="1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AA10" s="26" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="11" spans="1:27">
@@ -4285,7 +4294,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C11" s="1">
         <v>10</v>
@@ -4341,16 +4350,16 @@
       <c r="V11" s="1"/>
       <c r="W11" s="26"/>
       <c r="X11" s="27" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="Y11" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="Z11" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AA11" s="26" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="12" spans="1:27">
@@ -4358,7 +4367,7 @@
         <v>9</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C12" s="1">
         <v>10</v>
@@ -4414,16 +4423,16 @@
       <c r="V12" s="1"/>
       <c r="W12" s="26"/>
       <c r="X12" s="27" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="Y12" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="Z12" s="1" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AA12" s="26" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="13" spans="1:27">
@@ -4431,7 +4440,7 @@
         <v>10</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C13" s="1">
         <v>10</v>
@@ -4487,16 +4496,16 @@
       <c r="V13" s="1"/>
       <c r="W13" s="26"/>
       <c r="X13" s="27" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="Y13" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="Z13" s="1" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AA13" s="26" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="14" spans="1:27">
@@ -4504,7 +4513,7 @@
         <v>11</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C14" s="1">
         <v>10</v>
@@ -4560,16 +4569,16 @@
       <c r="V14" s="1"/>
       <c r="W14" s="26"/>
       <c r="X14" s="27" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="Y14" s="1" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="Z14" s="1" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AA14" s="26" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="15" spans="1:27">
@@ -4577,7 +4586,7 @@
         <v>12</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C15" s="1">
         <v>10</v>
@@ -4633,16 +4642,16 @@
       <c r="V15" s="1"/>
       <c r="W15" s="26"/>
       <c r="X15" s="27" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="Y15" s="1" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="Z15" s="1" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AA15" s="26" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="16" spans="1:27">
@@ -4650,7 +4659,7 @@
         <v>13</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C16" s="1">
         <v>10</v>
@@ -4706,16 +4715,16 @@
       <c r="V16" s="1"/>
       <c r="W16" s="26"/>
       <c r="X16" s="27" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="Y16" s="1" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="Z16" s="1" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AA16" s="26" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="17" spans="1:27">
@@ -4723,7 +4732,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C17" s="1">
         <v>10</v>
@@ -4779,16 +4788,16 @@
       <c r="V17" s="1"/>
       <c r="W17" s="26"/>
       <c r="X17" s="27" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="Y17" s="1" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="Z17" s="1" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AA17" s="26" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="18" spans="1:27">
@@ -4796,7 +4805,7 @@
         <v>15</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C18" s="1">
         <v>10</v>
@@ -4852,16 +4861,16 @@
       <c r="V18" s="1"/>
       <c r="W18" s="26"/>
       <c r="X18" s="27" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="Y18" s="1" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="Z18" s="1" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AA18" s="26" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="19" spans="1:27">
@@ -4869,7 +4878,7 @@
         <v>16</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C19" s="1">
         <v>10</v>
@@ -4925,16 +4934,16 @@
       <c r="V19" s="1"/>
       <c r="W19" s="26"/>
       <c r="X19" s="27" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="Y19" s="1" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="Z19" s="1" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="AA19" s="26" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="20" spans="1:27">
@@ -4942,7 +4951,7 @@
         <v>17</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C20" s="1">
         <v>10</v>
@@ -4998,16 +5007,16 @@
       <c r="V20" s="1"/>
       <c r="W20" s="26"/>
       <c r="X20" s="27" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="Y20" s="1" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="Z20" s="1" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="AA20" s="26" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="21" spans="1:27">
@@ -5015,7 +5024,7 @@
         <v>18</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C21" s="1">
         <v>10</v>
@@ -5071,16 +5080,16 @@
       <c r="V21" s="1"/>
       <c r="W21" s="26"/>
       <c r="X21" s="27" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="Y21" s="1" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="Z21" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="AA21" s="26" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="22" spans="1:27">
@@ -5088,7 +5097,7 @@
         <v>19</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C22" s="1">
         <v>10</v>
@@ -5144,16 +5153,16 @@
       <c r="V22" s="1"/>
       <c r="W22" s="26"/>
       <c r="X22" s="27" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="Y22" s="1" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="Z22" s="1" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AA22" s="26" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="23" spans="1:27">
@@ -5161,7 +5170,7 @@
         <v>20</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C23" s="1">
         <v>10</v>
@@ -5217,16 +5226,16 @@
       <c r="V23" s="1"/>
       <c r="W23" s="26"/>
       <c r="X23" s="27" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="Y23" s="1" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="Z23" s="1" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AA23" s="26" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="24" spans="1:27">
@@ -5234,7 +5243,7 @@
         <v>21</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C24" s="1">
         <v>10</v>
@@ -5290,16 +5299,16 @@
       <c r="V24" s="1"/>
       <c r="W24" s="26"/>
       <c r="X24" s="27" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="Y24" s="1" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="Z24" s="1" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="AA24" s="26" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="25" spans="1:27">
@@ -5307,7 +5316,7 @@
         <v>22</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C25" s="1">
         <v>10</v>
@@ -5363,16 +5372,16 @@
       <c r="V25" s="1"/>
       <c r="W25" s="26"/>
       <c r="X25" s="27" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="Y25" s="1" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="Z25" s="1" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="AA25" s="26" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="26" spans="1:27">
@@ -5380,7 +5389,7 @@
         <v>23</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C26" s="1">
         <v>10</v>
@@ -5436,16 +5445,16 @@
       <c r="V26" s="1"/>
       <c r="W26" s="26"/>
       <c r="X26" s="27" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="Y26" s="1" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="Z26" s="1" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="AA26" s="26" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="27" spans="1:27">
@@ -5453,7 +5462,7 @@
         <v>24</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C27" s="1">
         <v>10</v>
@@ -5509,16 +5518,16 @@
       <c r="V27" s="1"/>
       <c r="W27" s="26"/>
       <c r="X27" s="27" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="Y27" s="1" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="Z27" s="1" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="AA27" s="26" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="28" spans="1:27">
@@ -5526,7 +5535,7 @@
         <v>25</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C28" s="1">
         <v>10</v>
@@ -5582,16 +5591,16 @@
       <c r="V28" s="1"/>
       <c r="W28" s="26"/>
       <c r="X28" s="27" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="Y28" s="1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="Z28" s="1" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="AA28" s="26" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="29" spans="1:27">
@@ -5599,7 +5608,7 @@
         <v>26</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="C29" s="1">
         <v>10</v>
@@ -5655,16 +5664,16 @@
       <c r="V29" s="1"/>
       <c r="W29" s="26"/>
       <c r="X29" s="27" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="Y29" s="1" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="Z29" s="1" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="AA29" s="26" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="30" spans="1:27">
@@ -5672,7 +5681,7 @@
         <v>27</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="C30" s="1">
         <v>10</v>
@@ -5728,16 +5737,16 @@
       <c r="V30" s="1"/>
       <c r="W30" s="26"/>
       <c r="X30" s="27" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="Y30" s="1" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="Z30" s="1" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="AA30" s="26" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="31" spans="1:27">
@@ -5745,7 +5754,7 @@
         <v>28</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C31" s="1">
         <v>10</v>
@@ -5801,16 +5810,16 @@
       <c r="V31" s="1"/>
       <c r="W31" s="26"/>
       <c r="X31" s="27" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="Y31" s="1" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="Z31" s="1" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="AA31" s="26" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="32" spans="1:27">
@@ -5818,7 +5827,7 @@
         <v>29</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C32" s="1">
         <v>10</v>
@@ -5874,16 +5883,16 @@
       <c r="V32" s="1"/>
       <c r="W32" s="26"/>
       <c r="X32" s="27" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="Y32" s="1" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="Z32" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="AA32" s="26" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="33" spans="1:27">
@@ -5891,7 +5900,7 @@
         <v>30</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="C33" s="1">
         <v>10</v>
@@ -5947,16 +5956,16 @@
       <c r="V33" s="1"/>
       <c r="W33" s="26"/>
       <c r="X33" s="27" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="Y33" s="1" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="Z33" s="1" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="AA33" s="26" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="34" spans="1:27">
@@ -5964,7 +5973,7 @@
         <v>31</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C34" s="1">
         <v>10</v>
@@ -6020,16 +6029,16 @@
       <c r="V34" s="1"/>
       <c r="W34" s="26"/>
       <c r="X34" s="27" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="Y34" s="1" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="Z34" s="1" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="AA34" s="26" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="35" spans="1:27">
@@ -6037,7 +6046,7 @@
         <v>32</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="C35" s="1">
         <v>10</v>
@@ -6093,16 +6102,16 @@
       <c r="V35" s="1"/>
       <c r="W35" s="26"/>
       <c r="X35" s="27" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="Y35" s="1" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="Z35" s="1" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="AA35" s="26" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="36" spans="1:27">
@@ -6110,7 +6119,7 @@
         <v>33</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C36" s="1">
         <v>10</v>
@@ -6166,16 +6175,16 @@
       <c r="V36" s="1"/>
       <c r="W36" s="26"/>
       <c r="X36" s="27" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="Y36" s="1" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="Z36" s="1" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="AA36" s="26" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="37" spans="1:27">
@@ -6183,7 +6192,7 @@
         <v>34</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="C37" s="1">
         <v>10</v>
@@ -6239,16 +6248,16 @@
       <c r="V37" s="1"/>
       <c r="W37" s="26"/>
       <c r="X37" s="27" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="Y37" s="1" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="Z37" s="1" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AA37" s="26" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="38" spans="1:27">
@@ -6256,7 +6265,7 @@
         <v>35</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C38" s="1">
         <v>10</v>
@@ -6312,16 +6321,16 @@
       <c r="V38" s="1"/>
       <c r="W38" s="26"/>
       <c r="X38" s="27" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="Y38" s="1" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="Z38" s="1" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="AA38" s="26" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="39" spans="1:27">
@@ -6329,7 +6338,7 @@
         <v>36</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C39" s="1">
         <v>10</v>
@@ -6385,16 +6394,16 @@
       <c r="V39" s="1"/>
       <c r="W39" s="26"/>
       <c r="X39" s="27" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="Y39" s="1" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="Z39" s="1" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="AA39" s="26" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="40" spans="1:27">
@@ -6402,7 +6411,7 @@
         <v>37</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="C40" s="1">
         <v>10</v>
@@ -6458,16 +6467,16 @@
       <c r="V40" s="1"/>
       <c r="W40" s="26"/>
       <c r="X40" s="27" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="Y40" s="1" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="Z40" s="1" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="AA40" s="26" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="41" ht="14.25" spans="1:27">
@@ -6475,7 +6484,7 @@
         <v>38</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="C41" s="12">
         <v>10</v>
@@ -6531,16 +6540,16 @@
       <c r="V41" s="12"/>
       <c r="W41" s="29"/>
       <c r="X41" s="30" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="Y41" s="12" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="Z41" s="12" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="AA41" s="29" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
   </sheetData>
@@ -6604,7 +6613,7 @@
         <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -6612,7 +6621,7 @@
         <v>2</v>
       </c>
       <c r="B13" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -6620,7 +6629,7 @@
         <v>3</v>
       </c>
       <c r="B14" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -6628,7 +6637,7 @@
         <v>4</v>
       </c>
       <c r="B15" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="F15" t="s">
         <v>142</v>
@@ -6637,7 +6646,7 @@
         <v>142</v>
       </c>
       <c r="I15" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -6645,32 +6654,32 @@
         <v>5</v>
       </c>
       <c r="B16" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="F16" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="H16" t="s">
         <v>160</v>
       </c>
       <c r="I16" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="17" spans="6:9">
       <c r="F17" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="H17" t="s">
         <v>169</v>
       </c>
       <c r="I17" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="18" spans="2:9">
       <c r="B18" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="F18" t="s">
         <v>160</v>
@@ -6679,18 +6688,18 @@
         <v>153</v>
       </c>
       <c r="I18" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="19" spans="6:9">
       <c r="F19" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="H19" t="s">
         <v>178</v>
       </c>
       <c r="I19" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="20" spans="6:8">
@@ -6713,7 +6722,7 @@
     </row>
     <row r="22" spans="6:8">
       <c r="F22" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="H22">
         <f>IF('intent|意图'!F24='intent|意图'!F23,H21&amp;"*"&amp;'intent|意图'!D24,'intent|意图'!D24)</f>
@@ -6740,7 +6749,7 @@
     </row>
     <row r="25" spans="6:8">
       <c r="F25" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="H25">
         <f>IF('intent|意图'!F18='intent|意图'!F17,H24&amp;"*"&amp;'intent|意图'!D18,'intent|意图'!D18)</f>
@@ -6749,7 +6758,7 @@
     </row>
     <row r="26" spans="6:8">
       <c r="F26" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="H26">
         <f>IF('intent|意图'!F19='intent|意图'!F18,H25&amp;"*"&amp;'intent|意图'!D19,'intent|意图'!D19)</f>
@@ -6767,7 +6776,7 @@
     </row>
     <row r="28" spans="6:8">
       <c r="F28" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="H28">
         <f>IF('intent|意图'!F27='intent|意图'!F26,H27&amp;"*"&amp;'intent|意图'!D27,'intent|意图'!D27)</f>
@@ -6785,32 +6794,32 @@
     </row>
     <row r="30" spans="2:2">
       <c r="B30" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="42" spans="2:2">
       <c r="B42" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="50" spans="2:2">
       <c r="B50" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="54" spans="2:2">
       <c r="B54" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="62" spans="2:2">
       <c r="B62" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="66" spans="2:2">
       <c r="B66" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
   </sheetData>
@@ -6838,7 +6847,7 @@
       <c r="C1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="70" t="s">
+      <c r="D1" s="71" t="s">
         <v>14</v>
       </c>
       <c r="E1" s="5" t="s">
@@ -6855,7 +6864,7 @@
       <c r="C2" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="70" t="s">
+      <c r="D2" s="71" t="s">
         <v>19</v>
       </c>
       <c r="E2" s="5" t="s">
@@ -6872,7 +6881,7 @@
       <c r="C3" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="70" t="s">
+      <c r="D3" s="71" t="s">
         <v>21</v>
       </c>
       <c r="E3" s="5" t="s">
@@ -6889,7 +6898,7 @@
       <c r="C4" s="1">
         <v>80</v>
       </c>
-      <c r="D4" s="71">
+      <c r="D4" s="72">
         <v>0</v>
       </c>
       <c r="E4" s="1" t="s">
@@ -6906,10 +6915,10 @@
       <c r="C5" s="1">
         <v>30</v>
       </c>
-      <c r="D5" s="71">
+      <c r="D5" s="72">
         <v>10</v>
       </c>
-      <c r="E5" s="67" t="s">
+      <c r="E5" s="68" t="s">
         <v>25</v>
       </c>
     </row>
@@ -6923,10 +6932,10 @@
       <c r="C6" s="1">
         <v>50</v>
       </c>
-      <c r="D6" s="71">
+      <c r="D6" s="72">
         <v>10</v>
       </c>
-      <c r="E6" s="67" t="s">
+      <c r="E6" s="68" t="s">
         <v>27</v>
       </c>
     </row>
@@ -6940,10 +6949,10 @@
       <c r="C7" s="1">
         <v>50</v>
       </c>
-      <c r="D7" s="71">
+      <c r="D7" s="72">
         <v>10</v>
       </c>
-      <c r="E7" s="67" t="s">
+      <c r="E7" s="68" t="s">
         <v>30</v>
       </c>
     </row>
@@ -6957,10 +6966,10 @@
       <c r="C8" s="1">
         <v>50</v>
       </c>
-      <c r="D8" s="71">
+      <c r="D8" s="72">
         <v>10</v>
       </c>
-      <c r="E8" s="67" t="s">
+      <c r="E8" s="68" t="s">
         <v>33</v>
       </c>
     </row>
@@ -6974,10 +6983,10 @@
       <c r="C9" s="1">
         <v>50</v>
       </c>
-      <c r="D9" s="71">
+      <c r="D9" s="72">
         <v>10</v>
       </c>
-      <c r="E9" s="67" t="s">
+      <c r="E9" s="68" t="s">
         <v>36</v>
       </c>
     </row>
@@ -6993,7 +7002,7 @@
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultColWidth="8.86666666666667" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="8.33333333333333" style="69" customWidth="1"/>
+    <col min="1" max="1" width="8.33333333333333" style="70" customWidth="1"/>
     <col min="2" max="2" width="11.8666666666667" customWidth="1"/>
     <col min="3" max="3" width="31.4666666666667" customWidth="1"/>
   </cols>
@@ -7011,7 +7020,7 @@
       <c r="D1" s="5"/>
       <c r="E1" s="5"/>
     </row>
-    <row r="2" s="68" customFormat="1" spans="1:5">
+    <row r="2" s="69" customFormat="1" spans="1:5">
       <c r="A2" s="43" t="s">
         <v>16</v>
       </c>
@@ -7248,7 +7257,7 @@
       <c r="I1" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="J1" s="66" t="s">
+      <c r="J1" s="67" t="s">
         <v>64</v>
       </c>
     </row>
@@ -7277,10 +7286,10 @@
       <c r="H2" s="43" t="s">
         <v>71</v>
       </c>
-      <c r="I2" s="57" t="s">
+      <c r="I2" s="58" t="s">
         <v>72</v>
       </c>
-      <c r="J2" s="66" t="s">
+      <c r="J2" s="67" t="s">
         <v>73</v>
       </c>
     </row>
@@ -7312,8 +7321,8 @@
       <c r="I3" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="J3" s="66" t="s">
-        <v>9</v>
+      <c r="J3" s="67" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -7344,7 +7353,7 @@
       <c r="I4" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="J4" s="67"/>
+      <c r="J4" s="68"/>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="1" t="s">
@@ -7423,8 +7432,8 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="21.25" customWidth="1"/>
-    <col min="2" max="2" width="9.06666666666667" style="59"/>
-    <col min="4" max="7" width="9.06666666666667" style="59"/>
+    <col min="2" max="2" width="9.06666666666667" style="60"/>
+    <col min="4" max="7" width="9.06666666666667" style="60"/>
     <col min="8" max="8" width="62" customWidth="1"/>
     <col min="9" max="9" width="67.125" customWidth="1"/>
   </cols>
@@ -7433,19 +7442,19 @@
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="60" t="s">
+      <c r="B1" s="61" t="s">
         <v>93</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="60" t="s">
+      <c r="D1" s="61" t="s">
         <v>94</v>
       </c>
-      <c r="E1" s="60" t="s">
+      <c r="E1" s="61" t="s">
         <v>95</v>
       </c>
-      <c r="F1" s="60" t="s">
+      <c r="F1" s="61" t="s">
         <v>96</v>
       </c>
       <c r="G1" s="5" t="s">
@@ -7468,19 +7477,19 @@
       <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="60" t="s">
+      <c r="B2" s="61" t="s">
         <v>99</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="D2" s="60" t="s">
+      <c r="D2" s="61" t="s">
         <v>101</v>
       </c>
-      <c r="E2" s="60" t="s">
+      <c r="E2" s="61" t="s">
         <v>102</v>
       </c>
-      <c r="F2" s="60" t="s">
+      <c r="F2" s="61" t="s">
         <v>103</v>
       </c>
       <c r="G2" s="43" t="s">
@@ -7503,19 +7512,19 @@
       <c r="A3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="60" t="s">
+      <c r="B3" s="61" t="s">
         <v>9</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="60" t="s">
+      <c r="D3" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="60" t="s">
+      <c r="E3" s="61" t="s">
         <v>108</v>
       </c>
-      <c r="F3" s="60" t="s">
+      <c r="F3" s="61" t="s">
         <v>21</v>
       </c>
       <c r="G3" s="5" t="s">
@@ -7538,16 +7547,16 @@
       <c r="A4" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B4" s="61"/>
+      <c r="B4" s="62"/>
       <c r="C4" s="40" t="s">
         <v>110</v>
       </c>
-      <c r="D4" s="61">
-        <v>1</v>
-      </c>
-      <c r="E4" s="61"/>
-      <c r="F4" s="61"/>
-      <c r="G4" s="61"/>
+      <c r="D4" s="62">
+        <v>1</v>
+      </c>
+      <c r="E4" s="62"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="62"/>
       <c r="H4" s="40" t="s">
         <v>111</v>
       </c>
@@ -7563,16 +7572,16 @@
       <c r="A5" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="B5" s="61"/>
+      <c r="B5" s="62"/>
       <c r="C5" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D5" s="61">
+      <c r="D5" s="62">
         <v>2</v>
       </c>
-      <c r="E5" s="61"/>
-      <c r="F5" s="61"/>
-      <c r="G5" s="61"/>
+      <c r="E5" s="62"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="62"/>
       <c r="H5" s="40" t="s">
         <v>115</v>
       </c>
@@ -7588,16 +7597,16 @@
       <c r="A6" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B6" s="61"/>
+      <c r="B6" s="62"/>
       <c r="C6" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="D6" s="61">
+      <c r="D6" s="62">
         <v>3</v>
       </c>
-      <c r="E6" s="61"/>
-      <c r="F6" s="61"/>
-      <c r="G6" s="61"/>
+      <c r="E6" s="62"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="62"/>
       <c r="H6" s="40" t="s">
         <v>118</v>
       </c>
@@ -7613,16 +7622,16 @@
       <c r="A7" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="B7" s="61"/>
+      <c r="B7" s="62"/>
       <c r="C7" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="D7" s="61">
+      <c r="D7" s="62">
         <v>4</v>
       </c>
-      <c r="E7" s="61"/>
-      <c r="F7" s="61"/>
-      <c r="G7" s="61"/>
+      <c r="E7" s="62"/>
+      <c r="F7" s="62"/>
+      <c r="G7" s="62"/>
       <c r="H7" s="1" t="s">
         <v>122</v>
       </c>
@@ -7638,16 +7647,16 @@
       <c r="A8" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="B8" s="61"/>
+      <c r="B8" s="62"/>
       <c r="C8" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="D8" s="61">
+      <c r="D8" s="62">
         <v>5</v>
       </c>
-      <c r="E8" s="61"/>
-      <c r="F8" s="61"/>
-      <c r="G8" s="61"/>
+      <c r="E8" s="62"/>
+      <c r="F8" s="62"/>
+      <c r="G8" s="62"/>
       <c r="H8" s="1" t="s">
         <v>126</v>
       </c>
@@ -7663,16 +7672,16 @@
       <c r="A9" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="B9" s="61"/>
+      <c r="B9" s="62"/>
       <c r="C9" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="D9" s="61">
+      <c r="D9" s="62">
         <v>6</v>
       </c>
-      <c r="E9" s="61"/>
-      <c r="F9" s="61"/>
-      <c r="G9" s="61"/>
+      <c r="E9" s="62"/>
+      <c r="F9" s="62"/>
+      <c r="G9" s="62"/>
       <c r="H9" s="1" t="s">
         <v>130</v>
       </c>
@@ -7688,16 +7697,16 @@
       <c r="A10" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="B10" s="61"/>
+      <c r="B10" s="62"/>
       <c r="C10" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="D10" s="61">
+      <c r="D10" s="62">
         <v>7</v>
       </c>
-      <c r="E10" s="61"/>
-      <c r="F10" s="61"/>
-      <c r="G10" s="61"/>
+      <c r="E10" s="62"/>
+      <c r="F10" s="62"/>
+      <c r="G10" s="62"/>
       <c r="H10" s="1" t="s">
         <v>134</v>
       </c>
@@ -7713,16 +7722,16 @@
       <c r="A11" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B11" s="61"/>
+      <c r="B11" s="62"/>
       <c r="C11" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="D11" s="61">
+      <c r="D11" s="62">
         <v>8</v>
       </c>
-      <c r="E11" s="61"/>
-      <c r="F11" s="61"/>
-      <c r="G11" s="61"/>
+      <c r="E11" s="62"/>
+      <c r="F11" s="62"/>
+      <c r="G11" s="62"/>
       <c r="H11" s="1" t="s">
         <v>138</v>
       </c>
@@ -7738,20 +7747,20 @@
       <c r="A12" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B12" s="61"/>
+      <c r="B12" s="62"/>
       <c r="C12" s="40" t="s">
         <v>110</v>
       </c>
-      <c r="D12" s="61">
-        <v>1</v>
-      </c>
-      <c r="E12" s="61">
+      <c r="D12" s="62">
+        <v>1</v>
+      </c>
+      <c r="E12" s="62">
         <v>2</v>
       </c>
-      <c r="F12" s="61">
-        <v>0</v>
-      </c>
-      <c r="G12" s="61" t="s">
+      <c r="F12" s="62">
+        <v>0</v>
+      </c>
+      <c r="G12" s="62" t="s">
         <v>14</v>
       </c>
       <c r="H12" s="40" t="s">
@@ -7777,14 +7786,14 @@
       <c r="C13" s="47" t="s">
         <v>143</v>
       </c>
-      <c r="D13" s="62"/>
-      <c r="E13" s="62">
+      <c r="D13" s="63"/>
+      <c r="E13" s="63">
         <v>2</v>
       </c>
-      <c r="F13" s="62">
-        <v>0</v>
-      </c>
-      <c r="G13" s="61"/>
+      <c r="F13" s="63">
+        <v>0</v>
+      </c>
+      <c r="G13" s="62"/>
       <c r="H13" s="47" t="s">
         <v>144</v>
       </c>
@@ -7806,14 +7815,14 @@
       <c r="C14" s="49" t="s">
         <v>147</v>
       </c>
-      <c r="D14" s="63"/>
-      <c r="E14" s="63">
+      <c r="D14" s="64"/>
+      <c r="E14" s="64">
         <v>2</v>
       </c>
-      <c r="F14" s="63">
-        <v>1</v>
-      </c>
-      <c r="G14" s="61"/>
+      <c r="F14" s="64">
+        <v>1</v>
+      </c>
+      <c r="G14" s="62"/>
       <c r="H14" s="49" t="s">
         <v>144</v>
       </c>
@@ -7835,14 +7844,14 @@
       <c r="C15" s="49" t="s">
         <v>150</v>
       </c>
-      <c r="D15" s="63"/>
-      <c r="E15" s="63">
-        <v>1</v>
-      </c>
-      <c r="F15" s="63">
+      <c r="D15" s="64"/>
+      <c r="E15" s="64">
+        <v>1</v>
+      </c>
+      <c r="F15" s="64">
         <v>3</v>
       </c>
-      <c r="G15" s="61"/>
+      <c r="G15" s="62"/>
       <c r="H15" s="49" t="s">
         <v>144</v>
       </c>
@@ -7858,20 +7867,20 @@
       <c r="A16" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="B16" s="61"/>
+      <c r="B16" s="62"/>
       <c r="C16" s="40" t="s">
         <v>110</v>
       </c>
-      <c r="D16" s="61">
-        <v>1</v>
-      </c>
-      <c r="E16" s="61">
+      <c r="D16" s="62">
+        <v>1</v>
+      </c>
+      <c r="E16" s="62">
         <v>2</v>
       </c>
-      <c r="F16" s="61">
-        <v>0</v>
-      </c>
-      <c r="G16" s="61" t="s">
+      <c r="F16" s="62">
+        <v>0</v>
+      </c>
+      <c r="G16" s="62" t="s">
         <v>14</v>
       </c>
       <c r="H16" s="40" t="s">
@@ -7897,14 +7906,14 @@
       <c r="C17" s="51" t="s">
         <v>154</v>
       </c>
-      <c r="D17" s="64"/>
-      <c r="E17" s="64">
+      <c r="D17" s="65"/>
+      <c r="E17" s="65">
         <v>2</v>
       </c>
-      <c r="F17" s="64">
-        <v>0</v>
-      </c>
-      <c r="G17" s="61"/>
+      <c r="F17" s="65">
+        <v>0</v>
+      </c>
+      <c r="G17" s="62"/>
       <c r="H17" s="51" t="s">
         <v>144</v>
       </c>
@@ -7926,14 +7935,14 @@
       <c r="C18" s="51" t="s">
         <v>157</v>
       </c>
-      <c r="D18" s="64"/>
-      <c r="E18" s="64">
+      <c r="D18" s="65"/>
+      <c r="E18" s="65">
         <v>2</v>
       </c>
-      <c r="F18" s="64">
-        <v>1</v>
-      </c>
-      <c r="G18" s="61"/>
+      <c r="F18" s="65">
+        <v>1</v>
+      </c>
+      <c r="G18" s="62"/>
       <c r="H18" s="51" t="s">
         <v>144</v>
       </c>
@@ -7955,14 +7964,14 @@
       <c r="C19" s="51" t="s">
         <v>159</v>
       </c>
-      <c r="D19" s="64"/>
-      <c r="E19" s="64">
-        <v>1</v>
-      </c>
-      <c r="F19" s="64">
+      <c r="D19" s="65"/>
+      <c r="E19" s="65">
+        <v>1</v>
+      </c>
+      <c r="F19" s="65">
         <v>3</v>
       </c>
-      <c r="G19" s="61"/>
+      <c r="G19" s="62"/>
       <c r="H19" s="51" t="s">
         <v>144</v>
       </c>
@@ -7974,7 +7983,7 @@
       </c>
       <c r="K19" s="51"/>
     </row>
-    <row r="20" s="58" customFormat="1" spans="1:11">
+    <row r="20" s="59" customFormat="1" spans="1:11">
       <c r="A20" s="52" t="s">
         <v>160</v>
       </c>
@@ -7984,14 +7993,14 @@
       <c r="C20" s="53" t="s">
         <v>161</v>
       </c>
-      <c r="D20" s="65"/>
-      <c r="E20" s="65">
-        <v>1</v>
-      </c>
-      <c r="F20" s="65">
-        <v>0</v>
-      </c>
-      <c r="G20" s="65"/>
+      <c r="D20" s="66"/>
+      <c r="E20" s="66">
+        <v>1</v>
+      </c>
+      <c r="F20" s="66">
+        <v>0</v>
+      </c>
+      <c r="G20" s="66"/>
       <c r="H20" s="53" t="s">
         <v>162</v>
       </c>
@@ -8003,7 +8012,7 @@
       </c>
       <c r="K20" s="53"/>
     </row>
-    <row r="21" s="58" customFormat="1" spans="1:11">
+    <row r="21" s="59" customFormat="1" spans="1:11">
       <c r="A21" s="52" t="s">
         <v>163</v>
       </c>
@@ -8013,14 +8022,14 @@
       <c r="C21" s="53" t="s">
         <v>164</v>
       </c>
-      <c r="D21" s="65"/>
-      <c r="E21" s="65">
-        <v>1</v>
-      </c>
-      <c r="F21" s="65">
-        <v>1</v>
-      </c>
-      <c r="G21" s="65"/>
+      <c r="D21" s="66"/>
+      <c r="E21" s="66">
+        <v>1</v>
+      </c>
+      <c r="F21" s="66">
+        <v>1</v>
+      </c>
+      <c r="G21" s="66"/>
       <c r="H21" s="53" t="s">
         <v>165</v>
       </c>
@@ -8032,7 +8041,7 @@
       </c>
       <c r="K21" s="53"/>
     </row>
-    <row r="22" s="58" customFormat="1" spans="1:11">
+    <row r="22" s="59" customFormat="1" spans="1:11">
       <c r="A22" s="52" t="s">
         <v>166</v>
       </c>
@@ -8042,14 +8051,14 @@
       <c r="C22" s="53" t="s">
         <v>167</v>
       </c>
-      <c r="D22" s="65"/>
-      <c r="E22" s="65">
-        <v>1</v>
-      </c>
-      <c r="F22" s="65">
+      <c r="D22" s="66"/>
+      <c r="E22" s="66">
+        <v>1</v>
+      </c>
+      <c r="F22" s="66">
         <v>3</v>
       </c>
-      <c r="G22" s="65"/>
+      <c r="G22" s="66"/>
       <c r="H22" s="53" t="s">
         <v>168</v>
       </c>
@@ -8071,14 +8080,14 @@
       <c r="C23" s="49" t="s">
         <v>170</v>
       </c>
-      <c r="D23" s="63"/>
-      <c r="E23" s="63">
-        <v>1</v>
-      </c>
-      <c r="F23" s="63">
-        <v>0</v>
-      </c>
-      <c r="G23" s="63"/>
+      <c r="D23" s="64"/>
+      <c r="E23" s="64">
+        <v>1</v>
+      </c>
+      <c r="F23" s="64">
+        <v>0</v>
+      </c>
+      <c r="G23" s="64"/>
       <c r="H23" s="49" t="s">
         <v>171</v>
       </c>
@@ -8100,14 +8109,14 @@
       <c r="C24" s="49" t="s">
         <v>173</v>
       </c>
-      <c r="D24" s="63"/>
-      <c r="E24" s="63">
-        <v>1</v>
-      </c>
-      <c r="F24" s="63">
-        <v>1</v>
-      </c>
-      <c r="G24" s="63"/>
+      <c r="D24" s="64"/>
+      <c r="E24" s="64">
+        <v>1</v>
+      </c>
+      <c r="F24" s="64">
+        <v>1</v>
+      </c>
+      <c r="G24" s="64"/>
       <c r="H24" s="49" t="s">
         <v>174</v>
       </c>
@@ -8129,14 +8138,14 @@
       <c r="C25" s="49" t="s">
         <v>176</v>
       </c>
-      <c r="D25" s="63"/>
-      <c r="E25" s="63">
-        <v>1</v>
-      </c>
-      <c r="F25" s="63">
+      <c r="D25" s="64"/>
+      <c r="E25" s="64">
+        <v>1</v>
+      </c>
+      <c r="F25" s="64">
         <v>3</v>
       </c>
-      <c r="G25" s="63"/>
+      <c r="G25" s="64"/>
       <c r="H25" s="49" t="s">
         <v>177</v>
       </c>
@@ -8158,14 +8167,14 @@
       <c r="C26" s="49" t="s">
         <v>179</v>
       </c>
-      <c r="D26" s="63"/>
-      <c r="E26" s="63">
-        <v>1</v>
-      </c>
-      <c r="F26" s="63">
-        <v>0</v>
-      </c>
-      <c r="G26" s="63"/>
+      <c r="D26" s="64"/>
+      <c r="E26" s="64">
+        <v>1</v>
+      </c>
+      <c r="F26" s="64">
+        <v>0</v>
+      </c>
+      <c r="G26" s="64"/>
       <c r="H26" s="49" t="s">
         <v>180</v>
       </c>
@@ -8187,14 +8196,14 @@
       <c r="C27" s="49" t="s">
         <v>182</v>
       </c>
-      <c r="D27" s="63"/>
-      <c r="E27" s="63">
-        <v>1</v>
-      </c>
-      <c r="F27" s="63">
-        <v>1</v>
-      </c>
-      <c r="G27" s="63"/>
+      <c r="D27" s="64"/>
+      <c r="E27" s="64">
+        <v>1</v>
+      </c>
+      <c r="F27" s="64">
+        <v>1</v>
+      </c>
+      <c r="G27" s="64"/>
       <c r="H27" s="53" t="s">
         <v>168</v>
       </c>
@@ -8216,14 +8225,14 @@
       <c r="C28" s="47" t="s">
         <v>184</v>
       </c>
-      <c r="D28" s="62"/>
-      <c r="E28" s="62">
-        <v>1</v>
-      </c>
-      <c r="F28" s="62">
+      <c r="D28" s="63"/>
+      <c r="E28" s="63">
+        <v>1</v>
+      </c>
+      <c r="F28" s="63">
         <v>3</v>
       </c>
-      <c r="G28" s="62"/>
+      <c r="G28" s="63"/>
       <c r="H28" s="47" t="s">
         <v>185</v>
       </c>
@@ -8244,7 +8253,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="11.5" customWidth="1"/>
@@ -8312,7 +8321,7 @@
       <c r="H2" s="55" t="s">
         <v>195</v>
       </c>
-      <c r="I2" s="57" t="s">
+      <c r="I2" s="58" t="s">
         <v>72</v>
       </c>
     </row>
@@ -8345,120 +8354,118 @@
         <v>43</v>
       </c>
     </row>
-    <row r="4" s="54" customFormat="1" spans="1:9">
-      <c r="A4" s="56" t="s">
+    <row r="4" customFormat="1" spans="1:9">
+      <c r="A4" s="40" t="s">
+        <v>86</v>
+      </c>
+      <c r="B4" s="40" t="s">
         <v>197</v>
       </c>
-      <c r="B4" s="56" t="s">
+      <c r="C4" s="40" t="s">
         <v>198</v>
       </c>
-      <c r="C4" s="56" t="s">
+      <c r="D4" s="40"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="40"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="40"/>
+    </row>
+    <row r="5" s="54" customFormat="1" spans="1:9">
+      <c r="A5" s="57" t="s">
         <v>199</v>
       </c>
-      <c r="D4" s="56">
-        <v>1</v>
-      </c>
-      <c r="E4" s="56"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="40"/>
-      <c r="I4" s="56"/>
-    </row>
-    <row r="5" s="54" customFormat="1" spans="1:9">
-      <c r="A5" s="56" t="s">
+      <c r="B5" s="57" t="s">
         <v>200</v>
       </c>
-      <c r="B5" s="56" t="s">
+      <c r="C5" s="57" t="s">
         <v>201</v>
       </c>
-      <c r="C5" s="56" t="s">
+      <c r="D5" s="57">
+        <v>1</v>
+      </c>
+      <c r="E5" s="57"/>
+      <c r="F5" s="57"/>
+      <c r="G5" s="57"/>
+      <c r="H5" s="40"/>
+      <c r="I5" s="57"/>
+    </row>
+    <row r="6" s="54" customFormat="1" spans="1:9">
+      <c r="A6" s="57" t="s">
         <v>202</v>
       </c>
-      <c r="D5" s="56">
-        <v>1</v>
-      </c>
-      <c r="E5" s="56"/>
-      <c r="F5" s="56"/>
-      <c r="G5" s="56"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="56"/>
-    </row>
-    <row r="6" s="54" customFormat="1" spans="1:9">
-      <c r="A6" s="56" t="s">
+      <c r="B6" s="57" t="s">
         <v>203</v>
       </c>
-      <c r="B6" s="56" t="s">
+      <c r="C6" s="57" t="s">
         <v>204</v>
       </c>
-      <c r="C6" s="56" t="s">
+      <c r="D6" s="57">
+        <v>1</v>
+      </c>
+      <c r="E6" s="57"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="57"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="57"/>
+    </row>
+    <row r="7" s="54" customFormat="1" spans="1:9">
+      <c r="A7" s="57" t="s">
         <v>205</v>
       </c>
-      <c r="D6" s="56">
-        <v>1</v>
-      </c>
-      <c r="E6" s="56"/>
-      <c r="F6" s="56"/>
-      <c r="G6" s="56"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="56"/>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="57" t="s">
         <v>206</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="57" t="s">
         <v>207</v>
       </c>
-      <c r="D7" s="1">
-        <v>1</v>
-      </c>
-      <c r="E7" s="1">
-        <v>2</v>
-      </c>
-      <c r="F7" s="1">
-        <v>2</v>
-      </c>
-      <c r="G7" s="1">
-        <v>5</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>209</v>
-      </c>
+      <c r="D7" s="57">
+        <v>1</v>
+      </c>
+      <c r="E7" s="57"/>
+      <c r="F7" s="57"/>
+      <c r="G7" s="57"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="57"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
+      <c r="E8" s="1">
+        <v>2</v>
+      </c>
+      <c r="F8" s="1">
+        <v>2</v>
+      </c>
+      <c r="G8" s="1">
+        <v>5</v>
+      </c>
+      <c r="H8" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="I8" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="D8" s="1">
-        <v>0</v>
-      </c>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>214</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>215</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -8471,13 +8478,13 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="C10" s="1" t="s">
         <v>217</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>218</v>
       </c>
       <c r="D10" s="1">
         <v>0</v>
@@ -8490,10 +8497,10 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>219</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>150</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>220</v>
@@ -8504,8 +8511,27 @@
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
-      <c r="H11" s="47"/>
+      <c r="H11" s="1"/>
       <c r="I11" s="1"/>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="D12" s="1">
+        <v>0</v>
+      </c>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="47"/>
+      <c r="I12" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8532,22 +8558,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>61</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H1" s="5" t="s">
         <v>15</v>
@@ -8558,25 +8584,25 @@
         <v>16</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D2" s="44" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E2" s="43" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F2" s="43" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="G2" s="43" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -8635,7 +8661,7 @@
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="40" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D5" s="1">
         <v>1</v>
@@ -8650,12 +8676,12 @@
         <v>5</v>
       </c>
       <c r="H5" s="40" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="6" s="41" customFormat="1" spans="1:8">
       <c r="A6" s="45" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B6" s="45"/>
       <c r="C6" s="45" t="s">
@@ -8674,16 +8700,16 @@
         <v>8</v>
       </c>
       <c r="H6" s="45" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="7" s="41" customFormat="1" spans="1:8">
       <c r="A7" s="45" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B7" s="45"/>
       <c r="C7" s="45" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D7" s="45">
         <v>0</v>
@@ -8695,21 +8721,21 @@
         <v>3</v>
       </c>
       <c r="G7" s="45" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="H7" s="45" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="1" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D8" s="1">
         <v>0</v>
@@ -8724,15 +8750,15 @@
         <v>1</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>125</v>
@@ -8748,18 +8774,18 @@
         <v>2</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D10" s="1">
         <v>0</v>
@@ -8772,18 +8798,18 @@
         <v>3</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D11" s="1">
         <v>0</v>
@@ -8796,15 +8822,15 @@
         <v>4</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>121</v>
@@ -8820,18 +8846,18 @@
         <v>5</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D13" s="1">
         <v>0</v>
@@ -8844,18 +8870,18 @@
         <v>6</v>
       </c>
       <c r="H13" s="40" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D14" s="1">
         <v>0</v>
@@ -8868,18 +8894,18 @@
         <v>7</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -8892,18 +8918,18 @@
         <v>8</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D16" s="1">
         <v>0</v>
@@ -8916,7 +8942,7 @@
         <v>9</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -8924,10 +8950,10 @@
         <v>142</v>
       </c>
       <c r="B17" s="47" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C17" s="47" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D17" s="1">
         <v>0</v>
@@ -8936,7 +8962,7 @@
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
       <c r="H17" s="47" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -8956,10 +8982,10 @@
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
       <c r="H18" s="49" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="I18" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -8979,10 +9005,10 @@
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
       <c r="H19" s="49" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="I19" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="20" s="42" customFormat="1" spans="1:9">
@@ -9002,10 +9028,10 @@
       <c r="F20" s="51"/>
       <c r="G20" s="51"/>
       <c r="H20" s="51" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="I20" s="42" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="21" s="42" customFormat="1" spans="1:9">
@@ -9025,10 +9051,10 @@
       <c r="F21" s="51"/>
       <c r="G21" s="51"/>
       <c r="H21" s="51" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="I21" s="42" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="22" s="42" customFormat="1" spans="1:9">
@@ -9048,10 +9074,10 @@
       <c r="F22" s="51"/>
       <c r="G22" s="51"/>
       <c r="H22" s="51" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="I22" s="42" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -9071,10 +9097,10 @@
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
       <c r="H23" s="53" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="I23" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -9094,10 +9120,10 @@
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
       <c r="H24" s="1" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="I24" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -9120,7 +9146,7 @@
         <v>168</v>
       </c>
       <c r="I25" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -9140,10 +9166,10 @@
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
       <c r="H26" s="49" t="s">
+        <v>286</v>
+      </c>
+      <c r="I26" t="s">
         <v>284</v>
-      </c>
-      <c r="I26" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -9163,10 +9189,10 @@
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
       <c r="H27" s="49" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="I27" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -9206,10 +9232,10 @@
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
       <c r="H29" s="49" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="I29" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -9232,7 +9258,7 @@
         <v>168</v>
       </c>
       <c r="I30" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -9274,7 +9300,7 @@
         <v>5</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -9296,7 +9322,7 @@
         <v>8</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
   </sheetData>
@@ -9321,22 +9347,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="35" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C1" s="35" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D1" s="35" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="E1" s="35" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="F1" s="35" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="G1" s="35" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -9344,22 +9370,22 @@
         <v>16</v>
       </c>
       <c r="B2" s="37" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C2" s="37" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D2" s="37" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="E2" s="37" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F2" s="37" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="G2" s="38" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -9387,10 +9413,10 @@
     </row>
     <row r="4" ht="14.25" spans="1:7">
       <c r="A4" s="39" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B4" s="40" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C4" s="39">
         <v>100</v>
@@ -9405,15 +9431,15 @@
         <v>1</v>
       </c>
       <c r="G4" s="39" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="5" ht="14.25" spans="1:7">
       <c r="A5" s="39" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B5" s="40" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C5" s="39">
         <v>100</v>
@@ -9428,15 +9454,15 @@
         <v>1</v>
       </c>
       <c r="G5" s="39" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="6" ht="14.25" spans="1:7">
       <c r="A6" s="39" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B6" s="40" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C6" s="39">
         <v>3</v>
@@ -9451,15 +9477,15 @@
         <v>1</v>
       </c>
       <c r="G6" s="39" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="7" ht="14.25" spans="1:7">
       <c r="A7" s="39" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B7" s="40" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C7" s="39">
         <v>3</v>
@@ -9474,12 +9500,12 @@
         <v>1</v>
       </c>
       <c r="G7" s="39" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="8" ht="14.25" spans="1:7">
       <c r="A8" s="39" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B8" s="40" t="s">
         <v>19</v>
@@ -9497,15 +9523,15 @@
         <v>1</v>
       </c>
       <c r="G8" s="39" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="9" ht="14.25" spans="1:7">
       <c r="A9" s="39" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B9" s="40" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C9" s="39">
         <v>0</v>
@@ -9520,15 +9546,15 @@
         <v>1</v>
       </c>
       <c r="G9" s="39" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="10" ht="14.25" spans="1:7">
       <c r="A10" s="39" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B10" s="40" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C10" s="39">
         <v>0</v>
@@ -9543,15 +9569,15 @@
         <v>1</v>
       </c>
       <c r="G10" s="39" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="11" ht="14.25" spans="1:7">
       <c r="A11" s="39" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B11" s="40" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C11" s="39">
         <v>0</v>
@@ -9566,15 +9592,15 @@
         <v>1</v>
       </c>
       <c r="G11" s="39" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="12" ht="14.25" spans="1:7">
       <c r="A12" s="39" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B12" s="40" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C12" s="39">
         <v>0</v>
@@ -9589,15 +9615,15 @@
         <v>1</v>
       </c>
       <c r="G12" s="39" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="13" ht="14.25" spans="1:7">
       <c r="A13" s="39" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B13" s="40" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C13" s="39">
         <v>0</v>
@@ -9612,15 +9638,15 @@
         <v>1</v>
       </c>
       <c r="G13" s="39" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="14" ht="14.25" spans="1:7">
       <c r="A14" s="39" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B14" s="40" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C14" s="39">
         <v>0</v>
@@ -9635,7 +9661,7 @@
         <v>1</v>
       </c>
       <c r="G14" s="39" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
   </sheetData>

--- a/xlsdir/配置-总表.xlsx
+++ b/xlsdir/配置-总表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="673" activeTab="6"/>
+    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="673" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="combat|战斗" sheetId="31" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="861" uniqueCount="559">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="861" uniqueCount="558">
   <si>
     <t>ID</t>
   </si>
@@ -282,9 +282,6 @@
   </si>
   <si>
     <t>res://asserts/textures/cards/card_icons/card_strike.png</t>
-  </si>
-  <si>
-    <t>attack_01</t>
   </si>
   <si>
     <t>defense</t>
@@ -2885,7 +2882,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3087,12 +3084,6 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -3100,9 +3091,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1" quotePrefix="1">
@@ -3545,67 +3533,67 @@
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="P1" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="Q1" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="R1" s="13" t="s">
         <v>346</v>
       </c>
-      <c r="R1" s="13" t="s">
+      <c r="S1" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="T1" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="U1" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="V1" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="W1" s="14" t="s">
         <v>351</v>
-      </c>
-      <c r="W1" s="14" t="s">
-        <v>352</v>
       </c>
       <c r="X1" s="15"/>
       <c r="Y1" s="15"/>
@@ -3617,82 +3605,82 @@
         <v>16</v>
       </c>
       <c r="B2" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="D2" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="C2" s="5" t="s">
-        <v>303</v>
-      </c>
-      <c r="D2" s="5" t="s">
+      <c r="E2" s="5" t="s">
         <v>354</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="F2" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="G2" s="5" t="s">
         <v>355</v>
       </c>
-      <c r="F2" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="G2" s="5" t="s">
+      <c r="H2" s="5" t="s">
         <v>356</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="I2" s="5" t="s">
         <v>357</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="J2" s="5" t="s">
         <v>358</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="K2" s="5" t="s">
         <v>359</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="L2" s="5" t="s">
         <v>360</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="M2" s="5" t="s">
         <v>361</v>
       </c>
-      <c r="M2" s="5" t="s">
+      <c r="N2" s="5" t="s">
         <v>362</v>
       </c>
-      <c r="N2" s="5" t="s">
+      <c r="O2" s="5" t="s">
         <v>363</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="P2" s="5" t="s">
         <v>364</v>
       </c>
-      <c r="P2" s="5" t="s">
+      <c r="Q2" s="5" t="s">
         <v>365</v>
       </c>
-      <c r="Q2" s="5" t="s">
+      <c r="R2" s="16" t="s">
         <v>366</v>
       </c>
-      <c r="R2" s="16" t="s">
+      <c r="S2" s="5" t="s">
         <v>367</v>
       </c>
-      <c r="S2" s="5" t="s">
+      <c r="T2" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="U2" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="V2" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="T2" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="U2" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="V2" s="5" t="s">
+      <c r="W2" s="17" t="s">
+        <v>365</v>
+      </c>
+      <c r="X2" s="18" t="s">
         <v>369</v>
       </c>
-      <c r="W2" s="17" t="s">
-        <v>366</v>
-      </c>
-      <c r="X2" s="18" t="s">
+      <c r="Y2" s="32" t="s">
         <v>370</v>
       </c>
-      <c r="Y2" s="32" t="s">
+      <c r="Z2" s="32" t="s">
         <v>371</v>
       </c>
-      <c r="Z2" s="32" t="s">
+      <c r="AA2" s="33" t="s">
         <v>372</v>
-      </c>
-      <c r="AA2" s="33" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="3" ht="14.25" spans="1:27">
@@ -3783,7 +3771,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C4" s="9">
         <v>10</v>
@@ -3838,17 +3826,17 @@
       <c r="U4" s="9"/>
       <c r="V4" s="9"/>
       <c r="W4" s="23"/>
-      <c r="X4" s="73" t="s">
+      <c r="X4" s="70" t="s">
+        <v>374</v>
+      </c>
+      <c r="Y4" s="9" t="s">
         <v>375</v>
       </c>
-      <c r="Y4" s="9" t="s">
+      <c r="Z4" s="9" t="s">
         <v>376</v>
       </c>
-      <c r="Z4" s="9" t="s">
+      <c r="AA4" s="23" t="s">
         <v>377</v>
-      </c>
-      <c r="AA4" s="23" t="s">
-        <v>378</v>
       </c>
     </row>
     <row r="5" spans="1:27">
@@ -3856,7 +3844,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C5" s="1">
         <v>10</v>
@@ -3912,16 +3900,16 @@
       <c r="V5" s="1"/>
       <c r="W5" s="26"/>
       <c r="X5" s="27" t="s">
+        <v>379</v>
+      </c>
+      <c r="Y5" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="Z5" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="Y5" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="Z5" s="1" t="s">
-        <v>381</v>
-      </c>
       <c r="AA5" s="26" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="6" spans="1:27">
@@ -3929,7 +3917,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C6" s="1">
         <v>10</v>
@@ -3985,16 +3973,16 @@
       <c r="V6" s="1"/>
       <c r="W6" s="26"/>
       <c r="X6" s="27" t="s">
+        <v>382</v>
+      </c>
+      <c r="Y6" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="Z6" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="Y6" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="Z6" s="1" t="s">
+      <c r="AA6" s="26" t="s">
         <v>384</v>
-      </c>
-      <c r="AA6" s="26" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="7" spans="1:27">
@@ -4002,7 +3990,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C7" s="1">
         <v>10</v>
@@ -4058,16 +4046,16 @@
       <c r="V7" s="1"/>
       <c r="W7" s="26"/>
       <c r="X7" s="27" t="s">
+        <v>386</v>
+      </c>
+      <c r="Y7" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="Z7" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="Y7" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="Z7" s="1" t="s">
+      <c r="AA7" s="26" t="s">
         <v>388</v>
-      </c>
-      <c r="AA7" s="26" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="8" spans="1:27">
@@ -4075,7 +4063,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C8" s="1">
         <v>10</v>
@@ -4131,16 +4119,16 @@
       <c r="V8" s="1"/>
       <c r="W8" s="26"/>
       <c r="X8" s="27" t="s">
+        <v>390</v>
+      </c>
+      <c r="Y8" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="Z8" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="Y8" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="Z8" s="1" t="s">
+      <c r="AA8" s="26" t="s">
         <v>392</v>
-      </c>
-      <c r="AA8" s="26" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="9" spans="1:27">
@@ -4148,7 +4136,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C9" s="1">
         <v>10</v>
@@ -4204,16 +4192,16 @@
       <c r="V9" s="1"/>
       <c r="W9" s="26"/>
       <c r="X9" s="27" t="s">
+        <v>394</v>
+      </c>
+      <c r="Y9" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="Y9" s="1" t="s">
+      <c r="Z9" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="Z9" s="1" t="s">
+      <c r="AA9" s="26" t="s">
         <v>397</v>
-      </c>
-      <c r="AA9" s="26" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="10" spans="1:27">
@@ -4221,7 +4209,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C10" s="1">
         <v>10</v>
@@ -4277,16 +4265,16 @@
       <c r="V10" s="1"/>
       <c r="W10" s="26"/>
       <c r="X10" s="27" t="s">
+        <v>399</v>
+      </c>
+      <c r="Y10" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="Y10" s="1" t="s">
+      <c r="Z10" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="Z10" s="1" t="s">
+      <c r="AA10" s="26" t="s">
         <v>402</v>
-      </c>
-      <c r="AA10" s="26" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="11" spans="1:27">
@@ -4294,7 +4282,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C11" s="1">
         <v>10</v>
@@ -4350,16 +4338,16 @@
       <c r="V11" s="1"/>
       <c r="W11" s="26"/>
       <c r="X11" s="27" t="s">
+        <v>403</v>
+      </c>
+      <c r="Y11" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="Y11" s="1" t="s">
+      <c r="Z11" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="Z11" s="1" t="s">
+      <c r="AA11" s="26" t="s">
         <v>406</v>
-      </c>
-      <c r="AA11" s="26" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="12" spans="1:27">
@@ -4367,7 +4355,7 @@
         <v>9</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C12" s="1">
         <v>10</v>
@@ -4423,16 +4411,16 @@
       <c r="V12" s="1"/>
       <c r="W12" s="26"/>
       <c r="X12" s="27" t="s">
+        <v>408</v>
+      </c>
+      <c r="Y12" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="Y12" s="1" t="s">
+      <c r="Z12" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="Z12" s="1" t="s">
+      <c r="AA12" s="26" t="s">
         <v>411</v>
-      </c>
-      <c r="AA12" s="26" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="13" spans="1:27">
@@ -4440,7 +4428,7 @@
         <v>10</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C13" s="1">
         <v>10</v>
@@ -4496,16 +4484,16 @@
       <c r="V13" s="1"/>
       <c r="W13" s="26"/>
       <c r="X13" s="27" t="s">
+        <v>413</v>
+      </c>
+      <c r="Y13" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="Z13" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="Y13" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="Z13" s="1" t="s">
+      <c r="AA13" s="26" t="s">
         <v>415</v>
-      </c>
-      <c r="AA13" s="26" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="14" spans="1:27">
@@ -4513,7 +4501,7 @@
         <v>11</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C14" s="1">
         <v>10</v>
@@ -4569,16 +4557,16 @@
       <c r="V14" s="1"/>
       <c r="W14" s="26"/>
       <c r="X14" s="27" t="s">
+        <v>417</v>
+      </c>
+      <c r="Y14" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="Y14" s="1" t="s">
+      <c r="Z14" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="Z14" s="1" t="s">
+      <c r="AA14" s="26" t="s">
         <v>420</v>
-      </c>
-      <c r="AA14" s="26" t="s">
-        <v>421</v>
       </c>
     </row>
     <row r="15" spans="1:27">
@@ -4586,7 +4574,7 @@
         <v>12</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C15" s="1">
         <v>10</v>
@@ -4642,16 +4630,16 @@
       <c r="V15" s="1"/>
       <c r="W15" s="26"/>
       <c r="X15" s="27" t="s">
+        <v>422</v>
+      </c>
+      <c r="Y15" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="Y15" s="1" t="s">
+      <c r="Z15" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="Z15" s="1" t="s">
-        <v>425</v>
-      </c>
       <c r="AA15" s="26" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="16" spans="1:27">
@@ -4659,7 +4647,7 @@
         <v>13</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C16" s="1">
         <v>10</v>
@@ -4715,16 +4703,16 @@
       <c r="V16" s="1"/>
       <c r="W16" s="26"/>
       <c r="X16" s="27" t="s">
+        <v>426</v>
+      </c>
+      <c r="Y16" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="Y16" s="1" t="s">
+      <c r="Z16" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="Z16" s="1" t="s">
-        <v>429</v>
-      </c>
       <c r="AA16" s="26" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="17" spans="1:27">
@@ -4732,7 +4720,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C17" s="1">
         <v>10</v>
@@ -4788,16 +4776,16 @@
       <c r="V17" s="1"/>
       <c r="W17" s="26"/>
       <c r="X17" s="27" t="s">
+        <v>430</v>
+      </c>
+      <c r="Y17" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="Y17" s="1" t="s">
+      <c r="Z17" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="Z17" s="1" t="s">
+      <c r="AA17" s="26" t="s">
         <v>433</v>
-      </c>
-      <c r="AA17" s="26" t="s">
-        <v>434</v>
       </c>
     </row>
     <row r="18" spans="1:27">
@@ -4805,7 +4793,7 @@
         <v>15</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C18" s="1">
         <v>10</v>
@@ -4861,16 +4849,16 @@
       <c r="V18" s="1"/>
       <c r="W18" s="26"/>
       <c r="X18" s="27" t="s">
+        <v>435</v>
+      </c>
+      <c r="Y18" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="Y18" s="1" t="s">
+      <c r="Z18" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="Z18" s="1" t="s">
-        <v>438</v>
-      </c>
       <c r="AA18" s="26" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="19" spans="1:27">
@@ -4878,7 +4866,7 @@
         <v>16</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C19" s="1">
         <v>10</v>
@@ -4934,16 +4922,16 @@
       <c r="V19" s="1"/>
       <c r="W19" s="26"/>
       <c r="X19" s="27" t="s">
+        <v>439</v>
+      </c>
+      <c r="Y19" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="Y19" s="1" t="s">
+      <c r="Z19" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="Z19" s="1" t="s">
-        <v>442</v>
-      </c>
       <c r="AA19" s="26" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="20" spans="1:27">
@@ -4951,7 +4939,7 @@
         <v>17</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C20" s="1">
         <v>10</v>
@@ -5007,16 +4995,16 @@
       <c r="V20" s="1"/>
       <c r="W20" s="26"/>
       <c r="X20" s="27" t="s">
+        <v>443</v>
+      </c>
+      <c r="Y20" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="Y20" s="1" t="s">
+      <c r="Z20" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="Z20" s="1" t="s">
-        <v>446</v>
-      </c>
       <c r="AA20" s="26" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="21" spans="1:27">
@@ -5024,7 +5012,7 @@
         <v>18</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C21" s="1">
         <v>10</v>
@@ -5080,16 +5068,16 @@
       <c r="V21" s="1"/>
       <c r="W21" s="26"/>
       <c r="X21" s="27" t="s">
+        <v>447</v>
+      </c>
+      <c r="Y21" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="Y21" s="1" t="s">
+      <c r="Z21" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="Z21" s="1" t="s">
-        <v>450</v>
-      </c>
       <c r="AA21" s="26" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="22" spans="1:27">
@@ -5097,7 +5085,7 @@
         <v>19</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C22" s="1">
         <v>10</v>
@@ -5153,16 +5141,16 @@
       <c r="V22" s="1"/>
       <c r="W22" s="26"/>
       <c r="X22" s="27" t="s">
+        <v>451</v>
+      </c>
+      <c r="Y22" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="Y22" s="1" t="s">
+      <c r="Z22" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="Z22" s="1" t="s">
+      <c r="AA22" s="26" t="s">
         <v>454</v>
-      </c>
-      <c r="AA22" s="26" t="s">
-        <v>455</v>
       </c>
     </row>
     <row r="23" spans="1:27">
@@ -5170,7 +5158,7 @@
         <v>20</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C23" s="1">
         <v>10</v>
@@ -5226,16 +5214,16 @@
       <c r="V23" s="1"/>
       <c r="W23" s="26"/>
       <c r="X23" s="27" t="s">
+        <v>456</v>
+      </c>
+      <c r="Y23" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="Y23" s="1" t="s">
+      <c r="Z23" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="Z23" s="1" t="s">
+      <c r="AA23" s="26" t="s">
         <v>459</v>
-      </c>
-      <c r="AA23" s="26" t="s">
-        <v>460</v>
       </c>
     </row>
     <row r="24" spans="1:27">
@@ -5243,7 +5231,7 @@
         <v>21</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C24" s="1">
         <v>10</v>
@@ -5299,16 +5287,16 @@
       <c r="V24" s="1"/>
       <c r="W24" s="26"/>
       <c r="X24" s="27" t="s">
+        <v>461</v>
+      </c>
+      <c r="Y24" s="1" t="s">
         <v>462</v>
       </c>
-      <c r="Y24" s="1" t="s">
+      <c r="Z24" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="Z24" s="1" t="s">
+      <c r="AA24" s="26" t="s">
         <v>464</v>
-      </c>
-      <c r="AA24" s="26" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="25" spans="1:27">
@@ -5316,7 +5304,7 @@
         <v>22</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C25" s="1">
         <v>10</v>
@@ -5372,16 +5360,16 @@
       <c r="V25" s="1"/>
       <c r="W25" s="26"/>
       <c r="X25" s="27" t="s">
+        <v>466</v>
+      </c>
+      <c r="Y25" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="Y25" s="1" t="s">
+      <c r="Z25" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="Z25" s="1" t="s">
-        <v>469</v>
-      </c>
       <c r="AA25" s="26" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="26" spans="1:27">
@@ -5389,7 +5377,7 @@
         <v>23</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C26" s="1">
         <v>10</v>
@@ -5445,16 +5433,16 @@
       <c r="V26" s="1"/>
       <c r="W26" s="26"/>
       <c r="X26" s="27" t="s">
+        <v>470</v>
+      </c>
+      <c r="Y26" s="1" t="s">
         <v>471</v>
       </c>
-      <c r="Y26" s="1" t="s">
+      <c r="Z26" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="Z26" s="1" t="s">
+      <c r="AA26" s="26" t="s">
         <v>473</v>
-      </c>
-      <c r="AA26" s="26" t="s">
-        <v>474</v>
       </c>
     </row>
     <row r="27" spans="1:27">
@@ -5462,7 +5450,7 @@
         <v>24</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C27" s="1">
         <v>10</v>
@@ -5518,16 +5506,16 @@
       <c r="V27" s="1"/>
       <c r="W27" s="26"/>
       <c r="X27" s="27" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y27" s="1" t="s">
         <v>476</v>
       </c>
-      <c r="Y27" s="1" t="s">
+      <c r="Z27" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="Z27" s="1" t="s">
+      <c r="AA27" s="26" t="s">
         <v>478</v>
-      </c>
-      <c r="AA27" s="26" t="s">
-        <v>479</v>
       </c>
     </row>
     <row r="28" spans="1:27">
@@ -5535,7 +5523,7 @@
         <v>25</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C28" s="1">
         <v>10</v>
@@ -5591,16 +5579,16 @@
       <c r="V28" s="1"/>
       <c r="W28" s="26"/>
       <c r="X28" s="27" t="s">
+        <v>480</v>
+      </c>
+      <c r="Y28" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="Y28" s="1" t="s">
+      <c r="Z28" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="Z28" s="1" t="s">
+      <c r="AA28" s="26" t="s">
         <v>483</v>
-      </c>
-      <c r="AA28" s="26" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="29" spans="1:27">
@@ -5608,7 +5596,7 @@
         <v>26</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C29" s="1">
         <v>10</v>
@@ -5664,16 +5652,16 @@
       <c r="V29" s="1"/>
       <c r="W29" s="26"/>
       <c r="X29" s="27" t="s">
+        <v>485</v>
+      </c>
+      <c r="Y29" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="Y29" s="1" t="s">
+      <c r="Z29" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="Z29" s="1" t="s">
+      <c r="AA29" s="26" t="s">
         <v>488</v>
-      </c>
-      <c r="AA29" s="26" t="s">
-        <v>489</v>
       </c>
     </row>
     <row r="30" spans="1:27">
@@ -5681,7 +5669,7 @@
         <v>27</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C30" s="1">
         <v>10</v>
@@ -5737,16 +5725,16 @@
       <c r="V30" s="1"/>
       <c r="W30" s="26"/>
       <c r="X30" s="27" t="s">
+        <v>490</v>
+      </c>
+      <c r="Y30" s="1" t="s">
         <v>491</v>
       </c>
-      <c r="Y30" s="1" t="s">
+      <c r="Z30" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="Z30" s="1" t="s">
-        <v>493</v>
-      </c>
       <c r="AA30" s="26" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="31" spans="1:27">
@@ -5754,7 +5742,7 @@
         <v>28</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C31" s="1">
         <v>10</v>
@@ -5810,16 +5798,16 @@
       <c r="V31" s="1"/>
       <c r="W31" s="26"/>
       <c r="X31" s="27" t="s">
+        <v>494</v>
+      </c>
+      <c r="Y31" s="1" t="s">
         <v>495</v>
       </c>
-      <c r="Y31" s="1" t="s">
+      <c r="Z31" s="1" t="s">
         <v>496</v>
       </c>
-      <c r="Z31" s="1" t="s">
-        <v>497</v>
-      </c>
       <c r="AA31" s="26" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="32" spans="1:27">
@@ -5827,7 +5815,7 @@
         <v>29</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C32" s="1">
         <v>10</v>
@@ -5883,16 +5871,16 @@
       <c r="V32" s="1"/>
       <c r="W32" s="26"/>
       <c r="X32" s="27" t="s">
+        <v>498</v>
+      </c>
+      <c r="Y32" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="Y32" s="1" t="s">
+      <c r="Z32" s="1" t="s">
         <v>500</v>
       </c>
-      <c r="Z32" s="1" t="s">
+      <c r="AA32" s="26" t="s">
         <v>501</v>
-      </c>
-      <c r="AA32" s="26" t="s">
-        <v>502</v>
       </c>
     </row>
     <row r="33" spans="1:27">
@@ -5900,7 +5888,7 @@
         <v>30</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C33" s="1">
         <v>10</v>
@@ -5956,16 +5944,16 @@
       <c r="V33" s="1"/>
       <c r="W33" s="26"/>
       <c r="X33" s="27" t="s">
+        <v>503</v>
+      </c>
+      <c r="Y33" s="1" t="s">
         <v>504</v>
       </c>
-      <c r="Y33" s="1" t="s">
+      <c r="Z33" s="1" t="s">
         <v>505</v>
       </c>
-      <c r="Z33" s="1" t="s">
+      <c r="AA33" s="26" t="s">
         <v>506</v>
-      </c>
-      <c r="AA33" s="26" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="34" spans="1:27">
@@ -5973,7 +5961,7 @@
         <v>31</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C34" s="1">
         <v>10</v>
@@ -6029,16 +6017,16 @@
       <c r="V34" s="1"/>
       <c r="W34" s="26"/>
       <c r="X34" s="27" t="s">
+        <v>508</v>
+      </c>
+      <c r="Y34" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="Y34" s="1" t="s">
+      <c r="Z34" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="Z34" s="1" t="s">
-        <v>511</v>
-      </c>
       <c r="AA34" s="26" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="35" spans="1:27">
@@ -6046,7 +6034,7 @@
         <v>32</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C35" s="1">
         <v>10</v>
@@ -6102,16 +6090,16 @@
       <c r="V35" s="1"/>
       <c r="W35" s="26"/>
       <c r="X35" s="27" t="s">
+        <v>512</v>
+      </c>
+      <c r="Y35" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="Y35" s="1" t="s">
+      <c r="Z35" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="Z35" s="1" t="s">
+      <c r="AA35" s="26" t="s">
         <v>515</v>
-      </c>
-      <c r="AA35" s="26" t="s">
-        <v>516</v>
       </c>
     </row>
     <row r="36" spans="1:27">
@@ -6119,7 +6107,7 @@
         <v>33</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C36" s="1">
         <v>10</v>
@@ -6175,16 +6163,16 @@
       <c r="V36" s="1"/>
       <c r="W36" s="26"/>
       <c r="X36" s="27" t="s">
+        <v>517</v>
+      </c>
+      <c r="Y36" s="1" t="s">
         <v>518</v>
       </c>
-      <c r="Y36" s="1" t="s">
+      <c r="Z36" s="1" t="s">
         <v>519</v>
       </c>
-      <c r="Z36" s="1" t="s">
+      <c r="AA36" s="26" t="s">
         <v>520</v>
-      </c>
-      <c r="AA36" s="26" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="37" spans="1:27">
@@ -6192,7 +6180,7 @@
         <v>34</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C37" s="1">
         <v>10</v>
@@ -6248,16 +6236,16 @@
       <c r="V37" s="1"/>
       <c r="W37" s="26"/>
       <c r="X37" s="27" t="s">
+        <v>522</v>
+      </c>
+      <c r="Y37" s="1" t="s">
         <v>523</v>
       </c>
-      <c r="Y37" s="1" t="s">
+      <c r="Z37" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="Z37" s="1" t="s">
+      <c r="AA37" s="26" t="s">
         <v>525</v>
-      </c>
-      <c r="AA37" s="26" t="s">
-        <v>526</v>
       </c>
     </row>
     <row r="38" spans="1:27">
@@ -6265,7 +6253,7 @@
         <v>35</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C38" s="1">
         <v>10</v>
@@ -6321,16 +6309,16 @@
       <c r="V38" s="1"/>
       <c r="W38" s="26"/>
       <c r="X38" s="27" t="s">
+        <v>527</v>
+      </c>
+      <c r="Y38" s="1" t="s">
         <v>528</v>
       </c>
-      <c r="Y38" s="1" t="s">
+      <c r="Z38" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="Z38" s="1" t="s">
+      <c r="AA38" s="26" t="s">
         <v>530</v>
-      </c>
-      <c r="AA38" s="26" t="s">
-        <v>531</v>
       </c>
     </row>
     <row r="39" spans="1:27">
@@ -6338,7 +6326,7 @@
         <v>36</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C39" s="1">
         <v>10</v>
@@ -6394,16 +6382,16 @@
       <c r="V39" s="1"/>
       <c r="W39" s="26"/>
       <c r="X39" s="27" t="s">
+        <v>532</v>
+      </c>
+      <c r="Y39" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="Y39" s="1" t="s">
+      <c r="Z39" s="1" t="s">
         <v>534</v>
       </c>
-      <c r="Z39" s="1" t="s">
+      <c r="AA39" s="26" t="s">
         <v>535</v>
-      </c>
-      <c r="AA39" s="26" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="40" spans="1:27">
@@ -6411,7 +6399,7 @@
         <v>37</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C40" s="1">
         <v>10</v>
@@ -6467,16 +6455,16 @@
       <c r="V40" s="1"/>
       <c r="W40" s="26"/>
       <c r="X40" s="27" t="s">
+        <v>537</v>
+      </c>
+      <c r="Y40" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="Y40" s="1" t="s">
+      <c r="Z40" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="Z40" s="1" t="s">
-        <v>540</v>
-      </c>
       <c r="AA40" s="26" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="41" ht="14.25" spans="1:27">
@@ -6484,7 +6472,7 @@
         <v>38</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C41" s="12">
         <v>10</v>
@@ -6540,16 +6528,16 @@
       <c r="V41" s="12"/>
       <c r="W41" s="29"/>
       <c r="X41" s="30" t="s">
+        <v>541</v>
+      </c>
+      <c r="Y41" s="12" t="s">
         <v>542</v>
       </c>
-      <c r="Y41" s="12" t="s">
+      <c r="Z41" s="12" t="s">
         <v>543</v>
       </c>
-      <c r="Z41" s="12" t="s">
-        <v>544</v>
-      </c>
       <c r="AA41" s="29" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
   </sheetData>
@@ -6578,7 +6566,7 @@
     </row>
     <row r="8" spans="3:6">
       <c r="C8" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D8">
         <v>4</v>
@@ -6594,7 +6582,7 @@
     </row>
     <row r="9" spans="3:6">
       <c r="C9" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -6613,7 +6601,7 @@
         <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -6621,7 +6609,7 @@
         <v>2</v>
       </c>
       <c r="B13" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -6629,7 +6617,7 @@
         <v>3</v>
       </c>
       <c r="B14" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -6637,16 +6625,16 @@
         <v>4</v>
       </c>
       <c r="B15" t="s">
+        <v>547</v>
+      </c>
+      <c r="F15" t="s">
+        <v>141</v>
+      </c>
+      <c r="H15" t="s">
+        <v>141</v>
+      </c>
+      <c r="I15" t="s">
         <v>548</v>
-      </c>
-      <c r="F15" t="s">
-        <v>142</v>
-      </c>
-      <c r="H15" t="s">
-        <v>142</v>
-      </c>
-      <c r="I15" t="s">
-        <v>549</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -6654,52 +6642,52 @@
         <v>5</v>
       </c>
       <c r="B16" t="s">
+        <v>549</v>
+      </c>
+      <c r="F16" t="s">
+        <v>548</v>
+      </c>
+      <c r="H16" t="s">
+        <v>159</v>
+      </c>
+      <c r="I16" t="s">
         <v>550</v>
-      </c>
-      <c r="F16" t="s">
-        <v>549</v>
-      </c>
-      <c r="H16" t="s">
-        <v>160</v>
-      </c>
-      <c r="I16" t="s">
-        <v>551</v>
       </c>
     </row>
     <row r="17" spans="6:9">
       <c r="F17" t="s">
+        <v>551</v>
+      </c>
+      <c r="H17" t="s">
+        <v>168</v>
+      </c>
+      <c r="I17" t="s">
         <v>552</v>
-      </c>
-      <c r="H17" t="s">
-        <v>169</v>
-      </c>
-      <c r="I17" t="s">
-        <v>553</v>
       </c>
     </row>
     <row r="18" spans="2:9">
       <c r="B18" t="s">
+        <v>553</v>
+      </c>
+      <c r="F18" t="s">
+        <v>159</v>
+      </c>
+      <c r="H18" t="s">
+        <v>152</v>
+      </c>
+      <c r="I18" t="s">
         <v>554</v>
-      </c>
-      <c r="F18" t="s">
-        <v>160</v>
-      </c>
-      <c r="H18" t="s">
-        <v>153</v>
-      </c>
-      <c r="I18" t="s">
-        <v>555</v>
       </c>
     </row>
     <row r="19" spans="6:9">
       <c r="F19" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H19" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="I19" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="20" spans="6:8">
@@ -6713,7 +6701,7 @@
     </row>
     <row r="21" spans="6:8">
       <c r="F21" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H21">
         <f>IF('intent|意图'!F23='intent|意图'!F22,H20&amp;"*"&amp;'intent|意图'!D23,'intent|意图'!D23)</f>
@@ -6722,7 +6710,7 @@
     </row>
     <row r="22" spans="6:8">
       <c r="F22" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H22">
         <f>IF('intent|意图'!F24='intent|意图'!F23,H21&amp;"*"&amp;'intent|意图'!D24,'intent|意图'!D24)</f>
@@ -6740,7 +6728,7 @@
     </row>
     <row r="24" spans="6:8">
       <c r="F24" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H24">
         <f>IF('intent|意图'!F17='intent|意图'!F25,H23&amp;"*"&amp;'intent|意图'!D17,'intent|意图'!D17)</f>
@@ -6749,7 +6737,7 @@
     </row>
     <row r="25" spans="6:8">
       <c r="F25" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H25">
         <f>IF('intent|意图'!F18='intent|意图'!F17,H24&amp;"*"&amp;'intent|意图'!D18,'intent|意图'!D18)</f>
@@ -6758,7 +6746,7 @@
     </row>
     <row r="26" spans="6:8">
       <c r="F26" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H26">
         <f>IF('intent|意图'!F19='intent|意图'!F18,H25&amp;"*"&amp;'intent|意图'!D19,'intent|意图'!D19)</f>
@@ -6767,7 +6755,7 @@
     </row>
     <row r="27" spans="6:8">
       <c r="F27" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H27">
         <f>IF('intent|意图'!F26='intent|意图'!F19,H26&amp;"*"&amp;'intent|意图'!D26,'intent|意图'!D26)</f>
@@ -6776,7 +6764,7 @@
     </row>
     <row r="28" spans="6:8">
       <c r="F28" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H28">
         <f>IF('intent|意图'!F27='intent|意图'!F26,H27&amp;"*"&amp;'intent|意图'!D27,'intent|意图'!D27)</f>
@@ -6794,32 +6782,32 @@
     </row>
     <row r="30" spans="2:2">
       <c r="B30" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="42" spans="2:2">
       <c r="B42" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="50" spans="2:2">
       <c r="B50" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="54" spans="2:2">
       <c r="B54" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="62" spans="2:2">
       <c r="B62" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="66" spans="2:2">
       <c r="B66" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
   </sheetData>
@@ -6847,7 +6835,7 @@
       <c r="C1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="71" t="s">
+      <c r="D1" s="69" t="s">
         <v>14</v>
       </c>
       <c r="E1" s="5" t="s">
@@ -6864,7 +6852,7 @@
       <c r="C2" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="71" t="s">
+      <c r="D2" s="69" t="s">
         <v>19</v>
       </c>
       <c r="E2" s="5" t="s">
@@ -6881,7 +6869,7 @@
       <c r="C3" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="71" t="s">
+      <c r="D3" s="69" t="s">
         <v>21</v>
       </c>
       <c r="E3" s="5" t="s">
@@ -6898,7 +6886,7 @@
       <c r="C4" s="1">
         <v>80</v>
       </c>
-      <c r="D4" s="72">
+      <c r="D4" s="45">
         <v>0</v>
       </c>
       <c r="E4" s="1" t="s">
@@ -6915,10 +6903,10 @@
       <c r="C5" s="1">
         <v>30</v>
       </c>
-      <c r="D5" s="72">
+      <c r="D5" s="45">
         <v>10</v>
       </c>
-      <c r="E5" s="68" t="s">
+      <c r="E5" s="1" t="s">
         <v>25</v>
       </c>
     </row>
@@ -6932,10 +6920,10 @@
       <c r="C6" s="1">
         <v>50</v>
       </c>
-      <c r="D6" s="72">
+      <c r="D6" s="45">
         <v>10</v>
       </c>
-      <c r="E6" s="68" t="s">
+      <c r="E6" s="1" t="s">
         <v>27</v>
       </c>
     </row>
@@ -6949,10 +6937,10 @@
       <c r="C7" s="1">
         <v>50</v>
       </c>
-      <c r="D7" s="72">
+      <c r="D7" s="45">
         <v>10</v>
       </c>
-      <c r="E7" s="68" t="s">
+      <c r="E7" s="1" t="s">
         <v>30</v>
       </c>
     </row>
@@ -6966,10 +6954,10 @@
       <c r="C8" s="1">
         <v>50</v>
       </c>
-      <c r="D8" s="72">
+      <c r="D8" s="45">
         <v>10</v>
       </c>
-      <c r="E8" s="68" t="s">
+      <c r="E8" s="1" t="s">
         <v>33</v>
       </c>
     </row>
@@ -6983,10 +6971,10 @@
       <c r="C9" s="1">
         <v>50</v>
       </c>
-      <c r="D9" s="72">
+      <c r="D9" s="45">
         <v>10</v>
       </c>
-      <c r="E9" s="68" t="s">
+      <c r="E9" s="1" t="s">
         <v>36</v>
       </c>
     </row>
@@ -7002,7 +6990,7 @@
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultColWidth="8.86666666666667" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="8.33333333333333" style="70" customWidth="1"/>
+    <col min="1" max="1" width="8.33333333333333" style="68" customWidth="1"/>
     <col min="2" max="2" width="11.8666666666667" customWidth="1"/>
     <col min="3" max="3" width="31.4666666666667" customWidth="1"/>
   </cols>
@@ -7020,7 +7008,7 @@
       <c r="D1" s="5"/>
       <c r="E1" s="5"/>
     </row>
-    <row r="2" s="69" customFormat="1" spans="1:5">
+    <row r="2" s="67" customFormat="1" spans="1:5">
       <c r="A2" s="43" t="s">
         <v>16</v>
       </c>
@@ -7257,7 +7245,7 @@
       <c r="I1" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="J1" s="67" t="s">
+      <c r="J1" s="5" t="s">
         <v>64</v>
       </c>
     </row>
@@ -7289,7 +7277,7 @@
       <c r="I2" s="58" t="s">
         <v>72</v>
       </c>
-      <c r="J2" s="67" t="s">
+      <c r="J2" s="5" t="s">
         <v>73</v>
       </c>
     </row>
@@ -7321,7 +7309,7 @@
       <c r="I3" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="J3" s="67" t="s">
+      <c r="J3" s="5" t="s">
         <v>43</v>
       </c>
     </row>
@@ -7348,19 +7336,19 @@
         <v>2</v>
       </c>
       <c r="H4" s="40" t="s">
-        <v>79</v>
+        <v>14</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="J4" s="68"/>
+      <c r="J4" s="1"/>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>80</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>81</v>
       </c>
       <c r="C5" s="1">
         <v>2</v>
@@ -7369,30 +7357,30 @@
         <v>1</v>
       </c>
       <c r="E5" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="G5" s="1">
+        <v>1</v>
+      </c>
+      <c r="H5" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="G5" s="1">
-        <v>1</v>
-      </c>
-      <c r="H5" s="40" t="s">
+      <c r="I5" s="40" t="s">
         <v>84</v>
       </c>
-      <c r="I5" s="40" t="s">
+      <c r="J5" s="1" t="s">
         <v>85</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>87</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>88</v>
       </c>
       <c r="C6" s="1">
         <v>1</v>
@@ -7401,22 +7389,22 @@
         <v>2</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F6" s="40" t="s">
         <v>89</v>
-      </c>
-      <c r="F6" s="40" t="s">
-        <v>90</v>
       </c>
       <c r="G6" s="1">
         <v>2</v>
       </c>
       <c r="H6" s="40" t="s">
-        <v>79</v>
+        <v>14</v>
       </c>
       <c r="I6" s="40" t="s">
+        <v>90</v>
+      </c>
+      <c r="J6" s="1" t="s">
         <v>91</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -7443,31 +7431,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="61" t="s">
+        <v>92</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="61" t="s">
         <v>93</v>
       </c>
-      <c r="C1" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="61" t="s">
+      <c r="E1" s="61" t="s">
         <v>94</v>
       </c>
-      <c r="E1" s="61" t="s">
+      <c r="F1" s="61" t="s">
         <v>95</v>
-      </c>
-      <c r="F1" s="61" t="s">
-        <v>96</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>62</v>
       </c>
       <c r="H1" s="55" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I1" s="55" t="s">
         <v>60</v>
       </c>
       <c r="J1" s="55" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K1" s="55" t="s">
         <v>63</v>
@@ -7478,34 +7466,34 @@
         <v>0</v>
       </c>
       <c r="B2" s="61" t="s">
+        <v>98</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="D2" s="61" t="s">
         <v>100</v>
       </c>
-      <c r="D2" s="61" t="s">
+      <c r="E2" s="61" t="s">
         <v>101</v>
       </c>
-      <c r="E2" s="61" t="s">
+      <c r="F2" s="61" t="s">
         <v>102</v>
-      </c>
-      <c r="F2" s="61" t="s">
-        <v>103</v>
       </c>
       <c r="G2" s="43" t="s">
         <v>71</v>
       </c>
       <c r="H2" s="55" t="s">
+        <v>103</v>
+      </c>
+      <c r="I2" s="55" t="s">
         <v>104</v>
       </c>
-      <c r="I2" s="55" t="s">
+      <c r="J2" s="55" t="s">
         <v>105</v>
       </c>
-      <c r="J2" s="55" t="s">
+      <c r="K2" s="55" t="s">
         <v>106</v>
-      </c>
-      <c r="K2" s="55" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -7522,7 +7510,7 @@
         <v>21</v>
       </c>
       <c r="E3" s="61" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F3" s="61" t="s">
         <v>21</v>
@@ -7545,11 +7533,11 @@
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B4" s="62"/>
       <c r="C4" s="40" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D4" s="62">
         <v>1</v>
@@ -7558,10 +7546,10 @@
       <c r="F4" s="62"/>
       <c r="G4" s="62"/>
       <c r="H4" s="40" t="s">
+        <v>110</v>
+      </c>
+      <c r="I4" s="1" t="s">
         <v>111</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>112</v>
       </c>
       <c r="J4" s="1">
         <v>8</v>
@@ -7570,11 +7558,11 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B5" s="62"/>
       <c r="C5" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D5" s="62">
         <v>2</v>
@@ -7583,10 +7571,10 @@
       <c r="F5" s="62"/>
       <c r="G5" s="62"/>
       <c r="H5" s="40" t="s">
+        <v>114</v>
+      </c>
+      <c r="I5" s="40" t="s">
         <v>115</v>
-      </c>
-      <c r="I5" s="40" t="s">
-        <v>116</v>
       </c>
       <c r="J5" s="1">
         <v>3</v>
@@ -7595,11 +7583,11 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B6" s="62"/>
       <c r="C6" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D6" s="62">
         <v>3</v>
@@ -7608,10 +7596,10 @@
       <c r="F6" s="62"/>
       <c r="G6" s="62"/>
       <c r="H6" s="40" t="s">
+        <v>117</v>
+      </c>
+      <c r="I6" s="1" t="s">
         <v>118</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>119</v>
       </c>
       <c r="J6" s="1">
         <v>0</v>
@@ -7620,11 +7608,11 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B7" s="62"/>
       <c r="C7" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D7" s="62">
         <v>4</v>
@@ -7633,10 +7621,10 @@
       <c r="F7" s="62"/>
       <c r="G7" s="62"/>
       <c r="H7" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="I7" s="1" t="s">
         <v>122</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>123</v>
       </c>
       <c r="J7" s="1">
         <v>0</v>
@@ -7645,11 +7633,11 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B8" s="62"/>
       <c r="C8" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D8" s="62">
         <v>5</v>
@@ -7658,10 +7646,10 @@
       <c r="F8" s="62"/>
       <c r="G8" s="62"/>
       <c r="H8" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="I8" s="1" t="s">
         <v>126</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>127</v>
       </c>
       <c r="J8" s="1">
         <v>0</v>
@@ -7670,11 +7658,11 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B9" s="62"/>
       <c r="C9" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D9" s="62">
         <v>6</v>
@@ -7683,10 +7671,10 @@
       <c r="F9" s="62"/>
       <c r="G9" s="62"/>
       <c r="H9" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="I9" s="1" t="s">
         <v>130</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>131</v>
       </c>
       <c r="J9" s="1">
         <v>0</v>
@@ -7695,11 +7683,11 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B10" s="62"/>
       <c r="C10" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D10" s="62">
         <v>7</v>
@@ -7708,10 +7696,10 @@
       <c r="F10" s="62"/>
       <c r="G10" s="62"/>
       <c r="H10" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="I10" s="1" t="s">
         <v>134</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>135</v>
       </c>
       <c r="J10" s="1">
         <v>0</v>
@@ -7720,11 +7708,11 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B11" s="62"/>
       <c r="C11" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D11" s="62">
         <v>8</v>
@@ -7733,10 +7721,10 @@
       <c r="F11" s="62"/>
       <c r="G11" s="62"/>
       <c r="H11" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="I11" s="1" t="s">
         <v>138</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>139</v>
       </c>
       <c r="J11" s="1">
         <v>0</v>
@@ -7745,11 +7733,11 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B12" s="62"/>
       <c r="C12" s="40" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D12" s="62">
         <v>1</v>
@@ -7764,27 +7752,27 @@
         <v>14</v>
       </c>
       <c r="H12" s="40" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J12" s="1">
         <v>5</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="46" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B13" s="47" t="s">
         <v>11</v>
       </c>
       <c r="C13" s="47" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D13" s="63"/>
       <c r="E13" s="63">
@@ -7795,10 +7783,10 @@
       </c>
       <c r="G13" s="62"/>
       <c r="H13" s="47" t="s">
+        <v>143</v>
+      </c>
+      <c r="I13" s="47" t="s">
         <v>144</v>
-      </c>
-      <c r="I13" s="47" t="s">
-        <v>145</v>
       </c>
       <c r="J13" s="47">
         <v>0</v>
@@ -7807,13 +7795,13 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="48" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B14" s="49" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="49" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D14" s="64"/>
       <c r="E14" s="64">
@@ -7824,10 +7812,10 @@
       </c>
       <c r="G14" s="62"/>
       <c r="H14" s="49" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I14" s="49" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J14" s="49">
         <v>0</v>
@@ -7836,13 +7824,13 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="48" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B15" s="49" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="49" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D15" s="64"/>
       <c r="E15" s="64">
@@ -7853,10 +7841,10 @@
       </c>
       <c r="G15" s="62"/>
       <c r="H15" s="49" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I15" s="49" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J15" s="49">
         <v>0</v>
@@ -7865,11 +7853,11 @@
     </row>
     <row r="16" customFormat="1" spans="1:11">
       <c r="A16" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B16" s="62"/>
       <c r="C16" s="40" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D16" s="62">
         <v>1</v>
@@ -7884,27 +7872,27 @@
         <v>14</v>
       </c>
       <c r="H16" s="40" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J16" s="1">
         <v>8</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="17" s="42" customFormat="1" spans="1:11">
       <c r="A17" s="50" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B17" s="51" t="s">
         <v>12</v>
       </c>
       <c r="C17" s="51" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D17" s="65"/>
       <c r="E17" s="65">
@@ -7915,10 +7903,10 @@
       </c>
       <c r="G17" s="62"/>
       <c r="H17" s="51" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I17" s="51" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J17" s="51">
         <v>0</v>
@@ -7927,13 +7915,13 @@
     </row>
     <row r="18" s="42" customFormat="1" spans="1:11">
       <c r="A18" s="50" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B18" s="51" t="s">
         <v>12</v>
       </c>
       <c r="C18" s="51" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D18" s="65"/>
       <c r="E18" s="65">
@@ -7944,10 +7932,10 @@
       </c>
       <c r="G18" s="62"/>
       <c r="H18" s="51" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I18" s="51" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="J18" s="51">
         <v>0</v>
@@ -7956,13 +7944,13 @@
     </row>
     <row r="19" s="42" customFormat="1" spans="1:11">
       <c r="A19" s="50" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B19" s="51" t="s">
         <v>12</v>
       </c>
       <c r="C19" s="51" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D19" s="65"/>
       <c r="E19" s="65">
@@ -7973,10 +7961,10 @@
       </c>
       <c r="G19" s="62"/>
       <c r="H19" s="51" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I19" s="51" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J19" s="51">
         <v>0</v>
@@ -7985,13 +7973,13 @@
     </row>
     <row r="20" s="59" customFormat="1" spans="1:11">
       <c r="A20" s="52" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B20" s="53" t="s">
         <v>28</v>
       </c>
       <c r="C20" s="53" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D20" s="66"/>
       <c r="E20" s="66">
@@ -8002,10 +7990,10 @@
       </c>
       <c r="G20" s="66"/>
       <c r="H20" s="53" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I20" s="53" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J20" s="53">
         <v>0</v>
@@ -8014,13 +8002,13 @@
     </row>
     <row r="21" s="59" customFormat="1" spans="1:11">
       <c r="A21" s="52" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B21" s="53" t="s">
         <v>28</v>
       </c>
       <c r="C21" s="53" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D21" s="66"/>
       <c r="E21" s="66">
@@ -8031,10 +8019,10 @@
       </c>
       <c r="G21" s="66"/>
       <c r="H21" s="53" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I21" s="53" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J21" s="53">
         <v>0</v>
@@ -8043,13 +8031,13 @@
     </row>
     <row r="22" s="59" customFormat="1" spans="1:11">
       <c r="A22" s="52" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B22" s="53" t="s">
         <v>28</v>
       </c>
       <c r="C22" s="53" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D22" s="66"/>
       <c r="E22" s="66">
@@ -8060,10 +8048,10 @@
       </c>
       <c r="G22" s="66"/>
       <c r="H22" s="53" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I22" s="53" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J22" s="53">
         <v>0</v>
@@ -8072,13 +8060,13 @@
     </row>
     <row r="23" spans="1:11">
       <c r="A23" s="48" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B23" s="49" t="s">
         <v>31</v>
       </c>
       <c r="C23" s="49" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D23" s="64"/>
       <c r="E23" s="64">
@@ -8089,10 +8077,10 @@
       </c>
       <c r="G23" s="64"/>
       <c r="H23" s="49" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I23" s="49" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J23" s="49">
         <v>0</v>
@@ -8101,13 +8089,13 @@
     </row>
     <row r="24" spans="1:11">
       <c r="A24" s="48" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B24" s="49" t="s">
         <v>31</v>
       </c>
       <c r="C24" s="49" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D24" s="64"/>
       <c r="E24" s="64">
@@ -8118,10 +8106,10 @@
       </c>
       <c r="G24" s="64"/>
       <c r="H24" s="49" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I24" s="49" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J24" s="49">
         <v>0</v>
@@ -8130,13 +8118,13 @@
     </row>
     <row r="25" spans="1:11">
       <c r="A25" s="48" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B25" s="49" t="s">
         <v>31</v>
       </c>
       <c r="C25" s="49" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D25" s="64"/>
       <c r="E25" s="64">
@@ -8147,10 +8135,10 @@
       </c>
       <c r="G25" s="64"/>
       <c r="H25" s="49" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I25" s="49" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J25" s="49">
         <v>0</v>
@@ -8159,13 +8147,13 @@
     </row>
     <row r="26" spans="1:11">
       <c r="A26" s="48" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B26" s="49" t="s">
         <v>34</v>
       </c>
       <c r="C26" s="49" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D26" s="64"/>
       <c r="E26" s="64">
@@ -8176,10 +8164,10 @@
       </c>
       <c r="G26" s="64"/>
       <c r="H26" s="49" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="I26" s="49" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J26" s="49">
         <v>0</v>
@@ -8188,13 +8176,13 @@
     </row>
     <row r="27" spans="1:11">
       <c r="A27" s="48" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B27" s="49" t="s">
         <v>34</v>
       </c>
       <c r="C27" s="49" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D27" s="64"/>
       <c r="E27" s="64">
@@ -8205,10 +8193,10 @@
       </c>
       <c r="G27" s="64"/>
       <c r="H27" s="53" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I27" s="49" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J27" s="49">
         <v>0</v>
@@ -8217,13 +8205,13 @@
     </row>
     <row r="28" s="41" customFormat="1" spans="1:11">
       <c r="A28" s="46" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B28" s="47" t="s">
         <v>34</v>
       </c>
       <c r="C28" s="47" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D28" s="63"/>
       <c r="E28" s="63">
@@ -8234,10 +8222,10 @@
       </c>
       <c r="G28" s="63"/>
       <c r="H28" s="47" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I28" s="47" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J28" s="47">
         <v>0</v>
@@ -8278,16 +8266,16 @@
         <v>15</v>
       </c>
       <c r="D1" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>188</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>189</v>
       </c>
       <c r="H1" s="55" t="s">
         <v>60</v>
@@ -8301,25 +8289,25 @@
         <v>16</v>
       </c>
       <c r="B2" s="43" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D2" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="E2" s="43" t="s">
         <v>191</v>
       </c>
-      <c r="E2" s="43" t="s">
+      <c r="F2" s="43" t="s">
         <v>192</v>
       </c>
-      <c r="F2" s="43" t="s">
+      <c r="G2" s="43" t="s">
         <v>193</v>
       </c>
-      <c r="G2" s="43" t="s">
+      <c r="H2" s="55" t="s">
         <v>194</v>
-      </c>
-      <c r="H2" s="55" t="s">
-        <v>195</v>
       </c>
       <c r="I2" s="58" t="s">
         <v>72</v>
@@ -8336,7 +8324,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>21</v>
@@ -8356,13 +8344,13 @@
     </row>
     <row r="4" customFormat="1" spans="1:9">
       <c r="A4" s="40" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B4" s="40" t="s">
+        <v>196</v>
+      </c>
+      <c r="C4" s="40" t="s">
         <v>197</v>
-      </c>
-      <c r="C4" s="40" t="s">
-        <v>198</v>
       </c>
       <c r="D4" s="40"/>
       <c r="E4" s="40"/>
@@ -8373,13 +8361,13 @@
     </row>
     <row r="5" s="54" customFormat="1" spans="1:9">
       <c r="A5" s="57" t="s">
+        <v>198</v>
+      </c>
+      <c r="B5" s="57" t="s">
         <v>199</v>
       </c>
-      <c r="B5" s="57" t="s">
+      <c r="C5" s="57" t="s">
         <v>200</v>
-      </c>
-      <c r="C5" s="57" t="s">
-        <v>201</v>
       </c>
       <c r="D5" s="57">
         <v>1</v>
@@ -8392,13 +8380,13 @@
     </row>
     <row r="6" s="54" customFormat="1" spans="1:9">
       <c r="A6" s="57" t="s">
+        <v>201</v>
+      </c>
+      <c r="B6" s="57" t="s">
         <v>202</v>
       </c>
-      <c r="B6" s="57" t="s">
+      <c r="C6" s="57" t="s">
         <v>203</v>
-      </c>
-      <c r="C6" s="57" t="s">
-        <v>204</v>
       </c>
       <c r="D6" s="57">
         <v>1</v>
@@ -8411,13 +8399,13 @@
     </row>
     <row r="7" s="54" customFormat="1" spans="1:9">
       <c r="A7" s="57" t="s">
+        <v>204</v>
+      </c>
+      <c r="B7" s="57" t="s">
         <v>205</v>
       </c>
-      <c r="B7" s="57" t="s">
+      <c r="C7" s="57" t="s">
         <v>206</v>
-      </c>
-      <c r="C7" s="57" t="s">
-        <v>207</v>
       </c>
       <c r="D7" s="57">
         <v>1</v>
@@ -8430,13 +8418,13 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>208</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>209</v>
       </c>
       <c r="D8" s="1">
         <v>1</v>
@@ -8451,21 +8439,21 @@
         <v>5</v>
       </c>
       <c r="H8" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="I8" s="1" t="s">
         <v>210</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>213</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>214</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -8478,13 +8466,13 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="C10" s="1" t="s">
         <v>216</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>217</v>
       </c>
       <c r="D10" s="1">
         <v>0</v>
@@ -8497,13 +8485,13 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="C11" s="1" t="s">
         <v>219</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>220</v>
       </c>
       <c r="D11" s="1">
         <v>0</v>
@@ -8516,13 +8504,13 @@
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>221</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>222</v>
       </c>
       <c r="D12" s="1">
         <v>0</v>
@@ -8558,22 +8546,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>223</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>224</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>61</v>
       </c>
       <c r="E1" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="F1" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>226</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>227</v>
       </c>
       <c r="H1" s="5" t="s">
         <v>15</v>
@@ -8584,25 +8572,25 @@
         <v>16</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C2" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="D2" s="44" t="s">
         <v>228</v>
       </c>
-      <c r="D2" s="44" t="s">
+      <c r="E2" s="43" t="s">
         <v>229</v>
       </c>
-      <c r="E2" s="43" t="s">
+      <c r="F2" s="43" t="s">
         <v>230</v>
       </c>
-      <c r="F2" s="43" t="s">
+      <c r="G2" s="43" t="s">
         <v>231</v>
       </c>
-      <c r="G2" s="43" t="s">
+      <c r="H2" s="5" t="s">
         <v>232</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -8657,11 +8645,11 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="40" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="40" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D5" s="1">
         <v>1</v>
@@ -8676,16 +8664,16 @@
         <v>5</v>
       </c>
       <c r="H5" s="40" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="6" s="41" customFormat="1" spans="1:8">
       <c r="A6" s="45" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B6" s="45"/>
       <c r="C6" s="45" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D6" s="45">
         <v>0</v>
@@ -8700,16 +8688,16 @@
         <v>8</v>
       </c>
       <c r="H6" s="45" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="7" s="41" customFormat="1" spans="1:8">
       <c r="A7" s="45" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B7" s="45"/>
       <c r="C7" s="45" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D7" s="45">
         <v>0</v>
@@ -8721,21 +8709,21 @@
         <v>3</v>
       </c>
       <c r="G7" s="45" t="s">
+        <v>239</v>
+      </c>
+      <c r="H7" s="45" t="s">
         <v>240</v>
-      </c>
-      <c r="H7" s="45" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D8" s="1">
         <v>0</v>
@@ -8750,18 +8738,18 @@
         <v>1</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>245</v>
-      </c>
       <c r="C9" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -8774,18 +8762,18 @@
         <v>2</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>248</v>
-      </c>
       <c r="C10" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D10" s="1">
         <v>0</v>
@@ -8798,18 +8786,18 @@
         <v>3</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="C11" s="1" t="s">
         <v>251</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>252</v>
       </c>
       <c r="D11" s="1">
         <v>0</v>
@@ -8822,18 +8810,18 @@
         <v>4</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>255</v>
-      </c>
       <c r="C12" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D12" s="1">
         <v>0</v>
@@ -8846,18 +8834,18 @@
         <v>5</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>258</v>
-      </c>
       <c r="C13" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D13" s="1">
         <v>0</v>
@@ -8870,18 +8858,18 @@
         <v>6</v>
       </c>
       <c r="H13" s="40" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="C14" s="1" t="s">
         <v>261</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>262</v>
       </c>
       <c r="D14" s="1">
         <v>0</v>
@@ -8894,18 +8882,18 @@
         <v>7</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="C15" s="1" t="s">
         <v>265</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>266</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -8918,18 +8906,18 @@
         <v>8</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="C16" s="1" t="s">
         <v>269</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>270</v>
       </c>
       <c r="D16" s="1">
         <v>0</v>
@@ -8942,18 +8930,18 @@
         <v>9</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="46" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B17" s="47" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C17" s="47" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D17" s="1">
         <v>0</v>
@@ -8962,18 +8950,18 @@
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
       <c r="H17" s="47" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="48" t="s">
+        <v>145</v>
+      </c>
+      <c r="B18" s="49" t="s">
         <v>146</v>
       </c>
-      <c r="B18" s="49" t="s">
-        <v>147</v>
-      </c>
       <c r="C18" s="49" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D18" s="1">
         <v>0</v>
@@ -8982,21 +8970,21 @@
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
       <c r="H18" s="49" t="s">
+        <v>273</v>
+      </c>
+      <c r="I18" t="s">
         <v>274</v>
-      </c>
-      <c r="I18" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="48" t="s">
+        <v>148</v>
+      </c>
+      <c r="B19" s="49" t="s">
         <v>149</v>
       </c>
-      <c r="B19" s="49" t="s">
-        <v>150</v>
-      </c>
       <c r="C19" s="49" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D19" s="1">
         <v>0</v>
@@ -9005,21 +8993,21 @@
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
       <c r="H19" s="49" t="s">
+        <v>275</v>
+      </c>
+      <c r="I19" t="s">
         <v>276</v>
-      </c>
-      <c r="I19" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="20" s="42" customFormat="1" spans="1:9">
       <c r="A20" s="50" t="s">
+        <v>152</v>
+      </c>
+      <c r="B20" s="51" t="s">
         <v>153</v>
       </c>
-      <c r="B20" s="51" t="s">
-        <v>154</v>
-      </c>
       <c r="C20" s="51" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D20" s="51">
         <v>0</v>
@@ -9028,21 +9016,21 @@
       <c r="F20" s="51"/>
       <c r="G20" s="51"/>
       <c r="H20" s="51" t="s">
+        <v>277</v>
+      </c>
+      <c r="I20" s="42" t="s">
         <v>278</v>
-      </c>
-      <c r="I20" s="42" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="21" s="42" customFormat="1" spans="1:9">
       <c r="A21" s="50" t="s">
+        <v>155</v>
+      </c>
+      <c r="B21" s="51" t="s">
         <v>156</v>
       </c>
-      <c r="B21" s="51" t="s">
-        <v>157</v>
-      </c>
       <c r="C21" s="51" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D21" s="51">
         <v>0</v>
@@ -9051,21 +9039,21 @@
       <c r="F21" s="51"/>
       <c r="G21" s="51"/>
       <c r="H21" s="51" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="I21" s="42" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="22" s="42" customFormat="1" spans="1:9">
       <c r="A22" s="50" t="s">
+        <v>157</v>
+      </c>
+      <c r="B22" s="51" t="s">
         <v>158</v>
       </c>
-      <c r="B22" s="51" t="s">
-        <v>159</v>
-      </c>
       <c r="C22" s="51" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D22" s="51">
         <v>0</v>
@@ -9074,21 +9062,21 @@
       <c r="F22" s="51"/>
       <c r="G22" s="51"/>
       <c r="H22" s="51" t="s">
+        <v>280</v>
+      </c>
+      <c r="I22" s="42" t="s">
         <v>281</v>
-      </c>
-      <c r="I22" s="42" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="52" t="s">
+        <v>159</v>
+      </c>
+      <c r="B23" s="53" t="s">
         <v>160</v>
       </c>
-      <c r="B23" s="53" t="s">
-        <v>161</v>
-      </c>
       <c r="C23" s="53" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D23" s="1">
         <v>0</v>
@@ -9097,21 +9085,21 @@
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
       <c r="H23" s="53" t="s">
+        <v>282</v>
+      </c>
+      <c r="I23" t="s">
         <v>283</v>
-      </c>
-      <c r="I23" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="52" t="s">
+        <v>162</v>
+      </c>
+      <c r="B24" s="53" t="s">
         <v>163</v>
       </c>
-      <c r="B24" s="53" t="s">
-        <v>164</v>
-      </c>
       <c r="C24" s="53" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D24" s="1">
         <v>0</v>
@@ -9120,21 +9108,21 @@
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
       <c r="H24" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="I24" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="52" t="s">
+        <v>165</v>
+      </c>
+      <c r="B25" s="53" t="s">
         <v>166</v>
       </c>
-      <c r="B25" s="53" t="s">
-        <v>167</v>
-      </c>
       <c r="C25" s="53" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D25" s="1">
         <v>0</v>
@@ -9143,21 +9131,21 @@
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
       <c r="H25" s="53" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I25" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="48" t="s">
+        <v>168</v>
+      </c>
+      <c r="B26" s="49" t="s">
         <v>169</v>
       </c>
-      <c r="B26" s="49" t="s">
-        <v>170</v>
-      </c>
       <c r="C26" s="49" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D26" s="1">
         <v>0</v>
@@ -9166,21 +9154,21 @@
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
       <c r="H26" s="49" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="I26" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="48" t="s">
+        <v>171</v>
+      </c>
+      <c r="B27" s="49" t="s">
         <v>172</v>
       </c>
-      <c r="B27" s="49" t="s">
-        <v>173</v>
-      </c>
       <c r="C27" s="49" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D27" s="1">
         <v>0</v>
@@ -9189,21 +9177,21 @@
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
       <c r="H27" s="49" t="s">
+        <v>286</v>
+      </c>
+      <c r="I27" t="s">
         <v>287</v>
-      </c>
-      <c r="I27" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="48" t="s">
+        <v>174</v>
+      </c>
+      <c r="B28" s="49" t="s">
         <v>175</v>
       </c>
-      <c r="B28" s="49" t="s">
-        <v>176</v>
-      </c>
       <c r="C28" s="49" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D28" s="1">
         <v>0</v>
@@ -9212,18 +9200,18 @@
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
       <c r="H28" s="47" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="48" t="s">
+        <v>177</v>
+      </c>
+      <c r="B29" s="49" t="s">
         <v>178</v>
       </c>
-      <c r="B29" s="49" t="s">
-        <v>179</v>
-      </c>
       <c r="C29" s="49" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D29" s="1">
         <v>0</v>
@@ -9232,21 +9220,21 @@
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
       <c r="H29" s="49" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="I29" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="48" t="s">
+        <v>180</v>
+      </c>
+      <c r="B30" s="49" t="s">
         <v>181</v>
       </c>
-      <c r="B30" s="49" t="s">
-        <v>182</v>
-      </c>
       <c r="C30" s="49" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D30" s="1">
         <v>0</v>
@@ -9255,21 +9243,21 @@
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
       <c r="H30" s="53" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I30" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="46" t="s">
+        <v>182</v>
+      </c>
+      <c r="B31" s="47" t="s">
         <v>183</v>
       </c>
-      <c r="B31" s="47" t="s">
-        <v>184</v>
-      </c>
       <c r="C31" s="47" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D31" s="1">
         <v>0</v>
@@ -9278,12 +9266,12 @@
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
       <c r="H31" s="47" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="40" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B32" s="1"/>
       <c r="C32" s="40"/>
@@ -9300,12 +9288,12 @@
         <v>5</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="40" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B33" s="1"/>
       <c r="C33" s="40"/>
@@ -9322,7 +9310,7 @@
         <v>8</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
   </sheetData>
@@ -9347,22 +9335,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="35" t="s">
+        <v>290</v>
+      </c>
+      <c r="C1" s="35" t="s">
         <v>291</v>
       </c>
-      <c r="C1" s="35" t="s">
+      <c r="D1" s="35" t="s">
         <v>292</v>
       </c>
-      <c r="D1" s="35" t="s">
+      <c r="E1" s="35" t="s">
         <v>293</v>
       </c>
-      <c r="E1" s="35" t="s">
+      <c r="F1" s="35" t="s">
         <v>294</v>
       </c>
-      <c r="F1" s="35" t="s">
+      <c r="G1" s="35" t="s">
         <v>295</v>
-      </c>
-      <c r="G1" s="35" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -9370,22 +9358,22 @@
         <v>16</v>
       </c>
       <c r="B2" s="37" t="s">
+        <v>296</v>
+      </c>
+      <c r="C2" s="37" t="s">
+        <v>227</v>
+      </c>
+      <c r="D2" s="37" t="s">
         <v>297</v>
       </c>
-      <c r="C2" s="37" t="s">
-        <v>228</v>
-      </c>
-      <c r="D2" s="37" t="s">
+      <c r="E2" s="37" t="s">
         <v>298</v>
       </c>
-      <c r="E2" s="37" t="s">
+      <c r="F2" s="37" t="s">
         <v>299</v>
       </c>
-      <c r="F2" s="37" t="s">
+      <c r="G2" s="38" t="s">
         <v>300</v>
-      </c>
-      <c r="G2" s="38" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -9396,16 +9384,16 @@
         <v>9</v>
       </c>
       <c r="C3" s="37" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D3" s="37" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E3" s="37" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F3" s="37" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G3" s="37" t="s">
         <v>9</v>
@@ -9413,10 +9401,10 @@
     </row>
     <row r="4" ht="14.25" spans="1:7">
       <c r="A4" s="39" t="s">
+        <v>301</v>
+      </c>
+      <c r="B4" s="40" t="s">
         <v>302</v>
-      </c>
-      <c r="B4" s="40" t="s">
-        <v>303</v>
       </c>
       <c r="C4" s="39">
         <v>100</v>
@@ -9431,15 +9419,15 @@
         <v>1</v>
       </c>
       <c r="G4" s="39" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="5" ht="14.25" spans="1:7">
       <c r="A5" s="39" t="s">
+        <v>304</v>
+      </c>
+      <c r="B5" s="40" t="s">
         <v>305</v>
-      </c>
-      <c r="B5" s="40" t="s">
-        <v>306</v>
       </c>
       <c r="C5" s="39">
         <v>100</v>
@@ -9454,15 +9442,15 @@
         <v>1</v>
       </c>
       <c r="G5" s="39" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="6" ht="14.25" spans="1:7">
       <c r="A6" s="39" t="s">
+        <v>307</v>
+      </c>
+      <c r="B6" s="40" t="s">
         <v>308</v>
-      </c>
-      <c r="B6" s="40" t="s">
-        <v>309</v>
       </c>
       <c r="C6" s="39">
         <v>3</v>
@@ -9477,15 +9465,15 @@
         <v>1</v>
       </c>
       <c r="G6" s="39" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="7" ht="14.25" spans="1:7">
       <c r="A7" s="39" t="s">
+        <v>310</v>
+      </c>
+      <c r="B7" s="40" t="s">
         <v>311</v>
-      </c>
-      <c r="B7" s="40" t="s">
-        <v>312</v>
       </c>
       <c r="C7" s="39">
         <v>3</v>
@@ -9500,12 +9488,12 @@
         <v>1</v>
       </c>
       <c r="G7" s="39" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="8" ht="14.25" spans="1:7">
       <c r="A8" s="39" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B8" s="40" t="s">
         <v>19</v>
@@ -9523,145 +9511,145 @@
         <v>1</v>
       </c>
       <c r="G8" s="39" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="9" ht="14.25" spans="1:7">
       <c r="A9" s="39" t="s">
+        <v>315</v>
+      </c>
+      <c r="B9" s="40" t="s">
         <v>316</v>
       </c>
-      <c r="B9" s="40" t="s">
+      <c r="C9" s="39">
+        <v>0</v>
+      </c>
+      <c r="D9" s="1">
+        <v>0</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0</v>
+      </c>
+      <c r="F9" s="1">
+        <v>1</v>
+      </c>
+      <c r="G9" s="39" t="s">
         <v>317</v>
-      </c>
-      <c r="C9" s="39">
-        <v>0</v>
-      </c>
-      <c r="D9" s="1">
-        <v>0</v>
-      </c>
-      <c r="E9" s="1">
-        <v>0</v>
-      </c>
-      <c r="F9" s="1">
-        <v>1</v>
-      </c>
-      <c r="G9" s="39" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="10" ht="14.25" spans="1:7">
       <c r="A10" s="39" t="s">
+        <v>318</v>
+      </c>
+      <c r="B10" s="40" t="s">
         <v>319</v>
       </c>
-      <c r="B10" s="40" t="s">
+      <c r="C10" s="39">
+        <v>0</v>
+      </c>
+      <c r="D10" s="1">
+        <v>0</v>
+      </c>
+      <c r="E10" s="1">
+        <v>0</v>
+      </c>
+      <c r="F10" s="1">
+        <v>1</v>
+      </c>
+      <c r="G10" s="39" t="s">
         <v>320</v>
-      </c>
-      <c r="C10" s="39">
-        <v>0</v>
-      </c>
-      <c r="D10" s="1">
-        <v>0</v>
-      </c>
-      <c r="E10" s="1">
-        <v>0</v>
-      </c>
-      <c r="F10" s="1">
-        <v>1</v>
-      </c>
-      <c r="G10" s="39" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="11" ht="14.25" spans="1:7">
       <c r="A11" s="39" t="s">
+        <v>321</v>
+      </c>
+      <c r="B11" s="40" t="s">
+        <v>199</v>
+      </c>
+      <c r="C11" s="39">
+        <v>0</v>
+      </c>
+      <c r="D11" s="1">
+        <v>0</v>
+      </c>
+      <c r="E11" s="1">
+        <v>0</v>
+      </c>
+      <c r="F11" s="1">
+        <v>1</v>
+      </c>
+      <c r="G11" s="39" t="s">
         <v>322</v>
-      </c>
-      <c r="B11" s="40" t="s">
-        <v>200</v>
-      </c>
-      <c r="C11" s="39">
-        <v>0</v>
-      </c>
-      <c r="D11" s="1">
-        <v>0</v>
-      </c>
-      <c r="E11" s="1">
-        <v>0</v>
-      </c>
-      <c r="F11" s="1">
-        <v>1</v>
-      </c>
-      <c r="G11" s="39" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="12" ht="14.25" spans="1:7">
       <c r="A12" s="39" t="s">
+        <v>323</v>
+      </c>
+      <c r="B12" s="40" t="s">
+        <v>202</v>
+      </c>
+      <c r="C12" s="39">
+        <v>0</v>
+      </c>
+      <c r="D12" s="1">
+        <v>0</v>
+      </c>
+      <c r="E12" s="1">
+        <v>0</v>
+      </c>
+      <c r="F12" s="1">
+        <v>1</v>
+      </c>
+      <c r="G12" s="39" t="s">
         <v>324</v>
-      </c>
-      <c r="B12" s="40" t="s">
-        <v>203</v>
-      </c>
-      <c r="C12" s="39">
-        <v>0</v>
-      </c>
-      <c r="D12" s="1">
-        <v>0</v>
-      </c>
-      <c r="E12" s="1">
-        <v>0</v>
-      </c>
-      <c r="F12" s="1">
-        <v>1</v>
-      </c>
-      <c r="G12" s="39" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="13" ht="14.25" spans="1:7">
       <c r="A13" s="39" t="s">
+        <v>325</v>
+      </c>
+      <c r="B13" s="40" t="s">
         <v>326</v>
       </c>
-      <c r="B13" s="40" t="s">
+      <c r="C13" s="39">
+        <v>0</v>
+      </c>
+      <c r="D13" s="1">
+        <v>0</v>
+      </c>
+      <c r="E13" s="1">
+        <v>0</v>
+      </c>
+      <c r="F13" s="1">
+        <v>1</v>
+      </c>
+      <c r="G13" s="39" t="s">
         <v>327</v>
-      </c>
-      <c r="C13" s="39">
-        <v>0</v>
-      </c>
-      <c r="D13" s="1">
-        <v>0</v>
-      </c>
-      <c r="E13" s="1">
-        <v>0</v>
-      </c>
-      <c r="F13" s="1">
-        <v>1</v>
-      </c>
-      <c r="G13" s="39" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="14" ht="14.25" spans="1:7">
       <c r="A14" s="39" t="s">
+        <v>328</v>
+      </c>
+      <c r="B14" s="40" t="s">
         <v>329</v>
       </c>
-      <c r="B14" s="40" t="s">
+      <c r="C14" s="39">
+        <v>0</v>
+      </c>
+      <c r="D14" s="1">
+        <v>0</v>
+      </c>
+      <c r="E14" s="1">
+        <v>0</v>
+      </c>
+      <c r="F14" s="1">
+        <v>1</v>
+      </c>
+      <c r="G14" s="39" t="s">
         <v>330</v>
-      </c>
-      <c r="C14" s="39">
-        <v>0</v>
-      </c>
-      <c r="D14" s="1">
-        <v>0</v>
-      </c>
-      <c r="E14" s="1">
-        <v>0</v>
-      </c>
-      <c r="F14" s="1">
-        <v>1</v>
-      </c>
-      <c r="G14" s="39" t="s">
-        <v>331</v>
       </c>
     </row>
   </sheetData>

--- a/xlsdir/配置-总表.xlsx
+++ b/xlsdir/配置-总表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="673" activeTab="4"/>
+    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="673" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="combat|战斗" sheetId="31" r:id="rId1"/>
@@ -16,8 +16,8 @@
     <sheet name="buff|增益" sheetId="39" r:id="rId7"/>
     <sheet name="ability_effect|技能效果" sheetId="34" r:id="rId8"/>
     <sheet name="attribute|属性" sheetId="35" r:id="rId9"/>
-    <sheet name="Sheet1" sheetId="11" r:id="rId10"/>
-    <sheet name="sheet2" sheetId="30" r:id="rId11"/>
+    <sheet name="Sheet1" sheetId="11" state="hidden" r:id="rId10"/>
+    <sheet name="sheet" sheetId="30" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'monster|魔物'!$A$1:$B$4</definedName>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="861" uniqueCount="558">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="837" uniqueCount="552">
   <si>
     <t>ID</t>
   </si>
@@ -195,10 +195,10 @@
     <t>意图池</t>
   </si>
   <si>
-    <t>split*absorb*entangle*attack_5</t>
-  </si>
-  <si>
-    <t>toxin_spray*healing_spore*hallucinogenic_spore*attack_8</t>
+    <t>split*attack_5</t>
+  </si>
+  <si>
+    <t>toxin_spray*attack_8</t>
   </si>
   <si>
     <t>heavy_strike*bone_shield*summon_assistance</t>
@@ -473,55 +473,31 @@
     <t>split</t>
   </si>
   <si>
-    <t>脆弱</t>
+    <t>增益法术</t>
+  </si>
+  <si>
+    <t>敌人打算释放一个正面效果的法术</t>
+  </si>
+  <si>
+    <t>res://asserts/textures/widgets/Buffs/ghost_form_(physical_damage_immunity).png</t>
+  </si>
+  <si>
+    <t>attack_8</t>
+  </si>
+  <si>
+    <t>敌人打算进行攻击,造成8点伤害</t>
+  </si>
+  <si>
+    <t>toxin_spray</t>
+  </si>
+  <si>
+    <t>攻击法术</t>
   </si>
   <si>
     <t>敌人打算释放一个负面效果的法术</t>
   </si>
   <si>
-    <t>res://asserts/textures/widgets/Buffs/ghost_form_(physical_damage_immunity).png</t>
-  </si>
-  <si>
-    <t>absorb</t>
-  </si>
-  <si>
-    <t>吸收</t>
-  </si>
-  <si>
-    <t>res://asserts/textures/widgets/Buffs/summoning_spell.png</t>
-  </si>
-  <si>
-    <t>entangle</t>
-  </si>
-  <si>
-    <t>缠绕</t>
-  </si>
-  <si>
-    <t>attack_8</t>
-  </si>
-  <si>
-    <t>敌人打算进行攻击,造成8点伤害</t>
-  </si>
-  <si>
-    <t>toxin_spray</t>
-  </si>
-  <si>
-    <t>毒素喷射</t>
-  </si>
-  <si>
     <t>res://asserts/textures/widgets/Buffs/poisoned.png</t>
-  </si>
-  <si>
-    <t>healing_spore</t>
-  </si>
-  <si>
-    <t>治疗孢子</t>
-  </si>
-  <si>
-    <t>hallucinogenic_spore</t>
-  </si>
-  <si>
-    <t>迷幻孢子</t>
   </si>
   <si>
     <t>destruction_ray</t>
@@ -724,6 +700,9 @@
     <t>entangled</t>
   </si>
   <si>
+    <t>缠绕</t>
+  </si>
+  <si>
     <t>目标在下一个回合无法攻击</t>
   </si>
   <si>
@@ -797,6 +776,21 @@
     <t>给与2层易伤</t>
   </si>
   <si>
+    <t>造成5点伤害</t>
+  </si>
+  <si>
+    <t>防护</t>
+  </si>
+  <si>
+    <t>自身获得5点护盾</t>
+  </si>
+  <si>
+    <t>毒素喷雾</t>
+  </si>
+  <si>
+    <t>造成2回合易伤BUFF</t>
+  </si>
+  <si>
     <t>易伤（Vulnerable）</t>
   </si>
   <si>
@@ -887,31 +881,22 @@
     <t>目标在下一回合无法行动。</t>
   </si>
   <si>
-    <t>分裂</t>
-  </si>
-  <si>
-    <t>史莱姆分裂成两个较小的实体，增加战斗中的敌人数量。</t>
-  </si>
-  <si>
-    <t>回复一定量的生命值，吸收的量取决于其当前生命值。</t>
+    <t>healing_spore</t>
+  </si>
+  <si>
+    <t>治疗孢子</t>
+  </si>
+  <si>
+    <t>所有人恢复10点生命值。</t>
   </si>
   <si>
     <t>恢复</t>
   </si>
   <si>
-    <t>减少玩家下一回合的行动点数。</t>
-  </si>
-  <si>
-    <t>减少行动点数</t>
-  </si>
-  <si>
-    <t>造成持续性的毒素伤害。</t>
-  </si>
-  <si>
-    <t>放毒</t>
-  </si>
-  <si>
-    <t>所有人恢复10点生命值。</t>
+    <t>hallucinogenic_spore</t>
+  </si>
+  <si>
+    <t>迷幻孢子</t>
   </si>
   <si>
     <t>玩家获得“混乱”卡牌。</t>
@@ -939,9 +924,6 @@
   </si>
   <si>
     <t>造成15点伤害</t>
-  </si>
-  <si>
-    <t>造成5点伤害</t>
   </si>
   <si>
     <t>Name</t>
@@ -2060,7 +2042,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="38">
+  <fills count="42">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2075,7 +2057,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="3" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2087,13 +2093,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="2" tint="-0.1"/>
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2758,7 +2764,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="27" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="27" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2782,16 +2788,16 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="30" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="30" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="32" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="30" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="30" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="32" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="33" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -2800,25 +2806,13 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="34" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2881,8 +2875,20 @@
     <xf numFmtId="0" fontId="24" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3012,6 +3018,12 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -3021,22 +3033,28 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3045,7 +3063,25 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
@@ -3054,13 +3090,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -3072,16 +3114,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -3533,67 +3590,67 @@
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="I1" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="P1" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="Q1" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="R1" s="13" t="s">
         <v>340</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="S1" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="T1" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="U1" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="V1" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="W1" s="14" t="s">
         <v>345</v>
-      </c>
-      <c r="R1" s="13" t="s">
-        <v>346</v>
-      </c>
-      <c r="S1" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="T1" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="U1" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="V1" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="W1" s="14" t="s">
-        <v>351</v>
       </c>
       <c r="X1" s="15"/>
       <c r="Y1" s="15"/>
@@ -3605,82 +3662,82 @@
         <v>16</v>
       </c>
       <c r="B2" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>348</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="J2" s="5" t="s">
         <v>352</v>
       </c>
-      <c r="C2" s="5" t="s">
-        <v>302</v>
-      </c>
-      <c r="D2" s="5" t="s">
+      <c r="K2" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="L2" s="5" t="s">
         <v>354</v>
       </c>
-      <c r="F2" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="G2" s="5" t="s">
+      <c r="M2" s="5" t="s">
         <v>355</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="N2" s="5" t="s">
         <v>356</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="O2" s="5" t="s">
         <v>357</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="P2" s="5" t="s">
         <v>358</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="Q2" s="5" t="s">
         <v>359</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="R2" s="16" t="s">
         <v>360</v>
       </c>
-      <c r="M2" s="5" t="s">
+      <c r="S2" s="5" t="s">
         <v>361</v>
       </c>
-      <c r="N2" s="5" t="s">
+      <c r="T2" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="U2" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="V2" s="5" t="s">
         <v>362</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="W2" s="17" t="s">
+        <v>359</v>
+      </c>
+      <c r="X2" s="18" t="s">
         <v>363</v>
       </c>
-      <c r="P2" s="5" t="s">
+      <c r="Y2" s="32" t="s">
         <v>364</v>
       </c>
-      <c r="Q2" s="5" t="s">
+      <c r="Z2" s="32" t="s">
         <v>365</v>
       </c>
-      <c r="R2" s="16" t="s">
+      <c r="AA2" s="33" t="s">
         <v>366</v>
-      </c>
-      <c r="S2" s="5" t="s">
-        <v>367</v>
-      </c>
-      <c r="T2" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="U2" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="V2" s="5" t="s">
-        <v>368</v>
-      </c>
-      <c r="W2" s="17" t="s">
-        <v>365</v>
-      </c>
-      <c r="X2" s="18" t="s">
-        <v>369</v>
-      </c>
-      <c r="Y2" s="32" t="s">
-        <v>370</v>
-      </c>
-      <c r="Z2" s="32" t="s">
-        <v>371</v>
-      </c>
-      <c r="AA2" s="33" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="3" ht="14.25" spans="1:27">
@@ -3771,7 +3828,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="C4" s="9">
         <v>10</v>
@@ -3826,17 +3883,17 @@
       <c r="U4" s="9"/>
       <c r="V4" s="9"/>
       <c r="W4" s="23"/>
-      <c r="X4" s="70" t="s">
-        <v>374</v>
+      <c r="X4" s="87" t="s">
+        <v>368</v>
       </c>
       <c r="Y4" s="9" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="Z4" s="9" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="AA4" s="23" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
     </row>
     <row r="5" spans="1:27">
@@ -3844,7 +3901,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="C5" s="1">
         <v>10</v>
@@ -3900,16 +3957,16 @@
       <c r="V5" s="1"/>
       <c r="W5" s="26"/>
       <c r="X5" s="27" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="Y5" s="1" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="Z5" s="1" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="AA5" s="26" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
     </row>
     <row r="6" spans="1:27">
@@ -3917,7 +3974,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="C6" s="1">
         <v>10</v>
@@ -3973,16 +4030,16 @@
       <c r="V6" s="1"/>
       <c r="W6" s="26"/>
       <c r="X6" s="27" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="Y6" s="1" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="Z6" s="1" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="AA6" s="26" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
     </row>
     <row r="7" spans="1:27">
@@ -3990,7 +4047,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="C7" s="1">
         <v>10</v>
@@ -4046,16 +4103,16 @@
       <c r="V7" s="1"/>
       <c r="W7" s="26"/>
       <c r="X7" s="27" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="Y7" s="1" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="Z7" s="1" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="AA7" s="26" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
     </row>
     <row r="8" spans="1:27">
@@ -4063,7 +4120,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="C8" s="1">
         <v>10</v>
@@ -4119,16 +4176,16 @@
       <c r="V8" s="1"/>
       <c r="W8" s="26"/>
       <c r="X8" s="27" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="Y8" s="1" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="Z8" s="1" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="AA8" s="26" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
     </row>
     <row r="9" spans="1:27">
@@ -4136,7 +4193,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="C9" s="1">
         <v>10</v>
@@ -4192,16 +4249,16 @@
       <c r="V9" s="1"/>
       <c r="W9" s="26"/>
       <c r="X9" s="27" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="Y9" s="1" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="Z9" s="1" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="AA9" s="26" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
     </row>
     <row r="10" spans="1:27">
@@ -4209,7 +4266,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="C10" s="1">
         <v>10</v>
@@ -4265,16 +4322,16 @@
       <c r="V10" s="1"/>
       <c r="W10" s="26"/>
       <c r="X10" s="27" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="Y10" s="1" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="Z10" s="1" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="AA10" s="26" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
     </row>
     <row r="11" spans="1:27">
@@ -4282,7 +4339,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="C11" s="1">
         <v>10</v>
@@ -4338,16 +4395,16 @@
       <c r="V11" s="1"/>
       <c r="W11" s="26"/>
       <c r="X11" s="27" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="Y11" s="1" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="Z11" s="1" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="AA11" s="26" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
     </row>
     <row r="12" spans="1:27">
@@ -4355,7 +4412,7 @@
         <v>9</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="C12" s="1">
         <v>10</v>
@@ -4411,16 +4468,16 @@
       <c r="V12" s="1"/>
       <c r="W12" s="26"/>
       <c r="X12" s="27" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="Y12" s="1" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="Z12" s="1" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="AA12" s="26" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
     </row>
     <row r="13" spans="1:27">
@@ -4428,7 +4485,7 @@
         <v>10</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="C13" s="1">
         <v>10</v>
@@ -4484,16 +4541,16 @@
       <c r="V13" s="1"/>
       <c r="W13" s="26"/>
       <c r="X13" s="27" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="Y13" s="1" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="Z13" s="1" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="AA13" s="26" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
     </row>
     <row r="14" spans="1:27">
@@ -4501,7 +4558,7 @@
         <v>11</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="C14" s="1">
         <v>10</v>
@@ -4557,16 +4614,16 @@
       <c r="V14" s="1"/>
       <c r="W14" s="26"/>
       <c r="X14" s="27" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="Y14" s="1" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="Z14" s="1" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="AA14" s="26" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
     </row>
     <row r="15" spans="1:27">
@@ -4574,7 +4631,7 @@
         <v>12</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="C15" s="1">
         <v>10</v>
@@ -4630,16 +4687,16 @@
       <c r="V15" s="1"/>
       <c r="W15" s="26"/>
       <c r="X15" s="27" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="Y15" s="1" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="Z15" s="1" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="AA15" s="26" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
     </row>
     <row r="16" spans="1:27">
@@ -4647,7 +4704,7 @@
         <v>13</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="C16" s="1">
         <v>10</v>
@@ -4703,16 +4760,16 @@
       <c r="V16" s="1"/>
       <c r="W16" s="26"/>
       <c r="X16" s="27" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="Y16" s="1" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="Z16" s="1" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="AA16" s="26" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
     </row>
     <row r="17" spans="1:27">
@@ -4720,7 +4777,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="C17" s="1">
         <v>10</v>
@@ -4776,16 +4833,16 @@
       <c r="V17" s="1"/>
       <c r="W17" s="26"/>
       <c r="X17" s="27" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="Y17" s="1" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="Z17" s="1" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="AA17" s="26" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
     </row>
     <row r="18" spans="1:27">
@@ -4793,7 +4850,7 @@
         <v>15</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="C18" s="1">
         <v>10</v>
@@ -4849,16 +4906,16 @@
       <c r="V18" s="1"/>
       <c r="W18" s="26"/>
       <c r="X18" s="27" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="Y18" s="1" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="Z18" s="1" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="AA18" s="26" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
     </row>
     <row r="19" spans="1:27">
@@ -4866,7 +4923,7 @@
         <v>16</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="C19" s="1">
         <v>10</v>
@@ -4922,16 +4979,16 @@
       <c r="V19" s="1"/>
       <c r="W19" s="26"/>
       <c r="X19" s="27" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="Y19" s="1" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="Z19" s="1" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="AA19" s="26" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
     </row>
     <row r="20" spans="1:27">
@@ -4939,7 +4996,7 @@
         <v>17</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="C20" s="1">
         <v>10</v>
@@ -4995,16 +5052,16 @@
       <c r="V20" s="1"/>
       <c r="W20" s="26"/>
       <c r="X20" s="27" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="Y20" s="1" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="Z20" s="1" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="AA20" s="26" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
     </row>
     <row r="21" spans="1:27">
@@ -5012,7 +5069,7 @@
         <v>18</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="C21" s="1">
         <v>10</v>
@@ -5068,16 +5125,16 @@
       <c r="V21" s="1"/>
       <c r="W21" s="26"/>
       <c r="X21" s="27" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="Y21" s="1" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="Z21" s="1" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="AA21" s="26" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
     </row>
     <row r="22" spans="1:27">
@@ -5085,7 +5142,7 @@
         <v>19</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="C22" s="1">
         <v>10</v>
@@ -5141,16 +5198,16 @@
       <c r="V22" s="1"/>
       <c r="W22" s="26"/>
       <c r="X22" s="27" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="Y22" s="1" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="Z22" s="1" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="AA22" s="26" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
     </row>
     <row r="23" spans="1:27">
@@ -5158,7 +5215,7 @@
         <v>20</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="C23" s="1">
         <v>10</v>
@@ -5214,16 +5271,16 @@
       <c r="V23" s="1"/>
       <c r="W23" s="26"/>
       <c r="X23" s="27" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="Y23" s="1" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="Z23" s="1" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="AA23" s="26" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
     </row>
     <row r="24" spans="1:27">
@@ -5231,7 +5288,7 @@
         <v>21</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="C24" s="1">
         <v>10</v>
@@ -5287,16 +5344,16 @@
       <c r="V24" s="1"/>
       <c r="W24" s="26"/>
       <c r="X24" s="27" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="Y24" s="1" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="Z24" s="1" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="AA24" s="26" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
     </row>
     <row r="25" spans="1:27">
@@ -5304,7 +5361,7 @@
         <v>22</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="C25" s="1">
         <v>10</v>
@@ -5360,16 +5417,16 @@
       <c r="V25" s="1"/>
       <c r="W25" s="26"/>
       <c r="X25" s="27" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="Y25" s="1" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="Z25" s="1" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="AA25" s="26" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
     </row>
     <row r="26" spans="1:27">
@@ -5377,7 +5434,7 @@
         <v>23</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="C26" s="1">
         <v>10</v>
@@ -5433,16 +5490,16 @@
       <c r="V26" s="1"/>
       <c r="W26" s="26"/>
       <c r="X26" s="27" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="Y26" s="1" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="Z26" s="1" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="AA26" s="26" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
     </row>
     <row r="27" spans="1:27">
@@ -5450,7 +5507,7 @@
         <v>24</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="C27" s="1">
         <v>10</v>
@@ -5506,16 +5563,16 @@
       <c r="V27" s="1"/>
       <c r="W27" s="26"/>
       <c r="X27" s="27" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="Y27" s="1" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="Z27" s="1" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="AA27" s="26" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
     </row>
     <row r="28" spans="1:27">
@@ -5523,7 +5580,7 @@
         <v>25</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="C28" s="1">
         <v>10</v>
@@ -5579,16 +5636,16 @@
       <c r="V28" s="1"/>
       <c r="W28" s="26"/>
       <c r="X28" s="27" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="Y28" s="1" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="Z28" s="1" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="AA28" s="26" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
     </row>
     <row r="29" spans="1:27">
@@ -5596,7 +5653,7 @@
         <v>26</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="C29" s="1">
         <v>10</v>
@@ -5652,16 +5709,16 @@
       <c r="V29" s="1"/>
       <c r="W29" s="26"/>
       <c r="X29" s="27" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="Y29" s="1" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="Z29" s="1" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="AA29" s="26" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
     </row>
     <row r="30" spans="1:27">
@@ -5669,7 +5726,7 @@
         <v>27</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="C30" s="1">
         <v>10</v>
@@ -5725,16 +5782,16 @@
       <c r="V30" s="1"/>
       <c r="W30" s="26"/>
       <c r="X30" s="27" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="Y30" s="1" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="Z30" s="1" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="AA30" s="26" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
     </row>
     <row r="31" spans="1:27">
@@ -5742,7 +5799,7 @@
         <v>28</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="C31" s="1">
         <v>10</v>
@@ -5798,16 +5855,16 @@
       <c r="V31" s="1"/>
       <c r="W31" s="26"/>
       <c r="X31" s="27" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="Y31" s="1" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="Z31" s="1" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="AA31" s="26" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
     </row>
     <row r="32" spans="1:27">
@@ -5815,7 +5872,7 @@
         <v>29</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="C32" s="1">
         <v>10</v>
@@ -5871,16 +5928,16 @@
       <c r="V32" s="1"/>
       <c r="W32" s="26"/>
       <c r="X32" s="27" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="Y32" s="1" t="s">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="Z32" s="1" t="s">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="AA32" s="26" t="s">
-        <v>501</v>
+        <v>495</v>
       </c>
     </row>
     <row r="33" spans="1:27">
@@ -5888,7 +5945,7 @@
         <v>30</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="C33" s="1">
         <v>10</v>
@@ -5944,16 +6001,16 @@
       <c r="V33" s="1"/>
       <c r="W33" s="26"/>
       <c r="X33" s="27" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="Y33" s="1" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="Z33" s="1" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="AA33" s="26" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
     </row>
     <row r="34" spans="1:27">
@@ -5961,7 +6018,7 @@
         <v>31</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="C34" s="1">
         <v>10</v>
@@ -6017,16 +6074,16 @@
       <c r="V34" s="1"/>
       <c r="W34" s="26"/>
       <c r="X34" s="27" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="Y34" s="1" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="Z34" s="1" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="AA34" s="26" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
     </row>
     <row r="35" spans="1:27">
@@ -6034,7 +6091,7 @@
         <v>32</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="C35" s="1">
         <v>10</v>
@@ -6090,16 +6147,16 @@
       <c r="V35" s="1"/>
       <c r="W35" s="26"/>
       <c r="X35" s="27" t="s">
-        <v>512</v>
+        <v>506</v>
       </c>
       <c r="Y35" s="1" t="s">
-        <v>513</v>
+        <v>507</v>
       </c>
       <c r="Z35" s="1" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="AA35" s="26" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
     </row>
     <row r="36" spans="1:27">
@@ -6107,7 +6164,7 @@
         <v>33</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="C36" s="1">
         <v>10</v>
@@ -6163,16 +6220,16 @@
       <c r="V36" s="1"/>
       <c r="W36" s="26"/>
       <c r="X36" s="27" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="Y36" s="1" t="s">
-        <v>518</v>
+        <v>512</v>
       </c>
       <c r="Z36" s="1" t="s">
-        <v>519</v>
+        <v>513</v>
       </c>
       <c r="AA36" s="26" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
     </row>
     <row r="37" spans="1:27">
@@ -6180,7 +6237,7 @@
         <v>34</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>521</v>
+        <v>515</v>
       </c>
       <c r="C37" s="1">
         <v>10</v>
@@ -6236,16 +6293,16 @@
       <c r="V37" s="1"/>
       <c r="W37" s="26"/>
       <c r="X37" s="27" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="Y37" s="1" t="s">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="Z37" s="1" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="AA37" s="26" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
     </row>
     <row r="38" spans="1:27">
@@ -6253,7 +6310,7 @@
         <v>35</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="C38" s="1">
         <v>10</v>
@@ -6309,16 +6366,16 @@
       <c r="V38" s="1"/>
       <c r="W38" s="26"/>
       <c r="X38" s="27" t="s">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="Y38" s="1" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="Z38" s="1" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="AA38" s="26" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
     </row>
     <row r="39" spans="1:27">
@@ -6326,7 +6383,7 @@
         <v>36</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="C39" s="1">
         <v>10</v>
@@ -6382,16 +6439,16 @@
       <c r="V39" s="1"/>
       <c r="W39" s="26"/>
       <c r="X39" s="27" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="Y39" s="1" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="Z39" s="1" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="AA39" s="26" t="s">
-        <v>535</v>
+        <v>529</v>
       </c>
     </row>
     <row r="40" spans="1:27">
@@ -6399,7 +6456,7 @@
         <v>37</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="C40" s="1">
         <v>10</v>
@@ -6455,16 +6512,16 @@
       <c r="V40" s="1"/>
       <c r="W40" s="26"/>
       <c r="X40" s="27" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
       <c r="Y40" s="1" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="Z40" s="1" t="s">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="AA40" s="26" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
     </row>
     <row r="41" ht="14.25" spans="1:27">
@@ -6472,7 +6529,7 @@
         <v>38</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="C41" s="12">
         <v>10</v>
@@ -6528,16 +6585,16 @@
       <c r="V41" s="12"/>
       <c r="W41" s="29"/>
       <c r="X41" s="30" t="s">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="Y41" s="12" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="Z41" s="12" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="AA41" s="29" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
     </row>
   </sheetData>
@@ -6601,7 +6658,7 @@
         <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>544</v>
+        <v>538</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -6609,7 +6666,7 @@
         <v>2</v>
       </c>
       <c r="B13" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -6617,7 +6674,7 @@
         <v>3</v>
       </c>
       <c r="B14" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -6625,7 +6682,7 @@
         <v>4</v>
       </c>
       <c r="B15" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="F15" t="s">
         <v>141</v>
@@ -6634,7 +6691,7 @@
         <v>141</v>
       </c>
       <c r="I15" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -6642,52 +6699,52 @@
         <v>5</v>
       </c>
       <c r="B16" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="F16" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="H16" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="I16" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
     </row>
     <row r="17" spans="6:9">
       <c r="F17" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="H17" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="I17" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
     </row>
     <row r="18" spans="2:9">
       <c r="B18" t="s">
-        <v>553</v>
+        <v>547</v>
       </c>
       <c r="F18" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="H18" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="I18" t="s">
-        <v>554</v>
+        <v>548</v>
       </c>
     </row>
     <row r="19" spans="6:9">
       <c r="F19" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="H19" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="I19" t="s">
-        <v>555</v>
+        <v>549</v>
       </c>
     </row>
     <row r="20" spans="6:8">
@@ -6695,25 +6752,25 @@
         <v>54</v>
       </c>
       <c r="H20">
-        <f>IF('intent|意图'!F22='intent|意图'!F21,#REF!&amp;"*"&amp;'intent|意图'!D22,'intent|意图'!D22)</f>
+        <f>IF('intent|意图'!F18='intent|意图'!F17,#REF!&amp;"*"&amp;'intent|意图'!D18,'intent|意图'!D18)</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="6:8">
       <c r="F21" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="H21">
-        <f>IF('intent|意图'!F23='intent|意图'!F22,H20&amp;"*"&amp;'intent|意图'!D23,'intent|意图'!D23)</f>
+        <f>IF('intent|意图'!F19='intent|意图'!F18,H20&amp;"*"&amp;'intent|意图'!D19,'intent|意图'!D19)</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="6:8">
       <c r="F22" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="H22">
-        <f>IF('intent|意图'!F24='intent|意图'!F23,H21&amp;"*"&amp;'intent|意图'!D24,'intent|意图'!D24)</f>
+        <f>IF('intent|意图'!F20='intent|意图'!F19,H21&amp;"*"&amp;'intent|意图'!D20,'intent|意图'!D20)</f>
         <v>0</v>
       </c>
     </row>
@@ -6722,52 +6779,52 @@
         <v>55</v>
       </c>
       <c r="H23">
-        <f>IF('intent|意图'!F25='intent|意图'!F24,H22&amp;"*"&amp;'intent|意图'!D25,'intent|意图'!D25)</f>
+        <f>IF('intent|意图'!F21='intent|意图'!F20,H22&amp;"*"&amp;'intent|意图'!D21,'intent|意图'!D21)</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="6:8">
       <c r="F24" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="H24">
-        <f>IF('intent|意图'!F17='intent|意图'!F25,H23&amp;"*"&amp;'intent|意图'!D17,'intent|意图'!D17)</f>
-        <v>0</v>
+        <f>IF('intent|意图'!F15='intent|意图'!F21,H23&amp;"*"&amp;'intent|意图'!D15,'intent|意图'!D15)</f>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="6:8">
       <c r="F25" t="s">
-        <v>554</v>
-      </c>
-      <c r="H25">
-        <f>IF('intent|意图'!F18='intent|意图'!F17,H24&amp;"*"&amp;'intent|意图'!D18,'intent|意图'!D18)</f>
-        <v>0</v>
+        <v>548</v>
+      </c>
+      <c r="H25" t="e">
+        <f>IF('intent|意图'!#REF!='intent|意图'!F15,H24&amp;"*"&amp;'intent|意图'!#REF!,'intent|意图'!#REF!)</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="26" spans="6:8">
       <c r="F26" t="s">
-        <v>556</v>
-      </c>
-      <c r="H26">
-        <f>IF('intent|意图'!F19='intent|意图'!F18,H25&amp;"*"&amp;'intent|意图'!D19,'intent|意图'!D19)</f>
-        <v>0</v>
+        <v>550</v>
+      </c>
+      <c r="H26" t="e">
+        <f>IF('intent|意图'!#REF!='intent|意图'!#REF!,H25&amp;"*"&amp;'intent|意图'!#REF!,'intent|意图'!#REF!)</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="27" spans="6:8">
       <c r="F27" t="s">
-        <v>177</v>
-      </c>
-      <c r="H27">
-        <f>IF('intent|意图'!F26='intent|意图'!F19,H26&amp;"*"&amp;'intent|意图'!D26,'intent|意图'!D26)</f>
-        <v>0</v>
+        <v>169</v>
+      </c>
+      <c r="H27" t="e">
+        <f>IF('intent|意图'!F22='intent|意图'!#REF!,H26&amp;"*"&amp;'intent|意图'!D22,'intent|意图'!D22)</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="28" spans="6:8">
       <c r="F28" t="s">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="H28">
-        <f>IF('intent|意图'!F27='intent|意图'!F26,H27&amp;"*"&amp;'intent|意图'!D27,'intent|意图'!D27)</f>
+        <f>IF('intent|意图'!F23='intent|意图'!F22,H27&amp;"*"&amp;'intent|意图'!D23,'intent|意图'!D23)</f>
         <v>0</v>
       </c>
     </row>
@@ -6776,38 +6833,38 @@
         <v>53</v>
       </c>
       <c r="H29">
-        <f>IF('intent|意图'!F28='intent|意图'!F27,H28&amp;"*"&amp;'intent|意图'!D28,'intent|意图'!D28)</f>
+        <f>IF('intent|意图'!F24='intent|意图'!F23,H28&amp;"*"&amp;'intent|意图'!D24,'intent|意图'!D24)</f>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="2:2">
       <c r="B30" t="s">
-        <v>553</v>
+        <v>547</v>
       </c>
     </row>
     <row r="42" spans="2:2">
       <c r="B42" t="s">
-        <v>553</v>
+        <v>547</v>
       </c>
     </row>
     <row r="50" spans="2:2">
       <c r="B50" t="s">
-        <v>557</v>
+        <v>551</v>
       </c>
     </row>
     <row r="54" spans="2:2">
       <c r="B54" t="s">
-        <v>553</v>
+        <v>547</v>
       </c>
     </row>
     <row r="62" spans="2:2">
       <c r="B62" t="s">
-        <v>557</v>
+        <v>551</v>
       </c>
     </row>
     <row r="66" spans="2:2">
       <c r="B66" t="s">
-        <v>553</v>
+        <v>547</v>
       </c>
     </row>
   </sheetData>
@@ -6835,7 +6892,7 @@
       <c r="C1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="69" t="s">
+      <c r="D1" s="86" t="s">
         <v>14</v>
       </c>
       <c r="E1" s="5" t="s">
@@ -6843,16 +6900,16 @@
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="43" t="s">
+      <c r="A2" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="43" t="s">
+      <c r="B2" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="43" t="s">
+      <c r="C2" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="69" t="s">
+      <c r="D2" s="86" t="s">
         <v>19</v>
       </c>
       <c r="E2" s="5" t="s">
@@ -6869,7 +6926,7 @@
       <c r="C3" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="69" t="s">
+      <c r="D3" s="86" t="s">
         <v>21</v>
       </c>
       <c r="E3" s="5" t="s">
@@ -6886,7 +6943,7 @@
       <c r="C4" s="1">
         <v>80</v>
       </c>
-      <c r="D4" s="45">
+      <c r="D4" s="47">
         <v>0</v>
       </c>
       <c r="E4" s="1" t="s">
@@ -6903,7 +6960,7 @@
       <c r="C5" s="1">
         <v>30</v>
       </c>
-      <c r="D5" s="45">
+      <c r="D5" s="47">
         <v>10</v>
       </c>
       <c r="E5" s="1" t="s">
@@ -6920,7 +6977,7 @@
       <c r="C6" s="1">
         <v>50</v>
       </c>
-      <c r="D6" s="45">
+      <c r="D6" s="47">
         <v>10</v>
       </c>
       <c r="E6" s="1" t="s">
@@ -6937,7 +6994,7 @@
       <c r="C7" s="1">
         <v>50</v>
       </c>
-      <c r="D7" s="45">
+      <c r="D7" s="47">
         <v>10</v>
       </c>
       <c r="E7" s="1" t="s">
@@ -6954,7 +7011,7 @@
       <c r="C8" s="1">
         <v>50</v>
       </c>
-      <c r="D8" s="45">
+      <c r="D8" s="47">
         <v>10</v>
       </c>
       <c r="E8" s="1" t="s">
@@ -6971,7 +7028,7 @@
       <c r="C9" s="1">
         <v>50</v>
       </c>
-      <c r="D9" s="45">
+      <c r="D9" s="47">
         <v>10</v>
       </c>
       <c r="E9" s="1" t="s">
@@ -6990,7 +7047,7 @@
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultColWidth="8.86666666666667" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="8.33333333333333" style="68" customWidth="1"/>
+    <col min="1" max="1" width="8.33333333333333" style="85" customWidth="1"/>
     <col min="2" max="2" width="11.8666666666667" customWidth="1"/>
     <col min="3" max="3" width="31.4666666666667" customWidth="1"/>
   </cols>
@@ -7008,20 +7065,20 @@
       <c r="D1" s="5"/>
       <c r="E1" s="5"/>
     </row>
-    <row r="2" s="67" customFormat="1" spans="1:5">
-      <c r="A2" s="43" t="s">
+    <row r="2" s="84" customFormat="1" spans="1:5">
+      <c r="A2" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="43" t="s">
+      <c r="B2" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="C2" s="43" t="s">
+      <c r="C2" s="45" t="s">
         <v>40</v>
       </c>
-      <c r="D2" s="43" t="s">
+      <c r="D2" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="E2" s="43" t="s">
+      <c r="E2" s="45" t="s">
         <v>42</v>
       </c>
     </row>
@@ -7250,31 +7307,31 @@
       </c>
     </row>
     <row r="2" ht="54" spans="1:10">
-      <c r="A2" s="43" t="s">
+      <c r="A2" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="43" t="s">
+      <c r="B2" s="45" t="s">
         <v>65</v>
       </c>
-      <c r="C2" s="43" t="s">
+      <c r="C2" s="45" t="s">
         <v>66</v>
       </c>
-      <c r="D2" s="43" t="s">
+      <c r="D2" s="45" t="s">
         <v>67</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="F2" s="43" t="s">
+      <c r="F2" s="45" t="s">
         <v>69</v>
       </c>
-      <c r="G2" s="44" t="s">
+      <c r="G2" s="46" t="s">
         <v>70</v>
       </c>
-      <c r="H2" s="43" t="s">
+      <c r="H2" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="I2" s="58" t="s">
+      <c r="I2" s="68" t="s">
         <v>72</v>
       </c>
       <c r="J2" s="5" t="s">
@@ -7416,12 +7473,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K28"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="21.25" customWidth="1"/>
-    <col min="2" max="2" width="9.06666666666667" style="60"/>
-    <col min="4" max="7" width="9.06666666666667" style="60"/>
+    <col min="2" max="2" width="9.06666666666667" style="72"/>
+    <col min="4" max="7" width="9.06666666666667" style="72"/>
     <col min="8" max="8" width="62" customWidth="1"/>
     <col min="9" max="9" width="67.125" customWidth="1"/>
   </cols>
@@ -7430,34 +7487,34 @@
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="61" t="s">
+      <c r="B1" s="73" t="s">
         <v>92</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="61" t="s">
+      <c r="D1" s="73" t="s">
         <v>93</v>
       </c>
-      <c r="E1" s="61" t="s">
+      <c r="E1" s="73" t="s">
         <v>94</v>
       </c>
-      <c r="F1" s="61" t="s">
+      <c r="F1" s="73" t="s">
         <v>95</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="H1" s="55" t="s">
+      <c r="H1" s="65" t="s">
         <v>96</v>
       </c>
-      <c r="I1" s="55" t="s">
+      <c r="I1" s="65" t="s">
         <v>60</v>
       </c>
-      <c r="J1" s="55" t="s">
+      <c r="J1" s="65" t="s">
         <v>97</v>
       </c>
-      <c r="K1" s="55" t="s">
+      <c r="K1" s="65" t="s">
         <v>63</v>
       </c>
     </row>
@@ -7465,34 +7522,34 @@
       <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="73" t="s">
         <v>98</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="D2" s="61" t="s">
+      <c r="D2" s="73" t="s">
         <v>100</v>
       </c>
-      <c r="E2" s="61" t="s">
+      <c r="E2" s="73" t="s">
         <v>101</v>
       </c>
-      <c r="F2" s="61" t="s">
+      <c r="F2" s="73" t="s">
         <v>102</v>
       </c>
-      <c r="G2" s="43" t="s">
+      <c r="G2" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="H2" s="55" t="s">
+      <c r="H2" s="65" t="s">
         <v>103</v>
       </c>
-      <c r="I2" s="55" t="s">
+      <c r="I2" s="65" t="s">
         <v>104</v>
       </c>
-      <c r="J2" s="55" t="s">
+      <c r="J2" s="65" t="s">
         <v>105</v>
       </c>
-      <c r="K2" s="55" t="s">
+      <c r="K2" s="65" t="s">
         <v>106</v>
       </c>
     </row>
@@ -7500,34 +7557,34 @@
       <c r="A3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="61" t="s">
+      <c r="B3" s="73" t="s">
         <v>9</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="61" t="s">
+      <c r="D3" s="73" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="61" t="s">
+      <c r="E3" s="73" t="s">
         <v>107</v>
       </c>
-      <c r="F3" s="61" t="s">
+      <c r="F3" s="73" t="s">
         <v>21</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="55" t="s">
+      <c r="H3" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="55" t="s">
+      <c r="I3" s="65" t="s">
         <v>74</v>
       </c>
-      <c r="J3" s="55" t="s">
+      <c r="J3" s="65" t="s">
         <v>21</v>
       </c>
-      <c r="K3" s="55" t="s">
+      <c r="K3" s="65" t="s">
         <v>43</v>
       </c>
     </row>
@@ -7535,16 +7592,16 @@
       <c r="A4" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="B4" s="62"/>
+      <c r="B4" s="74"/>
       <c r="C4" s="40" t="s">
         <v>109</v>
       </c>
-      <c r="D4" s="62">
-        <v>1</v>
-      </c>
-      <c r="E4" s="62"/>
-      <c r="F4" s="62"/>
-      <c r="G4" s="62"/>
+      <c r="D4" s="74">
+        <v>1</v>
+      </c>
+      <c r="E4" s="74"/>
+      <c r="F4" s="74"/>
+      <c r="G4" s="74"/>
       <c r="H4" s="40" t="s">
         <v>110</v>
       </c>
@@ -7560,16 +7617,16 @@
       <c r="A5" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B5" s="62"/>
+      <c r="B5" s="74"/>
       <c r="C5" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="D5" s="62">
+      <c r="D5" s="74">
         <v>2</v>
       </c>
-      <c r="E5" s="62"/>
-      <c r="F5" s="62"/>
-      <c r="G5" s="62"/>
+      <c r="E5" s="74"/>
+      <c r="F5" s="74"/>
+      <c r="G5" s="74"/>
       <c r="H5" s="40" t="s">
         <v>114</v>
       </c>
@@ -7585,16 +7642,16 @@
       <c r="A6" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="B6" s="62"/>
+      <c r="B6" s="74"/>
       <c r="C6" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D6" s="62">
+      <c r="D6" s="74">
         <v>3</v>
       </c>
-      <c r="E6" s="62"/>
-      <c r="F6" s="62"/>
-      <c r="G6" s="62"/>
+      <c r="E6" s="74"/>
+      <c r="F6" s="74"/>
+      <c r="G6" s="74"/>
       <c r="H6" s="40" t="s">
         <v>117</v>
       </c>
@@ -7610,16 +7667,16 @@
       <c r="A7" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="B7" s="62"/>
+      <c r="B7" s="74"/>
       <c r="C7" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="D7" s="62">
+      <c r="D7" s="74">
         <v>4</v>
       </c>
-      <c r="E7" s="62"/>
-      <c r="F7" s="62"/>
-      <c r="G7" s="62"/>
+      <c r="E7" s="74"/>
+      <c r="F7" s="74"/>
+      <c r="G7" s="74"/>
       <c r="H7" s="1" t="s">
         <v>121</v>
       </c>
@@ -7635,16 +7692,16 @@
       <c r="A8" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B8" s="62"/>
+      <c r="B8" s="74"/>
       <c r="C8" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="D8" s="62">
+      <c r="D8" s="74">
         <v>5</v>
       </c>
-      <c r="E8" s="62"/>
-      <c r="F8" s="62"/>
-      <c r="G8" s="62"/>
+      <c r="E8" s="74"/>
+      <c r="F8" s="74"/>
+      <c r="G8" s="74"/>
       <c r="H8" s="1" t="s">
         <v>125</v>
       </c>
@@ -7660,16 +7717,16 @@
       <c r="A9" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B9" s="62"/>
+      <c r="B9" s="74"/>
       <c r="C9" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D9" s="62">
+      <c r="D9" s="74">
         <v>6</v>
       </c>
-      <c r="E9" s="62"/>
-      <c r="F9" s="62"/>
-      <c r="G9" s="62"/>
+      <c r="E9" s="74"/>
+      <c r="F9" s="74"/>
+      <c r="G9" s="74"/>
       <c r="H9" s="1" t="s">
         <v>129</v>
       </c>
@@ -7685,16 +7742,16 @@
       <c r="A10" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="B10" s="62"/>
+      <c r="B10" s="74"/>
       <c r="C10" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="D10" s="62">
+      <c r="D10" s="74">
         <v>7</v>
       </c>
-      <c r="E10" s="62"/>
-      <c r="F10" s="62"/>
-      <c r="G10" s="62"/>
+      <c r="E10" s="74"/>
+      <c r="F10" s="74"/>
+      <c r="G10" s="74"/>
       <c r="H10" s="1" t="s">
         <v>133</v>
       </c>
@@ -7710,16 +7767,16 @@
       <c r="A11" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B11" s="62"/>
+      <c r="B11" s="74"/>
       <c r="C11" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="D11" s="62">
+      <c r="D11" s="74">
         <v>8</v>
       </c>
-      <c r="E11" s="62"/>
-      <c r="F11" s="62"/>
-      <c r="G11" s="62"/>
+      <c r="E11" s="74"/>
+      <c r="F11" s="74"/>
+      <c r="G11" s="74"/>
       <c r="H11" s="1" t="s">
         <v>137</v>
       </c>
@@ -7731,506 +7788,406 @@
       </c>
       <c r="K11" s="1"/>
     </row>
-    <row r="12" spans="1:11">
-      <c r="A12" s="1" t="s">
+    <row r="12" s="69" customFormat="1" spans="1:11">
+      <c r="A12" s="49" t="s">
         <v>139</v>
       </c>
-      <c r="B12" s="62"/>
-      <c r="C12" s="40" t="s">
+      <c r="B12" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="48" t="s">
         <v>109</v>
       </c>
-      <c r="D12" s="62">
-        <v>1</v>
-      </c>
-      <c r="E12" s="62">
+      <c r="D12" s="75">
+        <v>1</v>
+      </c>
+      <c r="E12" s="75">
+        <v>1</v>
+      </c>
+      <c r="F12" s="75">
+        <v>0</v>
+      </c>
+      <c r="G12" s="75" t="s">
+        <v>14</v>
+      </c>
+      <c r="H12" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="I12" s="49" t="s">
+        <v>111</v>
+      </c>
+      <c r="J12" s="49">
+        <v>5</v>
+      </c>
+      <c r="K12" s="49" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="13" s="69" customFormat="1" spans="1:11">
+      <c r="A13" s="50" t="s">
+        <v>141</v>
+      </c>
+      <c r="B13" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="51" t="s">
+        <v>142</v>
+      </c>
+      <c r="D13" s="76">
+        <v>3</v>
+      </c>
+      <c r="E13" s="76">
+        <v>5</v>
+      </c>
+      <c r="F13" s="76">
         <v>2</v>
       </c>
-      <c r="F12" s="62">
-        <v>0</v>
-      </c>
-      <c r="G12" s="62" t="s">
+      <c r="G13" s="75" t="s">
         <v>14</v>
       </c>
-      <c r="H12" s="40" t="s">
-        <v>140</v>
-      </c>
-      <c r="I12" s="1" t="s">
+      <c r="H13" s="51" t="s">
+        <v>143</v>
+      </c>
+      <c r="I13" s="51" t="s">
+        <v>144</v>
+      </c>
+      <c r="J13" s="51">
+        <v>0</v>
+      </c>
+      <c r="K13" s="50" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="14" s="70" customFormat="1" spans="1:11">
+      <c r="A14" s="77" t="s">
+        <v>145</v>
+      </c>
+      <c r="B14" s="77" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="78" t="s">
+        <v>109</v>
+      </c>
+      <c r="D14" s="79">
+        <v>1</v>
+      </c>
+      <c r="E14" s="79">
+        <v>1</v>
+      </c>
+      <c r="F14" s="79">
+        <v>0</v>
+      </c>
+      <c r="G14" s="79" t="s">
+        <v>14</v>
+      </c>
+      <c r="H14" s="78" t="s">
+        <v>146</v>
+      </c>
+      <c r="I14" s="77" t="s">
         <v>111</v>
       </c>
-      <c r="J12" s="1">
+      <c r="J14" s="77">
+        <v>8</v>
+      </c>
+      <c r="K14" s="77" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="15" s="70" customFormat="1" spans="1:11">
+      <c r="A15" s="80" t="s">
+        <v>147</v>
+      </c>
+      <c r="B15" s="77" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="77" t="s">
+        <v>148</v>
+      </c>
+      <c r="D15" s="79">
         <v>5</v>
       </c>
-      <c r="K12" s="1" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
-      <c r="A13" s="46" t="s">
-        <v>141</v>
-      </c>
-      <c r="B13" s="47" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" s="47" t="s">
-        <v>142</v>
-      </c>
-      <c r="D13" s="63"/>
-      <c r="E13" s="63">
+      <c r="E15" s="79">
+        <v>1</v>
+      </c>
+      <c r="F15" s="79">
         <v>2</v>
       </c>
-      <c r="F13" s="63">
-        <v>0</v>
-      </c>
-      <c r="G13" s="62"/>
-      <c r="H13" s="47" t="s">
-        <v>143</v>
-      </c>
-      <c r="I13" s="47" t="s">
-        <v>144</v>
-      </c>
-      <c r="J13" s="47">
-        <v>0</v>
-      </c>
-      <c r="K13" s="49"/>
-    </row>
-    <row r="14" spans="1:11">
-      <c r="A14" s="48" t="s">
-        <v>145</v>
-      </c>
-      <c r="B14" s="49" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="49" t="s">
-        <v>146</v>
-      </c>
-      <c r="D14" s="64"/>
-      <c r="E14" s="64">
-        <v>2</v>
-      </c>
-      <c r="F14" s="64">
-        <v>1</v>
-      </c>
-      <c r="G14" s="62"/>
-      <c r="H14" s="49" t="s">
-        <v>143</v>
-      </c>
-      <c r="I14" s="49" t="s">
+      <c r="G15" s="75" t="s">
+        <v>14</v>
+      </c>
+      <c r="H15" s="77" t="s">
+        <v>149</v>
+      </c>
+      <c r="I15" s="77" t="s">
+        <v>150</v>
+      </c>
+      <c r="J15" s="77">
+        <v>0</v>
+      </c>
+      <c r="K15" s="80" t="s">
         <v>147</v>
       </c>
-      <c r="J14" s="49">
-        <v>0</v>
-      </c>
-      <c r="K14" s="49"/>
-    </row>
-    <row r="15" spans="1:11">
-      <c r="A15" s="48" t="s">
-        <v>148</v>
-      </c>
-      <c r="B15" s="49" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="49" t="s">
-        <v>149</v>
-      </c>
-      <c r="D15" s="64"/>
-      <c r="E15" s="64">
-        <v>1</v>
-      </c>
-      <c r="F15" s="64">
+    </row>
+    <row r="16" s="71" customFormat="1" spans="1:11">
+      <c r="A16" s="58" t="s">
+        <v>151</v>
+      </c>
+      <c r="B16" s="59" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" s="59" t="s">
+        <v>152</v>
+      </c>
+      <c r="D16" s="81"/>
+      <c r="E16" s="81">
+        <v>1</v>
+      </c>
+      <c r="F16" s="81">
+        <v>0</v>
+      </c>
+      <c r="G16" s="81"/>
+      <c r="H16" s="59" t="s">
+        <v>153</v>
+      </c>
+      <c r="I16" s="59" t="s">
+        <v>138</v>
+      </c>
+      <c r="J16" s="59">
+        <v>0</v>
+      </c>
+      <c r="K16" s="59"/>
+    </row>
+    <row r="17" s="71" customFormat="1" spans="1:11">
+      <c r="A17" s="58" t="s">
+        <v>154</v>
+      </c>
+      <c r="B17" s="59" t="s">
+        <v>28</v>
+      </c>
+      <c r="C17" s="59" t="s">
+        <v>155</v>
+      </c>
+      <c r="D17" s="81"/>
+      <c r="E17" s="81">
+        <v>1</v>
+      </c>
+      <c r="F17" s="81">
+        <v>1</v>
+      </c>
+      <c r="G17" s="81"/>
+      <c r="H17" s="59" t="s">
+        <v>156</v>
+      </c>
+      <c r="I17" s="59" t="s">
+        <v>138</v>
+      </c>
+      <c r="J17" s="59">
+        <v>0</v>
+      </c>
+      <c r="K17" s="59"/>
+    </row>
+    <row r="18" s="71" customFormat="1" spans="1:11">
+      <c r="A18" s="58" t="s">
+        <v>157</v>
+      </c>
+      <c r="B18" s="59" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18" s="59" t="s">
+        <v>158</v>
+      </c>
+      <c r="D18" s="81"/>
+      <c r="E18" s="81">
+        <v>1</v>
+      </c>
+      <c r="F18" s="81">
         <v>3</v>
       </c>
-      <c r="G15" s="62"/>
-      <c r="H15" s="49" t="s">
-        <v>143</v>
-      </c>
-      <c r="I15" s="49" t="s">
-        <v>115</v>
-      </c>
-      <c r="J15" s="49">
-        <v>0</v>
-      </c>
-      <c r="K15" s="49"/>
-    </row>
-    <row r="16" customFormat="1" spans="1:11">
-      <c r="A16" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="B16" s="62"/>
-      <c r="C16" s="40" t="s">
-        <v>109</v>
-      </c>
-      <c r="D16" s="62">
-        <v>1</v>
-      </c>
-      <c r="E16" s="62">
-        <v>2</v>
-      </c>
-      <c r="F16" s="62">
-        <v>0</v>
-      </c>
-      <c r="G16" s="62" t="s">
-        <v>14</v>
-      </c>
-      <c r="H16" s="40" t="s">
-        <v>151</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="J16" s="1">
-        <v>8</v>
-      </c>
-      <c r="K16" s="1" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="17" s="42" customFormat="1" spans="1:11">
-      <c r="A17" s="50" t="s">
-        <v>152</v>
-      </c>
-      <c r="B17" s="51" t="s">
-        <v>12</v>
-      </c>
-      <c r="C17" s="51" t="s">
-        <v>153</v>
-      </c>
-      <c r="D17" s="65"/>
-      <c r="E17" s="65">
-        <v>2</v>
-      </c>
-      <c r="F17" s="65">
-        <v>0</v>
-      </c>
-      <c r="G17" s="62"/>
-      <c r="H17" s="51" t="s">
-        <v>143</v>
-      </c>
-      <c r="I17" s="51" t="s">
-        <v>154</v>
-      </c>
-      <c r="J17" s="51">
-        <v>0</v>
-      </c>
-      <c r="K17" s="51"/>
-    </row>
-    <row r="18" s="42" customFormat="1" spans="1:11">
-      <c r="A18" s="50" t="s">
-        <v>155</v>
-      </c>
-      <c r="B18" s="51" t="s">
-        <v>12</v>
-      </c>
-      <c r="C18" s="51" t="s">
-        <v>156</v>
-      </c>
-      <c r="D18" s="65"/>
-      <c r="E18" s="65">
-        <v>2</v>
-      </c>
-      <c r="F18" s="65">
-        <v>1</v>
-      </c>
-      <c r="G18" s="62"/>
-      <c r="H18" s="51" t="s">
-        <v>143</v>
-      </c>
-      <c r="I18" s="51" t="s">
-        <v>130</v>
-      </c>
-      <c r="J18" s="51">
-        <v>0</v>
-      </c>
-      <c r="K18" s="51"/>
-    </row>
-    <row r="19" s="42" customFormat="1" spans="1:11">
-      <c r="A19" s="50" t="s">
-        <v>157</v>
-      </c>
-      <c r="B19" s="51" t="s">
-        <v>12</v>
-      </c>
-      <c r="C19" s="51" t="s">
-        <v>158</v>
-      </c>
-      <c r="D19" s="65"/>
-      <c r="E19" s="65">
-        <v>1</v>
-      </c>
-      <c r="F19" s="65">
+      <c r="G18" s="81"/>
+      <c r="H18" s="59" t="s">
+        <v>159</v>
+      </c>
+      <c r="I18" s="59" t="s">
+        <v>138</v>
+      </c>
+      <c r="J18" s="59">
+        <v>0</v>
+      </c>
+      <c r="K18" s="59"/>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" s="60" t="s">
+        <v>160</v>
+      </c>
+      <c r="B19" s="61" t="s">
+        <v>31</v>
+      </c>
+      <c r="C19" s="61" t="s">
+        <v>161</v>
+      </c>
+      <c r="D19" s="82"/>
+      <c r="E19" s="82">
+        <v>1</v>
+      </c>
+      <c r="F19" s="82">
+        <v>0</v>
+      </c>
+      <c r="G19" s="82"/>
+      <c r="H19" s="61" t="s">
+        <v>162</v>
+      </c>
+      <c r="I19" s="61" t="s">
+        <v>138</v>
+      </c>
+      <c r="J19" s="61">
+        <v>0</v>
+      </c>
+      <c r="K19" s="61"/>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" s="60" t="s">
+        <v>163</v>
+      </c>
+      <c r="B20" s="61" t="s">
+        <v>31</v>
+      </c>
+      <c r="C20" s="61" t="s">
+        <v>164</v>
+      </c>
+      <c r="D20" s="82"/>
+      <c r="E20" s="82">
+        <v>1</v>
+      </c>
+      <c r="F20" s="82">
+        <v>1</v>
+      </c>
+      <c r="G20" s="82"/>
+      <c r="H20" s="61" t="s">
+        <v>165</v>
+      </c>
+      <c r="I20" s="61" t="s">
+        <v>138</v>
+      </c>
+      <c r="J20" s="61">
+        <v>0</v>
+      </c>
+      <c r="K20" s="61"/>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" s="60" t="s">
+        <v>166</v>
+      </c>
+      <c r="B21" s="61" t="s">
+        <v>31</v>
+      </c>
+      <c r="C21" s="61" t="s">
+        <v>167</v>
+      </c>
+      <c r="D21" s="82"/>
+      <c r="E21" s="82">
+        <v>1</v>
+      </c>
+      <c r="F21" s="82">
         <v>3</v>
       </c>
-      <c r="G19" s="62"/>
-      <c r="H19" s="51" t="s">
-        <v>143</v>
-      </c>
-      <c r="I19" s="51" t="s">
-        <v>134</v>
-      </c>
-      <c r="J19" s="51">
-        <v>0</v>
-      </c>
-      <c r="K19" s="51"/>
-    </row>
-    <row r="20" s="59" customFormat="1" spans="1:11">
-      <c r="A20" s="52" t="s">
+      <c r="G21" s="82"/>
+      <c r="H21" s="61" t="s">
+        <v>168</v>
+      </c>
+      <c r="I21" s="61" t="s">
+        <v>138</v>
+      </c>
+      <c r="J21" s="61">
+        <v>0</v>
+      </c>
+      <c r="K21" s="61"/>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" s="60" t="s">
+        <v>169</v>
+      </c>
+      <c r="B22" s="61" t="s">
+        <v>34</v>
+      </c>
+      <c r="C22" s="61" t="s">
+        <v>170</v>
+      </c>
+      <c r="D22" s="82"/>
+      <c r="E22" s="82">
+        <v>1</v>
+      </c>
+      <c r="F22" s="82">
+        <v>0</v>
+      </c>
+      <c r="G22" s="82"/>
+      <c r="H22" s="61" t="s">
+        <v>171</v>
+      </c>
+      <c r="I22" s="61" t="s">
+        <v>138</v>
+      </c>
+      <c r="J22" s="61">
+        <v>0</v>
+      </c>
+      <c r="K22" s="61"/>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" s="60" t="s">
+        <v>172</v>
+      </c>
+      <c r="B23" s="61" t="s">
+        <v>34</v>
+      </c>
+      <c r="C23" s="61" t="s">
+        <v>173</v>
+      </c>
+      <c r="D23" s="82"/>
+      <c r="E23" s="82">
+        <v>1</v>
+      </c>
+      <c r="F23" s="82">
+        <v>1</v>
+      </c>
+      <c r="G23" s="82"/>
+      <c r="H23" s="59" t="s">
         <v>159</v>
       </c>
-      <c r="B20" s="53" t="s">
-        <v>28</v>
-      </c>
-      <c r="C20" s="53" t="s">
-        <v>160</v>
-      </c>
-      <c r="D20" s="66"/>
-      <c r="E20" s="66">
-        <v>1</v>
-      </c>
-      <c r="F20" s="66">
-        <v>0</v>
-      </c>
-      <c r="G20" s="66"/>
-      <c r="H20" s="53" t="s">
-        <v>161</v>
-      </c>
-      <c r="I20" s="53" t="s">
+      <c r="I23" s="61" t="s">
         <v>138</v>
       </c>
-      <c r="J20" s="53">
-        <v>0</v>
-      </c>
-      <c r="K20" s="53"/>
-    </row>
-    <row r="21" s="59" customFormat="1" spans="1:11">
-      <c r="A21" s="52" t="s">
-        <v>162</v>
-      </c>
-      <c r="B21" s="53" t="s">
-        <v>28</v>
-      </c>
-      <c r="C21" s="53" t="s">
-        <v>163</v>
-      </c>
-      <c r="D21" s="66"/>
-      <c r="E21" s="66">
-        <v>1</v>
-      </c>
-      <c r="F21" s="66">
-        <v>1</v>
-      </c>
-      <c r="G21" s="66"/>
-      <c r="H21" s="53" t="s">
-        <v>164</v>
-      </c>
-      <c r="I21" s="53" t="s">
+      <c r="J23" s="61">
+        <v>0</v>
+      </c>
+      <c r="K23" s="61"/>
+    </row>
+    <row r="24" s="41" customFormat="1" spans="1:11">
+      <c r="A24" s="63" t="s">
+        <v>174</v>
+      </c>
+      <c r="B24" s="62" t="s">
+        <v>34</v>
+      </c>
+      <c r="C24" s="62" t="s">
+        <v>175</v>
+      </c>
+      <c r="D24" s="83"/>
+      <c r="E24" s="83">
+        <v>1</v>
+      </c>
+      <c r="F24" s="83">
+        <v>3</v>
+      </c>
+      <c r="G24" s="83"/>
+      <c r="H24" s="62" t="s">
+        <v>176</v>
+      </c>
+      <c r="I24" s="62" t="s">
         <v>138</v>
       </c>
-      <c r="J21" s="53">
-        <v>0</v>
-      </c>
-      <c r="K21" s="53"/>
-    </row>
-    <row r="22" s="59" customFormat="1" spans="1:11">
-      <c r="A22" s="52" t="s">
-        <v>165</v>
-      </c>
-      <c r="B22" s="53" t="s">
-        <v>28</v>
-      </c>
-      <c r="C22" s="53" t="s">
-        <v>166</v>
-      </c>
-      <c r="D22" s="66"/>
-      <c r="E22" s="66">
-        <v>1</v>
-      </c>
-      <c r="F22" s="66">
-        <v>3</v>
-      </c>
-      <c r="G22" s="66"/>
-      <c r="H22" s="53" t="s">
-        <v>167</v>
-      </c>
-      <c r="I22" s="53" t="s">
-        <v>138</v>
-      </c>
-      <c r="J22" s="53">
-        <v>0</v>
-      </c>
-      <c r="K22" s="53"/>
-    </row>
-    <row r="23" spans="1:11">
-      <c r="A23" s="48" t="s">
-        <v>168</v>
-      </c>
-      <c r="B23" s="49" t="s">
-        <v>31</v>
-      </c>
-      <c r="C23" s="49" t="s">
-        <v>169</v>
-      </c>
-      <c r="D23" s="64"/>
-      <c r="E23" s="64">
-        <v>1</v>
-      </c>
-      <c r="F23" s="64">
-        <v>0</v>
-      </c>
-      <c r="G23" s="64"/>
-      <c r="H23" s="49" t="s">
-        <v>170</v>
-      </c>
-      <c r="I23" s="49" t="s">
-        <v>138</v>
-      </c>
-      <c r="J23" s="49">
-        <v>0</v>
-      </c>
-      <c r="K23" s="49"/>
-    </row>
-    <row r="24" spans="1:11">
-      <c r="A24" s="48" t="s">
-        <v>171</v>
-      </c>
-      <c r="B24" s="49" t="s">
-        <v>31</v>
-      </c>
-      <c r="C24" s="49" t="s">
-        <v>172</v>
-      </c>
-      <c r="D24" s="64"/>
-      <c r="E24" s="64">
-        <v>1</v>
-      </c>
-      <c r="F24" s="64">
-        <v>1</v>
-      </c>
-      <c r="G24" s="64"/>
-      <c r="H24" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="I24" s="49" t="s">
-        <v>138</v>
-      </c>
-      <c r="J24" s="49">
-        <v>0</v>
-      </c>
-      <c r="K24" s="49"/>
-    </row>
-    <row r="25" spans="1:11">
-      <c r="A25" s="48" t="s">
-        <v>174</v>
-      </c>
-      <c r="B25" s="49" t="s">
-        <v>31</v>
-      </c>
-      <c r="C25" s="49" t="s">
-        <v>175</v>
-      </c>
-      <c r="D25" s="64"/>
-      <c r="E25" s="64">
-        <v>1</v>
-      </c>
-      <c r="F25" s="64">
-        <v>3</v>
-      </c>
-      <c r="G25" s="64"/>
-      <c r="H25" s="49" t="s">
-        <v>176</v>
-      </c>
-      <c r="I25" s="49" t="s">
-        <v>138</v>
-      </c>
-      <c r="J25" s="49">
-        <v>0</v>
-      </c>
-      <c r="K25" s="49"/>
-    </row>
-    <row r="26" spans="1:11">
-      <c r="A26" s="48" t="s">
-        <v>177</v>
-      </c>
-      <c r="B26" s="49" t="s">
-        <v>34</v>
-      </c>
-      <c r="C26" s="49" t="s">
-        <v>178</v>
-      </c>
-      <c r="D26" s="64"/>
-      <c r="E26" s="64">
-        <v>1</v>
-      </c>
-      <c r="F26" s="64">
-        <v>0</v>
-      </c>
-      <c r="G26" s="64"/>
-      <c r="H26" s="49" t="s">
-        <v>179</v>
-      </c>
-      <c r="I26" s="49" t="s">
-        <v>138</v>
-      </c>
-      <c r="J26" s="49">
-        <v>0</v>
-      </c>
-      <c r="K26" s="49"/>
-    </row>
-    <row r="27" spans="1:11">
-      <c r="A27" s="48" t="s">
-        <v>180</v>
-      </c>
-      <c r="B27" s="49" t="s">
-        <v>34</v>
-      </c>
-      <c r="C27" s="49" t="s">
-        <v>181</v>
-      </c>
-      <c r="D27" s="64"/>
-      <c r="E27" s="64">
-        <v>1</v>
-      </c>
-      <c r="F27" s="64">
-        <v>1</v>
-      </c>
-      <c r="G27" s="64"/>
-      <c r="H27" s="53" t="s">
-        <v>167</v>
-      </c>
-      <c r="I27" s="49" t="s">
-        <v>138</v>
-      </c>
-      <c r="J27" s="49">
-        <v>0</v>
-      </c>
-      <c r="K27" s="49"/>
-    </row>
-    <row r="28" s="41" customFormat="1" spans="1:11">
-      <c r="A28" s="46" t="s">
-        <v>182</v>
-      </c>
-      <c r="B28" s="47" t="s">
-        <v>34</v>
-      </c>
-      <c r="C28" s="47" t="s">
-        <v>183</v>
-      </c>
-      <c r="D28" s="63"/>
-      <c r="E28" s="63">
-        <v>1</v>
-      </c>
-      <c r="F28" s="63">
-        <v>3</v>
-      </c>
-      <c r="G28" s="63"/>
-      <c r="H28" s="47" t="s">
-        <v>184</v>
-      </c>
-      <c r="I28" s="47" t="s">
-        <v>138</v>
-      </c>
-      <c r="J28" s="47">
-        <v>0</v>
-      </c>
-      <c r="K28" s="47"/>
+      <c r="J24" s="62">
+        <v>0</v>
+      </c>
+      <c r="K24" s="62"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8266,18 +8223,18 @@
         <v>15</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="H1" s="55" t="s">
+        <v>180</v>
+      </c>
+      <c r="H1" s="65" t="s">
         <v>60</v>
       </c>
       <c r="I1" s="5" t="s">
@@ -8285,31 +8242,31 @@
       </c>
     </row>
     <row r="2" ht="148.5" spans="1:9">
-      <c r="A2" s="43" t="s">
+      <c r="A2" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="43" t="s">
-        <v>189</v>
+      <c r="B2" s="45" t="s">
+        <v>181</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="E2" s="43" t="s">
-        <v>191</v>
-      </c>
-      <c r="F2" s="43" t="s">
-        <v>192</v>
-      </c>
-      <c r="G2" s="43" t="s">
-        <v>193</v>
-      </c>
-      <c r="H2" s="55" t="s">
-        <v>194</v>
-      </c>
-      <c r="I2" s="58" t="s">
+        <v>182</v>
+      </c>
+      <c r="E2" s="45" t="s">
+        <v>183</v>
+      </c>
+      <c r="F2" s="45" t="s">
+        <v>184</v>
+      </c>
+      <c r="G2" s="45" t="s">
+        <v>185</v>
+      </c>
+      <c r="H2" s="65" t="s">
+        <v>186</v>
+      </c>
+      <c r="I2" s="68" t="s">
         <v>72</v>
       </c>
     </row>
@@ -8324,7 +8281,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>21</v>
@@ -8335,7 +8292,7 @@
       <c r="G3" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="H3" s="55" t="s">
+      <c r="H3" s="65" t="s">
         <v>74</v>
       </c>
       <c r="I3" s="5" t="s">
@@ -8347,84 +8304,84 @@
         <v>85</v>
       </c>
       <c r="B4" s="40" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="C4" s="40" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="D4" s="40"/>
       <c r="E4" s="40"/>
       <c r="F4" s="40"/>
       <c r="G4" s="40"/>
-      <c r="H4" s="56"/>
+      <c r="H4" s="66"/>
       <c r="I4" s="40"/>
     </row>
-    <row r="5" s="54" customFormat="1" spans="1:9">
-      <c r="A5" s="57" t="s">
+    <row r="5" s="64" customFormat="1" spans="1:9">
+      <c r="A5" s="67" t="s">
+        <v>190</v>
+      </c>
+      <c r="B5" s="67" t="s">
+        <v>191</v>
+      </c>
+      <c r="C5" s="67" t="s">
+        <v>192</v>
+      </c>
+      <c r="D5" s="67">
+        <v>1</v>
+      </c>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
+      <c r="H5" s="40"/>
+      <c r="I5" s="67"/>
+    </row>
+    <row r="6" s="64" customFormat="1" spans="1:9">
+      <c r="A6" s="67" t="s">
+        <v>193</v>
+      </c>
+      <c r="B6" s="67" t="s">
+        <v>194</v>
+      </c>
+      <c r="C6" s="67" t="s">
+        <v>195</v>
+      </c>
+      <c r="D6" s="67">
+        <v>1</v>
+      </c>
+      <c r="E6" s="67"/>
+      <c r="F6" s="67"/>
+      <c r="G6" s="67"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="67"/>
+    </row>
+    <row r="7" s="64" customFormat="1" spans="1:9">
+      <c r="A7" s="67" t="s">
+        <v>196</v>
+      </c>
+      <c r="B7" s="67" t="s">
+        <v>197</v>
+      </c>
+      <c r="C7" s="67" t="s">
         <v>198</v>
       </c>
-      <c r="B5" s="57" t="s">
-        <v>199</v>
-      </c>
-      <c r="C5" s="57" t="s">
-        <v>200</v>
-      </c>
-      <c r="D5" s="57">
-        <v>1</v>
-      </c>
-      <c r="E5" s="57"/>
-      <c r="F5" s="57"/>
-      <c r="G5" s="57"/>
-      <c r="H5" s="40"/>
-      <c r="I5" s="57"/>
-    </row>
-    <row r="6" s="54" customFormat="1" spans="1:9">
-      <c r="A6" s="57" t="s">
-        <v>201</v>
-      </c>
-      <c r="B6" s="57" t="s">
-        <v>202</v>
-      </c>
-      <c r="C6" s="57" t="s">
-        <v>203</v>
-      </c>
-      <c r="D6" s="57">
-        <v>1</v>
-      </c>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="57"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="57"/>
-    </row>
-    <row r="7" s="54" customFormat="1" spans="1:9">
-      <c r="A7" s="57" t="s">
-        <v>204</v>
-      </c>
-      <c r="B7" s="57" t="s">
-        <v>205</v>
-      </c>
-      <c r="C7" s="57" t="s">
-        <v>206</v>
-      </c>
-      <c r="D7" s="57">
-        <v>1</v>
-      </c>
-      <c r="E7" s="57"/>
-      <c r="F7" s="57"/>
-      <c r="G7" s="57"/>
+      <c r="D7" s="67">
+        <v>1</v>
+      </c>
+      <c r="E7" s="67"/>
+      <c r="F7" s="67"/>
+      <c r="G7" s="67"/>
       <c r="H7" s="1"/>
-      <c r="I7" s="57"/>
+      <c r="I7" s="67"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
         <v>91</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="D8" s="1">
         <v>1</v>
@@ -8439,21 +8396,21 @@
         <v>5</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -8466,13 +8423,13 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="D10" s="1">
         <v>0</v>
@@ -8485,13 +8442,13 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="D11" s="1">
         <v>0</v>
@@ -8504,13 +8461,13 @@
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="1" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>149</v>
+        <v>213</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="D12" s="1">
         <v>0</v>
@@ -8518,7 +8475,7 @@
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
-      <c r="H12" s="47"/>
+      <c r="H12" s="62"/>
       <c r="I12" s="1"/>
     </row>
   </sheetData>
@@ -8530,7 +8487,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="22.625" customWidth="1"/>
@@ -8546,51 +8503,51 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>61</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="H1" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="2" ht="81" spans="1:8">
-      <c r="A2" s="43" t="s">
+      <c r="A2" s="45" t="s">
         <v>16</v>
       </c>
       <c r="B2" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="D2" s="46" t="s">
+        <v>221</v>
+      </c>
+      <c r="E2" s="45" t="s">
         <v>222</v>
       </c>
-      <c r="C2" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="D2" s="44" t="s">
-        <v>228</v>
-      </c>
-      <c r="E2" s="43" t="s">
-        <v>229</v>
-      </c>
-      <c r="F2" s="43" t="s">
-        <v>230</v>
-      </c>
-      <c r="G2" s="43" t="s">
-        <v>231</v>
+      <c r="F2" s="45" t="s">
+        <v>223</v>
+      </c>
+      <c r="G2" s="45" t="s">
+        <v>224</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -8649,7 +8606,7 @@
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="40" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="D5" s="1">
         <v>1</v>
@@ -8664,212 +8621,212 @@
         <v>5</v>
       </c>
       <c r="H5" s="40" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="6" s="41" customFormat="1" spans="1:8">
+      <c r="A6" s="47" t="s">
+        <v>228</v>
+      </c>
+      <c r="B6" s="47"/>
+      <c r="C6" s="47" t="s">
+        <v>87</v>
+      </c>
+      <c r="D6" s="47">
+        <v>0</v>
+      </c>
+      <c r="E6" s="47">
+        <v>0</v>
+      </c>
+      <c r="F6" s="47">
+        <v>1</v>
+      </c>
+      <c r="G6" s="47">
+        <v>8</v>
+      </c>
+      <c r="H6" s="47" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="7" s="41" customFormat="1" spans="1:8">
+      <c r="A7" s="47" t="s">
+        <v>230</v>
+      </c>
+      <c r="B7" s="47"/>
+      <c r="C7" s="47" t="s">
+        <v>231</v>
+      </c>
+      <c r="D7" s="47">
+        <v>0</v>
+      </c>
+      <c r="E7" s="47">
+        <v>0</v>
+      </c>
+      <c r="F7" s="47">
+        <v>3</v>
+      </c>
+      <c r="G7" s="47" t="s">
+        <v>232</v>
+      </c>
+      <c r="H7" s="47" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="48" t="s">
+        <v>139</v>
+      </c>
+      <c r="B8" s="49"/>
+      <c r="C8" s="48" t="s">
+        <v>109</v>
+      </c>
+      <c r="D8" s="49">
+        <v>0</v>
+      </c>
+      <c r="E8" s="49">
+        <v>0</v>
+      </c>
+      <c r="F8" s="49">
+        <v>1</v>
+      </c>
+      <c r="G8" s="48">
+        <v>5</v>
+      </c>
+      <c r="H8" s="49" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="6" s="41" customFormat="1" spans="1:8">
-      <c r="A6" s="45" t="s">
+    <row r="9" spans="1:8">
+      <c r="A9" s="50" t="s">
+        <v>141</v>
+      </c>
+      <c r="B9" s="51"/>
+      <c r="C9" s="51" t="s">
         <v>235</v>
       </c>
-      <c r="B6" s="45"/>
-      <c r="C6" s="45" t="s">
-        <v>87</v>
-      </c>
-      <c r="D6" s="45">
-        <v>0</v>
-      </c>
-      <c r="E6" s="45">
-        <v>0</v>
-      </c>
-      <c r="F6" s="45">
-        <v>1</v>
-      </c>
-      <c r="G6" s="45">
+      <c r="D9" s="49">
+        <v>1</v>
+      </c>
+      <c r="E9" s="49">
+        <v>0</v>
+      </c>
+      <c r="F9" s="49">
+        <v>2</v>
+      </c>
+      <c r="G9" s="49">
+        <v>5</v>
+      </c>
+      <c r="H9" s="51" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="10" s="42" customFormat="1" spans="1:8">
+      <c r="A10" s="52" t="s">
+        <v>145</v>
+      </c>
+      <c r="B10" s="53"/>
+      <c r="C10" s="52" t="s">
+        <v>109</v>
+      </c>
+      <c r="D10" s="53">
+        <v>0</v>
+      </c>
+      <c r="E10" s="53">
+        <v>0</v>
+      </c>
+      <c r="F10" s="53">
+        <v>1</v>
+      </c>
+      <c r="G10" s="52">
         <v>8</v>
       </c>
-      <c r="H6" s="45" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="7" s="41" customFormat="1" spans="1:8">
-      <c r="A7" s="45" t="s">
+      <c r="H10" s="53" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="11" s="43" customFormat="1" spans="1:8">
+      <c r="A11" s="54" t="s">
+        <v>147</v>
+      </c>
+      <c r="B11" s="53"/>
+      <c r="C11" s="53" t="s">
         <v>237</v>
       </c>
-      <c r="B7" s="45"/>
-      <c r="C7" s="45" t="s">
+      <c r="D11" s="53">
+        <v>0</v>
+      </c>
+      <c r="E11" s="53">
+        <v>0</v>
+      </c>
+      <c r="F11" s="53">
+        <v>3</v>
+      </c>
+      <c r="G11" s="55" t="s">
+        <v>232</v>
+      </c>
+      <c r="H11" s="53" t="s">
         <v>238</v>
-      </c>
-      <c r="D7" s="45">
-        <v>0</v>
-      </c>
-      <c r="E7" s="45">
-        <v>0</v>
-      </c>
-      <c r="F7" s="45">
-        <v>3</v>
-      </c>
-      <c r="G7" s="45" t="s">
-        <v>239</v>
-      </c>
-      <c r="H7" s="45" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="D8" s="1">
-        <v>0</v>
-      </c>
-      <c r="E8" s="1">
-        <v>2</v>
-      </c>
-      <c r="F8" s="1">
-        <v>4</v>
-      </c>
-      <c r="G8" s="1">
-        <v>1</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="D9" s="1">
-        <v>0</v>
-      </c>
-      <c r="E9" s="1">
-        <v>1</v>
-      </c>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1">
-        <v>2</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="D10" s="1">
-        <v>0</v>
-      </c>
-      <c r="E10" s="1">
-        <v>-1</v>
-      </c>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1">
-        <v>3</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="D11" s="1">
-        <v>0</v>
-      </c>
-      <c r="E11" s="1">
-        <v>-1</v>
-      </c>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1">
-        <v>4</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
-        <v>253</v>
+        <v>202</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>254</v>
+        <v>239</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>120</v>
+        <v>199</v>
       </c>
       <c r="D12" s="1">
         <v>0</v>
       </c>
       <c r="E12" s="1">
-        <v>1</v>
-      </c>
-      <c r="F12" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="F12" s="1">
+        <v>4</v>
+      </c>
       <c r="G12" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>255</v>
+        <v>240</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1" t="s">
-        <v>256</v>
+        <v>241</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>257</v>
+        <v>242</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>205</v>
+        <v>124</v>
       </c>
       <c r="D13" s="1">
         <v>0</v>
       </c>
       <c r="E13" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F13" s="1"/>
       <c r="G13" s="1">
-        <v>6</v>
-      </c>
-      <c r="H13" s="40" t="s">
-        <v>258</v>
+        <v>2</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>259</v>
+        <v>244</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>260</v>
+        <v>245</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>261</v>
+        <v>207</v>
       </c>
       <c r="D14" s="1">
         <v>0</v>
@@ -8879,45 +8836,45 @@
       </c>
       <c r="F14" s="1"/>
       <c r="G14" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>262</v>
+        <v>246</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1" t="s">
-        <v>263</v>
+        <v>247</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>264</v>
+        <v>248</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>265</v>
+        <v>249</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
       </c>
       <c r="E15" s="1">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1" t="s">
-        <v>267</v>
+        <v>251</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>268</v>
+        <v>252</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>269</v>
+        <v>120</v>
       </c>
       <c r="D16" s="1">
         <v>0</v>
@@ -8927,156 +8884,163 @@
       </c>
       <c r="F16" s="1"/>
       <c r="G16" s="1">
+        <v>5</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="D17" s="1">
+        <v>0</v>
+      </c>
+      <c r="E17" s="1">
+        <v>5</v>
+      </c>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1">
+        <v>6</v>
+      </c>
+      <c r="H17" s="40" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="D18" s="1">
+        <v>0</v>
+      </c>
+      <c r="E18" s="1">
+        <v>-1</v>
+      </c>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1">
+        <v>7</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="D19" s="1">
+        <v>0</v>
+      </c>
+      <c r="E19" s="1">
+        <v>1</v>
+      </c>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1">
+        <v>8</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="D20" s="1">
+        <v>0</v>
+      </c>
+      <c r="E20" s="1">
+        <v>1</v>
+      </c>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1">
         <v>9</v>
       </c>
-      <c r="H16" s="1" t="s">
+      <c r="H20" s="1" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="21" s="44" customFormat="1" spans="1:9">
+      <c r="A21" s="56" t="s">
+        <v>269</v>
+      </c>
+      <c r="B21" s="57" t="s">
         <v>270</v>
       </c>
-    </row>
-    <row r="17" spans="1:8">
-      <c r="A17" s="46" t="s">
-        <v>141</v>
-      </c>
-      <c r="B17" s="47" t="s">
+      <c r="C21" s="57" t="s">
+        <v>270</v>
+      </c>
+      <c r="D21" s="57">
+        <v>0</v>
+      </c>
+      <c r="E21" s="57"/>
+      <c r="F21" s="57"/>
+      <c r="G21" s="57"/>
+      <c r="H21" s="57" t="s">
         <v>271</v>
       </c>
-      <c r="C17" s="47" t="s">
-        <v>271</v>
-      </c>
-      <c r="D17" s="1">
-        <v>0</v>
-      </c>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="47" t="s">
+      <c r="I21" s="44" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="18" spans="1:9">
-      <c r="A18" s="48" t="s">
-        <v>145</v>
-      </c>
-      <c r="B18" s="49" t="s">
-        <v>146</v>
-      </c>
-      <c r="C18" s="49" t="s">
-        <v>146</v>
-      </c>
-      <c r="D18" s="1">
-        <v>0</v>
-      </c>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="49" t="s">
+    <row r="22" s="44" customFormat="1" spans="1:9">
+      <c r="A22" s="56" t="s">
         <v>273</v>
       </c>
-      <c r="I18" t="s">
+      <c r="B22" s="57" t="s">
         <v>274</v>
       </c>
-    </row>
-    <row r="19" spans="1:9">
-      <c r="A19" s="48" t="s">
-        <v>148</v>
-      </c>
-      <c r="B19" s="49" t="s">
-        <v>149</v>
-      </c>
-      <c r="C19" s="49" t="s">
-        <v>149</v>
-      </c>
-      <c r="D19" s="1">
-        <v>0</v>
-      </c>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="49" t="s">
+      <c r="C22" s="57" t="s">
+        <v>274</v>
+      </c>
+      <c r="D22" s="57">
+        <v>0</v>
+      </c>
+      <c r="E22" s="57"/>
+      <c r="F22" s="57"/>
+      <c r="G22" s="57"/>
+      <c r="H22" s="57" t="s">
         <v>275</v>
       </c>
-      <c r="I19" t="s">
+      <c r="I22" s="44" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="20" s="42" customFormat="1" spans="1:9">
-      <c r="A20" s="50" t="s">
+    <row r="23" spans="1:9">
+      <c r="A23" s="58" t="s">
+        <v>151</v>
+      </c>
+      <c r="B23" s="59" t="s">
         <v>152</v>
       </c>
-      <c r="B20" s="51" t="s">
-        <v>153</v>
-      </c>
-      <c r="C20" s="51" t="s">
-        <v>153</v>
-      </c>
-      <c r="D20" s="51">
-        <v>0</v>
-      </c>
-      <c r="E20" s="51"/>
-      <c r="F20" s="51"/>
-      <c r="G20" s="51"/>
-      <c r="H20" s="51" t="s">
-        <v>277</v>
-      </c>
-      <c r="I20" s="42" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="21" s="42" customFormat="1" spans="1:9">
-      <c r="A21" s="50" t="s">
-        <v>155</v>
-      </c>
-      <c r="B21" s="51" t="s">
-        <v>156</v>
-      </c>
-      <c r="C21" s="51" t="s">
-        <v>156</v>
-      </c>
-      <c r="D21" s="51">
-        <v>0</v>
-      </c>
-      <c r="E21" s="51"/>
-      <c r="F21" s="51"/>
-      <c r="G21" s="51"/>
-      <c r="H21" s="51" t="s">
-        <v>279</v>
-      </c>
-      <c r="I21" s="42" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="22" s="42" customFormat="1" spans="1:9">
-      <c r="A22" s="50" t="s">
-        <v>157</v>
-      </c>
-      <c r="B22" s="51" t="s">
-        <v>158</v>
-      </c>
-      <c r="C22" s="51" t="s">
-        <v>158</v>
-      </c>
-      <c r="D22" s="51">
-        <v>0</v>
-      </c>
-      <c r="E22" s="51"/>
-      <c r="F22" s="51"/>
-      <c r="G22" s="51"/>
-      <c r="H22" s="51" t="s">
-        <v>280</v>
-      </c>
-      <c r="I22" s="42" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9">
-      <c r="A23" s="52" t="s">
-        <v>159</v>
-      </c>
-      <c r="B23" s="53" t="s">
-        <v>160</v>
-      </c>
-      <c r="C23" s="53" t="s">
-        <v>160</v>
+      <c r="C23" s="59" t="s">
+        <v>152</v>
       </c>
       <c r="D23" s="1">
         <v>0</v>
@@ -9084,22 +9048,22 @@
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
-      <c r="H23" s="53" t="s">
-        <v>282</v>
+      <c r="H23" s="59" t="s">
+        <v>277</v>
       </c>
       <c r="I23" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="52" t="s">
-        <v>162</v>
-      </c>
-      <c r="B24" s="53" t="s">
-        <v>163</v>
-      </c>
-      <c r="C24" s="53" t="s">
-        <v>163</v>
+      <c r="A24" s="58" t="s">
+        <v>154</v>
+      </c>
+      <c r="B24" s="59" t="s">
+        <v>155</v>
+      </c>
+      <c r="C24" s="59" t="s">
+        <v>155</v>
       </c>
       <c r="D24" s="1">
         <v>0</v>
@@ -9108,21 +9072,21 @@
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
       <c r="H24" s="1" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="I24" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="52" t="s">
-        <v>165</v>
-      </c>
-      <c r="B25" s="53" t="s">
-        <v>166</v>
-      </c>
-      <c r="C25" s="53" t="s">
-        <v>166</v>
+      <c r="A25" s="58" t="s">
+        <v>157</v>
+      </c>
+      <c r="B25" s="59" t="s">
+        <v>158</v>
+      </c>
+      <c r="C25" s="59" t="s">
+        <v>158</v>
       </c>
       <c r="D25" s="1">
         <v>0</v>
@@ -9130,22 +9094,22 @@
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
-      <c r="H25" s="53" t="s">
-        <v>167</v>
+      <c r="H25" s="59" t="s">
+        <v>159</v>
       </c>
       <c r="I25" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" s="48" t="s">
-        <v>168</v>
-      </c>
-      <c r="B26" s="49" t="s">
-        <v>169</v>
-      </c>
-      <c r="C26" s="49" t="s">
-        <v>169</v>
+      <c r="A26" s="60" t="s">
+        <v>160</v>
+      </c>
+      <c r="B26" s="61" t="s">
+        <v>161</v>
+      </c>
+      <c r="C26" s="61" t="s">
+        <v>161</v>
       </c>
       <c r="D26" s="1">
         <v>0</v>
@@ -9153,22 +9117,22 @@
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
-      <c r="H26" s="49" t="s">
-        <v>285</v>
+      <c r="H26" s="61" t="s">
+        <v>280</v>
       </c>
       <c r="I26" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="48" t="s">
-        <v>171</v>
-      </c>
-      <c r="B27" s="49" t="s">
-        <v>172</v>
-      </c>
-      <c r="C27" s="49" t="s">
-        <v>172</v>
+      <c r="A27" s="60" t="s">
+        <v>163</v>
+      </c>
+      <c r="B27" s="61" t="s">
+        <v>164</v>
+      </c>
+      <c r="C27" s="61" t="s">
+        <v>164</v>
       </c>
       <c r="D27" s="1">
         <v>0</v>
@@ -9176,22 +9140,22 @@
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
-      <c r="H27" s="49" t="s">
-        <v>286</v>
+      <c r="H27" s="61" t="s">
+        <v>281</v>
       </c>
       <c r="I27" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
     </row>
     <row r="28" spans="1:8">
-      <c r="A28" s="48" t="s">
-        <v>174</v>
-      </c>
-      <c r="B28" s="49" t="s">
-        <v>175</v>
-      </c>
-      <c r="C28" s="49" t="s">
-        <v>175</v>
+      <c r="A28" s="60" t="s">
+        <v>166</v>
+      </c>
+      <c r="B28" s="61" t="s">
+        <v>167</v>
+      </c>
+      <c r="C28" s="61" t="s">
+        <v>167</v>
       </c>
       <c r="D28" s="1">
         <v>0</v>
@@ -9199,19 +9163,19 @@
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
-      <c r="H28" s="47" t="s">
-        <v>176</v>
+      <c r="H28" s="62" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="29" spans="1:9">
-      <c r="A29" s="48" t="s">
-        <v>177</v>
-      </c>
-      <c r="B29" s="49" t="s">
-        <v>178</v>
-      </c>
-      <c r="C29" s="49" t="s">
-        <v>178</v>
+      <c r="A29" s="60" t="s">
+        <v>169</v>
+      </c>
+      <c r="B29" s="61" t="s">
+        <v>170</v>
+      </c>
+      <c r="C29" s="61" t="s">
+        <v>170</v>
       </c>
       <c r="D29" s="1">
         <v>0</v>
@@ -9219,22 +9183,22 @@
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
-      <c r="H29" s="49" t="s">
-        <v>288</v>
+      <c r="H29" s="61" t="s">
+        <v>283</v>
       </c>
       <c r="I29" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
     </row>
     <row r="30" spans="1:9">
-      <c r="A30" s="48" t="s">
-        <v>180</v>
-      </c>
-      <c r="B30" s="49" t="s">
-        <v>181</v>
-      </c>
-      <c r="C30" s="49" t="s">
-        <v>181</v>
+      <c r="A30" s="60" t="s">
+        <v>172</v>
+      </c>
+      <c r="B30" s="61" t="s">
+        <v>173</v>
+      </c>
+      <c r="C30" s="61" t="s">
+        <v>173</v>
       </c>
       <c r="D30" s="1">
         <v>0</v>
@@ -9242,22 +9206,22 @@
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
-      <c r="H30" s="53" t="s">
-        <v>167</v>
+      <c r="H30" s="59" t="s">
+        <v>159</v>
       </c>
       <c r="I30" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
     </row>
     <row r="31" spans="1:8">
-      <c r="A31" s="46" t="s">
-        <v>182</v>
-      </c>
-      <c r="B31" s="47" t="s">
-        <v>183</v>
-      </c>
-      <c r="C31" s="47" t="s">
-        <v>183</v>
+      <c r="A31" s="63" t="s">
+        <v>174</v>
+      </c>
+      <c r="B31" s="62" t="s">
+        <v>175</v>
+      </c>
+      <c r="C31" s="62" t="s">
+        <v>175</v>
       </c>
       <c r="D31" s="1">
         <v>0</v>
@@ -9265,52 +9229,8 @@
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
-      <c r="H31" s="47" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8">
-      <c r="A32" s="40" t="s">
-        <v>139</v>
-      </c>
-      <c r="B32" s="1"/>
-      <c r="C32" s="40"/>
-      <c r="D32" s="1">
-        <v>1</v>
-      </c>
-      <c r="E32" s="1">
-        <v>0</v>
-      </c>
-      <c r="F32" s="1">
-        <v>1</v>
-      </c>
-      <c r="G32" s="40">
-        <v>5</v>
-      </c>
-      <c r="H32" s="1" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8">
-      <c r="A33" s="40" t="s">
-        <v>150</v>
-      </c>
-      <c r="B33" s="1"/>
-      <c r="C33" s="40"/>
-      <c r="D33" s="1">
-        <v>1</v>
-      </c>
-      <c r="E33" s="1">
-        <v>0</v>
-      </c>
-      <c r="F33" s="1">
-        <v>1</v>
-      </c>
-      <c r="G33" s="40">
-        <v>8</v>
-      </c>
-      <c r="H33" s="1" t="s">
-        <v>236</v>
+      <c r="H31" s="62" t="s">
+        <v>176</v>
       </c>
     </row>
   </sheetData>
@@ -9335,22 +9255,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="35" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="C1" s="35" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="D1" s="35" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="E1" s="35" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="F1" s="35" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="G1" s="35" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -9358,22 +9278,22 @@
         <v>16</v>
       </c>
       <c r="B2" s="37" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="C2" s="37" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="D2" s="37" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="E2" s="37" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="F2" s="37" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="G2" s="38" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -9393,7 +9313,7 @@
         <v>107</v>
       </c>
       <c r="F3" s="37" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="G3" s="37" t="s">
         <v>9</v>
@@ -9401,10 +9321,10 @@
     </row>
     <row r="4" ht="14.25" spans="1:7">
       <c r="A4" s="39" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="B4" s="40" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="C4" s="39">
         <v>100</v>
@@ -9419,15 +9339,15 @@
         <v>1</v>
       </c>
       <c r="G4" s="39" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
     </row>
     <row r="5" ht="14.25" spans="1:7">
       <c r="A5" s="39" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="B5" s="40" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="C5" s="39">
         <v>100</v>
@@ -9442,15 +9362,15 @@
         <v>1</v>
       </c>
       <c r="G5" s="39" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
     </row>
     <row r="6" ht="14.25" spans="1:7">
       <c r="A6" s="39" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B6" s="40" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="C6" s="39">
         <v>3</v>
@@ -9465,15 +9385,15 @@
         <v>1</v>
       </c>
       <c r="G6" s="39" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
     </row>
     <row r="7" ht="14.25" spans="1:7">
       <c r="A7" s="39" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="B7" s="40" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="C7" s="39">
         <v>3</v>
@@ -9488,12 +9408,12 @@
         <v>1</v>
       </c>
       <c r="G7" s="39" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
     </row>
     <row r="8" ht="14.25" spans="1:7">
       <c r="A8" s="39" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="B8" s="40" t="s">
         <v>19</v>
@@ -9511,15 +9431,15 @@
         <v>1</v>
       </c>
       <c r="G8" s="39" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
     </row>
     <row r="9" ht="14.25" spans="1:7">
       <c r="A9" s="39" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="B9" s="40" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="C9" s="39">
         <v>0</v>
@@ -9534,15 +9454,15 @@
         <v>1</v>
       </c>
       <c r="G9" s="39" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
     </row>
     <row r="10" ht="14.25" spans="1:7">
       <c r="A10" s="39" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="B10" s="40" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="C10" s="39">
         <v>0</v>
@@ -9557,15 +9477,15 @@
         <v>1</v>
       </c>
       <c r="G10" s="39" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11" ht="14.25" spans="1:7">
       <c r="A11" s="39" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="B11" s="40" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="C11" s="39">
         <v>0</v>
@@ -9580,15 +9500,15 @@
         <v>1</v>
       </c>
       <c r="G11" s="39" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
     </row>
     <row r="12" ht="14.25" spans="1:7">
       <c r="A12" s="39" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="B12" s="40" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="C12" s="39">
         <v>0</v>
@@ -9603,15 +9523,15 @@
         <v>1</v>
       </c>
       <c r="G12" s="39" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
     </row>
     <row r="13" ht="14.25" spans="1:7">
       <c r="A13" s="39" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="B13" s="40" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="C13" s="39">
         <v>0</v>
@@ -9626,15 +9546,15 @@
         <v>1</v>
       </c>
       <c r="G13" s="39" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
     </row>
     <row r="14" ht="14.25" spans="1:7">
       <c r="A14" s="39" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="B14" s="40" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C14" s="39">
         <v>0</v>
@@ -9649,7 +9569,7 @@
         <v>1</v>
       </c>
       <c r="G14" s="39" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
     </row>
   </sheetData>

--- a/xlsdir/配置-总表.xlsx
+++ b/xlsdir/配置-总表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="673" activeTab="5"/>
+    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="673"/>
   </bookViews>
   <sheets>
     <sheet name="combat|战斗" sheetId="31" r:id="rId1"/>
@@ -281,7 +281,7 @@
     <t>造成6点伤害</t>
   </si>
   <si>
-    <t>res://asserts/textures/cards/card_icons/card_strike.png</t>
+    <t>res://assets/textures/cards/card_icons/card_strike.png</t>
   </si>
   <si>
     <t>defense</t>
@@ -293,7 +293,7 @@
     <t>获得5点[color=yellow]格挡[/color]</t>
   </si>
   <si>
-    <t>res://asserts/textures/cards/card_icons/card_defense.png</t>
+    <t>res://assets/textures/cards/card_icons/card_defense.png</t>
   </si>
   <si>
     <t>items</t>
@@ -314,7 +314,7 @@
     <t>造成8点伤害，给与2层[color=yellow]易伤[/color]</t>
   </si>
   <si>
-    <t>res://asserts/textures/cards/card_icons/card_trounce.png</t>
+    <t>res://assets/textures/cards/card_icons/card_trounce.png</t>
   </si>
   <si>
     <t>trounce_01*trounce_02</t>
@@ -380,7 +380,7 @@
     <t>敌人打算进行攻击。</t>
   </si>
   <si>
-    <t>res://asserts/textures/widgets/Buffs/poison_dagger.png</t>
+    <t>res://assets/textures/widgets/Buffs/poison_dagger.png</t>
   </si>
   <si>
     <t>MULTI_ATTACK</t>
@@ -392,7 +392,7 @@
     <t>敌人计划多次攻击。</t>
   </si>
   <si>
-    <t>res://asserts/textures/widgets/Buffs/thorn_vine_spell.png</t>
+    <t>res://assets/textures/widgets/Buffs/thorn_vine_spell.png</t>
   </si>
   <si>
     <t>DEFEND</t>
@@ -401,7 +401,7 @@
     <t>敌人将增加防御力</t>
   </si>
   <si>
-    <t>res://asserts/textures/widgets/Buffs/healing_spell.png</t>
+    <t>res://assets/textures/widgets/Buffs/healing_spell.png</t>
   </si>
   <si>
     <t>BUFF</t>
@@ -413,7 +413,7 @@
     <t>敌人将提升某项能力，如攻击力、防御力或特殊能力。</t>
   </si>
   <si>
-    <t>res://asserts/textures/widgets/Buffs/on_fire_(burning).png</t>
+    <t>res://assets/textures/widgets/Buffs/on_fire_(burning).png</t>
   </si>
   <si>
     <t>DEBUFF</t>
@@ -425,7 +425,7 @@
     <t>敌人计划施放会削弱玩家能力的效果，如减少玩家的攻击力或防御力。</t>
   </si>
   <si>
-    <t>res://asserts/textures/widgets/Buffs/disarmed.png</t>
+    <t>res://assets/textures/widgets/Buffs/disarmed.png</t>
   </si>
   <si>
     <t>HEAL</t>
@@ -437,7 +437,7 @@
     <t>敌人会恢复一定量的生命值。</t>
   </si>
   <si>
-    <t>res://asserts/textures/widgets/Buffs/lucky_boost.png</t>
+    <t>res://assets/textures/widgets/Buffs/lucky_boost.png</t>
   </si>
   <si>
     <t>STRATEGY</t>
@@ -449,7 +449,7 @@
     <t>敌人将采取某种特殊行动，如召唤援助、准备强力攻击或其他战术动作。</t>
   </si>
   <si>
-    <t>res://asserts/textures/widgets/Buffs/confused.png</t>
+    <t>res://assets/textures/widgets/Buffs/confused.png</t>
   </si>
   <si>
     <t>ESCAPE</t>
@@ -461,7 +461,7 @@
     <t>在某些战斗中，敌人可能会试图逃跑，尤其是在遭遇战中</t>
   </si>
   <si>
-    <t>res://asserts/textures/widgets/Buffs/swiftness.png</t>
+    <t>res://assets/textures/widgets/Buffs/swiftness.png</t>
   </si>
   <si>
     <t>attack_5</t>
@@ -479,7 +479,7 @@
     <t>敌人打算释放一个正面效果的法术</t>
   </si>
   <si>
-    <t>res://asserts/textures/widgets/Buffs/ghost_form_(physical_damage_immunity).png</t>
+    <t>res://assets/textures/widgets/Buffs/ghost_form_(physical_damage_immunity).png</t>
   </si>
   <si>
     <t>attack_8</t>
@@ -497,7 +497,7 @@
     <t>敌人打算释放一个负面效果的法术</t>
   </si>
   <si>
-    <t>res://asserts/textures/widgets/Buffs/poisoned.png</t>
+    <t>res://assets/textures/widgets/Buffs/poisoned.png</t>
   </si>
   <si>
     <t>destruction_ray</t>
@@ -664,7 +664,7 @@
     <t>使目标受到的攻击伤害增加</t>
   </si>
   <si>
-    <t>res://asserts/textures/widgets/Buffs/defense_down.png</t>
+    <t>res://assets/textures/widgets/Buffs/defense_down.png</t>
   </si>
   <si>
     <t>VULNERABLE</t>
@@ -2042,7 +2042,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="42">
+  <fills count="40">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2063,19 +2063,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="3" tint="0.6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="2" tint="-0.1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2764,7 +2752,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="27" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="27" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2788,16 +2776,16 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="30" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="30" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="32" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="30" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="30" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="32" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="33" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -2806,89 +2794,89 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="34" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3021,9 +3009,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -3033,112 +3018,103 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -3883,7 +3859,7 @@
       <c r="U4" s="9"/>
       <c r="V4" s="9"/>
       <c r="W4" s="23"/>
-      <c r="X4" s="87" t="s">
+      <c r="X4" s="83" t="s">
         <v>368</v>
       </c>
       <c r="Y4" s="9" t="s">
@@ -6892,7 +6868,7 @@
       <c r="C1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="86" t="s">
+      <c r="D1" s="82" t="s">
         <v>14</v>
       </c>
       <c r="E1" s="5" t="s">
@@ -6900,16 +6876,16 @@
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="45" t="s">
+      <c r="B2" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="45" t="s">
+      <c r="C2" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="86" t="s">
+      <c r="D2" s="82" t="s">
         <v>19</v>
       </c>
       <c r="E2" s="5" t="s">
@@ -6926,7 +6902,7 @@
       <c r="C3" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="86" t="s">
+      <c r="D3" s="82" t="s">
         <v>21</v>
       </c>
       <c r="E3" s="5" t="s">
@@ -6943,7 +6919,7 @@
       <c r="C4" s="1">
         <v>80</v>
       </c>
-      <c r="D4" s="47">
+      <c r="D4" s="46">
         <v>0</v>
       </c>
       <c r="E4" s="1" t="s">
@@ -6960,7 +6936,7 @@
       <c r="C5" s="1">
         <v>30</v>
       </c>
-      <c r="D5" s="47">
+      <c r="D5" s="46">
         <v>10</v>
       </c>
       <c r="E5" s="1" t="s">
@@ -6977,7 +6953,7 @@
       <c r="C6" s="1">
         <v>50</v>
       </c>
-      <c r="D6" s="47">
+      <c r="D6" s="46">
         <v>10</v>
       </c>
       <c r="E6" s="1" t="s">
@@ -6994,7 +6970,7 @@
       <c r="C7" s="1">
         <v>50</v>
       </c>
-      <c r="D7" s="47">
+      <c r="D7" s="46">
         <v>10</v>
       </c>
       <c r="E7" s="1" t="s">
@@ -7011,7 +6987,7 @@
       <c r="C8" s="1">
         <v>50</v>
       </c>
-      <c r="D8" s="47">
+      <c r="D8" s="46">
         <v>10</v>
       </c>
       <c r="E8" s="1" t="s">
@@ -7028,7 +7004,7 @@
       <c r="C9" s="1">
         <v>50</v>
       </c>
-      <c r="D9" s="47">
+      <c r="D9" s="46">
         <v>10</v>
       </c>
       <c r="E9" s="1" t="s">
@@ -7047,9 +7023,10 @@
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultColWidth="8.86666666666667" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="8.33333333333333" style="85" customWidth="1"/>
+    <col min="1" max="1" width="8.33333333333333" style="81" customWidth="1"/>
     <col min="2" max="2" width="11.8666666666667" customWidth="1"/>
-    <col min="3" max="3" width="31.4666666666667" customWidth="1"/>
+    <col min="3" max="3" width="31.5" customWidth="1"/>
+    <col min="5" max="5" width="34.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -7065,20 +7042,20 @@
       <c r="D1" s="5"/>
       <c r="E1" s="5"/>
     </row>
-    <row r="2" s="84" customFormat="1" spans="1:5">
-      <c r="A2" s="45" t="s">
+    <row r="2" s="80" customFormat="1" spans="1:5">
+      <c r="A2" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="45" t="s">
+      <c r="B2" s="44" t="s">
         <v>39</v>
       </c>
-      <c r="C2" s="45" t="s">
+      <c r="C2" s="44" t="s">
         <v>40</v>
       </c>
-      <c r="D2" s="45" t="s">
+      <c r="D2" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="E2" s="45" t="s">
+      <c r="E2" s="44" t="s">
         <v>42</v>
       </c>
     </row>
@@ -7307,31 +7284,31 @@
       </c>
     </row>
     <row r="2" ht="54" spans="1:10">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="45" t="s">
+      <c r="B2" s="44" t="s">
         <v>65</v>
       </c>
-      <c r="C2" s="45" t="s">
+      <c r="C2" s="44" t="s">
         <v>66</v>
       </c>
-      <c r="D2" s="45" t="s">
+      <c r="D2" s="44" t="s">
         <v>67</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="F2" s="45" t="s">
+      <c r="F2" s="44" t="s">
         <v>69</v>
       </c>
-      <c r="G2" s="46" t="s">
+      <c r="G2" s="45" t="s">
         <v>70</v>
       </c>
-      <c r="H2" s="45" t="s">
+      <c r="H2" s="44" t="s">
         <v>71</v>
       </c>
-      <c r="I2" s="68" t="s">
+      <c r="I2" s="66" t="s">
         <v>72</v>
       </c>
       <c r="J2" s="5" t="s">
@@ -7477,8 +7454,8 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="21.25" customWidth="1"/>
-    <col min="2" max="2" width="9.06666666666667" style="72"/>
-    <col min="4" max="7" width="9.06666666666667" style="72"/>
+    <col min="2" max="2" width="9.06666666666667" style="69"/>
+    <col min="4" max="7" width="9.06666666666667" style="69"/>
     <col min="8" max="8" width="62" customWidth="1"/>
     <col min="9" max="9" width="67.125" customWidth="1"/>
   </cols>
@@ -7487,34 +7464,34 @@
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="73" t="s">
+      <c r="B1" s="70" t="s">
         <v>92</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="73" t="s">
+      <c r="D1" s="70" t="s">
         <v>93</v>
       </c>
-      <c r="E1" s="73" t="s">
+      <c r="E1" s="70" t="s">
         <v>94</v>
       </c>
-      <c r="F1" s="73" t="s">
+      <c r="F1" s="70" t="s">
         <v>95</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="H1" s="65" t="s">
+      <c r="H1" s="63" t="s">
         <v>96</v>
       </c>
-      <c r="I1" s="65" t="s">
+      <c r="I1" s="63" t="s">
         <v>60</v>
       </c>
-      <c r="J1" s="65" t="s">
+      <c r="J1" s="63" t="s">
         <v>97</v>
       </c>
-      <c r="K1" s="65" t="s">
+      <c r="K1" s="63" t="s">
         <v>63</v>
       </c>
     </row>
@@ -7522,34 +7499,34 @@
       <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="73" t="s">
+      <c r="B2" s="70" t="s">
         <v>98</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="D2" s="73" t="s">
+      <c r="D2" s="70" t="s">
         <v>100</v>
       </c>
-      <c r="E2" s="73" t="s">
+      <c r="E2" s="70" t="s">
         <v>101</v>
       </c>
-      <c r="F2" s="73" t="s">
+      <c r="F2" s="70" t="s">
         <v>102</v>
       </c>
-      <c r="G2" s="45" t="s">
+      <c r="G2" s="44" t="s">
         <v>71</v>
       </c>
-      <c r="H2" s="65" t="s">
+      <c r="H2" s="63" t="s">
         <v>103</v>
       </c>
-      <c r="I2" s="65" t="s">
+      <c r="I2" s="63" t="s">
         <v>104</v>
       </c>
-      <c r="J2" s="65" t="s">
+      <c r="J2" s="63" t="s">
         <v>105</v>
       </c>
-      <c r="K2" s="65" t="s">
+      <c r="K2" s="63" t="s">
         <v>106</v>
       </c>
     </row>
@@ -7557,34 +7534,34 @@
       <c r="A3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="73" t="s">
+      <c r="B3" s="70" t="s">
         <v>9</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="73" t="s">
+      <c r="D3" s="70" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="73" t="s">
+      <c r="E3" s="70" t="s">
         <v>107</v>
       </c>
-      <c r="F3" s="73" t="s">
+      <c r="F3" s="70" t="s">
         <v>21</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="65" t="s">
+      <c r="H3" s="63" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="65" t="s">
+      <c r="I3" s="63" t="s">
         <v>74</v>
       </c>
-      <c r="J3" s="65" t="s">
+      <c r="J3" s="63" t="s">
         <v>21</v>
       </c>
-      <c r="K3" s="65" t="s">
+      <c r="K3" s="63" t="s">
         <v>43</v>
       </c>
     </row>
@@ -7592,16 +7569,16 @@
       <c r="A4" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="B4" s="74"/>
+      <c r="B4" s="71"/>
       <c r="C4" s="40" t="s">
         <v>109</v>
       </c>
-      <c r="D4" s="74">
-        <v>1</v>
-      </c>
-      <c r="E4" s="74"/>
-      <c r="F4" s="74"/>
-      <c r="G4" s="74"/>
+      <c r="D4" s="71">
+        <v>1</v>
+      </c>
+      <c r="E4" s="71"/>
+      <c r="F4" s="71"/>
+      <c r="G4" s="71"/>
       <c r="H4" s="40" t="s">
         <v>110</v>
       </c>
@@ -7617,16 +7594,16 @@
       <c r="A5" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B5" s="74"/>
+      <c r="B5" s="71"/>
       <c r="C5" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="D5" s="74">
+      <c r="D5" s="71">
         <v>2</v>
       </c>
-      <c r="E5" s="74"/>
-      <c r="F5" s="74"/>
-      <c r="G5" s="74"/>
+      <c r="E5" s="71"/>
+      <c r="F5" s="71"/>
+      <c r="G5" s="71"/>
       <c r="H5" s="40" t="s">
         <v>114</v>
       </c>
@@ -7642,16 +7619,16 @@
       <c r="A6" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="B6" s="74"/>
+      <c r="B6" s="71"/>
       <c r="C6" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D6" s="74">
+      <c r="D6" s="71">
         <v>3</v>
       </c>
-      <c r="E6" s="74"/>
-      <c r="F6" s="74"/>
-      <c r="G6" s="74"/>
+      <c r="E6" s="71"/>
+      <c r="F6" s="71"/>
+      <c r="G6" s="71"/>
       <c r="H6" s="40" t="s">
         <v>117</v>
       </c>
@@ -7667,16 +7644,16 @@
       <c r="A7" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="B7" s="74"/>
+      <c r="B7" s="71"/>
       <c r="C7" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="D7" s="74">
+      <c r="D7" s="71">
         <v>4</v>
       </c>
-      <c r="E7" s="74"/>
-      <c r="F7" s="74"/>
-      <c r="G7" s="74"/>
+      <c r="E7" s="71"/>
+      <c r="F7" s="71"/>
+      <c r="G7" s="71"/>
       <c r="H7" s="1" t="s">
         <v>121</v>
       </c>
@@ -7692,16 +7669,16 @@
       <c r="A8" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B8" s="74"/>
+      <c r="B8" s="71"/>
       <c r="C8" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="D8" s="74">
+      <c r="D8" s="71">
         <v>5</v>
       </c>
-      <c r="E8" s="74"/>
-      <c r="F8" s="74"/>
-      <c r="G8" s="74"/>
+      <c r="E8" s="71"/>
+      <c r="F8" s="71"/>
+      <c r="G8" s="71"/>
       <c r="H8" s="1" t="s">
         <v>125</v>
       </c>
@@ -7717,16 +7694,16 @@
       <c r="A9" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B9" s="74"/>
+      <c r="B9" s="71"/>
       <c r="C9" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D9" s="74">
+      <c r="D9" s="71">
         <v>6</v>
       </c>
-      <c r="E9" s="74"/>
-      <c r="F9" s="74"/>
-      <c r="G9" s="74"/>
+      <c r="E9" s="71"/>
+      <c r="F9" s="71"/>
+      <c r="G9" s="71"/>
       <c r="H9" s="1" t="s">
         <v>129</v>
       </c>
@@ -7742,16 +7719,16 @@
       <c r="A10" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="B10" s="74"/>
+      <c r="B10" s="71"/>
       <c r="C10" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="D10" s="74">
+      <c r="D10" s="71">
         <v>7</v>
       </c>
-      <c r="E10" s="74"/>
-      <c r="F10" s="74"/>
-      <c r="G10" s="74"/>
+      <c r="E10" s="71"/>
+      <c r="F10" s="71"/>
+      <c r="G10" s="71"/>
       <c r="H10" s="1" t="s">
         <v>133</v>
       </c>
@@ -7767,16 +7744,16 @@
       <c r="A11" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B11" s="74"/>
+      <c r="B11" s="71"/>
       <c r="C11" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="D11" s="74">
+      <c r="D11" s="71">
         <v>8</v>
       </c>
-      <c r="E11" s="74"/>
-      <c r="F11" s="74"/>
-      <c r="G11" s="74"/>
+      <c r="E11" s="71"/>
+      <c r="F11" s="71"/>
+      <c r="G11" s="71"/>
       <c r="H11" s="1" t="s">
         <v>137</v>
       </c>
@@ -7788,406 +7765,406 @@
       </c>
       <c r="K11" s="1"/>
     </row>
-    <row r="12" s="69" customFormat="1" spans="1:11">
-      <c r="A12" s="49" t="s">
+    <row r="12" s="67" customFormat="1" spans="1:11">
+      <c r="A12" s="48" t="s">
         <v>139</v>
       </c>
-      <c r="B12" s="51" t="s">
+      <c r="B12" s="50" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="48" t="s">
+      <c r="C12" s="47" t="s">
         <v>109</v>
       </c>
-      <c r="D12" s="75">
-        <v>1</v>
-      </c>
-      <c r="E12" s="75">
-        <v>1</v>
-      </c>
-      <c r="F12" s="75">
-        <v>0</v>
-      </c>
-      <c r="G12" s="75" t="s">
+      <c r="D12" s="72">
+        <v>1</v>
+      </c>
+      <c r="E12" s="72">
+        <v>1</v>
+      </c>
+      <c r="F12" s="72">
+        <v>0</v>
+      </c>
+      <c r="G12" s="72" t="s">
         <v>14</v>
       </c>
-      <c r="H12" s="48" t="s">
+      <c r="H12" s="47" t="s">
         <v>140</v>
       </c>
-      <c r="I12" s="49" t="s">
+      <c r="I12" s="48" t="s">
         <v>111</v>
       </c>
-      <c r="J12" s="49">
+      <c r="J12" s="48">
         <v>5</v>
       </c>
-      <c r="K12" s="49" t="s">
+      <c r="K12" s="48" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="13" s="69" customFormat="1" spans="1:11">
-      <c r="A13" s="50" t="s">
+    <row r="13" s="67" customFormat="1" spans="1:11">
+      <c r="A13" s="49" t="s">
         <v>141</v>
       </c>
-      <c r="B13" s="51" t="s">
+      <c r="B13" s="50" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="51" t="s">
+      <c r="C13" s="50" t="s">
         <v>142</v>
       </c>
-      <c r="D13" s="76">
+      <c r="D13" s="73">
         <v>3</v>
       </c>
-      <c r="E13" s="76">
+      <c r="E13" s="73">
         <v>5</v>
       </c>
-      <c r="F13" s="76">
+      <c r="F13" s="73">
         <v>2</v>
       </c>
-      <c r="G13" s="75" t="s">
+      <c r="G13" s="72" t="s">
         <v>14</v>
       </c>
-      <c r="H13" s="51" t="s">
+      <c r="H13" s="50" t="s">
         <v>143</v>
       </c>
-      <c r="I13" s="51" t="s">
+      <c r="I13" s="50" t="s">
         <v>144</v>
       </c>
-      <c r="J13" s="51">
-        <v>0</v>
-      </c>
-      <c r="K13" s="50" t="s">
+      <c r="J13" s="50">
+        <v>0</v>
+      </c>
+      <c r="K13" s="49" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="14" s="70" customFormat="1" spans="1:11">
-      <c r="A14" s="77" t="s">
+    <row r="14" s="68" customFormat="1" spans="1:11">
+      <c r="A14" s="74" t="s">
         <v>145</v>
       </c>
-      <c r="B14" s="77" t="s">
+      <c r="B14" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="78" t="s">
+      <c r="C14" s="75" t="s">
         <v>109</v>
       </c>
-      <c r="D14" s="79">
-        <v>1</v>
-      </c>
-      <c r="E14" s="79">
-        <v>1</v>
-      </c>
-      <c r="F14" s="79">
-        <v>0</v>
-      </c>
-      <c r="G14" s="79" t="s">
+      <c r="D14" s="76">
+        <v>1</v>
+      </c>
+      <c r="E14" s="76">
+        <v>1</v>
+      </c>
+      <c r="F14" s="76">
+        <v>0</v>
+      </c>
+      <c r="G14" s="76" t="s">
         <v>14</v>
       </c>
-      <c r="H14" s="78" t="s">
+      <c r="H14" s="75" t="s">
         <v>146</v>
       </c>
-      <c r="I14" s="77" t="s">
+      <c r="I14" s="74" t="s">
         <v>111</v>
       </c>
-      <c r="J14" s="77">
+      <c r="J14" s="74">
         <v>8</v>
       </c>
-      <c r="K14" s="77" t="s">
+      <c r="K14" s="74" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="15" s="70" customFormat="1" spans="1:11">
-      <c r="A15" s="80" t="s">
+    <row r="15" s="68" customFormat="1" spans="1:11">
+      <c r="A15" s="77" t="s">
         <v>147</v>
       </c>
-      <c r="B15" s="77" t="s">
+      <c r="B15" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="C15" s="77" t="s">
+      <c r="C15" s="74" t="s">
         <v>148</v>
       </c>
-      <c r="D15" s="79">
+      <c r="D15" s="76">
         <v>5</v>
       </c>
-      <c r="E15" s="79">
-        <v>1</v>
-      </c>
-      <c r="F15" s="79">
+      <c r="E15" s="76">
+        <v>1</v>
+      </c>
+      <c r="F15" s="76">
         <v>2</v>
       </c>
-      <c r="G15" s="75" t="s">
+      <c r="G15" s="72" t="s">
         <v>14</v>
       </c>
-      <c r="H15" s="77" t="s">
+      <c r="H15" s="74" t="s">
         <v>149</v>
       </c>
-      <c r="I15" s="77" t="s">
+      <c r="I15" s="74" t="s">
         <v>150</v>
       </c>
-      <c r="J15" s="77">
-        <v>0</v>
-      </c>
-      <c r="K15" s="80" t="s">
+      <c r="J15" s="74">
+        <v>0</v>
+      </c>
+      <c r="K15" s="77" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="16" s="71" customFormat="1" spans="1:11">
-      <c r="A16" s="58" t="s">
+    <row r="16" s="67" customFormat="1" spans="1:11">
+      <c r="A16" s="57" t="s">
         <v>151</v>
       </c>
-      <c r="B16" s="59" t="s">
+      <c r="B16" s="48" t="s">
         <v>28</v>
       </c>
-      <c r="C16" s="59" t="s">
+      <c r="C16" s="48" t="s">
         <v>152</v>
       </c>
-      <c r="D16" s="81"/>
-      <c r="E16" s="81">
-        <v>1</v>
-      </c>
-      <c r="F16" s="81">
-        <v>0</v>
-      </c>
-      <c r="G16" s="81"/>
-      <c r="H16" s="59" t="s">
+      <c r="D16" s="72"/>
+      <c r="E16" s="72">
+        <v>1</v>
+      </c>
+      <c r="F16" s="72">
+        <v>0</v>
+      </c>
+      <c r="G16" s="72"/>
+      <c r="H16" s="48" t="s">
         <v>153</v>
       </c>
-      <c r="I16" s="59" t="s">
+      <c r="I16" s="48" t="s">
         <v>138</v>
       </c>
-      <c r="J16" s="59">
-        <v>0</v>
-      </c>
-      <c r="K16" s="59"/>
-    </row>
-    <row r="17" s="71" customFormat="1" spans="1:11">
-      <c r="A17" s="58" t="s">
+      <c r="J16" s="48">
+        <v>0</v>
+      </c>
+      <c r="K16" s="48"/>
+    </row>
+    <row r="17" s="67" customFormat="1" spans="1:11">
+      <c r="A17" s="57" t="s">
         <v>154</v>
       </c>
-      <c r="B17" s="59" t="s">
+      <c r="B17" s="48" t="s">
         <v>28</v>
       </c>
-      <c r="C17" s="59" t="s">
+      <c r="C17" s="48" t="s">
         <v>155</v>
       </c>
-      <c r="D17" s="81"/>
-      <c r="E17" s="81">
-        <v>1</v>
-      </c>
-      <c r="F17" s="81">
-        <v>1</v>
-      </c>
-      <c r="G17" s="81"/>
-      <c r="H17" s="59" t="s">
+      <c r="D17" s="72"/>
+      <c r="E17" s="72">
+        <v>1</v>
+      </c>
+      <c r="F17" s="72">
+        <v>1</v>
+      </c>
+      <c r="G17" s="72"/>
+      <c r="H17" s="48" t="s">
         <v>156</v>
       </c>
-      <c r="I17" s="59" t="s">
+      <c r="I17" s="48" t="s">
         <v>138</v>
       </c>
-      <c r="J17" s="59">
-        <v>0</v>
-      </c>
-      <c r="K17" s="59"/>
-    </row>
-    <row r="18" s="71" customFormat="1" spans="1:11">
-      <c r="A18" s="58" t="s">
+      <c r="J17" s="48">
+        <v>0</v>
+      </c>
+      <c r="K17" s="48"/>
+    </row>
+    <row r="18" s="67" customFormat="1" spans="1:11">
+      <c r="A18" s="57" t="s">
         <v>157</v>
       </c>
-      <c r="B18" s="59" t="s">
+      <c r="B18" s="48" t="s">
         <v>28</v>
       </c>
-      <c r="C18" s="59" t="s">
+      <c r="C18" s="48" t="s">
         <v>158</v>
       </c>
-      <c r="D18" s="81"/>
-      <c r="E18" s="81">
-        <v>1</v>
-      </c>
-      <c r="F18" s="81">
+      <c r="D18" s="72"/>
+      <c r="E18" s="72">
+        <v>1</v>
+      </c>
+      <c r="F18" s="72">
         <v>3</v>
       </c>
-      <c r="G18" s="81"/>
-      <c r="H18" s="59" t="s">
+      <c r="G18" s="72"/>
+      <c r="H18" s="48" t="s">
         <v>159</v>
       </c>
-      <c r="I18" s="59" t="s">
+      <c r="I18" s="48" t="s">
         <v>138</v>
       </c>
-      <c r="J18" s="59">
-        <v>0</v>
-      </c>
-      <c r="K18" s="59"/>
+      <c r="J18" s="48">
+        <v>0</v>
+      </c>
+      <c r="K18" s="48"/>
     </row>
     <row r="19" spans="1:11">
-      <c r="A19" s="60" t="s">
+      <c r="A19" s="58" t="s">
         <v>160</v>
       </c>
-      <c r="B19" s="61" t="s">
+      <c r="B19" s="59" t="s">
         <v>31</v>
       </c>
-      <c r="C19" s="61" t="s">
+      <c r="C19" s="59" t="s">
         <v>161</v>
       </c>
-      <c r="D19" s="82"/>
-      <c r="E19" s="82">
-        <v>1</v>
-      </c>
-      <c r="F19" s="82">
-        <v>0</v>
-      </c>
-      <c r="G19" s="82"/>
-      <c r="H19" s="61" t="s">
+      <c r="D19" s="78"/>
+      <c r="E19" s="78">
+        <v>1</v>
+      </c>
+      <c r="F19" s="78">
+        <v>0</v>
+      </c>
+      <c r="G19" s="78"/>
+      <c r="H19" s="59" t="s">
         <v>162</v>
       </c>
-      <c r="I19" s="61" t="s">
+      <c r="I19" s="59" t="s">
         <v>138</v>
       </c>
-      <c r="J19" s="61">
-        <v>0</v>
-      </c>
-      <c r="K19" s="61"/>
+      <c r="J19" s="59">
+        <v>0</v>
+      </c>
+      <c r="K19" s="59"/>
     </row>
     <row r="20" spans="1:11">
-      <c r="A20" s="60" t="s">
+      <c r="A20" s="58" t="s">
         <v>163</v>
       </c>
-      <c r="B20" s="61" t="s">
+      <c r="B20" s="59" t="s">
         <v>31</v>
       </c>
-      <c r="C20" s="61" t="s">
+      <c r="C20" s="59" t="s">
         <v>164</v>
       </c>
-      <c r="D20" s="82"/>
-      <c r="E20" s="82">
-        <v>1</v>
-      </c>
-      <c r="F20" s="82">
-        <v>1</v>
-      </c>
-      <c r="G20" s="82"/>
-      <c r="H20" s="61" t="s">
+      <c r="D20" s="78"/>
+      <c r="E20" s="78">
+        <v>1</v>
+      </c>
+      <c r="F20" s="78">
+        <v>1</v>
+      </c>
+      <c r="G20" s="78"/>
+      <c r="H20" s="59" t="s">
         <v>165</v>
       </c>
-      <c r="I20" s="61" t="s">
+      <c r="I20" s="59" t="s">
         <v>138</v>
       </c>
-      <c r="J20" s="61">
-        <v>0</v>
-      </c>
-      <c r="K20" s="61"/>
+      <c r="J20" s="59">
+        <v>0</v>
+      </c>
+      <c r="K20" s="59"/>
     </row>
     <row r="21" spans="1:11">
-      <c r="A21" s="60" t="s">
+      <c r="A21" s="58" t="s">
         <v>166</v>
       </c>
-      <c r="B21" s="61" t="s">
+      <c r="B21" s="59" t="s">
         <v>31</v>
       </c>
-      <c r="C21" s="61" t="s">
+      <c r="C21" s="59" t="s">
         <v>167</v>
       </c>
-      <c r="D21" s="82"/>
-      <c r="E21" s="82">
-        <v>1</v>
-      </c>
-      <c r="F21" s="82">
+      <c r="D21" s="78"/>
+      <c r="E21" s="78">
+        <v>1</v>
+      </c>
+      <c r="F21" s="78">
         <v>3</v>
       </c>
-      <c r="G21" s="82"/>
-      <c r="H21" s="61" t="s">
+      <c r="G21" s="78"/>
+      <c r="H21" s="59" t="s">
         <v>168</v>
       </c>
-      <c r="I21" s="61" t="s">
+      <c r="I21" s="59" t="s">
         <v>138</v>
       </c>
-      <c r="J21" s="61">
-        <v>0</v>
-      </c>
-      <c r="K21" s="61"/>
+      <c r="J21" s="59">
+        <v>0</v>
+      </c>
+      <c r="K21" s="59"/>
     </row>
     <row r="22" spans="1:11">
-      <c r="A22" s="60" t="s">
+      <c r="A22" s="58" t="s">
         <v>169</v>
       </c>
-      <c r="B22" s="61" t="s">
+      <c r="B22" s="59" t="s">
         <v>34</v>
       </c>
-      <c r="C22" s="61" t="s">
+      <c r="C22" s="59" t="s">
         <v>170</v>
       </c>
-      <c r="D22" s="82"/>
-      <c r="E22" s="82">
-        <v>1</v>
-      </c>
-      <c r="F22" s="82">
-        <v>0</v>
-      </c>
-      <c r="G22" s="82"/>
-      <c r="H22" s="61" t="s">
+      <c r="D22" s="78"/>
+      <c r="E22" s="78">
+        <v>1</v>
+      </c>
+      <c r="F22" s="78">
+        <v>0</v>
+      </c>
+      <c r="G22" s="78"/>
+      <c r="H22" s="59" t="s">
         <v>171</v>
       </c>
-      <c r="I22" s="61" t="s">
+      <c r="I22" s="59" t="s">
         <v>138</v>
       </c>
-      <c r="J22" s="61">
-        <v>0</v>
-      </c>
-      <c r="K22" s="61"/>
+      <c r="J22" s="59">
+        <v>0</v>
+      </c>
+      <c r="K22" s="59"/>
     </row>
     <row r="23" spans="1:11">
-      <c r="A23" s="60" t="s">
+      <c r="A23" s="58" t="s">
         <v>172</v>
       </c>
-      <c r="B23" s="61" t="s">
+      <c r="B23" s="59" t="s">
         <v>34</v>
       </c>
-      <c r="C23" s="61" t="s">
+      <c r="C23" s="59" t="s">
         <v>173</v>
       </c>
-      <c r="D23" s="82"/>
-      <c r="E23" s="82">
-        <v>1</v>
-      </c>
-      <c r="F23" s="82">
-        <v>1</v>
-      </c>
-      <c r="G23" s="82"/>
-      <c r="H23" s="59" t="s">
+      <c r="D23" s="78"/>
+      <c r="E23" s="78">
+        <v>1</v>
+      </c>
+      <c r="F23" s="78">
+        <v>1</v>
+      </c>
+      <c r="G23" s="78"/>
+      <c r="H23" s="48" t="s">
         <v>159</v>
       </c>
-      <c r="I23" s="61" t="s">
+      <c r="I23" s="59" t="s">
         <v>138</v>
       </c>
-      <c r="J23" s="61">
-        <v>0</v>
-      </c>
-      <c r="K23" s="61"/>
+      <c r="J23" s="59">
+        <v>0</v>
+      </c>
+      <c r="K23" s="59"/>
     </row>
     <row r="24" s="41" customFormat="1" spans="1:11">
-      <c r="A24" s="63" t="s">
+      <c r="A24" s="61" t="s">
         <v>174</v>
       </c>
-      <c r="B24" s="62" t="s">
+      <c r="B24" s="60" t="s">
         <v>34</v>
       </c>
-      <c r="C24" s="62" t="s">
+      <c r="C24" s="60" t="s">
         <v>175</v>
       </c>
-      <c r="D24" s="83"/>
-      <c r="E24" s="83">
-        <v>1</v>
-      </c>
-      <c r="F24" s="83">
+      <c r="D24" s="79"/>
+      <c r="E24" s="79">
+        <v>1</v>
+      </c>
+      <c r="F24" s="79">
         <v>3</v>
       </c>
-      <c r="G24" s="83"/>
-      <c r="H24" s="62" t="s">
+      <c r="G24" s="79"/>
+      <c r="H24" s="60" t="s">
         <v>176</v>
       </c>
-      <c r="I24" s="62" t="s">
+      <c r="I24" s="60" t="s">
         <v>138</v>
       </c>
-      <c r="J24" s="62">
-        <v>0</v>
-      </c>
-      <c r="K24" s="62"/>
+      <c r="J24" s="60">
+        <v>0</v>
+      </c>
+      <c r="K24" s="60"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8234,7 +8211,7 @@
       <c r="G1" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="H1" s="65" t="s">
+      <c r="H1" s="63" t="s">
         <v>60</v>
       </c>
       <c r="I1" s="5" t="s">
@@ -8242,10 +8219,10 @@
       </c>
     </row>
     <row r="2" ht="148.5" spans="1:9">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="45" t="s">
+      <c r="B2" s="44" t="s">
         <v>181</v>
       </c>
       <c r="C2" s="5" t="s">
@@ -8254,19 +8231,19 @@
       <c r="D2" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="E2" s="45" t="s">
+      <c r="E2" s="44" t="s">
         <v>183</v>
       </c>
-      <c r="F2" s="45" t="s">
+      <c r="F2" s="44" t="s">
         <v>184</v>
       </c>
-      <c r="G2" s="45" t="s">
+      <c r="G2" s="44" t="s">
         <v>185</v>
       </c>
-      <c r="H2" s="65" t="s">
+      <c r="H2" s="63" t="s">
         <v>186</v>
       </c>
-      <c r="I2" s="68" t="s">
+      <c r="I2" s="66" t="s">
         <v>72</v>
       </c>
     </row>
@@ -8292,7 +8269,7 @@
       <c r="G3" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="H3" s="65" t="s">
+      <c r="H3" s="63" t="s">
         <v>74</v>
       </c>
       <c r="I3" s="5" t="s">
@@ -8313,65 +8290,65 @@
       <c r="E4" s="40"/>
       <c r="F4" s="40"/>
       <c r="G4" s="40"/>
-      <c r="H4" s="66"/>
+      <c r="H4" s="64"/>
       <c r="I4" s="40"/>
     </row>
-    <row r="5" s="64" customFormat="1" spans="1:9">
-      <c r="A5" s="67" t="s">
+    <row r="5" s="62" customFormat="1" spans="1:9">
+      <c r="A5" s="65" t="s">
         <v>190</v>
       </c>
-      <c r="B5" s="67" t="s">
+      <c r="B5" s="65" t="s">
         <v>191</v>
       </c>
-      <c r="C5" s="67" t="s">
+      <c r="C5" s="65" t="s">
         <v>192</v>
       </c>
-      <c r="D5" s="67">
-        <v>1</v>
-      </c>
-      <c r="E5" s="67"/>
-      <c r="F5" s="67"/>
-      <c r="G5" s="67"/>
+      <c r="D5" s="65">
+        <v>1</v>
+      </c>
+      <c r="E5" s="65"/>
+      <c r="F5" s="65"/>
+      <c r="G5" s="65"/>
       <c r="H5" s="40"/>
-      <c r="I5" s="67"/>
-    </row>
-    <row r="6" s="64" customFormat="1" spans="1:9">
-      <c r="A6" s="67" t="s">
+      <c r="I5" s="65"/>
+    </row>
+    <row r="6" s="62" customFormat="1" spans="1:9">
+      <c r="A6" s="65" t="s">
         <v>193</v>
       </c>
-      <c r="B6" s="67" t="s">
+      <c r="B6" s="65" t="s">
         <v>194</v>
       </c>
-      <c r="C6" s="67" t="s">
+      <c r="C6" s="65" t="s">
         <v>195</v>
       </c>
-      <c r="D6" s="67">
-        <v>1</v>
-      </c>
-      <c r="E6" s="67"/>
-      <c r="F6" s="67"/>
-      <c r="G6" s="67"/>
+      <c r="D6" s="65">
+        <v>1</v>
+      </c>
+      <c r="E6" s="65"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="65"/>
       <c r="H6" s="1"/>
-      <c r="I6" s="67"/>
-    </row>
-    <row r="7" s="64" customFormat="1" spans="1:9">
-      <c r="A7" s="67" t="s">
+      <c r="I6" s="65"/>
+    </row>
+    <row r="7" s="62" customFormat="1" spans="1:9">
+      <c r="A7" s="65" t="s">
         <v>196</v>
       </c>
-      <c r="B7" s="67" t="s">
+      <c r="B7" s="65" t="s">
         <v>197</v>
       </c>
-      <c r="C7" s="67" t="s">
+      <c r="C7" s="65" t="s">
         <v>198</v>
       </c>
-      <c r="D7" s="67">
-        <v>1</v>
-      </c>
-      <c r="E7" s="67"/>
-      <c r="F7" s="67"/>
-      <c r="G7" s="67"/>
+      <c r="D7" s="65">
+        <v>1</v>
+      </c>
+      <c r="E7" s="65"/>
+      <c r="F7" s="65"/>
+      <c r="G7" s="65"/>
       <c r="H7" s="1"/>
-      <c r="I7" s="67"/>
+      <c r="I7" s="65"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
@@ -8475,7 +8452,7 @@
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
-      <c r="H12" s="62"/>
+      <c r="H12" s="60"/>
       <c r="I12" s="1"/>
     </row>
   </sheetData>
@@ -8525,7 +8502,7 @@
       </c>
     </row>
     <row r="2" ht="81" spans="1:8">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="44" t="s">
         <v>16</v>
       </c>
       <c r="B2" s="5" t="s">
@@ -8534,16 +8511,16 @@
       <c r="C2" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="D2" s="46" t="s">
+      <c r="D2" s="45" t="s">
         <v>221</v>
       </c>
-      <c r="E2" s="45" t="s">
+      <c r="E2" s="44" t="s">
         <v>222</v>
       </c>
-      <c r="F2" s="45" t="s">
+      <c r="F2" s="44" t="s">
         <v>223</v>
       </c>
-      <c r="G2" s="45" t="s">
+      <c r="G2" s="44" t="s">
         <v>224</v>
       </c>
       <c r="H2" s="5" t="s">
@@ -8625,146 +8602,146 @@
       </c>
     </row>
     <row r="6" s="41" customFormat="1" spans="1:8">
-      <c r="A6" s="47" t="s">
+      <c r="A6" s="46" t="s">
         <v>228</v>
       </c>
-      <c r="B6" s="47"/>
-      <c r="C6" s="47" t="s">
+      <c r="B6" s="46"/>
+      <c r="C6" s="46" t="s">
         <v>87</v>
       </c>
-      <c r="D6" s="47">
-        <v>0</v>
-      </c>
-      <c r="E6" s="47">
-        <v>0</v>
-      </c>
-      <c r="F6" s="47">
-        <v>1</v>
-      </c>
-      <c r="G6" s="47">
+      <c r="D6" s="46">
+        <v>0</v>
+      </c>
+      <c r="E6" s="46">
+        <v>0</v>
+      </c>
+      <c r="F6" s="46">
+        <v>1</v>
+      </c>
+      <c r="G6" s="46">
         <v>8</v>
       </c>
-      <c r="H6" s="47" t="s">
+      <c r="H6" s="46" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="7" s="41" customFormat="1" spans="1:8">
-      <c r="A7" s="47" t="s">
+      <c r="A7" s="46" t="s">
         <v>230</v>
       </c>
-      <c r="B7" s="47"/>
-      <c r="C7" s="47" t="s">
+      <c r="B7" s="46"/>
+      <c r="C7" s="46" t="s">
         <v>231</v>
       </c>
-      <c r="D7" s="47">
-        <v>0</v>
-      </c>
-      <c r="E7" s="47">
-        <v>0</v>
-      </c>
-      <c r="F7" s="47">
+      <c r="D7" s="46">
+        <v>0</v>
+      </c>
+      <c r="E7" s="46">
+        <v>0</v>
+      </c>
+      <c r="F7" s="46">
         <v>3</v>
       </c>
-      <c r="G7" s="47" t="s">
+      <c r="G7" s="46" t="s">
         <v>232</v>
       </c>
-      <c r="H7" s="47" t="s">
+      <c r="H7" s="46" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="48" t="s">
+      <c r="A8" s="47" t="s">
         <v>139</v>
       </c>
-      <c r="B8" s="49"/>
-      <c r="C8" s="48" t="s">
+      <c r="B8" s="48"/>
+      <c r="C8" s="47" t="s">
         <v>109</v>
       </c>
-      <c r="D8" s="49">
-        <v>0</v>
-      </c>
-      <c r="E8" s="49">
-        <v>0</v>
-      </c>
-      <c r="F8" s="49">
-        <v>1</v>
-      </c>
-      <c r="G8" s="48">
+      <c r="D8" s="48">
+        <v>0</v>
+      </c>
+      <c r="E8" s="48">
+        <v>0</v>
+      </c>
+      <c r="F8" s="48">
+        <v>1</v>
+      </c>
+      <c r="G8" s="47">
         <v>5</v>
       </c>
-      <c r="H8" s="49" t="s">
+      <c r="H8" s="48" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="50" t="s">
+      <c r="A9" s="49" t="s">
         <v>141</v>
       </c>
-      <c r="B9" s="51"/>
-      <c r="C9" s="51" t="s">
+      <c r="B9" s="50"/>
+      <c r="C9" s="50" t="s">
         <v>235</v>
       </c>
-      <c r="D9" s="49">
-        <v>1</v>
-      </c>
-      <c r="E9" s="49">
-        <v>0</v>
-      </c>
-      <c r="F9" s="49">
+      <c r="D9" s="48">
+        <v>1</v>
+      </c>
+      <c r="E9" s="48">
+        <v>0</v>
+      </c>
+      <c r="F9" s="48">
         <v>2</v>
       </c>
-      <c r="G9" s="49">
+      <c r="G9" s="48">
         <v>5</v>
       </c>
-      <c r="H9" s="51" t="s">
+      <c r="H9" s="50" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="10" s="42" customFormat="1" spans="1:8">
-      <c r="A10" s="52" t="s">
+      <c r="A10" s="51" t="s">
         <v>145</v>
       </c>
-      <c r="B10" s="53"/>
-      <c r="C10" s="52" t="s">
+      <c r="B10" s="52"/>
+      <c r="C10" s="51" t="s">
         <v>109</v>
       </c>
-      <c r="D10" s="53">
-        <v>0</v>
-      </c>
-      <c r="E10" s="53">
-        <v>0</v>
-      </c>
-      <c r="F10" s="53">
-        <v>1</v>
-      </c>
-      <c r="G10" s="52">
+      <c r="D10" s="52">
+        <v>0</v>
+      </c>
+      <c r="E10" s="52">
+        <v>0</v>
+      </c>
+      <c r="F10" s="52">
+        <v>1</v>
+      </c>
+      <c r="G10" s="51">
         <v>8</v>
       </c>
-      <c r="H10" s="53" t="s">
+      <c r="H10" s="52" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="11" s="43" customFormat="1" spans="1:8">
-      <c r="A11" s="54" t="s">
+    <row r="11" s="42" customFormat="1" spans="1:8">
+      <c r="A11" s="53" t="s">
         <v>147</v>
       </c>
-      <c r="B11" s="53"/>
-      <c r="C11" s="53" t="s">
+      <c r="B11" s="52"/>
+      <c r="C11" s="52" t="s">
         <v>237</v>
       </c>
-      <c r="D11" s="53">
-        <v>0</v>
-      </c>
-      <c r="E11" s="53">
-        <v>0</v>
-      </c>
-      <c r="F11" s="53">
+      <c r="D11" s="52">
+        <v>0</v>
+      </c>
+      <c r="E11" s="52">
+        <v>0</v>
+      </c>
+      <c r="F11" s="52">
         <v>3</v>
       </c>
-      <c r="G11" s="55" t="s">
+      <c r="G11" s="54" t="s">
         <v>232</v>
       </c>
-      <c r="H11" s="53" t="s">
+      <c r="H11" s="52" t="s">
         <v>238</v>
       </c>
     </row>
@@ -8986,60 +8963,60 @@
         <v>268</v>
       </c>
     </row>
-    <row r="21" s="44" customFormat="1" spans="1:9">
-      <c r="A21" s="56" t="s">
+    <row r="21" s="43" customFormat="1" spans="1:9">
+      <c r="A21" s="55" t="s">
         <v>269</v>
       </c>
-      <c r="B21" s="57" t="s">
+      <c r="B21" s="56" t="s">
         <v>270</v>
       </c>
-      <c r="C21" s="57" t="s">
+      <c r="C21" s="56" t="s">
         <v>270</v>
       </c>
-      <c r="D21" s="57">
-        <v>0</v>
-      </c>
-      <c r="E21" s="57"/>
-      <c r="F21" s="57"/>
-      <c r="G21" s="57"/>
-      <c r="H21" s="57" t="s">
+      <c r="D21" s="56">
+        <v>0</v>
+      </c>
+      <c r="E21" s="56"/>
+      <c r="F21" s="56"/>
+      <c r="G21" s="56"/>
+      <c r="H21" s="56" t="s">
         <v>271</v>
       </c>
-      <c r="I21" s="44" t="s">
+      <c r="I21" s="43" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="22" s="44" customFormat="1" spans="1:9">
-      <c r="A22" s="56" t="s">
+    <row r="22" s="43" customFormat="1" spans="1:9">
+      <c r="A22" s="55" t="s">
         <v>273</v>
       </c>
-      <c r="B22" s="57" t="s">
+      <c r="B22" s="56" t="s">
         <v>274</v>
       </c>
-      <c r="C22" s="57" t="s">
+      <c r="C22" s="56" t="s">
         <v>274</v>
       </c>
-      <c r="D22" s="57">
-        <v>0</v>
-      </c>
-      <c r="E22" s="57"/>
-      <c r="F22" s="57"/>
-      <c r="G22" s="57"/>
-      <c r="H22" s="57" t="s">
+      <c r="D22" s="56">
+        <v>0</v>
+      </c>
+      <c r="E22" s="56"/>
+      <c r="F22" s="56"/>
+      <c r="G22" s="56"/>
+      <c r="H22" s="56" t="s">
         <v>275</v>
       </c>
-      <c r="I22" s="44" t="s">
+      <c r="I22" s="43" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="58" t="s">
+      <c r="A23" s="57" t="s">
         <v>151</v>
       </c>
-      <c r="B23" s="59" t="s">
+      <c r="B23" s="48" t="s">
         <v>152</v>
       </c>
-      <c r="C23" s="59" t="s">
+      <c r="C23" s="48" t="s">
         <v>152</v>
       </c>
       <c r="D23" s="1">
@@ -9048,7 +9025,7 @@
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
-      <c r="H23" s="59" t="s">
+      <c r="H23" s="48" t="s">
         <v>277</v>
       </c>
       <c r="I23" t="s">
@@ -9056,13 +9033,13 @@
       </c>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="58" t="s">
+      <c r="A24" s="57" t="s">
         <v>154</v>
       </c>
-      <c r="B24" s="59" t="s">
+      <c r="B24" s="48" t="s">
         <v>155</v>
       </c>
-      <c r="C24" s="59" t="s">
+      <c r="C24" s="48" t="s">
         <v>155</v>
       </c>
       <c r="D24" s="1">
@@ -9079,13 +9056,13 @@
       </c>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="58" t="s">
+      <c r="A25" s="57" t="s">
         <v>157</v>
       </c>
-      <c r="B25" s="59" t="s">
+      <c r="B25" s="48" t="s">
         <v>158</v>
       </c>
-      <c r="C25" s="59" t="s">
+      <c r="C25" s="48" t="s">
         <v>158</v>
       </c>
       <c r="D25" s="1">
@@ -9094,7 +9071,7 @@
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
-      <c r="H25" s="59" t="s">
+      <c r="H25" s="48" t="s">
         <v>159</v>
       </c>
       <c r="I25" t="s">
@@ -9102,13 +9079,13 @@
       </c>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" s="60" t="s">
+      <c r="A26" s="58" t="s">
         <v>160</v>
       </c>
-      <c r="B26" s="61" t="s">
+      <c r="B26" s="59" t="s">
         <v>161</v>
       </c>
-      <c r="C26" s="61" t="s">
+      <c r="C26" s="59" t="s">
         <v>161</v>
       </c>
       <c r="D26" s="1">
@@ -9117,7 +9094,7 @@
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
-      <c r="H26" s="61" t="s">
+      <c r="H26" s="59" t="s">
         <v>280</v>
       </c>
       <c r="I26" t="s">
@@ -9125,13 +9102,13 @@
       </c>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="60" t="s">
+      <c r="A27" s="58" t="s">
         <v>163</v>
       </c>
-      <c r="B27" s="61" t="s">
+      <c r="B27" s="59" t="s">
         <v>164</v>
       </c>
-      <c r="C27" s="61" t="s">
+      <c r="C27" s="59" t="s">
         <v>164</v>
       </c>
       <c r="D27" s="1">
@@ -9140,7 +9117,7 @@
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
-      <c r="H27" s="61" t="s">
+      <c r="H27" s="59" t="s">
         <v>281</v>
       </c>
       <c r="I27" t="s">
@@ -9148,13 +9125,13 @@
       </c>
     </row>
     <row r="28" spans="1:8">
-      <c r="A28" s="60" t="s">
+      <c r="A28" s="58" t="s">
         <v>166</v>
       </c>
-      <c r="B28" s="61" t="s">
+      <c r="B28" s="59" t="s">
         <v>167</v>
       </c>
-      <c r="C28" s="61" t="s">
+      <c r="C28" s="59" t="s">
         <v>167</v>
       </c>
       <c r="D28" s="1">
@@ -9163,18 +9140,18 @@
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
-      <c r="H28" s="62" t="s">
+      <c r="H28" s="60" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="29" spans="1:9">
-      <c r="A29" s="60" t="s">
+      <c r="A29" s="58" t="s">
         <v>169</v>
       </c>
-      <c r="B29" s="61" t="s">
+      <c r="B29" s="59" t="s">
         <v>170</v>
       </c>
-      <c r="C29" s="61" t="s">
+      <c r="C29" s="59" t="s">
         <v>170</v>
       </c>
       <c r="D29" s="1">
@@ -9183,7 +9160,7 @@
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
-      <c r="H29" s="61" t="s">
+      <c r="H29" s="59" t="s">
         <v>283</v>
       </c>
       <c r="I29" t="s">
@@ -9191,13 +9168,13 @@
       </c>
     </row>
     <row r="30" spans="1:9">
-      <c r="A30" s="60" t="s">
+      <c r="A30" s="58" t="s">
         <v>172</v>
       </c>
-      <c r="B30" s="61" t="s">
+      <c r="B30" s="59" t="s">
         <v>173</v>
       </c>
-      <c r="C30" s="61" t="s">
+      <c r="C30" s="59" t="s">
         <v>173</v>
       </c>
       <c r="D30" s="1">
@@ -9206,7 +9183,7 @@
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
-      <c r="H30" s="59" t="s">
+      <c r="H30" s="48" t="s">
         <v>159</v>
       </c>
       <c r="I30" t="s">
@@ -9214,13 +9191,13 @@
       </c>
     </row>
     <row r="31" spans="1:8">
-      <c r="A31" s="63" t="s">
+      <c r="A31" s="61" t="s">
         <v>174</v>
       </c>
-      <c r="B31" s="62" t="s">
+      <c r="B31" s="60" t="s">
         <v>175</v>
       </c>
-      <c r="C31" s="62" t="s">
+      <c r="C31" s="60" t="s">
         <v>175</v>
       </c>
       <c r="D31" s="1">
@@ -9229,7 +9206,7 @@
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
-      <c r="H31" s="62" t="s">
+      <c r="H31" s="60" t="s">
         <v>176</v>
       </c>
     </row>

--- a/xlsdir/配置-总表.xlsx
+++ b/xlsdir/配置-总表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="673"/>
+    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="673" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="combat|战斗" sheetId="31" r:id="rId1"/>
@@ -6584,6 +6584,9 @@
   <sheetPr/>
   <dimension ref="A7:I66"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <cols>
+    <col min="13" max="13" width="9.375"/>
+  </cols>
   <sheetData>
     <row r="7" spans="3:5">
       <c r="C7" s="1" t="s">

--- a/xlsdir/配置-总表.xlsx
+++ b/xlsdir/配置-总表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="673" activeTab="4"/>
+    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="673" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="combat|战斗" sheetId="31" r:id="rId1"/>
@@ -8471,8 +8471,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="22.625" customWidth="1"/>
-    <col min="3" max="3" width="9.125" customWidth="1"/>
-    <col min="4" max="4" width="14.125" customWidth="1"/>
+    <col min="3" max="4" width="14.125" customWidth="1"/>
     <col min="6" max="6" width="14.125" customWidth="1"/>
     <col min="7" max="7" width="14.375" customWidth="1"/>
     <col min="8" max="8" width="71.2" customWidth="1"/>
